--- a/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
+++ b/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
@@ -1390,7 +1390,7 @@
         <v/>
       </c>
       <c r="D5" s="118">
-        <f>'Факт расходов'!F38</f>
+        <f>'Факт расходов'!F46</f>
         <v/>
       </c>
       <c r="E5" s="118" t="n">
@@ -1489,7 +1489,7 @@
         <v>23000</v>
       </c>
       <c r="C11" s="46">
-        <f>SUMIF('Факт расходов'!C5:C37, "*Юр.*", 'Факт расходов'!F5:F37)+SUMIF('Факт расходов'!C5:C37, "*Безопасность*", 'Факт расходов'!F5:F37)+SUMIF('Факт расходов'!C5:C37, "*IT*", 'Факт расходов'!F5:F37)+SUMIF('Факт расходов'!C5:C37, "*Электроэнергия*", 'Факт расходов'!F5:F37)</f>
+        <f>SUMIF('Факт расходов'!C5:C45, "*Юр.*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*Безопасность*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*IT*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*Электроэнергия*", 'Факт расходов'!F5:F45)</f>
         <v/>
       </c>
       <c r="D11" s="124">
@@ -1775,7 +1775,7 @@
         <v/>
       </c>
       <c r="C23" s="46">
-        <f>SUMIF('Факт расходов'!C5:C37, "*Демонтаж*", 'Факт расходов'!F5:F37)</f>
+        <f>SUMIF('Факт расходов'!C5:C45, "*Демонтаж*", 'Факт расходов'!F5:F45)</f>
         <v/>
       </c>
       <c r="D23" s="45">
@@ -1808,7 +1808,7 @@
         <v/>
       </c>
       <c r="C24" s="51">
-        <f>SUMIF('Факт расходов'!C5:C37, "*Двери*", 'Факт расходов'!F5:F37)</f>
+        <f>SUMIF('Факт расходов'!C5:C45, "*Двери*", 'Факт расходов'!F5:F45)</f>
         <v/>
       </c>
       <c r="D24" s="50">
@@ -1841,7 +1841,7 @@
         <v/>
       </c>
       <c r="C25" s="46">
-        <f>SUMIF('Факт расходов'!C5:C37, "*Электрика*", 'Факт расходов'!F5:F37)</f>
+        <f>SUMIF('Факт расходов'!C5:C45, "*Электрика*", 'Факт расходов'!F5:F45)</f>
         <v/>
       </c>
       <c r="D25" s="45">
@@ -1874,7 +1874,7 @@
         <v/>
       </c>
       <c r="C26" s="51">
-        <f>SUMIF('Факт расходов'!C5:C37, "*Сантехника*", 'Факт расходов'!F5:F37)</f>
+        <f>SUMIF('Факт расходов'!C5:C45, "*Сантехника*", 'Факт расходов'!F5:F45)</f>
         <v/>
       </c>
       <c r="D26" s="50">
@@ -1906,7 +1906,7 @@
         <v>5000</v>
       </c>
       <c r="C27" s="46">
-        <f>SUMIF('Факт расходов'!C5:C37, "*Газ*", 'Факт расходов'!F5:F37)</f>
+        <f>SUMIF('Факт расходов'!C5:C45, "*Газ*", 'Факт расходов'!F5:F45)</f>
         <v/>
       </c>
       <c r="D27" s="45">
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="C29" s="46">
-        <f>SUMIF('Факт расходов'!C5:C37, "*Черновая*", 'Факт расходов'!F5:F37)</f>
+        <f>SUMIF('Факт расходов'!C5:C45, "*Черновая*", 'Факт расходов'!F5:F45)</f>
         <v/>
       </c>
       <c r="D29" s="45">
@@ -2003,8 +2003,9 @@
         <f>'План vs Рынок (Смета)'!E11</f>
         <v/>
       </c>
-      <c r="C30" s="51" t="n">
-        <v>0</v>
+      <c r="C30" s="51">
+        <f>SUMIF('Факт расходов'!C5:C45, "*Чистовая*", 'Факт расходов'!F5:F45)</f>
+        <v/>
       </c>
       <c r="D30" s="50">
         <f>B30-C30</f>
@@ -2163,7 +2164,7 @@
         <v>10000</v>
       </c>
       <c r="C35" s="46">
-        <f>SUMIF('Факт расходов'!C5:C37, "*Инструмент*", 'Факт расходов'!F5:F37)+SUMIF('Факт расходов'!C5:C37, "*Расходные*", 'Факт расходов'!F5:F37)</f>
+        <f>SUMIF('Факт расходов'!C5:C45, "*Инструмент*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*Расходные*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*Логистика*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*доставка*", 'Факт расходов'!F5:F45)</f>
         <v/>
       </c>
       <c r="D35" s="45">
@@ -2195,7 +2196,7 @@
         <v>5000</v>
       </c>
       <c r="C36" s="51">
-        <f>SUMIF('Факт расходов'!C5:C37, "*хозмаг*", 'Факт расходов'!F5:F37)+SUMIF('Факт расходов'!C5:C37, "*Хоз.*", 'Факт расходов'!F5:F37)+SUMIF('Факт расходов'!C5:C37, "*Оснащение*", 'Факт расходов'!F5:F37)</f>
+        <f>SUMIF('Факт расходов'!C5:C45, "*хозмаг*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*Хоз.*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*Оснащение*", 'Факт расходов'!F5:F45)</f>
         <v/>
       </c>
       <c r="D36" s="50">
@@ -2383,11 +2384,11 @@
         </is>
       </c>
       <c r="B45" s="45">
-        <f>'Факт расходов'!E38</f>
+        <f>'Факт расходов'!E46</f>
         <v/>
       </c>
       <c r="C45" s="45">
-        <f>'Факт расходов'!F38</f>
+        <f>'Факт расходов'!F46</f>
         <v/>
       </c>
       <c r="D45" s="124">
@@ -2470,7 +2471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4188,197 +4189,437 @@
       <c r="M37" s="30" t="n"/>
       <c r="N37" s="30" t="n"/>
     </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="94" t="n"/>
-      <c r="B38" s="94" t="n"/>
-      <c r="C38" s="54" t="n"/>
-      <c r="D38" s="65" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДОВ:</t>
-        </is>
-      </c>
-      <c r="E38" s="55">
-        <f>SUM(E5:E37)</f>
-        <v/>
-      </c>
-      <c r="F38" s="55">
-        <f>SUM(F5:F37)</f>
-        <v/>
-      </c>
-      <c r="G38" s="55">
-        <f>SUM(G5:G37)</f>
-        <v/>
-      </c>
-      <c r="H38" s="104">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="64" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="64" t="inlineStr">
+        <is>
+          <t>13.09.2026</t>
+        </is>
+      </c>
+      <c r="C38" s="49" t="inlineStr">
+        <is>
+          <t>Сантехника / Санфаянс</t>
+        </is>
+      </c>
+      <c r="D38" s="49" t="inlineStr">
+        <is>
+          <t>Сантехника и санфаянс для санузла (ванна Неоре 150х70 акрил, каркас Sensea, унитаз Sanita Master, раковина Cersanit 60см, смесители 2шт, душ Konsensa, сифон)</t>
+        </is>
+      </c>
+      <c r="E38" s="50" t="n">
+        <v>33621</v>
+      </c>
+      <c r="F38" s="51" t="n">
+        <v>30021</v>
+      </c>
+      <c r="G38" s="47">
+        <f>E38-F38</f>
+        <v/>
+      </c>
+      <c r="H38" s="63">
         <f>IFERROR(G38/E38, 0)</f>
         <v/>
       </c>
-      <c r="I38" s="54" t="n"/>
-      <c r="J38" s="54" t="n"/>
-      <c r="K38" s="30" t="n"/>
-      <c r="L38" s="30" t="n"/>
-      <c r="M38" s="30" t="n"/>
-      <c r="N38" s="30" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="30" t="n"/>
-      <c r="B39" s="30" t="n"/>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="30" t="n"/>
-      <c r="F39" s="30" t="n"/>
-      <c r="G39" s="30" t="n"/>
-      <c r="H39" s="30" t="n"/>
-      <c r="I39" s="30" t="n"/>
-      <c r="J39" s="30" t="n"/>
-      <c r="K39" s="30" t="n"/>
-      <c r="L39" s="30" t="n"/>
-      <c r="M39" s="30" t="n"/>
-      <c r="N39" s="30" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="30" t="n"/>
-      <c r="B40" s="30" t="n"/>
-      <c r="C40" s="30" t="n"/>
-      <c r="D40" s="30" t="n"/>
-      <c r="E40" s="30" t="n"/>
-      <c r="F40" s="30" t="n"/>
-      <c r="G40" s="30" t="n"/>
-      <c r="H40" s="30" t="n"/>
-      <c r="I40" s="30" t="n"/>
-      <c r="J40" s="30" t="n"/>
-      <c r="K40" s="30" t="n"/>
-      <c r="L40" s="30" t="n"/>
-      <c r="M40" s="30" t="n"/>
-      <c r="N40" s="30" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="30" t="n"/>
-      <c r="B41" s="30" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="30" t="n"/>
-      <c r="E41" s="30" t="n"/>
-      <c r="F41" s="30" t="n"/>
-      <c r="G41" s="30" t="n"/>
-      <c r="H41" s="30" t="n"/>
-      <c r="I41" s="30" t="n"/>
-      <c r="J41" s="30" t="n"/>
-      <c r="K41" s="30" t="n"/>
-      <c r="L41" s="30" t="n"/>
-      <c r="M41" s="30" t="n"/>
-      <c r="N41" s="30" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="30" t="n"/>
-      <c r="B42" s="30" t="n"/>
-      <c r="C42" s="30" t="n"/>
-      <c r="D42" s="30" t="n"/>
-      <c r="E42" s="30" t="n"/>
-      <c r="F42" s="30" t="n"/>
-      <c r="G42" s="30" t="n"/>
-      <c r="H42" s="30" t="n"/>
-      <c r="I42" s="30" t="n"/>
-      <c r="J42" s="30" t="n"/>
+      <c r="I38" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J38" s="49" t="inlineStr">
+        <is>
+          <t>Чек от 13.09.2026 15:31 (заказ 774): Ванна Неоре 150х70 (9141₽), каркас Sensea (3252₽), унитаз Sanita Master (5580₽), раковина Cersanit 60см (5470₽), смеситель для ванны Aqua-Rivus (2978₽), смеситель для раковины (1894₽), душ Konsensa (1269₽), сифон Equation (437₽). Фронтальная панель 150см (2847₽) возвращена из-за брака (чек возврата №47 от 13.09.2026 17:41). Общая скидка по заказу -3600₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="62" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="62" t="inlineStr">
+        <is>
+          <t>13.09.2026</t>
+        </is>
+      </c>
+      <c r="C39" s="44" t="inlineStr">
+        <is>
+          <t>Чистовая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D39" s="44" t="inlineStr">
+        <is>
+          <t>Керамогранит и затирка для санузла (керамогранит Calacatta superwhite 60х120 14 упак./20.16 м² + водоотталкивающая затирка Ceresit CE 40 2кг 2шт)</t>
+        </is>
+      </c>
+      <c r="E39" s="45" t="n">
+        <v>37174</v>
+      </c>
+      <c r="F39" s="46" t="n">
+        <v>33457</v>
+      </c>
+      <c r="G39" s="47">
+        <f>E39-F39</f>
+        <v/>
+      </c>
+      <c r="H39" s="63">
+        <f>IFERROR(G39/E39, 0)</f>
+        <v/>
+      </c>
+      <c r="I39" s="44" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J39" s="44" t="inlineStr">
+        <is>
+          <t>Чек от 13.09.2026 15:31 (заказ 774): Керамогранит Calacatta superwhite 60х120 14 упак. по 1.44м²=20.16м² (32193₽, скидка -3577₽), затирка Ceresit CE 40 2кг (2 шт. × 632₽ = 1264₽, скидка -140₽). Общая скидка по промокоду -3717₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="64" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="64" t="inlineStr">
+        <is>
+          <t>13.09.2026</t>
+        </is>
+      </c>
+      <c r="C40" s="49" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D40" s="49" t="inlineStr">
+        <is>
+          <t>Плиточный клей Unis 2000 C1T 25 кг для укладки плитки и керамогранита (13 мешков)</t>
+        </is>
+      </c>
+      <c r="E40" s="50" t="n">
+        <v>5525</v>
+      </c>
+      <c r="F40" s="51" t="n">
+        <v>4973</v>
+      </c>
+      <c r="G40" s="47">
+        <f>E40-F40</f>
+        <v/>
+      </c>
+      <c r="H40" s="63">
+        <f>IFERROR(G40/E40, 0)</f>
+        <v/>
+      </c>
+      <c r="I40" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J40" s="49" t="inlineStr">
+        <is>
+          <t>Чек от 13.09.2026 15:31 (заказ 774): Клей для плитки Unis 2000 C1T 25 кг (13 мешков по 382.54₽ = 4973₽). Базовая цена 5525₽, скидка по промокоду -552₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="62" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="62" t="inlineStr">
+        <is>
+          <t>13.09.2026</t>
+        </is>
+      </c>
+      <c r="C41" s="44" t="inlineStr">
+        <is>
+          <t>Инструмент и расходники</t>
+        </is>
+      </c>
+      <c r="D41" s="44" t="inlineStr">
+        <is>
+          <t>Система выравнивания плитки СВП DILWIS (зажимы 1 мм 200 шт, клинья 100 шт)</t>
+        </is>
+      </c>
+      <c r="E41" s="45" t="n">
+        <v>947</v>
+      </c>
+      <c r="F41" s="46" t="n">
+        <v>853</v>
+      </c>
+      <c r="G41" s="47">
+        <f>E41-F41</f>
+        <v/>
+      </c>
+      <c r="H41" s="63">
+        <f>IFERROR(G41/E41, 0)</f>
+        <v/>
+      </c>
+      <c r="I41" s="44" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J41" s="44" t="inlineStr">
+        <is>
+          <t>Чек от 13.09.2026 15:31 (заказ 774): Зажимы DILWIS 1мм 100шт (2 упак. × 291₽ = 582₽, скидка -64₽), клинья DILWIS 100шт (1 упак. 271₽, скидка -30₽). Общая скидка -94₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="64" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="64" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="C42" s="49" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D42" s="49" t="inlineStr">
+        <is>
+          <t>Материалы для штукатурки и шпаклёвки (шпатлевка Старатели финиш 20кг, штукатурка Старатели 30кг 2шт, перчатки) — повторная закупка</t>
+        </is>
+      </c>
+      <c r="E42" s="50" t="n">
+        <v>1594</v>
+      </c>
+      <c r="F42" s="51" t="n">
+        <v>1594</v>
+      </c>
+      <c r="G42" s="47">
+        <f>E42-F42</f>
+        <v/>
+      </c>
+      <c r="H42" s="63">
+        <f>IFERROR(G42/E42, 0)</f>
+        <v/>
+      </c>
+      <c r="I42" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J42" s="49" t="inlineStr">
+        <is>
+          <t>Повторная закупка тех же материалов от 08.09.2026 (шпатлевка Старатели финиш 20кг 530₽, штукатурка 30кг 2шт по 505₽=1010₽, перчатки 54₽). Чек не сохранён</t>
+        </is>
+      </c>
       <c r="K42" s="30" t="n"/>
       <c r="L42" s="30" t="n"/>
       <c r="M42" s="30" t="n"/>
       <c r="N42" s="30" t="n"/>
     </row>
-    <row r="43">
-      <c r="A43" s="30" t="n"/>
-      <c r="B43" s="30" t="n"/>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="30" t="n"/>
-      <c r="E43" s="30" t="n"/>
-      <c r="F43" s="30" t="n"/>
-      <c r="G43" s="30" t="n"/>
-      <c r="H43" s="30" t="n"/>
-      <c r="I43" s="30" t="n"/>
-      <c r="J43" s="30" t="n"/>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="62" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="62" t="inlineStr">
+        <is>
+          <t>13.09.2026</t>
+        </is>
+      </c>
+      <c r="C43" s="44" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D43" s="44" t="inlineStr">
+        <is>
+          <t>Материалы для стяжки пола и короба с/у (пескобетон М-300 6 шт., профиль Knauf 50х40, ГСП влагост. Knauf 2 шт., фибра 150г, саморезы, мешки, стамеска)</t>
+        </is>
+      </c>
+      <c r="E43" s="45" t="n">
+        <v>3182.67</v>
+      </c>
+      <c r="F43" s="46" t="n">
+        <v>3182.67</v>
+      </c>
+      <c r="G43" s="47">
+        <f>E43-F43</f>
+        <v/>
+      </c>
+      <c r="H43" s="63">
+        <f>IFERROR(G43/E43, 0)</f>
+        <v/>
+      </c>
+      <c r="I43" s="44" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J43" s="44" t="inlineStr">
+        <is>
+          <t>Чек №201 от 13.09.2026 15:36 (касса 71): пескобетон М300 30кг (6 шт. × 260₽ = 1560₽), профиль 50х40х3м (375₽), ГСП влагост. 1500х600х12.5 (2 шт. × 230₽ = 460₽), фибра 150г (194₽), саморезы (21.67₽), мешки 10шт (196₽), стамеска Dexter 14мм (376₽)</t>
+        </is>
+      </c>
       <c r="K43" s="30" t="n"/>
       <c r="L43" s="30" t="n"/>
       <c r="M43" s="30" t="n"/>
       <c r="N43" s="30" t="n"/>
     </row>
-    <row r="44">
-      <c r="A44" s="30" t="n"/>
-      <c r="B44" s="30" t="n"/>
-      <c r="C44" s="30" t="n"/>
-      <c r="D44" s="30" t="n"/>
-      <c r="E44" s="30" t="n"/>
-      <c r="F44" s="30" t="n"/>
-      <c r="G44" s="30" t="n"/>
-      <c r="H44" s="30" t="n"/>
-      <c r="I44" s="30" t="n"/>
-      <c r="J44" s="30" t="n"/>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="64" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="64" t="inlineStr">
+        <is>
+          <t>13.09.2026</t>
+        </is>
+      </c>
+      <c r="C44" s="49" t="inlineStr">
+        <is>
+          <t>Логистика и доставка</t>
+        </is>
+      </c>
+      <c r="D44" s="49" t="inlineStr">
+        <is>
+          <t>Грузовое такси / Доставка закупки материалов и сантехники (Лемана ПРО — ул. Фрунзе 17)</t>
+        </is>
+      </c>
+      <c r="E44" s="50" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F44" s="51" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G44" s="47">
+        <f>E44-F44</f>
+        <v/>
+      </c>
+      <c r="H44" s="63">
+        <f>IFERROR(G44/E44, 0)</f>
+        <v/>
+      </c>
+      <c r="I44" s="49" t="inlineStr">
+        <is>
+          <t>Грузовое такси / Перевозка</t>
+        </is>
+      </c>
+      <c r="J44" s="49" t="inlineStr">
+        <is>
+          <t>Перевозка партии материалов и сантехники от 13.09.2026 (заказ 774 + черновая закупка) из гипермаркета Лемана ПРО на объект ул. Фрунзе 17 (выгода 400 ₽)</t>
+        </is>
+      </c>
       <c r="K44" s="30" t="n"/>
       <c r="L44" s="30" t="n"/>
       <c r="M44" s="30" t="n"/>
       <c r="N44" s="30" t="n"/>
     </row>
-    <row r="45">
-      <c r="A45" s="140" t="n"/>
-      <c r="B45" s="140" t="n"/>
-      <c r="C45" s="140" t="n"/>
-      <c r="D45" s="140" t="n"/>
-      <c r="E45" s="140" t="n"/>
-      <c r="F45" s="140" t="n"/>
-      <c r="G45" s="140" t="n"/>
-      <c r="H45" s="140" t="n"/>
-      <c r="I45" s="140" t="n"/>
-      <c r="J45" s="140" t="n"/>
-      <c r="K45" s="140" t="n"/>
-      <c r="L45" s="140" t="n"/>
-      <c r="M45" s="140" t="n"/>
-      <c r="N45" s="140" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="140" t="n"/>
-      <c r="B46" s="140" t="n"/>
-      <c r="C46" s="140" t="n"/>
-      <c r="D46" s="140" t="n"/>
-      <c r="E46" s="140" t="n"/>
-      <c r="F46" s="140" t="n"/>
-      <c r="G46" s="140" t="n"/>
-      <c r="H46" s="140" t="n"/>
-      <c r="I46" s="140" t="n"/>
-      <c r="J46" s="140" t="n"/>
-      <c r="K46" s="140" t="n"/>
-      <c r="L46" s="140" t="n"/>
-      <c r="M46" s="140" t="n"/>
-      <c r="N46" s="140" t="n"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="62" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="62" t="inlineStr">
+        <is>
+          <t>13.09.2026</t>
+        </is>
+      </c>
+      <c r="C45" s="44" t="inlineStr">
+        <is>
+          <t>Демонтаж и зачистка</t>
+        </is>
+      </c>
+      <c r="D45" s="44" t="inlineStr">
+        <is>
+          <t>Погрузка в Лемана ПРО, разгрузка и подъём на 5 этаж + демонтаж старой плитки пола санузла и вынос мусора</t>
+        </is>
+      </c>
+      <c r="E45" s="45" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F45" s="46" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G45" s="47">
+        <f>E45-F45</f>
+        <v/>
+      </c>
+      <c r="H45" s="63">
+        <f>IFERROR(G45/E45, 0)</f>
+        <v/>
+      </c>
+      <c r="I45" s="44" t="inlineStr">
+        <is>
+          <t>Бригада грузчиков / Разнорабочие</t>
+        </is>
+      </c>
+      <c r="J45" s="44" t="inlineStr">
+        <is>
+          <t>Комплекс работ: погрузка всей закупки в Лемана ПРО (~850 кг), разгрузка и ручной подъём на 5 этаж без лифта, сбитие всей старой напольной плитки в санузле и вынос мусора (рынок ~18к, экономия 3 000 ₽)</t>
+        </is>
+      </c>
+      <c r="K45" s="30" t="n"/>
+      <c r="L45" s="30" t="n"/>
+      <c r="M45" s="30" t="n"/>
+      <c r="N45" s="30" t="n"/>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="94" t="n"/>
+      <c r="B46" s="94" t="n"/>
+      <c r="C46" s="54" t="n"/>
+      <c r="D46" s="65" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДОВ:</t>
+        </is>
+      </c>
+      <c r="E46" s="55">
+        <f>SUM(E5:E45)</f>
+        <v/>
+      </c>
+      <c r="F46" s="55">
+        <f>SUM(F5:F45)</f>
+        <v/>
+      </c>
+      <c r="G46" s="55">
+        <f>SUM(G5:G45)</f>
+        <v/>
+      </c>
+      <c r="H46" s="104">
+        <f>IFERROR(G46/E46, 0)</f>
+        <v/>
+      </c>
+      <c r="I46" s="54" t="n"/>
+      <c r="J46" s="54" t="n"/>
+      <c r="K46" s="30" t="n"/>
+      <c r="L46" s="30" t="n"/>
+      <c r="M46" s="30" t="n"/>
+      <c r="N46" s="30" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="140" t="n"/>
-      <c r="B47" s="140" t="n"/>
-      <c r="C47" s="140" t="n"/>
-      <c r="D47" s="140" t="n"/>
-      <c r="E47" s="140" t="n"/>
-      <c r="F47" s="140" t="n"/>
-      <c r="G47" s="140" t="n"/>
-      <c r="H47" s="140" t="n"/>
-      <c r="I47" s="140" t="n"/>
-      <c r="J47" s="140" t="n"/>
-      <c r="K47" s="140" t="n"/>
-      <c r="L47" s="140" t="n"/>
-      <c r="M47" s="140" t="n"/>
-      <c r="N47" s="140" t="n"/>
+      <c r="A47" s="30" t="n"/>
+      <c r="B47" s="30" t="n"/>
+      <c r="C47" s="30" t="n"/>
+      <c r="D47" s="30" t="n"/>
+      <c r="E47" s="30" t="n"/>
+      <c r="F47" s="30" t="n"/>
+      <c r="G47" s="30" t="n"/>
+      <c r="H47" s="30" t="n"/>
+      <c r="I47" s="30" t="n"/>
+      <c r="J47" s="30" t="n"/>
+      <c r="K47" s="30" t="n"/>
+      <c r="L47" s="30" t="n"/>
+      <c r="M47" s="30" t="n"/>
+      <c r="N47" s="30" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="140" t="n"/>
-      <c r="B48" s="140" t="n"/>
-      <c r="C48" s="140" t="n"/>
-      <c r="D48" s="140" t="n"/>
-      <c r="E48" s="140" t="n"/>
-      <c r="F48" s="140" t="n"/>
-      <c r="G48" s="140" t="n"/>
-      <c r="H48" s="140" t="n"/>
-      <c r="I48" s="140" t="n"/>
-      <c r="J48" s="140" t="n"/>
-      <c r="K48" s="140" t="n"/>
-      <c r="L48" s="140" t="n"/>
-      <c r="M48" s="140" t="n"/>
-      <c r="N48" s="140" t="n"/>
+      <c r="A48" s="30" t="n"/>
+      <c r="B48" s="30" t="n"/>
+      <c r="C48" s="30" t="n"/>
+      <c r="D48" s="30" t="n"/>
+      <c r="E48" s="30" t="n"/>
+      <c r="F48" s="30" t="n"/>
+      <c r="G48" s="30" t="n"/>
+      <c r="H48" s="30" t="n"/>
+      <c r="I48" s="30" t="n"/>
+      <c r="J48" s="30" t="n"/>
+      <c r="K48" s="30" t="n"/>
+      <c r="L48" s="30" t="n"/>
+      <c r="M48" s="30" t="n"/>
+      <c r="N48" s="30" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="140" t="n"/>
@@ -4523,6 +4764,134 @@
       <c r="L57" s="140" t="n"/>
       <c r="M57" s="140" t="n"/>
       <c r="N57" s="140" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="140" t="n"/>
+      <c r="B58" s="140" t="n"/>
+      <c r="C58" s="140" t="n"/>
+      <c r="D58" s="140" t="n"/>
+      <c r="E58" s="140" t="n"/>
+      <c r="F58" s="140" t="n"/>
+      <c r="G58" s="140" t="n"/>
+      <c r="H58" s="140" t="n"/>
+      <c r="I58" s="140" t="n"/>
+      <c r="J58" s="140" t="n"/>
+      <c r="K58" s="140" t="n"/>
+      <c r="L58" s="140" t="n"/>
+      <c r="M58" s="140" t="n"/>
+      <c r="N58" s="140" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="140" t="n"/>
+      <c r="B59" s="140" t="n"/>
+      <c r="C59" s="140" t="n"/>
+      <c r="D59" s="140" t="n"/>
+      <c r="E59" s="140" t="n"/>
+      <c r="F59" s="140" t="n"/>
+      <c r="G59" s="140" t="n"/>
+      <c r="H59" s="140" t="n"/>
+      <c r="I59" s="140" t="n"/>
+      <c r="J59" s="140" t="n"/>
+      <c r="K59" s="140" t="n"/>
+      <c r="L59" s="140" t="n"/>
+      <c r="M59" s="140" t="n"/>
+      <c r="N59" s="140" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="140" t="n"/>
+      <c r="B60" s="140" t="n"/>
+      <c r="C60" s="140" t="n"/>
+      <c r="D60" s="140" t="n"/>
+      <c r="E60" s="140" t="n"/>
+      <c r="F60" s="140" t="n"/>
+      <c r="G60" s="140" t="n"/>
+      <c r="H60" s="140" t="n"/>
+      <c r="I60" s="140" t="n"/>
+      <c r="J60" s="140" t="n"/>
+      <c r="K60" s="140" t="n"/>
+      <c r="L60" s="140" t="n"/>
+      <c r="M60" s="140" t="n"/>
+      <c r="N60" s="140" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="140" t="n"/>
+      <c r="B61" s="140" t="n"/>
+      <c r="C61" s="140" t="n"/>
+      <c r="D61" s="140" t="n"/>
+      <c r="E61" s="140" t="n"/>
+      <c r="F61" s="140" t="n"/>
+      <c r="G61" s="140" t="n"/>
+      <c r="H61" s="140" t="n"/>
+      <c r="I61" s="140" t="n"/>
+      <c r="J61" s="140" t="n"/>
+      <c r="K61" s="140" t="n"/>
+      <c r="L61" s="140" t="n"/>
+      <c r="M61" s="140" t="n"/>
+      <c r="N61" s="140" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="140" t="n"/>
+      <c r="B62" s="140" t="n"/>
+      <c r="C62" s="140" t="n"/>
+      <c r="D62" s="140" t="n"/>
+      <c r="E62" s="140" t="n"/>
+      <c r="F62" s="140" t="n"/>
+      <c r="G62" s="140" t="n"/>
+      <c r="H62" s="140" t="n"/>
+      <c r="I62" s="140" t="n"/>
+      <c r="J62" s="140" t="n"/>
+      <c r="K62" s="140" t="n"/>
+      <c r="L62" s="140" t="n"/>
+      <c r="M62" s="140" t="n"/>
+      <c r="N62" s="140" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="140" t="n"/>
+      <c r="B63" s="140" t="n"/>
+      <c r="C63" s="140" t="n"/>
+      <c r="D63" s="140" t="n"/>
+      <c r="E63" s="140" t="n"/>
+      <c r="F63" s="140" t="n"/>
+      <c r="G63" s="140" t="n"/>
+      <c r="H63" s="140" t="n"/>
+      <c r="I63" s="140" t="n"/>
+      <c r="J63" s="140" t="n"/>
+      <c r="K63" s="140" t="n"/>
+      <c r="L63" s="140" t="n"/>
+      <c r="M63" s="140" t="n"/>
+      <c r="N63" s="140" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="140" t="n"/>
+      <c r="B64" s="140" t="n"/>
+      <c r="C64" s="140" t="n"/>
+      <c r="D64" s="140" t="n"/>
+      <c r="E64" s="140" t="n"/>
+      <c r="F64" s="140" t="n"/>
+      <c r="G64" s="140" t="n"/>
+      <c r="H64" s="140" t="n"/>
+      <c r="I64" s="140" t="n"/>
+      <c r="J64" s="140" t="n"/>
+      <c r="K64" s="140" t="n"/>
+      <c r="L64" s="140" t="n"/>
+      <c r="M64" s="140" t="n"/>
+      <c r="N64" s="140" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="140" t="n"/>
+      <c r="B65" s="140" t="n"/>
+      <c r="C65" s="140" t="n"/>
+      <c r="D65" s="140" t="n"/>
+      <c r="E65" s="140" t="n"/>
+      <c r="F65" s="140" t="n"/>
+      <c r="G65" s="140" t="n"/>
+      <c r="H65" s="140" t="n"/>
+      <c r="I65" s="140" t="n"/>
+      <c r="J65" s="140" t="n"/>
+      <c r="K65" s="140" t="n"/>
+      <c r="L65" s="140" t="n"/>
+      <c r="M65" s="140" t="n"/>
+      <c r="N65" s="140" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
+++ b/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Экономика и Сводка" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Факт расходов" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="План vs Рынок (Смета)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="База материалов (Комплектация)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00 &quot;₽&quot;"/>
     <numFmt numFmtId="167" formatCode="+0.0%"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -179,8 +180,69 @@
       <color rgb="00475569"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000284C7"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00334155"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00334155"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -229,8 +291,20 @@
         <bgColor rgb="001E293B"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E7FF"/>
+        <bgColor rgb="00E0E7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -531,11 +605,25 @@
       <right/>
       <bottom/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -956,6 +1044,129 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="3" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1353,7 +1564,7 @@
           <t>ПОКУПКА ОБЪЕКТА</t>
         </is>
       </c>
-      <c r="B4" s="117" t="n"/>
+      <c r="B4" s="114" t="n"/>
       <c r="C4" s="117" t="inlineStr">
         <is>
           <t>БЮДЖЕТ РЕМОНТА</t>
@@ -1384,7 +1595,7 @@
       <c r="A5" s="118" t="n">
         <v>3900000</v>
       </c>
-      <c r="B5" s="119" t="n"/>
+      <c r="B5" s="114" t="n"/>
       <c r="C5" s="118">
         <f>'План vs Рынок (Смета)'!E16</f>
         <v/>
@@ -1411,12 +1622,6 @@
           <t>1. ИНВЕСТИЦИОННАЯ МОДЕЛЬ СДЕЛКИ (ПОЛНАЯ СЕБЕСТОИМОСТЬ И ДОХОДНОСТЬ)</t>
         </is>
       </c>
-      <c r="B8" s="122" t="n"/>
-      <c r="C8" s="122" t="n"/>
-      <c r="D8" s="122" t="n"/>
-      <c r="E8" s="122" t="n"/>
-      <c r="F8" s="122" t="n"/>
-      <c r="G8" s="122" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="41" t="inlineStr">
@@ -1449,7 +1654,7 @@
           <t>Примечание / Обоснование</t>
         </is>
       </c>
-      <c r="G9" s="41" t="n"/>
+      <c r="G9" s="161" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="49" t="inlineStr">
@@ -1477,7 +1682,7 @@
           <t>Базовый актив, договор купли-продажи</t>
         </is>
       </c>
-      <c r="G10" s="49" t="n"/>
+      <c r="G10" s="146" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="44" t="inlineStr">
@@ -1506,7 +1711,7 @@
           <t>ЭЦП (7к), Росреестр (5к), вскрытие (8к), AI (3к)</t>
         </is>
       </c>
-      <c r="G11" s="44" t="n"/>
+      <c r="G11" s="146" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="49" t="inlineStr">
@@ -1536,7 +1741,7 @@
           <t>Смета по 11 этапам (цель 621 000 ₽ vs рынок 825 000 ₽)</t>
         </is>
       </c>
-      <c r="G12" s="49" t="n"/>
+      <c r="G12" s="146" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="44" t="inlineStr">
@@ -1564,7 +1769,7 @@
           <t>Запас прочности на скрытые дефекты</t>
         </is>
       </c>
-      <c r="G13" s="44" t="n"/>
+      <c r="G13" s="146" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="54" t="inlineStr">
@@ -1594,7 +1799,7 @@
           <t>Покупка (3.9М) + юристы (23к) + смета ремонта (621к)</t>
         </is>
       </c>
-      <c r="G14" s="125" t="n"/>
+      <c r="G14" s="95" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="126" t="inlineStr">
@@ -1623,7 +1828,7 @@
           <t>Покупка 3.9М + оформление 23к + факт ремонта 96.7к</t>
         </is>
       </c>
-      <c r="G15" s="44" t="n"/>
+      <c r="G15" s="146" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="129" t="inlineStr">
@@ -1652,7 +1857,7 @@
           <t>129 630 ₽/м² (верхняя планка Советского р-на)</t>
         </is>
       </c>
-      <c r="G16" s="49" t="n"/>
+      <c r="G16" s="146" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="126" t="inlineStr">
@@ -1682,7 +1887,7 @@
           <t>Чистый финансовый результат по итогам проекта</t>
         </is>
       </c>
-      <c r="G17" s="44" t="n"/>
+      <c r="G17" s="146" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="129" t="inlineStr">
@@ -1712,7 +1917,7 @@
           <t>Доходность капитала за 2 месяца</t>
         </is>
       </c>
-      <c r="G18" s="49" t="n"/>
+      <c r="G18" s="146" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="160" t="inlineStr">
@@ -1720,12 +1925,6 @@
           <t>2. ОПЕРАЦИОННЫЙ ТРЕКЕР БЮДЖЕТА РЕМОНТА (ПЛАН VS ФАКТ VS ОСТАТОК)</t>
         </is>
       </c>
-      <c r="B21" s="122" t="n"/>
-      <c r="C21" s="122" t="n"/>
-      <c r="D21" s="122" t="n"/>
-      <c r="E21" s="122" t="n"/>
-      <c r="F21" s="122" t="n"/>
-      <c r="G21" s="122" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="41" t="inlineStr">
@@ -2257,12 +2456,6 @@
           <t>3. КАРТА ЭКОНОМИИ ИНВЕСТОРА (ОПТИМИЗАЦИЯ УЗЛОВ + СКИДКИ НА ЗАКУПКАХ)</t>
         </is>
       </c>
-      <c r="B40" s="122" t="n"/>
-      <c r="C40" s="122" t="n"/>
-      <c r="D40" s="122" t="n"/>
-      <c r="E40" s="122" t="n"/>
-      <c r="F40" s="122" t="n"/>
-      <c r="G40" s="122" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="41" t="inlineStr">
@@ -2295,7 +2488,7 @@
           <t>Обоснование / Способ оптимизации</t>
         </is>
       </c>
-      <c r="G41" s="41" t="n"/>
+      <c r="G41" s="161" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="49" t="inlineStr">
@@ -2322,7 +2515,7 @@
           <t>Сохранены все стеклопакеты и балконный блок (регулировка + откосы)</t>
         </is>
       </c>
-      <c r="G42" s="49" t="n"/>
+      <c r="G42" s="146" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
@@ -2349,7 +2542,7 @@
           <t>Уже заменён на пластик ПВХ/ПП 110мм, перекрытия долбить не нужно</t>
         </is>
       </c>
-      <c r="G43" s="44" t="n"/>
+      <c r="G43" s="146" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="49" t="inlineStr">
@@ -2375,7 +2568,7 @@
           <t>Новый счётчик закуплен в составе материалов (поз. 17 на 16.5к); распломбировка 2.5к закрыта</t>
         </is>
       </c>
-      <c r="G44" s="49" t="n"/>
+      <c r="G44" s="146" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
@@ -2404,7 +2597,7 @@
           <t>Скидки от поставщиков (дверь -6к, кабель -2к, мусор -0.5к, демонтаж -4к и др.)</t>
         </is>
       </c>
-      <c r="G45" s="44" t="n"/>
+      <c r="G45" s="146" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="54" t="inlineStr">
@@ -2433,7 +2626,7 @@
           <t>Прямой вклад в повышение маржинальности сделки</t>
         </is>
       </c>
-      <c r="G46" s="125" t="n"/>
+      <c r="G46" s="95" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -5384,4 +5577,2581 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000F172A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.66666666666667" customWidth="1" min="1" max="1"/>
+    <col width="21.33333333333333" customWidth="1" min="2" max="2"/>
+    <col width="21.33333333333333" customWidth="1" min="3" max="3"/>
+    <col width="45.33333333333334" customWidth="1" min="4" max="4"/>
+    <col width="18.66666666666667" customWidth="1" min="5" max="5"/>
+    <col width="10.66666666666667" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15.33333333333333" customWidth="1" min="8" max="8"/>
+    <col width="16.66666666666667" customWidth="1" min="9" max="9"/>
+    <col width="29.33333333333333" customWidth="1" min="10" max="10"/>
+    <col width="14.66666666666667" customWidth="1" min="11" max="11"/>
+    <col width="34.66666666666666" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>ГЕНЕРАЛЬНАЯ МАТРИЦА БЮДЖЕТА И КОМПЛЕКТАЦИИ (316 021,27 ₽)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>Полная структура расходов Фрунзе 17 | Точная сверка с листом «Факт расходов» (1-в-1 до копейки, все 41 позиция)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="39" t="inlineStr">
+        <is>
+          <t>💡 Используй слева значки [-] и [+] для сворачивания блоков (Материалы, Работы, Юр. расходы), либо фильтр по Зоне</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="204" t="inlineStr">
+        <is>
+          <t>№ в Факте</t>
+        </is>
+      </c>
+      <c r="B4" s="204" t="inlineStr">
+        <is>
+          <t>Зона / Помещение</t>
+        </is>
+      </c>
+      <c r="C4" s="204" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="D4" s="204" t="inlineStr">
+        <is>
+          <t>Наименование расхода</t>
+        </is>
+      </c>
+      <c r="E4" s="204" t="inlineStr">
+        <is>
+          <t>Артикул / Код</t>
+        </is>
+      </c>
+      <c r="F4" s="204" t="inlineStr">
+        <is>
+          <t>Ед. изм.</t>
+        </is>
+      </c>
+      <c r="G4" s="204" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+      <c r="H4" s="204" t="inlineStr">
+        <is>
+          <t>Цена / ед. (₽)</t>
+        </is>
+      </c>
+      <c r="I4" s="204" t="inlineStr">
+        <is>
+          <t>Сумма (₽)</t>
+        </is>
+      </c>
+      <c r="J4" s="204" t="inlineStr">
+        <is>
+          <t>Поставщик / Подрядчик</t>
+        </is>
+      </c>
+      <c r="K4" s="204" t="inlineStr">
+        <is>
+          <t>Ссылка / Документ</t>
+        </is>
+      </c>
+      <c r="L4" s="204" t="inlineStr">
+        <is>
+          <t>Примечание (Фрунзе 17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="205" t="inlineStr"/>
+      <c r="B5" s="205" t="inlineStr">
+        <is>
+          <t>🛁 БЛОК 1: СТРОИТЕЛЬНЫЕ И ЧИСТОВЫЕ МАТЕРИАЛЫ «ЛЕМАНА ПРО» (13 ЧЕКОВ)</t>
+        </is>
+      </c>
+      <c r="C5" s="205" t="inlineStr"/>
+      <c r="D5" s="205" t="inlineStr"/>
+      <c r="E5" s="205" t="inlineStr"/>
+      <c r="F5" s="205" t="inlineStr"/>
+      <c r="G5" s="205" t="inlineStr"/>
+      <c r="H5" s="205" t="inlineStr"/>
+      <c r="I5" s="205" t="inlineStr"/>
+      <c r="J5" s="205" t="inlineStr"/>
+      <c r="K5" s="205" t="inlineStr"/>
+      <c r="L5" s="205" t="inlineStr"/>
+    </row>
+    <row r="6" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A6" s="192" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" s="191" t="inlineStr">
+        <is>
+          <t>Расходники</t>
+        </is>
+      </c>
+      <c r="C6" s="191" t="inlineStr">
+        <is>
+          <t>Пылесос</t>
+        </is>
+      </c>
+      <c r="D6" s="191" t="inlineStr">
+        <is>
+          <t>Мешки для пылесоса синт. 12л (5 шт) — Леруа/Лемана</t>
+        </is>
+      </c>
+      <c r="E6" s="191" t="inlineStr">
+        <is>
+          <t>4607086338088</t>
+        </is>
+      </c>
+      <c r="F6" s="191" t="inlineStr">
+        <is>
+          <t>упак.</t>
+        </is>
+      </c>
+      <c r="G6" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="193" t="n">
+        <v>717</v>
+      </c>
+      <c r="I6" s="193">
+        <f>G6*H6</f>
+        <v/>
+      </c>
+      <c r="J6" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K6" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L6" s="191" t="inlineStr">
+        <is>
+          <t>Чек 3831 от 23.08.2026: Сбор пыли штробления</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A7" s="192" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" s="191" t="inlineStr">
+        <is>
+          <t>Инструмент</t>
+        </is>
+      </c>
+      <c r="C7" s="191" t="inlineStr">
+        <is>
+          <t>Демонтаж</t>
+        </is>
+      </c>
+      <c r="D7" s="191" t="inlineStr">
+        <is>
+          <t>Лом-гвоздодер, мешки 15шт, лента, перчатки 6п, опрыскиватель</t>
+        </is>
+      </c>
+      <c r="E7" s="191" t="inlineStr">
+        <is>
+          <t>4603333000001</t>
+        </is>
+      </c>
+      <c r="F7" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G7" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="193" t="n">
+        <v>1830</v>
+      </c>
+      <c r="I7" s="193">
+        <f>G7*H7</f>
+        <v/>
+      </c>
+      <c r="J7" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K7" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L7" s="191" t="inlineStr">
+        <is>
+          <t>Чек 3832 от 23.08.2026: Инструмент демонтажа</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A8" s="192" t="n">
+        <v>25</v>
+      </c>
+      <c r="B8" s="191" t="inlineStr">
+        <is>
+          <t>Черновые стены</t>
+        </is>
+      </c>
+      <c r="C8" s="191" t="inlineStr">
+        <is>
+          <t>Шпатлевка / Грунт</t>
+        </is>
+      </c>
+      <c r="D8" s="191" t="inlineStr">
+        <is>
+          <t>Материалы для зачистки и грунтования (шпатлевка 20кг, грунт 10л, СТ99, фильтр Rommer)</t>
+        </is>
+      </c>
+      <c r="E8" s="191" t="inlineStr">
+        <is>
+          <t>3276006224277</t>
+        </is>
+      </c>
+      <c r="F8" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G8" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="193" t="n">
+        <v>4803.6</v>
+      </c>
+      <c r="I8" s="193">
+        <f>G8*H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K8" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L8" s="191" t="inlineStr">
+        <is>
+          <t>Чек от 30.08.2026: Подготовка стен зала и с/у</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A9" s="192" t="n">
+        <v>26</v>
+      </c>
+      <c r="B9" s="191" t="inlineStr">
+        <is>
+          <t>Инструмент</t>
+        </is>
+      </c>
+      <c r="C9" s="191" t="inlineStr">
+        <is>
+          <t>Ёмкости</t>
+        </is>
+      </c>
+      <c r="D9" s="191" t="inlineStr">
+        <is>
+          <t>Ведро строительное круглое 20 л (2 шт.)</t>
+        </is>
+      </c>
+      <c r="E9" s="191" t="inlineStr">
+        <is>
+          <t>4610008470475</t>
+        </is>
+      </c>
+      <c r="F9" s="191" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G9" s="192" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="193" t="n">
+        <v>128</v>
+      </c>
+      <c r="I9" s="193">
+        <f>G9*H9</f>
+        <v/>
+      </c>
+      <c r="J9" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K9" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L9" s="191" t="inlineStr">
+        <is>
+          <t>Чек от 30.08.2026: Ёмкости для замеса растворов</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A10" s="192" t="n">
+        <v>28</v>
+      </c>
+      <c r="B10" s="191" t="inlineStr">
+        <is>
+          <t>Черновые стены</t>
+        </is>
+      </c>
+      <c r="C10" s="191" t="inlineStr">
+        <is>
+          <t>Шпатлевка / Шпатели</t>
+        </is>
+      </c>
+      <c r="D10" s="191" t="inlineStr">
+        <is>
+          <t>Материалы для подготовки стен (грунт Axton 10л 4шт, шпатлевка 20кг 2шт, шпатели, мешки)</t>
+        </is>
+      </c>
+      <c r="E10" s="191" t="inlineStr">
+        <is>
+          <t>4601745004252</t>
+        </is>
+      </c>
+      <c r="F10" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G10" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="193" t="n">
+        <v>3308</v>
+      </c>
+      <c r="I10" s="193">
+        <f>G10*H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K10" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L10" s="191" t="inlineStr">
+        <is>
+          <t>Чек от 05.09.2026: Подготовка спальни</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A11" s="192" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" s="191" t="inlineStr">
+        <is>
+          <t>Черновые стены</t>
+        </is>
+      </c>
+      <c r="C11" s="191" t="inlineStr">
+        <is>
+          <t>Штукатурка / Бетонконтакт</t>
+        </is>
+      </c>
+      <c r="D11" s="191" t="inlineStr">
+        <is>
+          <t>Материалы штукатурки и шпаклёвки (Бетонконтакт 12кг 3шт, финиш 5шт, штукатурка 3шт, правило, углы)</t>
+        </is>
+      </c>
+      <c r="E11" s="191" t="inlineStr">
+        <is>
+          <t>4607017518816</t>
+        </is>
+      </c>
+      <c r="F11" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G11" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="193" t="n">
+        <v>8162</v>
+      </c>
+      <c r="I11" s="193">
+        <f>G11*H11</f>
+        <v/>
+      </c>
+      <c r="J11" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K11" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L11" s="191" t="inlineStr">
+        <is>
+          <t>Чек от 06.09.2026: Основное выравнивание стен</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A12" s="192" t="n">
+        <v>32</v>
+      </c>
+      <c r="B12" s="191" t="inlineStr">
+        <is>
+          <t>Черновые стены</t>
+        </is>
+      </c>
+      <c r="C12" s="191" t="inlineStr">
+        <is>
+          <t>Шпаклёвка</t>
+        </is>
+      </c>
+      <c r="D12" s="191" t="inlineStr">
+        <is>
+          <t>Материалы штукатурки и шпаклёвки (шпатлевка финиш 20кг, штукатурка 30кг 2шт, перчатки)</t>
+        </is>
+      </c>
+      <c r="E12" s="191" t="inlineStr">
+        <is>
+          <t>4601745002814</t>
+        </is>
+      </c>
+      <c r="F12" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G12" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="193" t="n">
+        <v>1594</v>
+      </c>
+      <c r="I12" s="193">
+        <f>G12*H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K12" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L12" s="191" t="inlineStr">
+        <is>
+          <t>Чек от 08.09.2026: Добор смесей на спальню</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A13" s="192" t="n">
+        <v>34</v>
+      </c>
+      <c r="B13" s="191" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C13" s="191" t="inlineStr">
+        <is>
+          <t>Санфаянс / Смесители</t>
+        </is>
+      </c>
+      <c r="D13" s="191" t="inlineStr">
+        <is>
+          <t>Сантехника и санфаянс с/у (ванна Нерея 150, каркас Sensea, унитаз Sanita, раковина 60, смесители 2шт, душ, сифон)</t>
+        </is>
+      </c>
+      <c r="E13" s="191" t="inlineStr">
+        <is>
+          <t>4600779023659</t>
+        </is>
+      </c>
+      <c r="F13" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G13" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="193" t="n">
+        <v>30021</v>
+      </c>
+      <c r="I13" s="193">
+        <f>G13*H13</f>
+        <v/>
+      </c>
+      <c r="J13" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K13" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L13" s="191" t="inlineStr">
+        <is>
+          <t>Чек от 13.09.2026 (заказ 774): Полный комплект с/у</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A14" s="192" t="n">
+        <v>35</v>
+      </c>
+      <c r="B14" s="191" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C14" s="191" t="inlineStr">
+        <is>
+          <t>Керамогранит / Затирка</t>
+        </is>
+      </c>
+      <c r="D14" s="191" t="inlineStr">
+        <is>
+          <t>Керамогранит Calacatta 60х120 (14 упак. / 20.16 м²) + затирка Ceresit CE 40 2кг 2шт</t>
+        </is>
+      </c>
+      <c r="E14" s="191" t="inlineStr">
+        <is>
+          <t>4673766221451</t>
+        </is>
+      </c>
+      <c r="F14" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G14" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="193" t="n">
+        <v>33457</v>
+      </c>
+      <c r="I14" s="193">
+        <f>G14*H14</f>
+        <v/>
+      </c>
+      <c r="J14" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K14" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L14" s="191" t="inlineStr">
+        <is>
+          <t>Чек от 13.09.2026 (заказ 774): Плитка на все стены с/у</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A15" s="192" t="n">
+        <v>36</v>
+      </c>
+      <c r="B15" s="191" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C15" s="191" t="inlineStr">
+        <is>
+          <t>Плиточный клей</t>
+        </is>
+      </c>
+      <c r="D15" s="191" t="inlineStr">
+        <is>
+          <t>Плиточный клей Unis 2000 C1T 25 кг для формата 60х120 (13 мешков)</t>
+        </is>
+      </c>
+      <c r="E15" s="191" t="inlineStr">
+        <is>
+          <t>4607005180063</t>
+        </is>
+      </c>
+      <c r="F15" s="191" t="inlineStr">
+        <is>
+          <t>мешок</t>
+        </is>
+      </c>
+      <c r="G15" s="192" t="n">
+        <v>13</v>
+      </c>
+      <c r="H15" s="193" t="n">
+        <v>382.53846</v>
+      </c>
+      <c r="I15" s="193">
+        <f>G15*H15</f>
+        <v/>
+      </c>
+      <c r="J15" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K15" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L15" s="191" t="inlineStr">
+        <is>
+          <t>Чек от 13.09.2026 (заказ 774): Клей под керамогранит</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A16" s="192" t="n">
+        <v>37</v>
+      </c>
+      <c r="B16" s="191" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C16" s="191" t="inlineStr">
+        <is>
+          <t>СВП</t>
+        </is>
+      </c>
+      <c r="D16" s="191" t="inlineStr">
+        <is>
+          <t>Система выравнивания плитки СВП DILWIS (зажимы 1 мм 200 шт, клинья 100 шт)</t>
+        </is>
+      </c>
+      <c r="E16" s="191" t="inlineStr">
+        <is>
+          <t>4610085150475</t>
+        </is>
+      </c>
+      <c r="F16" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G16" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="193" t="n">
+        <v>853</v>
+      </c>
+      <c r="I16" s="193">
+        <f>G16*H16</f>
+        <v/>
+      </c>
+      <c r="J16" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K16" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L16" s="191" t="inlineStr">
+        <is>
+          <t>Чек от 13.09.2026 (заказ 774): Идеальный шов 1 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A17" s="192" t="n">
+        <v>38</v>
+      </c>
+      <c r="B17" s="191" t="inlineStr">
+        <is>
+          <t>Черновые стены</t>
+        </is>
+      </c>
+      <c r="C17" s="191" t="inlineStr">
+        <is>
+          <t>Шпаклёвка</t>
+        </is>
+      </c>
+      <c r="D17" s="191" t="inlineStr">
+        <is>
+          <t>Материалы для штукатурки и шпаклёвки (повторный добор: финиш 20кг, штукатурка 2шт)</t>
+        </is>
+      </c>
+      <c r="E17" s="191" t="inlineStr">
+        <is>
+          <t>4601745000407</t>
+        </is>
+      </c>
+      <c r="F17" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G17" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="193" t="n">
+        <v>1594</v>
+      </c>
+      <c r="I17" s="193">
+        <f>G17*H17</f>
+        <v/>
+      </c>
+      <c r="J17" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K17" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L17" s="191" t="inlineStr">
+        <is>
+          <t>Чек от 13.09.2026: Добор смесей на гардероб</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A18" s="192" t="n">
+        <v>39</v>
+      </c>
+      <c r="B18" s="191" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C18" s="191" t="inlineStr">
+        <is>
+          <t>Стяжка / Короба</t>
+        </is>
+      </c>
+      <c r="D18" s="191" t="inlineStr">
+        <is>
+          <t>Материалы для стяжки пола и короба с/у (пескобетон М-300 6шт, Knauf 50х40, ГСП 2шт, фибра, саморезы, стамеска)</t>
+        </is>
+      </c>
+      <c r="E18" s="191" t="inlineStr">
+        <is>
+          <t>4610007550932</t>
+        </is>
+      </c>
+      <c r="F18" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G18" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="193" t="n">
+        <v>3182.67</v>
+      </c>
+      <c r="I18" s="193">
+        <f>G18*H18</f>
+        <v/>
+      </c>
+      <c r="J18" s="191" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K18" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L18" s="191" t="inlineStr">
+        <is>
+          <t>Чек №201 от 13.09.2026: Стяжка пола и стояк с/у</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="206" t="inlineStr"/>
+      <c r="B19" s="206" t="inlineStr">
+        <is>
+          <t>ИТОГО МАТЕРИАЛЫ ЛЕМАНА ПРО (ПО ЧЕКАМ):</t>
+        </is>
+      </c>
+      <c r="C19" s="206" t="inlineStr"/>
+      <c r="D19" s="206" t="inlineStr"/>
+      <c r="E19" s="206" t="inlineStr"/>
+      <c r="F19" s="206" t="inlineStr"/>
+      <c r="G19" s="206" t="inlineStr"/>
+      <c r="H19" s="206" t="inlineStr"/>
+      <c r="I19" s="200">
+        <f>SUM(I6:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="206" t="inlineStr"/>
+      <c r="K19" s="206" t="inlineStr"/>
+      <c r="L19" s="206" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="207" t="inlineStr"/>
+      <c r="B20" s="207" t="inlineStr">
+        <is>
+          <t>⚡ БЛОК 2: ИНЖЕНЕРНЫЕ МАТЕРИАЛЫ, ДВЕРИ И ОСНАЩЕНИЕ (СПЕЦПОСТАВЩИКИ)</t>
+        </is>
+      </c>
+      <c r="C20" s="207" t="inlineStr"/>
+      <c r="D20" s="207" t="inlineStr"/>
+      <c r="E20" s="207" t="inlineStr"/>
+      <c r="F20" s="207" t="inlineStr"/>
+      <c r="G20" s="207" t="inlineStr"/>
+      <c r="H20" s="207" t="inlineStr"/>
+      <c r="I20" s="207" t="inlineStr"/>
+      <c r="J20" s="207" t="inlineStr"/>
+      <c r="K20" s="207" t="inlineStr"/>
+      <c r="L20" s="207" t="inlineStr"/>
+    </row>
+    <row r="21" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A21" s="192" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="191" t="inlineStr">
+        <is>
+          <t>Расходники</t>
+        </is>
+      </c>
+      <c r="C21" s="191" t="inlineStr">
+        <is>
+          <t>Демонтаж</t>
+        </is>
+      </c>
+      <c r="D21" s="191" t="inlineStr">
+        <is>
+          <t>Мешки мусорные плотные, перчатки рабочие (хозмаг/рынок)</t>
+        </is>
+      </c>
+      <c r="E21" s="191" t="inlineStr">
+        <is>
+          <t>ХОЗМАГ-МЕШКИ</t>
+        </is>
+      </c>
+      <c r="F21" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G21" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="193" t="n">
+        <v>300</v>
+      </c>
+      <c r="I21" s="193">
+        <f>G21*H21</f>
+        <v/>
+      </c>
+      <c r="J21" s="191" t="inlineStr">
+        <is>
+          <t>Хозмаг / Рынок</t>
+        </is>
+      </c>
+      <c r="K21" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L21" s="191" t="inlineStr">
+        <is>
+          <t>Оперативная докупка расходников для демонтажа</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A22" s="192" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="191" t="inlineStr">
+        <is>
+          <t>Сантехника</t>
+        </is>
+      </c>
+      <c r="C22" s="191" t="inlineStr">
+        <is>
+          <t>Учёт воды</t>
+        </is>
+      </c>
+      <c r="D22" s="191" t="inlineStr">
+        <is>
+          <t>Счётчик горячей/холодной воды + кран на ввод (материалы)</t>
+        </is>
+      </c>
+      <c r="E22" s="191" t="inlineStr">
+        <is>
+          <t>СЧЕТЧИК-ВОДЫ</t>
+        </is>
+      </c>
+      <c r="F22" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G22" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="193" t="n">
+        <v>2100</v>
+      </c>
+      <c r="I22" s="193">
+        <f>G22*H22</f>
+        <v/>
+      </c>
+      <c r="J22" s="191" t="inlineStr">
+        <is>
+          <t>Вадим (сантехник УК)</t>
+        </is>
+      </c>
+      <c r="K22" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L22" s="191" t="inlineStr">
+        <is>
+          <t>Замена вводных узлов и прибора учёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A23" s="192" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="191" t="inlineStr">
+        <is>
+          <t>Сантехника</t>
+        </is>
+      </c>
+      <c r="C23" s="191" t="inlineStr">
+        <is>
+          <t>Учёт воды</t>
+        </is>
+      </c>
+      <c r="D23" s="191" t="inlineStr">
+        <is>
+          <t>Покупка и установка счётчика и кранов (доплата за фитинги и муфты)</t>
+        </is>
+      </c>
+      <c r="E23" s="191" t="inlineStr">
+        <is>
+          <t>ФИТИНГИ-САНТЕХ</t>
+        </is>
+      </c>
+      <c r="F23" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G23" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="193" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I23" s="193">
+        <f>G23*H23</f>
+        <v/>
+      </c>
+      <c r="J23" s="191" t="inlineStr">
+        <is>
+          <t>Вадим (сантехник УК)</t>
+        </is>
+      </c>
+      <c r="K23" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L23" s="191" t="inlineStr">
+        <is>
+          <t>Латунные фитинги, муфты, уплотнители</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A24" s="192" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="191" t="inlineStr">
+        <is>
+          <t>Входная группа</t>
+        </is>
+      </c>
+      <c r="C24" s="191" t="inlineStr">
+        <is>
+          <t>Двери</t>
+        </is>
+      </c>
+      <c r="D24" s="191" t="inlineStr">
+        <is>
+          <t>Покупка входной металлической двери с внутренней МДФ-панелью</t>
+        </is>
+      </c>
+      <c r="E24" s="191" t="inlineStr">
+        <is>
+          <t>ДВЕРЬ-ВХОД-МДФ</t>
+        </is>
+      </c>
+      <c r="F24" s="191" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G24" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="193" t="n">
+        <v>16000</v>
+      </c>
+      <c r="I24" s="193">
+        <f>G24*H24</f>
+        <v/>
+      </c>
+      <c r="J24" s="191" t="inlineStr">
+        <is>
+          <t>Владимир (двери)</t>
+        </is>
+      </c>
+      <c r="K24" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L24" s="191" t="inlineStr">
+        <is>
+          <t>Металл 1.5 мм, МДФ-панель, надежные замки</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A25" s="192" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="191" t="inlineStr">
+        <is>
+          <t>Входная группа</t>
+        </is>
+      </c>
+      <c r="C25" s="191" t="inlineStr">
+        <is>
+          <t>Логистика</t>
+        </is>
+      </c>
+      <c r="D25" s="191" t="inlineStr">
+        <is>
+          <t>Доставка входной металлической двери на объект</t>
+        </is>
+      </c>
+      <c r="E25" s="191" t="inlineStr">
+        <is>
+          <t>ДОСТАВКА-ДВЕРЬ</t>
+        </is>
+      </c>
+      <c r="F25" s="191" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="G25" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="193" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I25" s="193">
+        <f>G25*H25</f>
+        <v/>
+      </c>
+      <c r="J25" s="191" t="inlineStr">
+        <is>
+          <t>Владимир / Доставка</t>
+        </is>
+      </c>
+      <c r="K25" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L25" s="191" t="inlineStr">
+        <is>
+          <t>Транспортировка двери на ул. Фрунзе 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A26" s="192" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="191" t="inlineStr">
+        <is>
+          <t>Электрика</t>
+        </is>
+      </c>
+      <c r="C26" s="191" t="inlineStr">
+        <is>
+          <t>Щит / Автоматика</t>
+        </is>
+      </c>
+      <c r="D26" s="191" t="inlineStr">
+        <is>
+          <t>Черновые материалы электрики (щит 18м, новый электросчётчик, автоматы, УЗО, гофра)</t>
+        </is>
+      </c>
+      <c r="E26" s="191" t="inlineStr">
+        <is>
+          <t>ЩИТ-АВТ-КОМПЛЕКТ</t>
+        </is>
+      </c>
+      <c r="F26" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G26" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="193" t="n">
+        <v>16500</v>
+      </c>
+      <c r="I26" s="193">
+        <f>G26*H26</f>
+        <v/>
+      </c>
+      <c r="J26" s="191" t="inlineStr">
+        <is>
+          <t>Анатолий / Поставщик</t>
+        </is>
+      </c>
+      <c r="K26" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L26" s="191" t="inlineStr">
+        <is>
+          <t>Комплектная начинка щита и прибор учёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A27" s="192" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="191" t="inlineStr">
+        <is>
+          <t>Электрика</t>
+        </is>
+      </c>
+      <c r="C27" s="191" t="inlineStr">
+        <is>
+          <t>Кабель</t>
+        </is>
+      </c>
+      <c r="D27" s="191" t="inlineStr">
+        <is>
+          <t>Кабель силовой ВВГнг-LS (ГОСТ 3х2.5 и 3х1.5 для всех трасс)</t>
+        </is>
+      </c>
+      <c r="E27" s="191" t="inlineStr">
+        <is>
+          <t>ВВГнг-LS-ГОСТ-1</t>
+        </is>
+      </c>
+      <c r="F27" s="191" t="inlineStr">
+        <is>
+          <t>бухта</t>
+        </is>
+      </c>
+      <c r="G27" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="193" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I27" s="193">
+        <f>G27*H27</f>
+        <v/>
+      </c>
+      <c r="J27" s="191" t="inlineStr">
+        <is>
+          <t>Электромонтаж / Поставщик</t>
+        </is>
+      </c>
+      <c r="K27" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L27" s="191" t="inlineStr">
+        <is>
+          <t>Силовой кабель ГОСТ под розетки и свет</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A28" s="192" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" s="191" t="inlineStr">
+        <is>
+          <t>Электрика</t>
+        </is>
+      </c>
+      <c r="C28" s="191" t="inlineStr">
+        <is>
+          <t>Крепёж</t>
+        </is>
+      </c>
+      <c r="D28" s="191" t="inlineStr">
+        <is>
+          <t>Стяжки нейлоновые и крепёж для монтажа кабеля</t>
+        </is>
+      </c>
+      <c r="E28" s="191" t="inlineStr">
+        <is>
+          <t>КРЕПЕЖ-КАБЕЛЬ</t>
+        </is>
+      </c>
+      <c r="F28" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G28" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="193" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I28" s="193">
+        <f>G28*H28</f>
+        <v/>
+      </c>
+      <c r="J28" s="191" t="inlineStr">
+        <is>
+          <t>Хозмаг / Электромонтаж</t>
+        </is>
+      </c>
+      <c r="K28" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L28" s="191" t="inlineStr">
+        <is>
+          <t>Дюбель-хомуты и стяжки для трасс</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A29" s="192" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" s="191" t="inlineStr">
+        <is>
+          <t>Электрика</t>
+        </is>
+      </c>
+      <c r="C29" s="191" t="inlineStr">
+        <is>
+          <t>Кабель</t>
+        </is>
+      </c>
+      <c r="D29" s="191" t="inlineStr">
+        <is>
+          <t>Докупка силового кабеля ВВГнг-LS (дополнительный метраж трасс)</t>
+        </is>
+      </c>
+      <c r="E29" s="191" t="inlineStr">
+        <is>
+          <t>ВВГнг-LS-ГОСТ-2</t>
+        </is>
+      </c>
+      <c r="F29" s="191" t="inlineStr">
+        <is>
+          <t>бухта</t>
+        </is>
+      </c>
+      <c r="G29" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="193" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I29" s="193">
+        <f>G29*H29</f>
+        <v/>
+      </c>
+      <c r="J29" s="191" t="inlineStr">
+        <is>
+          <t>Электромонтаж / Поставщик</t>
+        </is>
+      </c>
+      <c r="K29" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L29" s="191" t="inlineStr">
+        <is>
+          <t>Дополнительный кабель на трассы кухни и коридора</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A30" s="192" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="191" t="inlineStr">
+        <is>
+          <t>Оснащение</t>
+        </is>
+      </c>
+      <c r="C30" s="191" t="inlineStr">
+        <is>
+          <t>Инвентарь</t>
+        </is>
+      </c>
+      <c r="D30" s="191" t="inlineStr">
+        <is>
+          <t>Портативная акустика Xiaomi Bluetooth Speaker Essential Green</t>
+        </is>
+      </c>
+      <c r="E30" s="191" t="inlineStr">
+        <is>
+          <t>XIAOMI-SPK-ESS</t>
+        </is>
+      </c>
+      <c r="F30" s="191" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G30" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="193" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I30" s="193">
+        <f>G30*H30</f>
+        <v/>
+      </c>
+      <c r="J30" s="191" t="inlineStr">
+        <is>
+          <t>ООО ДНС Ритейл (DNS)</t>
+        </is>
+      </c>
+      <c r="K30" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L30" s="191" t="inlineStr">
+        <is>
+          <t>Акустическое оснащение объекта для бригад</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A31" s="192" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="191" t="inlineStr">
+        <is>
+          <t>Оснащение</t>
+        </is>
+      </c>
+      <c r="C31" s="191" t="inlineStr">
+        <is>
+          <t>Хознужды</t>
+        </is>
+      </c>
+      <c r="D31" s="191" t="inlineStr">
+        <is>
+          <t>Хозрасходы на объект: салфетки влажные и питьевая вода для мастеров</t>
+        </is>
+      </c>
+      <c r="E31" s="191" t="inlineStr">
+        <is>
+          <t>ХОЗ-ВОДА-САЛФЕТКИ</t>
+        </is>
+      </c>
+      <c r="F31" s="191" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G31" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="193" t="n">
+        <v>520</v>
+      </c>
+      <c r="I31" s="193">
+        <f>G31*H31</f>
+        <v/>
+      </c>
+      <c r="J31" s="191" t="inlineStr">
+        <is>
+          <t>Хозмаг / Продукты</t>
+        </is>
+      </c>
+      <c r="K31" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L31" s="191" t="inlineStr">
+        <is>
+          <t>Бытовое снабжение объекта</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="206" t="inlineStr"/>
+      <c r="B32" s="206" t="inlineStr">
+        <is>
+          <t>ИТОГО МАТЕРИАЛЫ СПЕЦПОСТАВЩИКОВ:</t>
+        </is>
+      </c>
+      <c r="C32" s="206" t="inlineStr"/>
+      <c r="D32" s="206" t="inlineStr"/>
+      <c r="E32" s="206" t="inlineStr"/>
+      <c r="F32" s="206" t="inlineStr"/>
+      <c r="G32" s="206" t="inlineStr"/>
+      <c r="H32" s="206" t="inlineStr"/>
+      <c r="I32" s="200">
+        <f>SUM(I21:I31)</f>
+        <v/>
+      </c>
+      <c r="J32" s="206" t="inlineStr"/>
+      <c r="K32" s="206" t="inlineStr"/>
+      <c r="L32" s="206" t="inlineStr"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="208" t="inlineStr"/>
+      <c r="B33" s="208" t="inlineStr">
+        <is>
+          <t>👷‍♂️ БЛОК 3: РАБОТЫ МАСТЕРОВ, ДЕМОНТАЖ, МОНТАЖ И ЛОГИСТИКА</t>
+        </is>
+      </c>
+      <c r="C33" s="208" t="inlineStr"/>
+      <c r="D33" s="208" t="inlineStr"/>
+      <c r="E33" s="208" t="inlineStr"/>
+      <c r="F33" s="208" t="inlineStr"/>
+      <c r="G33" s="208" t="inlineStr"/>
+      <c r="H33" s="208" t="inlineStr"/>
+      <c r="I33" s="208" t="inlineStr"/>
+      <c r="J33" s="208" t="inlineStr"/>
+      <c r="K33" s="208" t="inlineStr"/>
+      <c r="L33" s="208" t="inlineStr"/>
+    </row>
+    <row r="34" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A34" s="192" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="191" t="inlineStr">
+        <is>
+          <t>Безопасность</t>
+        </is>
+      </c>
+      <c r="C34" s="191" t="inlineStr">
+        <is>
+          <t>Вскрытие</t>
+        </is>
+      </c>
+      <c r="D34" s="191" t="inlineStr">
+        <is>
+          <t>Вскрытие старого замка и обеспечение первого доступа</t>
+        </is>
+      </c>
+      <c r="E34" s="191" t="inlineStr">
+        <is>
+          <t>ВСКРЫТИЕ-ЗАМКА</t>
+        </is>
+      </c>
+      <c r="F34" s="191" t="inlineStr">
+        <is>
+          <t>выезд</t>
+        </is>
+      </c>
+      <c r="G34" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="193" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I34" s="193">
+        <f>G34*H34</f>
+        <v/>
+      </c>
+      <c r="J34" s="191" t="inlineStr">
+        <is>
+          <t>Служба вскрытия</t>
+        </is>
+      </c>
+      <c r="K34" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L34" s="191" t="inlineStr">
+        <is>
+          <t>Аварийное открытие двери после торгов</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A35" s="192" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="191" t="inlineStr">
+        <is>
+          <t>Демонтаж</t>
+        </is>
+      </c>
+      <c r="C35" s="191" t="inlineStr">
+        <is>
+          <t>Вывоз мусора</t>
+        </is>
+      </c>
+      <c r="D35" s="191" t="inlineStr">
+        <is>
+          <t>Заказ мусорного контейнера 8 м³ (лодочка)</t>
+        </is>
+      </c>
+      <c r="E35" s="191" t="inlineStr">
+        <is>
+          <t>КОНТЕЙНЕР-МУСОР-8М3</t>
+        </is>
+      </c>
+      <c r="F35" s="191" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="G35" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="193" t="n">
+        <v>8500</v>
+      </c>
+      <c r="I35" s="193">
+        <f>G35*H35</f>
+        <v/>
+      </c>
+      <c r="J35" s="191" t="inlineStr">
+        <is>
+          <t>Елена (вывоз мусора)</t>
+        </is>
+      </c>
+      <c r="K35" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L35" s="191" t="inlineStr">
+        <is>
+          <t>Вывоз мебели, санузла, чугуна, досок</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A36" s="192" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="191" t="inlineStr">
+        <is>
+          <t>Демонтаж</t>
+        </is>
+      </c>
+      <c r="C36" s="191" t="inlineStr">
+        <is>
+          <t>Аренда</t>
+        </is>
+      </c>
+      <c r="D36" s="191" t="inlineStr">
+        <is>
+          <t>Аренда инструмента и помощь соседа по дому</t>
+        </is>
+      </c>
+      <c r="E36" s="191" t="inlineStr">
+        <is>
+          <t>АРЕНДА-ИНСТРУМЕНТ</t>
+        </is>
+      </c>
+      <c r="F36" s="191" t="inlineStr">
+        <is>
+          <t>услуга</t>
+        </is>
+      </c>
+      <c r="G36" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="193" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I36" s="193">
+        <f>G36*H36</f>
+        <v/>
+      </c>
+      <c r="J36" s="191" t="inlineStr">
+        <is>
+          <t>Сосед по дому</t>
+        </is>
+      </c>
+      <c r="K36" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L36" s="191" t="inlineStr">
+        <is>
+          <t>Перфоратор и монтировки для первичного демонтажа</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A37" s="192" t="n">
+        <v>7</v>
+      </c>
+      <c r="B37" s="191" t="inlineStr">
+        <is>
+          <t>Демонтаж</t>
+        </is>
+      </c>
+      <c r="C37" s="191" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="D37" s="191" t="inlineStr">
+        <is>
+          <t>Оплата работы бригады разнорабочих (4 чел., 28 чел.-час, спуск с 5 этажа)</t>
+        </is>
+      </c>
+      <c r="E37" s="191" t="inlineStr">
+        <is>
+          <t>ДЕМОНТАЖ-БРИГАДА-1</t>
+        </is>
+      </c>
+      <c r="F37" s="191" t="inlineStr">
+        <is>
+          <t>смена</t>
+        </is>
+      </c>
+      <c r="G37" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="193" t="n">
+        <v>16000</v>
+      </c>
+      <c r="I37" s="193">
+        <f>G37*H37</f>
+        <v/>
+      </c>
+      <c r="J37" s="191" t="inlineStr">
+        <is>
+          <t>Бригада разнорабочих</t>
+        </is>
+      </c>
+      <c r="K37" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L37" s="191" t="inlineStr">
+        <is>
+          <t>Тотальная зачистка и вынос мусора без лифта</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A38" s="192" t="n">
+        <v>18</v>
+      </c>
+      <c r="B38" s="191" t="inlineStr">
+        <is>
+          <t>Входная группа</t>
+        </is>
+      </c>
+      <c r="C38" s="191" t="inlineStr">
+        <is>
+          <t>Монтаж</t>
+        </is>
+      </c>
+      <c r="D38" s="191" t="inlineStr">
+        <is>
+          <t>Монтаж входной двери (демонтаж 2 старых дверей + монтаж новой)</t>
+        </is>
+      </c>
+      <c r="E38" s="191" t="inlineStr">
+        <is>
+          <t>МОНТАЖ-ДВЕРИ-ВХОД</t>
+        </is>
+      </c>
+      <c r="F38" s="191" t="inlineStr">
+        <is>
+          <t>услуга</t>
+        </is>
+      </c>
+      <c r="G38" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="193" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I38" s="193">
+        <f>G38*H38</f>
+        <v/>
+      </c>
+      <c r="J38" s="191" t="inlineStr">
+        <is>
+          <t>Андрей (монтаж дверей)</t>
+        </is>
+      </c>
+      <c r="K38" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L38" s="191" t="inlineStr">
+        <is>
+          <t>Сняли старые двери, расширили проем, выставили по уровню</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A39" s="192" t="n">
+        <v>22</v>
+      </c>
+      <c r="B39" s="191" t="inlineStr">
+        <is>
+          <t>Электрика</t>
+        </is>
+      </c>
+      <c r="C39" s="191" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="D39" s="191" t="inlineStr">
+        <is>
+          <t>Электромонтажные работы под ключ (разводка 32 точек, штробы, щит, счётчик)</t>
+        </is>
+      </c>
+      <c r="E39" s="191" t="inlineStr">
+        <is>
+          <t>РАБОТА-ЭЛЕКТРИКА-32</t>
+        </is>
+      </c>
+      <c r="F39" s="191" t="inlineStr">
+        <is>
+          <t>договор</t>
+        </is>
+      </c>
+      <c r="G39" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="193" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I39" s="193">
+        <f>G39*H39</f>
+        <v/>
+      </c>
+      <c r="J39" s="191" t="inlineStr">
+        <is>
+          <t>Анатолий Кушнарев (бригада)</t>
+        </is>
+      </c>
+      <c r="K39" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L39" s="191" t="inlineStr">
+        <is>
+          <t>Монтаж всей проводки, сборка щита и счётчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A40" s="192" t="n">
+        <v>24</v>
+      </c>
+      <c r="B40" s="191" t="inlineStr">
+        <is>
+          <t>Демонтаж</t>
+        </is>
+      </c>
+      <c r="C40" s="191" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="D40" s="191" t="inlineStr">
+        <is>
+          <t>Зачистка стен/потолка (обои, плитка в зале и спальне), вынос мусора, 1-й слой грунта</t>
+        </is>
+      </c>
+      <c r="E40" s="191" t="inlineStr">
+        <is>
+          <t>ДЕМОНТАЖ-ЗАЧИСТКА-2</t>
+        </is>
+      </c>
+      <c r="F40" s="191" t="inlineStr">
+        <is>
+          <t>смена</t>
+        </is>
+      </c>
+      <c r="G40" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="193" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I40" s="193">
+        <f>G40*H40</f>
+        <v/>
+      </c>
+      <c r="J40" s="191" t="inlineStr">
+        <is>
+          <t>Бригада разнорабочих</t>
+        </is>
+      </c>
+      <c r="K40" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L40" s="191" t="inlineStr">
+        <is>
+          <t>Снятие старых слоев, обеспыливание поверхностей</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A41" s="192" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="191" t="inlineStr">
+        <is>
+          <t>Логистика</t>
+        </is>
+      </c>
+      <c r="C41" s="191" t="inlineStr">
+        <is>
+          <t>Доставка</t>
+        </is>
+      </c>
+      <c r="D41" s="191" t="inlineStr">
+        <is>
+          <t>Грузовое такси / Доставка закупки материалов и сантехники (Лемана — Фрунзе 17)</t>
+        </is>
+      </c>
+      <c r="E41" s="191" t="inlineStr">
+        <is>
+          <t>ГРУЗОТАКСИ-ЛЕРОЙ</t>
+        </is>
+      </c>
+      <c r="F41" s="191" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="G41" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="193" t="n">
+        <v>2100</v>
+      </c>
+      <c r="I41" s="193">
+        <f>G41*H41</f>
+        <v/>
+      </c>
+      <c r="J41" s="191" t="inlineStr">
+        <is>
+          <t>Грузовое такси / Перевозка</t>
+        </is>
+      </c>
+      <c r="K41" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L41" s="191" t="inlineStr">
+        <is>
+          <t>Перевозка партии смесей, керамогранита и ванны</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A42" s="192" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="191" t="inlineStr">
+        <is>
+          <t>Демонтаж</t>
+        </is>
+      </c>
+      <c r="C42" s="191" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="D42" s="191" t="inlineStr">
+        <is>
+          <t>Погрузка в Лемана ПРО, разгрузка и подъём на 5 этаж + демонтаж плитки пола с/у</t>
+        </is>
+      </c>
+      <c r="E42" s="191" t="inlineStr">
+        <is>
+          <t>ПОДЪЕМ-ДЕМОНТАЖ-СУ</t>
+        </is>
+      </c>
+      <c r="F42" s="191" t="inlineStr">
+        <is>
+          <t>смена</t>
+        </is>
+      </c>
+      <c r="G42" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="193" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I42" s="193">
+        <f>G42*H42</f>
+        <v/>
+      </c>
+      <c r="J42" s="191" t="inlineStr">
+        <is>
+          <t>Бригада грузчиков / Разнорабочие</t>
+        </is>
+      </c>
+      <c r="K42" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L42" s="191" t="inlineStr">
+        <is>
+          <t>Разгрузка 1.5 тонн смесей на 5 этаж без лифта</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="206" t="inlineStr"/>
+      <c r="B43" s="206" t="inlineStr">
+        <is>
+          <t>ИТОГО РАБОТЫ И ЛОГИСТИКА:</t>
+        </is>
+      </c>
+      <c r="C43" s="206" t="inlineStr"/>
+      <c r="D43" s="206" t="inlineStr"/>
+      <c r="E43" s="206" t="inlineStr"/>
+      <c r="F43" s="206" t="inlineStr"/>
+      <c r="G43" s="206" t="inlineStr"/>
+      <c r="H43" s="206" t="inlineStr"/>
+      <c r="I43" s="200">
+        <f>SUM(I34:I42)</f>
+        <v/>
+      </c>
+      <c r="J43" s="206" t="inlineStr"/>
+      <c r="K43" s="206" t="inlineStr"/>
+      <c r="L43" s="206" t="inlineStr"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="209" t="inlineStr"/>
+      <c r="B44" s="209" t="inlineStr">
+        <is>
+          <t>🏛 БЛОК 4: ЮРИДИЧЕСКИЕ РАСХОДЫ, ПОШЛИНЫ, ГАЗ, ЭНЕРГОСБЫТ И IT</t>
+        </is>
+      </c>
+      <c r="C44" s="209" t="inlineStr"/>
+      <c r="D44" s="209" t="inlineStr"/>
+      <c r="E44" s="209" t="inlineStr"/>
+      <c r="F44" s="209" t="inlineStr"/>
+      <c r="G44" s="209" t="inlineStr"/>
+      <c r="H44" s="209" t="inlineStr"/>
+      <c r="I44" s="209" t="inlineStr"/>
+      <c r="J44" s="209" t="inlineStr"/>
+      <c r="K44" s="209" t="inlineStr"/>
+      <c r="L44" s="209" t="inlineStr"/>
+    </row>
+    <row r="45" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A45" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" s="191" t="inlineStr">
+        <is>
+          <t>Юр. оформление</t>
+        </is>
+      </c>
+      <c r="C45" s="191" t="inlineStr">
+        <is>
+          <t>Торги</t>
+        </is>
+      </c>
+      <c r="D45" s="191" t="inlineStr">
+        <is>
+          <t>Выпуск квалифицированной ЭЦП (электронная цифровая подпись)</t>
+        </is>
+      </c>
+      <c r="E45" s="191" t="inlineStr">
+        <is>
+          <t>ЭЦП-КОНТУР</t>
+        </is>
+      </c>
+      <c r="F45" s="191" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G45" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="193" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I45" s="193">
+        <f>G45*H45</f>
+        <v/>
+      </c>
+      <c r="J45" s="191" t="inlineStr">
+        <is>
+          <t>УЦ / Контур</t>
+        </is>
+      </c>
+      <c r="K45" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L45" s="191" t="inlineStr">
+        <is>
+          <t>ЭЦП для участия в торгах и регистрации права</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A46" s="192" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" s="191" t="inlineStr">
+        <is>
+          <t>Юр. оформление</t>
+        </is>
+      </c>
+      <c r="C46" s="191" t="inlineStr">
+        <is>
+          <t>Росреестр</t>
+        </is>
+      </c>
+      <c r="D46" s="191" t="inlineStr">
+        <is>
+          <t>Государственная пошлина (регистрация перехода права собственности)</t>
+        </is>
+      </c>
+      <c r="E46" s="191" t="inlineStr">
+        <is>
+          <t>ГОСПОШЛИНА-ПРАВО</t>
+        </is>
+      </c>
+      <c r="F46" s="191" t="inlineStr">
+        <is>
+          <t>платеж</t>
+        </is>
+      </c>
+      <c r="G46" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="193" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I46" s="193">
+        <f>G46*H46</f>
+        <v/>
+      </c>
+      <c r="J46" s="191" t="inlineStr">
+        <is>
+          <t>Росреестр</t>
+        </is>
+      </c>
+      <c r="K46" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L46" s="191" t="inlineStr">
+        <is>
+          <t>Официальная пошлина Росреестра</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A47" s="192" t="n">
+        <v>10</v>
+      </c>
+      <c r="B47" s="191" t="inlineStr">
+        <is>
+          <t>IT / AI</t>
+        </is>
+      </c>
+      <c r="C47" s="191" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="D47" s="191" t="inlineStr">
+        <is>
+          <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 1</t>
+        </is>
+      </c>
+      <c r="E47" s="191" t="inlineStr">
+        <is>
+          <t>OPENROUTER-TRANS-1</t>
+        </is>
+      </c>
+      <c r="F47" s="191" t="inlineStr">
+        <is>
+          <t>платёж</t>
+        </is>
+      </c>
+      <c r="G47" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="193" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I47" s="193">
+        <f>G47*H47</f>
+        <v/>
+      </c>
+      <c r="J47" s="191" t="inlineStr">
+        <is>
+          <t>OpenRouter</t>
+        </is>
+      </c>
+      <c r="K47" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L47" s="191" t="inlineStr">
+        <is>
+          <t>Инфраструктура проектов и аналитика</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A48" s="192" t="n">
+        <v>12</v>
+      </c>
+      <c r="B48" s="191" t="inlineStr">
+        <is>
+          <t>Газ</t>
+        </is>
+      </c>
+      <c r="C48" s="191" t="inlineStr">
+        <is>
+          <t>Безопасность</t>
+        </is>
+      </c>
+      <c r="D48" s="191" t="inlineStr">
+        <is>
+          <t>Акт ВДПО — проверка дымохода и вентканала</t>
+        </is>
+      </c>
+      <c r="E48" s="191" t="inlineStr">
+        <is>
+          <t>ВДПО-АКТ-ВЕНТ</t>
+        </is>
+      </c>
+      <c r="F48" s="191" t="inlineStr">
+        <is>
+          <t>акт</t>
+        </is>
+      </c>
+      <c r="G48" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="193" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I48" s="193">
+        <f>G48*H48</f>
+        <v/>
+      </c>
+      <c r="J48" s="191" t="inlineStr">
+        <is>
+          <t>ВДПО / Газовая служба</t>
+        </is>
+      </c>
+      <c r="K48" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L48" s="191" t="inlineStr">
+        <is>
+          <t>Обязательная проверка тяги для газовой колонки</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A49" s="192" t="n">
+        <v>13</v>
+      </c>
+      <c r="B49" s="191" t="inlineStr">
+        <is>
+          <t>Газ</t>
+        </is>
+      </c>
+      <c r="C49" s="191" t="inlineStr">
+        <is>
+          <t>Коммуналка</t>
+        </is>
+      </c>
+      <c r="D49" s="191" t="inlineStr">
+        <is>
+          <t>Оплата квитанций Тулагоргаз (платежки/техобслуживание)</t>
+        </is>
+      </c>
+      <c r="E49" s="191" t="inlineStr">
+        <is>
+          <t>ТУЛАГОРГАЗ-КВИТАНЦИЯ</t>
+        </is>
+      </c>
+      <c r="F49" s="191" t="inlineStr">
+        <is>
+          <t>платеж</t>
+        </is>
+      </c>
+      <c r="G49" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="193" t="n">
+        <v>800</v>
+      </c>
+      <c r="I49" s="193">
+        <f>G49*H49</f>
+        <v/>
+      </c>
+      <c r="J49" s="191" t="inlineStr">
+        <is>
+          <t>Тулагоргаз</t>
+        </is>
+      </c>
+      <c r="K49" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L49" s="191" t="inlineStr">
+        <is>
+          <t>Погашение начислений газовой службы</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A50" s="192" t="n">
+        <v>21</v>
+      </c>
+      <c r="B50" s="191" t="inlineStr">
+        <is>
+          <t>Энергосбыт</t>
+        </is>
+      </c>
+      <c r="C50" s="191" t="inlineStr">
+        <is>
+          <t>Учёт</t>
+        </is>
+      </c>
+      <c r="D50" s="191" t="inlineStr">
+        <is>
+          <t>Срочный выезд инспектора ТНС энерго Тула (снятие пломбы со старого счётчика)</t>
+        </is>
+      </c>
+      <c r="E50" s="191" t="inlineStr">
+        <is>
+          <t>ТНС-ВЫЕЗД-ПЛОМБА</t>
+        </is>
+      </c>
+      <c r="F50" s="191" t="inlineStr">
+        <is>
+          <t>услуга</t>
+        </is>
+      </c>
+      <c r="G50" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="193" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I50" s="193">
+        <f>G50*H50</f>
+        <v/>
+      </c>
+      <c r="J50" s="191" t="inlineStr">
+        <is>
+          <t>АО "ТНС энерго Тула"</t>
+        </is>
+      </c>
+      <c r="K50" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L50" s="191" t="inlineStr">
+        <is>
+          <t>Срочное снятие пломбы за 5 дней</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A51" s="192" t="n">
+        <v>31</v>
+      </c>
+      <c r="B51" s="191" t="inlineStr">
+        <is>
+          <t>IT / AI</t>
+        </is>
+      </c>
+      <c r="C51" s="191" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="D51" s="191" t="inlineStr">
+        <is>
+          <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 2</t>
+        </is>
+      </c>
+      <c r="E51" s="191" t="inlineStr">
+        <is>
+          <t>OPENROUTER-TRANS-2</t>
+        </is>
+      </c>
+      <c r="F51" s="191" t="inlineStr">
+        <is>
+          <t>платёж</t>
+        </is>
+      </c>
+      <c r="G51" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="193" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I51" s="193">
+        <f>G51*H51</f>
+        <v/>
+      </c>
+      <c r="J51" s="191" t="inlineStr">
+        <is>
+          <t>OpenRouter</t>
+        </is>
+      </c>
+      <c r="K51" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L51" s="191" t="inlineStr">
+        <is>
+          <t>Пополнение баланса API для расчётов и смет</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A52" s="192" t="n">
+        <v>33</v>
+      </c>
+      <c r="B52" s="191" t="inlineStr">
+        <is>
+          <t>Энергосбыт</t>
+        </is>
+      </c>
+      <c r="C52" s="191" t="inlineStr">
+        <is>
+          <t>Учёт</t>
+        </is>
+      </c>
+      <c r="D52" s="191" t="inlineStr">
+        <is>
+          <t>Дистанционная распломбировка старого электросчётчика (согласование)</t>
+        </is>
+      </c>
+      <c r="E52" s="191" t="inlineStr">
+        <is>
+          <t>ТНС-РАСПЛОМБ-ДИСТ</t>
+        </is>
+      </c>
+      <c r="F52" s="191" t="inlineStr">
+        <is>
+          <t>услуга</t>
+        </is>
+      </c>
+      <c r="G52" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="193" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I52" s="193">
+        <f>G52*H52</f>
+        <v/>
+      </c>
+      <c r="J52" s="191" t="inlineStr">
+        <is>
+          <t>ТНС энерго Тула / Энергосбыт</t>
+        </is>
+      </c>
+      <c r="K52" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L52" s="191" t="inlineStr">
+        <is>
+          <t>Официальное согласование замены электроузла</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="206" t="inlineStr"/>
+      <c r="B53" s="206" t="inlineStr">
+        <is>
+          <t>ИТОГО ЮР. РАСХОДЫ, СЛУЖБЫ И IT:</t>
+        </is>
+      </c>
+      <c r="C53" s="206" t="inlineStr"/>
+      <c r="D53" s="206" t="inlineStr"/>
+      <c r="E53" s="206" t="inlineStr"/>
+      <c r="F53" s="206" t="inlineStr"/>
+      <c r="G53" s="206" t="inlineStr"/>
+      <c r="H53" s="206" t="inlineStr"/>
+      <c r="I53" s="200">
+        <f>SUM(I45:I52)</f>
+        <v/>
+      </c>
+      <c r="J53" s="206" t="inlineStr"/>
+      <c r="K53" s="206" t="inlineStr"/>
+      <c r="L53" s="206" t="inlineStr"/>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="210" t="inlineStr"/>
+      <c r="B54" s="210" t="inlineStr">
+        <is>
+          <t>ОБЩИЙ ИТОГО ФАКТ РАСХОДОВ (ДИНАМИЧЕСКИЙ):</t>
+        </is>
+      </c>
+      <c r="C54" s="210" t="inlineStr"/>
+      <c r="D54" s="210" t="inlineStr"/>
+      <c r="E54" s="210" t="inlineStr"/>
+      <c r="F54" s="210" t="inlineStr"/>
+      <c r="G54" s="210" t="inlineStr"/>
+      <c r="H54" s="210" t="inlineStr"/>
+      <c r="I54" s="198">
+        <f>SUBTOTAL(109; I6:I18; I21:I31; I34:I42; I45:I52)</f>
+        <v/>
+      </c>
+      <c r="J54" s="210" t="inlineStr"/>
+      <c r="K54" s="210" t="inlineStr"/>
+      <c r="L54" s="210" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
+++ b/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
@@ -623,7 +623,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1166,6 +1166,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1601,7 +1613,7 @@
         <v/>
       </c>
       <c r="D5" s="118">
-        <f>'Факт расходов'!F46</f>
+        <f>'Факт расходов'!F47</f>
         <v/>
       </c>
       <c r="E5" s="118" t="n">
@@ -1694,7 +1706,7 @@
         <v>23000</v>
       </c>
       <c r="C11" s="46">
-        <f>SUMIF('Факт расходов'!C5:C45, "*Юр.*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*Безопасность*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*IT*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*Электроэнергия*", 'Факт расходов'!F5:F45)</f>
+        <f>SUMIF('Факт расходов'!C5:C46, "*Юр.*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*Безопасность*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*IT*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*Электроэнергия*", 'Факт расходов'!F5:F46)</f>
         <v/>
       </c>
       <c r="D11" s="124">
@@ -1974,7 +1986,7 @@
         <v/>
       </c>
       <c r="C23" s="46">
-        <f>SUMIF('Факт расходов'!C5:C45, "*Демонтаж*", 'Факт расходов'!F5:F45)</f>
+        <f>SUMIF('Факт расходов'!C5:C46, "*Демонтаж*", 'Факт расходов'!F5:F46)</f>
         <v/>
       </c>
       <c r="D23" s="45">
@@ -2007,7 +2019,7 @@
         <v/>
       </c>
       <c r="C24" s="51">
-        <f>SUMIF('Факт расходов'!C5:C45, "*Двери*", 'Факт расходов'!F5:F45)</f>
+        <f>SUMIF('Факт расходов'!C5:C46, "*Двери*", 'Факт расходов'!F5:F46)</f>
         <v/>
       </c>
       <c r="D24" s="50">
@@ -2040,7 +2052,7 @@
         <v/>
       </c>
       <c r="C25" s="46">
-        <f>SUMIF('Факт расходов'!C5:C45, "*Электрика*", 'Факт расходов'!F5:F45)</f>
+        <f>SUMIF('Факт расходов'!C5:C46, "*Электрика*", 'Факт расходов'!F5:F46)</f>
         <v/>
       </c>
       <c r="D25" s="45">
@@ -2073,7 +2085,7 @@
         <v/>
       </c>
       <c r="C26" s="51">
-        <f>SUMIF('Факт расходов'!C5:C45, "*Сантехника*", 'Факт расходов'!F5:F45)</f>
+        <f>SUMIF('Факт расходов'!C5:C46, "*Сантехника*", 'Факт расходов'!F5:F46)</f>
         <v/>
       </c>
       <c r="D26" s="50">
@@ -2105,7 +2117,7 @@
         <v>5000</v>
       </c>
       <c r="C27" s="46">
-        <f>SUMIF('Факт расходов'!C5:C45, "*Газ*", 'Факт расходов'!F5:F45)</f>
+        <f>SUMIF('Факт расходов'!C5:C46, "*Газ*", 'Факт расходов'!F5:F46)</f>
         <v/>
       </c>
       <c r="D27" s="45">
@@ -2170,7 +2182,7 @@
         <v/>
       </c>
       <c r="C29" s="46">
-        <f>SUMIF('Факт расходов'!C5:C45, "*Черновая*", 'Факт расходов'!F5:F45)</f>
+        <f>SUMIF('Факт расходов'!C5:C46, "*Черновая*", 'Факт расходов'!F5:F46)</f>
         <v/>
       </c>
       <c r="D29" s="45">
@@ -2203,7 +2215,7 @@
         <v/>
       </c>
       <c r="C30" s="51">
-        <f>SUMIF('Факт расходов'!C5:C45, "*Чистовая*", 'Факт расходов'!F5:F45)</f>
+        <f>SUMIF('Факт расходов'!C5:C46, "*Чистовая*", 'Факт расходов'!F5:F46)</f>
         <v/>
       </c>
       <c r="D30" s="50">
@@ -2363,7 +2375,7 @@
         <v>10000</v>
       </c>
       <c r="C35" s="46">
-        <f>SUMIF('Факт расходов'!C5:C45, "*Инструмент*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*Расходные*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*Логистика*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*доставка*", 'Факт расходов'!F5:F45)</f>
+        <f>SUMIF('Факт расходов'!C5:C46, "*Инструмент*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*Расходные*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*Логистика*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*доставка*", 'Факт расходов'!F5:F46)</f>
         <v/>
       </c>
       <c r="D35" s="45">
@@ -2395,7 +2407,7 @@
         <v>5000</v>
       </c>
       <c r="C36" s="51">
-        <f>SUMIF('Факт расходов'!C5:C45, "*хозмаг*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*Хоз.*", 'Факт расходов'!F5:F45)+SUMIF('Факт расходов'!C5:C45, "*Оснащение*", 'Факт расходов'!F5:F45)</f>
+        <f>SUMIF('Факт расходов'!C5:C46, "*хозмаг*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*Хоз.*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*Оснащение*", 'Факт расходов'!F5:F46)</f>
         <v/>
       </c>
       <c r="D36" s="50">
@@ -2577,11 +2589,11 @@
         </is>
       </c>
       <c r="B45" s="45">
-        <f>'Факт расходов'!E46</f>
+        <f>'Факт расходов'!E47</f>
         <v/>
       </c>
       <c r="C45" s="45">
-        <f>'Факт расходов'!F46</f>
+        <f>'Факт расходов'!F47</f>
         <v/>
       </c>
       <c r="D45" s="124">
@@ -2664,7 +2676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4750,49 +4762,81 @@
       <c r="M45" s="30" t="n"/>
       <c r="N45" s="30" t="n"/>
     </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="94" t="n"/>
-      <c r="B46" s="94" t="n"/>
-      <c r="C46" s="54" t="n"/>
-      <c r="D46" s="65" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДОВ:</t>
-        </is>
-      </c>
-      <c r="E46" s="55">
-        <f>SUM(E5:E45)</f>
-        <v/>
-      </c>
-      <c r="F46" s="55">
-        <f>SUM(F5:F45)</f>
-        <v/>
-      </c>
-      <c r="G46" s="55">
-        <f>SUM(G5:G45)</f>
-        <v/>
-      </c>
-      <c r="H46" s="104">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="64" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="64" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="C46" s="49" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Работы</t>
+        </is>
+      </c>
+      <c r="D46" s="49" t="inlineStr">
+        <is>
+          <t>Штукатурка (69 м/м² по 500 ₽) и шпаклёвка стен White Box (106 м² по 500 ₽)</t>
+        </is>
+      </c>
+      <c r="E46" s="50" t="n">
+        <v>99700</v>
+      </c>
+      <c r="F46" s="51" t="n">
+        <v>87500</v>
+      </c>
+      <c r="G46" s="47">
+        <f>E46-F46</f>
+        <v/>
+      </c>
+      <c r="H46" s="63">
         <f>IFERROR(G46/E46, 0)</f>
         <v/>
       </c>
-      <c r="I46" s="54" t="n"/>
-      <c r="J46" s="54" t="n"/>
+      <c r="I46" s="49" t="inlineStr">
+        <is>
+          <t>Елена (мастер-отделочник)</t>
+        </is>
+      </c>
+      <c r="J46" s="49" t="inlineStr">
+        <is>
+          <t>Штукатурка 69 м² по 500₽ (34 500₽, частично погонаж/углы/штробы, усреднено) + шпаклёвка стен 106 м² по 500₽ (53 000₽). White Box готов к финишу (экономия 12 200 ₽)</t>
+        </is>
+      </c>
       <c r="K46" s="30" t="n"/>
       <c r="L46" s="30" t="n"/>
       <c r="M46" s="30" t="n"/>
       <c r="N46" s="30" t="n"/>
     </row>
-    <row r="47">
-      <c r="A47" s="30" t="n"/>
-      <c r="B47" s="30" t="n"/>
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="30" t="n"/>
-      <c r="E47" s="30" t="n"/>
-      <c r="F47" s="30" t="n"/>
-      <c r="G47" s="30" t="n"/>
-      <c r="H47" s="30" t="n"/>
-      <c r="I47" s="30" t="n"/>
-      <c r="J47" s="30" t="n"/>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="94" t="n"/>
+      <c r="B47" s="94" t="n"/>
+      <c r="C47" s="54" t="n"/>
+      <c r="D47" s="65" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДОВ:</t>
+        </is>
+      </c>
+      <c r="E47" s="55">
+        <f>SUM(E5:E46)</f>
+        <v/>
+      </c>
+      <c r="F47" s="55">
+        <f>SUM(F5:F46)</f>
+        <v/>
+      </c>
+      <c r="G47" s="55">
+        <f>SUM(G5:G46)</f>
+        <v/>
+      </c>
+      <c r="H47" s="104">
+        <f>IFERROR(G47/E47, 0)</f>
+        <v/>
+      </c>
+      <c r="I47" s="54" t="n"/>
+      <c r="J47" s="54" t="n"/>
       <c r="K47" s="30" t="n"/>
       <c r="L47" s="30" t="n"/>
       <c r="M47" s="30" t="n"/>
@@ -5085,6 +5129,22 @@
       <c r="L65" s="140" t="n"/>
       <c r="M65" s="140" t="n"/>
       <c r="N65" s="140" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="140" t="n"/>
+      <c r="B66" s="140" t="n"/>
+      <c r="C66" s="140" t="n"/>
+      <c r="D66" s="140" t="n"/>
+      <c r="E66" s="140" t="n"/>
+      <c r="F66" s="140" t="n"/>
+      <c r="G66" s="140" t="n"/>
+      <c r="H66" s="140" t="n"/>
+      <c r="I66" s="140" t="n"/>
+      <c r="J66" s="140" t="n"/>
+      <c r="K66" s="140" t="n"/>
+      <c r="L66" s="140" t="n"/>
+      <c r="M66" s="140" t="n"/>
+      <c r="N66" s="140" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5582,31 +5642,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F172A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.66666666666667" customWidth="1" min="1" max="1"/>
-    <col width="21.33333333333333" customWidth="1" min="2" max="2"/>
-    <col width="21.33333333333333" customWidth="1" min="3" max="3"/>
-    <col width="45.33333333333334" customWidth="1" min="4" max="4"/>
+    <col width="8.666666666666666" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="41.33333333333334" customWidth="1" min="4" max="4"/>
     <col width="18.66666666666667" customWidth="1" min="5" max="5"/>
-    <col width="10.66666666666667" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15.33333333333333" customWidth="1" min="8" max="8"/>
+    <col width="9.333333333333334" customWidth="1" min="6" max="6"/>
+    <col width="8.666666666666666" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16.66666666666667" customWidth="1" min="9" max="9"/>
-    <col width="29.33333333333333" customWidth="1" min="10" max="10"/>
-    <col width="14.66666666666667" customWidth="1" min="11" max="11"/>
-    <col width="34.66666666666666" customWidth="1" min="12" max="12"/>
+    <col width="25.33333333333333" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="38" t="inlineStr">
         <is>
-          <t>ГЕНЕРАЛЬНАЯ МАТРИЦА БЮДЖЕТА И КОМПЛЕКТАЦИИ (316 021,27 ₽)</t>
+          <t>ГЕНЕРАЛЬНАЯ МАТРИЦА БЮДЖЕТА И КОМПЛЕКТАЦИИ (403 521,27 ₽)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -5621,10 +5680,10 @@
       <c r="K1" t="inlineStr"/>
       <c r="L1" t="inlineStr"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Полная структура расходов Фрунзе 17 | Точная сверка с листом «Факт расходов» (1-в-1 до копейки, все 41 позиция)</t>
+          <t>Полная структура расходов Фрунзе 17 | Точная сверка с листом «Факт расходов» (1-в-1 до копейки, все 42 позиции)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -5639,7 +5698,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3">
       <c r="A3" s="39" t="inlineStr">
         <is>
           <t>💡 Используй слева значки [-] и [+] для сворачивания блоков (Материалы, Работы, Юр. расходы), либо фильтр по Зоне</t>
@@ -5657,69 +5716,69 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
     </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="204" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="162" t="inlineStr">
         <is>
           <t>№ в Факте</t>
         </is>
       </c>
-      <c r="B4" s="204" t="inlineStr">
+      <c r="B4" s="162" t="inlineStr">
         <is>
           <t>Зона / Помещение</t>
         </is>
       </c>
-      <c r="C4" s="204" t="inlineStr">
+      <c r="C4" s="162" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="D4" s="204" t="inlineStr">
+      <c r="D4" s="162" t="inlineStr">
         <is>
           <t>Наименование расхода</t>
         </is>
       </c>
-      <c r="E4" s="204" t="inlineStr">
+      <c r="E4" s="162" t="inlineStr">
         <is>
           <t>Артикул / Код</t>
         </is>
       </c>
-      <c r="F4" s="204" t="inlineStr">
+      <c r="F4" s="162" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="G4" s="204" t="inlineStr">
+      <c r="G4" s="162" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="H4" s="204" t="inlineStr">
+      <c r="H4" s="162" t="inlineStr">
         <is>
           <t>Цена / ед. (₽)</t>
         </is>
       </c>
-      <c r="I4" s="204" t="inlineStr">
+      <c r="I4" s="162" t="inlineStr">
         <is>
           <t>Сумма (₽)</t>
         </is>
       </c>
-      <c r="J4" s="204" t="inlineStr">
+      <c r="J4" s="162" t="inlineStr">
         <is>
           <t>Поставщик / Подрядчик</t>
         </is>
       </c>
-      <c r="K4" s="204" t="inlineStr">
+      <c r="K4" s="162" t="inlineStr">
         <is>
           <t>Ссылка / Документ</t>
         </is>
       </c>
-      <c r="L4" s="204" t="inlineStr">
+      <c r="L4" s="162" t="inlineStr">
         <is>
           <t>Примечание (Фрунзе 17)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
+    <row r="5">
       <c r="A5" s="205" t="inlineStr"/>
       <c r="B5" s="205" t="inlineStr">
         <is>
@@ -5737,7 +5796,7 @@
       <c r="K5" s="205" t="inlineStr"/>
       <c r="L5" s="205" t="inlineStr"/>
     </row>
-    <row r="6" outlineLevel="1" ht="20" customHeight="1">
+    <row r="6" outlineLevel="1">
       <c r="A6" s="192" t="n">
         <v>8</v>
       </c>
@@ -5792,7 +5851,7 @@
         </is>
       </c>
     </row>
-    <row r="7" outlineLevel="1" ht="20" customHeight="1">
+    <row r="7" outlineLevel="1">
       <c r="A7" s="192" t="n">
         <v>9</v>
       </c>
@@ -5847,7 +5906,7 @@
         </is>
       </c>
     </row>
-    <row r="8" outlineLevel="1" ht="20" customHeight="1">
+    <row r="8" outlineLevel="1">
       <c r="A8" s="192" t="n">
         <v>25</v>
       </c>
@@ -5902,7 +5961,7 @@
         </is>
       </c>
     </row>
-    <row r="9" outlineLevel="1" ht="20" customHeight="1">
+    <row r="9" outlineLevel="1">
       <c r="A9" s="192" t="n">
         <v>26</v>
       </c>
@@ -5957,7 +6016,7 @@
         </is>
       </c>
     </row>
-    <row r="10" outlineLevel="1" ht="20" customHeight="1">
+    <row r="10" outlineLevel="1">
       <c r="A10" s="192" t="n">
         <v>28</v>
       </c>
@@ -6012,7 +6071,7 @@
         </is>
       </c>
     </row>
-    <row r="11" outlineLevel="1" ht="20" customHeight="1">
+    <row r="11" outlineLevel="1">
       <c r="A11" s="192" t="n">
         <v>30</v>
       </c>
@@ -6067,7 +6126,7 @@
         </is>
       </c>
     </row>
-    <row r="12" outlineLevel="1" ht="20" customHeight="1">
+    <row r="12" outlineLevel="1">
       <c r="A12" s="192" t="n">
         <v>32</v>
       </c>
@@ -6122,7 +6181,7 @@
         </is>
       </c>
     </row>
-    <row r="13" outlineLevel="1" ht="20" customHeight="1">
+    <row r="13" outlineLevel="1">
       <c r="A13" s="192" t="n">
         <v>34</v>
       </c>
@@ -6177,7 +6236,7 @@
         </is>
       </c>
     </row>
-    <row r="14" outlineLevel="1" ht="20" customHeight="1">
+    <row r="14" outlineLevel="1">
       <c r="A14" s="192" t="n">
         <v>35</v>
       </c>
@@ -6232,7 +6291,7 @@
         </is>
       </c>
     </row>
-    <row r="15" outlineLevel="1" ht="20" customHeight="1">
+    <row r="15" outlineLevel="1">
       <c r="A15" s="192" t="n">
         <v>36</v>
       </c>
@@ -6287,7 +6346,7 @@
         </is>
       </c>
     </row>
-    <row r="16" outlineLevel="1" ht="20" customHeight="1">
+    <row r="16" outlineLevel="1">
       <c r="A16" s="192" t="n">
         <v>37</v>
       </c>
@@ -6342,7 +6401,7 @@
         </is>
       </c>
     </row>
-    <row r="17" outlineLevel="1" ht="20" customHeight="1">
+    <row r="17" outlineLevel="1">
       <c r="A17" s="192" t="n">
         <v>38</v>
       </c>
@@ -6397,7 +6456,7 @@
         </is>
       </c>
     </row>
-    <row r="18" outlineLevel="1" ht="20" customHeight="1">
+    <row r="18" outlineLevel="1">
       <c r="A18" s="192" t="n">
         <v>39</v>
       </c>
@@ -6452,28 +6511,28 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="206" t="inlineStr"/>
-      <c r="B19" s="206" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="211" t="inlineStr"/>
+      <c r="B19" s="211" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ ЛЕМАНА ПРО (ПО ЧЕКАМ):</t>
         </is>
       </c>
-      <c r="C19" s="206" t="inlineStr"/>
-      <c r="D19" s="206" t="inlineStr"/>
-      <c r="E19" s="206" t="inlineStr"/>
-      <c r="F19" s="206" t="inlineStr"/>
-      <c r="G19" s="206" t="inlineStr"/>
-      <c r="H19" s="206" t="inlineStr"/>
-      <c r="I19" s="200">
+      <c r="C19" s="211" t="inlineStr"/>
+      <c r="D19" s="211" t="inlineStr"/>
+      <c r="E19" s="211" t="inlineStr"/>
+      <c r="F19" s="211" t="inlineStr"/>
+      <c r="G19" s="211" t="inlineStr"/>
+      <c r="H19" s="211" t="inlineStr"/>
+      <c r="I19" s="212">
         <f>SUM(I6:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="206" t="inlineStr"/>
-      <c r="K19" s="206" t="inlineStr"/>
-      <c r="L19" s="206" t="inlineStr"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
+      <c r="J19" s="211" t="inlineStr"/>
+      <c r="K19" s="211" t="inlineStr"/>
+      <c r="L19" s="211" t="inlineStr"/>
+    </row>
+    <row r="20">
       <c r="A20" s="207" t="inlineStr"/>
       <c r="B20" s="207" t="inlineStr">
         <is>
@@ -6491,7 +6550,7 @@
       <c r="K20" s="207" t="inlineStr"/>
       <c r="L20" s="207" t="inlineStr"/>
     </row>
-    <row r="21" outlineLevel="1" ht="20" customHeight="1">
+    <row r="21" outlineLevel="1">
       <c r="A21" s="192" t="n">
         <v>6</v>
       </c>
@@ -6546,7 +6605,7 @@
         </is>
       </c>
     </row>
-    <row r="22" outlineLevel="1" ht="20" customHeight="1">
+    <row r="22" outlineLevel="1">
       <c r="A22" s="192" t="n">
         <v>11</v>
       </c>
@@ -6601,7 +6660,7 @@
         </is>
       </c>
     </row>
-    <row r="23" outlineLevel="1" ht="20" customHeight="1">
+    <row r="23" outlineLevel="1">
       <c r="A23" s="192" t="n">
         <v>14</v>
       </c>
@@ -6656,7 +6715,7 @@
         </is>
       </c>
     </row>
-    <row r="24" outlineLevel="1" ht="20" customHeight="1">
+    <row r="24" outlineLevel="1">
       <c r="A24" s="192" t="n">
         <v>15</v>
       </c>
@@ -6711,7 +6770,7 @@
         </is>
       </c>
     </row>
-    <row r="25" outlineLevel="1" ht="20" customHeight="1">
+    <row r="25" outlineLevel="1">
       <c r="A25" s="192" t="n">
         <v>16</v>
       </c>
@@ -6766,7 +6825,7 @@
         </is>
       </c>
     </row>
-    <row r="26" outlineLevel="1" ht="20" customHeight="1">
+    <row r="26" outlineLevel="1">
       <c r="A26" s="192" t="n">
         <v>17</v>
       </c>
@@ -6821,7 +6880,7 @@
         </is>
       </c>
     </row>
-    <row r="27" outlineLevel="1" ht="20" customHeight="1">
+    <row r="27" outlineLevel="1">
       <c r="A27" s="192" t="n">
         <v>19</v>
       </c>
@@ -6876,7 +6935,7 @@
         </is>
       </c>
     </row>
-    <row r="28" outlineLevel="1" ht="20" customHeight="1">
+    <row r="28" outlineLevel="1">
       <c r="A28" s="192" t="n">
         <v>20</v>
       </c>
@@ -6931,7 +6990,7 @@
         </is>
       </c>
     </row>
-    <row r="29" outlineLevel="1" ht="20" customHeight="1">
+    <row r="29" outlineLevel="1">
       <c r="A29" s="192" t="n">
         <v>23</v>
       </c>
@@ -6986,7 +7045,7 @@
         </is>
       </c>
     </row>
-    <row r="30" outlineLevel="1" ht="20" customHeight="1">
+    <row r="30" outlineLevel="1">
       <c r="A30" s="192" t="n">
         <v>27</v>
       </c>
@@ -7041,7 +7100,7 @@
         </is>
       </c>
     </row>
-    <row r="31" outlineLevel="1" ht="20" customHeight="1">
+    <row r="31" outlineLevel="1">
       <c r="A31" s="192" t="n">
         <v>29</v>
       </c>
@@ -7096,32 +7155,32 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="206" t="inlineStr"/>
-      <c r="B32" s="206" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="211" t="inlineStr"/>
+      <c r="B32" s="211" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ СПЕЦПОСТАВЩИКОВ:</t>
         </is>
       </c>
-      <c r="C32" s="206" t="inlineStr"/>
-      <c r="D32" s="206" t="inlineStr"/>
-      <c r="E32" s="206" t="inlineStr"/>
-      <c r="F32" s="206" t="inlineStr"/>
-      <c r="G32" s="206" t="inlineStr"/>
-      <c r="H32" s="206" t="inlineStr"/>
-      <c r="I32" s="200">
+      <c r="C32" s="211" t="inlineStr"/>
+      <c r="D32" s="211" t="inlineStr"/>
+      <c r="E32" s="211" t="inlineStr"/>
+      <c r="F32" s="211" t="inlineStr"/>
+      <c r="G32" s="211" t="inlineStr"/>
+      <c r="H32" s="211" t="inlineStr"/>
+      <c r="I32" s="212">
         <f>SUM(I21:I31)</f>
         <v/>
       </c>
-      <c r="J32" s="206" t="inlineStr"/>
-      <c r="K32" s="206" t="inlineStr"/>
-      <c r="L32" s="206" t="inlineStr"/>
-    </row>
-    <row r="33" ht="24" customHeight="1">
+      <c r="J32" s="211" t="inlineStr"/>
+      <c r="K32" s="211" t="inlineStr"/>
+      <c r="L32" s="211" t="inlineStr"/>
+    </row>
+    <row r="33">
       <c r="A33" s="208" t="inlineStr"/>
       <c r="B33" s="208" t="inlineStr">
         <is>
-          <t>👷‍♂️ БЛОК 3: РАБОТЫ МАСТЕРОВ, ДЕМОНТАЖ, МОНТАЖ И ЛОГИСТИКА</t>
+          <t>👷‍♂️ БЛОК 3: РАБОТЫ МАСТЕРОВ, ОТДЕЛКА, ДЕМОНТАЖ И ЛОГИСТИКА</t>
         </is>
       </c>
       <c r="C33" s="208" t="inlineStr"/>
@@ -7135,7 +7194,7 @@
       <c r="K33" s="208" t="inlineStr"/>
       <c r="L33" s="208" t="inlineStr"/>
     </row>
-    <row r="34" outlineLevel="1" ht="20" customHeight="1">
+    <row r="34" outlineLevel="1">
       <c r="A34" s="192" t="n">
         <v>3</v>
       </c>
@@ -7190,7 +7249,7 @@
         </is>
       </c>
     </row>
-    <row r="35" outlineLevel="1" ht="20" customHeight="1">
+    <row r="35" outlineLevel="1">
       <c r="A35" s="192" t="n">
         <v>4</v>
       </c>
@@ -7245,7 +7304,7 @@
         </is>
       </c>
     </row>
-    <row r="36" outlineLevel="1" ht="20" customHeight="1">
+    <row r="36" outlineLevel="1">
       <c r="A36" s="192" t="n">
         <v>5</v>
       </c>
@@ -7300,7 +7359,7 @@
         </is>
       </c>
     </row>
-    <row r="37" outlineLevel="1" ht="20" customHeight="1">
+    <row r="37" outlineLevel="1">
       <c r="A37" s="192" t="n">
         <v>7</v>
       </c>
@@ -7355,7 +7414,7 @@
         </is>
       </c>
     </row>
-    <row r="38" outlineLevel="1" ht="20" customHeight="1">
+    <row r="38" outlineLevel="1">
       <c r="A38" s="192" t="n">
         <v>18</v>
       </c>
@@ -7410,7 +7469,7 @@
         </is>
       </c>
     </row>
-    <row r="39" outlineLevel="1" ht="20" customHeight="1">
+    <row r="39" outlineLevel="1">
       <c r="A39" s="192" t="n">
         <v>22</v>
       </c>
@@ -7465,7 +7524,7 @@
         </is>
       </c>
     </row>
-    <row r="40" outlineLevel="1" ht="20" customHeight="1">
+    <row r="40" outlineLevel="1">
       <c r="A40" s="192" t="n">
         <v>24</v>
       </c>
@@ -7520,7 +7579,7 @@
         </is>
       </c>
     </row>
-    <row r="41" outlineLevel="1" ht="20" customHeight="1">
+    <row r="41" outlineLevel="1">
       <c r="A41" s="192" t="n">
         <v>40</v>
       </c>
@@ -7575,7 +7634,7 @@
         </is>
       </c>
     </row>
-    <row r="42" outlineLevel="1" ht="20" customHeight="1">
+    <row r="42" outlineLevel="1">
       <c r="A42" s="192" t="n">
         <v>41</v>
       </c>
@@ -7630,134 +7689,134 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="206" t="inlineStr"/>
-      <c r="B43" s="206" t="inlineStr">
+    <row r="43" outlineLevel="1">
+      <c r="A43" s="192" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="191" t="inlineStr">
+        <is>
+          <t>Черновые стены</t>
+        </is>
+      </c>
+      <c r="C43" s="191" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="D43" s="191" t="inlineStr">
+        <is>
+          <t>Штукатурка (69 м² по 500 ₽) и шпаклёвка стен White Box (106 м² по 500 ₽)</t>
+        </is>
+      </c>
+      <c r="E43" s="191" t="inlineStr">
+        <is>
+          <t>ОТДЕЛКА-СТЕН-ЕЛЕНА</t>
+        </is>
+      </c>
+      <c r="F43" s="191" t="inlineStr">
+        <is>
+          <t>комплекс</t>
+        </is>
+      </c>
+      <c r="G43" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="193" t="n">
+        <v>87500</v>
+      </c>
+      <c r="I43" s="193">
+        <f>G43*H43</f>
+        <v/>
+      </c>
+      <c r="J43" s="191" t="inlineStr">
+        <is>
+          <t>Елена (мастер-отделочник)</t>
+        </is>
+      </c>
+      <c r="K43" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L43" s="191" t="inlineStr">
+        <is>
+          <t>Штукатурка 69 м² + шпаклёвка стен 106 м² по 500₽. White Box под ключ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="211" t="inlineStr"/>
+      <c r="B44" s="211" t="inlineStr">
         <is>
           <t>ИТОГО РАБОТЫ И ЛОГИСТИКА:</t>
         </is>
       </c>
-      <c r="C43" s="206" t="inlineStr"/>
-      <c r="D43" s="206" t="inlineStr"/>
-      <c r="E43" s="206" t="inlineStr"/>
-      <c r="F43" s="206" t="inlineStr"/>
-      <c r="G43" s="206" t="inlineStr"/>
-      <c r="H43" s="206" t="inlineStr"/>
-      <c r="I43" s="200">
-        <f>SUM(I34:I42)</f>
-        <v/>
-      </c>
-      <c r="J43" s="206" t="inlineStr"/>
-      <c r="K43" s="206" t="inlineStr"/>
-      <c r="L43" s="206" t="inlineStr"/>
-    </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="209" t="inlineStr"/>
-      <c r="B44" s="209" t="inlineStr">
+      <c r="C44" s="211" t="inlineStr"/>
+      <c r="D44" s="211" t="inlineStr"/>
+      <c r="E44" s="211" t="inlineStr"/>
+      <c r="F44" s="211" t="inlineStr"/>
+      <c r="G44" s="211" t="inlineStr"/>
+      <c r="H44" s="211" t="inlineStr"/>
+      <c r="I44" s="212">
+        <f>SUM(I34:I43)</f>
+        <v/>
+      </c>
+      <c r="J44" s="211" t="inlineStr"/>
+      <c r="K44" s="211" t="inlineStr"/>
+      <c r="L44" s="211" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="209" t="inlineStr"/>
+      <c r="B45" s="209" t="inlineStr">
         <is>
           <t>🏛 БЛОК 4: ЮРИДИЧЕСКИЕ РАСХОДЫ, ПОШЛИНЫ, ГАЗ, ЭНЕРГОСБЫТ И IT</t>
         </is>
       </c>
-      <c r="C44" s="209" t="inlineStr"/>
-      <c r="D44" s="209" t="inlineStr"/>
-      <c r="E44" s="209" t="inlineStr"/>
-      <c r="F44" s="209" t="inlineStr"/>
-      <c r="G44" s="209" t="inlineStr"/>
-      <c r="H44" s="209" t="inlineStr"/>
-      <c r="I44" s="209" t="inlineStr"/>
-      <c r="J44" s="209" t="inlineStr"/>
-      <c r="K44" s="209" t="inlineStr"/>
-      <c r="L44" s="209" t="inlineStr"/>
-    </row>
-    <row r="45" outlineLevel="1" ht="20" customHeight="1">
-      <c r="A45" s="192" t="n">
+      <c r="C45" s="209" t="inlineStr"/>
+      <c r="D45" s="209" t="inlineStr"/>
+      <c r="E45" s="209" t="inlineStr"/>
+      <c r="F45" s="209" t="inlineStr"/>
+      <c r="G45" s="209" t="inlineStr"/>
+      <c r="H45" s="209" t="inlineStr"/>
+      <c r="I45" s="209" t="inlineStr"/>
+      <c r="J45" s="209" t="inlineStr"/>
+      <c r="K45" s="209" t="inlineStr"/>
+      <c r="L45" s="209" t="inlineStr"/>
+    </row>
+    <row r="46" outlineLevel="1">
+      <c r="A46" s="192" t="n">
         <v>1</v>
       </c>
-      <c r="B45" s="191" t="inlineStr">
+      <c r="B46" s="191" t="inlineStr">
         <is>
           <t>Юр. оформление</t>
         </is>
       </c>
-      <c r="C45" s="191" t="inlineStr">
+      <c r="C46" s="191" t="inlineStr">
         <is>
           <t>Торги</t>
         </is>
       </c>
-      <c r="D45" s="191" t="inlineStr">
+      <c r="D46" s="191" t="inlineStr">
         <is>
           <t>Выпуск квалифицированной ЭЦП (электронная цифровая подпись)</t>
         </is>
       </c>
-      <c r="E45" s="191" t="inlineStr">
+      <c r="E46" s="191" t="inlineStr">
         <is>
           <t>ЭЦП-КОНТУР</t>
         </is>
       </c>
-      <c r="F45" s="191" t="inlineStr">
+      <c r="F46" s="191" t="inlineStr">
         <is>
           <t>шт.</t>
-        </is>
-      </c>
-      <c r="G45" s="192" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="193" t="n">
-        <v>7000</v>
-      </c>
-      <c r="I45" s="193">
-        <f>G45*H45</f>
-        <v/>
-      </c>
-      <c r="J45" s="191" t="inlineStr">
-        <is>
-          <t>УЦ / Контур</t>
-        </is>
-      </c>
-      <c r="K45" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L45" s="191" t="inlineStr">
-        <is>
-          <t>ЭЦП для участия в торгах и регистрации права</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" outlineLevel="1" ht="20" customHeight="1">
-      <c r="A46" s="192" t="n">
-        <v>2</v>
-      </c>
-      <c r="B46" s="191" t="inlineStr">
-        <is>
-          <t>Юр. оформление</t>
-        </is>
-      </c>
-      <c r="C46" s="191" t="inlineStr">
-        <is>
-          <t>Росреестр</t>
-        </is>
-      </c>
-      <c r="D46" s="191" t="inlineStr">
-        <is>
-          <t>Государственная пошлина (регистрация перехода права собственности)</t>
-        </is>
-      </c>
-      <c r="E46" s="191" t="inlineStr">
-        <is>
-          <t>ГОСПОШЛИНА-ПРАВО</t>
-        </is>
-      </c>
-      <c r="F46" s="191" t="inlineStr">
-        <is>
-          <t>платеж</t>
         </is>
       </c>
       <c r="G46" s="192" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="193" t="n">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="I46" s="193">
         <f>G46*H46</f>
@@ -7765,54 +7824,54 @@
       </c>
       <c r="J46" s="191" t="inlineStr">
         <is>
+          <t>УЦ / Контур</t>
+        </is>
+      </c>
+      <c r="K46" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L46" s="191" t="inlineStr">
+        <is>
+          <t>ЭЦП для участия в торгах и регистрации права</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" outlineLevel="1">
+      <c r="A47" s="192" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="191" t="inlineStr">
+        <is>
+          <t>Юр. оформление</t>
+        </is>
+      </c>
+      <c r="C47" s="191" t="inlineStr">
+        <is>
           <t>Росреестр</t>
         </is>
       </c>
-      <c r="K46" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L46" s="191" t="inlineStr">
-        <is>
-          <t>Официальная пошлина Росреестра</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" outlineLevel="1" ht="20" customHeight="1">
-      <c r="A47" s="192" t="n">
-        <v>10</v>
-      </c>
-      <c r="B47" s="191" t="inlineStr">
-        <is>
-          <t>IT / AI</t>
-        </is>
-      </c>
-      <c r="C47" s="191" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
       <c r="D47" s="191" t="inlineStr">
         <is>
-          <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 1</t>
+          <t>Государственная пошлина (регистрация перехода права собственности)</t>
         </is>
       </c>
       <c r="E47" s="191" t="inlineStr">
         <is>
-          <t>OPENROUTER-TRANS-1</t>
+          <t>ГОСПОШЛИНА-ПРАВО</t>
         </is>
       </c>
       <c r="F47" s="191" t="inlineStr">
         <is>
-          <t>платёж</t>
+          <t>платеж</t>
         </is>
       </c>
       <c r="G47" s="192" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="193" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="I47" s="193">
         <f>G47*H47</f>
@@ -7820,7 +7879,7 @@
       </c>
       <c r="J47" s="191" t="inlineStr">
         <is>
-          <t>OpenRouter</t>
+          <t>Росреестр</t>
         </is>
       </c>
       <c r="K47" s="194" t="inlineStr">
@@ -7830,44 +7889,44 @@
       </c>
       <c r="L47" s="191" t="inlineStr">
         <is>
-          <t>Инфраструктура проектов и аналитика</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" outlineLevel="1" ht="20" customHeight="1">
+          <t>Официальная пошлина Росреестра</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" outlineLevel="1">
       <c r="A48" s="192" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B48" s="191" t="inlineStr">
         <is>
-          <t>Газ</t>
+          <t>IT / AI</t>
         </is>
       </c>
       <c r="C48" s="191" t="inlineStr">
         <is>
-          <t>Безопасность</t>
+          <t>Инфраструктура</t>
         </is>
       </c>
       <c r="D48" s="191" t="inlineStr">
         <is>
-          <t>Акт ВДПО — проверка дымохода и вентканала</t>
+          <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 1</t>
         </is>
       </c>
       <c r="E48" s="191" t="inlineStr">
         <is>
-          <t>ВДПО-АКТ-ВЕНТ</t>
+          <t>OPENROUTER-TRANS-1</t>
         </is>
       </c>
       <c r="F48" s="191" t="inlineStr">
         <is>
-          <t>акт</t>
+          <t>платёж</t>
         </is>
       </c>
       <c r="G48" s="192" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="193" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="I48" s="193">
         <f>G48*H48</f>
@@ -7875,7 +7934,7 @@
       </c>
       <c r="J48" s="191" t="inlineStr">
         <is>
-          <t>ВДПО / Газовая служба</t>
+          <t>OpenRouter</t>
         </is>
       </c>
       <c r="K48" s="194" t="inlineStr">
@@ -7885,13 +7944,13 @@
       </c>
       <c r="L48" s="191" t="inlineStr">
         <is>
-          <t>Обязательная проверка тяги для газовой колонки</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" outlineLevel="1" ht="20" customHeight="1">
+          <t>Инфраструктура проектов и аналитика</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" outlineLevel="1">
       <c r="A49" s="192" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B49" s="191" t="inlineStr">
         <is>
@@ -7900,29 +7959,29 @@
       </c>
       <c r="C49" s="191" t="inlineStr">
         <is>
-          <t>Коммуналка</t>
+          <t>Безопасность</t>
         </is>
       </c>
       <c r="D49" s="191" t="inlineStr">
         <is>
-          <t>Оплата квитанций Тулагоргаз (платежки/техобслуживание)</t>
+          <t>Акт ВДПО — проверка дымохода и вентканала</t>
         </is>
       </c>
       <c r="E49" s="191" t="inlineStr">
         <is>
-          <t>ТУЛАГОРГАЗ-КВИТАНЦИЯ</t>
+          <t>ВДПО-АКТ-ВЕНТ</t>
         </is>
       </c>
       <c r="F49" s="191" t="inlineStr">
         <is>
-          <t>платеж</t>
+          <t>акт</t>
         </is>
       </c>
       <c r="G49" s="192" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="193" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="I49" s="193">
         <f>G49*H49</f>
@@ -7930,7 +7989,7 @@
       </c>
       <c r="J49" s="191" t="inlineStr">
         <is>
-          <t>Тулагоргаз</t>
+          <t>ВДПО / Газовая служба</t>
         </is>
       </c>
       <c r="K49" s="194" t="inlineStr">
@@ -7940,44 +7999,44 @@
       </c>
       <c r="L49" s="191" t="inlineStr">
         <is>
-          <t>Погашение начислений газовой службы</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" outlineLevel="1" ht="20" customHeight="1">
+          <t>Обязательная проверка тяги для газовой колонки</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" outlineLevel="1">
       <c r="A50" s="192" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B50" s="191" t="inlineStr">
         <is>
-          <t>Энергосбыт</t>
+          <t>Газ</t>
         </is>
       </c>
       <c r="C50" s="191" t="inlineStr">
         <is>
-          <t>Учёт</t>
+          <t>Коммуналка</t>
         </is>
       </c>
       <c r="D50" s="191" t="inlineStr">
         <is>
-          <t>Срочный выезд инспектора ТНС энерго Тула (снятие пломбы со старого счётчика)</t>
+          <t>Оплата квитанций Тулагоргаз (платежки/техобслуживание)</t>
         </is>
       </c>
       <c r="E50" s="191" t="inlineStr">
         <is>
-          <t>ТНС-ВЫЕЗД-ПЛОМБА</t>
+          <t>ТУЛАГОРГАЗ-КВИТАНЦИЯ</t>
         </is>
       </c>
       <c r="F50" s="191" t="inlineStr">
         <is>
-          <t>услуга</t>
+          <t>платеж</t>
         </is>
       </c>
       <c r="G50" s="192" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="193" t="n">
-        <v>2500</v>
+        <v>800</v>
       </c>
       <c r="I50" s="193">
         <f>G50*H50</f>
@@ -7985,7 +8044,7 @@
       </c>
       <c r="J50" s="191" t="inlineStr">
         <is>
-          <t>АО "ТНС энерго Тула"</t>
+          <t>Тулагоргаз</t>
         </is>
       </c>
       <c r="K50" s="194" t="inlineStr">
@@ -7995,37 +8054,37 @@
       </c>
       <c r="L50" s="191" t="inlineStr">
         <is>
-          <t>Срочное снятие пломбы за 5 дней</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" outlineLevel="1" ht="20" customHeight="1">
+          <t>Погашение начислений газовой службы</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1">
       <c r="A51" s="192" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B51" s="191" t="inlineStr">
         <is>
-          <t>IT / AI</t>
+          <t>Энергосбыт</t>
         </is>
       </c>
       <c r="C51" s="191" t="inlineStr">
         <is>
-          <t>Инфраструктура</t>
+          <t>Учёт</t>
         </is>
       </c>
       <c r="D51" s="191" t="inlineStr">
         <is>
-          <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 2</t>
+          <t>Срочный выезд инспектора ТНС энерго Тула (снятие пломбы со старого счётчика)</t>
         </is>
       </c>
       <c r="E51" s="191" t="inlineStr">
         <is>
-          <t>OPENROUTER-TRANS-2</t>
+          <t>ТНС-ВЫЕЗД-ПЛОМБА</t>
         </is>
       </c>
       <c r="F51" s="191" t="inlineStr">
         <is>
-          <t>платёж</t>
+          <t>услуга</t>
         </is>
       </c>
       <c r="G51" s="192" t="n">
@@ -8040,7 +8099,7 @@
       </c>
       <c r="J51" s="191" t="inlineStr">
         <is>
-          <t>OpenRouter</t>
+          <t>АО "ТНС энерго Тула"</t>
         </is>
       </c>
       <c r="K51" s="194" t="inlineStr">
@@ -8050,44 +8109,44 @@
       </c>
       <c r="L51" s="191" t="inlineStr">
         <is>
-          <t>Пополнение баланса API для расчётов и смет</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" outlineLevel="1" ht="20" customHeight="1">
+          <t>Срочное снятие пломбы за 5 дней</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" outlineLevel="1">
       <c r="A52" s="192" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B52" s="191" t="inlineStr">
         <is>
-          <t>Энергосбыт</t>
+          <t>IT / AI</t>
         </is>
       </c>
       <c r="C52" s="191" t="inlineStr">
         <is>
-          <t>Учёт</t>
+          <t>Инфраструктура</t>
         </is>
       </c>
       <c r="D52" s="191" t="inlineStr">
         <is>
-          <t>Дистанционная распломбировка старого электросчётчика (согласование)</t>
+          <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 2</t>
         </is>
       </c>
       <c r="E52" s="191" t="inlineStr">
         <is>
-          <t>ТНС-РАСПЛОМБ-ДИСТ</t>
+          <t>OPENROUTER-TRANS-2</t>
         </is>
       </c>
       <c r="F52" s="191" t="inlineStr">
         <is>
-          <t>услуга</t>
+          <t>платёж</t>
         </is>
       </c>
       <c r="G52" s="192" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="193" t="n">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="I52" s="193">
         <f>G52*H52</f>
@@ -8095,61 +8154,116 @@
       </c>
       <c r="J52" s="191" t="inlineStr">
         <is>
+          <t>OpenRouter</t>
+        </is>
+      </c>
+      <c r="K52" s="194" t="inlineStr">
+        <is>
+          <t>Открыть ↗</t>
+        </is>
+      </c>
+      <c r="L52" s="191" t="inlineStr">
+        <is>
+          <t>Пополнение баланса API для расчётов и смет</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" outlineLevel="1">
+      <c r="A53" s="192" t="n">
+        <v>33</v>
+      </c>
+      <c r="B53" s="191" t="inlineStr">
+        <is>
+          <t>Энергосбыт</t>
+        </is>
+      </c>
+      <c r="C53" s="191" t="inlineStr">
+        <is>
+          <t>Учёт</t>
+        </is>
+      </c>
+      <c r="D53" s="191" t="inlineStr">
+        <is>
+          <t>Дистанционная распломбировка старого электросчётчика (согласование)</t>
+        </is>
+      </c>
+      <c r="E53" s="191" t="inlineStr">
+        <is>
+          <t>ТНС-РАСПЛОМБ-ДИСТ</t>
+        </is>
+      </c>
+      <c r="F53" s="191" t="inlineStr">
+        <is>
+          <t>услуга</t>
+        </is>
+      </c>
+      <c r="G53" s="192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="193" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I53" s="193">
+        <f>G53*H53</f>
+        <v/>
+      </c>
+      <c r="J53" s="191" t="inlineStr">
+        <is>
           <t>ТНС энерго Тула / Энергосбыт</t>
         </is>
       </c>
-      <c r="K52" s="194" t="inlineStr">
+      <c r="K53" s="194" t="inlineStr">
         <is>
           <t>Открыть ↗</t>
         </is>
       </c>
-      <c r="L52" s="191" t="inlineStr">
+      <c r="L53" s="191" t="inlineStr">
         <is>
           <t>Официальное согласование замены электроузла</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="206" t="inlineStr"/>
-      <c r="B53" s="206" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="211" t="inlineStr"/>
+      <c r="B54" s="211" t="inlineStr">
         <is>
           <t>ИТОГО ЮР. РАСХОДЫ, СЛУЖБЫ И IT:</t>
         </is>
       </c>
-      <c r="C53" s="206" t="inlineStr"/>
-      <c r="D53" s="206" t="inlineStr"/>
-      <c r="E53" s="206" t="inlineStr"/>
-      <c r="F53" s="206" t="inlineStr"/>
-      <c r="G53" s="206" t="inlineStr"/>
-      <c r="H53" s="206" t="inlineStr"/>
-      <c r="I53" s="200">
-        <f>SUM(I45:I52)</f>
-        <v/>
-      </c>
-      <c r="J53" s="206" t="inlineStr"/>
-      <c r="K53" s="206" t="inlineStr"/>
-      <c r="L53" s="206" t="inlineStr"/>
-    </row>
-    <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="210" t="inlineStr"/>
-      <c r="B54" s="210" t="inlineStr">
+      <c r="C54" s="211" t="inlineStr"/>
+      <c r="D54" s="211" t="inlineStr"/>
+      <c r="E54" s="211" t="inlineStr"/>
+      <c r="F54" s="211" t="inlineStr"/>
+      <c r="G54" s="211" t="inlineStr"/>
+      <c r="H54" s="211" t="inlineStr"/>
+      <c r="I54" s="212">
+        <f>SUM(I46:I53)</f>
+        <v/>
+      </c>
+      <c r="J54" s="211" t="inlineStr"/>
+      <c r="K54" s="211" t="inlineStr"/>
+      <c r="L54" s="211" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="213" t="inlineStr"/>
+      <c r="B55" s="213" t="inlineStr">
         <is>
           <t>ОБЩИЙ ИТОГО ФАКТ РАСХОДОВ (ДИНАМИЧЕСКИЙ):</t>
         </is>
       </c>
-      <c r="C54" s="210" t="inlineStr"/>
-      <c r="D54" s="210" t="inlineStr"/>
-      <c r="E54" s="210" t="inlineStr"/>
-      <c r="F54" s="210" t="inlineStr"/>
-      <c r="G54" s="210" t="inlineStr"/>
-      <c r="H54" s="210" t="inlineStr"/>
-      <c r="I54" s="198">
-        <f>SUBTOTAL(109; I6:I18; I21:I31; I34:I42; I45:I52)</f>
-        <v/>
-      </c>
-      <c r="J54" s="210" t="inlineStr"/>
-      <c r="K54" s="210" t="inlineStr"/>
-      <c r="L54" s="210" t="inlineStr"/>
+      <c r="C55" s="213" t="inlineStr"/>
+      <c r="D55" s="213" t="inlineStr"/>
+      <c r="E55" s="213" t="inlineStr"/>
+      <c r="F55" s="213" t="inlineStr"/>
+      <c r="G55" s="213" t="inlineStr"/>
+      <c r="H55" s="213" t="inlineStr"/>
+      <c r="I55" s="214">
+        <f>SUBTOTAL(109; I6:I18; I21:I31; I34:I43; I46:I53)</f>
+        <v/>
+      </c>
+      <c r="J55" s="213" t="inlineStr"/>
+      <c r="K55" s="213" t="inlineStr"/>
+      <c r="L55" s="213" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
+++ b/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
@@ -19,13 +19,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00 &quot;₽&quot;"/>
     <numFmt numFmtId="167" formatCode="+0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -241,8 +242,14 @@
       <color rgb="00334155"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00581C87"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -301,6 +308,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FEF3C7"/>
         <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E8FF"/>
+        <bgColor rgb="00F3E8FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -623,7 +636,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1177,6 +1190,45 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="24" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1613,7 +1665,7 @@
         <v/>
       </c>
       <c r="D5" s="118">
-        <f>'Факт расходов'!F47</f>
+        <f>'Факт расходов'!F52</f>
         <v/>
       </c>
       <c r="E5" s="118" t="n">
@@ -1706,7 +1758,7 @@
         <v>23000</v>
       </c>
       <c r="C11" s="46">
-        <f>SUMIF('Факт расходов'!C5:C46, "*Юр.*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*Безопасность*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*IT*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*Электроэнергия*", 'Факт расходов'!F5:F46)</f>
+        <f>SUMIF('Факт расходов'!C5:C51, "*Юр.*", 'Факт расходов'!F5:F51)+SUMIF('Факт расходов'!C5:C51, "*Безопасность*", 'Факт расходов'!F5:F51)+SUMIF('Факт расходов'!C5:C51, "*IT*", 'Факт расходов'!F5:F51)+SUMIF('Факт расходов'!C5:C51, "*Электроэнергия*", 'Факт расходов'!F5:F51)</f>
         <v/>
       </c>
       <c r="D11" s="124">
@@ -1986,7 +2038,7 @@
         <v/>
       </c>
       <c r="C23" s="46">
-        <f>SUMIF('Факт расходов'!C5:C46, "*Демонтаж*", 'Факт расходов'!F5:F46)</f>
+        <f>SUMIF('Факт расходов'!C5:C51, "*Демонтаж*", 'Факт расходов'!F5:F51)</f>
         <v/>
       </c>
       <c r="D23" s="45">
@@ -2019,7 +2071,7 @@
         <v/>
       </c>
       <c r="C24" s="51">
-        <f>SUMIF('Факт расходов'!C5:C46, "*Двери*", 'Факт расходов'!F5:F46)</f>
+        <f>SUMIF('Факт расходов'!C5:C51, "*Двери*", 'Факт расходов'!F5:F51)</f>
         <v/>
       </c>
       <c r="D24" s="50">
@@ -2052,7 +2104,7 @@
         <v/>
       </c>
       <c r="C25" s="46">
-        <f>SUMIF('Факт расходов'!C5:C46, "*Электрика*", 'Факт расходов'!F5:F46)</f>
+        <f>SUMIF('Факт расходов'!C5:C51, "*Электрика*", 'Факт расходов'!F5:F51)</f>
         <v/>
       </c>
       <c r="D25" s="45">
@@ -2085,7 +2137,7 @@
         <v/>
       </c>
       <c r="C26" s="51">
-        <f>SUMIF('Факт расходов'!C5:C46, "*Сантехника*", 'Факт расходов'!F5:F46)</f>
+        <f>SUMIF('Факт расходов'!C5:C51, "*Сантехника*", 'Факт расходов'!F5:F51)</f>
         <v/>
       </c>
       <c r="D26" s="50">
@@ -2117,7 +2169,7 @@
         <v>5000</v>
       </c>
       <c r="C27" s="46">
-        <f>SUMIF('Факт расходов'!C5:C46, "*Газ*", 'Факт расходов'!F5:F46)</f>
+        <f>SUMIF('Факт расходов'!C5:C51, "*Газ*", 'Факт расходов'!F5:F51)</f>
         <v/>
       </c>
       <c r="D27" s="45">
@@ -2182,7 +2234,7 @@
         <v/>
       </c>
       <c r="C29" s="46">
-        <f>SUMIF('Факт расходов'!C5:C46, "*Черновая*", 'Факт расходов'!F5:F46)</f>
+        <f>SUMIF('Факт расходов'!C5:C51, "*Черновая*", 'Факт расходов'!F5:F51)</f>
         <v/>
       </c>
       <c r="D29" s="45">
@@ -2215,7 +2267,7 @@
         <v/>
       </c>
       <c r="C30" s="51">
-        <f>SUMIF('Факт расходов'!C5:C46, "*Чистовая*", 'Факт расходов'!F5:F46)</f>
+        <f>SUMIF('Факт расходов'!C5:C51, "*Чистовая*", 'Факт расходов'!F5:F51)</f>
         <v/>
       </c>
       <c r="D30" s="50">
@@ -2375,7 +2427,7 @@
         <v>10000</v>
       </c>
       <c r="C35" s="46">
-        <f>SUMIF('Факт расходов'!C5:C46, "*Инструмент*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*Расходные*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*Логистика*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*доставка*", 'Факт расходов'!F5:F46)</f>
+        <f>SUMIF('Факт расходов'!C5:C51, "*Инструмент*", 'Факт расходов'!F5:F51)+SUMIF('Факт расходов'!C5:C51, "*Расходные*", 'Факт расходов'!F5:F51)+SUMIF('Факт расходов'!C5:C51, "*Логистика*", 'Факт расходов'!F5:F51)</f>
         <v/>
       </c>
       <c r="D35" s="45">
@@ -2407,7 +2459,7 @@
         <v>5000</v>
       </c>
       <c r="C36" s="51">
-        <f>SUMIF('Факт расходов'!C5:C46, "*хозмаг*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*Хоз.*", 'Факт расходов'!F5:F46)+SUMIF('Факт расходов'!C5:C46, "*Оснащение*", 'Факт расходов'!F5:F46)</f>
+        <f>SUMIF('Факт расходов'!C5:C51, "*Оснащение*", 'Факт расходов'!F5:F51)</f>
         <v/>
       </c>
       <c r="D36" s="50">
@@ -2589,11 +2641,11 @@
         </is>
       </c>
       <c r="B45" s="45">
-        <f>'Факт расходов'!E47</f>
+        <f>'Факт расходов'!E52</f>
         <v/>
       </c>
       <c r="C45" s="45">
-        <f>'Факт расходов'!F47</f>
+        <f>'Факт расходов'!F52</f>
         <v/>
       </c>
       <c r="D45" s="124">
@@ -2676,7 +2728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4810,113 +4862,273 @@
       <c r="M46" s="30" t="n"/>
       <c r="N46" s="30" t="n"/>
     </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="94" t="n"/>
-      <c r="B47" s="94" t="n"/>
-      <c r="C47" s="54" t="n"/>
-      <c r="D47" s="65" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДОВ:</t>
-        </is>
-      </c>
-      <c r="E47" s="55">
-        <f>SUM(E5:E46)</f>
-        <v/>
-      </c>
-      <c r="F47" s="55">
-        <f>SUM(F5:F46)</f>
-        <v/>
-      </c>
-      <c r="G47" s="55">
-        <f>SUM(G5:G46)</f>
-        <v/>
-      </c>
-      <c r="H47" s="104">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="62" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="62" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="C47" s="44" t="inlineStr">
+        <is>
+          <t>Сантехника / Материалы</t>
+        </is>
+      </c>
+      <c r="D47" s="44" t="inlineStr">
+        <is>
+          <t>Канализация с/у (муфта-восстановитель раструба DN 110/110, трубы ПП 50, тройник 110/50, заглушка, отводы, манжеты, хомуты)</t>
+        </is>
+      </c>
+      <c r="E47" s="45" t="n">
+        <v>2988</v>
+      </c>
+      <c r="F47" s="46" t="n">
+        <v>2988</v>
+      </c>
+      <c r="G47" s="47">
+        <f>E47-F47</f>
+        <v/>
+      </c>
+      <c r="H47" s="63">
         <f>IFERROR(G47/E47, 0)</f>
         <v/>
       </c>
-      <c r="I47" s="54" t="n"/>
-      <c r="J47" s="54" t="n"/>
+      <c r="I47" s="44" t="inlineStr">
+        <is>
+          <t>ИП Кучеров М.И. (магазин «Полимерстрой», Тула)</t>
+        </is>
+      </c>
+      <c r="J47" s="44" t="inlineStr">
+        <is>
+          <t>Чек от 15.09.2026 17:25 (карта *6730): восстановитель раструба DN110 (1315₽), тройник 110/50 (189₽), трубы ПП 50 5шт (664₽), заглушка (50₽), отводы/фитинги (394₽), хомуты/манжеты (376₽). Для разводки канализации с/у</t>
+        </is>
+      </c>
       <c r="K47" s="30" t="n"/>
       <c r="L47" s="30" t="n"/>
       <c r="M47" s="30" t="n"/>
       <c r="N47" s="30" t="n"/>
     </row>
-    <row r="48">
-      <c r="A48" s="30" t="n"/>
-      <c r="B48" s="30" t="n"/>
-      <c r="C48" s="30" t="n"/>
-      <c r="D48" s="30" t="n"/>
-      <c r="E48" s="30" t="n"/>
-      <c r="F48" s="30" t="n"/>
-      <c r="G48" s="30" t="n"/>
-      <c r="H48" s="30" t="n"/>
-      <c r="I48" s="30" t="n"/>
-      <c r="J48" s="30" t="n"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="64" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="64" t="inlineStr">
+        <is>
+          <t>19.09.2026</t>
+        </is>
+      </c>
+      <c r="C48" s="49" t="inlineStr">
+        <is>
+          <t>Сантехника / Материалы</t>
+        </is>
+      </c>
+      <c r="D48" s="49" t="inlineStr">
+        <is>
+          <t>Трубы и фитинги PPR для разводки водоснабжения ХВС/ГВС (трубы армированные Faser 20х2.8 12м, фитинги, планка смесителя, кран DN15, клипсы)</t>
+        </is>
+      </c>
+      <c r="E48" s="50" t="n">
+        <v>3139.54</v>
+      </c>
+      <c r="F48" s="51" t="n">
+        <v>3139.54</v>
+      </c>
+      <c r="G48" s="47">
+        <f>E48-F48</f>
+        <v/>
+      </c>
+      <c r="H48" s="63">
+        <f>IFERROR(G48/E48, 0)</f>
+        <v/>
+      </c>
+      <c r="I48" s="49" t="inlineStr">
+        <is>
+          <t>ТС «Ваттсон» (АО «Центргазсервис», Тула)</t>
+        </is>
+      </c>
+      <c r="J48" s="49" t="inlineStr">
+        <is>
+          <t>Чек №23 от 19.09.2026 13:04: труба PN20 Faser 20х2.8 (3 шт. × 4м = 913.11₽), настенный комплект для смесителя (334.22₽), кран шаровой DN15 (258.30₽), муфты/уголки с ВР (716.53₽), углы 90°/45° (305.76₽), тройники (122.40₽), обводы (108.52₽), клипсы (191.70₽), заглушки (189₽)</t>
+        </is>
+      </c>
       <c r="K48" s="30" t="n"/>
       <c r="L48" s="30" t="n"/>
       <c r="M48" s="30" t="n"/>
       <c r="N48" s="30" t="n"/>
     </row>
-    <row r="49">
-      <c r="A49" s="140" t="n"/>
-      <c r="B49" s="140" t="n"/>
-      <c r="C49" s="140" t="n"/>
-      <c r="D49" s="140" t="n"/>
-      <c r="E49" s="140" t="n"/>
-      <c r="F49" s="140" t="n"/>
-      <c r="G49" s="140" t="n"/>
-      <c r="H49" s="140" t="n"/>
-      <c r="I49" s="140" t="n"/>
-      <c r="J49" s="140" t="n"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="62" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="62" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+      <c r="C49" s="44" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D49" s="44" t="inlineStr">
+        <is>
+          <t>Материалы для штукатурки и гидроизоляции с/у, ревизионный люк, PPR фитинги и инструмент (штукатурка Старатели 8 шт., гидроизоляция Unis 4 кг, люк Fonet, маяки, профиль)</t>
+        </is>
+      </c>
+      <c r="E49" s="45" t="n">
+        <v>7827.6</v>
+      </c>
+      <c r="F49" s="46" t="n">
+        <v>7827.6</v>
+      </c>
+      <c r="G49" s="47">
+        <f>E49-F49</f>
+        <v/>
+      </c>
+      <c r="H49" s="63">
+        <f>IFERROR(G49/E49, 0)</f>
+        <v/>
+      </c>
+      <c r="I49" s="44" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J49" s="44" t="inlineStr">
+        <is>
+          <t>Чек от 20.09.2026 12:03: штукатурка Старатели 30кг 8шт (4040₽), гидроизоляция Unis Blue Membran 4кг (1568₽), люк Fonet 200х250 (333₽), маяки 10шт (450₽), профиль 50х40 (234₽), PPR фитинги (353.60₽), подводка 1м (248₽), рулетки (405₽), кисть/перчатки/пакет (196₽)</t>
+        </is>
+      </c>
       <c r="K49" s="140" t="n"/>
       <c r="L49" s="140" t="n"/>
       <c r="M49" s="140" t="n"/>
       <c r="N49" s="140" t="n"/>
     </row>
-    <row r="50">
-      <c r="A50" s="140" t="n"/>
-      <c r="B50" s="140" t="n"/>
-      <c r="C50" s="140" t="n"/>
-      <c r="D50" s="140" t="n"/>
-      <c r="E50" s="140" t="n"/>
-      <c r="F50" s="140" t="n"/>
-      <c r="G50" s="140" t="n"/>
-      <c r="H50" s="140" t="n"/>
-      <c r="I50" s="140" t="n"/>
-      <c r="J50" s="140" t="n"/>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="64" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="64" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+      <c r="C50" s="49" t="inlineStr">
+        <is>
+          <t>Чистовая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D50" s="49" t="inlineStr">
+        <is>
+          <t>Эмаль аэрозольная Luxens белая сатиновая и матовая 520 мл (2 шт.) для радиаторов отопления и труб</t>
+        </is>
+      </c>
+      <c r="E50" s="50" t="n">
+        <v>648</v>
+      </c>
+      <c r="F50" s="51" t="n">
+        <v>648</v>
+      </c>
+      <c r="G50" s="47">
+        <f>E50-F50</f>
+        <v/>
+      </c>
+      <c r="H50" s="63">
+        <f>IFERROR(G50/E50, 0)</f>
+        <v/>
+      </c>
+      <c r="I50" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J50" s="49" t="inlineStr">
+        <is>
+          <t>Чек №123 от 20.09.2026 12:39: эмаль Luxens сатин белый 520мл (324₽) + эмаль Luxens матовая белый 520мл (324₽). Покраска чугунных радиаторов отопления и труб</t>
+        </is>
+      </c>
       <c r="K50" s="140" t="n"/>
       <c r="L50" s="140" t="n"/>
       <c r="M50" s="140" t="n"/>
       <c r="N50" s="140" t="n"/>
     </row>
-    <row r="51">
-      <c r="A51" s="140" t="n"/>
-      <c r="B51" s="140" t="n"/>
-      <c r="C51" s="140" t="n"/>
-      <c r="D51" s="140" t="n"/>
-      <c r="E51" s="140" t="n"/>
-      <c r="F51" s="140" t="n"/>
-      <c r="G51" s="140" t="n"/>
-      <c r="H51" s="140" t="n"/>
-      <c r="I51" s="140" t="n"/>
-      <c r="J51" s="140" t="n"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="62" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="62" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+      <c r="C51" s="44" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D51" s="44" t="inlineStr">
+        <is>
+          <t>Ускоритель твердения Cemfix для стяжки пола санузла, 1 литр (добавка в раствор/пескобетон М300)</t>
+        </is>
+      </c>
+      <c r="E51" s="45" t="n">
+        <v>262</v>
+      </c>
+      <c r="F51" s="46" t="n">
+        <v>262</v>
+      </c>
+      <c r="G51" s="47">
+        <f>E51-F51</f>
+        <v/>
+      </c>
+      <c r="H51" s="63">
+        <f>IFERROR(G51/E51, 0)</f>
+        <v/>
+      </c>
+      <c r="I51" s="44" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J51" s="44" t="inlineStr">
+        <is>
+          <t>Чек №138 от 20.09.2026 13:02 (касса 75, карта *6730): ускоритель твердения Cemfix 1л (262₽). Добавка в пескобетон М300 для быстрого набора прочности стяжки пола с/у перед гидроизоляцией</t>
+        </is>
+      </c>
       <c r="K51" s="140" t="n"/>
       <c r="L51" s="140" t="n"/>
       <c r="M51" s="140" t="n"/>
       <c r="N51" s="140" t="n"/>
     </row>
-    <row r="52">
-      <c r="A52" s="140" t="n"/>
-      <c r="B52" s="140" t="n"/>
-      <c r="C52" s="140" t="n"/>
-      <c r="D52" s="140" t="n"/>
-      <c r="E52" s="140" t="n"/>
-      <c r="F52" s="140" t="n"/>
-      <c r="G52" s="140" t="n"/>
-      <c r="H52" s="140" t="n"/>
-      <c r="I52" s="140" t="n"/>
-      <c r="J52" s="140" t="n"/>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="94" t="n"/>
+      <c r="B52" s="94" t="n"/>
+      <c r="C52" s="54" t="n"/>
+      <c r="D52" s="65" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДОВ:</t>
+        </is>
+      </c>
+      <c r="E52" s="55">
+        <f>SUM(E5:E51)</f>
+        <v/>
+      </c>
+      <c r="F52" s="55">
+        <f>SUM(F5:F51)</f>
+        <v/>
+      </c>
+      <c r="G52" s="55">
+        <f>SUM(G5:G51)</f>
+        <v/>
+      </c>
+      <c r="H52" s="104">
+        <f>IFERROR(G52/E52, 0)</f>
+        <v/>
+      </c>
+      <c r="I52" s="54" t="n"/>
+      <c r="J52" s="54" t="n"/>
       <c r="K52" s="140" t="n"/>
       <c r="L52" s="140" t="n"/>
       <c r="M52" s="140" t="n"/>
@@ -5145,6 +5357,86 @@
       <c r="L66" s="140" t="n"/>
       <c r="M66" s="140" t="n"/>
       <c r="N66" s="140" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="140" t="n"/>
+      <c r="B67" s="140" t="n"/>
+      <c r="C67" s="140" t="n"/>
+      <c r="D67" s="140" t="n"/>
+      <c r="E67" s="140" t="n"/>
+      <c r="F67" s="140" t="n"/>
+      <c r="G67" s="140" t="n"/>
+      <c r="H67" s="140" t="n"/>
+      <c r="I67" s="140" t="n"/>
+      <c r="J67" s="140" t="n"/>
+      <c r="K67" s="140" t="n"/>
+      <c r="L67" s="140" t="n"/>
+      <c r="M67" s="140" t="n"/>
+      <c r="N67" s="140" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="140" t="n"/>
+      <c r="B68" s="140" t="n"/>
+      <c r="C68" s="140" t="n"/>
+      <c r="D68" s="140" t="n"/>
+      <c r="E68" s="140" t="n"/>
+      <c r="F68" s="140" t="n"/>
+      <c r="G68" s="140" t="n"/>
+      <c r="H68" s="140" t="n"/>
+      <c r="I68" s="140" t="n"/>
+      <c r="J68" s="140" t="n"/>
+      <c r="K68" s="140" t="n"/>
+      <c r="L68" s="140" t="n"/>
+      <c r="M68" s="140" t="n"/>
+      <c r="N68" s="140" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="140" t="n"/>
+      <c r="B69" s="140" t="n"/>
+      <c r="C69" s="140" t="n"/>
+      <c r="D69" s="140" t="n"/>
+      <c r="E69" s="140" t="n"/>
+      <c r="F69" s="140" t="n"/>
+      <c r="G69" s="140" t="n"/>
+      <c r="H69" s="140" t="n"/>
+      <c r="I69" s="140" t="n"/>
+      <c r="J69" s="140" t="n"/>
+      <c r="K69" s="140" t="n"/>
+      <c r="L69" s="140" t="n"/>
+      <c r="M69" s="140" t="n"/>
+      <c r="N69" s="140" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="140" t="n"/>
+      <c r="B70" s="140" t="n"/>
+      <c r="C70" s="140" t="n"/>
+      <c r="D70" s="140" t="n"/>
+      <c r="E70" s="140" t="n"/>
+      <c r="F70" s="140" t="n"/>
+      <c r="G70" s="140" t="n"/>
+      <c r="H70" s="140" t="n"/>
+      <c r="I70" s="140" t="n"/>
+      <c r="J70" s="140" t="n"/>
+      <c r="K70" s="140" t="n"/>
+      <c r="L70" s="140" t="n"/>
+      <c r="M70" s="140" t="n"/>
+      <c r="N70" s="140" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="140" t="n"/>
+      <c r="B71" s="140" t="n"/>
+      <c r="C71" s="140" t="n"/>
+      <c r="D71" s="140" t="n"/>
+      <c r="E71" s="140" t="n"/>
+      <c r="F71" s="140" t="n"/>
+      <c r="G71" s="140" t="n"/>
+      <c r="H71" s="140" t="n"/>
+      <c r="I71" s="140" t="n"/>
+      <c r="J71" s="140" t="n"/>
+      <c r="K71" s="140" t="n"/>
+      <c r="L71" s="140" t="n"/>
+      <c r="M71" s="140" t="n"/>
+      <c r="N71" s="140" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5645,27 +5937,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8.666666666666666" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="41.33333333333334" customWidth="1" min="4" max="4"/>
-    <col width="18.66666666666667" customWidth="1" min="5" max="5"/>
-    <col width="9.333333333333334" customWidth="1" min="6" max="6"/>
-    <col width="8.666666666666666" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16.66666666666667" customWidth="1" min="9" max="9"/>
-    <col width="25.33333333333333" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="38" t="inlineStr">
         <is>
-          <t>ГЕНЕРАЛЬНАЯ МАТРИЦА БЮДЖЕТА И КОМПЛЕКТАЦИИ (403 521,27 ₽)</t>
+          <t>ГЕНЕРАЛЬНАЯ МАТРИЦА БЮДЖЕТА И КОМПЛЕКТАЦИИ (418 386,41 ₽)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -5683,7 +5975,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Полная структура расходов Фрунзе 17 | Точная сверка с листом «Факт расходов» (1-в-1 до копейки, все 42 позиции)</t>
+          <t>Полная структура расходов Фрунзе 17 | Точная сверка с листом «Факт расходов» (1-в-1 до копейки, все 47 позиций)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -5782,7 +6074,7 @@
       <c r="A5" s="205" t="inlineStr"/>
       <c r="B5" s="205" t="inlineStr">
         <is>
-          <t>🛁 БЛОК 1: СТРОИТЕЛЬНЫЕ И ЧИСТОВЫЕ МАТЕРИАЛЫ «ЛЕМАНА ПРО» (13 ЧЕКОВ)</t>
+          <t>🛁 БЛОК 1: СТРОИТЕЛЬНЫЕ И ЧИСТОВЫЕ МАТЕРИАЛЫ «ЛЕМАНА ПРО» (16 ЧЕКОВ)</t>
         </is>
       </c>
       <c r="C5" s="205" t="inlineStr"/>
@@ -5796,2474 +6088,2702 @@
       <c r="K5" s="205" t="inlineStr"/>
       <c r="L5" s="205" t="inlineStr"/>
     </row>
-    <row r="6" outlineLevel="1">
-      <c r="A6" s="192" t="n">
+    <row r="6">
+      <c r="A6" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="B6" s="191" t="inlineStr">
+      <c r="B6" s="62" t="inlineStr">
         <is>
           <t>Расходники</t>
         </is>
       </c>
-      <c r="C6" s="191" t="inlineStr">
+      <c r="C6" s="62" t="inlineStr">
         <is>
           <t>Пылесос</t>
         </is>
       </c>
-      <c r="D6" s="191" t="inlineStr">
+      <c r="D6" s="44" t="inlineStr">
         <is>
           <t>Мешки для пылесоса синт. 12л (5 шт) — Леруа/Лемана</t>
         </is>
       </c>
-      <c r="E6" s="191" t="inlineStr">
+      <c r="E6" s="62" t="inlineStr">
         <is>
           <t>4607086338088</t>
         </is>
       </c>
-      <c r="F6" s="191" t="inlineStr">
+      <c r="F6" s="62" t="inlineStr">
         <is>
           <t>упак.</t>
         </is>
       </c>
-      <c r="G6" s="192" t="n">
+      <c r="G6" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="193" t="n">
+      <c r="H6" s="173" t="n">
         <v>717</v>
       </c>
-      <c r="I6" s="193">
+      <c r="I6" s="217">
         <f>G6*H6</f>
         <v/>
       </c>
-      <c r="J6" s="191" t="inlineStr">
+      <c r="J6" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K6" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L6" s="191" t="inlineStr">
+      <c r="K6" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=мешки+для+пылесоса+12л"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L6" s="44" t="inlineStr">
         <is>
           <t>Чек 3831 от 23.08.2026: Сбор пыли штробления</t>
         </is>
       </c>
     </row>
-    <row r="7" outlineLevel="1">
-      <c r="A7" s="192" t="n">
+    <row r="7">
+      <c r="A7" s="64" t="n">
         <v>9</v>
       </c>
-      <c r="B7" s="191" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>Инструмент</t>
         </is>
       </c>
-      <c r="C7" s="191" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="D7" s="191" t="inlineStr">
+      <c r="D7" s="49" t="inlineStr">
         <is>
           <t>Лом-гвоздодер, мешки 15шт, лента, перчатки 6п, опрыскиватель</t>
         </is>
       </c>
-      <c r="E7" s="191" t="inlineStr">
+      <c r="E7" s="64" t="inlineStr">
         <is>
           <t>4603333000001</t>
         </is>
       </c>
-      <c r="F7" s="191" t="inlineStr">
+      <c r="F7" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G7" s="192" t="n">
+      <c r="G7" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="193" t="n">
+      <c r="H7" s="172" t="n">
         <v>1830</v>
       </c>
-      <c r="I7" s="193">
+      <c r="I7" s="219">
         <f>G7*H7</f>
         <v/>
       </c>
-      <c r="J7" s="191" t="inlineStr">
+      <c r="J7" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K7" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L7" s="191" t="inlineStr">
+      <c r="K7" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=лом+гвоздодер"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L7" s="49" t="inlineStr">
         <is>
           <t>Чек 3832 от 23.08.2026: Инструмент демонтажа</t>
         </is>
       </c>
     </row>
-    <row r="8" outlineLevel="1">
-      <c r="A8" s="192" t="n">
+    <row r="8">
+      <c r="A8" s="62" t="n">
         <v>25</v>
       </c>
-      <c r="B8" s="191" t="inlineStr">
+      <c r="B8" s="62" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C8" s="191" t="inlineStr">
+      <c r="C8" s="62" t="inlineStr">
         <is>
           <t>Шпатлевка / Грунт</t>
         </is>
       </c>
-      <c r="D8" s="191" t="inlineStr">
+      <c r="D8" s="44" t="inlineStr">
         <is>
           <t>Материалы для зачистки и грунтования (шпатлевка 20кг, грунт 10л, СТ99, фильтр Rommer)</t>
         </is>
       </c>
-      <c r="E8" s="191" t="inlineStr">
+      <c r="E8" s="62" t="inlineStr">
         <is>
           <t>3276006224277</t>
         </is>
       </c>
-      <c r="F8" s="191" t="inlineStr">
+      <c r="F8" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G8" s="192" t="n">
+      <c r="G8" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="193" t="n">
+      <c r="H8" s="173" t="n">
         <v>4803.6</v>
       </c>
-      <c r="I8" s="193">
+      <c r="I8" s="217">
         <f>G8*H8</f>
         <v/>
       </c>
-      <c r="J8" s="191" t="inlineStr">
+      <c r="J8" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K8" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L8" s="191" t="inlineStr">
+      <c r="K8" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=грунт+axton+10л"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L8" s="44" t="inlineStr">
         <is>
           <t>Чек от 30.08.2026: Подготовка стен зала и с/у</t>
         </is>
       </c>
     </row>
-    <row r="9" outlineLevel="1">
-      <c r="A9" s="192" t="n">
+    <row r="9">
+      <c r="A9" s="64" t="n">
         <v>26</v>
       </c>
-      <c r="B9" s="191" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>Инструмент</t>
         </is>
       </c>
-      <c r="C9" s="191" t="inlineStr">
+      <c r="C9" s="64" t="inlineStr">
         <is>
           <t>Ёмкости</t>
         </is>
       </c>
-      <c r="D9" s="191" t="inlineStr">
+      <c r="D9" s="49" t="inlineStr">
         <is>
           <t>Ведро строительное круглое 20 л (2 шт.)</t>
         </is>
       </c>
-      <c r="E9" s="191" t="inlineStr">
+      <c r="E9" s="64" t="inlineStr">
         <is>
           <t>4610008470475</t>
         </is>
       </c>
-      <c r="F9" s="191" t="inlineStr">
+      <c r="F9" s="64" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G9" s="192" t="n">
+      <c r="G9" s="218" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="193" t="n">
+      <c r="H9" s="172" t="n">
         <v>128</v>
       </c>
-      <c r="I9" s="193">
+      <c r="I9" s="219">
         <f>G9*H9</f>
         <v/>
       </c>
-      <c r="J9" s="191" t="inlineStr">
+      <c r="J9" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K9" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L9" s="191" t="inlineStr">
+      <c r="K9" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=ведро+строительное+20л"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L9" s="49" t="inlineStr">
         <is>
           <t>Чек от 30.08.2026: Ёмкости для замеса растворов</t>
         </is>
       </c>
     </row>
-    <row r="10" outlineLevel="1">
-      <c r="A10" s="192" t="n">
+    <row r="10">
+      <c r="A10" s="62" t="n">
         <v>28</v>
       </c>
-      <c r="B10" s="191" t="inlineStr">
+      <c r="B10" s="62" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C10" s="191" t="inlineStr">
+      <c r="C10" s="62" t="inlineStr">
         <is>
           <t>Шпатлевка / Шпатели</t>
         </is>
       </c>
-      <c r="D10" s="191" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr">
         <is>
           <t>Материалы для подготовки стен (грунт Axton 10л 4шт, шпатлевка 20кг 2шт, шпатели, мешки)</t>
         </is>
       </c>
-      <c r="E10" s="191" t="inlineStr">
+      <c r="E10" s="62" t="inlineStr">
         <is>
           <t>4601745004252</t>
         </is>
       </c>
-      <c r="F10" s="191" t="inlineStr">
+      <c r="F10" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G10" s="192" t="n">
+      <c r="G10" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="193" t="n">
+      <c r="H10" s="173" t="n">
         <v>3308</v>
       </c>
-      <c r="I10" s="193">
+      <c r="I10" s="217">
         <f>G10*H10</f>
         <v/>
       </c>
-      <c r="J10" s="191" t="inlineStr">
+      <c r="J10" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K10" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L10" s="191" t="inlineStr">
+      <c r="K10" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=шпатлевка+старатели+20кг"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L10" s="44" t="inlineStr">
         <is>
           <t>Чек от 05.09.2026: Подготовка спальни</t>
         </is>
       </c>
     </row>
-    <row r="11" outlineLevel="1">
-      <c r="A11" s="192" t="n">
+    <row r="11">
+      <c r="A11" s="64" t="n">
         <v>30</v>
       </c>
-      <c r="B11" s="191" t="inlineStr">
+      <c r="B11" s="64" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C11" s="191" t="inlineStr">
+      <c r="C11" s="64" t="inlineStr">
         <is>
           <t>Штукатурка / Бетонконтакт</t>
         </is>
       </c>
-      <c r="D11" s="191" t="inlineStr">
+      <c r="D11" s="49" t="inlineStr">
         <is>
           <t>Материалы штукатурки и шпаклёвки (Бетонконтакт 12кг 3шт, финиш 5шт, штукатурка 3шт, правило, углы)</t>
         </is>
       </c>
-      <c r="E11" s="191" t="inlineStr">
+      <c r="E11" s="64" t="inlineStr">
         <is>
           <t>4607017518816</t>
         </is>
       </c>
-      <c r="F11" s="191" t="inlineStr">
+      <c r="F11" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G11" s="192" t="n">
+      <c r="G11" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="193" t="n">
+      <c r="H11" s="172" t="n">
         <v>8162</v>
       </c>
-      <c r="I11" s="193">
+      <c r="I11" s="219">
         <f>G11*H11</f>
         <v/>
       </c>
-      <c r="J11" s="191" t="inlineStr">
+      <c r="J11" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K11" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L11" s="191" t="inlineStr">
+      <c r="K11" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=бетонконтакт+axton+12кг"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L11" s="49" t="inlineStr">
         <is>
           <t>Чек от 06.09.2026: Основное выравнивание стен</t>
         </is>
       </c>
     </row>
-    <row r="12" outlineLevel="1">
-      <c r="A12" s="192" t="n">
+    <row r="12">
+      <c r="A12" s="62" t="n">
         <v>32</v>
       </c>
-      <c r="B12" s="191" t="inlineStr">
+      <c r="B12" s="62" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C12" s="191" t="inlineStr">
+      <c r="C12" s="62" t="inlineStr">
         <is>
           <t>Шпаклёвка</t>
         </is>
       </c>
-      <c r="D12" s="191" t="inlineStr">
+      <c r="D12" s="44" t="inlineStr">
         <is>
           <t>Материалы штукатурки и шпаклёвки (шпатлевка финиш 20кг, штукатурка 30кг 2шт, перчатки)</t>
         </is>
       </c>
-      <c r="E12" s="191" t="inlineStr">
+      <c r="E12" s="62" t="inlineStr">
         <is>
           <t>4601745002814</t>
         </is>
       </c>
-      <c r="F12" s="191" t="inlineStr">
+      <c r="F12" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G12" s="192" t="n">
+      <c r="G12" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="193" t="n">
+      <c r="H12" s="173" t="n">
         <v>1594</v>
       </c>
-      <c r="I12" s="193">
+      <c r="I12" s="217">
         <f>G12*H12</f>
         <v/>
       </c>
-      <c r="J12" s="191" t="inlineStr">
+      <c r="J12" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K12" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L12" s="191" t="inlineStr">
+      <c r="K12" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=шпатлевка+финишная+старатели"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L12" s="44" t="inlineStr">
         <is>
           <t>Чек от 08.09.2026: Добор смесей на спальню</t>
         </is>
       </c>
     </row>
-    <row r="13" outlineLevel="1">
-      <c r="A13" s="192" t="n">
+    <row r="13">
+      <c r="A13" s="64" t="n">
         <v>34</v>
       </c>
-      <c r="B13" s="191" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C13" s="191" t="inlineStr">
+      <c r="C13" s="64" t="inlineStr">
         <is>
           <t>Санфаянс / Смесители</t>
         </is>
       </c>
-      <c r="D13" s="191" t="inlineStr">
+      <c r="D13" s="49" t="inlineStr">
         <is>
           <t>Сантехника и санфаянс с/у (ванна Нерея 150, каркас Sensea, унитаз Sanita, раковина 60, смесители 2шт, душ, сифон)</t>
         </is>
       </c>
-      <c r="E13" s="191" t="inlineStr">
+      <c r="E13" s="64" t="inlineStr">
         <is>
           <t>4600779023659</t>
         </is>
       </c>
-      <c r="F13" s="191" t="inlineStr">
+      <c r="F13" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G13" s="192" t="n">
+      <c r="G13" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="193" t="n">
+      <c r="H13" s="172" t="n">
         <v>30021</v>
       </c>
-      <c r="I13" s="193">
+      <c r="I13" s="219">
         <f>G13*H13</f>
         <v/>
       </c>
-      <c r="J13" s="191" t="inlineStr">
+      <c r="J13" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K13" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L13" s="191" t="inlineStr">
+      <c r="K13" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4600779023659"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L13" s="49" t="inlineStr">
         <is>
           <t>Чек от 13.09.2026 (заказ 774): Полный комплект с/у</t>
         </is>
       </c>
     </row>
-    <row r="14" outlineLevel="1">
-      <c r="A14" s="192" t="n">
+    <row r="14">
+      <c r="A14" s="62" t="n">
         <v>35</v>
       </c>
-      <c r="B14" s="191" t="inlineStr">
+      <c r="B14" s="62" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C14" s="191" t="inlineStr">
+      <c r="C14" s="62" t="inlineStr">
         <is>
           <t>Керамогранит / Затирка</t>
         </is>
       </c>
-      <c r="D14" s="191" t="inlineStr">
+      <c r="D14" s="44" t="inlineStr">
         <is>
           <t>Керамогранит Calacatta 60х120 (14 упак. / 20.16 м²) + затирка Ceresit CE 40 2кг 2шт</t>
         </is>
       </c>
-      <c r="E14" s="191" t="inlineStr">
+      <c r="E14" s="62" t="inlineStr">
         <is>
           <t>4673766221451</t>
         </is>
       </c>
-      <c r="F14" s="191" t="inlineStr">
+      <c r="F14" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G14" s="192" t="n">
+      <c r="G14" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="193" t="n">
+      <c r="H14" s="173" t="n">
         <v>33457</v>
       </c>
-      <c r="I14" s="193">
+      <c r="I14" s="217">
         <f>G14*H14</f>
         <v/>
       </c>
-      <c r="J14" s="191" t="inlineStr">
+      <c r="J14" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K14" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L14" s="191" t="inlineStr">
+      <c r="K14" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4673766221451"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L14" s="44" t="inlineStr">
         <is>
           <t>Чек от 13.09.2026 (заказ 774): Плитка на все стены с/у</t>
         </is>
       </c>
     </row>
-    <row r="15" outlineLevel="1">
-      <c r="A15" s="192" t="n">
+    <row r="15">
+      <c r="A15" s="64" t="n">
         <v>36</v>
       </c>
-      <c r="B15" s="191" t="inlineStr">
+      <c r="B15" s="64" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C15" s="191" t="inlineStr">
+      <c r="C15" s="64" t="inlineStr">
         <is>
           <t>Плиточный клей</t>
         </is>
       </c>
-      <c r="D15" s="191" t="inlineStr">
+      <c r="D15" s="49" t="inlineStr">
         <is>
           <t>Плиточный клей Unis 2000 C1T 25 кг для формата 60х120 (13 мешков)</t>
         </is>
       </c>
-      <c r="E15" s="191" t="inlineStr">
+      <c r="E15" s="64" t="inlineStr">
         <is>
           <t>4607005180063</t>
         </is>
       </c>
-      <c r="F15" s="191" t="inlineStr">
+      <c r="F15" s="64" t="inlineStr">
         <is>
           <t>мешок</t>
         </is>
       </c>
-      <c r="G15" s="192" t="n">
+      <c r="G15" s="218" t="n">
         <v>13</v>
       </c>
-      <c r="H15" s="193" t="n">
+      <c r="H15" s="172" t="n">
         <v>382.53846</v>
       </c>
-      <c r="I15" s="193">
+      <c r="I15" s="219">
         <f>G15*H15</f>
         <v/>
       </c>
-      <c r="J15" s="191" t="inlineStr">
+      <c r="J15" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K15" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L15" s="191" t="inlineStr">
+      <c r="K15" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4607005180063"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L15" s="49" t="inlineStr">
         <is>
           <t>Чек от 13.09.2026 (заказ 774): Клей под керамогранит</t>
         </is>
       </c>
     </row>
-    <row r="16" outlineLevel="1">
-      <c r="A16" s="192" t="n">
+    <row r="16">
+      <c r="A16" s="62" t="n">
         <v>37</v>
       </c>
-      <c r="B16" s="191" t="inlineStr">
+      <c r="B16" s="62" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C16" s="191" t="inlineStr">
+      <c r="C16" s="62" t="inlineStr">
         <is>
           <t>СВП</t>
         </is>
       </c>
-      <c r="D16" s="191" t="inlineStr">
+      <c r="D16" s="44" t="inlineStr">
         <is>
           <t>Система выравнивания плитки СВП DILWIS (зажимы 1 мм 200 шт, клинья 100 шт)</t>
         </is>
       </c>
-      <c r="E16" s="191" t="inlineStr">
+      <c r="E16" s="62" t="inlineStr">
         <is>
           <t>4610085150475</t>
         </is>
       </c>
-      <c r="F16" s="191" t="inlineStr">
+      <c r="F16" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G16" s="192" t="n">
+      <c r="G16" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="193" t="n">
+      <c r="H16" s="173" t="n">
         <v>853</v>
       </c>
-      <c r="I16" s="193">
+      <c r="I16" s="217">
         <f>G16*H16</f>
         <v/>
       </c>
-      <c r="J16" s="191" t="inlineStr">
+      <c r="J16" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K16" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L16" s="191" t="inlineStr">
+      <c r="K16" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4610085150475"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L16" s="44" t="inlineStr">
         <is>
           <t>Чек от 13.09.2026 (заказ 774): Идеальный шов 1 мм</t>
         </is>
       </c>
     </row>
-    <row r="17" outlineLevel="1">
-      <c r="A17" s="192" t="n">
+    <row r="17">
+      <c r="A17" s="64" t="n">
         <v>38</v>
       </c>
-      <c r="B17" s="191" t="inlineStr">
+      <c r="B17" s="64" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C17" s="191" t="inlineStr">
+      <c r="C17" s="64" t="inlineStr">
         <is>
           <t>Шпаклёвка</t>
         </is>
       </c>
-      <c r="D17" s="191" t="inlineStr">
+      <c r="D17" s="49" t="inlineStr">
         <is>
           <t>Материалы для штукатурки и шпаклёвки (повторный добор: финиш 20кг, штукатурка 2шт)</t>
         </is>
       </c>
-      <c r="E17" s="191" t="inlineStr">
+      <c r="E17" s="64" t="inlineStr">
         <is>
           <t>4601745000407</t>
         </is>
       </c>
-      <c r="F17" s="191" t="inlineStr">
+      <c r="F17" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G17" s="192" t="n">
+      <c r="G17" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="193" t="n">
+      <c r="H17" s="172" t="n">
         <v>1594</v>
       </c>
-      <c r="I17" s="193">
+      <c r="I17" s="219">
         <f>G17*H17</f>
         <v/>
       </c>
-      <c r="J17" s="191" t="inlineStr">
+      <c r="J17" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K17" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L17" s="191" t="inlineStr">
+      <c r="K17" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=штукатурка+старатели+30кг"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L17" s="49" t="inlineStr">
         <is>
           <t>Чек от 13.09.2026: Добор смесей на гардероб</t>
         </is>
       </c>
     </row>
-    <row r="18" outlineLevel="1">
-      <c r="A18" s="192" t="n">
+    <row r="18">
+      <c r="A18" s="62" t="n">
         <v>39</v>
       </c>
-      <c r="B18" s="191" t="inlineStr">
+      <c r="B18" s="62" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C18" s="191" t="inlineStr">
+      <c r="C18" s="62" t="inlineStr">
         <is>
           <t>Стяжка / Короба</t>
         </is>
       </c>
-      <c r="D18" s="191" t="inlineStr">
+      <c r="D18" s="44" t="inlineStr">
         <is>
           <t>Материалы для стяжки пола и короба с/у (пескобетон М-300 6шт, Knauf 50х40, ГСП 2шт, фибра, саморезы, стамеска)</t>
         </is>
       </c>
-      <c r="E18" s="191" t="inlineStr">
+      <c r="E18" s="62" t="inlineStr">
         <is>
           <t>4610007550932</t>
         </is>
       </c>
-      <c r="F18" s="191" t="inlineStr">
+      <c r="F18" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G18" s="192" t="n">
+      <c r="G18" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="193" t="n">
+      <c r="H18" s="173" t="n">
         <v>3182.67</v>
       </c>
-      <c r="I18" s="193">
+      <c r="I18" s="217">
         <f>G18*H18</f>
         <v/>
       </c>
-      <c r="J18" s="191" t="inlineStr">
+      <c r="J18" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K18" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L18" s="191" t="inlineStr">
+      <c r="K18" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=пескобетон+м300"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L18" s="44" t="inlineStr">
         <is>
           <t>Чек №201 от 13.09.2026: Стяжка пола и стояк с/у</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="211" t="inlineStr"/>
-      <c r="B19" s="211" t="inlineStr">
+      <c r="A19" s="64" t="n">
+        <v>45</v>
+      </c>
+      <c r="B19" s="64" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C19" s="64" t="inlineStr">
+        <is>
+          <t>Черновые стены / Гидроизоляция</t>
+        </is>
+      </c>
+      <c r="D19" s="49" t="inlineStr">
+        <is>
+          <t>Штукатурка Старатели 8шт, гидроизоляция Unis 4кг, люк Fonet 200х250, маяки, профиль, фитинги, рулетки</t>
+        </is>
+      </c>
+      <c r="E19" s="64" t="inlineStr">
+        <is>
+          <t>4601745000407</t>
+        </is>
+      </c>
+      <c r="F19" s="64" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G19" s="218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="172" t="n">
+        <v>7827.6</v>
+      </c>
+      <c r="I19" s="219">
+        <f>G19*H19</f>
+        <v/>
+      </c>
+      <c r="J19" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K19" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4601745000407"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L19" s="49" t="inlineStr">
+        <is>
+          <t>Чек от 20.09.2026 12:03: Выравнивание ванны под 90°, гидроизоляция, люк стояка</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="62" t="n">
+        <v>46</v>
+      </c>
+      <c r="B20" s="62" t="inlineStr">
+        <is>
+          <t>Все зоны</t>
+        </is>
+      </c>
+      <c r="C20" s="62" t="inlineStr">
+        <is>
+          <t>Радиаторы / Трубы</t>
+        </is>
+      </c>
+      <c r="D20" s="44" t="inlineStr">
+        <is>
+          <t>Эмаль аэрозольная Luxens белая сатиновая и матовая 520 мл (2 шт.)</t>
+        </is>
+      </c>
+      <c r="E20" s="62" t="inlineStr">
+        <is>
+          <t>3276007227604</t>
+        </is>
+      </c>
+      <c r="F20" s="62" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G20" s="216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="173" t="n">
+        <v>648</v>
+      </c>
+      <c r="I20" s="217">
+        <f>G20*H20</f>
+        <v/>
+      </c>
+      <c r="J20" s="44" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K20" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=3276007227604"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L20" s="44" t="inlineStr">
+        <is>
+          <t>Чек №123 от 20.09.2026 12:39: Покраска чугунных радиаторов отопления и труб</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="64" t="n">
+        <v>47</v>
+      </c>
+      <c r="B21" s="64" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C21" s="64" t="inlineStr">
+        <is>
+          <t>Стяжка / Добавки</t>
+        </is>
+      </c>
+      <c r="D21" s="49" t="inlineStr">
+        <is>
+          <t>Ускоритель твердения Cemfix для стяжки пола, 1 литр (добавка в пескобетон М300)</t>
+        </is>
+      </c>
+      <c r="E21" s="64" t="inlineStr">
+        <is>
+          <t>4650068600092</t>
+        </is>
+      </c>
+      <c r="F21" s="64" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G21" s="218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="172" t="n">
+        <v>262</v>
+      </c>
+      <c r="I21" s="219">
+        <f>G21*H21</f>
+        <v/>
+      </c>
+      <c r="J21" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K21" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4650068600092"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L21" s="49" t="inlineStr">
+        <is>
+          <t>Чек №138 от 20.09.2026 13:02: Ускорение набора прочности стяжки пола с/у</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="223" t="inlineStr"/>
+      <c r="B22" s="223" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ ЛЕМАНА ПРО (ПО ЧЕКАМ):</t>
         </is>
       </c>
-      <c r="C19" s="211" t="inlineStr"/>
-      <c r="D19" s="211" t="inlineStr"/>
-      <c r="E19" s="211" t="inlineStr"/>
-      <c r="F19" s="211" t="inlineStr"/>
-      <c r="G19" s="211" t="inlineStr"/>
-      <c r="H19" s="211" t="inlineStr"/>
-      <c r="I19" s="212">
-        <f>SUM(I6:I18)</f>
-        <v/>
-      </c>
-      <c r="J19" s="211" t="inlineStr"/>
-      <c r="K19" s="211" t="inlineStr"/>
-      <c r="L19" s="211" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="207" t="inlineStr"/>
-      <c r="B20" s="207" t="inlineStr">
+      <c r="C22" s="223" t="inlineStr"/>
+      <c r="D22" s="223" t="inlineStr"/>
+      <c r="E22" s="223" t="inlineStr"/>
+      <c r="F22" s="223" t="inlineStr"/>
+      <c r="G22" s="223" t="inlineStr"/>
+      <c r="H22" s="223" t="inlineStr"/>
+      <c r="I22" s="224">
+        <f>SUM(I6:I21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="223" t="inlineStr"/>
+      <c r="K22" s="223" t="inlineStr"/>
+      <c r="L22" s="223" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="207" t="inlineStr"/>
+      <c r="B23" s="207" t="inlineStr">
         <is>
           <t>⚡ БЛОК 2: ИНЖЕНЕРНЫЕ МАТЕРИАЛЫ, ДВЕРИ И ОСНАЩЕНИЕ (СПЕЦПОСТАВЩИКИ)</t>
         </is>
       </c>
-      <c r="C20" s="207" t="inlineStr"/>
-      <c r="D20" s="207" t="inlineStr"/>
-      <c r="E20" s="207" t="inlineStr"/>
-      <c r="F20" s="207" t="inlineStr"/>
-      <c r="G20" s="207" t="inlineStr"/>
-      <c r="H20" s="207" t="inlineStr"/>
-      <c r="I20" s="207" t="inlineStr"/>
-      <c r="J20" s="207" t="inlineStr"/>
-      <c r="K20" s="207" t="inlineStr"/>
-      <c r="L20" s="207" t="inlineStr"/>
-    </row>
-    <row r="21" outlineLevel="1">
-      <c r="A21" s="192" t="n">
+      <c r="C23" s="207" t="inlineStr"/>
+      <c r="D23" s="207" t="inlineStr"/>
+      <c r="E23" s="207" t="inlineStr"/>
+      <c r="F23" s="207" t="inlineStr"/>
+      <c r="G23" s="207" t="inlineStr"/>
+      <c r="H23" s="207" t="inlineStr"/>
+      <c r="I23" s="207" t="inlineStr"/>
+      <c r="J23" s="207" t="inlineStr"/>
+      <c r="K23" s="207" t="inlineStr"/>
+      <c r="L23" s="207" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="191" t="inlineStr">
+      <c r="B24" s="62" t="inlineStr">
         <is>
           <t>Расходники</t>
         </is>
       </c>
-      <c r="C21" s="191" t="inlineStr">
+      <c r="C24" s="62" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="D21" s="191" t="inlineStr">
+      <c r="D24" s="44" t="inlineStr">
         <is>
           <t>Мешки мусорные плотные, перчатки рабочие (хозмаг/рынок)</t>
         </is>
       </c>
-      <c r="E21" s="191" t="inlineStr">
+      <c r="E24" s="62" t="inlineStr">
         <is>
           <t>ХОЗМАГ-МЕШКИ</t>
         </is>
       </c>
-      <c r="F21" s="191" t="inlineStr">
+      <c r="F24" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G21" s="192" t="n">
+      <c r="G24" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="193" t="n">
+      <c r="H24" s="173" t="n">
         <v>300</v>
       </c>
-      <c r="I21" s="193">
-        <f>G21*H21</f>
-        <v/>
-      </c>
-      <c r="J21" s="191" t="inlineStr">
+      <c r="I24" s="217">
+        <f>G24*H24</f>
+        <v/>
+      </c>
+      <c r="J24" s="44" t="inlineStr">
         <is>
           <t>Хозмаг / Рынок</t>
         </is>
       </c>
-      <c r="K21" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L21" s="191" t="inlineStr">
+      <c r="K24" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=мешки+мусорные+строительные"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L24" s="44" t="inlineStr">
         <is>
           <t>Оперативная докупка расходников для демонтажа</t>
         </is>
       </c>
     </row>
-    <row r="22" outlineLevel="1">
-      <c r="A22" s="192" t="n">
+    <row r="25">
+      <c r="A25" s="64" t="n">
         <v>11</v>
       </c>
-      <c r="B22" s="191" t="inlineStr">
+      <c r="B25" s="64" t="inlineStr">
         <is>
           <t>Сантехника</t>
         </is>
       </c>
-      <c r="C22" s="191" t="inlineStr">
+      <c r="C25" s="64" t="inlineStr">
         <is>
           <t>Учёт воды</t>
         </is>
       </c>
-      <c r="D22" s="191" t="inlineStr">
+      <c r="D25" s="49" t="inlineStr">
         <is>
           <t>Счётчик горячей/холодной воды + кран на ввод (материалы)</t>
         </is>
       </c>
-      <c r="E22" s="191" t="inlineStr">
+      <c r="E25" s="64" t="inlineStr">
         <is>
           <t>СЧЕТЧИК-ВОДЫ</t>
         </is>
       </c>
-      <c r="F22" s="191" t="inlineStr">
+      <c r="F25" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G22" s="192" t="n">
+      <c r="G25" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="193" t="n">
+      <c r="H25" s="172" t="n">
         <v>2100</v>
       </c>
-      <c r="I22" s="193">
-        <f>G22*H22</f>
-        <v/>
-      </c>
-      <c r="J22" s="191" t="inlineStr">
+      <c r="I25" s="219">
+        <f>G25*H25</f>
+        <v/>
+      </c>
+      <c r="J25" s="49" t="inlineStr">
         <is>
           <t>Вадим (сантехник УК)</t>
         </is>
       </c>
-      <c r="K22" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L22" s="191" t="inlineStr">
+      <c r="K25" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=счетчик+воды+универсальный"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L25" s="49" t="inlineStr">
         <is>
           <t>Замена вводных узлов и прибора учёта</t>
         </is>
       </c>
     </row>
-    <row r="23" outlineLevel="1">
-      <c r="A23" s="192" t="n">
+    <row r="26">
+      <c r="A26" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="191" t="inlineStr">
+      <c r="B26" s="62" t="inlineStr">
         <is>
           <t>Сантехника</t>
         </is>
       </c>
-      <c r="C23" s="191" t="inlineStr">
+      <c r="C26" s="62" t="inlineStr">
         <is>
           <t>Учёт воды</t>
         </is>
       </c>
-      <c r="D23" s="191" t="inlineStr">
+      <c r="D26" s="44" t="inlineStr">
         <is>
           <t>Покупка и установка счётчика и кранов (доплата за фитинги и муфты)</t>
         </is>
       </c>
-      <c r="E23" s="191" t="inlineStr">
+      <c r="E26" s="62" t="inlineStr">
         <is>
           <t>ФИТИНГИ-САНТЕХ</t>
         </is>
       </c>
-      <c r="F23" s="191" t="inlineStr">
+      <c r="F26" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G23" s="192" t="n">
+      <c r="G26" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="193" t="n">
+      <c r="H26" s="173" t="n">
         <v>2000</v>
       </c>
-      <c r="I23" s="193">
-        <f>G23*H23</f>
-        <v/>
-      </c>
-      <c r="J23" s="191" t="inlineStr">
+      <c r="I26" s="217">
+        <f>G26*H26</f>
+        <v/>
+      </c>
+      <c r="J26" s="44" t="inlineStr">
         <is>
           <t>Вадим (сантехник УК)</t>
         </is>
       </c>
-      <c r="K23" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L23" s="191" t="inlineStr">
+      <c r="K26" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=шаровый+кран+1/2"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L26" s="44" t="inlineStr">
         <is>
           <t>Латунные фитинги, муфты, уплотнители</t>
         </is>
       </c>
     </row>
-    <row r="24" outlineLevel="1">
-      <c r="A24" s="192" t="n">
+    <row r="27">
+      <c r="A27" s="64" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="191" t="inlineStr">
+      <c r="B27" s="64" t="inlineStr">
         <is>
           <t>Входная группа</t>
         </is>
       </c>
-      <c r="C24" s="191" t="inlineStr">
+      <c r="C27" s="64" t="inlineStr">
         <is>
           <t>Двери</t>
         </is>
       </c>
-      <c r="D24" s="191" t="inlineStr">
+      <c r="D27" s="49" t="inlineStr">
         <is>
           <t>Покупка входной металлической двери с внутренней МДФ-панелью</t>
         </is>
       </c>
-      <c r="E24" s="191" t="inlineStr">
+      <c r="E27" s="64" t="inlineStr">
         <is>
           <t>ДВЕРЬ-ВХОД-МДФ</t>
         </is>
       </c>
-      <c r="F24" s="191" t="inlineStr">
+      <c r="F27" s="64" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G24" s="192" t="n">
+      <c r="G27" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="193" t="n">
+      <c r="H27" s="172" t="n">
         <v>16000</v>
       </c>
-      <c r="I24" s="193">
-        <f>G24*H24</f>
-        <v/>
-      </c>
-      <c r="J24" s="191" t="inlineStr">
+      <c r="I27" s="219">
+        <f>G27*H27</f>
+        <v/>
+      </c>
+      <c r="J27" s="49" t="inlineStr">
         <is>
           <t>Владимир (двери)</t>
         </is>
       </c>
-      <c r="K24" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L24" s="191" t="inlineStr">
+      <c r="K27" s="175">
+        <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=входная+металлическая+дверь+мдф"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L27" s="49" t="inlineStr">
         <is>
           <t>Металл 1.5 мм, МДФ-панель, надежные замки</t>
         </is>
       </c>
     </row>
-    <row r="25" outlineLevel="1">
-      <c r="A25" s="192" t="n">
+    <row r="28">
+      <c r="A28" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="191" t="inlineStr">
+      <c r="B28" s="62" t="inlineStr">
         <is>
           <t>Входная группа</t>
         </is>
       </c>
-      <c r="C25" s="191" t="inlineStr">
+      <c r="C28" s="62" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="D25" s="191" t="inlineStr">
+      <c r="D28" s="44" t="inlineStr">
         <is>
           <t>Доставка входной металлической двери на объект</t>
         </is>
       </c>
-      <c r="E25" s="191" t="inlineStr">
+      <c r="E28" s="62" t="inlineStr">
         <is>
           <t>ДОСТАВКА-ДВЕРЬ</t>
         </is>
       </c>
-      <c r="F25" s="191" t="inlineStr">
+      <c r="F28" s="62" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G25" s="192" t="n">
+      <c r="G28" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="193" t="n">
+      <c r="H28" s="173" t="n">
         <v>1500</v>
       </c>
-      <c r="I25" s="193">
-        <f>G25*H25</f>
-        <v/>
-      </c>
-      <c r="J25" s="191" t="inlineStr">
+      <c r="I28" s="217">
+        <f>G28*H28</f>
+        <v/>
+      </c>
+      <c r="J28" s="44" t="inlineStr">
         <is>
           <t>Владимир / Доставка</t>
         </is>
       </c>
-      <c r="K25" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L25" s="191" t="inlineStr">
+      <c r="K28" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=доставка+дверей+грузоперевозки"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L28" s="44" t="inlineStr">
         <is>
           <t>Транспортировка двери на ул. Фрунзе 17</t>
         </is>
       </c>
     </row>
-    <row r="26" outlineLevel="1">
-      <c r="A26" s="192" t="n">
+    <row r="29">
+      <c r="A29" s="64" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="191" t="inlineStr">
+      <c r="B29" s="64" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C26" s="191" t="inlineStr">
+      <c r="C29" s="64" t="inlineStr">
         <is>
           <t>Щит / Автоматика</t>
         </is>
       </c>
-      <c r="D26" s="191" t="inlineStr">
+      <c r="D29" s="49" t="inlineStr">
         <is>
           <t>Черновые материалы электрики (щит 18м, новый электросчётчик, автоматы, УЗО, гофра)</t>
         </is>
       </c>
-      <c r="E26" s="191" t="inlineStr">
+      <c r="E29" s="64" t="inlineStr">
         <is>
           <t>ЩИТ-АВТ-КОМПЛЕКТ</t>
         </is>
       </c>
-      <c r="F26" s="191" t="inlineStr">
+      <c r="F29" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G26" s="192" t="n">
+      <c r="G29" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="193" t="n">
+      <c r="H29" s="172" t="n">
         <v>16500</v>
       </c>
-      <c r="I26" s="193">
-        <f>G26*H26</f>
-        <v/>
-      </c>
-      <c r="J26" s="191" t="inlineStr">
+      <c r="I29" s="219">
+        <f>G29*H29</f>
+        <v/>
+      </c>
+      <c r="J29" s="49" t="inlineStr">
         <is>
           <t>Анатолий / Поставщик</t>
         </is>
       </c>
-      <c r="K26" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L26" s="191" t="inlineStr">
+      <c r="K29" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=щит+встраиваемый+18+модулей"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L29" s="49" t="inlineStr">
         <is>
           <t>Комплектная начинка щита и прибор учёта</t>
         </is>
       </c>
     </row>
-    <row r="27" outlineLevel="1">
-      <c r="A27" s="192" t="n">
+    <row r="30">
+      <c r="A30" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="191" t="inlineStr">
+      <c r="B30" s="62" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C27" s="191" t="inlineStr">
+      <c r="C30" s="62" t="inlineStr">
         <is>
           <t>Кабель</t>
         </is>
       </c>
-      <c r="D27" s="191" t="inlineStr">
+      <c r="D30" s="44" t="inlineStr">
         <is>
           <t>Кабель силовой ВВГнг-LS (ГОСТ 3х2.5 и 3х1.5 для всех трасс)</t>
         </is>
       </c>
-      <c r="E27" s="191" t="inlineStr">
+      <c r="E30" s="62" t="inlineStr">
         <is>
           <t>ВВГнг-LS-ГОСТ-1</t>
         </is>
       </c>
-      <c r="F27" s="191" t="inlineStr">
+      <c r="F30" s="62" t="inlineStr">
         <is>
           <t>бухта</t>
         </is>
       </c>
-      <c r="G27" s="192" t="n">
+      <c r="G30" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="193" t="n">
+      <c r="H30" s="173" t="n">
         <v>18000</v>
       </c>
-      <c r="I27" s="193">
-        <f>G27*H27</f>
-        <v/>
-      </c>
-      <c r="J27" s="191" t="inlineStr">
+      <c r="I30" s="217">
+        <f>G30*H30</f>
+        <v/>
+      </c>
+      <c r="J30" s="44" t="inlineStr">
         <is>
           <t>Электромонтаж / Поставщик</t>
         </is>
       </c>
-      <c r="K27" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L27" s="191" t="inlineStr">
+      <c r="K30" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=кабель+ВВГнг-LS+3х2.5"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L30" s="44" t="inlineStr">
         <is>
           <t>Силовой кабель ГОСТ под розетки и свет</t>
         </is>
       </c>
     </row>
-    <row r="28" outlineLevel="1">
-      <c r="A28" s="192" t="n">
+    <row r="31">
+      <c r="A31" s="64" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="191" t="inlineStr">
+      <c r="B31" s="64" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C28" s="191" t="inlineStr">
+      <c r="C31" s="64" t="inlineStr">
         <is>
           <t>Крепёж</t>
         </is>
       </c>
-      <c r="D28" s="191" t="inlineStr">
+      <c r="D31" s="49" t="inlineStr">
         <is>
           <t>Стяжки нейлоновые и крепёж для монтажа кабеля</t>
         </is>
       </c>
-      <c r="E28" s="191" t="inlineStr">
+      <c r="E31" s="64" t="inlineStr">
         <is>
           <t>КРЕПЕЖ-КАБЕЛЬ</t>
         </is>
       </c>
-      <c r="F28" s="191" t="inlineStr">
+      <c r="F31" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G28" s="192" t="n">
+      <c r="G31" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="193" t="n">
+      <c r="H31" s="172" t="n">
         <v>1000</v>
       </c>
-      <c r="I28" s="193">
-        <f>G28*H28</f>
-        <v/>
-      </c>
-      <c r="J28" s="191" t="inlineStr">
+      <c r="I31" s="219">
+        <f>G31*H31</f>
+        <v/>
+      </c>
+      <c r="J31" s="49" t="inlineStr">
         <is>
           <t>Хозмаг / Электромонтаж</t>
         </is>
       </c>
-      <c r="K28" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L28" s="191" t="inlineStr">
+      <c r="K31" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=дюбель+хомут+для+кабеля"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L31" s="49" t="inlineStr">
         <is>
           <t>Дюбель-хомуты и стяжки для трасс</t>
         </is>
       </c>
     </row>
-    <row r="29" outlineLevel="1">
-      <c r="A29" s="192" t="n">
+    <row r="32">
+      <c r="A32" s="62" t="n">
         <v>23</v>
       </c>
-      <c r="B29" s="191" t="inlineStr">
+      <c r="B32" s="62" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C29" s="191" t="inlineStr">
+      <c r="C32" s="62" t="inlineStr">
         <is>
           <t>Кабель</t>
         </is>
       </c>
-      <c r="D29" s="191" t="inlineStr">
+      <c r="D32" s="44" t="inlineStr">
         <is>
           <t>Докупка силового кабеля ВВГнг-LS (дополнительный метраж трасс)</t>
         </is>
       </c>
-      <c r="E29" s="191" t="inlineStr">
+      <c r="E32" s="62" t="inlineStr">
         <is>
           <t>ВВГнг-LS-ГОСТ-2</t>
         </is>
       </c>
-      <c r="F29" s="191" t="inlineStr">
+      <c r="F32" s="62" t="inlineStr">
         <is>
           <t>бухта</t>
         </is>
       </c>
-      <c r="G29" s="192" t="n">
+      <c r="G32" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="193" t="n">
+      <c r="H32" s="173" t="n">
         <v>13000</v>
       </c>
-      <c r="I29" s="193">
-        <f>G29*H29</f>
-        <v/>
-      </c>
-      <c r="J29" s="191" t="inlineStr">
+      <c r="I32" s="217">
+        <f>G32*H32</f>
+        <v/>
+      </c>
+      <c r="J32" s="44" t="inlineStr">
         <is>
           <t>Электромонтаж / Поставщик</t>
         </is>
       </c>
-      <c r="K29" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L29" s="191" t="inlineStr">
+      <c r="K32" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=кабель+ВВГнг-LS+3х1.5"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L32" s="44" t="inlineStr">
         <is>
           <t>Дополнительный кабель на трассы кухни и коридора</t>
         </is>
       </c>
     </row>
-    <row r="30" outlineLevel="1">
-      <c r="A30" s="192" t="n">
+    <row r="33">
+      <c r="A33" s="64" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="191" t="inlineStr">
+      <c r="B33" s="64" t="inlineStr">
         <is>
           <t>Оснащение</t>
         </is>
       </c>
-      <c r="C30" s="191" t="inlineStr">
+      <c r="C33" s="64" t="inlineStr">
         <is>
           <t>Инвентарь</t>
         </is>
       </c>
-      <c r="D30" s="191" t="inlineStr">
+      <c r="D33" s="49" t="inlineStr">
         <is>
           <t>Портативная акустика Xiaomi Bluetooth Speaker Essential Green</t>
         </is>
       </c>
-      <c r="E30" s="191" t="inlineStr">
+      <c r="E33" s="64" t="inlineStr">
         <is>
           <t>XIAOMI-SPK-ESS</t>
         </is>
       </c>
-      <c r="F30" s="191" t="inlineStr">
+      <c r="F33" s="64" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G30" s="192" t="n">
+      <c r="G33" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="193" t="n">
+      <c r="H33" s="172" t="n">
         <v>1250</v>
       </c>
-      <c r="I30" s="193">
-        <f>G30*H30</f>
-        <v/>
-      </c>
-      <c r="J30" s="191" t="inlineStr">
+      <c r="I33" s="219">
+        <f>G33*H33</f>
+        <v/>
+      </c>
+      <c r="J33" s="49" t="inlineStr">
         <is>
           <t>ООО ДНС Ритейл (DNS)</t>
         </is>
       </c>
-      <c r="K30" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L30" s="191" t="inlineStr">
+      <c r="K33" s="175">
+        <f>HYPERLINK("https://www.dns-shop.ru/search/?q=Xiaomi+Bluetooth+Speaker"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L33" s="49" t="inlineStr">
         <is>
           <t>Акустическое оснащение объекта для бригад</t>
         </is>
       </c>
     </row>
-    <row r="31" outlineLevel="1">
-      <c r="A31" s="192" t="n">
+    <row r="34">
+      <c r="A34" s="62" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="191" t="inlineStr">
+      <c r="B34" s="62" t="inlineStr">
         <is>
           <t>Оснащение</t>
         </is>
       </c>
-      <c r="C31" s="191" t="inlineStr">
+      <c r="C34" s="62" t="inlineStr">
         <is>
           <t>Хознужды</t>
         </is>
       </c>
-      <c r="D31" s="191" t="inlineStr">
+      <c r="D34" s="44" t="inlineStr">
         <is>
           <t>Хозрасходы на объект: салфетки влажные и питьевая вода для мастеров</t>
         </is>
       </c>
-      <c r="E31" s="191" t="inlineStr">
+      <c r="E34" s="62" t="inlineStr">
         <is>
           <t>ХОЗ-ВОДА-САЛФЕТКИ</t>
         </is>
       </c>
-      <c r="F31" s="191" t="inlineStr">
+      <c r="F34" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G31" s="192" t="n">
+      <c r="G34" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="193" t="n">
+      <c r="H34" s="173" t="n">
         <v>520</v>
       </c>
-      <c r="I31" s="193">
-        <f>G31*H31</f>
-        <v/>
-      </c>
-      <c r="J31" s="191" t="inlineStr">
+      <c r="I34" s="217">
+        <f>G34*H34</f>
+        <v/>
+      </c>
+      <c r="J34" s="44" t="inlineStr">
         <is>
           <t>Хозмаг / Продукты</t>
         </is>
       </c>
-      <c r="K31" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L31" s="191" t="inlineStr">
+      <c r="K34" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/produkty_pitaniya?q=питьевая+вода+19л"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L34" s="44" t="inlineStr">
         <is>
           <t>Бытовое снабжение объекта</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="211" t="inlineStr"/>
-      <c r="B32" s="211" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="64" t="n">
+        <v>43</v>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>Канализация</t>
+        </is>
+      </c>
+      <c r="D35" s="49" t="inlineStr">
+        <is>
+          <t>Канализация с/у (муфта-восстановитель раструба 110/110, трубы ПП 50, тройник 110/50, заглушка, отводы)</t>
+        </is>
+      </c>
+      <c r="E35" s="64" t="inlineStr">
+        <is>
+          <t>КАНАЛ-СУ-110-50</t>
+        </is>
+      </c>
+      <c r="F35" s="64" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G35" s="218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="172" t="n">
+        <v>2988</v>
+      </c>
+      <c r="I35" s="219">
+        <f>G35*H35</f>
+        <v/>
+      </c>
+      <c r="J35" s="49" t="inlineStr">
+        <is>
+          <t>ИП Кучеров М.И. (Полимерстрой)</t>
+        </is>
+      </c>
+      <c r="K35" s="175">
+        <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=восстановитель+раструба+110"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L35" s="49" t="inlineStr">
+        <is>
+          <t>Чек от 15.09.2026: Муфта-восстановитель 110/110, разводка труб под ванну, раковину, унитаз</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="62" t="n">
+        <v>44</v>
+      </c>
+      <c r="B36" s="62" t="inlineStr">
+        <is>
+          <t>Санузел / Кухня</t>
+        </is>
+      </c>
+      <c r="C36" s="62" t="inlineStr">
+        <is>
+          <t>Водоснабжение</t>
+        </is>
+      </c>
+      <c r="D36" s="44" t="inlineStr">
+        <is>
+          <t>Трубы армированные Faser 20х2.8 12м, настенная планка смесителя, кран DN15, муфты, клипсы</t>
+        </is>
+      </c>
+      <c r="E36" s="62" t="inlineStr">
+        <is>
+          <t>PPR-FASER-WATSON</t>
+        </is>
+      </c>
+      <c r="F36" s="62" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G36" s="216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="173" t="n">
+        <v>3139.54</v>
+      </c>
+      <c r="I36" s="217">
+        <f>G36*H36</f>
+        <v/>
+      </c>
+      <c r="J36" s="44" t="inlineStr">
+        <is>
+          <t>ТС «Ваттсон» (Центргазсервис)</t>
+        </is>
+      </c>
+      <c r="K36" s="174">
+        <f>HYPERLINK("https://wattson.ru/search/?q=Faser+20"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L36" s="44" t="inlineStr">
+        <is>
+          <t>Чек №23 от 19.09.2026: Разводка труб ХВС/ГВС, шаровой кран ввода, планка под смеситель ванны</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="223" t="inlineStr"/>
+      <c r="B37" s="223" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ СПЕЦПОСТАВЩИКОВ:</t>
         </is>
       </c>
-      <c r="C32" s="211" t="inlineStr"/>
-      <c r="D32" s="211" t="inlineStr"/>
-      <c r="E32" s="211" t="inlineStr"/>
-      <c r="F32" s="211" t="inlineStr"/>
-      <c r="G32" s="211" t="inlineStr"/>
-      <c r="H32" s="211" t="inlineStr"/>
-      <c r="I32" s="212">
-        <f>SUM(I21:I31)</f>
-        <v/>
-      </c>
-      <c r="J32" s="211" t="inlineStr"/>
-      <c r="K32" s="211" t="inlineStr"/>
-      <c r="L32" s="211" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="208" t="inlineStr"/>
-      <c r="B33" s="208" t="inlineStr">
+      <c r="C37" s="223" t="inlineStr"/>
+      <c r="D37" s="223" t="inlineStr"/>
+      <c r="E37" s="223" t="inlineStr"/>
+      <c r="F37" s="223" t="inlineStr"/>
+      <c r="G37" s="223" t="inlineStr"/>
+      <c r="H37" s="223" t="inlineStr"/>
+      <c r="I37" s="224">
+        <f>SUM(I24:I36)</f>
+        <v/>
+      </c>
+      <c r="J37" s="223" t="inlineStr"/>
+      <c r="K37" s="223" t="inlineStr"/>
+      <c r="L37" s="223" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="208" t="inlineStr"/>
+      <c r="B38" s="208" t="inlineStr">
         <is>
           <t>👷‍♂️ БЛОК 3: РАБОТЫ МАСТЕРОВ, ОТДЕЛКА, ДЕМОНТАЖ И ЛОГИСТИКА</t>
         </is>
       </c>
-      <c r="C33" s="208" t="inlineStr"/>
-      <c r="D33" s="208" t="inlineStr"/>
-      <c r="E33" s="208" t="inlineStr"/>
-      <c r="F33" s="208" t="inlineStr"/>
-      <c r="G33" s="208" t="inlineStr"/>
-      <c r="H33" s="208" t="inlineStr"/>
-      <c r="I33" s="208" t="inlineStr"/>
-      <c r="J33" s="208" t="inlineStr"/>
-      <c r="K33" s="208" t="inlineStr"/>
-      <c r="L33" s="208" t="inlineStr"/>
-    </row>
-    <row r="34" outlineLevel="1">
-      <c r="A34" s="192" t="n">
+      <c r="C38" s="208" t="inlineStr"/>
+      <c r="D38" s="208" t="inlineStr"/>
+      <c r="E38" s="208" t="inlineStr"/>
+      <c r="F38" s="208" t="inlineStr"/>
+      <c r="G38" s="208" t="inlineStr"/>
+      <c r="H38" s="208" t="inlineStr"/>
+      <c r="I38" s="208" t="inlineStr"/>
+      <c r="J38" s="208" t="inlineStr"/>
+      <c r="K38" s="208" t="inlineStr"/>
+      <c r="L38" s="208" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="191" t="inlineStr">
+      <c r="B39" s="64" t="inlineStr">
         <is>
           <t>Безопасность</t>
         </is>
       </c>
-      <c r="C34" s="191" t="inlineStr">
+      <c r="C39" s="64" t="inlineStr">
         <is>
           <t>Вскрытие</t>
         </is>
       </c>
-      <c r="D34" s="191" t="inlineStr">
+      <c r="D39" s="49" t="inlineStr">
         <is>
           <t>Вскрытие старого замка и обеспечение первого доступа</t>
         </is>
       </c>
-      <c r="E34" s="191" t="inlineStr">
+      <c r="E39" s="64" t="inlineStr">
         <is>
           <t>ВСКРЫТИЕ-ЗАМКА</t>
         </is>
       </c>
-      <c r="F34" s="191" t="inlineStr">
+      <c r="F39" s="64" t="inlineStr">
         <is>
           <t>выезд</t>
         </is>
       </c>
-      <c r="G34" s="192" t="n">
+      <c r="G39" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="193" t="n">
+      <c r="H39" s="172" t="n">
         <v>8000</v>
       </c>
-      <c r="I34" s="193">
-        <f>G34*H34</f>
-        <v/>
-      </c>
-      <c r="J34" s="191" t="inlineStr">
+      <c r="I39" s="219">
+        <f>G39*H39</f>
+        <v/>
+      </c>
+      <c r="J39" s="49" t="inlineStr">
         <is>
           <t>Служба вскрытия</t>
         </is>
       </c>
-      <c r="K34" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L34" s="191" t="inlineStr">
+      <c r="K39" s="175">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=вскрытие+замков"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L39" s="49" t="inlineStr">
         <is>
           <t>Аварийное открытие двери после торгов</t>
         </is>
       </c>
     </row>
-    <row r="35" outlineLevel="1">
-      <c r="A35" s="192" t="n">
+    <row r="40">
+      <c r="A40" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="191" t="inlineStr">
+      <c r="B40" s="62" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C35" s="191" t="inlineStr">
+      <c r="C40" s="62" t="inlineStr">
         <is>
           <t>Вывоз мусора</t>
         </is>
       </c>
-      <c r="D35" s="191" t="inlineStr">
+      <c r="D40" s="44" t="inlineStr">
         <is>
           <t>Заказ мусорного контейнера 8 м³ (лодочка)</t>
         </is>
       </c>
-      <c r="E35" s="191" t="inlineStr">
+      <c r="E40" s="62" t="inlineStr">
         <is>
           <t>КОНТЕЙНЕР-МУСОР-8М3</t>
         </is>
       </c>
-      <c r="F35" s="191" t="inlineStr">
+      <c r="F40" s="62" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G35" s="192" t="n">
+      <c r="G40" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="193" t="n">
+      <c r="H40" s="173" t="n">
         <v>8500</v>
       </c>
-      <c r="I35" s="193">
-        <f>G35*H35</f>
-        <v/>
-      </c>
-      <c r="J35" s="191" t="inlineStr">
+      <c r="I40" s="217">
+        <f>G40*H40</f>
+        <v/>
+      </c>
+      <c r="J40" s="44" t="inlineStr">
         <is>
           <t>Елена (вывоз мусора)</t>
         </is>
       </c>
-      <c r="K35" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L35" s="191" t="inlineStr">
+      <c r="K40" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=вывоз+мусора+контейнер+8+м3"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L40" s="44" t="inlineStr">
         <is>
           <t>Вывоз мебели, санузла, чугуна, досок</t>
         </is>
       </c>
     </row>
-    <row r="36" outlineLevel="1">
-      <c r="A36" s="192" t="n">
+    <row r="41">
+      <c r="A41" s="64" t="n">
         <v>5</v>
       </c>
-      <c r="B36" s="191" t="inlineStr">
+      <c r="B41" s="64" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C36" s="191" t="inlineStr">
+      <c r="C41" s="64" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
-      <c r="D36" s="191" t="inlineStr">
+      <c r="D41" s="49" t="inlineStr">
         <is>
           <t>Аренда инструмента и помощь соседа по дому</t>
         </is>
       </c>
-      <c r="E36" s="191" t="inlineStr">
+      <c r="E41" s="64" t="inlineStr">
         <is>
           <t>АРЕНДА-ИНСТРУМЕНТ</t>
         </is>
       </c>
-      <c r="F36" s="191" t="inlineStr">
+      <c r="F41" s="64" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G36" s="192" t="n">
+      <c r="G41" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="193" t="n">
+      <c r="H41" s="172" t="n">
         <v>1000</v>
       </c>
-      <c r="I36" s="193">
-        <f>G36*H36</f>
-        <v/>
-      </c>
-      <c r="J36" s="191" t="inlineStr">
+      <c r="I41" s="219">
+        <f>G41*H41</f>
+        <v/>
+      </c>
+      <c r="J41" s="49" t="inlineStr">
         <is>
           <t>Сосед по дому</t>
         </is>
       </c>
-      <c r="K36" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L36" s="191" t="inlineStr">
+      <c r="K41" s="175">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=аренда+перфоратора"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L41" s="49" t="inlineStr">
         <is>
           <t>Перфоратор и монтировки для первичного демонтажа</t>
         </is>
       </c>
     </row>
-    <row r="37" outlineLevel="1">
-      <c r="A37" s="192" t="n">
+    <row r="42">
+      <c r="A42" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="B37" s="191" t="inlineStr">
+      <c r="B42" s="62" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C37" s="191" t="inlineStr">
+      <c r="C42" s="62" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D37" s="191" t="inlineStr">
+      <c r="D42" s="44" t="inlineStr">
         <is>
           <t>Оплата работы бригады разнорабочих (4 чел., 28 чел.-час, спуск с 5 этажа)</t>
         </is>
       </c>
-      <c r="E37" s="191" t="inlineStr">
+      <c r="E42" s="62" t="inlineStr">
         <is>
           <t>ДЕМОНТАЖ-БРИГАДА-1</t>
         </is>
       </c>
-      <c r="F37" s="191" t="inlineStr">
+      <c r="F42" s="62" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="G37" s="192" t="n">
+      <c r="G42" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="193" t="n">
+      <c r="H42" s="173" t="n">
         <v>16000</v>
       </c>
-      <c r="I37" s="193">
-        <f>G37*H37</f>
-        <v/>
-      </c>
-      <c r="J37" s="191" t="inlineStr">
+      <c r="I42" s="217">
+        <f>G42*H42</f>
+        <v/>
+      </c>
+      <c r="J42" s="44" t="inlineStr">
         <is>
           <t>Бригада разнорабочих</t>
         </is>
       </c>
-      <c r="K37" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L37" s="191" t="inlineStr">
+      <c r="K42" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=демонтаж+квартиры+разнорабочие"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L42" s="44" t="inlineStr">
         <is>
           <t>Тотальная зачистка и вынос мусора без лифта</t>
         </is>
       </c>
     </row>
-    <row r="38" outlineLevel="1">
-      <c r="A38" s="192" t="n">
+    <row r="43">
+      <c r="A43" s="64" t="n">
         <v>18</v>
       </c>
-      <c r="B38" s="191" t="inlineStr">
+      <c r="B43" s="64" t="inlineStr">
         <is>
           <t>Входная группа</t>
         </is>
       </c>
-      <c r="C38" s="191" t="inlineStr">
+      <c r="C43" s="64" t="inlineStr">
         <is>
           <t>Монтаж</t>
         </is>
       </c>
-      <c r="D38" s="191" t="inlineStr">
+      <c r="D43" s="49" t="inlineStr">
         <is>
           <t>Монтаж входной двери (демонтаж 2 старых дверей + монтаж новой)</t>
         </is>
       </c>
-      <c r="E38" s="191" t="inlineStr">
+      <c r="E43" s="64" t="inlineStr">
         <is>
           <t>МОНТАЖ-ДВЕРИ-ВХОД</t>
         </is>
       </c>
-      <c r="F38" s="191" t="inlineStr">
+      <c r="F43" s="64" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G38" s="192" t="n">
+      <c r="G43" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="193" t="n">
+      <c r="H43" s="172" t="n">
         <v>9000</v>
       </c>
-      <c r="I38" s="193">
-        <f>G38*H38</f>
-        <v/>
-      </c>
-      <c r="J38" s="191" t="inlineStr">
+      <c r="I43" s="219">
+        <f>G43*H43</f>
+        <v/>
+      </c>
+      <c r="J43" s="49" t="inlineStr">
         <is>
           <t>Андрей (монтаж дверей)</t>
         </is>
       </c>
-      <c r="K38" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L38" s="191" t="inlineStr">
+      <c r="K43" s="175">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=установка+входных+дверей"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L43" s="49" t="inlineStr">
         <is>
           <t>Сняли старые двери, расширили проем, выставили по уровню</t>
         </is>
       </c>
     </row>
-    <row r="39" outlineLevel="1">
-      <c r="A39" s="192" t="n">
+    <row r="44">
+      <c r="A44" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="B39" s="191" t="inlineStr">
+      <c r="B44" s="62" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C39" s="191" t="inlineStr">
+      <c r="C44" s="62" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D39" s="191" t="inlineStr">
+      <c r="D44" s="44" t="inlineStr">
         <is>
           <t>Электромонтажные работы под ключ (разводка 32 точек, штробы, щит, счётчик)</t>
         </is>
       </c>
-      <c r="E39" s="191" t="inlineStr">
+      <c r="E44" s="62" t="inlineStr">
         <is>
           <t>РАБОТА-ЭЛЕКТРИКА-32</t>
         </is>
       </c>
-      <c r="F39" s="191" t="inlineStr">
+      <c r="F44" s="62" t="inlineStr">
         <is>
           <t>договор</t>
         </is>
       </c>
-      <c r="G39" s="192" t="n">
+      <c r="G44" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="193" t="n">
+      <c r="H44" s="173" t="n">
         <v>50000</v>
       </c>
-      <c r="I39" s="193">
-        <f>G39*H39</f>
-        <v/>
-      </c>
-      <c r="J39" s="191" t="inlineStr">
+      <c r="I44" s="217">
+        <f>G44*H44</f>
+        <v/>
+      </c>
+      <c r="J44" s="44" t="inlineStr">
         <is>
           <t>Анатолий Кушнарев (бригада)</t>
         </is>
       </c>
-      <c r="K39" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L39" s="191" t="inlineStr">
+      <c r="K44" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=электромонтаж+квартиры+под+ключ"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L44" s="44" t="inlineStr">
         <is>
           <t>Монтаж всей проводки, сборка щита и счётчика</t>
         </is>
       </c>
     </row>
-    <row r="40" outlineLevel="1">
-      <c r="A40" s="192" t="n">
+    <row r="45">
+      <c r="A45" s="64" t="n">
         <v>24</v>
       </c>
-      <c r="B40" s="191" t="inlineStr">
+      <c r="B45" s="64" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C40" s="191" t="inlineStr">
+      <c r="C45" s="64" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D40" s="191" t="inlineStr">
+      <c r="D45" s="49" t="inlineStr">
         <is>
           <t>Зачистка стен/потолка (обои, плитка в зале и спальне), вынос мусора, 1-й слой грунта</t>
         </is>
       </c>
-      <c r="E40" s="191" t="inlineStr">
+      <c r="E45" s="64" t="inlineStr">
         <is>
           <t>ДЕМОНТАЖ-ЗАЧИСТКА-2</t>
         </is>
       </c>
-      <c r="F40" s="191" t="inlineStr">
+      <c r="F45" s="64" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="G40" s="192" t="n">
+      <c r="G45" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="193" t="n">
+      <c r="H45" s="172" t="n">
         <v>15000</v>
       </c>
-      <c r="I40" s="193">
-        <f>G40*H40</f>
-        <v/>
-      </c>
-      <c r="J40" s="191" t="inlineStr">
+      <c r="I45" s="219">
+        <f>G45*H45</f>
+        <v/>
+      </c>
+      <c r="J45" s="49" t="inlineStr">
         <is>
           <t>Бригада разнорабочих</t>
         </is>
       </c>
-      <c r="K40" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L40" s="191" t="inlineStr">
+      <c r="K45" s="175">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=зачистка+стен+демонтаж+обоев"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L45" s="49" t="inlineStr">
         <is>
           <t>Снятие старых слоев, обеспыливание поверхностей</t>
         </is>
       </c>
     </row>
-    <row r="41" outlineLevel="1">
-      <c r="A41" s="192" t="n">
+    <row r="46">
+      <c r="A46" s="62" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="191" t="inlineStr">
+      <c r="B46" s="62" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="C41" s="191" t="inlineStr">
+      <c r="C46" s="62" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
-      <c r="D41" s="191" t="inlineStr">
+      <c r="D46" s="44" t="inlineStr">
         <is>
           <t>Грузовое такси / Доставка закупки материалов и сантехники (Лемана — Фрунзе 17)</t>
         </is>
       </c>
-      <c r="E41" s="191" t="inlineStr">
+      <c r="E46" s="62" t="inlineStr">
         <is>
           <t>ГРУЗОТАКСИ-ЛЕРОЙ</t>
         </is>
       </c>
-      <c r="F41" s="191" t="inlineStr">
+      <c r="F46" s="62" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G41" s="192" t="n">
+      <c r="G46" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="193" t="n">
+      <c r="H46" s="173" t="n">
         <v>2100</v>
       </c>
-      <c r="I41" s="193">
-        <f>G41*H41</f>
-        <v/>
-      </c>
-      <c r="J41" s="191" t="inlineStr">
+      <c r="I46" s="217">
+        <f>G46*H46</f>
+        <v/>
+      </c>
+      <c r="J46" s="44" t="inlineStr">
         <is>
           <t>Грузовое такси / Перевозка</t>
         </is>
       </c>
-      <c r="K41" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L41" s="191" t="inlineStr">
+      <c r="K46" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=грузоперевозки+грузовое+такси"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L46" s="44" t="inlineStr">
         <is>
           <t>Перевозка партии смесей, керамогранита и ванны</t>
         </is>
       </c>
     </row>
-    <row r="42" outlineLevel="1">
-      <c r="A42" s="192" t="n">
+    <row r="47">
+      <c r="A47" s="64" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="191" t="inlineStr">
+      <c r="B47" s="64" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C42" s="191" t="inlineStr">
+      <c r="C47" s="64" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D42" s="191" t="inlineStr">
+      <c r="D47" s="49" t="inlineStr">
         <is>
           <t>Погрузка в Лемана ПРО, разгрузка и подъём на 5 этаж + демонтаж плитки пола с/у</t>
         </is>
       </c>
-      <c r="E42" s="191" t="inlineStr">
+      <c r="E47" s="64" t="inlineStr">
         <is>
           <t>ПОДЪЕМ-ДЕМОНТАЖ-СУ</t>
         </is>
       </c>
-      <c r="F42" s="191" t="inlineStr">
+      <c r="F47" s="64" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="G42" s="192" t="n">
+      <c r="G47" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="193" t="n">
+      <c r="H47" s="172" t="n">
         <v>15000</v>
       </c>
-      <c r="I42" s="193">
-        <f>G42*H42</f>
-        <v/>
-      </c>
-      <c r="J42" s="191" t="inlineStr">
+      <c r="I47" s="219">
+        <f>G47*H47</f>
+        <v/>
+      </c>
+      <c r="J47" s="49" t="inlineStr">
         <is>
           <t>Бригада грузчиков / Разнорабочие</t>
         </is>
       </c>
-      <c r="K42" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L42" s="191" t="inlineStr">
+      <c r="K47" s="175">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=подъем+стройматериалов+на+этаж+грузчики"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L47" s="49" t="inlineStr">
         <is>
           <t>Разгрузка 1.5 тонн смесей на 5 этаж без лифта</t>
         </is>
       </c>
     </row>
-    <row r="43" outlineLevel="1">
-      <c r="A43" s="192" t="n">
+    <row r="48">
+      <c r="A48" s="62" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="191" t="inlineStr">
+      <c r="B48" s="62" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C43" s="191" t="inlineStr">
+      <c r="C48" s="62" t="inlineStr">
         <is>
           <t>Отделочные работы</t>
         </is>
       </c>
-      <c r="D43" s="191" t="inlineStr">
+      <c r="D48" s="44" t="inlineStr">
         <is>
           <t>Штукатурка (69 м² по 500 ₽) и шпаклёвка стен White Box (106 м² по 500 ₽)</t>
         </is>
       </c>
-      <c r="E43" s="191" t="inlineStr">
+      <c r="E48" s="62" t="inlineStr">
         <is>
           <t>ОТДЕЛКА-СТЕН-ЕЛЕНА</t>
         </is>
       </c>
-      <c r="F43" s="191" t="inlineStr">
+      <c r="F48" s="62" t="inlineStr">
         <is>
           <t>комплекс</t>
         </is>
       </c>
-      <c r="G43" s="192" t="n">
+      <c r="G48" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="193" t="n">
+      <c r="H48" s="173" t="n">
         <v>87500</v>
       </c>
-      <c r="I43" s="193">
-        <f>G43*H43</f>
-        <v/>
-      </c>
-      <c r="J43" s="191" t="inlineStr">
+      <c r="I48" s="217">
+        <f>G48*H48</f>
+        <v/>
+      </c>
+      <c r="J48" s="44" t="inlineStr">
         <is>
           <t>Елена (мастер-отделочник)</t>
         </is>
       </c>
-      <c r="K43" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L43" s="191" t="inlineStr">
+      <c r="K48" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=штукатурка+шпаклевка+стен"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L48" s="44" t="inlineStr">
         <is>
           <t>Штукатурка 69 м² + шпаклёвка стен 106 м² по 500₽. White Box под ключ</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="211" t="inlineStr"/>
-      <c r="B44" s="211" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="223" t="inlineStr"/>
+      <c r="B49" s="223" t="inlineStr">
         <is>
           <t>ИТОГО РАБОТЫ И ЛОГИСТИКА:</t>
         </is>
       </c>
-      <c r="C44" s="211" t="inlineStr"/>
-      <c r="D44" s="211" t="inlineStr"/>
-      <c r="E44" s="211" t="inlineStr"/>
-      <c r="F44" s="211" t="inlineStr"/>
-      <c r="G44" s="211" t="inlineStr"/>
-      <c r="H44" s="211" t="inlineStr"/>
-      <c r="I44" s="212">
-        <f>SUM(I34:I43)</f>
-        <v/>
-      </c>
-      <c r="J44" s="211" t="inlineStr"/>
-      <c r="K44" s="211" t="inlineStr"/>
-      <c r="L44" s="211" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="209" t="inlineStr"/>
-      <c r="B45" s="209" t="inlineStr">
+      <c r="C49" s="223" t="inlineStr"/>
+      <c r="D49" s="223" t="inlineStr"/>
+      <c r="E49" s="223" t="inlineStr"/>
+      <c r="F49" s="223" t="inlineStr"/>
+      <c r="G49" s="223" t="inlineStr"/>
+      <c r="H49" s="223" t="inlineStr"/>
+      <c r="I49" s="224">
+        <f>SUM(I39:I48)</f>
+        <v/>
+      </c>
+      <c r="J49" s="223" t="inlineStr"/>
+      <c r="K49" s="223" t="inlineStr"/>
+      <c r="L49" s="223" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="225" t="inlineStr"/>
+      <c r="B50" s="225" t="inlineStr">
         <is>
           <t>🏛 БЛОК 4: ЮРИДИЧЕСКИЕ РАСХОДЫ, ПОШЛИНЫ, ГАЗ, ЭНЕРГОСБЫТ И IT</t>
         </is>
       </c>
-      <c r="C45" s="209" t="inlineStr"/>
-      <c r="D45" s="209" t="inlineStr"/>
-      <c r="E45" s="209" t="inlineStr"/>
-      <c r="F45" s="209" t="inlineStr"/>
-      <c r="G45" s="209" t="inlineStr"/>
-      <c r="H45" s="209" t="inlineStr"/>
-      <c r="I45" s="209" t="inlineStr"/>
-      <c r="J45" s="209" t="inlineStr"/>
-      <c r="K45" s="209" t="inlineStr"/>
-      <c r="L45" s="209" t="inlineStr"/>
-    </row>
-    <row r="46" outlineLevel="1">
-      <c r="A46" s="192" t="n">
+      <c r="C50" s="225" t="inlineStr"/>
+      <c r="D50" s="225" t="inlineStr"/>
+      <c r="E50" s="225" t="inlineStr"/>
+      <c r="F50" s="225" t="inlineStr"/>
+      <c r="G50" s="225" t="inlineStr"/>
+      <c r="H50" s="225" t="inlineStr"/>
+      <c r="I50" s="225" t="inlineStr"/>
+      <c r="J50" s="225" t="inlineStr"/>
+      <c r="K50" s="225" t="inlineStr"/>
+      <c r="L50" s="225" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="B46" s="191" t="inlineStr">
+      <c r="B51" s="64" t="inlineStr">
         <is>
           <t>Юр. оформление</t>
         </is>
       </c>
-      <c r="C46" s="191" t="inlineStr">
+      <c r="C51" s="64" t="inlineStr">
         <is>
           <t>Торги</t>
         </is>
       </c>
-      <c r="D46" s="191" t="inlineStr">
+      <c r="D51" s="49" t="inlineStr">
         <is>
           <t>Выпуск квалифицированной ЭЦП (электронная цифровая подпись)</t>
         </is>
       </c>
-      <c r="E46" s="191" t="inlineStr">
+      <c r="E51" s="64" t="inlineStr">
         <is>
           <t>ЭЦП-КОНТУР</t>
         </is>
       </c>
-      <c r="F46" s="191" t="inlineStr">
+      <c r="F51" s="64" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G46" s="192" t="n">
+      <c r="G51" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="193" t="n">
+      <c r="H51" s="172" t="n">
         <v>7000</v>
       </c>
-      <c r="I46" s="193">
-        <f>G46*H46</f>
-        <v/>
-      </c>
-      <c r="J46" s="191" t="inlineStr">
+      <c r="I51" s="219">
+        <f>G51*H51</f>
+        <v/>
+      </c>
+      <c r="J51" s="49" t="inlineStr">
         <is>
           <t>УЦ / Контур</t>
         </is>
       </c>
-      <c r="K46" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L46" s="191" t="inlineStr">
+      <c r="K51" s="175">
+        <f>HYPERLINK("https://ca.kontur.ru/"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L51" s="49" t="inlineStr">
         <is>
           <t>ЭЦП для участия в торгах и регистрации права</t>
         </is>
       </c>
     </row>
-    <row r="47" outlineLevel="1">
-      <c r="A47" s="192" t="n">
+    <row r="52">
+      <c r="A52" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="B47" s="191" t="inlineStr">
+      <c r="B52" s="62" t="inlineStr">
         <is>
           <t>Юр. оформление</t>
         </is>
       </c>
-      <c r="C47" s="191" t="inlineStr">
+      <c r="C52" s="62" t="inlineStr">
         <is>
           <t>Росреестр</t>
         </is>
       </c>
-      <c r="D47" s="191" t="inlineStr">
+      <c r="D52" s="44" t="inlineStr">
         <is>
           <t>Государственная пошлина (регистрация перехода права собственности)</t>
         </is>
       </c>
-      <c r="E47" s="191" t="inlineStr">
+      <c r="E52" s="62" t="inlineStr">
         <is>
           <t>ГОСПОШЛИНА-ПРАВО</t>
         </is>
       </c>
-      <c r="F47" s="191" t="inlineStr">
+      <c r="F52" s="62" t="inlineStr">
         <is>
           <t>платеж</t>
         </is>
       </c>
-      <c r="G47" s="192" t="n">
+      <c r="G52" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="193" t="n">
+      <c r="H52" s="173" t="n">
         <v>5000</v>
       </c>
-      <c r="I47" s="193">
-        <f>G47*H47</f>
-        <v/>
-      </c>
-      <c r="J47" s="191" t="inlineStr">
+      <c r="I52" s="217">
+        <f>G52*H52</f>
+        <v/>
+      </c>
+      <c r="J52" s="44" t="inlineStr">
         <is>
           <t>Росреестр</t>
         </is>
       </c>
-      <c r="K47" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L47" s="191" t="inlineStr">
+      <c r="K52" s="174">
+        <f>HYPERLINK("https://rosreestr.gov.ru/"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L52" s="44" t="inlineStr">
         <is>
           <t>Официальная пошлина Росреестра</t>
         </is>
       </c>
     </row>
-    <row r="48" outlineLevel="1">
-      <c r="A48" s="192" t="n">
+    <row r="53">
+      <c r="A53" s="64" t="n">
         <v>10</v>
       </c>
-      <c r="B48" s="191" t="inlineStr">
+      <c r="B53" s="64" t="inlineStr">
         <is>
           <t>IT / AI</t>
         </is>
       </c>
-      <c r="C48" s="191" t="inlineStr">
+      <c r="C53" s="64" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="D48" s="191" t="inlineStr">
+      <c r="D53" s="49" t="inlineStr">
         <is>
           <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 1</t>
         </is>
       </c>
-      <c r="E48" s="191" t="inlineStr">
+      <c r="E53" s="64" t="inlineStr">
         <is>
           <t>OPENROUTER-TRANS-1</t>
         </is>
       </c>
-      <c r="F48" s="191" t="inlineStr">
+      <c r="F53" s="64" t="inlineStr">
         <is>
           <t>платёж</t>
         </is>
       </c>
-      <c r="G48" s="192" t="n">
+      <c r="G53" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="193" t="n">
+      <c r="H53" s="172" t="n">
         <v>3000</v>
       </c>
-      <c r="I48" s="193">
-        <f>G48*H48</f>
-        <v/>
-      </c>
-      <c r="J48" s="191" t="inlineStr">
+      <c r="I53" s="219">
+        <f>G53*H53</f>
+        <v/>
+      </c>
+      <c r="J53" s="49" t="inlineStr">
         <is>
           <t>OpenRouter</t>
         </is>
       </c>
-      <c r="K48" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L48" s="191" t="inlineStr">
+      <c r="K53" s="175">
+        <f>HYPERLINK("https://openrouter.ai/"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L53" s="49" t="inlineStr">
         <is>
           <t>Инфраструктура проектов и аналитика</t>
         </is>
       </c>
     </row>
-    <row r="49" outlineLevel="1">
-      <c r="A49" s="192" t="n">
+    <row r="54">
+      <c r="A54" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="B49" s="191" t="inlineStr">
+      <c r="B54" s="62" t="inlineStr">
         <is>
           <t>Газ</t>
         </is>
       </c>
-      <c r="C49" s="191" t="inlineStr">
+      <c r="C54" s="62" t="inlineStr">
         <is>
           <t>Безопасность</t>
         </is>
       </c>
-      <c r="D49" s="191" t="inlineStr">
+      <c r="D54" s="44" t="inlineStr">
         <is>
           <t>Акт ВДПО — проверка дымохода и вентканала</t>
         </is>
       </c>
-      <c r="E49" s="191" t="inlineStr">
+      <c r="E54" s="62" t="inlineStr">
         <is>
           <t>ВДПО-АКТ-ВЕНТ</t>
         </is>
       </c>
-      <c r="F49" s="191" t="inlineStr">
+      <c r="F54" s="62" t="inlineStr">
         <is>
           <t>акт</t>
         </is>
       </c>
-      <c r="G49" s="192" t="n">
+      <c r="G54" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="193" t="n">
+      <c r="H54" s="173" t="n">
         <v>1500</v>
       </c>
-      <c r="I49" s="193">
-        <f>G49*H49</f>
-        <v/>
-      </c>
-      <c r="J49" s="191" t="inlineStr">
+      <c r="I54" s="217">
+        <f>G54*H54</f>
+        <v/>
+      </c>
+      <c r="J54" s="44" t="inlineStr">
         <is>
           <t>ВДПО / Газовая служба</t>
         </is>
       </c>
-      <c r="K49" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L49" s="191" t="inlineStr">
+      <c r="K54" s="174">
+        <f>HYPERLINK("https://vdpo71.ru/"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L54" s="44" t="inlineStr">
         <is>
           <t>Обязательная проверка тяги для газовой колонки</t>
         </is>
       </c>
     </row>
-    <row r="50" outlineLevel="1">
-      <c r="A50" s="192" t="n">
+    <row r="55">
+      <c r="A55" s="64" t="n">
         <v>13</v>
       </c>
-      <c r="B50" s="191" t="inlineStr">
+      <c r="B55" s="64" t="inlineStr">
         <is>
           <t>Газ</t>
         </is>
       </c>
-      <c r="C50" s="191" t="inlineStr">
+      <c r="C55" s="64" t="inlineStr">
         <is>
           <t>Коммуналка</t>
         </is>
       </c>
-      <c r="D50" s="191" t="inlineStr">
+      <c r="D55" s="49" t="inlineStr">
         <is>
           <t>Оплата квитанций Тулагоргаз (платежки/техобслуживание)</t>
         </is>
       </c>
-      <c r="E50" s="191" t="inlineStr">
+      <c r="E55" s="64" t="inlineStr">
         <is>
           <t>ТУЛАГОРГАЗ-КВИТАНЦИЯ</t>
         </is>
       </c>
-      <c r="F50" s="191" t="inlineStr">
+      <c r="F55" s="64" t="inlineStr">
         <is>
           <t>платеж</t>
         </is>
       </c>
-      <c r="G50" s="192" t="n">
+      <c r="G55" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="193" t="n">
+      <c r="H55" s="172" t="n">
         <v>800</v>
       </c>
-      <c r="I50" s="193">
-        <f>G50*H50</f>
-        <v/>
-      </c>
-      <c r="J50" s="191" t="inlineStr">
+      <c r="I55" s="219">
+        <f>G55*H55</f>
+        <v/>
+      </c>
+      <c r="J55" s="49" t="inlineStr">
         <is>
           <t>Тулагоргаз</t>
         </is>
       </c>
-      <c r="K50" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L50" s="191" t="inlineStr">
+      <c r="K55" s="175">
+        <f>HYPERLINK("https://tulagorgaz.ru/"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L55" s="49" t="inlineStr">
         <is>
           <t>Погашение начислений газовой службы</t>
         </is>
       </c>
     </row>
-    <row r="51" outlineLevel="1">
-      <c r="A51" s="192" t="n">
+    <row r="56">
+      <c r="A56" s="62" t="n">
         <v>21</v>
       </c>
-      <c r="B51" s="191" t="inlineStr">
+      <c r="B56" s="62" t="inlineStr">
         <is>
           <t>Энергосбыт</t>
         </is>
       </c>
-      <c r="C51" s="191" t="inlineStr">
+      <c r="C56" s="62" t="inlineStr">
         <is>
           <t>Учёт</t>
         </is>
       </c>
-      <c r="D51" s="191" t="inlineStr">
+      <c r="D56" s="44" t="inlineStr">
         <is>
           <t>Срочный выезд инспектора ТНС энерго Тула (снятие пломбы со старого счётчика)</t>
         </is>
       </c>
-      <c r="E51" s="191" t="inlineStr">
+      <c r="E56" s="62" t="inlineStr">
         <is>
           <t>ТНС-ВЫЕЗД-ПЛОМБА</t>
         </is>
       </c>
-      <c r="F51" s="191" t="inlineStr">
+      <c r="F56" s="62" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G51" s="192" t="n">
+      <c r="G56" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="193" t="n">
+      <c r="H56" s="173" t="n">
         <v>2500</v>
       </c>
-      <c r="I51" s="193">
-        <f>G51*H51</f>
-        <v/>
-      </c>
-      <c r="J51" s="191" t="inlineStr">
+      <c r="I56" s="217">
+        <f>G56*H56</f>
+        <v/>
+      </c>
+      <c r="J56" s="44" t="inlineStr">
         <is>
           <t>АО "ТНС энерго Тула"</t>
         </is>
       </c>
-      <c r="K51" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L51" s="191" t="inlineStr">
+      <c r="K56" s="174">
+        <f>HYPERLINK("https://tns-e.ru/"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L56" s="44" t="inlineStr">
         <is>
           <t>Срочное снятие пломбы за 5 дней</t>
         </is>
       </c>
     </row>
-    <row r="52" outlineLevel="1">
-      <c r="A52" s="192" t="n">
+    <row r="57">
+      <c r="A57" s="64" t="n">
         <v>31</v>
       </c>
-      <c r="B52" s="191" t="inlineStr">
+      <c r="B57" s="64" t="inlineStr">
         <is>
           <t>IT / AI</t>
         </is>
       </c>
-      <c r="C52" s="191" t="inlineStr">
+      <c r="C57" s="64" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="D52" s="191" t="inlineStr">
+      <c r="D57" s="49" t="inlineStr">
         <is>
           <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 2</t>
         </is>
       </c>
-      <c r="E52" s="191" t="inlineStr">
+      <c r="E57" s="64" t="inlineStr">
         <is>
           <t>OPENROUTER-TRANS-2</t>
         </is>
       </c>
-      <c r="F52" s="191" t="inlineStr">
+      <c r="F57" s="64" t="inlineStr">
         <is>
           <t>платёж</t>
         </is>
       </c>
-      <c r="G52" s="192" t="n">
+      <c r="G57" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="193" t="n">
+      <c r="H57" s="172" t="n">
         <v>2500</v>
       </c>
-      <c r="I52" s="193">
-        <f>G52*H52</f>
-        <v/>
-      </c>
-      <c r="J52" s="191" t="inlineStr">
+      <c r="I57" s="219">
+        <f>G57*H57</f>
+        <v/>
+      </c>
+      <c r="J57" s="49" t="inlineStr">
         <is>
           <t>OpenRouter</t>
         </is>
       </c>
-      <c r="K52" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L52" s="191" t="inlineStr">
+      <c r="K57" s="175">
+        <f>HYPERLINK("https://openrouter.ai/"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L57" s="49" t="inlineStr">
         <is>
           <t>Пополнение баланса API для расчётов и смет</t>
         </is>
       </c>
     </row>
-    <row r="53" outlineLevel="1">
-      <c r="A53" s="192" t="n">
+    <row r="58">
+      <c r="A58" s="62" t="n">
         <v>33</v>
       </c>
-      <c r="B53" s="191" t="inlineStr">
+      <c r="B58" s="62" t="inlineStr">
         <is>
           <t>Энергосбыт</t>
         </is>
       </c>
-      <c r="C53" s="191" t="inlineStr">
+      <c r="C58" s="62" t="inlineStr">
         <is>
           <t>Учёт</t>
         </is>
       </c>
-      <c r="D53" s="191" t="inlineStr">
+      <c r="D58" s="44" t="inlineStr">
         <is>
           <t>Дистанционная распломбировка старого электросчётчика (согласование)</t>
         </is>
       </c>
-      <c r="E53" s="191" t="inlineStr">
+      <c r="E58" s="62" t="inlineStr">
         <is>
           <t>ТНС-РАСПЛОМБ-ДИСТ</t>
         </is>
       </c>
-      <c r="F53" s="191" t="inlineStr">
+      <c r="F58" s="62" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G53" s="192" t="n">
+      <c r="G58" s="216" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="193" t="n">
+      <c r="H58" s="173" t="n">
         <v>2200</v>
       </c>
-      <c r="I53" s="193">
-        <f>G53*H53</f>
-        <v/>
-      </c>
-      <c r="J53" s="191" t="inlineStr">
+      <c r="I58" s="217">
+        <f>G58*H58</f>
+        <v/>
+      </c>
+      <c r="J58" s="44" t="inlineStr">
         <is>
           <t>ТНС энерго Тула / Энергосбыт</t>
         </is>
       </c>
-      <c r="K53" s="194" t="inlineStr">
-        <is>
-          <t>Открыть ↗</t>
-        </is>
-      </c>
-      <c r="L53" s="191" t="inlineStr">
+      <c r="K58" s="174">
+        <f>HYPERLINK("https://tns-e.ru/"; "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L58" s="44" t="inlineStr">
         <is>
           <t>Официальное согласование замены электроузла</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="211" t="inlineStr"/>
-      <c r="B54" s="211" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="223" t="inlineStr"/>
+      <c r="B59" s="223" t="inlineStr">
         <is>
           <t>ИТОГО ЮР. РАСХОДЫ, СЛУЖБЫ И IT:</t>
         </is>
       </c>
-      <c r="C54" s="211" t="inlineStr"/>
-      <c r="D54" s="211" t="inlineStr"/>
-      <c r="E54" s="211" t="inlineStr"/>
-      <c r="F54" s="211" t="inlineStr"/>
-      <c r="G54" s="211" t="inlineStr"/>
-      <c r="H54" s="211" t="inlineStr"/>
-      <c r="I54" s="212">
-        <f>SUM(I46:I53)</f>
-        <v/>
-      </c>
-      <c r="J54" s="211" t="inlineStr"/>
-      <c r="K54" s="211" t="inlineStr"/>
-      <c r="L54" s="211" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="213" t="inlineStr"/>
-      <c r="B55" s="213" t="inlineStr">
+      <c r="C59" s="223" t="inlineStr"/>
+      <c r="D59" s="223" t="inlineStr"/>
+      <c r="E59" s="223" t="inlineStr"/>
+      <c r="F59" s="223" t="inlineStr"/>
+      <c r="G59" s="223" t="inlineStr"/>
+      <c r="H59" s="223" t="inlineStr"/>
+      <c r="I59" s="224">
+        <f>SUM(I51:I58)</f>
+        <v/>
+      </c>
+      <c r="J59" s="223" t="inlineStr"/>
+      <c r="K59" s="223" t="inlineStr"/>
+      <c r="L59" s="223" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="226" t="inlineStr"/>
+      <c r="B60" s="226" t="inlineStr">
         <is>
           <t>ОБЩИЙ ИТОГО ФАКТ РАСХОДОВ (ДИНАМИЧЕСКИЙ):</t>
         </is>
       </c>
-      <c r="C55" s="213" t="inlineStr"/>
-      <c r="D55" s="213" t="inlineStr"/>
-      <c r="E55" s="213" t="inlineStr"/>
-      <c r="F55" s="213" t="inlineStr"/>
-      <c r="G55" s="213" t="inlineStr"/>
-      <c r="H55" s="213" t="inlineStr"/>
-      <c r="I55" s="214">
-        <f>SUBTOTAL(109; I6:I18; I21:I31; I34:I43; I46:I53)</f>
-        <v/>
-      </c>
-      <c r="J55" s="213" t="inlineStr"/>
-      <c r="K55" s="213" t="inlineStr"/>
-      <c r="L55" s="213" t="inlineStr"/>
+      <c r="C60" s="226" t="inlineStr"/>
+      <c r="D60" s="226" t="inlineStr"/>
+      <c r="E60" s="226" t="inlineStr"/>
+      <c r="F60" s="226" t="inlineStr"/>
+      <c r="G60" s="226" t="inlineStr"/>
+      <c r="H60" s="226" t="inlineStr"/>
+      <c r="I60" s="227">
+        <f>SUBTOTAL(109; I6:I21; I24:I36; I39:I48; I51:I58)</f>
+        <v/>
+      </c>
+      <c r="J60" s="226" t="inlineStr"/>
+      <c r="K60" s="226" t="inlineStr"/>
+      <c r="L60" s="226" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
+++ b/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
@@ -317,7 +317,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -632,11 +632,27 @@
         <color rgb="000F172A"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1229,6 +1245,30 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="16" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="27" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1665,7 +1705,7 @@
         <v/>
       </c>
       <c r="D5" s="118">
-        <f>'Факт расходов'!F52</f>
+        <f>'Факт расходов'!F55</f>
         <v/>
       </c>
       <c r="E5" s="118" t="n">
@@ -1758,7 +1798,7 @@
         <v>23000</v>
       </c>
       <c r="C11" s="46">
-        <f>SUMIF('Факт расходов'!C5:C51, "*Юр.*", 'Факт расходов'!F5:F51)+SUMIF('Факт расходов'!C5:C51, "*Безопасность*", 'Факт расходов'!F5:F51)+SUMIF('Факт расходов'!C5:C51, "*IT*", 'Факт расходов'!F5:F51)+SUMIF('Факт расходов'!C5:C51, "*Электроэнергия*", 'Факт расходов'!F5:F51)</f>
+        <f>SUMIF('Факт расходов'!C5:C54, "*Юр.*", 'Факт расходов'!F5:F54)+SUMIF('Факт расходов'!C5:C54, "*Безопасность*", 'Факт расходов'!F5:F54)+SUMIF('Факт расходов'!C5:C54, "*IT*", 'Факт расходов'!F5:F54)+SUMIF('Факт расходов'!C5:C54, "*Электроэнергия*", 'Факт расходов'!F5:F54)</f>
         <v/>
       </c>
       <c r="D11" s="124">
@@ -2038,7 +2078,7 @@
         <v/>
       </c>
       <c r="C23" s="46">
-        <f>SUMIF('Факт расходов'!C5:C51, "*Демонтаж*", 'Факт расходов'!F5:F51)</f>
+        <f>SUMIF('Факт расходов'!C5:C54, "*Демонтаж*", 'Факт расходов'!F5:F54)</f>
         <v/>
       </c>
       <c r="D23" s="45">
@@ -2071,7 +2111,7 @@
         <v/>
       </c>
       <c r="C24" s="51">
-        <f>SUMIF('Факт расходов'!C5:C51, "*Двери*", 'Факт расходов'!F5:F51)</f>
+        <f>SUMIF('Факт расходов'!C5:C54, "*Двери*", 'Факт расходов'!F5:F54)</f>
         <v/>
       </c>
       <c r="D24" s="50">
@@ -2104,7 +2144,7 @@
         <v/>
       </c>
       <c r="C25" s="46">
-        <f>SUMIF('Факт расходов'!C5:C51, "*Электрика*", 'Факт расходов'!F5:F51)</f>
+        <f>SUMIF('Факт расходов'!C5:C54, "*Электрика*", 'Факт расходов'!F5:F54)</f>
         <v/>
       </c>
       <c r="D25" s="45">
@@ -2137,7 +2177,7 @@
         <v/>
       </c>
       <c r="C26" s="51">
-        <f>SUMIF('Факт расходов'!C5:C51, "*Сантехника*", 'Факт расходов'!F5:F51)</f>
+        <f>SUMIF('Факт расходов'!C5:C54, "*Сантехника*", 'Факт расходов'!F5:F54)</f>
         <v/>
       </c>
       <c r="D26" s="50">
@@ -2169,7 +2209,7 @@
         <v>5000</v>
       </c>
       <c r="C27" s="46">
-        <f>SUMIF('Факт расходов'!C5:C51, "*Газ*", 'Факт расходов'!F5:F51)</f>
+        <f>SUMIF('Факт расходов'!C5:C54, "*Газ*", 'Факт расходов'!F5:F54)</f>
         <v/>
       </c>
       <c r="D27" s="45">
@@ -2234,7 +2274,7 @@
         <v/>
       </c>
       <c r="C29" s="46">
-        <f>SUMIF('Факт расходов'!C5:C51, "*Черновая*", 'Факт расходов'!F5:F51)</f>
+        <f>SUMIF('Факт расходов'!C5:C54, "*Черновая*", 'Факт расходов'!F5:F54)</f>
         <v/>
       </c>
       <c r="D29" s="45">
@@ -2267,7 +2307,7 @@
         <v/>
       </c>
       <c r="C30" s="51">
-        <f>SUMIF('Факт расходов'!C5:C51, "*Чистовая*", 'Факт расходов'!F5:F51)</f>
+        <f>SUMIF('Факт расходов'!C5:C54, "*Чистовая*", 'Факт расходов'!F5:F54)</f>
         <v/>
       </c>
       <c r="D30" s="50">
@@ -2427,7 +2467,7 @@
         <v>10000</v>
       </c>
       <c r="C35" s="46">
-        <f>SUMIF('Факт расходов'!C5:C51, "*Инструмент*", 'Факт расходов'!F5:F51)+SUMIF('Факт расходов'!C5:C51, "*Расходные*", 'Факт расходов'!F5:F51)+SUMIF('Факт расходов'!C5:C51, "*Логистика*", 'Факт расходов'!F5:F51)</f>
+        <f>SUMIF('Факт расходов'!C5:C54, "*Инструмент*", 'Факт расходов'!F5:F54)+SUMIF('Факт расходов'!C5:C54, "*Расходные*", 'Факт расходов'!F5:F54)+SUMIF('Факт расходов'!C5:C54, "*Логистика*", 'Факт расходов'!F5:F54)</f>
         <v/>
       </c>
       <c r="D35" s="45">
@@ -2459,7 +2499,7 @@
         <v>5000</v>
       </c>
       <c r="C36" s="51">
-        <f>SUMIF('Факт расходов'!C5:C51, "*Оснащение*", 'Факт расходов'!F5:F51)</f>
+        <f>SUMIF('Факт расходов'!C5:C54, "*Оснащение*", 'Факт расходов'!F5:F54)</f>
         <v/>
       </c>
       <c r="D36" s="50">
@@ -2641,11 +2681,11 @@
         </is>
       </c>
       <c r="B45" s="45">
-        <f>'Факт расходов'!E52</f>
+        <f>'Факт расходов'!E55</f>
         <v/>
       </c>
       <c r="C45" s="45">
-        <f>'Факт расходов'!F52</f>
+        <f>'Факт расходов'!F55</f>
         <v/>
       </c>
       <c r="D45" s="124">
@@ -2728,7 +2768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5102,81 +5142,177 @@
       <c r="M51" s="140" t="n"/>
       <c r="N51" s="140" t="n"/>
     </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="94" t="n"/>
-      <c r="B52" s="94" t="n"/>
-      <c r="C52" s="54" t="n"/>
-      <c r="D52" s="65" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДОВ:</t>
-        </is>
-      </c>
-      <c r="E52" s="55">
-        <f>SUM(E5:E51)</f>
-        <v/>
-      </c>
-      <c r="F52" s="55">
-        <f>SUM(F5:F51)</f>
-        <v/>
-      </c>
-      <c r="G52" s="55">
-        <f>SUM(G5:G51)</f>
-        <v/>
-      </c>
-      <c r="H52" s="104">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="64" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="64" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="C52" s="49" t="inlineStr">
+        <is>
+          <t>Сантехника / Работы</t>
+        </is>
+      </c>
+      <c r="D52" s="49" t="inlineStr">
+        <is>
+          <t>Работы сантехника: демонтаж (срезка) полотенцесушителя и нарезка резьб на трубах стояка</t>
+        </is>
+      </c>
+      <c r="E52" s="50" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F52" s="51" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G52" s="47">
+        <f>E52-F52</f>
+        <v/>
+      </c>
+      <c r="H52" s="63">
         <f>IFERROR(G52/E52, 0)</f>
         <v/>
       </c>
-      <c r="I52" s="54" t="n"/>
-      <c r="J52" s="54" t="n"/>
+      <c r="I52" s="49" t="inlineStr">
+        <is>
+          <t>Вадим (сантехник УК) / Сантехник</t>
+        </is>
+      </c>
+      <c r="J52" s="49" t="inlineStr">
+        <is>
+          <t>Срезка старого полотенцесушителя (змеевика), нарезка 2 трубных резьб клуппом под установку запорных кранов</t>
+        </is>
+      </c>
       <c r="K52" s="140" t="n"/>
       <c r="L52" s="140" t="n"/>
       <c r="M52" s="140" t="n"/>
       <c r="N52" s="140" t="n"/>
     </row>
-    <row r="53">
-      <c r="A53" s="140" t="n"/>
-      <c r="B53" s="140" t="n"/>
-      <c r="C53" s="140" t="n"/>
-      <c r="D53" s="140" t="n"/>
-      <c r="E53" s="140" t="n"/>
-      <c r="F53" s="140" t="n"/>
-      <c r="G53" s="140" t="n"/>
-      <c r="H53" s="140" t="n"/>
-      <c r="I53" s="140" t="n"/>
-      <c r="J53" s="140" t="n"/>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="62" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="62" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="C53" s="44" t="inlineStr">
+        <is>
+          <t>Логистика и доставка</t>
+        </is>
+      </c>
+      <c r="D53" s="44" t="inlineStr">
+        <is>
+          <t>Такси (доставка / оперативный подвоз материалов и инструмента из Лемана ПРО на объект)</t>
+        </is>
+      </c>
+      <c r="E53" s="45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F53" s="46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G53" s="47">
+        <f>E53-F53</f>
+        <v/>
+      </c>
+      <c r="H53" s="63">
+        <f>IFERROR(G53/E53, 0)</f>
+        <v/>
+      </c>
+      <c r="I53" s="44" t="inlineStr">
+        <is>
+          <t>Такси (Яндекс Go)</t>
+        </is>
+      </c>
+      <c r="J53" s="44" t="inlineStr">
+        <is>
+          <t>Оперативная доставка закупленного инструмента и материалов из Лемана ПРО на ул. Фрунзе 17</t>
+        </is>
+      </c>
       <c r="K53" s="140" t="n"/>
       <c r="L53" s="140" t="n"/>
       <c r="M53" s="140" t="n"/>
       <c r="N53" s="140" t="n"/>
     </row>
-    <row r="54">
-      <c r="A54" s="140" t="n"/>
-      <c r="B54" s="140" t="n"/>
-      <c r="C54" s="140" t="n"/>
-      <c r="D54" s="140" t="n"/>
-      <c r="E54" s="140" t="n"/>
-      <c r="F54" s="140" t="n"/>
-      <c r="G54" s="140" t="n"/>
-      <c r="H54" s="140" t="n"/>
-      <c r="I54" s="140" t="n"/>
-      <c r="J54" s="140" t="n"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="64" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="64" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="C54" s="49" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D54" s="49" t="inlineStr">
+        <is>
+          <t>Пистолет для герметика (скелетный/усиленный) и герметик санитарный силиконовый (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="E54" s="50" t="n">
+        <v>650</v>
+      </c>
+      <c r="F54" s="51" t="n">
+        <v>650</v>
+      </c>
+      <c r="G54" s="47">
+        <f>E54-F54</f>
+        <v/>
+      </c>
+      <c r="H54" s="63">
+        <f>IFERROR(G54/E54, 0)</f>
+        <v/>
+      </c>
+      <c r="I54" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J54" s="49" t="inlineStr">
+        <is>
+          <t>Пистолет для туб герметика + влагостойкий санитарный герметик для санузла и ванны</t>
+        </is>
+      </c>
       <c r="K54" s="140" t="n"/>
       <c r="L54" s="140" t="n"/>
       <c r="M54" s="140" t="n"/>
       <c r="N54" s="140" t="n"/>
     </row>
-    <row r="55">
-      <c r="A55" s="140" t="n"/>
-      <c r="B55" s="140" t="n"/>
-      <c r="C55" s="140" t="n"/>
-      <c r="D55" s="140" t="n"/>
-      <c r="E55" s="140" t="n"/>
-      <c r="F55" s="140" t="n"/>
-      <c r="G55" s="140" t="n"/>
-      <c r="H55" s="140" t="n"/>
-      <c r="I55" s="140" t="n"/>
-      <c r="J55" s="140" t="n"/>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="94" t="n"/>
+      <c r="B55" s="94" t="n"/>
+      <c r="C55" s="54" t="n"/>
+      <c r="D55" s="65" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДОВ:</t>
+        </is>
+      </c>
+      <c r="E55" s="55">
+        <f>SUM(E5:E54)</f>
+        <v/>
+      </c>
+      <c r="F55" s="55">
+        <f>SUM(F5:F54)</f>
+        <v/>
+      </c>
+      <c r="G55" s="55">
+        <f>SUM(G5:G54)</f>
+        <v/>
+      </c>
+      <c r="H55" s="104">
+        <f>IFERROR(G55/E55, 0)</f>
+        <v/>
+      </c>
+      <c r="I55" s="54" t="n"/>
+      <c r="J55" s="54" t="n"/>
       <c r="K55" s="140" t="n"/>
       <c r="L55" s="140" t="n"/>
       <c r="M55" s="140" t="n"/>
@@ -5437,6 +5573,54 @@
       <c r="L71" s="140" t="n"/>
       <c r="M71" s="140" t="n"/>
       <c r="N71" s="140" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="140" t="n"/>
+      <c r="B72" s="140" t="n"/>
+      <c r="C72" s="140" t="n"/>
+      <c r="D72" s="140" t="n"/>
+      <c r="E72" s="140" t="n"/>
+      <c r="F72" s="140" t="n"/>
+      <c r="G72" s="140" t="n"/>
+      <c r="H72" s="140" t="n"/>
+      <c r="I72" s="140" t="n"/>
+      <c r="J72" s="140" t="n"/>
+      <c r="K72" s="140" t="n"/>
+      <c r="L72" s="140" t="n"/>
+      <c r="M72" s="140" t="n"/>
+      <c r="N72" s="140" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="140" t="n"/>
+      <c r="B73" s="140" t="n"/>
+      <c r="C73" s="140" t="n"/>
+      <c r="D73" s="140" t="n"/>
+      <c r="E73" s="140" t="n"/>
+      <c r="F73" s="140" t="n"/>
+      <c r="G73" s="140" t="n"/>
+      <c r="H73" s="140" t="n"/>
+      <c r="I73" s="140" t="n"/>
+      <c r="J73" s="140" t="n"/>
+      <c r="K73" s="140" t="n"/>
+      <c r="L73" s="140" t="n"/>
+      <c r="M73" s="140" t="n"/>
+      <c r="N73" s="140" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="140" t="n"/>
+      <c r="B74" s="140" t="n"/>
+      <c r="C74" s="140" t="n"/>
+      <c r="D74" s="140" t="n"/>
+      <c r="E74" s="140" t="n"/>
+      <c r="F74" s="140" t="n"/>
+      <c r="G74" s="140" t="n"/>
+      <c r="H74" s="140" t="n"/>
+      <c r="I74" s="140" t="n"/>
+      <c r="J74" s="140" t="n"/>
+      <c r="K74" s="140" t="n"/>
+      <c r="L74" s="140" t="n"/>
+      <c r="M74" s="140" t="n"/>
+      <c r="N74" s="140" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5937,27 +6121,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="45" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="38" t="inlineStr">
         <is>
-          <t>ГЕНЕРАЛЬНАЯ МАТРИЦА БЮДЖЕТА И КОМПЛЕКТАЦИИ (418 386,41 ₽)</t>
+          <t>ГЕНЕРАЛЬНАЯ МАТРИЦА БЮДЖЕТА И КОМПЛЕКТАЦИИ (423 036,41 ₽)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -5972,10 +6156,10 @@
       <c r="K1" t="inlineStr"/>
       <c r="L1" t="inlineStr"/>
     </row>
-    <row r="2">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Полная структура расходов Фрунзе 17 | Точная сверка с листом «Факт расходов» (1-в-1 до копейки, все 47 позиций)</t>
+          <t>Полная структура расходов Фрунзе 17 | Точная сверка с листом «Факт расходов» (1-в-1 до копейки, все 50 позиций)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -5990,7 +6174,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
     </row>
-    <row r="3">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="39" t="inlineStr">
         <is>
           <t>💡 Используй слева значки [-] и [+] для сворачивания блоков (Материалы, Работы, Юр. расходы), либо фильтр по Зоне</t>
@@ -6008,7 +6192,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
     </row>
-    <row r="4">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="162" t="inlineStr">
         <is>
           <t>№ в Факте</t>
@@ -6070,11 +6254,11 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="205" t="inlineStr"/>
       <c r="B5" s="205" t="inlineStr">
         <is>
-          <t>🛁 БЛОК 1: СТРОИТЕЛЬНЫЕ И ЧИСТОВЫЕ МАТЕРИАЛЫ «ЛЕМАНА ПРО» (16 ЧЕКОВ)</t>
+          <t>🛁 БЛОК 1: СТРОИТЕЛЬНЫЕ И ЧИСТОВЫЕ МАТЕРИАЛЫ «ЛЕМАНА ПРО» (17 ЧЕКОВ)</t>
         </is>
       </c>
       <c r="C5" s="205" t="inlineStr"/>
@@ -6088,7 +6272,7 @@
       <c r="K5" s="205" t="inlineStr"/>
       <c r="L5" s="205" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="6" ht="19" customHeight="1">
       <c r="A6" s="62" t="n">
         <v>8</v>
       </c>
@@ -6133,7 +6317,7 @@
         </is>
       </c>
       <c r="K6" s="174">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=мешки+для+пылесоса+12л"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=мешки+для+пылесоса+12л", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L6" s="44" t="inlineStr">
@@ -6142,7 +6326,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="19" customHeight="1">
       <c r="A7" s="64" t="n">
         <v>9</v>
       </c>
@@ -6187,7 +6371,7 @@
         </is>
       </c>
       <c r="K7" s="175">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=лом+гвоздодер"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=лом+гвоздодер", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L7" s="49" t="inlineStr">
@@ -6196,7 +6380,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="19" customHeight="1">
       <c r="A8" s="62" t="n">
         <v>25</v>
       </c>
@@ -6241,7 +6425,7 @@
         </is>
       </c>
       <c r="K8" s="174">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=грунт+axton+10л"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=грунт+axton+10л", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L8" s="44" t="inlineStr">
@@ -6250,7 +6434,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="19" customHeight="1">
       <c r="A9" s="64" t="n">
         <v>26</v>
       </c>
@@ -6295,7 +6479,7 @@
         </is>
       </c>
       <c r="K9" s="175">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=ведро+строительное+20л"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=ведро+строительное+20л", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L9" s="49" t="inlineStr">
@@ -6304,7 +6488,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="19" customHeight="1">
       <c r="A10" s="62" t="n">
         <v>28</v>
       </c>
@@ -6349,7 +6533,7 @@
         </is>
       </c>
       <c r="K10" s="174">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=шпатлевка+старатели+20кг"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=шпатлевка+старатели+20кг", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L10" s="44" t="inlineStr">
@@ -6358,7 +6542,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="19" customHeight="1">
       <c r="A11" s="64" t="n">
         <v>30</v>
       </c>
@@ -6403,7 +6587,7 @@
         </is>
       </c>
       <c r="K11" s="175">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=бетонконтакт+axton+12кг"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=бетонконтакт+axton+12кг", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L11" s="49" t="inlineStr">
@@ -6412,7 +6596,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="19" customHeight="1">
       <c r="A12" s="62" t="n">
         <v>32</v>
       </c>
@@ -6457,7 +6641,7 @@
         </is>
       </c>
       <c r="K12" s="174">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=шпатлевка+финишная+старатели"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=шпатлевка+финишная+старатели", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L12" s="44" t="inlineStr">
@@ -6466,7 +6650,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="19" customHeight="1">
       <c r="A13" s="64" t="n">
         <v>34</v>
       </c>
@@ -6511,7 +6695,7 @@
         </is>
       </c>
       <c r="K13" s="175">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4600779023659"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4600779023659", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L13" s="49" t="inlineStr">
@@ -6520,7 +6704,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="19" customHeight="1">
       <c r="A14" s="62" t="n">
         <v>35</v>
       </c>
@@ -6565,7 +6749,7 @@
         </is>
       </c>
       <c r="K14" s="174">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4673766221451"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4673766221451", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L14" s="44" t="inlineStr">
@@ -6574,7 +6758,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="19" customHeight="1">
       <c r="A15" s="64" t="n">
         <v>36</v>
       </c>
@@ -6619,7 +6803,7 @@
         </is>
       </c>
       <c r="K15" s="175">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4607005180063"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4607005180063", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L15" s="49" t="inlineStr">
@@ -6628,7 +6812,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="19" customHeight="1">
       <c r="A16" s="62" t="n">
         <v>37</v>
       </c>
@@ -6673,7 +6857,7 @@
         </is>
       </c>
       <c r="K16" s="174">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4610085150475"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4610085150475", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L16" s="44" t="inlineStr">
@@ -6682,7 +6866,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="19" customHeight="1">
       <c r="A17" s="64" t="n">
         <v>38</v>
       </c>
@@ -6727,7 +6911,7 @@
         </is>
       </c>
       <c r="K17" s="175">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=штукатурка+старатели+30кг"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=штукатурка+старатели+30кг", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L17" s="49" t="inlineStr">
@@ -6736,7 +6920,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="19" customHeight="1">
       <c r="A18" s="62" t="n">
         <v>39</v>
       </c>
@@ -6781,7 +6965,7 @@
         </is>
       </c>
       <c r="K18" s="174">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=пескобетон+м300"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=пескобетон+м300", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L18" s="44" t="inlineStr">
@@ -6790,7 +6974,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="19" customHeight="1">
       <c r="A19" s="64" t="n">
         <v>45</v>
       </c>
@@ -6835,7 +7019,7 @@
         </is>
       </c>
       <c r="K19" s="175">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4601745000407"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4601745000407", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L19" s="49" t="inlineStr">
@@ -6844,7 +7028,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="19" customHeight="1">
       <c r="A20" s="62" t="n">
         <v>46</v>
       </c>
@@ -6889,7 +7073,7 @@
         </is>
       </c>
       <c r="K20" s="174">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=3276007227604"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=3276007227604", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L20" s="44" t="inlineStr">
@@ -6898,7 +7082,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="19" customHeight="1">
       <c r="A21" s="64" t="n">
         <v>47</v>
       </c>
@@ -6943,7 +7127,7 @@
         </is>
       </c>
       <c r="K21" s="175">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4650068600092"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4650068600092", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L21" s="49" t="inlineStr">
@@ -6952,121 +7136,121 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="223" t="inlineStr"/>
-      <c r="B22" s="223" t="inlineStr">
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="62" t="n">
+        <v>50</v>
+      </c>
+      <c r="B22" s="62" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C22" s="62" t="inlineStr">
+        <is>
+          <t>Расходники / Инструмент</t>
+        </is>
+      </c>
+      <c r="D22" s="44" t="inlineStr">
+        <is>
+          <t>Пистолет для герметика скелетный + герметик санитарный силиконовый (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="E22" s="62" t="inlineStr">
+        <is>
+          <t>82420455</t>
+        </is>
+      </c>
+      <c r="F22" s="62" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G22" s="216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="173" t="n">
+        <v>650</v>
+      </c>
+      <c r="I22" s="217">
+        <f>G22*H22</f>
+        <v/>
+      </c>
+      <c r="J22" s="44" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K22" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=пистолет+для+герметика", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L22" s="44" t="inlineStr">
+        <is>
+          <t>Покупка от 21.09.2026: Пистолет и санитарный герметик для ванны и швов</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="234" t="inlineStr"/>
+      <c r="B23" s="234" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ ЛЕМАНА ПРО (ПО ЧЕКАМ):</t>
         </is>
       </c>
-      <c r="C22" s="223" t="inlineStr"/>
-      <c r="D22" s="223" t="inlineStr"/>
-      <c r="E22" s="223" t="inlineStr"/>
-      <c r="F22" s="223" t="inlineStr"/>
-      <c r="G22" s="223" t="inlineStr"/>
-      <c r="H22" s="223" t="inlineStr"/>
-      <c r="I22" s="224">
-        <f>SUM(I6:I21)</f>
-        <v/>
-      </c>
-      <c r="J22" s="223" t="inlineStr"/>
-      <c r="K22" s="223" t="inlineStr"/>
-      <c r="L22" s="223" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="207" t="inlineStr"/>
-      <c r="B23" s="207" t="inlineStr">
+      <c r="C23" s="234" t="inlineStr"/>
+      <c r="D23" s="234" t="inlineStr"/>
+      <c r="E23" s="234" t="inlineStr"/>
+      <c r="F23" s="234" t="inlineStr"/>
+      <c r="G23" s="234" t="inlineStr"/>
+      <c r="H23" s="234" t="inlineStr"/>
+      <c r="I23" s="235">
+        <f>SUM(I6:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="234" t="inlineStr"/>
+      <c r="K23" s="234" t="inlineStr"/>
+      <c r="L23" s="234" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="207" t="inlineStr"/>
+      <c r="B24" s="207" t="inlineStr">
         <is>
           <t>⚡ БЛОК 2: ИНЖЕНЕРНЫЕ МАТЕРИАЛЫ, ДВЕРИ И ОСНАЩЕНИЕ (СПЕЦПОСТАВЩИКИ)</t>
         </is>
       </c>
-      <c r="C23" s="207" t="inlineStr"/>
-      <c r="D23" s="207" t="inlineStr"/>
-      <c r="E23" s="207" t="inlineStr"/>
-      <c r="F23" s="207" t="inlineStr"/>
-      <c r="G23" s="207" t="inlineStr"/>
-      <c r="H23" s="207" t="inlineStr"/>
-      <c r="I23" s="207" t="inlineStr"/>
-      <c r="J23" s="207" t="inlineStr"/>
-      <c r="K23" s="207" t="inlineStr"/>
-      <c r="L23" s="207" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="62" t="n">
+      <c r="C24" s="207" t="inlineStr"/>
+      <c r="D24" s="207" t="inlineStr"/>
+      <c r="E24" s="207" t="inlineStr"/>
+      <c r="F24" s="207" t="inlineStr"/>
+      <c r="G24" s="207" t="inlineStr"/>
+      <c r="H24" s="207" t="inlineStr"/>
+      <c r="I24" s="207" t="inlineStr"/>
+      <c r="J24" s="207" t="inlineStr"/>
+      <c r="K24" s="207" t="inlineStr"/>
+      <c r="L24" s="207" t="inlineStr"/>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="64" t="n">
         <v>6</v>
       </c>
-      <c r="B24" s="62" t="inlineStr">
+      <c r="B25" s="64" t="inlineStr">
         <is>
           <t>Расходники</t>
         </is>
       </c>
-      <c r="C24" s="62" t="inlineStr">
+      <c r="C25" s="64" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="D24" s="44" t="inlineStr">
+      <c r="D25" s="49" t="inlineStr">
         <is>
           <t>Мешки мусорные плотные, перчатки рабочие (хозмаг/рынок)</t>
         </is>
       </c>
-      <c r="E24" s="62" t="inlineStr">
+      <c r="E25" s="64" t="inlineStr">
         <is>
           <t>ХОЗМАГ-МЕШКИ</t>
-        </is>
-      </c>
-      <c r="F24" s="62" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G24" s="216" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="173" t="n">
-        <v>300</v>
-      </c>
-      <c r="I24" s="217">
-        <f>G24*H24</f>
-        <v/>
-      </c>
-      <c r="J24" s="44" t="inlineStr">
-        <is>
-          <t>Хозмаг / Рынок</t>
-        </is>
-      </c>
-      <c r="K24" s="174">
-        <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=мешки+мусорные+строительные"; "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L24" s="44" t="inlineStr">
-        <is>
-          <t>Оперативная докупка расходников для демонтажа</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="64" t="n">
-        <v>11</v>
-      </c>
-      <c r="B25" s="64" t="inlineStr">
-        <is>
-          <t>Сантехника</t>
-        </is>
-      </c>
-      <c r="C25" s="64" t="inlineStr">
-        <is>
-          <t>Учёт воды</t>
-        </is>
-      </c>
-      <c r="D25" s="49" t="inlineStr">
-        <is>
-          <t>Счётчик горячей/холодной воды + кран на ввод (материалы)</t>
-        </is>
-      </c>
-      <c r="E25" s="64" t="inlineStr">
-        <is>
-          <t>СЧЕТЧИК-ВОДЫ</t>
         </is>
       </c>
       <c r="F25" s="64" t="inlineStr">
@@ -7078,7 +7262,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="172" t="n">
-        <v>2100</v>
+        <v>300</v>
       </c>
       <c r="I25" s="219">
         <f>G25*H25</f>
@@ -7086,22 +7270,22 @@
       </c>
       <c r="J25" s="49" t="inlineStr">
         <is>
-          <t>Вадим (сантехник УК)</t>
+          <t>Хозмаг / Рынок</t>
         </is>
       </c>
       <c r="K25" s="175">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=счетчик+воды+универсальный"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=мешки+мусорные+строительные", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L25" s="49" t="inlineStr">
         <is>
-          <t>Замена вводных узлов и прибора учёта</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+          <t>Оперативная докупка расходников для демонтажа</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
       <c r="A26" s="62" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B26" s="62" t="inlineStr">
         <is>
@@ -7115,12 +7299,12 @@
       </c>
       <c r="D26" s="44" t="inlineStr">
         <is>
-          <t>Покупка и установка счётчика и кранов (доплата за фитинги и муфты)</t>
+          <t>Счётчик горячей/холодной воды + кран на ввод (материалы)</t>
         </is>
       </c>
       <c r="E26" s="62" t="inlineStr">
         <is>
-          <t>ФИТИНГИ-САНТЕХ</t>
+          <t>СЧЕТЧИК-ВОДЫ</t>
         </is>
       </c>
       <c r="F26" s="62" t="inlineStr">
@@ -7132,7 +7316,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="173" t="n">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="I26" s="217">
         <f>G26*H26</f>
@@ -7144,49 +7328,49 @@
         </is>
       </c>
       <c r="K26" s="174">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=шаровый+кран+1/2"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=счетчик+воды+универсальный", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L26" s="44" t="inlineStr">
         <is>
-          <t>Латунные фитинги, муфты, уплотнители</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+          <t>Замена вводных узлов и прибора учёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
       <c r="A27" s="64" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="64" t="inlineStr">
         <is>
-          <t>Входная группа</t>
+          <t>Сантехника</t>
         </is>
       </c>
       <c r="C27" s="64" t="inlineStr">
         <is>
-          <t>Двери</t>
+          <t>Учёт воды</t>
         </is>
       </c>
       <c r="D27" s="49" t="inlineStr">
         <is>
-          <t>Покупка входной металлической двери с внутренней МДФ-панелью</t>
+          <t>Покупка и установка счётчика и кранов (доплата за фитинги и муфты)</t>
         </is>
       </c>
       <c r="E27" s="64" t="inlineStr">
         <is>
-          <t>ДВЕРЬ-ВХОД-МДФ</t>
+          <t>ФИТИНГИ-САНТЕХ</t>
         </is>
       </c>
       <c r="F27" s="64" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G27" s="218" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="172" t="n">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="I27" s="219">
         <f>G27*H27</f>
@@ -7194,22 +7378,22 @@
       </c>
       <c r="J27" s="49" t="inlineStr">
         <is>
-          <t>Владимир (двери)</t>
+          <t>Вадим (сантехник УК)</t>
         </is>
       </c>
       <c r="K27" s="175">
-        <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=входная+металлическая+дверь+мдф"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=шаровый+кран+1/2", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L27" s="49" t="inlineStr">
         <is>
-          <t>Металл 1.5 мм, МДФ-панель, надежные замки</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
+          <t>Латунные фитинги, муфты, уплотнители</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1">
       <c r="A28" s="62" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" s="62" t="inlineStr">
         <is>
@@ -7218,29 +7402,29 @@
       </c>
       <c r="C28" s="62" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Двери</t>
         </is>
       </c>
       <c r="D28" s="44" t="inlineStr">
         <is>
-          <t>Доставка входной металлической двери на объект</t>
+          <t>Покупка входной металлической двери с внутренней МДФ-панелью</t>
         </is>
       </c>
       <c r="E28" s="62" t="inlineStr">
         <is>
-          <t>ДОСТАВКА-ДВЕРЬ</t>
+          <t>ДВЕРЬ-ВХОД-МДФ</t>
         </is>
       </c>
       <c r="F28" s="62" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G28" s="216" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="173" t="n">
-        <v>1500</v>
+        <v>16000</v>
       </c>
       <c r="I28" s="217">
         <f>G28*H28</f>
@@ -7248,53 +7432,53 @@
       </c>
       <c r="J28" s="44" t="inlineStr">
         <is>
-          <t>Владимир / Доставка</t>
+          <t>Владимир (двери)</t>
         </is>
       </c>
       <c r="K28" s="174">
-        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=доставка+дверей+грузоперевозки"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=входная+металлическая+дверь+мдф", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L28" s="44" t="inlineStr">
         <is>
-          <t>Транспортировка двери на ул. Фрунзе 17</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+          <t>Металл 1.5 мм, МДФ-панель, надежные замки</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1">
       <c r="A29" s="64" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" s="64" t="inlineStr">
         <is>
-          <t>Электрика</t>
+          <t>Входная группа</t>
         </is>
       </c>
       <c r="C29" s="64" t="inlineStr">
         <is>
-          <t>Щит / Автоматика</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="D29" s="49" t="inlineStr">
         <is>
-          <t>Черновые материалы электрики (щит 18м, новый электросчётчик, автоматы, УЗО, гофра)</t>
+          <t>Доставка входной металлической двери на объект</t>
         </is>
       </c>
       <c r="E29" s="64" t="inlineStr">
         <is>
-          <t>ЩИТ-АВТ-КОМПЛЕКТ</t>
+          <t>ДОСТАВКА-ДВЕРЬ</t>
         </is>
       </c>
       <c r="F29" s="64" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="G29" s="218" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="172" t="n">
-        <v>16500</v>
+        <v>1500</v>
       </c>
       <c r="I29" s="219">
         <f>G29*H29</f>
@@ -7302,22 +7486,22 @@
       </c>
       <c r="J29" s="49" t="inlineStr">
         <is>
-          <t>Анатолий / Поставщик</t>
+          <t>Владимир / Доставка</t>
         </is>
       </c>
       <c r="K29" s="175">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=щит+встраиваемый+18+модулей"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=доставка+дверей+грузоперевозки", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L29" s="49" t="inlineStr">
         <is>
-          <t>Комплектная начинка щита и прибор учёта</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
+          <t>Транспортировка двери на ул. Фрунзе 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1">
       <c r="A30" s="62" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B30" s="62" t="inlineStr">
         <is>
@@ -7326,29 +7510,29 @@
       </c>
       <c r="C30" s="62" t="inlineStr">
         <is>
-          <t>Кабель</t>
+          <t>Щит / Автоматика</t>
         </is>
       </c>
       <c r="D30" s="44" t="inlineStr">
         <is>
-          <t>Кабель силовой ВВГнг-LS (ГОСТ 3х2.5 и 3х1.5 для всех трасс)</t>
+          <t>Черновые материалы электрики (щит 18м, новый электросчётчик, автоматы, УЗО, гофра)</t>
         </is>
       </c>
       <c r="E30" s="62" t="inlineStr">
         <is>
-          <t>ВВГнг-LS-ГОСТ-1</t>
+          <t>ЩИТ-АВТ-КОМПЛЕКТ</t>
         </is>
       </c>
       <c r="F30" s="62" t="inlineStr">
         <is>
-          <t>бухта</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G30" s="216" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="173" t="n">
-        <v>18000</v>
+        <v>16500</v>
       </c>
       <c r="I30" s="217">
         <f>G30*H30</f>
@@ -7356,22 +7540,22 @@
       </c>
       <c r="J30" s="44" t="inlineStr">
         <is>
-          <t>Электромонтаж / Поставщик</t>
+          <t>Анатолий / Поставщик</t>
         </is>
       </c>
       <c r="K30" s="174">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=кабель+ВВГнг-LS+3х2.5"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=щит+встраиваемый+18+модулей", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L30" s="44" t="inlineStr">
         <is>
-          <t>Силовой кабель ГОСТ под розетки и свет</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
+          <t>Комплектная начинка щита и прибор учёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
       <c r="A31" s="64" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B31" s="64" t="inlineStr">
         <is>
@@ -7380,29 +7564,29 @@
       </c>
       <c r="C31" s="64" t="inlineStr">
         <is>
-          <t>Крепёж</t>
+          <t>Кабель</t>
         </is>
       </c>
       <c r="D31" s="49" t="inlineStr">
         <is>
-          <t>Стяжки нейлоновые и крепёж для монтажа кабеля</t>
+          <t>Кабель силовой ВВГнг-LS (ГОСТ 3х2.5 и 3х1.5 для всех трасс)</t>
         </is>
       </c>
       <c r="E31" s="64" t="inlineStr">
         <is>
-          <t>КРЕПЕЖ-КАБЕЛЬ</t>
+          <t>ВВГнг-LS-ГОСТ-1</t>
         </is>
       </c>
       <c r="F31" s="64" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>бухта</t>
         </is>
       </c>
       <c r="G31" s="218" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="172" t="n">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="I31" s="219">
         <f>G31*H31</f>
@@ -7410,22 +7594,22 @@
       </c>
       <c r="J31" s="49" t="inlineStr">
         <is>
-          <t>Хозмаг / Электромонтаж</t>
+          <t>Электромонтаж / Поставщик</t>
         </is>
       </c>
       <c r="K31" s="175">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=дюбель+хомут+для+кабеля"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=кабель+ВВГнг-LS+3х2.5", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L31" s="49" t="inlineStr">
         <is>
-          <t>Дюбель-хомуты и стяжки для трасс</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+          <t>Силовой кабель ГОСТ под розетки и свет</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1">
       <c r="A32" s="62" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B32" s="62" t="inlineStr">
         <is>
@@ -7434,29 +7618,29 @@
       </c>
       <c r="C32" s="62" t="inlineStr">
         <is>
-          <t>Кабель</t>
+          <t>Крепёж</t>
         </is>
       </c>
       <c r="D32" s="44" t="inlineStr">
         <is>
-          <t>Докупка силового кабеля ВВГнг-LS (дополнительный метраж трасс)</t>
+          <t>Стяжки нейлоновые и крепёж для монтажа кабеля</t>
         </is>
       </c>
       <c r="E32" s="62" t="inlineStr">
         <is>
-          <t>ВВГнг-LS-ГОСТ-2</t>
+          <t>КРЕПЕЖ-КАБЕЛЬ</t>
         </is>
       </c>
       <c r="F32" s="62" t="inlineStr">
         <is>
-          <t>бухта</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G32" s="216" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="173" t="n">
-        <v>13000</v>
+        <v>1000</v>
       </c>
       <c r="I32" s="217">
         <f>G32*H32</f>
@@ -7464,53 +7648,53 @@
       </c>
       <c r="J32" s="44" t="inlineStr">
         <is>
-          <t>Электромонтаж / Поставщик</t>
+          <t>Хозмаг / Электромонтаж</t>
         </is>
       </c>
       <c r="K32" s="174">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=кабель+ВВГнг-LS+3х1.5"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=дюбель+хомут+для+кабеля", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L32" s="44" t="inlineStr">
         <is>
-          <t>Дополнительный кабель на трассы кухни и коридора</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
+          <t>Дюбель-хомуты и стяжки для трасс</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1">
       <c r="A33" s="64" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B33" s="64" t="inlineStr">
         <is>
-          <t>Оснащение</t>
+          <t>Электрика</t>
         </is>
       </c>
       <c r="C33" s="64" t="inlineStr">
         <is>
-          <t>Инвентарь</t>
+          <t>Кабель</t>
         </is>
       </c>
       <c r="D33" s="49" t="inlineStr">
         <is>
-          <t>Портативная акустика Xiaomi Bluetooth Speaker Essential Green</t>
+          <t>Докупка силового кабеля ВВГнг-LS (дополнительный метраж трасс)</t>
         </is>
       </c>
       <c r="E33" s="64" t="inlineStr">
         <is>
-          <t>XIAOMI-SPK-ESS</t>
+          <t>ВВГнг-LS-ГОСТ-2</t>
         </is>
       </c>
       <c r="F33" s="64" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>бухта</t>
         </is>
       </c>
       <c r="G33" s="218" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="172" t="n">
-        <v>1250</v>
+        <v>13000</v>
       </c>
       <c r="I33" s="219">
         <f>G33*H33</f>
@@ -7518,22 +7702,22 @@
       </c>
       <c r="J33" s="49" t="inlineStr">
         <is>
-          <t>ООО ДНС Ритейл (DNS)</t>
+          <t>Электромонтаж / Поставщик</t>
         </is>
       </c>
       <c r="K33" s="175">
-        <f>HYPERLINK("https://www.dns-shop.ru/search/?q=Xiaomi+Bluetooth+Speaker"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=кабель+ВВГнг-LS+3х1.5", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L33" s="49" t="inlineStr">
         <is>
-          <t>Акустическое оснащение объекта для бригад</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
+          <t>Дополнительный кабель на трассы кухни и коридора</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1">
       <c r="A34" s="62" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B34" s="62" t="inlineStr">
         <is>
@@ -7542,29 +7726,29 @@
       </c>
       <c r="C34" s="62" t="inlineStr">
         <is>
-          <t>Хознужды</t>
+          <t>Инвентарь</t>
         </is>
       </c>
       <c r="D34" s="44" t="inlineStr">
         <is>
-          <t>Хозрасходы на объект: салфетки влажные и питьевая вода для мастеров</t>
+          <t>Портативная акустика Xiaomi Bluetooth Speaker Essential Green</t>
         </is>
       </c>
       <c r="E34" s="62" t="inlineStr">
         <is>
-          <t>ХОЗ-ВОДА-САЛФЕТКИ</t>
+          <t>XIAOMI-SPK-ESS</t>
         </is>
       </c>
       <c r="F34" s="62" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G34" s="216" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="173" t="n">
-        <v>520</v>
+        <v>1250</v>
       </c>
       <c r="I34" s="217">
         <f>G34*H34</f>
@@ -7572,41 +7756,41 @@
       </c>
       <c r="J34" s="44" t="inlineStr">
         <is>
-          <t>Хозмаг / Продукты</t>
+          <t>ООО ДНС Ритейл (DNS)</t>
         </is>
       </c>
       <c r="K34" s="174">
-        <f>HYPERLINK("https://www.avito.ru/tula/produkty_pitaniya?q=питьевая+вода+19л"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.dns-shop.ru/search/?q=Xiaomi+Bluetooth+Speaker", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L34" s="44" t="inlineStr">
         <is>
-          <t>Бытовое снабжение объекта</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+          <t>Акустическое оснащение объекта для бригад</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19" customHeight="1">
       <c r="A35" s="64" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B35" s="64" t="inlineStr">
         <is>
-          <t>Санузел</t>
+          <t>Оснащение</t>
         </is>
       </c>
       <c r="C35" s="64" t="inlineStr">
         <is>
-          <t>Канализация</t>
+          <t>Хознужды</t>
         </is>
       </c>
       <c r="D35" s="49" t="inlineStr">
         <is>
-          <t>Канализация с/у (муфта-восстановитель раструба 110/110, трубы ПП 50, тройник 110/50, заглушка, отводы)</t>
+          <t>Хозрасходы на объект: салфетки влажные и питьевая вода для мастеров</t>
         </is>
       </c>
       <c r="E35" s="64" t="inlineStr">
         <is>
-          <t>КАНАЛ-СУ-110-50</t>
+          <t>ХОЗ-ВОДА-САЛФЕТКИ</t>
         </is>
       </c>
       <c r="F35" s="64" t="inlineStr">
@@ -7618,7 +7802,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="172" t="n">
-        <v>2988</v>
+        <v>520</v>
       </c>
       <c r="I35" s="219">
         <f>G35*H35</f>
@@ -7626,41 +7810,41 @@
       </c>
       <c r="J35" s="49" t="inlineStr">
         <is>
-          <t>ИП Кучеров М.И. (Полимерстрой)</t>
+          <t>Хозмаг / Продукты</t>
         </is>
       </c>
       <c r="K35" s="175">
-        <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=восстановитель+раструба+110"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/produkty_pitaniya?q=питьевая+вода+19л", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L35" s="49" t="inlineStr">
         <is>
-          <t>Чек от 15.09.2026: Муфта-восстановитель 110/110, разводка труб под ванну, раковину, унитаз</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
+          <t>Бытовое снабжение объекта</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1">
       <c r="A36" s="62" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="62" t="inlineStr">
         <is>
-          <t>Санузел / Кухня</t>
+          <t>Санузел</t>
         </is>
       </c>
       <c r="C36" s="62" t="inlineStr">
         <is>
-          <t>Водоснабжение</t>
+          <t>Канализация</t>
         </is>
       </c>
       <c r="D36" s="44" t="inlineStr">
         <is>
-          <t>Трубы армированные Faser 20х2.8 12м, настенная планка смесителя, кран DN15, муфты, клипсы</t>
+          <t>Канализация с/у (муфта-восстановитель раструба 110/110, трубы ПП 50, тройник 110/50, заглушка, отводы)</t>
         </is>
       </c>
       <c r="E36" s="62" t="inlineStr">
         <is>
-          <t>PPR-FASER-WATSON</t>
+          <t>КАНАЛ-СУ-110-50</t>
         </is>
       </c>
       <c r="F36" s="62" t="inlineStr">
@@ -7672,7 +7856,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="173" t="n">
-        <v>3139.54</v>
+        <v>2988</v>
       </c>
       <c r="I36" s="217">
         <f>G36*H36</f>
@@ -7680,146 +7864,146 @@
       </c>
       <c r="J36" s="44" t="inlineStr">
         <is>
+          <t>ИП Кучеров М.И. (Полимерстрой)</t>
+        </is>
+      </c>
+      <c r="K36" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=восстановитель+раструба+110", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L36" s="44" t="inlineStr">
+        <is>
+          <t>Чек от 15.09.2026: Муфта-восстановитель 110/110, разводка труб под ванну, раковину, унитаз</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="64" t="n">
+        <v>44</v>
+      </c>
+      <c r="B37" s="64" t="inlineStr">
+        <is>
+          <t>Санузел / Кухня</t>
+        </is>
+      </c>
+      <c r="C37" s="64" t="inlineStr">
+        <is>
+          <t>Водоснабжение</t>
+        </is>
+      </c>
+      <c r="D37" s="49" t="inlineStr">
+        <is>
+          <t>Трубы армированные Faser 20х2.8 12м, настенная планка смесителя, кран DN15, муфты, клипсы</t>
+        </is>
+      </c>
+      <c r="E37" s="64" t="inlineStr">
+        <is>
+          <t>PPR-FASER-WATSON</t>
+        </is>
+      </c>
+      <c r="F37" s="64" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G37" s="218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="172" t="n">
+        <v>3139.54</v>
+      </c>
+      <c r="I37" s="219">
+        <f>G37*H37</f>
+        <v/>
+      </c>
+      <c r="J37" s="49" t="inlineStr">
+        <is>
           <t>ТС «Ваттсон» (Центргазсервис)</t>
         </is>
       </c>
-      <c r="K36" s="174">
-        <f>HYPERLINK("https://wattson.ru/search/?q=Faser+20"; "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L36" s="44" t="inlineStr">
+      <c r="K37" s="175">
+        <f>HYPERLINK("https://wattson.ru/search/?q=Faser+20", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L37" s="49" t="inlineStr">
         <is>
           <t>Чек №23 от 19.09.2026: Разводка труб ХВС/ГВС, шаровой кран ввода, планка под смеситель ванны</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="223" t="inlineStr"/>
-      <c r="B37" s="223" t="inlineStr">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="234" t="inlineStr"/>
+      <c r="B38" s="234" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ СПЕЦПОСТАВЩИКОВ:</t>
         </is>
       </c>
-      <c r="C37" s="223" t="inlineStr"/>
-      <c r="D37" s="223" t="inlineStr"/>
-      <c r="E37" s="223" t="inlineStr"/>
-      <c r="F37" s="223" t="inlineStr"/>
-      <c r="G37" s="223" t="inlineStr"/>
-      <c r="H37" s="223" t="inlineStr"/>
-      <c r="I37" s="224">
-        <f>SUM(I24:I36)</f>
-        <v/>
-      </c>
-      <c r="J37" s="223" t="inlineStr"/>
-      <c r="K37" s="223" t="inlineStr"/>
-      <c r="L37" s="223" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="208" t="inlineStr"/>
-      <c r="B38" s="208" t="inlineStr">
+      <c r="C38" s="234" t="inlineStr"/>
+      <c r="D38" s="234" t="inlineStr"/>
+      <c r="E38" s="234" t="inlineStr"/>
+      <c r="F38" s="234" t="inlineStr"/>
+      <c r="G38" s="234" t="inlineStr"/>
+      <c r="H38" s="234" t="inlineStr"/>
+      <c r="I38" s="235">
+        <f>SUM(I25:I37)</f>
+        <v/>
+      </c>
+      <c r="J38" s="234" t="inlineStr"/>
+      <c r="K38" s="234" t="inlineStr"/>
+      <c r="L38" s="234" t="inlineStr"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="208" t="inlineStr"/>
+      <c r="B39" s="208" t="inlineStr">
         <is>
           <t>👷‍♂️ БЛОК 3: РАБОТЫ МАСТЕРОВ, ОТДЕЛКА, ДЕМОНТАЖ И ЛОГИСТИКА</t>
         </is>
       </c>
-      <c r="C38" s="208" t="inlineStr"/>
-      <c r="D38" s="208" t="inlineStr"/>
-      <c r="E38" s="208" t="inlineStr"/>
-      <c r="F38" s="208" t="inlineStr"/>
-      <c r="G38" s="208" t="inlineStr"/>
-      <c r="H38" s="208" t="inlineStr"/>
-      <c r="I38" s="208" t="inlineStr"/>
-      <c r="J38" s="208" t="inlineStr"/>
-      <c r="K38" s="208" t="inlineStr"/>
-      <c r="L38" s="208" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="64" t="n">
+      <c r="C39" s="208" t="inlineStr"/>
+      <c r="D39" s="208" t="inlineStr"/>
+      <c r="E39" s="208" t="inlineStr"/>
+      <c r="F39" s="208" t="inlineStr"/>
+      <c r="G39" s="208" t="inlineStr"/>
+      <c r="H39" s="208" t="inlineStr"/>
+      <c r="I39" s="208" t="inlineStr"/>
+      <c r="J39" s="208" t="inlineStr"/>
+      <c r="K39" s="208" t="inlineStr"/>
+      <c r="L39" s="208" t="inlineStr"/>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="B39" s="64" t="inlineStr">
+      <c r="B40" s="62" t="inlineStr">
         <is>
           <t>Безопасность</t>
         </is>
       </c>
-      <c r="C39" s="64" t="inlineStr">
+      <c r="C40" s="62" t="inlineStr">
         <is>
           <t>Вскрытие</t>
         </is>
       </c>
-      <c r="D39" s="49" t="inlineStr">
+      <c r="D40" s="44" t="inlineStr">
         <is>
           <t>Вскрытие старого замка и обеспечение первого доступа</t>
         </is>
       </c>
-      <c r="E39" s="64" t="inlineStr">
+      <c r="E40" s="62" t="inlineStr">
         <is>
           <t>ВСКРЫТИЕ-ЗАМКА</t>
         </is>
       </c>
-      <c r="F39" s="64" t="inlineStr">
+      <c r="F40" s="62" t="inlineStr">
         <is>
           <t>выезд</t>
-        </is>
-      </c>
-      <c r="G39" s="218" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="172" t="n">
-        <v>8000</v>
-      </c>
-      <c r="I39" s="219">
-        <f>G39*H39</f>
-        <v/>
-      </c>
-      <c r="J39" s="49" t="inlineStr">
-        <is>
-          <t>Служба вскрытия</t>
-        </is>
-      </c>
-      <c r="K39" s="175">
-        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=вскрытие+замков"; "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L39" s="49" t="inlineStr">
-        <is>
-          <t>Аварийное открытие двери после торгов</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="62" t="n">
-        <v>4</v>
-      </c>
-      <c r="B40" s="62" t="inlineStr">
-        <is>
-          <t>Демонтаж</t>
-        </is>
-      </c>
-      <c r="C40" s="62" t="inlineStr">
-        <is>
-          <t>Вывоз мусора</t>
-        </is>
-      </c>
-      <c r="D40" s="44" t="inlineStr">
-        <is>
-          <t>Заказ мусорного контейнера 8 м³ (лодочка)</t>
-        </is>
-      </c>
-      <c r="E40" s="62" t="inlineStr">
-        <is>
-          <t>КОНТЕЙНЕР-МУСОР-8М3</t>
-        </is>
-      </c>
-      <c r="F40" s="62" t="inlineStr">
-        <is>
-          <t>рейс</t>
         </is>
       </c>
       <c r="G40" s="216" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="173" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="I40" s="217">
         <f>G40*H40</f>
@@ -7827,22 +8011,22 @@
       </c>
       <c r="J40" s="44" t="inlineStr">
         <is>
-          <t>Елена (вывоз мусора)</t>
+          <t>Служба вскрытия</t>
         </is>
       </c>
       <c r="K40" s="174">
-        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=вывоз+мусора+контейнер+8+м3"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=вскрытие+замков", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L40" s="44" t="inlineStr">
         <is>
-          <t>Вывоз мебели, санузла, чугуна, досок</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
+          <t>Аварийное открытие двери после торгов</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="19" customHeight="1">
       <c r="A41" s="64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B41" s="64" t="inlineStr">
         <is>
@@ -7851,29 +8035,29 @@
       </c>
       <c r="C41" s="64" t="inlineStr">
         <is>
-          <t>Аренда</t>
+          <t>Вывоз мусора</t>
         </is>
       </c>
       <c r="D41" s="49" t="inlineStr">
         <is>
-          <t>Аренда инструмента и помощь соседа по дому</t>
+          <t>Заказ мусорного контейнера 8 м³ (лодочка)</t>
         </is>
       </c>
       <c r="E41" s="64" t="inlineStr">
         <is>
-          <t>АРЕНДА-ИНСТРУМЕНТ</t>
+          <t>КОНТЕЙНЕР-МУСОР-8М3</t>
         </is>
       </c>
       <c r="F41" s="64" t="inlineStr">
         <is>
-          <t>услуга</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="G41" s="218" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="172" t="n">
-        <v>1000</v>
+        <v>8500</v>
       </c>
       <c r="I41" s="219">
         <f>G41*H41</f>
@@ -7881,22 +8065,22 @@
       </c>
       <c r="J41" s="49" t="inlineStr">
         <is>
-          <t>Сосед по дому</t>
+          <t>Елена (вывоз мусора)</t>
         </is>
       </c>
       <c r="K41" s="175">
-        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=аренда+перфоратора"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=вывоз+мусора+контейнер+8+м3", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L41" s="49" t="inlineStr">
         <is>
-          <t>Перфоратор и монтировки для первичного демонтажа</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
+          <t>Вывоз мебели, санузла, чугуна, досок</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="19" customHeight="1">
       <c r="A42" s="62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B42" s="62" t="inlineStr">
         <is>
@@ -7905,29 +8089,29 @@
       </c>
       <c r="C42" s="62" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Аренда</t>
         </is>
       </c>
       <c r="D42" s="44" t="inlineStr">
         <is>
-          <t>Оплата работы бригады разнорабочих (4 чел., 28 чел.-час, спуск с 5 этажа)</t>
+          <t>Аренда инструмента и помощь соседа по дому</t>
         </is>
       </c>
       <c r="E42" s="62" t="inlineStr">
         <is>
-          <t>ДЕМОНТАЖ-БРИГАДА-1</t>
+          <t>АРЕНДА-ИНСТРУМЕНТ</t>
         </is>
       </c>
       <c r="F42" s="62" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>услуга</t>
         </is>
       </c>
       <c r="G42" s="216" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="173" t="n">
-        <v>16000</v>
+        <v>1000</v>
       </c>
       <c r="I42" s="217">
         <f>G42*H42</f>
@@ -7935,53 +8119,53 @@
       </c>
       <c r="J42" s="44" t="inlineStr">
         <is>
-          <t>Бригада разнорабочих</t>
+          <t>Сосед по дому</t>
         </is>
       </c>
       <c r="K42" s="174">
-        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=демонтаж+квартиры+разнорабочие"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=аренда+перфоратора", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L42" s="44" t="inlineStr">
         <is>
-          <t>Тотальная зачистка и вынос мусора без лифта</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
+          <t>Перфоратор и монтировки для первичного демонтажа</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
       <c r="A43" s="64" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B43" s="64" t="inlineStr">
         <is>
-          <t>Входная группа</t>
+          <t>Демонтаж</t>
         </is>
       </c>
       <c r="C43" s="64" t="inlineStr">
         <is>
-          <t>Монтаж</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="D43" s="49" t="inlineStr">
         <is>
-          <t>Монтаж входной двери (демонтаж 2 старых дверей + монтаж новой)</t>
+          <t>Оплата работы бригады разнорабочих (4 чел., 28 чел.-час, спуск с 5 этажа)</t>
         </is>
       </c>
       <c r="E43" s="64" t="inlineStr">
         <is>
-          <t>МОНТАЖ-ДВЕРИ-ВХОД</t>
+          <t>ДЕМОНТАЖ-БРИГАДА-1</t>
         </is>
       </c>
       <c r="F43" s="64" t="inlineStr">
         <is>
-          <t>услуга</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="G43" s="218" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="172" t="n">
-        <v>9000</v>
+        <v>16000</v>
       </c>
       <c r="I43" s="219">
         <f>G43*H43</f>
@@ -7989,53 +8173,53 @@
       </c>
       <c r="J43" s="49" t="inlineStr">
         <is>
-          <t>Андрей (монтаж дверей)</t>
+          <t>Бригада разнорабочих</t>
         </is>
       </c>
       <c r="K43" s="175">
-        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=установка+входных+дверей"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=демонтаж+квартиры+разнорабочие", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L43" s="49" t="inlineStr">
         <is>
-          <t>Сняли старые двери, расширили проем, выставили по уровню</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+          <t>Тотальная зачистка и вынос мусора без лифта</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="19" customHeight="1">
       <c r="A44" s="62" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B44" s="62" t="inlineStr">
         <is>
-          <t>Электрика</t>
+          <t>Входная группа</t>
         </is>
       </c>
       <c r="C44" s="62" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Монтаж</t>
         </is>
       </c>
       <c r="D44" s="44" t="inlineStr">
         <is>
-          <t>Электромонтажные работы под ключ (разводка 32 точек, штробы, щит, счётчик)</t>
+          <t>Монтаж входной двери (демонтаж 2 старых дверей + монтаж новой)</t>
         </is>
       </c>
       <c r="E44" s="62" t="inlineStr">
         <is>
-          <t>РАБОТА-ЭЛЕКТРИКА-32</t>
+          <t>МОНТАЖ-ДВЕРИ-ВХОД</t>
         </is>
       </c>
       <c r="F44" s="62" t="inlineStr">
         <is>
-          <t>договор</t>
+          <t>услуга</t>
         </is>
       </c>
       <c r="G44" s="216" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="173" t="n">
-        <v>50000</v>
+        <v>9000</v>
       </c>
       <c r="I44" s="217">
         <f>G44*H44</f>
@@ -8043,26 +8227,26 @@
       </c>
       <c r="J44" s="44" t="inlineStr">
         <is>
-          <t>Анатолий Кушнарев (бригада)</t>
+          <t>Андрей (монтаж дверей)</t>
         </is>
       </c>
       <c r="K44" s="174">
-        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=электромонтаж+квартиры+под+ключ"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=установка+входных+дверей", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L44" s="44" t="inlineStr">
         <is>
-          <t>Монтаж всей проводки, сборка щита и счётчика</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
+          <t>Сняли старые двери, расширили проем, выставили по уровню</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="19" customHeight="1">
       <c r="A45" s="64" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B45" s="64" t="inlineStr">
         <is>
-          <t>Демонтаж</t>
+          <t>Электрика</t>
         </is>
       </c>
       <c r="C45" s="64" t="inlineStr">
@@ -8072,24 +8256,24 @@
       </c>
       <c r="D45" s="49" t="inlineStr">
         <is>
-          <t>Зачистка стен/потолка (обои, плитка в зале и спальне), вынос мусора, 1-й слой грунта</t>
+          <t>Электромонтажные работы под ключ (разводка 32 точек, штробы, щит, счётчик)</t>
         </is>
       </c>
       <c r="E45" s="64" t="inlineStr">
         <is>
-          <t>ДЕМОНТАЖ-ЗАЧИСТКА-2</t>
+          <t>РАБОТА-ЭЛЕКТРИКА-32</t>
         </is>
       </c>
       <c r="F45" s="64" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>договор</t>
         </is>
       </c>
       <c r="G45" s="218" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="172" t="n">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="I45" s="219">
         <f>G45*H45</f>
@@ -8097,53 +8281,53 @@
       </c>
       <c r="J45" s="49" t="inlineStr">
         <is>
-          <t>Бригада разнорабочих</t>
+          <t>Анатолий Кушнарев (бригада)</t>
         </is>
       </c>
       <c r="K45" s="175">
-        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=зачистка+стен+демонтаж+обоев"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=электромонтаж+квартиры+под+ключ", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L45" s="49" t="inlineStr">
         <is>
-          <t>Снятие старых слоев, обеспыливание поверхностей</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
+          <t>Монтаж всей проводки, сборка щита и счётчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="19" customHeight="1">
       <c r="A46" s="62" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B46" s="62" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Демонтаж</t>
         </is>
       </c>
       <c r="C46" s="62" t="inlineStr">
         <is>
-          <t>Доставка</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="D46" s="44" t="inlineStr">
         <is>
-          <t>Грузовое такси / Доставка закупки материалов и сантехники (Лемана — Фрунзе 17)</t>
+          <t>Зачистка стен/потолка (обои, плитка в зале и спальне), вынос мусора, 1-й слой грунта</t>
         </is>
       </c>
       <c r="E46" s="62" t="inlineStr">
         <is>
-          <t>ГРУЗОТАКСИ-ЛЕРОЙ</t>
+          <t>ДЕМОНТАЖ-ЗАЧИСТКА-2</t>
         </is>
       </c>
       <c r="F46" s="62" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="G46" s="216" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="173" t="n">
-        <v>2100</v>
+        <v>15000</v>
       </c>
       <c r="I46" s="217">
         <f>G46*H46</f>
@@ -8151,53 +8335,53 @@
       </c>
       <c r="J46" s="44" t="inlineStr">
         <is>
-          <t>Грузовое такси / Перевозка</t>
+          <t>Бригада разнорабочих</t>
         </is>
       </c>
       <c r="K46" s="174">
-        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=грузоперевозки+грузовое+такси"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=зачистка+стен+демонтаж+обоев", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L46" s="44" t="inlineStr">
         <is>
-          <t>Перевозка партии смесей, керамогранита и ванны</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+          <t>Снятие старых слоев, обеспыливание поверхностей</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="19" customHeight="1">
       <c r="A47" s="64" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="64" t="inlineStr">
         <is>
-          <t>Демонтаж</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C47" s="64" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Доставка</t>
         </is>
       </c>
       <c r="D47" s="49" t="inlineStr">
         <is>
-          <t>Погрузка в Лемана ПРО, разгрузка и подъём на 5 этаж + демонтаж плитки пола с/у</t>
+          <t>Грузовое такси / Доставка закупки материалов и сантехники (Лемана — Фрунзе 17)</t>
         </is>
       </c>
       <c r="E47" s="64" t="inlineStr">
         <is>
-          <t>ПОДЪЕМ-ДЕМОНТАЖ-СУ</t>
+          <t>ГРУЗОТАКСИ-ЛЕРОЙ</t>
         </is>
       </c>
       <c r="F47" s="64" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="G47" s="218" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="172" t="n">
-        <v>15000</v>
+        <v>2100</v>
       </c>
       <c r="I47" s="219">
         <f>G47*H47</f>
@@ -8205,53 +8389,53 @@
       </c>
       <c r="J47" s="49" t="inlineStr">
         <is>
-          <t>Бригада грузчиков / Разнорабочие</t>
+          <t>Грузовое такси / Перевозка</t>
         </is>
       </c>
       <c r="K47" s="175">
-        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=подъем+стройматериалов+на+этаж+грузчики"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=грузоперевозки+грузовое+такси", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L47" s="49" t="inlineStr">
         <is>
-          <t>Разгрузка 1.5 тонн смесей на 5 этаж без лифта</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
+          <t>Перевозка партии смесей, керамогранита и ванны</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="19" customHeight="1">
       <c r="A48" s="62" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="62" t="inlineStr">
         <is>
-          <t>Черновые стены</t>
+          <t>Демонтаж</t>
         </is>
       </c>
       <c r="C48" s="62" t="inlineStr">
         <is>
-          <t>Отделочные работы</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="D48" s="44" t="inlineStr">
         <is>
-          <t>Штукатурка (69 м² по 500 ₽) и шпаклёвка стен White Box (106 м² по 500 ₽)</t>
+          <t>Погрузка в Лемана ПРО, разгрузка и подъём на 5 этаж + демонтаж плитки пола с/у</t>
         </is>
       </c>
       <c r="E48" s="62" t="inlineStr">
         <is>
-          <t>ОТДЕЛКА-СТЕН-ЕЛЕНА</t>
+          <t>ПОДЪЕМ-ДЕМОНТАЖ-СУ</t>
         </is>
       </c>
       <c r="F48" s="62" t="inlineStr">
         <is>
-          <t>комплекс</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="G48" s="216" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="173" t="n">
-        <v>87500</v>
+        <v>15000</v>
       </c>
       <c r="I48" s="217">
         <f>G48*H48</f>
@@ -8259,92 +8443,161 @@
       </c>
       <c r="J48" s="44" t="inlineStr">
         <is>
+          <t>Бригада грузчиков / Разнорабочие</t>
+        </is>
+      </c>
+      <c r="K48" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=подъем+стройматериалов+на+этаж+грузчики", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L48" s="44" t="inlineStr">
+        <is>
+          <t>Разгрузка 1.5 тонн смесей на 5 этаж без лифта</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" s="64" t="n">
+        <v>42</v>
+      </c>
+      <c r="B49" s="64" t="inlineStr">
+        <is>
+          <t>Черновые стены</t>
+        </is>
+      </c>
+      <c r="C49" s="64" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="D49" s="49" t="inlineStr">
+        <is>
+          <t>Штукатурка (69 м² по 500 ₽) и шпаклёвка стен White Box (106 м² по 500 ₽)</t>
+        </is>
+      </c>
+      <c r="E49" s="64" t="inlineStr">
+        <is>
+          <t>ОТДЕЛКА-СТЕН-ЕЛЕНА</t>
+        </is>
+      </c>
+      <c r="F49" s="64" t="inlineStr">
+        <is>
+          <t>комплекс</t>
+        </is>
+      </c>
+      <c r="G49" s="218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="172" t="n">
+        <v>87500</v>
+      </c>
+      <c r="I49" s="219">
+        <f>G49*H49</f>
+        <v/>
+      </c>
+      <c r="J49" s="49" t="inlineStr">
+        <is>
           <t>Елена (мастер-отделочник)</t>
         </is>
       </c>
-      <c r="K48" s="174">
-        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=штукатурка+шпаклевка+стен"; "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L48" s="44" t="inlineStr">
+      <c r="K49" s="175">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=штукатурка+шпаклевка+стен", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L49" s="49" t="inlineStr">
         <is>
           <t>Штукатурка 69 м² + шпаклёвка стен 106 м² по 500₽. White Box под ключ</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="223" t="inlineStr"/>
-      <c r="B49" s="223" t="inlineStr">
-        <is>
-          <t>ИТОГО РАБОТЫ И ЛОГИСТИКА:</t>
-        </is>
-      </c>
-      <c r="C49" s="223" t="inlineStr"/>
-      <c r="D49" s="223" t="inlineStr"/>
-      <c r="E49" s="223" t="inlineStr"/>
-      <c r="F49" s="223" t="inlineStr"/>
-      <c r="G49" s="223" t="inlineStr"/>
-      <c r="H49" s="223" t="inlineStr"/>
-      <c r="I49" s="224">
-        <f>SUM(I39:I48)</f>
-        <v/>
-      </c>
-      <c r="J49" s="223" t="inlineStr"/>
-      <c r="K49" s="223" t="inlineStr"/>
-      <c r="L49" s="223" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="225" t="inlineStr"/>
-      <c r="B50" s="225" t="inlineStr">
-        <is>
-          <t>🏛 БЛОК 4: ЮРИДИЧЕСКИЕ РАСХОДЫ, ПОШЛИНЫ, ГАЗ, ЭНЕРГОСБЫТ И IT</t>
-        </is>
-      </c>
-      <c r="C50" s="225" t="inlineStr"/>
-      <c r="D50" s="225" t="inlineStr"/>
-      <c r="E50" s="225" t="inlineStr"/>
-      <c r="F50" s="225" t="inlineStr"/>
-      <c r="G50" s="225" t="inlineStr"/>
-      <c r="H50" s="225" t="inlineStr"/>
-      <c r="I50" s="225" t="inlineStr"/>
-      <c r="J50" s="225" t="inlineStr"/>
-      <c r="K50" s="225" t="inlineStr"/>
-      <c r="L50" s="225" t="inlineStr"/>
-    </row>
-    <row r="51">
+    <row r="50" ht="19" customHeight="1">
+      <c r="A50" s="62" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="62" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C50" s="62" t="inlineStr">
+        <is>
+          <t>Сантехника / Работы</t>
+        </is>
+      </c>
+      <c r="D50" s="44" t="inlineStr">
+        <is>
+          <t>Срезка полотенцесушителя и нарезка трубной резьбы на отводах стояка</t>
+        </is>
+      </c>
+      <c r="E50" s="62" t="inlineStr">
+        <is>
+          <t>РАБОТА-САНТЕХ-СУШ</t>
+        </is>
+      </c>
+      <c r="F50" s="62" t="inlineStr">
+        <is>
+          <t>услуга</t>
+        </is>
+      </c>
+      <c r="G50" s="216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="173" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I50" s="217">
+        <f>G50*H50</f>
+        <v/>
+      </c>
+      <c r="J50" s="44" t="inlineStr">
+        <is>
+          <t>Вадим (сантехник УК) / Сантехник</t>
+        </is>
+      </c>
+      <c r="K50" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=сантехник+срезка+полотенцесушителя", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L50" s="44" t="inlineStr">
+        <is>
+          <t>Демонтаж старого змеевика, нарезка 2 резьб клуппом под установку запорных кранов</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
       <c r="A51" s="64" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="B51" s="64" t="inlineStr">
         <is>
-          <t>Юр. оформление</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C51" s="64" t="inlineStr">
         <is>
-          <t>Торги</t>
+          <t>Доставка</t>
         </is>
       </c>
       <c r="D51" s="49" t="inlineStr">
         <is>
-          <t>Выпуск квалифицированной ЭЦП (электронная цифровая подпись)</t>
+          <t>Такси (оперативная доставка материалов и инструмента из Лемана ПРО на объект)</t>
         </is>
       </c>
       <c r="E51" s="64" t="inlineStr">
         <is>
-          <t>ЭЦП-КОНТУР</t>
+          <t>ТАКСИ-ЛЕРОЙ-ОБЪЕКТ</t>
         </is>
       </c>
       <c r="F51" s="64" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="G51" s="218" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="172" t="n">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="I51" s="219">
         <f>G51*H51</f>
@@ -8352,161 +8605,92 @@
       </c>
       <c r="J51" s="49" t="inlineStr">
         <is>
-          <t>УЦ / Контур</t>
+          <t>Такси (Яндекс Go)</t>
         </is>
       </c>
       <c r="K51" s="175">
-        <f>HYPERLINK("https://ca.kontur.ru/"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=такси+доставка+курьер", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L51" s="49" t="inlineStr">
         <is>
-          <t>ЭЦП для участия в торгах и регистрации права</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="62" t="n">
-        <v>2</v>
-      </c>
-      <c r="B52" s="62" t="inlineStr">
+          <t>Оперативный подвоз купленного инструмента и материалов из Лемана ПРО на ул. Фрунзе 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="234" t="inlineStr"/>
+      <c r="B52" s="234" t="inlineStr">
+        <is>
+          <t>ИТОГО РАБОТЫ И ЛОГИСТИКА:</t>
+        </is>
+      </c>
+      <c r="C52" s="234" t="inlineStr"/>
+      <c r="D52" s="234" t="inlineStr"/>
+      <c r="E52" s="234" t="inlineStr"/>
+      <c r="F52" s="234" t="inlineStr"/>
+      <c r="G52" s="234" t="inlineStr"/>
+      <c r="H52" s="234" t="inlineStr"/>
+      <c r="I52" s="235">
+        <f>SUM(I40:I51)</f>
+        <v/>
+      </c>
+      <c r="J52" s="234" t="inlineStr"/>
+      <c r="K52" s="234" t="inlineStr"/>
+      <c r="L52" s="234" t="inlineStr"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="225" t="inlineStr"/>
+      <c r="B53" s="225" t="inlineStr">
+        <is>
+          <t>🏛 БЛОК 4: ЮРИДИЧЕСКИЕ РАСХОДЫ, ПОШЛИНЫ, ГАЗ, ЭНЕРГОСБЫТ И IT</t>
+        </is>
+      </c>
+      <c r="C53" s="225" t="inlineStr"/>
+      <c r="D53" s="225" t="inlineStr"/>
+      <c r="E53" s="225" t="inlineStr"/>
+      <c r="F53" s="225" t="inlineStr"/>
+      <c r="G53" s="225" t="inlineStr"/>
+      <c r="H53" s="225" t="inlineStr"/>
+      <c r="I53" s="225" t="inlineStr"/>
+      <c r="J53" s="225" t="inlineStr"/>
+      <c r="K53" s="225" t="inlineStr"/>
+      <c r="L53" s="225" t="inlineStr"/>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" s="62" t="inlineStr">
         <is>
           <t>Юр. оформление</t>
         </is>
       </c>
-      <c r="C52" s="62" t="inlineStr">
-        <is>
-          <t>Росреестр</t>
-        </is>
-      </c>
-      <c r="D52" s="44" t="inlineStr">
-        <is>
-          <t>Государственная пошлина (регистрация перехода права собственности)</t>
-        </is>
-      </c>
-      <c r="E52" s="62" t="inlineStr">
-        <is>
-          <t>ГОСПОШЛИНА-ПРАВО</t>
-        </is>
-      </c>
-      <c r="F52" s="62" t="inlineStr">
-        <is>
-          <t>платеж</t>
-        </is>
-      </c>
-      <c r="G52" s="216" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="173" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I52" s="217">
-        <f>G52*H52</f>
-        <v/>
-      </c>
-      <c r="J52" s="44" t="inlineStr">
-        <is>
-          <t>Росреестр</t>
-        </is>
-      </c>
-      <c r="K52" s="174">
-        <f>HYPERLINK("https://rosreestr.gov.ru/"; "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L52" s="44" t="inlineStr">
-        <is>
-          <t>Официальная пошлина Росреестра</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="64" t="n">
-        <v>10</v>
-      </c>
-      <c r="B53" s="64" t="inlineStr">
-        <is>
-          <t>IT / AI</t>
-        </is>
-      </c>
-      <c r="C53" s="64" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="D53" s="49" t="inlineStr">
-        <is>
-          <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 1</t>
-        </is>
-      </c>
-      <c r="E53" s="64" t="inlineStr">
-        <is>
-          <t>OPENROUTER-TRANS-1</t>
-        </is>
-      </c>
-      <c r="F53" s="64" t="inlineStr">
-        <is>
-          <t>платёж</t>
-        </is>
-      </c>
-      <c r="G53" s="218" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="172" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I53" s="219">
-        <f>G53*H53</f>
-        <v/>
-      </c>
-      <c r="J53" s="49" t="inlineStr">
-        <is>
-          <t>OpenRouter</t>
-        </is>
-      </c>
-      <c r="K53" s="175">
-        <f>HYPERLINK("https://openrouter.ai/"; "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L53" s="49" t="inlineStr">
-        <is>
-          <t>Инфраструктура проектов и аналитика</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="62" t="n">
-        <v>12</v>
-      </c>
-      <c r="B54" s="62" t="inlineStr">
-        <is>
-          <t>Газ</t>
-        </is>
-      </c>
       <c r="C54" s="62" t="inlineStr">
         <is>
-          <t>Безопасность</t>
+          <t>Торги</t>
         </is>
       </c>
       <c r="D54" s="44" t="inlineStr">
         <is>
-          <t>Акт ВДПО — проверка дымохода и вентканала</t>
+          <t>Выпуск квалифицированной ЭЦП (электронная цифровая подпись)</t>
         </is>
       </c>
       <c r="E54" s="62" t="inlineStr">
         <is>
-          <t>ВДПО-АКТ-ВЕНТ</t>
+          <t>ЭЦП-КОНТУР</t>
         </is>
       </c>
       <c r="F54" s="62" t="inlineStr">
         <is>
-          <t>акт</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G54" s="216" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="173" t="n">
-        <v>1500</v>
+        <v>7000</v>
       </c>
       <c r="I54" s="217">
         <f>G54*H54</f>
@@ -8514,41 +8698,41 @@
       </c>
       <c r="J54" s="44" t="inlineStr">
         <is>
-          <t>ВДПО / Газовая служба</t>
+          <t>УЦ / Контур</t>
         </is>
       </c>
       <c r="K54" s="174">
-        <f>HYPERLINK("https://vdpo71.ru/"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://ca.kontur.ru/", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L54" s="44" t="inlineStr">
         <is>
-          <t>Обязательная проверка тяги для газовой колонки</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
+          <t>ЭЦП для участия в торгах и регистрации права</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="19" customHeight="1">
       <c r="A55" s="64" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B55" s="64" t="inlineStr">
         <is>
-          <t>Газ</t>
+          <t>Юр. оформление</t>
         </is>
       </c>
       <c r="C55" s="64" t="inlineStr">
         <is>
-          <t>Коммуналка</t>
+          <t>Росреестр</t>
         </is>
       </c>
       <c r="D55" s="49" t="inlineStr">
         <is>
-          <t>Оплата квитанций Тулагоргаз (платежки/техобслуживание)</t>
+          <t>Государственная пошлина (регистрация перехода права собственности)</t>
         </is>
       </c>
       <c r="E55" s="64" t="inlineStr">
         <is>
-          <t>ТУЛАГОРГАЗ-КВИТАНЦИЯ</t>
+          <t>ГОСПОШЛИНА-ПРАВО</t>
         </is>
       </c>
       <c r="F55" s="64" t="inlineStr">
@@ -8560,7 +8744,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="172" t="n">
-        <v>800</v>
+        <v>5000</v>
       </c>
       <c r="I55" s="219">
         <f>G55*H55</f>
@@ -8568,53 +8752,53 @@
       </c>
       <c r="J55" s="49" t="inlineStr">
         <is>
-          <t>Тулагоргаз</t>
+          <t>Росреестр</t>
         </is>
       </c>
       <c r="K55" s="175">
-        <f>HYPERLINK("https://tulagorgaz.ru/"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://rosreestr.gov.ru/", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L55" s="49" t="inlineStr">
         <is>
-          <t>Погашение начислений газовой службы</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
+          <t>Официальная пошлина Росреестра</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="19" customHeight="1">
       <c r="A56" s="62" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B56" s="62" t="inlineStr">
         <is>
-          <t>Энергосбыт</t>
+          <t>IT / AI</t>
         </is>
       </c>
       <c r="C56" s="62" t="inlineStr">
         <is>
-          <t>Учёт</t>
+          <t>Инфраструктура</t>
         </is>
       </c>
       <c r="D56" s="44" t="inlineStr">
         <is>
-          <t>Срочный выезд инспектора ТНС энерго Тула (снятие пломбы со старого счётчика)</t>
+          <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 1</t>
         </is>
       </c>
       <c r="E56" s="62" t="inlineStr">
         <is>
-          <t>ТНС-ВЫЕЗД-ПЛОМБА</t>
+          <t>OPENROUTER-TRANS-1</t>
         </is>
       </c>
       <c r="F56" s="62" t="inlineStr">
         <is>
-          <t>услуга</t>
+          <t>платёж</t>
         </is>
       </c>
       <c r="G56" s="216" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="173" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I56" s="217">
         <f>G56*H56</f>
@@ -8622,53 +8806,53 @@
       </c>
       <c r="J56" s="44" t="inlineStr">
         <is>
-          <t>АО "ТНС энерго Тула"</t>
+          <t>OpenRouter</t>
         </is>
       </c>
       <c r="K56" s="174">
-        <f>HYPERLINK("https://tns-e.ru/"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://openrouter.ai/", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L56" s="44" t="inlineStr">
         <is>
-          <t>Срочное снятие пломбы за 5 дней</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
+          <t>Инфраструктура проектов и аналитика</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="19" customHeight="1">
       <c r="A57" s="64" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B57" s="64" t="inlineStr">
         <is>
-          <t>IT / AI</t>
+          <t>Газ</t>
         </is>
       </c>
       <c r="C57" s="64" t="inlineStr">
         <is>
-          <t>Инфраструктура</t>
+          <t>Безопасность</t>
         </is>
       </c>
       <c r="D57" s="49" t="inlineStr">
         <is>
-          <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 2</t>
+          <t>Акт ВДПО — проверка дымохода и вентканала</t>
         </is>
       </c>
       <c r="E57" s="64" t="inlineStr">
         <is>
-          <t>OPENROUTER-TRANS-2</t>
+          <t>ВДПО-АКТ-ВЕНТ</t>
         </is>
       </c>
       <c r="F57" s="64" t="inlineStr">
         <is>
-          <t>платёж</t>
+          <t>акт</t>
         </is>
       </c>
       <c r="G57" s="218" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="172" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="I57" s="219">
         <f>G57*H57</f>
@@ -8676,53 +8860,53 @@
       </c>
       <c r="J57" s="49" t="inlineStr">
         <is>
-          <t>OpenRouter</t>
+          <t>ВДПО / Газовая служба</t>
         </is>
       </c>
       <c r="K57" s="175">
-        <f>HYPERLINK("https://openrouter.ai/"; "Открыть ↗")</f>
+        <f>HYPERLINK("https://vdpo71.ru/", "Открыть ↗")</f>
         <v/>
       </c>
       <c r="L57" s="49" t="inlineStr">
         <is>
-          <t>Пополнение баланса API для расчётов и смет</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
+          <t>Обязательная проверка тяги для газовой колонки</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="19" customHeight="1">
       <c r="A58" s="62" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B58" s="62" t="inlineStr">
         <is>
-          <t>Энергосбыт</t>
+          <t>Газ</t>
         </is>
       </c>
       <c r="C58" s="62" t="inlineStr">
         <is>
-          <t>Учёт</t>
+          <t>Коммуналка</t>
         </is>
       </c>
       <c r="D58" s="44" t="inlineStr">
         <is>
-          <t>Дистанционная распломбировка старого электросчётчика (согласование)</t>
+          <t>Оплата квитанций Тулагоргаз (платежки/техобслуживание)</t>
         </is>
       </c>
       <c r="E58" s="62" t="inlineStr">
         <is>
-          <t>ТНС-РАСПЛОМБ-ДИСТ</t>
+          <t>ТУЛАГОРГАЗ-КВИТАНЦИЯ</t>
         </is>
       </c>
       <c r="F58" s="62" t="inlineStr">
         <is>
-          <t>услуга</t>
+          <t>платеж</t>
         </is>
       </c>
       <c r="G58" s="216" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="173" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="I58" s="217">
         <f>G58*H58</f>
@@ -8730,60 +8914,222 @@
       </c>
       <c r="J58" s="44" t="inlineStr">
         <is>
+          <t>Тулагоргаз</t>
+        </is>
+      </c>
+      <c r="K58" s="174">
+        <f>HYPERLINK("https://tulagorgaz.ru/", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L58" s="44" t="inlineStr">
+        <is>
+          <t>Погашение начислений газовой службы</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="64" t="n">
+        <v>21</v>
+      </c>
+      <c r="B59" s="64" t="inlineStr">
+        <is>
+          <t>Энергосбыт</t>
+        </is>
+      </c>
+      <c r="C59" s="64" t="inlineStr">
+        <is>
+          <t>Учёт</t>
+        </is>
+      </c>
+      <c r="D59" s="49" t="inlineStr">
+        <is>
+          <t>Срочный выезд инспектора ТНС энерго Тула (снятие пломбы со старого счётчика)</t>
+        </is>
+      </c>
+      <c r="E59" s="64" t="inlineStr">
+        <is>
+          <t>ТНС-ВЫЕЗД-ПЛОМБА</t>
+        </is>
+      </c>
+      <c r="F59" s="64" t="inlineStr">
+        <is>
+          <t>услуга</t>
+        </is>
+      </c>
+      <c r="G59" s="218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="172" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I59" s="219">
+        <f>G59*H59</f>
+        <v/>
+      </c>
+      <c r="J59" s="49" t="inlineStr">
+        <is>
+          <t>АО "ТНС энерго Тула"</t>
+        </is>
+      </c>
+      <c r="K59" s="175">
+        <f>HYPERLINK("https://tns-e.ru/", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L59" s="49" t="inlineStr">
+        <is>
+          <t>Срочное снятие пломбы за 5 дней</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="19" customHeight="1">
+      <c r="A60" s="62" t="n">
+        <v>31</v>
+      </c>
+      <c r="B60" s="62" t="inlineStr">
+        <is>
+          <t>IT / AI</t>
+        </is>
+      </c>
+      <c r="C60" s="62" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="D60" s="44" t="inlineStr">
+        <is>
+          <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 2</t>
+        </is>
+      </c>
+      <c r="E60" s="62" t="inlineStr">
+        <is>
+          <t>OPENROUTER-TRANS-2</t>
+        </is>
+      </c>
+      <c r="F60" s="62" t="inlineStr">
+        <is>
+          <t>платёж</t>
+        </is>
+      </c>
+      <c r="G60" s="216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="173" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I60" s="217">
+        <f>G60*H60</f>
+        <v/>
+      </c>
+      <c r="J60" s="44" t="inlineStr">
+        <is>
+          <t>OpenRouter</t>
+        </is>
+      </c>
+      <c r="K60" s="174">
+        <f>HYPERLINK("https://openrouter.ai/", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L60" s="44" t="inlineStr">
+        <is>
+          <t>Пополнение баланса API для расчётов и смет</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="64" t="n">
+        <v>33</v>
+      </c>
+      <c r="B61" s="64" t="inlineStr">
+        <is>
+          <t>Энергосбыт</t>
+        </is>
+      </c>
+      <c r="C61" s="64" t="inlineStr">
+        <is>
+          <t>Учёт</t>
+        </is>
+      </c>
+      <c r="D61" s="49" t="inlineStr">
+        <is>
+          <t>Дистанционная распломбировка старого электросчётчика (согласование)</t>
+        </is>
+      </c>
+      <c r="E61" s="64" t="inlineStr">
+        <is>
+          <t>ТНС-РАСПЛОМБ-ДИСТ</t>
+        </is>
+      </c>
+      <c r="F61" s="64" t="inlineStr">
+        <is>
+          <t>услуга</t>
+        </is>
+      </c>
+      <c r="G61" s="218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="172" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I61" s="219">
+        <f>G61*H61</f>
+        <v/>
+      </c>
+      <c r="J61" s="49" t="inlineStr">
+        <is>
           <t>ТНС энерго Тула / Энергосбыт</t>
         </is>
       </c>
-      <c r="K58" s="174">
-        <f>HYPERLINK("https://tns-e.ru/"; "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L58" s="44" t="inlineStr">
+      <c r="K61" s="175">
+        <f>HYPERLINK("https://tns-e.ru/", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L61" s="49" t="inlineStr">
         <is>
           <t>Официальное согласование замены электроузла</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="223" t="inlineStr"/>
-      <c r="B59" s="223" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="234" t="inlineStr"/>
+      <c r="B62" s="234" t="inlineStr">
         <is>
           <t>ИТОГО ЮР. РАСХОДЫ, СЛУЖБЫ И IT:</t>
         </is>
       </c>
-      <c r="C59" s="223" t="inlineStr"/>
-      <c r="D59" s="223" t="inlineStr"/>
-      <c r="E59" s="223" t="inlineStr"/>
-      <c r="F59" s="223" t="inlineStr"/>
-      <c r="G59" s="223" t="inlineStr"/>
-      <c r="H59" s="223" t="inlineStr"/>
-      <c r="I59" s="224">
-        <f>SUM(I51:I58)</f>
-        <v/>
-      </c>
-      <c r="J59" s="223" t="inlineStr"/>
-      <c r="K59" s="223" t="inlineStr"/>
-      <c r="L59" s="223" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="226" t="inlineStr"/>
-      <c r="B60" s="226" t="inlineStr">
+      <c r="C62" s="234" t="inlineStr"/>
+      <c r="D62" s="234" t="inlineStr"/>
+      <c r="E62" s="234" t="inlineStr"/>
+      <c r="F62" s="234" t="inlineStr"/>
+      <c r="G62" s="234" t="inlineStr"/>
+      <c r="H62" s="234" t="inlineStr"/>
+      <c r="I62" s="235">
+        <f>SUM(I54:I61)</f>
+        <v/>
+      </c>
+      <c r="J62" s="234" t="inlineStr"/>
+      <c r="K62" s="234" t="inlineStr"/>
+      <c r="L62" s="234" t="inlineStr"/>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="236" t="inlineStr"/>
+      <c r="B63" s="236" t="inlineStr">
         <is>
           <t>ОБЩИЙ ИТОГО ФАКТ РАСХОДОВ (ДИНАМИЧЕСКИЙ):</t>
         </is>
       </c>
-      <c r="C60" s="226" t="inlineStr"/>
-      <c r="D60" s="226" t="inlineStr"/>
-      <c r="E60" s="226" t="inlineStr"/>
-      <c r="F60" s="226" t="inlineStr"/>
-      <c r="G60" s="226" t="inlineStr"/>
-      <c r="H60" s="226" t="inlineStr"/>
-      <c r="I60" s="227">
-        <f>SUBTOTAL(109; I6:I21; I24:I36; I39:I48; I51:I58)</f>
-        <v/>
-      </c>
-      <c r="J60" s="226" t="inlineStr"/>
-      <c r="K60" s="226" t="inlineStr"/>
-      <c r="L60" s="226" t="inlineStr"/>
+      <c r="C63" s="236" t="inlineStr"/>
+      <c r="D63" s="236" t="inlineStr"/>
+      <c r="E63" s="236" t="inlineStr"/>
+      <c r="F63" s="236" t="inlineStr"/>
+      <c r="G63" s="236" t="inlineStr"/>
+      <c r="H63" s="236" t="inlineStr"/>
+      <c r="I63" s="237">
+        <f>SUBTOTAL(109, I6:I22, I25:I37, I40:I51, I54:I61)</f>
+        <v/>
+      </c>
+      <c r="J63" s="236" t="inlineStr"/>
+      <c r="K63" s="236" t="inlineStr"/>
+      <c r="L63" s="236" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
+++ b/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="167" formatCode="+0.0%"/>
     <numFmt numFmtId="168" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -247,6 +247,12 @@
       <b val="1"/>
       <color rgb="00581C87"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="12">
@@ -652,7 +658,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1271,6 +1277,32 @@
     <xf numFmtId="166" fontId="16" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1705,7 +1737,7 @@
         <v/>
       </c>
       <c r="D5" s="118">
-        <f>'Факт расходов'!F55</f>
+        <f>'Факт расходов'!F69</f>
         <v/>
       </c>
       <c r="E5" s="118" t="n">
@@ -1798,7 +1830,7 @@
         <v>23000</v>
       </c>
       <c r="C11" s="46">
-        <f>SUMIF('Факт расходов'!C5:C54, "*Юр.*", 'Факт расходов'!F5:F54)+SUMIF('Факт расходов'!C5:C54, "*Безопасность*", 'Факт расходов'!F5:F54)+SUMIF('Факт расходов'!C5:C54, "*IT*", 'Факт расходов'!F5:F54)+SUMIF('Факт расходов'!C5:C54, "*Электроэнергия*", 'Факт расходов'!F5:F54)</f>
+        <f>SUMIF('Факт расходов'!C5:C68, "*Юр.*", 'Факт расходов'!F5:F68)+SUMIF('Факт расходов'!C5:C68, "*Безопасность*", 'Факт расходов'!F5:F68)+SUMIF('Факт расходов'!C5:C68, "*IT*", 'Факт расходов'!F5:F68)+SUMIF('Факт расходов'!C5:C68, "*Электроэнергия*", 'Факт расходов'!F5:F68)</f>
         <v/>
       </c>
       <c r="D11" s="124">
@@ -2078,7 +2110,7 @@
         <v/>
       </c>
       <c r="C23" s="46">
-        <f>SUMIF('Факт расходов'!C5:C54, "*Демонтаж*", 'Факт расходов'!F5:F54)</f>
+        <f>SUMIF('Факт расходов'!C5:C68, "*Демонтаж*", 'Факт расходов'!F5:F68)</f>
         <v/>
       </c>
       <c r="D23" s="45">
@@ -2111,7 +2143,7 @@
         <v/>
       </c>
       <c r="C24" s="51">
-        <f>SUMIF('Факт расходов'!C5:C54, "*Двери*", 'Факт расходов'!F5:F54)</f>
+        <f>SUMIF('Факт расходов'!C5:C68, "*Двери*", 'Факт расходов'!F5:F68)</f>
         <v/>
       </c>
       <c r="D24" s="50">
@@ -2144,7 +2176,7 @@
         <v/>
       </c>
       <c r="C25" s="46">
-        <f>SUMIF('Факт расходов'!C5:C54, "*Электрика*", 'Факт расходов'!F5:F54)</f>
+        <f>SUMIF('Факт расходов'!C5:C68, "*Электрика*", 'Факт расходов'!F5:F68)</f>
         <v/>
       </c>
       <c r="D25" s="45">
@@ -2177,7 +2209,7 @@
         <v/>
       </c>
       <c r="C26" s="51">
-        <f>SUMIF('Факт расходов'!C5:C54, "*Сантехника*", 'Факт расходов'!F5:F54)</f>
+        <f>SUMIF('Факт расходов'!C5:C68, "*Сантехника*", 'Факт расходов'!F5:F68)</f>
         <v/>
       </c>
       <c r="D26" s="50">
@@ -2209,7 +2241,7 @@
         <v>5000</v>
       </c>
       <c r="C27" s="46">
-        <f>SUMIF('Факт расходов'!C5:C54, "*Газ*", 'Факт расходов'!F5:F54)</f>
+        <f>SUMIF('Факт расходов'!C5:C68, "*Газ*", 'Факт расходов'!F5:F68)</f>
         <v/>
       </c>
       <c r="D27" s="45">
@@ -2274,7 +2306,7 @@
         <v/>
       </c>
       <c r="C29" s="46">
-        <f>SUMIF('Факт расходов'!C5:C54, "*Черновая*", 'Факт расходов'!F5:F54)</f>
+        <f>SUMIF('Факт расходов'!C5:C68, "*Черновая*", 'Факт расходов'!F5:F68)</f>
         <v/>
       </c>
       <c r="D29" s="45">
@@ -2307,7 +2339,7 @@
         <v/>
       </c>
       <c r="C30" s="51">
-        <f>SUMIF('Факт расходов'!C5:C54, "*Чистовая*", 'Факт расходов'!F5:F54)</f>
+        <f>SUMIF('Факт расходов'!C5:C68, "*Чистовая*", 'Факт расходов'!F5:F68)</f>
         <v/>
       </c>
       <c r="D30" s="50">
@@ -2467,7 +2499,7 @@
         <v>10000</v>
       </c>
       <c r="C35" s="46">
-        <f>SUMIF('Факт расходов'!C5:C54, "*Инструмент*", 'Факт расходов'!F5:F54)+SUMIF('Факт расходов'!C5:C54, "*Расходные*", 'Факт расходов'!F5:F54)+SUMIF('Факт расходов'!C5:C54, "*Логистика*", 'Факт расходов'!F5:F54)</f>
+        <f>SUMIF('Факт расходов'!C5:C68, "*Инструмент*", 'Факт расходов'!F5:F68)+SUMIF('Факт расходов'!C5:C68, "*Расходные*", 'Факт расходов'!F5:F68)+SUMIF('Факт расходов'!C5:C68, "*Логистика*", 'Факт расходов'!F5:F68)</f>
         <v/>
       </c>
       <c r="D35" s="45">
@@ -2499,7 +2531,7 @@
         <v>5000</v>
       </c>
       <c r="C36" s="51">
-        <f>SUMIF('Факт расходов'!C5:C54, "*Оснащение*", 'Факт расходов'!F5:F54)</f>
+        <f>SUMIF('Факт расходов'!C5:C68, "*Оснащение*", 'Факт расходов'!F5:F68)</f>
         <v/>
       </c>
       <c r="D36" s="50">
@@ -2681,11 +2713,11 @@
         </is>
       </c>
       <c r="B45" s="45">
-        <f>'Факт расходов'!E55</f>
+        <f>'Факт расходов'!E69</f>
         <v/>
       </c>
       <c r="C45" s="45">
-        <f>'Факт расходов'!F55</f>
+        <f>'Факт расходов'!F69</f>
         <v/>
       </c>
       <c r="D45" s="124">
@@ -2768,7 +2800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5286,257 +5318,705 @@
       <c r="M54" s="140" t="n"/>
       <c r="N54" s="140" t="n"/>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="94" t="n"/>
-      <c r="B55" s="94" t="n"/>
-      <c r="C55" s="54" t="n"/>
-      <c r="D55" s="65" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДОВ:</t>
-        </is>
-      </c>
-      <c r="E55" s="55">
-        <f>SUM(E5:E54)</f>
-        <v/>
-      </c>
-      <c r="F55" s="55">
-        <f>SUM(F5:F54)</f>
-        <v/>
-      </c>
-      <c r="G55" s="55">
-        <f>SUM(G5:G54)</f>
-        <v/>
-      </c>
-      <c r="H55" s="104">
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="86" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="86" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="C55" s="82" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D55" s="82" t="inlineStr">
+        <is>
+          <t>Штукатурка гипсовая Старатели 30кг 3шт (1515₽), перчатки, мешки 3шт (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="E55" s="83" t="n">
+        <v>1638</v>
+      </c>
+      <c r="F55" s="84" t="n">
+        <v>1638</v>
+      </c>
+      <c r="G55" s="85">
+        <f>E55-F55</f>
+        <v/>
+      </c>
+      <c r="H55" s="115">
         <f>IFERROR(G55/E55, 0)</f>
         <v/>
       </c>
-      <c r="I55" s="54" t="n"/>
-      <c r="J55" s="54" t="n"/>
+      <c r="I55" s="82" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J55" s="82" t="inlineStr">
+        <is>
+          <t>Чек от 23.09.2026 15:55 (касса 72): штукатурка Старатели 30кг 3шт по 505₽=1515₽, перчатки х/б 13кл 27₽, мешки 3шт по 32₽=96₽</t>
+        </is>
+      </c>
       <c r="K55" s="140" t="n"/>
       <c r="L55" s="140" t="n"/>
       <c r="M55" s="140" t="n"/>
       <c r="N55" s="140" t="n"/>
     </row>
-    <row r="56">
-      <c r="A56" s="140" t="n"/>
-      <c r="B56" s="140" t="n"/>
-      <c r="C56" s="140" t="n"/>
-      <c r="D56" s="140" t="n"/>
-      <c r="E56" s="140" t="n"/>
-      <c r="F56" s="140" t="n"/>
-      <c r="G56" s="140" t="n"/>
-      <c r="H56" s="140" t="n"/>
-      <c r="I56" s="140" t="n"/>
-      <c r="J56" s="140" t="n"/>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="91" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="91" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="C56" s="88" t="inlineStr">
+        <is>
+          <t>Чистовая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D56" s="88" t="inlineStr">
+        <is>
+          <t>Грунт-эмаль Luxens 3в1 белая 2.4кг (1492₽), щетка 5-рядная, кисть Dilwis 70мм (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="E56" s="89" t="n">
+        <v>1769</v>
+      </c>
+      <c r="F56" s="90" t="n">
+        <v>1769</v>
+      </c>
+      <c r="G56" s="85">
+        <f>E56-F56</f>
+        <v/>
+      </c>
+      <c r="H56" s="115">
+        <f>IFERROR(G56/E56, 0)</f>
+        <v/>
+      </c>
+      <c r="I56" s="88" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J56" s="88" t="inlineStr">
+        <is>
+          <t>Чек от 23.09.2026 16:10 (касса 75): грунт-эмаль Luxens 3в1 белая 2.4кг (1492₽), кисть Dilwis 70мм (171₽), щетка металл 260мм (106₽)</t>
+        </is>
+      </c>
       <c r="K56" s="140" t="n"/>
       <c r="L56" s="140" t="n"/>
       <c r="M56" s="140" t="n"/>
       <c r="N56" s="140" t="n"/>
     </row>
-    <row r="57">
-      <c r="A57" s="140" t="n"/>
-      <c r="B57" s="140" t="n"/>
-      <c r="C57" s="140" t="n"/>
-      <c r="D57" s="140" t="n"/>
-      <c r="E57" s="140" t="n"/>
-      <c r="F57" s="140" t="n"/>
-      <c r="G57" s="140" t="n"/>
-      <c r="H57" s="140" t="n"/>
-      <c r="I57" s="140" t="n"/>
-      <c r="J57" s="140" t="n"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="86" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="86" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="C57" s="82" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D57" s="82" t="inlineStr">
+        <is>
+          <t>Профиль ППН 27х28х3000 3шт, профиль ПП 60х27 1шт, саморезы ПШС и ШСГД/ШСГМ (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="E57" s="83" t="n">
+        <v>911.7</v>
+      </c>
+      <c r="F57" s="84" t="n">
+        <v>911.7</v>
+      </c>
+      <c r="G57" s="85">
+        <f>E57-F57</f>
+        <v/>
+      </c>
+      <c r="H57" s="115">
+        <f>IFERROR(G57/E57, 0)</f>
+        <v/>
+      </c>
+      <c r="I57" s="82" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J57" s="82" t="inlineStr">
+        <is>
+          <t>Чек от 25.09.2026 08:18 (касса 78): профиль ППН 3шт (372₽), профиль ПП 1шт (193₽), саморезы оцинкованные и фосфатированные 1.122кг (346.70₽)</t>
+        </is>
+      </c>
       <c r="K57" s="140" t="n"/>
       <c r="L57" s="140" t="n"/>
       <c r="M57" s="140" t="n"/>
       <c r="N57" s="140" t="n"/>
     </row>
-    <row r="58">
-      <c r="A58" s="140" t="n"/>
-      <c r="B58" s="140" t="n"/>
-      <c r="C58" s="140" t="n"/>
-      <c r="D58" s="140" t="n"/>
-      <c r="E58" s="140" t="n"/>
-      <c r="F58" s="140" t="n"/>
-      <c r="G58" s="140" t="n"/>
-      <c r="H58" s="140" t="n"/>
-      <c r="I58" s="140" t="n"/>
-      <c r="J58" s="140" t="n"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="91" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="91" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="C58" s="88" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D58" s="88" t="inlineStr">
+        <is>
+          <t>ГСП-Н3 Knauf влагост. 1500х600х12.5 2шт, штукатурка Старатели 30кг, профили 28х27 2шт и 60х27 1шт, перчатки (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="E58" s="89" t="n">
+        <v>1582</v>
+      </c>
+      <c r="F58" s="90" t="n">
+        <v>1582</v>
+      </c>
+      <c r="G58" s="85">
+        <f>E58-F58</f>
+        <v/>
+      </c>
+      <c r="H58" s="115">
+        <f>IFERROR(G58/E58, 0)</f>
+        <v/>
+      </c>
+      <c r="I58" s="88" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J58" s="88" t="inlineStr">
+        <is>
+          <t>Чек от 25.09.2026 15:53 (касса 76): ГСП влагост. Knauf 2шт (460₽), штукатурка Старатели 30кг (505₽), профиль ППН 28х27 2шт (282₽), профиль Knauf 60х27 (308₽), перчатки (27₽)</t>
+        </is>
+      </c>
       <c r="K58" s="140" t="n"/>
       <c r="L58" s="140" t="n"/>
       <c r="M58" s="140" t="n"/>
       <c r="N58" s="140" t="n"/>
     </row>
-    <row r="59">
-      <c r="A59" s="140" t="n"/>
-      <c r="B59" s="140" t="n"/>
-      <c r="C59" s="140" t="n"/>
-      <c r="D59" s="140" t="n"/>
-      <c r="E59" s="140" t="n"/>
-      <c r="F59" s="140" t="n"/>
-      <c r="G59" s="140" t="n"/>
-      <c r="H59" s="140" t="n"/>
-      <c r="I59" s="140" t="n"/>
-      <c r="J59" s="140" t="n"/>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="86" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="86" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="C59" s="82" t="inlineStr">
+        <is>
+          <t>Чистовая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D59" s="82" t="inlineStr">
+        <is>
+          <t>Ламинат Kronostep Ultrastep Дуб Ночиолла 33 кл 10мм 24 упак./41.52м², подложка Monlid 3мм 9шт, плинтус белый 8см 20шт</t>
+        </is>
+      </c>
+      <c r="E59" s="83" t="n">
+        <v>45551.52</v>
+      </c>
+      <c r="F59" s="84" t="n">
+        <v>41914.52</v>
+      </c>
+      <c r="G59" s="85">
+        <f>E59-F59</f>
+        <v/>
+      </c>
+      <c r="H59" s="115">
+        <f>IFERROR(G59/E59, 0)</f>
+        <v/>
+      </c>
+      <c r="I59" s="82" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J59" s="82" t="inlineStr">
+        <is>
+          <t>Чек от 26.09.2026 17:41: ламинат Дуб Ночиолла 24 упак. (32734.52₽ с учетом скидки -3637₽), подложка Monlid 3мм 9шт (4680₽), плинтус белый 80мм 20шт (4500₽). Скидка по промокоду -3 637.00 ₽</t>
+        </is>
+      </c>
       <c r="K59" s="140" t="n"/>
       <c r="L59" s="140" t="n"/>
       <c r="M59" s="140" t="n"/>
       <c r="N59" s="140" t="n"/>
     </row>
-    <row r="60">
-      <c r="A60" s="140" t="n"/>
-      <c r="B60" s="140" t="n"/>
-      <c r="C60" s="140" t="n"/>
-      <c r="D60" s="140" t="n"/>
-      <c r="E60" s="140" t="n"/>
-      <c r="F60" s="140" t="n"/>
-      <c r="G60" s="140" t="n"/>
-      <c r="H60" s="140" t="n"/>
-      <c r="I60" s="140" t="n"/>
-      <c r="J60" s="140" t="n"/>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="91" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="91" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="C60" s="88" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D60" s="88" t="inlineStr">
+        <is>
+          <t>Грунт перекрывающий пятна Axton 1л, клей монтажный Kudo 2шт, валик нат. мех 110мм, макловица-мини (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="E60" s="89" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F60" s="90" t="n">
+        <v>1070</v>
+      </c>
+      <c r="G60" s="85">
+        <f>E60-F60</f>
+        <v/>
+      </c>
+      <c r="H60" s="115">
+        <f>IFERROR(G60/E60, 0)</f>
+        <v/>
+      </c>
+      <c r="I60" s="88" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J60" s="88" t="inlineStr">
+        <is>
+          <t>Чек от 26.09.2026 17:40 (касса 76): грунт блокирующий пятна Axton 1л (427₽), клей монтажный Kudo 2шт (410₽), валик 110мм (96₽), макловица-мини (137₽)</t>
+        </is>
+      </c>
       <c r="K60" s="140" t="n"/>
       <c r="L60" s="140" t="n"/>
       <c r="M60" s="140" t="n"/>
       <c r="N60" s="140" t="n"/>
     </row>
-    <row r="61">
-      <c r="A61" s="140" t="n"/>
-      <c r="B61" s="140" t="n"/>
-      <c r="C61" s="140" t="n"/>
-      <c r="D61" s="140" t="n"/>
-      <c r="E61" s="140" t="n"/>
-      <c r="F61" s="140" t="n"/>
-      <c r="G61" s="140" t="n"/>
-      <c r="H61" s="140" t="n"/>
-      <c r="I61" s="140" t="n"/>
-      <c r="J61" s="140" t="n"/>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="86" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="86" t="inlineStr">
+        <is>
+          <t>27.09.2026</t>
+        </is>
+      </c>
+      <c r="C61" s="82" t="inlineStr">
+        <is>
+          <t>Инструмент и расходники</t>
+        </is>
+      </c>
+      <c r="D61" s="82" t="inlineStr">
+        <is>
+          <t>Расходные материалы и инструмент: швабра, тряпки 3шт, краска Olimp 0.9л, лента упак., саморезы, макловица, ножи 2шт, карандаш (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="E61" s="83" t="n">
+        <v>1707.17</v>
+      </c>
+      <c r="F61" s="84" t="n">
+        <v>1707.17</v>
+      </c>
+      <c r="G61" s="85">
+        <f>E61-F61</f>
+        <v/>
+      </c>
+      <c r="H61" s="115">
+        <f>IFERROR(G61/E61, 0)</f>
+        <v/>
+      </c>
+      <c r="I61" s="82" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J61" s="82" t="inlineStr">
+        <is>
+          <t>Чек от 27.09.2026 09:53 (касса 72): швабра In Loran (426₽), тряпки 3шт (120₽), краска Olimp акрил 0.9л (294₽), клейкая лента Axton (101₽), саморезы 0.314кг (140.67₽), макловица (137₽), ножи 2шт (160₽), карандаш (50₽) и др.</t>
+        </is>
+      </c>
       <c r="K61" s="140" t="n"/>
       <c r="L61" s="140" t="n"/>
       <c r="M61" s="140" t="n"/>
       <c r="N61" s="140" t="n"/>
     </row>
-    <row r="62">
-      <c r="A62" s="140" t="n"/>
-      <c r="B62" s="140" t="n"/>
-      <c r="C62" s="140" t="n"/>
-      <c r="D62" s="140" t="n"/>
-      <c r="E62" s="140" t="n"/>
-      <c r="F62" s="140" t="n"/>
-      <c r="G62" s="140" t="n"/>
-      <c r="H62" s="140" t="n"/>
-      <c r="I62" s="140" t="n"/>
-      <c r="J62" s="140" t="n"/>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="91" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="91" t="inlineStr">
+        <is>
+          <t>27.09.2026</t>
+        </is>
+      </c>
+      <c r="C62" s="88" t="inlineStr">
+        <is>
+          <t>Электрика / Материалы</t>
+        </is>
+      </c>
+      <c r="D62" s="88" t="inlineStr">
+        <is>
+          <t>Электротовары (расходники/комплектующие электрики, ул. Коминтерна 26)</t>
+        </is>
+      </c>
+      <c r="E62" s="89" t="n">
+        <v>190</v>
+      </c>
+      <c r="F62" s="90" t="n">
+        <v>190</v>
+      </c>
+      <c r="G62" s="85">
+        <f>E62-F62</f>
+        <v/>
+      </c>
+      <c r="H62" s="115">
+        <f>IFERROR(G62/E62, 0)</f>
+        <v/>
+      </c>
+      <c r="I62" s="88" t="inlineStr">
+        <is>
+          <t>Магазин «Электротовары» (Коминтерна 26)</t>
+        </is>
+      </c>
+      <c r="J62" s="88" t="inlineStr">
+        <is>
+          <t>Слип терминала Сбербанк от 27.09.2026 13:08 (карта *6730): покупка электротоваров на ул. Коминтерна 26</t>
+        </is>
+      </c>
       <c r="K62" s="140" t="n"/>
       <c r="L62" s="140" t="n"/>
       <c r="M62" s="140" t="n"/>
       <c r="N62" s="140" t="n"/>
     </row>
-    <row r="63">
-      <c r="A63" s="140" t="n"/>
-      <c r="B63" s="140" t="n"/>
-      <c r="C63" s="140" t="n"/>
-      <c r="D63" s="140" t="n"/>
-      <c r="E63" s="140" t="n"/>
-      <c r="F63" s="140" t="n"/>
-      <c r="G63" s="140" t="n"/>
-      <c r="H63" s="140" t="n"/>
-      <c r="I63" s="140" t="n"/>
-      <c r="J63" s="140" t="n"/>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="86" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="86" t="inlineStr">
+        <is>
+          <t>27.09.2026</t>
+        </is>
+      </c>
+      <c r="C63" s="82" t="inlineStr">
+        <is>
+          <t>Инструмент и расходники</t>
+        </is>
+      </c>
+      <c r="D63" s="82" t="inlineStr">
+        <is>
+          <t>Клинья для плитки СВП 32х8х9мм 50шт (Магазин крепежа, Мосина 29)</t>
+        </is>
+      </c>
+      <c r="E63" s="83" t="n">
+        <v>210</v>
+      </c>
+      <c r="F63" s="84" t="n">
+        <v>210</v>
+      </c>
+      <c r="G63" s="85">
+        <f>E63-F63</f>
+        <v/>
+      </c>
+      <c r="H63" s="115">
+        <f>IFERROR(G63/E63, 0)</f>
+        <v/>
+      </c>
+      <c r="I63" s="82" t="inlineStr">
+        <is>
+          <t>ИП Звягинцева С.Н. (Магазин крепежа)</t>
+        </is>
+      </c>
+      <c r="J63" s="82" t="inlineStr">
+        <is>
+          <t>Чек от 27.09.2026 13:23: клинья для плитки 50шт (210₽)</t>
+        </is>
+      </c>
       <c r="K63" s="140" t="n"/>
       <c r="L63" s="140" t="n"/>
       <c r="M63" s="140" t="n"/>
       <c r="N63" s="140" t="n"/>
     </row>
-    <row r="64">
-      <c r="A64" s="140" t="n"/>
-      <c r="B64" s="140" t="n"/>
-      <c r="C64" s="140" t="n"/>
-      <c r="D64" s="140" t="n"/>
-      <c r="E64" s="140" t="n"/>
-      <c r="F64" s="140" t="n"/>
-      <c r="G64" s="140" t="n"/>
-      <c r="H64" s="140" t="n"/>
-      <c r="I64" s="140" t="n"/>
-      <c r="J64" s="140" t="n"/>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="91" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="91" t="inlineStr">
+        <is>
+          <t>27.09.2026</t>
+        </is>
+      </c>
+      <c r="C64" s="88" t="inlineStr">
+        <is>
+          <t>Логистика и доставка</t>
+        </is>
+      </c>
+      <c r="D64" s="88" t="inlineStr">
+        <is>
+          <t>Такси (оперативная доставка / подвоз материалов на объект)</t>
+        </is>
+      </c>
+      <c r="E64" s="89" t="n">
+        <v>850</v>
+      </c>
+      <c r="F64" s="90" t="n">
+        <v>850</v>
+      </c>
+      <c r="G64" s="85">
+        <f>E64-F64</f>
+        <v/>
+      </c>
+      <c r="H64" s="115">
+        <f>IFERROR(G64/E64, 0)</f>
+        <v/>
+      </c>
+      <c r="I64" s="88" t="inlineStr">
+        <is>
+          <t>Такси (Яндекс Go)</t>
+        </is>
+      </c>
+      <c r="J64" s="88" t="inlineStr">
+        <is>
+          <t>Оперативная доставка материалов на объект ул. Фрунзе 17</t>
+        </is>
+      </c>
       <c r="K64" s="140" t="n"/>
       <c r="L64" s="140" t="n"/>
       <c r="M64" s="140" t="n"/>
       <c r="N64" s="140" t="n"/>
     </row>
-    <row r="65">
-      <c r="A65" s="140" t="n"/>
-      <c r="B65" s="140" t="n"/>
-      <c r="C65" s="140" t="n"/>
-      <c r="D65" s="140" t="n"/>
-      <c r="E65" s="140" t="n"/>
-      <c r="F65" s="140" t="n"/>
-      <c r="G65" s="140" t="n"/>
-      <c r="H65" s="140" t="n"/>
-      <c r="I65" s="140" t="n"/>
-      <c r="J65" s="140" t="n"/>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="86" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="86" t="inlineStr">
+        <is>
+          <t>27.09.2026</t>
+        </is>
+      </c>
+      <c r="C65" s="82" t="inlineStr">
+        <is>
+          <t>Чистовая отделка / Работы</t>
+        </is>
+      </c>
+      <c r="D65" s="82" t="inlineStr">
+        <is>
+          <t>Работы плиточника (аванс / подготовка к укладке плитки в санузле)</t>
+        </is>
+      </c>
+      <c r="E65" s="83" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F65" s="84" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G65" s="85">
+        <f>E65-F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="115">
+        <f>IFERROR(G65/E65, 0)</f>
+        <v/>
+      </c>
+      <c r="I65" s="82" t="inlineStr">
+        <is>
+          <t>Плиточник (мастер)</t>
+        </is>
+      </c>
+      <c r="J65" s="82" t="inlineStr">
+        <is>
+          <t>Оплата плиточнику за работы в санузле</t>
+        </is>
+      </c>
       <c r="K65" s="140" t="n"/>
       <c r="L65" s="140" t="n"/>
       <c r="M65" s="140" t="n"/>
       <c r="N65" s="140" t="n"/>
     </row>
-    <row r="66">
-      <c r="A66" s="140" t="n"/>
-      <c r="B66" s="140" t="n"/>
-      <c r="C66" s="140" t="n"/>
-      <c r="D66" s="140" t="n"/>
-      <c r="E66" s="140" t="n"/>
-      <c r="F66" s="140" t="n"/>
-      <c r="G66" s="140" t="n"/>
-      <c r="H66" s="140" t="n"/>
-      <c r="I66" s="140" t="n"/>
-      <c r="J66" s="140" t="n"/>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="91" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="91" t="inlineStr">
+        <is>
+          <t>27.09.2026</t>
+        </is>
+      </c>
+      <c r="C66" s="88" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Работы</t>
+        </is>
+      </c>
+      <c r="D66" s="88" t="inlineStr">
+        <is>
+          <t>Работы плиточника: заливка стяжки пола в санузле/туалете</t>
+        </is>
+      </c>
+      <c r="E66" s="89" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F66" s="90" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G66" s="85">
+        <f>E66-F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="115">
+        <f>IFERROR(G66/E66, 0)</f>
+        <v/>
+      </c>
+      <c r="I66" s="88" t="inlineStr">
+        <is>
+          <t>Плиточник (мастер)</t>
+        </is>
+      </c>
+      <c r="J66" s="88" t="inlineStr">
+        <is>
+          <t>Заливка стяжки пола в санузле по маякам (пескобетон М300 + фибра + Cemfix)</t>
+        </is>
+      </c>
       <c r="K66" s="140" t="n"/>
       <c r="L66" s="140" t="n"/>
       <c r="M66" s="140" t="n"/>
       <c r="N66" s="140" t="n"/>
     </row>
-    <row r="67">
-      <c r="A67" s="140" t="n"/>
-      <c r="B67" s="140" t="n"/>
-      <c r="C67" s="140" t="n"/>
-      <c r="D67" s="140" t="n"/>
-      <c r="E67" s="140" t="n"/>
-      <c r="F67" s="140" t="n"/>
-      <c r="G67" s="140" t="n"/>
-      <c r="H67" s="140" t="n"/>
-      <c r="I67" s="140" t="n"/>
-      <c r="J67" s="140" t="n"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="86" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="86" t="inlineStr">
+        <is>
+          <t>27.09.2026</t>
+        </is>
+      </c>
+      <c r="C67" s="82" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Работы</t>
+        </is>
+      </c>
+      <c r="D67" s="82" t="inlineStr">
+        <is>
+          <t>Оплата за штукатурку туалета (санузла) под 90° под ванну и плитку</t>
+        </is>
+      </c>
+      <c r="E67" s="83" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F67" s="84" t="n">
+        <v>13400</v>
+      </c>
+      <c r="G67" s="85">
+        <f>E67-F67</f>
+        <v/>
+      </c>
+      <c r="H67" s="115">
+        <f>IFERROR(G67/E67, 0)</f>
+        <v/>
+      </c>
+      <c r="I67" s="82" t="inlineStr">
+        <is>
+          <t>Елена (мастер-отделочник)</t>
+        </is>
+      </c>
+      <c r="J67" s="82" t="inlineStr">
+        <is>
+          <t>Штукатурка стен санузла по маякам с выведением геометрии под 90° для монтажа ванны (выгода 1 600 ₽)</t>
+        </is>
+      </c>
       <c r="K67" s="140" t="n"/>
       <c r="L67" s="140" t="n"/>
       <c r="M67" s="140" t="n"/>
       <c r="N67" s="140" t="n"/>
     </row>
-    <row r="68">
-      <c r="A68" s="140" t="n"/>
-      <c r="B68" s="140" t="n"/>
-      <c r="C68" s="140" t="n"/>
-      <c r="D68" s="140" t="n"/>
-      <c r="E68" s="140" t="n"/>
-      <c r="F68" s="140" t="n"/>
-      <c r="G68" s="140" t="n"/>
-      <c r="H68" s="140" t="n"/>
-      <c r="I68" s="140" t="n"/>
-      <c r="J68" s="140" t="n"/>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="91" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="91" t="inlineStr">
+        <is>
+          <t>27.09.2026</t>
+        </is>
+      </c>
+      <c r="C68" s="88" t="inlineStr">
+        <is>
+          <t>Сантехника / Материалы</t>
+        </is>
+      </c>
+      <c r="D68" s="88" t="inlineStr">
+        <is>
+          <t>Два крана на радиаторы отопления (запорно-регулировочные краны)</t>
+        </is>
+      </c>
+      <c r="E68" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F68" s="90" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G68" s="85">
+        <f>E68-F68</f>
+        <v/>
+      </c>
+      <c r="H68" s="115">
+        <f>IFERROR(G68/E68, 0)</f>
+        <v/>
+      </c>
+      <c r="I68" s="88" t="inlineStr">
+        <is>
+          <t>Сантехмаркет / Хозмаг</t>
+        </is>
+      </c>
+      <c r="J68" s="88" t="inlineStr">
+        <is>
+          <t>2 крана для радиаторов отопления (замена / обвязка приборов)</t>
+        </is>
+      </c>
       <c r="K68" s="140" t="n"/>
       <c r="L68" s="140" t="n"/>
       <c r="M68" s="140" t="n"/>
       <c r="N68" s="140" t="n"/>
     </row>
-    <row r="69">
-      <c r="A69" s="140" t="n"/>
-      <c r="B69" s="140" t="n"/>
-      <c r="C69" s="140" t="n"/>
-      <c r="D69" s="140" t="n"/>
-      <c r="E69" s="140" t="n"/>
-      <c r="F69" s="140" t="n"/>
-      <c r="G69" s="140" t="n"/>
-      <c r="H69" s="140" t="n"/>
-      <c r="I69" s="140" t="n"/>
-      <c r="J69" s="140" t="n"/>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="238" t="n"/>
+      <c r="B69" s="238" t="n"/>
+      <c r="C69" s="238" t="n"/>
+      <c r="D69" s="239" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДОВ:</t>
+        </is>
+      </c>
+      <c r="E69" s="171">
+        <f>SUM(E5:E68)</f>
+        <v/>
+      </c>
+      <c r="F69" s="171">
+        <f>SUM(F5:F68)</f>
+        <v/>
+      </c>
+      <c r="G69" s="56">
+        <f>SUM(G5:G68)</f>
+        <v/>
+      </c>
+      <c r="H69" s="139">
+        <f>IFERROR(G69/E69, 0)</f>
+        <v/>
+      </c>
+      <c r="I69" s="238" t="n"/>
+      <c r="J69" s="238" t="n"/>
       <c r="K69" s="140" t="n"/>
       <c r="L69" s="140" t="n"/>
       <c r="M69" s="140" t="n"/>
@@ -5621,6 +6101,114 @@
       <c r="L74" s="140" t="n"/>
       <c r="M74" s="140" t="n"/>
       <c r="N74" s="140" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="140" t="n"/>
+      <c r="B75" s="140" t="n"/>
+      <c r="C75" s="140" t="n"/>
+      <c r="D75" s="140" t="n"/>
+      <c r="E75" s="140" t="n"/>
+      <c r="F75" s="140" t="n"/>
+      <c r="G75" s="140" t="n"/>
+      <c r="H75" s="140" t="n"/>
+      <c r="I75" s="140" t="n"/>
+      <c r="J75" s="140" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="140" t="n"/>
+      <c r="B76" s="140" t="n"/>
+      <c r="C76" s="140" t="n"/>
+      <c r="D76" s="140" t="n"/>
+      <c r="E76" s="140" t="n"/>
+      <c r="F76" s="140" t="n"/>
+      <c r="G76" s="140" t="n"/>
+      <c r="H76" s="140" t="n"/>
+      <c r="I76" s="140" t="n"/>
+      <c r="J76" s="140" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="140" t="n"/>
+      <c r="B77" s="140" t="n"/>
+      <c r="C77" s="140" t="n"/>
+      <c r="D77" s="140" t="n"/>
+      <c r="E77" s="140" t="n"/>
+      <c r="F77" s="140" t="n"/>
+      <c r="G77" s="140" t="n"/>
+      <c r="H77" s="140" t="n"/>
+      <c r="I77" s="140" t="n"/>
+      <c r="J77" s="140" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="140" t="n"/>
+      <c r="B78" s="140" t="n"/>
+      <c r="C78" s="140" t="n"/>
+      <c r="D78" s="140" t="n"/>
+      <c r="E78" s="140" t="n"/>
+      <c r="F78" s="140" t="n"/>
+      <c r="G78" s="140" t="n"/>
+      <c r="H78" s="140" t="n"/>
+      <c r="I78" s="140" t="n"/>
+      <c r="J78" s="140" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="140" t="n"/>
+      <c r="B79" s="140" t="n"/>
+      <c r="C79" s="140" t="n"/>
+      <c r="D79" s="140" t="n"/>
+      <c r="E79" s="140" t="n"/>
+      <c r="F79" s="140" t="n"/>
+      <c r="G79" s="140" t="n"/>
+      <c r="H79" s="140" t="n"/>
+      <c r="I79" s="140" t="n"/>
+      <c r="J79" s="140" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="140" t="n"/>
+      <c r="B80" s="140" t="n"/>
+      <c r="C80" s="140" t="n"/>
+      <c r="D80" s="140" t="n"/>
+      <c r="E80" s="140" t="n"/>
+      <c r="F80" s="140" t="n"/>
+      <c r="G80" s="140" t="n"/>
+      <c r="H80" s="140" t="n"/>
+      <c r="I80" s="140" t="n"/>
+      <c r="J80" s="140" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="140" t="n"/>
+      <c r="B81" s="140" t="n"/>
+      <c r="C81" s="140" t="n"/>
+      <c r="D81" s="140" t="n"/>
+      <c r="E81" s="140" t="n"/>
+      <c r="F81" s="140" t="n"/>
+      <c r="G81" s="140" t="n"/>
+      <c r="H81" s="140" t="n"/>
+      <c r="I81" s="140" t="n"/>
+      <c r="J81" s="140" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="140" t="n"/>
+      <c r="B82" s="140" t="n"/>
+      <c r="C82" s="140" t="n"/>
+      <c r="D82" s="140" t="n"/>
+      <c r="E82" s="140" t="n"/>
+      <c r="F82" s="140" t="n"/>
+      <c r="G82" s="140" t="n"/>
+      <c r="H82" s="140" t="n"/>
+      <c r="I82" s="140" t="n"/>
+      <c r="J82" s="140" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="140" t="n"/>
+      <c r="B83" s="140" t="n"/>
+      <c r="C83" s="140" t="n"/>
+      <c r="D83" s="140" t="n"/>
+      <c r="E83" s="140" t="n"/>
+      <c r="F83" s="140" t="n"/>
+      <c r="G83" s="140" t="n"/>
+      <c r="H83" s="140" t="n"/>
+      <c r="I83" s="140" t="n"/>
+      <c r="J83" s="140" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6121,3015 +6709,3738 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
-        <is>
-          <t>ГЕНЕРАЛЬНАЯ МАТРИЦА БЮДЖЕТА И КОМПЛЕКТАЦИИ (423 036,41 ₽)</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
+      <c r="A1" s="240" t="inlineStr">
+        <is>
+          <t>ГЕНЕРАЛЬНАЯ МАТРИЦА БЮДЖЕТА И КОМПЛЕКТАЦИИ (ФРУНЗЕ 17)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Полная структура расходов Фрунзе 17 | Точная сверка с листом «Факт расходов» (1-в-1 до копейки, все 50 позиций)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Полная структура расходов Фрунзе 17 | Точная сверка с листом «Факт расходов» (1-в-1 до копейки, все 64 позиции)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="39" t="inlineStr">
-        <is>
-          <t>💡 Используй слева значки [-] и [+] для сворачивания блоков (Материалы, Работы, Юр. расходы), либо фильтр по Зоне</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="A3" s="241" t="inlineStr">
+        <is>
+          <t>💡 Используй значки [-] и [+] для сворачивания блоков (Материалы, Спецпоставщики, Работы, Юр. расходы)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="162" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>№ в Факте</t>
         </is>
       </c>
-      <c r="B4" s="162" t="inlineStr">
+      <c r="B4" s="81" t="inlineStr">
         <is>
           <t>Зона / Помещение</t>
         </is>
       </c>
-      <c r="C4" s="162" t="inlineStr">
+      <c r="C4" s="81" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="D4" s="162" t="inlineStr">
+      <c r="D4" s="81" t="inlineStr">
         <is>
           <t>Наименование расхода</t>
         </is>
       </c>
-      <c r="E4" s="162" t="inlineStr">
+      <c r="E4" s="81" t="inlineStr">
         <is>
           <t>Артикул / Код</t>
         </is>
       </c>
-      <c r="F4" s="162" t="inlineStr">
+      <c r="F4" s="81" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="G4" s="162" t="inlineStr">
+      <c r="G4" s="81" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="H4" s="162" t="inlineStr">
+      <c r="H4" s="81" t="inlineStr">
         <is>
           <t>Цена / ед. (₽)</t>
         </is>
       </c>
-      <c r="I4" s="162" t="inlineStr">
+      <c r="I4" s="81" t="inlineStr">
         <is>
           <t>Сумма (₽)</t>
         </is>
       </c>
-      <c r="J4" s="162" t="inlineStr">
+      <c r="J4" s="81" t="inlineStr">
         <is>
           <t>Поставщик / Подрядчик</t>
         </is>
       </c>
-      <c r="K4" s="162" t="inlineStr">
+      <c r="K4" s="81" t="inlineStr">
         <is>
           <t>Ссылка / Документ</t>
         </is>
       </c>
-      <c r="L4" s="162" t="inlineStr">
-        <is>
-          <t>Примечание (Фрунзе 17)</t>
+      <c r="L4" s="81" t="inlineStr">
+        <is>
+          <t>Примечание / Назначение</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="205" t="inlineStr"/>
-      <c r="B5" s="205" t="inlineStr">
-        <is>
-          <t>🛁 БЛОК 1: СТРОИТЕЛЬНЫЕ И ЧИСТОВЫЕ МАТЕРИАЛЫ «ЛЕМАНА ПРО» (17 ЧЕКОВ)</t>
-        </is>
-      </c>
-      <c r="C5" s="205" t="inlineStr"/>
-      <c r="D5" s="205" t="inlineStr"/>
-      <c r="E5" s="205" t="inlineStr"/>
-      <c r="F5" s="205" t="inlineStr"/>
-      <c r="G5" s="205" t="inlineStr"/>
-      <c r="H5" s="205" t="inlineStr"/>
-      <c r="I5" s="205" t="inlineStr"/>
-      <c r="J5" s="205" t="inlineStr"/>
-      <c r="K5" s="205" t="inlineStr"/>
-      <c r="L5" s="205" t="inlineStr"/>
-    </row>
-    <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="62" t="n">
+      <c r="A5" s="242" t="n"/>
+      <c r="B5" s="242" t="inlineStr">
+        <is>
+          <t>🛁 БЛОК 1: СТРОИТЕЛЬНЫЕ И ЧИСТОВЫЕ МАТЕРИАЛЫ «ЛЕМАНА ПРО» (23 ЧЕКА)</t>
+        </is>
+      </c>
+      <c r="C5" s="242" t="n"/>
+      <c r="D5" s="242" t="n"/>
+      <c r="E5" s="242" t="n"/>
+      <c r="F5" s="242" t="n"/>
+      <c r="G5" s="242" t="n"/>
+      <c r="H5" s="242" t="n"/>
+      <c r="I5" s="242" t="n"/>
+      <c r="J5" s="242" t="n"/>
+      <c r="K5" s="242" t="n"/>
+      <c r="L5" s="242" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="91" t="n">
         <v>8</v>
       </c>
-      <c r="B6" s="62" t="inlineStr">
+      <c r="B6" s="88" t="inlineStr">
         <is>
           <t>Расходники</t>
         </is>
       </c>
-      <c r="C6" s="62" t="inlineStr">
+      <c r="C6" s="88" t="inlineStr">
         <is>
           <t>Пылесос</t>
         </is>
       </c>
-      <c r="D6" s="44" t="inlineStr">
+      <c r="D6" s="88" t="inlineStr">
         <is>
           <t>Мешки для пылесоса синт. 12л (5 шт) — Леруа/Лемана</t>
         </is>
       </c>
-      <c r="E6" s="62" t="inlineStr">
+      <c r="E6" s="91" t="inlineStr">
         <is>
           <t>4607086338088</t>
         </is>
       </c>
-      <c r="F6" s="62" t="inlineStr">
+      <c r="F6" s="91" t="inlineStr">
         <is>
           <t>упак.</t>
         </is>
       </c>
-      <c r="G6" s="216" t="n">
+      <c r="G6" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="173" t="n">
+      <c r="H6" s="89" t="n">
         <v>717</v>
       </c>
-      <c r="I6" s="217">
+      <c r="I6" s="90">
         <f>G6*H6</f>
         <v/>
       </c>
-      <c r="J6" s="44" t="inlineStr">
+      <c r="J6" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K6" s="174">
+      <c r="K6" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=мешки+для+пылесоса+12л", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L6" s="44" t="inlineStr">
+      <c r="L6" s="88" t="inlineStr">
         <is>
           <t>Чек 3831 от 23.08.2026: Сбор пыли штробления</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="64" t="n">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="86" t="n">
         <v>9</v>
       </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="B7" s="82" t="inlineStr">
         <is>
           <t>Инструмент</t>
         </is>
       </c>
-      <c r="C7" s="64" t="inlineStr">
+      <c r="C7" s="82" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="D7" s="49" t="inlineStr">
+      <c r="D7" s="82" t="inlineStr">
         <is>
           <t>Лом-гвоздодер, мешки 15шт, лента, перчатки 6п, опрыскиватель</t>
         </is>
       </c>
-      <c r="E7" s="64" t="inlineStr">
+      <c r="E7" s="86" t="inlineStr">
         <is>
           <t>4603333000001</t>
         </is>
       </c>
-      <c r="F7" s="64" t="inlineStr">
+      <c r="F7" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G7" s="218" t="n">
+      <c r="G7" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="172" t="n">
+      <c r="H7" s="83" t="n">
         <v>1830</v>
       </c>
-      <c r="I7" s="219">
+      <c r="I7" s="84">
         <f>G7*H7</f>
         <v/>
       </c>
-      <c r="J7" s="49" t="inlineStr">
+      <c r="J7" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K7" s="175">
+      <c r="K7" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=лом+гвоздодер", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L7" s="49" t="inlineStr">
+      <c r="L7" s="82" t="inlineStr">
         <is>
           <t>Чек 3832 от 23.08.2026: Инструмент демонтажа</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="62" t="n">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="91" t="n">
         <v>25</v>
       </c>
-      <c r="B8" s="62" t="inlineStr">
+      <c r="B8" s="88" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C8" s="62" t="inlineStr">
+      <c r="C8" s="88" t="inlineStr">
         <is>
           <t>Шпатлевка / Грунт</t>
         </is>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D8" s="88" t="inlineStr">
         <is>
           <t>Материалы для зачистки и грунтования (шпатлевка 20кг, грунт 10л, СТ99, фильтр Rommer)</t>
         </is>
       </c>
-      <c r="E8" s="62" t="inlineStr">
+      <c r="E8" s="91" t="inlineStr">
         <is>
           <t>3276006224277</t>
         </is>
       </c>
-      <c r="F8" s="62" t="inlineStr">
+      <c r="F8" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G8" s="216" t="n">
+      <c r="G8" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="173" t="n">
+      <c r="H8" s="89" t="n">
         <v>4803.6</v>
       </c>
-      <c r="I8" s="217">
+      <c r="I8" s="90">
         <f>G8*H8</f>
         <v/>
       </c>
-      <c r="J8" s="44" t="inlineStr">
+      <c r="J8" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K8" s="174">
+      <c r="K8" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=грунт+axton+10л", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L8" s="44" t="inlineStr">
+      <c r="L8" s="88" t="inlineStr">
         <is>
           <t>Чек от 30.08.2026: Подготовка стен зала и с/у</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="64" t="n">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="86" t="n">
         <v>26</v>
       </c>
-      <c r="B9" s="64" t="inlineStr">
+      <c r="B9" s="82" t="inlineStr">
         <is>
           <t>Инструмент</t>
         </is>
       </c>
-      <c r="C9" s="64" t="inlineStr">
+      <c r="C9" s="82" t="inlineStr">
         <is>
           <t>Ёмкости</t>
         </is>
       </c>
-      <c r="D9" s="49" t="inlineStr">
+      <c r="D9" s="82" t="inlineStr">
         <is>
           <t>Ведро строительное круглое 20 л (2 шт.)</t>
         </is>
       </c>
-      <c r="E9" s="64" t="inlineStr">
+      <c r="E9" s="86" t="inlineStr">
         <is>
           <t>4610008470475</t>
         </is>
       </c>
-      <c r="F9" s="64" t="inlineStr">
+      <c r="F9" s="86" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G9" s="218" t="n">
+      <c r="G9" s="245" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="172" t="n">
+      <c r="H9" s="83" t="n">
         <v>128</v>
       </c>
-      <c r="I9" s="219">
+      <c r="I9" s="84">
         <f>G9*H9</f>
         <v/>
       </c>
-      <c r="J9" s="49" t="inlineStr">
+      <c r="J9" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K9" s="175">
+      <c r="K9" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=ведро+строительное+20л", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L9" s="49" t="inlineStr">
+      <c r="L9" s="82" t="inlineStr">
         <is>
           <t>Чек от 30.08.2026: Ёмкости для замеса растворов</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="62" t="n">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="91" t="n">
         <v>28</v>
       </c>
-      <c r="B10" s="62" t="inlineStr">
+      <c r="B10" s="88" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C10" s="62" t="inlineStr">
+      <c r="C10" s="88" t="inlineStr">
         <is>
           <t>Шпатлевка / Шпатели</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="88" t="inlineStr">
         <is>
           <t>Материалы для подготовки стен (грунт Axton 10л 4шт, шпатлевка 20кг 2шт, шпатели, мешки)</t>
         </is>
       </c>
-      <c r="E10" s="62" t="inlineStr">
+      <c r="E10" s="91" t="inlineStr">
         <is>
           <t>4601745004252</t>
         </is>
       </c>
-      <c r="F10" s="62" t="inlineStr">
+      <c r="F10" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G10" s="216" t="n">
+      <c r="G10" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="173" t="n">
+      <c r="H10" s="89" t="n">
         <v>3308</v>
       </c>
-      <c r="I10" s="217">
+      <c r="I10" s="90">
         <f>G10*H10</f>
         <v/>
       </c>
-      <c r="J10" s="44" t="inlineStr">
+      <c r="J10" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K10" s="174">
+      <c r="K10" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=шпатлевка+старатели+20кг", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L10" s="44" t="inlineStr">
+      <c r="L10" s="88" t="inlineStr">
         <is>
           <t>Чек от 05.09.2026: Подготовка спальни</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="64" t="n">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="86" t="n">
         <v>30</v>
       </c>
-      <c r="B11" s="64" t="inlineStr">
+      <c r="B11" s="82" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C11" s="64" t="inlineStr">
+      <c r="C11" s="82" t="inlineStr">
         <is>
           <t>Штукатурка / Бетонконтакт</t>
         </is>
       </c>
-      <c r="D11" s="49" t="inlineStr">
+      <c r="D11" s="82" t="inlineStr">
         <is>
           <t>Материалы штукатурки и шпаклёвки (Бетонконтакт 12кг 3шт, финиш 5шт, штукатурка 3шт, правило, углы)</t>
         </is>
       </c>
-      <c r="E11" s="64" t="inlineStr">
+      <c r="E11" s="86" t="inlineStr">
         <is>
           <t>4607017518816</t>
         </is>
       </c>
-      <c r="F11" s="64" t="inlineStr">
+      <c r="F11" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G11" s="218" t="n">
+      <c r="G11" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="172" t="n">
+      <c r="H11" s="83" t="n">
         <v>8162</v>
       </c>
-      <c r="I11" s="219">
+      <c r="I11" s="84">
         <f>G11*H11</f>
         <v/>
       </c>
-      <c r="J11" s="49" t="inlineStr">
+      <c r="J11" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K11" s="175">
+      <c r="K11" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=бетонконтакт+axton+12кг", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L11" s="49" t="inlineStr">
+      <c r="L11" s="82" t="inlineStr">
         <is>
           <t>Чек от 06.09.2026: Основное выравнивание стен</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="62" t="n">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="91" t="n">
         <v>32</v>
       </c>
-      <c r="B12" s="62" t="inlineStr">
+      <c r="B12" s="88" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C12" s="62" t="inlineStr">
+      <c r="C12" s="88" t="inlineStr">
         <is>
           <t>Шпаклёвка</t>
         </is>
       </c>
-      <c r="D12" s="44" t="inlineStr">
+      <c r="D12" s="88" t="inlineStr">
         <is>
           <t>Материалы штукатурки и шпаклёвки (шпатлевка финиш 20кг, штукатурка 30кг 2шт, перчатки)</t>
         </is>
       </c>
-      <c r="E12" s="62" t="inlineStr">
+      <c r="E12" s="91" t="inlineStr">
         <is>
           <t>4601745002814</t>
         </is>
       </c>
-      <c r="F12" s="62" t="inlineStr">
+      <c r="F12" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G12" s="216" t="n">
+      <c r="G12" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="173" t="n">
+      <c r="H12" s="89" t="n">
         <v>1594</v>
       </c>
-      <c r="I12" s="217">
+      <c r="I12" s="90">
         <f>G12*H12</f>
         <v/>
       </c>
-      <c r="J12" s="44" t="inlineStr">
+      <c r="J12" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K12" s="174">
+      <c r="K12" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=шпатлевка+финишная+старатели", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L12" s="44" t="inlineStr">
+      <c r="L12" s="88" t="inlineStr">
         <is>
           <t>Чек от 08.09.2026: Добор смесей на спальню</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="64" t="n">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="86" t="n">
         <v>34</v>
       </c>
-      <c r="B13" s="64" t="inlineStr">
+      <c r="B13" s="82" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C13" s="64" t="inlineStr">
+      <c r="C13" s="82" t="inlineStr">
         <is>
           <t>Санфаянс / Смесители</t>
         </is>
       </c>
-      <c r="D13" s="49" t="inlineStr">
+      <c r="D13" s="82" t="inlineStr">
         <is>
           <t>Сантехника и санфаянс с/у (ванна Нерея 150, каркас Sensea, унитаз Sanita, раковина 60, смесители 2шт, душ, сифон)</t>
         </is>
       </c>
-      <c r="E13" s="64" t="inlineStr">
+      <c r="E13" s="86" t="inlineStr">
         <is>
           <t>4600779023659</t>
         </is>
       </c>
-      <c r="F13" s="64" t="inlineStr">
+      <c r="F13" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G13" s="218" t="n">
+      <c r="G13" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="172" t="n">
+      <c r="H13" s="83" t="n">
         <v>30021</v>
       </c>
-      <c r="I13" s="219">
+      <c r="I13" s="84">
         <f>G13*H13</f>
         <v/>
       </c>
-      <c r="J13" s="49" t="inlineStr">
+      <c r="J13" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K13" s="175">
+      <c r="K13" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4600779023659", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L13" s="49" t="inlineStr">
+      <c r="L13" s="82" t="inlineStr">
         <is>
           <t>Чек от 13.09.2026 (заказ 774): Полный комплект с/у</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="62" t="n">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="91" t="n">
         <v>35</v>
       </c>
-      <c r="B14" s="62" t="inlineStr">
+      <c r="B14" s="88" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C14" s="62" t="inlineStr">
+      <c r="C14" s="88" t="inlineStr">
         <is>
           <t>Керамогранит / Затирка</t>
         </is>
       </c>
-      <c r="D14" s="44" t="inlineStr">
+      <c r="D14" s="88" t="inlineStr">
         <is>
           <t>Керамогранит Calacatta 60х120 (14 упак. / 20.16 м²) + затирка Ceresit CE 40 2кг 2шт</t>
         </is>
       </c>
-      <c r="E14" s="62" t="inlineStr">
+      <c r="E14" s="91" t="inlineStr">
         <is>
           <t>4673766221451</t>
         </is>
       </c>
-      <c r="F14" s="62" t="inlineStr">
+      <c r="F14" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G14" s="216" t="n">
+      <c r="G14" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="173" t="n">
+      <c r="H14" s="89" t="n">
         <v>33457</v>
       </c>
-      <c r="I14" s="217">
+      <c r="I14" s="90">
         <f>G14*H14</f>
         <v/>
       </c>
-      <c r="J14" s="44" t="inlineStr">
+      <c r="J14" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K14" s="174">
+      <c r="K14" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4673766221451", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L14" s="44" t="inlineStr">
+      <c r="L14" s="88" t="inlineStr">
         <is>
           <t>Чек от 13.09.2026 (заказ 774): Плитка на все стены с/у</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="64" t="n">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="86" t="n">
         <v>36</v>
       </c>
-      <c r="B15" s="64" t="inlineStr">
+      <c r="B15" s="82" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C15" s="64" t="inlineStr">
+      <c r="C15" s="82" t="inlineStr">
         <is>
           <t>Плиточный клей</t>
         </is>
       </c>
-      <c r="D15" s="49" t="inlineStr">
+      <c r="D15" s="82" t="inlineStr">
         <is>
           <t>Плиточный клей Unis 2000 C1T 25 кг для формата 60х120 (13 мешков)</t>
         </is>
       </c>
-      <c r="E15" s="64" t="inlineStr">
+      <c r="E15" s="86" t="inlineStr">
         <is>
           <t>4607005180063</t>
         </is>
       </c>
-      <c r="F15" s="64" t="inlineStr">
+      <c r="F15" s="86" t="inlineStr">
         <is>
           <t>мешок</t>
         </is>
       </c>
-      <c r="G15" s="218" t="n">
+      <c r="G15" s="245" t="n">
         <v>13</v>
       </c>
-      <c r="H15" s="172" t="n">
+      <c r="H15" s="83" t="n">
         <v>382.53846</v>
       </c>
-      <c r="I15" s="219">
+      <c r="I15" s="84">
         <f>G15*H15</f>
         <v/>
       </c>
-      <c r="J15" s="49" t="inlineStr">
+      <c r="J15" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4607005180063", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L15" s="49" t="inlineStr">
+      <c r="L15" s="82" t="inlineStr">
         <is>
           <t>Чек от 13.09.2026 (заказ 774): Клей под керамогранит</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="62" t="n">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="91" t="n">
         <v>37</v>
       </c>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="88" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C16" s="62" t="inlineStr">
+      <c r="C16" s="88" t="inlineStr">
         <is>
           <t>СВП</t>
         </is>
       </c>
-      <c r="D16" s="44" t="inlineStr">
+      <c r="D16" s="88" t="inlineStr">
         <is>
           <t>Система выравнивания плитки СВП DILWIS (зажимы 1 мм 200 шт, клинья 100 шт)</t>
         </is>
       </c>
-      <c r="E16" s="62" t="inlineStr">
+      <c r="E16" s="91" t="inlineStr">
         <is>
           <t>4610085150475</t>
         </is>
       </c>
-      <c r="F16" s="62" t="inlineStr">
+      <c r="F16" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G16" s="216" t="n">
+      <c r="G16" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="173" t="n">
+      <c r="H16" s="89" t="n">
         <v>853</v>
       </c>
-      <c r="I16" s="217">
+      <c r="I16" s="90">
         <f>G16*H16</f>
         <v/>
       </c>
-      <c r="J16" s="44" t="inlineStr">
+      <c r="J16" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K16" s="174">
+      <c r="K16" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4610085150475", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L16" s="44" t="inlineStr">
+      <c r="L16" s="88" t="inlineStr">
         <is>
           <t>Чек от 13.09.2026 (заказ 774): Идеальный шов 1 мм</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="64" t="n">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="86" t="n">
         <v>38</v>
       </c>
-      <c r="B17" s="64" t="inlineStr">
+      <c r="B17" s="82" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C17" s="64" t="inlineStr">
+      <c r="C17" s="82" t="inlineStr">
         <is>
           <t>Шпаклёвка</t>
         </is>
       </c>
-      <c r="D17" s="49" t="inlineStr">
+      <c r="D17" s="82" t="inlineStr">
         <is>
           <t>Материалы для штукатурки и шпаклёвки (повторный добор: финиш 20кг, штукатурка 2шт)</t>
         </is>
       </c>
-      <c r="E17" s="64" t="inlineStr">
+      <c r="E17" s="86" t="inlineStr">
         <is>
           <t>4601745000407</t>
         </is>
       </c>
-      <c r="F17" s="64" t="inlineStr">
+      <c r="F17" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G17" s="218" t="n">
+      <c r="G17" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="172" t="n">
+      <c r="H17" s="83" t="n">
         <v>1594</v>
       </c>
-      <c r="I17" s="219">
+      <c r="I17" s="84">
         <f>G17*H17</f>
         <v/>
       </c>
-      <c r="J17" s="49" t="inlineStr">
+      <c r="J17" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K17" s="175">
+      <c r="K17" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=штукатурка+старатели+30кг", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L17" s="49" t="inlineStr">
+      <c r="L17" s="82" t="inlineStr">
         <is>
           <t>Чек от 13.09.2026: Добор смесей на гардероб</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="62" t="n">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="91" t="n">
         <v>39</v>
       </c>
-      <c r="B18" s="62" t="inlineStr">
+      <c r="B18" s="88" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C18" s="62" t="inlineStr">
+      <c r="C18" s="88" t="inlineStr">
         <is>
           <t>Стяжка / Короба</t>
         </is>
       </c>
-      <c r="D18" s="44" t="inlineStr">
+      <c r="D18" s="88" t="inlineStr">
         <is>
           <t>Материалы для стяжки пола и короба с/у (пескобетон М-300 6шт, Knauf 50х40, ГСП 2шт, фибра, саморезы, стамеска)</t>
         </is>
       </c>
-      <c r="E18" s="62" t="inlineStr">
+      <c r="E18" s="91" t="inlineStr">
         <is>
           <t>4610007550932</t>
         </is>
       </c>
-      <c r="F18" s="62" t="inlineStr">
+      <c r="F18" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G18" s="216" t="n">
+      <c r="G18" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="173" t="n">
+      <c r="H18" s="89" t="n">
         <v>3182.67</v>
       </c>
-      <c r="I18" s="217">
+      <c r="I18" s="90">
         <f>G18*H18</f>
         <v/>
       </c>
-      <c r="J18" s="44" t="inlineStr">
+      <c r="J18" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K18" s="174">
+      <c r="K18" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=пескобетон+м300", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L18" s="44" t="inlineStr">
+      <c r="L18" s="88" t="inlineStr">
         <is>
           <t>Чек №201 от 13.09.2026: Стяжка пола и стояк с/у</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="64" t="n">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="86" t="n">
         <v>45</v>
       </c>
-      <c r="B19" s="64" t="inlineStr">
+      <c r="B19" s="82" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C19" s="64" t="inlineStr">
+      <c r="C19" s="82" t="inlineStr">
         <is>
           <t>Черновые стены / Гидроизоляция</t>
         </is>
       </c>
-      <c r="D19" s="49" t="inlineStr">
+      <c r="D19" s="82" t="inlineStr">
         <is>
           <t>Штукатурка Старатели 8шт, гидроизоляция Unis 4кг, люк Fonet 200х250, маяки, профиль, фитинги, рулетки</t>
         </is>
       </c>
-      <c r="E19" s="64" t="inlineStr">
+      <c r="E19" s="86" t="inlineStr">
         <is>
           <t>4601745000407</t>
         </is>
       </c>
-      <c r="F19" s="64" t="inlineStr">
+      <c r="F19" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G19" s="218" t="n">
+      <c r="G19" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="172" t="n">
+      <c r="H19" s="83" t="n">
         <v>7827.6</v>
       </c>
-      <c r="I19" s="219">
+      <c r="I19" s="84">
         <f>G19*H19</f>
         <v/>
       </c>
-      <c r="J19" s="49" t="inlineStr">
+      <c r="J19" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K19" s="175">
+      <c r="K19" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4601745000407", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L19" s="49" t="inlineStr">
+      <c r="L19" s="82" t="inlineStr">
         <is>
           <t>Чек от 20.09.2026 12:03: Выравнивание ванны под 90°, гидроизоляция, люк стояка</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="62" t="n">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="91" t="n">
         <v>46</v>
       </c>
-      <c r="B20" s="62" t="inlineStr">
+      <c r="B20" s="88" t="inlineStr">
         <is>
           <t>Все зоны</t>
         </is>
       </c>
-      <c r="C20" s="62" t="inlineStr">
+      <c r="C20" s="88" t="inlineStr">
         <is>
           <t>Радиаторы / Трубы</t>
         </is>
       </c>
-      <c r="D20" s="44" t="inlineStr">
+      <c r="D20" s="88" t="inlineStr">
         <is>
           <t>Эмаль аэрозольная Luxens белая сатиновая и матовая 520 мл (2 шт.)</t>
         </is>
       </c>
-      <c r="E20" s="62" t="inlineStr">
+      <c r="E20" s="91" t="inlineStr">
         <is>
           <t>3276007227604</t>
         </is>
       </c>
-      <c r="F20" s="62" t="inlineStr">
+      <c r="F20" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G20" s="216" t="n">
+      <c r="G20" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="173" t="n">
+      <c r="H20" s="89" t="n">
         <v>648</v>
       </c>
-      <c r="I20" s="217">
+      <c r="I20" s="90">
         <f>G20*H20</f>
         <v/>
       </c>
-      <c r="J20" s="44" t="inlineStr">
+      <c r="J20" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K20" s="174">
+      <c r="K20" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=3276007227604", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L20" s="44" t="inlineStr">
+      <c r="L20" s="88" t="inlineStr">
         <is>
           <t>Чек №123 от 20.09.2026 12:39: Покраска чугунных радиаторов отопления и труб</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="64" t="n">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="86" t="n">
         <v>47</v>
       </c>
-      <c r="B21" s="64" t="inlineStr">
+      <c r="B21" s="82" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C21" s="64" t="inlineStr">
+      <c r="C21" s="82" t="inlineStr">
         <is>
           <t>Стяжка / Добавки</t>
         </is>
       </c>
-      <c r="D21" s="49" t="inlineStr">
+      <c r="D21" s="82" t="inlineStr">
         <is>
           <t>Ускоритель твердения Cemfix для стяжки пола, 1 литр (добавка в пескобетон М300)</t>
         </is>
       </c>
-      <c r="E21" s="64" t="inlineStr">
+      <c r="E21" s="86" t="inlineStr">
         <is>
           <t>4650068600092</t>
         </is>
       </c>
-      <c r="F21" s="64" t="inlineStr">
+      <c r="F21" s="86" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G21" s="218" t="n">
+      <c r="G21" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="172" t="n">
+      <c r="H21" s="83" t="n">
         <v>262</v>
       </c>
-      <c r="I21" s="219">
+      <c r="I21" s="84">
         <f>G21*H21</f>
         <v/>
       </c>
-      <c r="J21" s="49" t="inlineStr">
+      <c r="J21" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K21" s="175">
+      <c r="K21" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4650068600092", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L21" s="49" t="inlineStr">
+      <c r="L21" s="82" t="inlineStr">
         <is>
           <t>Чек №138 от 20.09.2026 13:02: Ускорение набора прочности стяжки пола с/у</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="62" t="n">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="B22" s="62" t="inlineStr">
+      <c r="B22" s="88" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C22" s="62" t="inlineStr">
+      <c r="C22" s="88" t="inlineStr">
         <is>
           <t>Расходники / Инструмент</t>
         </is>
       </c>
-      <c r="D22" s="44" t="inlineStr">
+      <c r="D22" s="88" t="inlineStr">
         <is>
           <t>Пистолет для герметика скелетный + герметик санитарный силиконовый (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E22" s="62" t="inlineStr">
+      <c r="E22" s="91" t="inlineStr">
         <is>
           <t>82420455</t>
         </is>
       </c>
-      <c r="F22" s="62" t="inlineStr">
+      <c r="F22" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G22" s="216" t="n">
+      <c r="G22" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="173" t="n">
+      <c r="H22" s="89" t="n">
         <v>650</v>
       </c>
-      <c r="I22" s="217">
+      <c r="I22" s="90">
         <f>G22*H22</f>
         <v/>
       </c>
-      <c r="J22" s="44" t="inlineStr">
+      <c r="J22" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K22" s="174">
+      <c r="K22" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=пистолет+для+герметика", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L22" s="44" t="inlineStr">
+      <c r="L22" s="88" t="inlineStr">
         <is>
           <t>Покупка от 21.09.2026: Пистолет и санитарный герметик для ванны и швов</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="234" t="inlineStr"/>
-      <c r="B23" s="234" t="inlineStr">
+      <c r="A23" s="86" t="n">
+        <v>51</v>
+      </c>
+      <c r="B23" s="82" t="inlineStr">
+        <is>
+          <t>Санузел / Стены</t>
+        </is>
+      </c>
+      <c r="C23" s="82" t="inlineStr">
+        <is>
+          <t>Штукатурка / Мешки</t>
+        </is>
+      </c>
+      <c r="D23" s="82" t="inlineStr">
+        <is>
+          <t>Штукатурка гипсовая Старатели 30кг 3шт, перчатки, мешки 3шт (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="E23" s="86" t="inlineStr">
+        <is>
+          <t>4601745000407</t>
+        </is>
+      </c>
+      <c r="F23" s="86" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G23" s="245" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="83" t="n">
+        <v>1638</v>
+      </c>
+      <c r="I23" s="84">
+        <f>G23*H23</f>
+        <v/>
+      </c>
+      <c r="J23" s="82" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K23" s="244">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4601745000407", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L23" s="82" t="inlineStr">
+        <is>
+          <t>Чек от 23.09.2026 15:55: Штукатурка Старатели 3шт (1515₽), перчатки, мешки</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="91" t="n">
+        <v>52</v>
+      </c>
+      <c r="B24" s="88" t="inlineStr">
+        <is>
+          <t>Радиаторы / Стены</t>
+        </is>
+      </c>
+      <c r="C24" s="88" t="inlineStr">
+        <is>
+          <t>Краска / Кисти</t>
+        </is>
+      </c>
+      <c r="D24" s="88" t="inlineStr">
+        <is>
+          <t>Грунт-эмаль Luxens 3в1 белая 2.4кг, щетка металл 5-рядная, кисть Dilwis 70мм</t>
+        </is>
+      </c>
+      <c r="E24" s="91" t="inlineStr">
+        <is>
+          <t>4610088004195</t>
+        </is>
+      </c>
+      <c r="F24" s="91" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G24" s="243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="89" t="n">
+        <v>1769</v>
+      </c>
+      <c r="I24" s="90">
+        <f>G24*H24</f>
+        <v/>
+      </c>
+      <c r="J24" s="88" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K24" s="244">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4610088004195", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L24" s="88" t="inlineStr">
+        <is>
+          <t>Чек от 23.09.2026 16:10: Грунт-эмаль Luxens 3в1 2.4кг (1492₽), кисть, щетка</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="86" t="n">
+        <v>53</v>
+      </c>
+      <c r="B25" s="82" t="inlineStr">
+        <is>
+          <t>Санузел / Короб</t>
+        </is>
+      </c>
+      <c r="C25" s="82" t="inlineStr">
+        <is>
+          <t>Профиль / Саморезы</t>
+        </is>
+      </c>
+      <c r="D25" s="82" t="inlineStr">
+        <is>
+          <t>Профиль ППН 27х28 3шт, профиль ПП 60х27 1шт, саморезы оцинк./фосфат. (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="E25" s="86" t="inlineStr">
+        <is>
+          <t>4600776027292</t>
+        </is>
+      </c>
+      <c r="F25" s="86" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G25" s="245" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="83" t="n">
+        <v>911.7</v>
+      </c>
+      <c r="I25" s="84">
+        <f>G25*H25</f>
+        <v/>
+      </c>
+      <c r="J25" s="82" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K25" s="244">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4600776027292", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L25" s="82" t="inlineStr">
+        <is>
+          <t>Чек от 25.09.2026 08:18: Профили каркаса короба с/у и крепеж</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="91" t="n">
+        <v>54</v>
+      </c>
+      <c r="B26" s="88" t="inlineStr">
+        <is>
+          <t>Санузел / Короб</t>
+        </is>
+      </c>
+      <c r="C26" s="88" t="inlineStr">
+        <is>
+          <t>ГСП / Профиль / Смеси</t>
+        </is>
+      </c>
+      <c r="D26" s="88" t="inlineStr">
+        <is>
+          <t>ГСП-Н3 Knauf влагост. 1500х600х12.5 2шт, штукатурка Старатели 30кг, профили 28х27 2шт, 60х27 1шт</t>
+        </is>
+      </c>
+      <c r="E26" s="91" t="inlineStr">
+        <is>
+          <t>4607160003634</t>
+        </is>
+      </c>
+      <c r="F26" s="91" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G26" s="243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="89" t="n">
+        <v>1582</v>
+      </c>
+      <c r="I26" s="90">
+        <f>G26*H26</f>
+        <v/>
+      </c>
+      <c r="J26" s="88" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K26" s="244">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4607160003634", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L26" s="88" t="inlineStr">
+        <is>
+          <t>Чек от 25.09.2026 15:53: Влагостойкие плиты Knauf для короба с/у, штукатурка</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="86" t="n">
+        <v>55</v>
+      </c>
+      <c r="B27" s="82" t="inlineStr">
+        <is>
+          <t>Полы / Финиш</t>
+        </is>
+      </c>
+      <c r="C27" s="82" t="inlineStr">
+        <is>
+          <t>Ламинат / Плинтус</t>
+        </is>
+      </c>
+      <c r="D27" s="82" t="inlineStr">
+        <is>
+          <t>Ламинат Kronostep Дуб Ночиолла 33кл 10мм 24 упак./41.52м², подложка Monlid 9шт, плинтус белый 8см 20шт</t>
+        </is>
+      </c>
+      <c r="E27" s="86" t="inlineStr">
+        <is>
+          <t>4607113367721</t>
+        </is>
+      </c>
+      <c r="F27" s="86" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G27" s="245" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="83" t="n">
+        <v>41914.52</v>
+      </c>
+      <c r="I27" s="84">
+        <f>G27*H27</f>
+        <v/>
+      </c>
+      <c r="J27" s="82" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K27" s="244">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4607113367721", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L27" s="82" t="inlineStr">
+        <is>
+          <t>Чек от 26.09.2026 17:41: Ламинат 10мм единым контуром, подложка 3мм, плинтус 80мм. Скидка -3637₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="91" t="n">
+        <v>56</v>
+      </c>
+      <c r="B28" s="88" t="inlineStr">
+        <is>
+          <t>Стены / Потолок</t>
+        </is>
+      </c>
+      <c r="C28" s="88" t="inlineStr">
+        <is>
+          <t>Грунт / Клей</t>
+        </is>
+      </c>
+      <c r="D28" s="88" t="inlineStr">
+        <is>
+          <t>Грунт перекрывающий пятна Axton 1л, клей монтажный Kudo 2шт, валик нат. мех, макловица-мини</t>
+        </is>
+      </c>
+      <c r="E28" s="91" t="inlineStr">
+        <is>
+          <t>4690364027858</t>
+        </is>
+      </c>
+      <c r="F28" s="91" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G28" s="243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="89" t="n">
+        <v>1070</v>
+      </c>
+      <c r="I28" s="90">
+        <f>G28*H28</f>
+        <v/>
+      </c>
+      <c r="J28" s="88" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K28" s="244">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4690364027858", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L28" s="88" t="inlineStr">
+        <is>
+          <t>Чек от 26.09.2026 17:40: Блокирующий грунт Axton от старых пятен, клей Kudo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="86" t="n">
+        <v>57</v>
+      </c>
+      <c r="B29" s="82" t="inlineStr">
+        <is>
+          <t>Хознужды / Инструмент</t>
+        </is>
+      </c>
+      <c r="C29" s="82" t="inlineStr">
+        <is>
+          <t>Уборка / Краска</t>
+        </is>
+      </c>
+      <c r="D29" s="82" t="inlineStr">
+        <is>
+          <t>Швабра In Loran, тряпки 3шт, краска Olimp 0.9л, упак. лента Axton, саморезы, ножи 2шт, карандаш</t>
+        </is>
+      </c>
+      <c r="E29" s="86" t="inlineStr">
+        <is>
+          <t>4630085515241</t>
+        </is>
+      </c>
+      <c r="F29" s="86" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G29" s="245" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="83" t="n">
+        <v>1707.17</v>
+      </c>
+      <c r="I29" s="84">
+        <f>G29*H29</f>
+        <v/>
+      </c>
+      <c r="J29" s="82" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K29" s="244">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4630085515241", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L29" s="82" t="inlineStr">
+        <is>
+          <t>Чек от 27.09.2026 09:53: Инструмент для уборки, расходники, краска Olimp</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="246" t="n"/>
+      <c r="B30" s="247" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ ЛЕМАНА ПРО (ПО ЧЕКАМ):</t>
         </is>
       </c>
-      <c r="C23" s="234" t="inlineStr"/>
-      <c r="D23" s="234" t="inlineStr"/>
-      <c r="E23" s="234" t="inlineStr"/>
-      <c r="F23" s="234" t="inlineStr"/>
-      <c r="G23" s="234" t="inlineStr"/>
-      <c r="H23" s="234" t="inlineStr"/>
-      <c r="I23" s="235">
-        <f>SUM(I6:I22)</f>
-        <v/>
-      </c>
-      <c r="J23" s="234" t="inlineStr"/>
-      <c r="K23" s="234" t="inlineStr"/>
-      <c r="L23" s="234" t="inlineStr"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="207" t="inlineStr"/>
-      <c r="B24" s="207" t="inlineStr">
+      <c r="C30" s="246" t="n"/>
+      <c r="D30" s="246" t="n"/>
+      <c r="E30" s="246" t="n"/>
+      <c r="F30" s="246" t="n"/>
+      <c r="G30" s="246" t="n"/>
+      <c r="H30" s="246" t="n"/>
+      <c r="I30" s="248">
+        <f>SUM(I6:I29)</f>
+        <v/>
+      </c>
+      <c r="J30" s="246" t="n"/>
+      <c r="K30" s="246" t="n"/>
+      <c r="L30" s="246" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="249" t="n"/>
+      <c r="B31" s="249" t="inlineStr">
         <is>
           <t>⚡ БЛОК 2: ИНЖЕНЕРНЫЕ МАТЕРИАЛЫ, ДВЕРИ И ОСНАЩЕНИЕ (СПЕЦПОСТАВЩИКИ)</t>
         </is>
       </c>
-      <c r="C24" s="207" t="inlineStr"/>
-      <c r="D24" s="207" t="inlineStr"/>
-      <c r="E24" s="207" t="inlineStr"/>
-      <c r="F24" s="207" t="inlineStr"/>
-      <c r="G24" s="207" t="inlineStr"/>
-      <c r="H24" s="207" t="inlineStr"/>
-      <c r="I24" s="207" t="inlineStr"/>
-      <c r="J24" s="207" t="inlineStr"/>
-      <c r="K24" s="207" t="inlineStr"/>
-      <c r="L24" s="207" t="inlineStr"/>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="64" t="n">
+      <c r="C31" s="249" t="n"/>
+      <c r="D31" s="249" t="n"/>
+      <c r="E31" s="249" t="n"/>
+      <c r="F31" s="249" t="n"/>
+      <c r="G31" s="249" t="n"/>
+      <c r="H31" s="249" t="n"/>
+      <c r="I31" s="249" t="n"/>
+      <c r="J31" s="249" t="n"/>
+      <c r="K31" s="249" t="n"/>
+      <c r="L31" s="249" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="91" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="64" t="inlineStr">
+      <c r="B32" s="88" t="inlineStr">
         <is>
           <t>Расходники</t>
         </is>
       </c>
-      <c r="C25" s="64" t="inlineStr">
+      <c r="C32" s="88" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="D25" s="49" t="inlineStr">
+      <c r="D32" s="88" t="inlineStr">
         <is>
           <t>Мешки мусорные плотные, перчатки рабочие (хозмаг/рынок)</t>
         </is>
       </c>
-      <c r="E25" s="64" t="inlineStr">
+      <c r="E32" s="91" t="inlineStr">
         <is>
           <t>ХОЗМАГ-МЕШКИ</t>
         </is>
       </c>
-      <c r="F25" s="64" t="inlineStr">
+      <c r="F32" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G25" s="218" t="n">
+      <c r="G32" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="172" t="n">
+      <c r="H32" s="89" t="n">
         <v>300</v>
       </c>
-      <c r="I25" s="219">
-        <f>G25*H25</f>
-        <v/>
-      </c>
-      <c r="J25" s="49" t="inlineStr">
+      <c r="I32" s="90">
+        <f>G32*H32</f>
+        <v/>
+      </c>
+      <c r="J32" s="88" t="inlineStr">
         <is>
           <t>Хозмаг / Рынок</t>
         </is>
       </c>
-      <c r="K25" s="175">
+      <c r="K32" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=мешки+мусорные+строительные", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L25" s="49" t="inlineStr">
+      <c r="L32" s="88" t="inlineStr">
         <is>
           <t>Оперативная докупка расходников для демонтажа</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="62" t="n">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="86" t="n">
         <v>11</v>
       </c>
-      <c r="B26" s="62" t="inlineStr">
+      <c r="B33" s="82" t="inlineStr">
         <is>
           <t>Сантехника</t>
         </is>
       </c>
-      <c r="C26" s="62" t="inlineStr">
+      <c r="C33" s="82" t="inlineStr">
         <is>
           <t>Учёт воды</t>
         </is>
       </c>
-      <c r="D26" s="44" t="inlineStr">
+      <c r="D33" s="82" t="inlineStr">
         <is>
           <t>Счётчик горячей/холодной воды + кран на ввод (материалы)</t>
         </is>
       </c>
-      <c r="E26" s="62" t="inlineStr">
+      <c r="E33" s="86" t="inlineStr">
         <is>
           <t>СЧЕТЧИК-ВОДЫ</t>
         </is>
       </c>
-      <c r="F26" s="62" t="inlineStr">
+      <c r="F33" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G26" s="216" t="n">
+      <c r="G33" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="173" t="n">
+      <c r="H33" s="83" t="n">
         <v>2100</v>
       </c>
-      <c r="I26" s="217">
-        <f>G26*H26</f>
-        <v/>
-      </c>
-      <c r="J26" s="44" t="inlineStr">
+      <c r="I33" s="84">
+        <f>G33*H33</f>
+        <v/>
+      </c>
+      <c r="J33" s="82" t="inlineStr">
         <is>
           <t>Вадим (сантехник УК)</t>
         </is>
       </c>
-      <c r="K26" s="174">
+      <c r="K33" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=счетчик+воды+универсальный", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L26" s="44" t="inlineStr">
+      <c r="L33" s="82" t="inlineStr">
         <is>
           <t>Замена вводных узлов и прибора учёта</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="64" t="n">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="91" t="n">
         <v>14</v>
       </c>
-      <c r="B27" s="64" t="inlineStr">
+      <c r="B34" s="88" t="inlineStr">
         <is>
           <t>Сантехника</t>
         </is>
       </c>
-      <c r="C27" s="64" t="inlineStr">
+      <c r="C34" s="88" t="inlineStr">
         <is>
           <t>Учёт воды</t>
         </is>
       </c>
-      <c r="D27" s="49" t="inlineStr">
+      <c r="D34" s="88" t="inlineStr">
         <is>
           <t>Покупка и установка счётчика и кранов (доплата за фитинги и муфты)</t>
         </is>
       </c>
-      <c r="E27" s="64" t="inlineStr">
+      <c r="E34" s="91" t="inlineStr">
         <is>
           <t>ФИТИНГИ-САНТЕХ</t>
         </is>
       </c>
-      <c r="F27" s="64" t="inlineStr">
+      <c r="F34" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G27" s="218" t="n">
+      <c r="G34" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="172" t="n">
+      <c r="H34" s="89" t="n">
         <v>2000</v>
       </c>
-      <c r="I27" s="219">
-        <f>G27*H27</f>
-        <v/>
-      </c>
-      <c r="J27" s="49" t="inlineStr">
+      <c r="I34" s="90">
+        <f>G34*H34</f>
+        <v/>
+      </c>
+      <c r="J34" s="88" t="inlineStr">
         <is>
           <t>Вадим (сантехник УК)</t>
         </is>
       </c>
-      <c r="K27" s="175">
+      <c r="K34" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=шаровый+кран+1/2", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L27" s="49" t="inlineStr">
+      <c r="L34" s="88" t="inlineStr">
         <is>
           <t>Латунные фитинги, муфты, уплотнители</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="62" t="n">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="86" t="n">
         <v>15</v>
       </c>
-      <c r="B28" s="62" t="inlineStr">
+      <c r="B35" s="82" t="inlineStr">
         <is>
           <t>Входная группа</t>
         </is>
       </c>
-      <c r="C28" s="62" t="inlineStr">
+      <c r="C35" s="82" t="inlineStr">
         <is>
           <t>Двери</t>
         </is>
       </c>
-      <c r="D28" s="44" t="inlineStr">
+      <c r="D35" s="82" t="inlineStr">
         <is>
           <t>Покупка входной металлической двери с внутренней МДФ-панелью</t>
         </is>
       </c>
-      <c r="E28" s="62" t="inlineStr">
+      <c r="E35" s="86" t="inlineStr">
         <is>
           <t>ДВЕРЬ-ВХОД-МДФ</t>
         </is>
       </c>
-      <c r="F28" s="62" t="inlineStr">
+      <c r="F35" s="86" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G28" s="216" t="n">
+      <c r="G35" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="173" t="n">
+      <c r="H35" s="83" t="n">
         <v>16000</v>
       </c>
-      <c r="I28" s="217">
-        <f>G28*H28</f>
-        <v/>
-      </c>
-      <c r="J28" s="44" t="inlineStr">
+      <c r="I35" s="84">
+        <f>G35*H35</f>
+        <v/>
+      </c>
+      <c r="J35" s="82" t="inlineStr">
         <is>
           <t>Владимир (двери)</t>
         </is>
       </c>
-      <c r="K28" s="174">
+      <c r="K35" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=входная+металлическая+дверь+мдф", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L28" s="44" t="inlineStr">
+      <c r="L35" s="82" t="inlineStr">
         <is>
           <t>Металл 1.5 мм, МДФ-панель, надежные замки</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="64" t="n">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="91" t="n">
         <v>16</v>
       </c>
-      <c r="B29" s="64" t="inlineStr">
+      <c r="B36" s="88" t="inlineStr">
         <is>
           <t>Входная группа</t>
         </is>
       </c>
-      <c r="C29" s="64" t="inlineStr">
+      <c r="C36" s="88" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="D29" s="49" t="inlineStr">
+      <c r="D36" s="88" t="inlineStr">
         <is>
           <t>Доставка входной металлической двери на объект</t>
         </is>
       </c>
-      <c r="E29" s="64" t="inlineStr">
+      <c r="E36" s="91" t="inlineStr">
         <is>
           <t>ДОСТАВКА-ДВЕРЬ</t>
         </is>
       </c>
-      <c r="F29" s="64" t="inlineStr">
+      <c r="F36" s="91" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G29" s="218" t="n">
+      <c r="G36" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="172" t="n">
+      <c r="H36" s="89" t="n">
         <v>1500</v>
       </c>
-      <c r="I29" s="219">
-        <f>G29*H29</f>
-        <v/>
-      </c>
-      <c r="J29" s="49" t="inlineStr">
+      <c r="I36" s="90">
+        <f>G36*H36</f>
+        <v/>
+      </c>
+      <c r="J36" s="88" t="inlineStr">
         <is>
           <t>Владимир / Доставка</t>
         </is>
       </c>
-      <c r="K29" s="175">
+      <c r="K36" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=доставка+дверей+грузоперевозки", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L29" s="49" t="inlineStr">
+      <c r="L36" s="88" t="inlineStr">
         <is>
           <t>Транспортировка двери на ул. Фрунзе 17</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="62" t="n">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="86" t="n">
         <v>17</v>
       </c>
-      <c r="B30" s="62" t="inlineStr">
+      <c r="B37" s="82" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C30" s="62" t="inlineStr">
+      <c r="C37" s="82" t="inlineStr">
         <is>
           <t>Щит / Автоматика</t>
         </is>
       </c>
-      <c r="D30" s="44" t="inlineStr">
+      <c r="D37" s="82" t="inlineStr">
         <is>
           <t>Черновые материалы электрики (щит 18м, новый электросчётчик, автоматы, УЗО, гофра)</t>
         </is>
       </c>
-      <c r="E30" s="62" t="inlineStr">
+      <c r="E37" s="86" t="inlineStr">
         <is>
           <t>ЩИТ-АВТ-КОМПЛЕКТ</t>
         </is>
       </c>
-      <c r="F30" s="62" t="inlineStr">
+      <c r="F37" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G30" s="216" t="n">
+      <c r="G37" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="173" t="n">
+      <c r="H37" s="83" t="n">
         <v>16500</v>
       </c>
-      <c r="I30" s="217">
-        <f>G30*H30</f>
-        <v/>
-      </c>
-      <c r="J30" s="44" t="inlineStr">
+      <c r="I37" s="84">
+        <f>G37*H37</f>
+        <v/>
+      </c>
+      <c r="J37" s="82" t="inlineStr">
         <is>
           <t>Анатолий / Поставщик</t>
         </is>
       </c>
-      <c r="K30" s="174">
+      <c r="K37" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=щит+встраиваемый+18+модулей", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L30" s="44" t="inlineStr">
+      <c r="L37" s="82" t="inlineStr">
         <is>
           <t>Комплектная начинка щита и прибор учёта</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="64" t="n">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="91" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="64" t="inlineStr">
+      <c r="B38" s="88" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C31" s="64" t="inlineStr">
+      <c r="C38" s="88" t="inlineStr">
         <is>
           <t>Кабель</t>
         </is>
       </c>
-      <c r="D31" s="49" t="inlineStr">
+      <c r="D38" s="88" t="inlineStr">
         <is>
           <t>Кабель силовой ВВГнг-LS (ГОСТ 3х2.5 и 3х1.5 для всех трасс)</t>
         </is>
       </c>
-      <c r="E31" s="64" t="inlineStr">
+      <c r="E38" s="91" t="inlineStr">
         <is>
           <t>ВВГнг-LS-ГОСТ-1</t>
         </is>
       </c>
-      <c r="F31" s="64" t="inlineStr">
+      <c r="F38" s="91" t="inlineStr">
         <is>
           <t>бухта</t>
         </is>
       </c>
-      <c r="G31" s="218" t="n">
+      <c r="G38" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="172" t="n">
+      <c r="H38" s="89" t="n">
         <v>18000</v>
       </c>
-      <c r="I31" s="219">
-        <f>G31*H31</f>
-        <v/>
-      </c>
-      <c r="J31" s="49" t="inlineStr">
+      <c r="I38" s="90">
+        <f>G38*H38</f>
+        <v/>
+      </c>
+      <c r="J38" s="88" t="inlineStr">
         <is>
           <t>Электромонтаж / Поставщик</t>
         </is>
       </c>
-      <c r="K31" s="175">
+      <c r="K38" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=кабель+ВВГнг-LS+3х2.5", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L31" s="49" t="inlineStr">
+      <c r="L38" s="88" t="inlineStr">
         <is>
           <t>Силовой кабель ГОСТ под розетки и свет</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="62" t="n">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="86" t="n">
         <v>20</v>
       </c>
-      <c r="B32" s="62" t="inlineStr">
+      <c r="B39" s="82" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C32" s="62" t="inlineStr">
+      <c r="C39" s="82" t="inlineStr">
         <is>
           <t>Крепёж</t>
         </is>
       </c>
-      <c r="D32" s="44" t="inlineStr">
+      <c r="D39" s="82" t="inlineStr">
         <is>
           <t>Стяжки нейлоновые и крепёж для монтажа кабеля</t>
         </is>
       </c>
-      <c r="E32" s="62" t="inlineStr">
+      <c r="E39" s="86" t="inlineStr">
         <is>
           <t>КРЕПЕЖ-КАБЕЛЬ</t>
         </is>
       </c>
-      <c r="F32" s="62" t="inlineStr">
+      <c r="F39" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G32" s="216" t="n">
+      <c r="G39" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="173" t="n">
+      <c r="H39" s="83" t="n">
         <v>1000</v>
       </c>
-      <c r="I32" s="217">
-        <f>G32*H32</f>
-        <v/>
-      </c>
-      <c r="J32" s="44" t="inlineStr">
+      <c r="I39" s="84">
+        <f>G39*H39</f>
+        <v/>
+      </c>
+      <c r="J39" s="82" t="inlineStr">
         <is>
           <t>Хозмаг / Электромонтаж</t>
         </is>
       </c>
-      <c r="K32" s="174">
+      <c r="K39" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=дюбель+хомут+для+кабеля", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L32" s="44" t="inlineStr">
+      <c r="L39" s="82" t="inlineStr">
         <is>
           <t>Дюбель-хомуты и стяжки для трасс</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="64" t="n">
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="91" t="n">
         <v>23</v>
       </c>
-      <c r="B33" s="64" t="inlineStr">
+      <c r="B40" s="88" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C33" s="64" t="inlineStr">
+      <c r="C40" s="88" t="inlineStr">
         <is>
           <t>Кабель</t>
         </is>
       </c>
-      <c r="D33" s="49" t="inlineStr">
+      <c r="D40" s="88" t="inlineStr">
         <is>
           <t>Докупка силового кабеля ВВГнг-LS (дополнительный метраж трасс)</t>
         </is>
       </c>
-      <c r="E33" s="64" t="inlineStr">
+      <c r="E40" s="91" t="inlineStr">
         <is>
           <t>ВВГнг-LS-ГОСТ-2</t>
         </is>
       </c>
-      <c r="F33" s="64" t="inlineStr">
+      <c r="F40" s="91" t="inlineStr">
         <is>
           <t>бухта</t>
         </is>
       </c>
-      <c r="G33" s="218" t="n">
+      <c r="G40" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="172" t="n">
+      <c r="H40" s="89" t="n">
         <v>13000</v>
       </c>
-      <c r="I33" s="219">
-        <f>G33*H33</f>
-        <v/>
-      </c>
-      <c r="J33" s="49" t="inlineStr">
+      <c r="I40" s="90">
+        <f>G40*H40</f>
+        <v/>
+      </c>
+      <c r="J40" s="88" t="inlineStr">
         <is>
           <t>Электромонтаж / Поставщик</t>
         </is>
       </c>
-      <c r="K33" s="175">
+      <c r="K40" s="244">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=кабель+ВВГнг-LS+3х1.5", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L33" s="49" t="inlineStr">
+      <c r="L40" s="88" t="inlineStr">
         <is>
           <t>Дополнительный кабель на трассы кухни и коридора</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="62" t="n">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="86" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="62" t="inlineStr">
+      <c r="B41" s="82" t="inlineStr">
         <is>
           <t>Оснащение</t>
         </is>
       </c>
-      <c r="C34" s="62" t="inlineStr">
+      <c r="C41" s="82" t="inlineStr">
         <is>
           <t>Инвентарь</t>
         </is>
       </c>
-      <c r="D34" s="44" t="inlineStr">
+      <c r="D41" s="82" t="inlineStr">
         <is>
           <t>Портативная акустика Xiaomi Bluetooth Speaker Essential Green</t>
         </is>
       </c>
-      <c r="E34" s="62" t="inlineStr">
+      <c r="E41" s="86" t="inlineStr">
         <is>
           <t>XIAOMI-SPK-ESS</t>
         </is>
       </c>
-      <c r="F34" s="62" t="inlineStr">
+      <c r="F41" s="86" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G34" s="216" t="n">
+      <c r="G41" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="173" t="n">
+      <c r="H41" s="83" t="n">
         <v>1250</v>
       </c>
-      <c r="I34" s="217">
-        <f>G34*H34</f>
-        <v/>
-      </c>
-      <c r="J34" s="44" t="inlineStr">
+      <c r="I41" s="84">
+        <f>G41*H41</f>
+        <v/>
+      </c>
+      <c r="J41" s="82" t="inlineStr">
         <is>
           <t>ООО ДНС Ритейл (DNS)</t>
         </is>
       </c>
-      <c r="K34" s="174">
+      <c r="K41" s="244">
         <f>HYPERLINK("https://www.dns-shop.ru/search/?q=Xiaomi+Bluetooth+Speaker", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L34" s="44" t="inlineStr">
+      <c r="L41" s="82" t="inlineStr">
         <is>
           <t>Акустическое оснащение объекта для бригад</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="64" t="n">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="91" t="n">
         <v>29</v>
       </c>
-      <c r="B35" s="64" t="inlineStr">
+      <c r="B42" s="88" t="inlineStr">
         <is>
           <t>Оснащение</t>
         </is>
       </c>
-      <c r="C35" s="64" t="inlineStr">
+      <c r="C42" s="88" t="inlineStr">
         <is>
           <t>Хознужды</t>
         </is>
       </c>
-      <c r="D35" s="49" t="inlineStr">
+      <c r="D42" s="88" t="inlineStr">
         <is>
           <t>Хозрасходы на объект: салфетки влажные и питьевая вода для мастеров</t>
         </is>
       </c>
-      <c r="E35" s="64" t="inlineStr">
+      <c r="E42" s="91" t="inlineStr">
         <is>
           <t>ХОЗ-ВОДА-САЛФЕТКИ</t>
         </is>
       </c>
-      <c r="F35" s="64" t="inlineStr">
+      <c r="F42" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G35" s="218" t="n">
+      <c r="G42" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="172" t="n">
+      <c r="H42" s="89" t="n">
         <v>520</v>
       </c>
-      <c r="I35" s="219">
-        <f>G35*H35</f>
-        <v/>
-      </c>
-      <c r="J35" s="49" t="inlineStr">
+      <c r="I42" s="90">
+        <f>G42*H42</f>
+        <v/>
+      </c>
+      <c r="J42" s="88" t="inlineStr">
         <is>
           <t>Хозмаг / Продукты</t>
         </is>
       </c>
-      <c r="K35" s="175">
+      <c r="K42" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/produkty_pitaniya?q=питьевая+вода+19л", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L35" s="49" t="inlineStr">
+      <c r="L42" s="88" t="inlineStr">
         <is>
           <t>Бытовое снабжение объекта</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="62" t="n">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="86" t="n">
         <v>43</v>
       </c>
-      <c r="B36" s="62" t="inlineStr">
+      <c r="B43" s="82" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C36" s="62" t="inlineStr">
+      <c r="C43" s="82" t="inlineStr">
         <is>
           <t>Канализация</t>
         </is>
       </c>
-      <c r="D36" s="44" t="inlineStr">
+      <c r="D43" s="82" t="inlineStr">
         <is>
           <t>Канализация с/у (муфта-восстановитель раструба 110/110, трубы ПП 50, тройник 110/50, заглушка, отводы)</t>
         </is>
       </c>
-      <c r="E36" s="62" t="inlineStr">
+      <c r="E43" s="86" t="inlineStr">
         <is>
           <t>КАНАЛ-СУ-110-50</t>
         </is>
       </c>
-      <c r="F36" s="62" t="inlineStr">
+      <c r="F43" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G36" s="216" t="n">
+      <c r="G43" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="173" t="n">
+      <c r="H43" s="83" t="n">
         <v>2988</v>
       </c>
-      <c r="I36" s="217">
-        <f>G36*H36</f>
-        <v/>
-      </c>
-      <c r="J36" s="44" t="inlineStr">
+      <c r="I43" s="84">
+        <f>G43*H43</f>
+        <v/>
+      </c>
+      <c r="J43" s="82" t="inlineStr">
         <is>
           <t>ИП Кучеров М.И. (Полимерстрой)</t>
         </is>
       </c>
-      <c r="K36" s="174">
+      <c r="K43" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=восстановитель+раструба+110", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L36" s="44" t="inlineStr">
+      <c r="L43" s="82" t="inlineStr">
         <is>
           <t>Чек от 15.09.2026: Муфта-восстановитель 110/110, разводка труб под ванну, раковину, унитаз</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="64" t="n">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="91" t="n">
         <v>44</v>
       </c>
-      <c r="B37" s="64" t="inlineStr">
+      <c r="B44" s="88" t="inlineStr">
         <is>
           <t>Санузел / Кухня</t>
         </is>
       </c>
-      <c r="C37" s="64" t="inlineStr">
+      <c r="C44" s="88" t="inlineStr">
         <is>
           <t>Водоснабжение</t>
         </is>
       </c>
-      <c r="D37" s="49" t="inlineStr">
+      <c r="D44" s="88" t="inlineStr">
         <is>
           <t>Трубы армированные Faser 20х2.8 12м, настенная планка смесителя, кран DN15, муфты, клипсы</t>
         </is>
       </c>
-      <c r="E37" s="64" t="inlineStr">
+      <c r="E44" s="91" t="inlineStr">
         <is>
           <t>PPR-FASER-WATSON</t>
         </is>
       </c>
-      <c r="F37" s="64" t="inlineStr">
+      <c r="F44" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G37" s="218" t="n">
+      <c r="G44" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="172" t="n">
+      <c r="H44" s="89" t="n">
         <v>3139.54</v>
       </c>
-      <c r="I37" s="219">
-        <f>G37*H37</f>
-        <v/>
-      </c>
-      <c r="J37" s="49" t="inlineStr">
+      <c r="I44" s="90">
+        <f>G44*H44</f>
+        <v/>
+      </c>
+      <c r="J44" s="88" t="inlineStr">
         <is>
           <t>ТС «Ваттсон» (Центргазсервис)</t>
         </is>
       </c>
-      <c r="K37" s="175">
+      <c r="K44" s="244">
         <f>HYPERLINK("https://wattson.ru/search/?q=Faser+20", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L37" s="49" t="inlineStr">
+      <c r="L44" s="88" t="inlineStr">
         <is>
           <t>Чек №23 от 19.09.2026: Разводка труб ХВС/ГВС, шаровой кран ввода, планка под смеситель ванны</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="234" t="inlineStr"/>
-      <c r="B38" s="234" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="86" t="n">
+        <v>58</v>
+      </c>
+      <c r="B45" s="82" t="inlineStr">
+        <is>
+          <t>Электрика</t>
+        </is>
+      </c>
+      <c r="C45" s="82" t="inlineStr">
+        <is>
+          <t>Материалы / Розетки</t>
+        </is>
+      </c>
+      <c r="D45" s="82" t="inlineStr">
+        <is>
+          <t>Электротовары (комплектующие/расходники электрики, ул. Коминтерна 26)</t>
+        </is>
+      </c>
+      <c r="E45" s="86" t="inlineStr">
+        <is>
+          <t>ЭЛЕКТРО-КОМИНТЕРНА</t>
+        </is>
+      </c>
+      <c r="F45" s="86" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G45" s="245" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="83" t="n">
+        <v>190</v>
+      </c>
+      <c r="I45" s="84">
+        <f>G45*H45</f>
+        <v/>
+      </c>
+      <c r="J45" s="82" t="inlineStr">
+        <is>
+          <t>Магазин «Электротовары»</t>
+        </is>
+      </c>
+      <c r="K45" s="244">
+        <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=электротовары+коминтерна", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L45" s="82" t="inlineStr">
+        <is>
+          <t>Слип от 27.09.2026 13:08: расходники для электрики</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="91" t="n">
+        <v>59</v>
+      </c>
+      <c r="B46" s="88" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C46" s="88" t="inlineStr">
+        <is>
+          <t>СВП / Клинья</t>
+        </is>
+      </c>
+      <c r="D46" s="88" t="inlineStr">
+        <is>
+          <t>Клинья для плитки СВП 32х8х9мм 50шт (Магазин крепежа, ул. Мосина 29)</t>
+        </is>
+      </c>
+      <c r="E46" s="91" t="inlineStr">
+        <is>
+          <t>СВП-КЛИНЬЯ-50</t>
+        </is>
+      </c>
+      <c r="F46" s="91" t="inlineStr">
+        <is>
+          <t>упак.</t>
+        </is>
+      </c>
+      <c r="G46" s="243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="89" t="n">
+        <v>210</v>
+      </c>
+      <c r="I46" s="90">
+        <f>G46*H46</f>
+        <v/>
+      </c>
+      <c r="J46" s="88" t="inlineStr">
+        <is>
+          <t>ИП Звягинцева С.Н. (Крепеж)</t>
+        </is>
+      </c>
+      <c r="K46" s="244">
+        <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=клинья+для+плитки+свп", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L46" s="88" t="inlineStr">
+        <is>
+          <t>Чек от 27.09.2026 13:23: клинья для укладки плитки</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="86" t="n">
+        <v>64</v>
+      </c>
+      <c r="B47" s="82" t="inlineStr">
+        <is>
+          <t>Отопление</t>
+        </is>
+      </c>
+      <c r="C47" s="82" t="inlineStr">
+        <is>
+          <t>Краны радиаторов</t>
+        </is>
+      </c>
+      <c r="D47" s="82" t="inlineStr">
+        <is>
+          <t>Два крана на радиаторы отопления (запорно-регулировочные краны)</t>
+        </is>
+      </c>
+      <c r="E47" s="86" t="inlineStr">
+        <is>
+          <t>КРАНЫ-РАДИАТОР-2</t>
+        </is>
+      </c>
+      <c r="F47" s="86" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G47" s="245" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="83" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I47" s="84">
+        <f>G47*H47</f>
+        <v/>
+      </c>
+      <c r="J47" s="82" t="inlineStr">
+        <is>
+          <t>Сантехмаркет / Хозмаг</t>
+        </is>
+      </c>
+      <c r="K47" s="244">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=кран+для+радиатора+отопления", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L47" s="82" t="inlineStr">
+        <is>
+          <t>Запорно-регулировочные краны на батареи отопления</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="246" t="n"/>
+      <c r="B48" s="247" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ СПЕЦПОСТАВЩИКОВ:</t>
         </is>
       </c>
-      <c r="C38" s="234" t="inlineStr"/>
-      <c r="D38" s="234" t="inlineStr"/>
-      <c r="E38" s="234" t="inlineStr"/>
-      <c r="F38" s="234" t="inlineStr"/>
-      <c r="G38" s="234" t="inlineStr"/>
-      <c r="H38" s="234" t="inlineStr"/>
-      <c r="I38" s="235">
-        <f>SUM(I25:I37)</f>
-        <v/>
-      </c>
-      <c r="J38" s="234" t="inlineStr"/>
-      <c r="K38" s="234" t="inlineStr"/>
-      <c r="L38" s="234" t="inlineStr"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="208" t="inlineStr"/>
-      <c r="B39" s="208" t="inlineStr">
-        <is>
-          <t>👷‍♂️ БЛОК 3: РАБОТЫ МАСТЕРОВ, ОТДЕЛКА, ДЕМОНТАЖ И ЛОГИСТИКА</t>
-        </is>
-      </c>
-      <c r="C39" s="208" t="inlineStr"/>
-      <c r="D39" s="208" t="inlineStr"/>
-      <c r="E39" s="208" t="inlineStr"/>
-      <c r="F39" s="208" t="inlineStr"/>
-      <c r="G39" s="208" t="inlineStr"/>
-      <c r="H39" s="208" t="inlineStr"/>
-      <c r="I39" s="208" t="inlineStr"/>
-      <c r="J39" s="208" t="inlineStr"/>
-      <c r="K39" s="208" t="inlineStr"/>
-      <c r="L39" s="208" t="inlineStr"/>
-    </row>
-    <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="62" t="n">
+      <c r="C48" s="246" t="n"/>
+      <c r="D48" s="246" t="n"/>
+      <c r="E48" s="246" t="n"/>
+      <c r="F48" s="246" t="n"/>
+      <c r="G48" s="246" t="n"/>
+      <c r="H48" s="246" t="n"/>
+      <c r="I48" s="248">
+        <f>SUM(I32:I47)</f>
+        <v/>
+      </c>
+      <c r="J48" s="246" t="n"/>
+      <c r="K48" s="246" t="n"/>
+      <c r="L48" s="246" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="250" t="n"/>
+      <c r="B49" s="250" t="inlineStr">
+        <is>
+          <t>👷‍♂️ БЛОК 3: РАБОТЫ МАСТЕРОВ, ОТДЕЛКА, ДЕМОНТАЖ И ЛОГИСТИКА (16 ПОЗИЦИЙ)</t>
+        </is>
+      </c>
+      <c r="C49" s="250" t="n"/>
+      <c r="D49" s="250" t="n"/>
+      <c r="E49" s="250" t="n"/>
+      <c r="F49" s="250" t="n"/>
+      <c r="G49" s="250" t="n"/>
+      <c r="H49" s="250" t="n"/>
+      <c r="I49" s="250" t="n"/>
+      <c r="J49" s="250" t="n"/>
+      <c r="K49" s="250" t="n"/>
+      <c r="L49" s="250" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="91" t="n">
         <v>3</v>
       </c>
-      <c r="B40" s="62" t="inlineStr">
+      <c r="B50" s="88" t="inlineStr">
         <is>
           <t>Безопасность</t>
         </is>
       </c>
-      <c r="C40" s="62" t="inlineStr">
+      <c r="C50" s="88" t="inlineStr">
         <is>
           <t>Вскрытие</t>
         </is>
       </c>
-      <c r="D40" s="44" t="inlineStr">
+      <c r="D50" s="88" t="inlineStr">
         <is>
           <t>Вскрытие старого замка и обеспечение первого доступа</t>
         </is>
       </c>
-      <c r="E40" s="62" t="inlineStr">
+      <c r="E50" s="91" t="inlineStr">
         <is>
           <t>ВСКРЫТИЕ-ЗАМКА</t>
         </is>
       </c>
-      <c r="F40" s="62" t="inlineStr">
+      <c r="F50" s="91" t="inlineStr">
         <is>
           <t>выезд</t>
         </is>
       </c>
-      <c r="G40" s="216" t="n">
+      <c r="G50" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="173" t="n">
+      <c r="H50" s="89" t="n">
         <v>8000</v>
       </c>
-      <c r="I40" s="217">
-        <f>G40*H40</f>
-        <v/>
-      </c>
-      <c r="J40" s="44" t="inlineStr">
+      <c r="I50" s="90">
+        <f>G50*H50</f>
+        <v/>
+      </c>
+      <c r="J50" s="88" t="inlineStr">
         <is>
           <t>Служба вскрытия</t>
         </is>
       </c>
-      <c r="K40" s="174">
+      <c r="K50" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=вскрытие+замков", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L40" s="44" t="inlineStr">
+      <c r="L50" s="88" t="inlineStr">
         <is>
           <t>Аварийное открытие двери после торгов</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="64" t="n">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="B41" s="64" t="inlineStr">
+      <c r="B51" s="82" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C41" s="64" t="inlineStr">
+      <c r="C51" s="82" t="inlineStr">
         <is>
           <t>Вывоз мусора</t>
         </is>
       </c>
-      <c r="D41" s="49" t="inlineStr">
+      <c r="D51" s="82" t="inlineStr">
         <is>
           <t>Заказ мусорного контейнера 8 м³ (лодочка)</t>
         </is>
       </c>
-      <c r="E41" s="64" t="inlineStr">
+      <c r="E51" s="86" t="inlineStr">
         <is>
           <t>КОНТЕЙНЕР-МУСОР-8М3</t>
         </is>
       </c>
-      <c r="F41" s="64" t="inlineStr">
+      <c r="F51" s="86" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G41" s="218" t="n">
+      <c r="G51" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="172" t="n">
+      <c r="H51" s="83" t="n">
         <v>8500</v>
       </c>
-      <c r="I41" s="219">
-        <f>G41*H41</f>
-        <v/>
-      </c>
-      <c r="J41" s="49" t="inlineStr">
+      <c r="I51" s="84">
+        <f>G51*H51</f>
+        <v/>
+      </c>
+      <c r="J51" s="82" t="inlineStr">
         <is>
           <t>Елена (вывоз мусора)</t>
         </is>
       </c>
-      <c r="K41" s="175">
+      <c r="K51" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=вывоз+мусора+контейнер+8+м3", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L41" s="49" t="inlineStr">
+      <c r="L51" s="82" t="inlineStr">
         <is>
           <t>Вывоз мебели, санузла, чугуна, досок</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="19" customHeight="1">
-      <c r="A42" s="62" t="n">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="91" t="n">
         <v>5</v>
       </c>
-      <c r="B42" s="62" t="inlineStr">
+      <c r="B52" s="88" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C42" s="62" t="inlineStr">
+      <c r="C52" s="88" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
-      <c r="D42" s="44" t="inlineStr">
+      <c r="D52" s="88" t="inlineStr">
         <is>
           <t>Аренда инструмента и помощь соседа по дому</t>
         </is>
       </c>
-      <c r="E42" s="62" t="inlineStr">
+      <c r="E52" s="91" t="inlineStr">
         <is>
           <t>АРЕНДА-ИНСТРУМЕНТ</t>
         </is>
       </c>
-      <c r="F42" s="62" t="inlineStr">
+      <c r="F52" s="91" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G42" s="216" t="n">
+      <c r="G52" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="173" t="n">
+      <c r="H52" s="89" t="n">
         <v>1000</v>
       </c>
-      <c r="I42" s="217">
-        <f>G42*H42</f>
-        <v/>
-      </c>
-      <c r="J42" s="44" t="inlineStr">
+      <c r="I52" s="90">
+        <f>G52*H52</f>
+        <v/>
+      </c>
+      <c r="J52" s="88" t="inlineStr">
         <is>
           <t>Сосед по дому</t>
         </is>
       </c>
-      <c r="K42" s="174">
+      <c r="K52" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=аренда+перфоратора", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L42" s="44" t="inlineStr">
+      <c r="L52" s="88" t="inlineStr">
         <is>
           <t>Перфоратор и монтировки для первичного демонтажа</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="64" t="n">
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="86" t="n">
         <v>7</v>
       </c>
-      <c r="B43" s="64" t="inlineStr">
+      <c r="B53" s="82" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C43" s="64" t="inlineStr">
+      <c r="C53" s="82" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D43" s="49" t="inlineStr">
+      <c r="D53" s="82" t="inlineStr">
         <is>
           <t>Оплата работы бригады разнорабочих (4 чел., 28 чел.-час, спуск с 5 этажа)</t>
         </is>
       </c>
-      <c r="E43" s="64" t="inlineStr">
+      <c r="E53" s="86" t="inlineStr">
         <is>
           <t>ДЕМОНТАЖ-БРИГАДА-1</t>
         </is>
       </c>
-      <c r="F43" s="64" t="inlineStr">
+      <c r="F53" s="86" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="G43" s="218" t="n">
+      <c r="G53" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="172" t="n">
+      <c r="H53" s="83" t="n">
         <v>16000</v>
       </c>
-      <c r="I43" s="219">
-        <f>G43*H43</f>
-        <v/>
-      </c>
-      <c r="J43" s="49" t="inlineStr">
+      <c r="I53" s="84">
+        <f>G53*H53</f>
+        <v/>
+      </c>
+      <c r="J53" s="82" t="inlineStr">
         <is>
           <t>Бригада разнорабочих</t>
         </is>
       </c>
-      <c r="K43" s="175">
+      <c r="K53" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=демонтаж+квартиры+разнорабочие", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L43" s="49" t="inlineStr">
+      <c r="L53" s="82" t="inlineStr">
         <is>
           <t>Тотальная зачистка и вынос мусора без лифта</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="19" customHeight="1">
-      <c r="A44" s="62" t="n">
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="91" t="n">
         <v>18</v>
       </c>
-      <c r="B44" s="62" t="inlineStr">
+      <c r="B54" s="88" t="inlineStr">
         <is>
           <t>Входная группа</t>
         </is>
       </c>
-      <c r="C44" s="62" t="inlineStr">
+      <c r="C54" s="88" t="inlineStr">
         <is>
           <t>Монтаж</t>
         </is>
       </c>
-      <c r="D44" s="44" t="inlineStr">
+      <c r="D54" s="88" t="inlineStr">
         <is>
           <t>Монтаж входной двери (демонтаж 2 старых дверей + монтаж новой)</t>
         </is>
       </c>
-      <c r="E44" s="62" t="inlineStr">
+      <c r="E54" s="91" t="inlineStr">
         <is>
           <t>МОНТАЖ-ДВЕРИ-ВХОД</t>
         </is>
       </c>
-      <c r="F44" s="62" t="inlineStr">
+      <c r="F54" s="91" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G44" s="216" t="n">
+      <c r="G54" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="173" t="n">
+      <c r="H54" s="89" t="n">
         <v>9000</v>
       </c>
-      <c r="I44" s="217">
-        <f>G44*H44</f>
-        <v/>
-      </c>
-      <c r="J44" s="44" t="inlineStr">
+      <c r="I54" s="90">
+        <f>G54*H54</f>
+        <v/>
+      </c>
+      <c r="J54" s="88" t="inlineStr">
         <is>
           <t>Андрей (монтаж дверей)</t>
         </is>
       </c>
-      <c r="K44" s="174">
+      <c r="K54" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=установка+входных+дверей", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L44" s="44" t="inlineStr">
+      <c r="L54" s="88" t="inlineStr">
         <is>
           <t>Сняли старые двери, расширили проем, выставили по уровню</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="64" t="n">
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="86" t="n">
         <v>22</v>
       </c>
-      <c r="B45" s="64" t="inlineStr">
+      <c r="B55" s="82" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C45" s="64" t="inlineStr">
+      <c r="C55" s="82" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D45" s="49" t="inlineStr">
+      <c r="D55" s="82" t="inlineStr">
         <is>
           <t>Электромонтажные работы под ключ (разводка 32 точек, штробы, щит, счётчик)</t>
         </is>
       </c>
-      <c r="E45" s="64" t="inlineStr">
+      <c r="E55" s="86" t="inlineStr">
         <is>
           <t>РАБОТА-ЭЛЕКТРИКА-32</t>
         </is>
       </c>
-      <c r="F45" s="64" t="inlineStr">
+      <c r="F55" s="86" t="inlineStr">
         <is>
           <t>договор</t>
         </is>
       </c>
-      <c r="G45" s="218" t="n">
+      <c r="G55" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="172" t="n">
+      <c r="H55" s="83" t="n">
         <v>50000</v>
       </c>
-      <c r="I45" s="219">
-        <f>G45*H45</f>
-        <v/>
-      </c>
-      <c r="J45" s="49" t="inlineStr">
+      <c r="I55" s="84">
+        <f>G55*H55</f>
+        <v/>
+      </c>
+      <c r="J55" s="82" t="inlineStr">
         <is>
           <t>Анатолий Кушнарев (бригада)</t>
         </is>
       </c>
-      <c r="K45" s="175">
+      <c r="K55" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=электромонтаж+квартиры+под+ключ", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L45" s="49" t="inlineStr">
+      <c r="L55" s="82" t="inlineStr">
         <is>
           <t>Монтаж всей проводки, сборка щита и счётчика</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="62" t="n">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="91" t="n">
         <v>24</v>
       </c>
-      <c r="B46" s="62" t="inlineStr">
+      <c r="B56" s="88" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C46" s="62" t="inlineStr">
+      <c r="C56" s="88" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D46" s="44" t="inlineStr">
+      <c r="D56" s="88" t="inlineStr">
         <is>
           <t>Зачистка стен/потолка (обои, плитка в зале и спальне), вынос мусора, 1-й слой грунта</t>
         </is>
       </c>
-      <c r="E46" s="62" t="inlineStr">
+      <c r="E56" s="91" t="inlineStr">
         <is>
           <t>ДЕМОНТАЖ-ЗАЧИСТКА-2</t>
         </is>
       </c>
-      <c r="F46" s="62" t="inlineStr">
+      <c r="F56" s="91" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="G46" s="216" t="n">
+      <c r="G56" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="173" t="n">
+      <c r="H56" s="89" t="n">
         <v>15000</v>
       </c>
-      <c r="I46" s="217">
-        <f>G46*H46</f>
-        <v/>
-      </c>
-      <c r="J46" s="44" t="inlineStr">
+      <c r="I56" s="90">
+        <f>G56*H56</f>
+        <v/>
+      </c>
+      <c r="J56" s="88" t="inlineStr">
         <is>
           <t>Бригада разнорабочих</t>
         </is>
       </c>
-      <c r="K46" s="174">
+      <c r="K56" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=зачистка+стен+демонтаж+обоев", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L46" s="44" t="inlineStr">
+      <c r="L56" s="88" t="inlineStr">
         <is>
           <t>Снятие старых слоев, обеспыливание поверхностей</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="64" t="n">
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="86" t="n">
         <v>40</v>
       </c>
-      <c r="B47" s="64" t="inlineStr">
+      <c r="B57" s="82" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="C47" s="64" t="inlineStr">
+      <c r="C57" s="82" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
-      <c r="D47" s="49" t="inlineStr">
+      <c r="D57" s="82" t="inlineStr">
         <is>
           <t>Грузовое такси / Доставка закупки материалов и сантехники (Лемана — Фрунзе 17)</t>
         </is>
       </c>
-      <c r="E47" s="64" t="inlineStr">
+      <c r="E57" s="86" t="inlineStr">
         <is>
           <t>ГРУЗОТАКСИ-ЛЕРОЙ</t>
         </is>
       </c>
-      <c r="F47" s="64" t="inlineStr">
+      <c r="F57" s="86" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G47" s="218" t="n">
+      <c r="G57" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="172" t="n">
+      <c r="H57" s="83" t="n">
         <v>2100</v>
       </c>
-      <c r="I47" s="219">
-        <f>G47*H47</f>
-        <v/>
-      </c>
-      <c r="J47" s="49" t="inlineStr">
+      <c r="I57" s="84">
+        <f>G57*H57</f>
+        <v/>
+      </c>
+      <c r="J57" s="82" t="inlineStr">
         <is>
           <t>Грузовое такси / Перевозка</t>
         </is>
       </c>
-      <c r="K47" s="175">
+      <c r="K57" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=грузоперевозки+грузовое+такси", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L47" s="49" t="inlineStr">
+      <c r="L57" s="82" t="inlineStr">
         <is>
           <t>Перевозка партии смесей, керамогранита и ванны</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="62" t="n">
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="91" t="n">
         <v>41</v>
       </c>
-      <c r="B48" s="62" t="inlineStr">
+      <c r="B58" s="88" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C48" s="62" t="inlineStr">
+      <c r="C58" s="88" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D48" s="44" t="inlineStr">
+      <c r="D58" s="88" t="inlineStr">
         <is>
           <t>Погрузка в Лемана ПРО, разгрузка и подъём на 5 этаж + демонтаж плитки пола с/у</t>
         </is>
       </c>
-      <c r="E48" s="62" t="inlineStr">
+      <c r="E58" s="91" t="inlineStr">
         <is>
           <t>ПОДЪЕМ-ДЕМОНТАЖ-СУ</t>
         </is>
       </c>
-      <c r="F48" s="62" t="inlineStr">
+      <c r="F58" s="91" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="G48" s="216" t="n">
+      <c r="G58" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="173" t="n">
+      <c r="H58" s="89" t="n">
         <v>15000</v>
       </c>
-      <c r="I48" s="217">
-        <f>G48*H48</f>
-        <v/>
-      </c>
-      <c r="J48" s="44" t="inlineStr">
+      <c r="I58" s="90">
+        <f>G58*H58</f>
+        <v/>
+      </c>
+      <c r="J58" s="88" t="inlineStr">
         <is>
           <t>Бригада грузчиков / Разнорабочие</t>
         </is>
       </c>
-      <c r="K48" s="174">
+      <c r="K58" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=подъем+стройматериалов+на+этаж+грузчики", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L48" s="44" t="inlineStr">
+      <c r="L58" s="88" t="inlineStr">
         <is>
           <t>Разгрузка 1.5 тонн смесей на 5 этаж без лифта</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="64" t="n">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="86" t="n">
         <v>42</v>
       </c>
-      <c r="B49" s="64" t="inlineStr">
+      <c r="B59" s="82" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C49" s="64" t="inlineStr">
+      <c r="C59" s="82" t="inlineStr">
         <is>
           <t>Отделочные работы</t>
         </is>
       </c>
-      <c r="D49" s="49" t="inlineStr">
+      <c r="D59" s="82" t="inlineStr">
         <is>
           <t>Штукатурка (69 м² по 500 ₽) и шпаклёвка стен White Box (106 м² по 500 ₽)</t>
         </is>
       </c>
-      <c r="E49" s="64" t="inlineStr">
+      <c r="E59" s="86" t="inlineStr">
         <is>
           <t>ОТДЕЛКА-СТЕН-ЕЛЕНА</t>
         </is>
       </c>
-      <c r="F49" s="64" t="inlineStr">
+      <c r="F59" s="86" t="inlineStr">
         <is>
           <t>комплекс</t>
         </is>
       </c>
-      <c r="G49" s="218" t="n">
+      <c r="G59" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="172" t="n">
+      <c r="H59" s="83" t="n">
         <v>87500</v>
       </c>
-      <c r="I49" s="219">
-        <f>G49*H49</f>
-        <v/>
-      </c>
-      <c r="J49" s="49" t="inlineStr">
+      <c r="I59" s="84">
+        <f>G59*H59</f>
+        <v/>
+      </c>
+      <c r="J59" s="82" t="inlineStr">
         <is>
           <t>Елена (мастер-отделочник)</t>
         </is>
       </c>
-      <c r="K49" s="175">
+      <c r="K59" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=штукатурка+шпаклевка+стен", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L49" s="49" t="inlineStr">
+      <c r="L59" s="82" t="inlineStr">
         <is>
           <t>Штукатурка 69 м² + шпаклёвка стен 106 м² по 500₽. White Box под ключ</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="19" customHeight="1">
-      <c r="A50" s="62" t="n">
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="91" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="62" t="inlineStr">
+      <c r="B60" s="88" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C50" s="62" t="inlineStr">
+      <c r="C60" s="88" t="inlineStr">
         <is>
           <t>Сантехника / Работы</t>
         </is>
       </c>
-      <c r="D50" s="44" t="inlineStr">
+      <c r="D60" s="88" t="inlineStr">
         <is>
           <t>Срезка полотенцесушителя и нарезка трубной резьбы на отводах стояка</t>
         </is>
       </c>
-      <c r="E50" s="62" t="inlineStr">
+      <c r="E60" s="91" t="inlineStr">
         <is>
           <t>РАБОТА-САНТЕХ-СУШ</t>
         </is>
       </c>
-      <c r="F50" s="62" t="inlineStr">
+      <c r="F60" s="91" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G50" s="216" t="n">
+      <c r="G60" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="173" t="n">
+      <c r="H60" s="89" t="n">
         <v>3000</v>
       </c>
-      <c r="I50" s="217">
-        <f>G50*H50</f>
-        <v/>
-      </c>
-      <c r="J50" s="44" t="inlineStr">
+      <c r="I60" s="90">
+        <f>G60*H60</f>
+        <v/>
+      </c>
+      <c r="J60" s="88" t="inlineStr">
         <is>
           <t>Вадим (сантехник УК) / Сантехник</t>
         </is>
       </c>
-      <c r="K50" s="174">
+      <c r="K60" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=сантехник+срезка+полотенцесушителя", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L50" s="44" t="inlineStr">
+      <c r="L60" s="88" t="inlineStr">
         <is>
           <t>Демонтаж старого змеевика, нарезка 2 резьб клуппом под установку запорных кранов</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="64" t="n">
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="86" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="64" t="inlineStr">
+      <c r="B61" s="82" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="C51" s="64" t="inlineStr">
+      <c r="C61" s="82" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
-      <c r="D51" s="49" t="inlineStr">
+      <c r="D61" s="82" t="inlineStr">
         <is>
           <t>Такси (оперативная доставка материалов и инструмента из Лемана ПРО на объект)</t>
         </is>
       </c>
-      <c r="E51" s="64" t="inlineStr">
+      <c r="E61" s="86" t="inlineStr">
         <is>
           <t>ТАКСИ-ЛЕРОЙ-ОБЪЕКТ</t>
         </is>
       </c>
-      <c r="F51" s="64" t="inlineStr">
+      <c r="F61" s="86" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G51" s="218" t="n">
+      <c r="G61" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="172" t="n">
+      <c r="H61" s="83" t="n">
         <v>1000</v>
       </c>
-      <c r="I51" s="219">
-        <f>G51*H51</f>
-        <v/>
-      </c>
-      <c r="J51" s="49" t="inlineStr">
+      <c r="I61" s="84">
+        <f>G61*H61</f>
+        <v/>
+      </c>
+      <c r="J61" s="82" t="inlineStr">
         <is>
           <t>Такси (Яндекс Go)</t>
         </is>
       </c>
-      <c r="K51" s="175">
+      <c r="K61" s="244">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=такси+доставка+курьер", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L51" s="49" t="inlineStr">
+      <c r="L61" s="82" t="inlineStr">
         <is>
           <t>Оперативный подвоз купленного инструмента и материалов из Лемана ПРО на ул. Фрунзе 17</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="234" t="inlineStr"/>
-      <c r="B52" s="234" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="91" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="88" t="inlineStr">
+        <is>
+          <t>Логистика</t>
+        </is>
+      </c>
+      <c r="C62" s="88" t="inlineStr">
+        <is>
+          <t>Доставка</t>
+        </is>
+      </c>
+      <c r="D62" s="88" t="inlineStr">
+        <is>
+          <t>Такси (оперативная доставка / подвоз материалов на объект)</t>
+        </is>
+      </c>
+      <c r="E62" s="91" t="inlineStr">
+        <is>
+          <t>ТАКСИ-ДОСТАВКА-2</t>
+        </is>
+      </c>
+      <c r="F62" s="91" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="G62" s="243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="89" t="n">
+        <v>850</v>
+      </c>
+      <c r="I62" s="90">
+        <f>G62*H62</f>
+        <v/>
+      </c>
+      <c r="J62" s="88" t="inlineStr">
+        <is>
+          <t>Такси (Яндекс Go)</t>
+        </is>
+      </c>
+      <c r="K62" s="244">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=такси+доставка+курьер", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L62" s="88" t="inlineStr">
+        <is>
+          <t>Оперативный подвоз материалов и крепежа</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="86" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="82" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C63" s="82" t="inlineStr">
+        <is>
+          <t>Плиточные работы</t>
+        </is>
+      </c>
+      <c r="D63" s="82" t="inlineStr">
+        <is>
+          <t>Работы плиточника (аванс / подготовка к укладке плитки в санузле)</t>
+        </is>
+      </c>
+      <c r="E63" s="86" t="inlineStr">
+        <is>
+          <t>РАБОТА-ПЛИТОЧНИК-1</t>
+        </is>
+      </c>
+      <c r="F63" s="86" t="inlineStr">
+        <is>
+          <t>аванс</t>
+        </is>
+      </c>
+      <c r="G63" s="245" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="83" t="n">
+        <v>1700</v>
+      </c>
+      <c r="I63" s="84">
+        <f>G63*H63</f>
+        <v/>
+      </c>
+      <c r="J63" s="82" t="inlineStr">
+        <is>
+          <t>Плиточник (мастер)</t>
+        </is>
+      </c>
+      <c r="K63" s="244">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=плиточник+укладка+плитки", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L63" s="82" t="inlineStr">
+        <is>
+          <t>Подготовка и аванс плиточнику за работы в с/у</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="91" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="88" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C64" s="88" t="inlineStr">
+        <is>
+          <t>Стяжка пола</t>
+        </is>
+      </c>
+      <c r="D64" s="88" t="inlineStr">
+        <is>
+          <t>Работы плиточника: заливка стяжки пола в санузле/туалете</t>
+        </is>
+      </c>
+      <c r="E64" s="91" t="inlineStr">
+        <is>
+          <t>СТЯЖКА-ПОЛА-СУ</t>
+        </is>
+      </c>
+      <c r="F64" s="91" t="inlineStr">
+        <is>
+          <t>услуга</t>
+        </is>
+      </c>
+      <c r="G64" s="243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="89" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I64" s="90">
+        <f>G64*H64</f>
+        <v/>
+      </c>
+      <c r="J64" s="88" t="inlineStr">
+        <is>
+          <t>Плиточник (мастер)</t>
+        </is>
+      </c>
+      <c r="K64" s="244">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=стяжка+пола+санузел", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L64" s="88" t="inlineStr">
+        <is>
+          <t>Заливка прочной стяжки пола с/у по маякам с ускорителем Cemfix</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="86" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="82" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C65" s="82" t="inlineStr">
+        <is>
+          <t>Штукатурка стен</t>
+        </is>
+      </c>
+      <c r="D65" s="82" t="inlineStr">
+        <is>
+          <t>Оплата за штукатурку туалета (санузла) под 90° под ванну и плитку</t>
+        </is>
+      </c>
+      <c r="E65" s="86" t="inlineStr">
+        <is>
+          <t>ШТУКАТУРКА-СУ-90</t>
+        </is>
+      </c>
+      <c r="F65" s="86" t="inlineStr">
+        <is>
+          <t>комплекс</t>
+        </is>
+      </c>
+      <c r="G65" s="245" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="83" t="n">
+        <v>13400</v>
+      </c>
+      <c r="I65" s="84">
+        <f>G65*H65</f>
+        <v/>
+      </c>
+      <c r="J65" s="82" t="inlineStr">
+        <is>
+          <t>Елена (мастер-отделочник)</t>
+        </is>
+      </c>
+      <c r="K65" s="244">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=штукатурка+санузла+под+90", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L65" s="82" t="inlineStr">
+        <is>
+          <t>Штукатурка стен с/у по маякам с идеальной геометрией 90° под ванну 150см</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="246" t="n"/>
+      <c r="B66" s="247" t="inlineStr">
         <is>
           <t>ИТОГО РАБОТЫ И ЛОГИСТИКА:</t>
         </is>
       </c>
-      <c r="C52" s="234" t="inlineStr"/>
-      <c r="D52" s="234" t="inlineStr"/>
-      <c r="E52" s="234" t="inlineStr"/>
-      <c r="F52" s="234" t="inlineStr"/>
-      <c r="G52" s="234" t="inlineStr"/>
-      <c r="H52" s="234" t="inlineStr"/>
-      <c r="I52" s="235">
-        <f>SUM(I40:I51)</f>
-        <v/>
-      </c>
-      <c r="J52" s="234" t="inlineStr"/>
-      <c r="K52" s="234" t="inlineStr"/>
-      <c r="L52" s="234" t="inlineStr"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="225" t="inlineStr"/>
-      <c r="B53" s="225" t="inlineStr">
-        <is>
-          <t>🏛 БЛОК 4: ЮРИДИЧЕСКИЕ РАСХОДЫ, ПОШЛИНЫ, ГАЗ, ЭНЕРГОСБЫТ И IT</t>
-        </is>
-      </c>
-      <c r="C53" s="225" t="inlineStr"/>
-      <c r="D53" s="225" t="inlineStr"/>
-      <c r="E53" s="225" t="inlineStr"/>
-      <c r="F53" s="225" t="inlineStr"/>
-      <c r="G53" s="225" t="inlineStr"/>
-      <c r="H53" s="225" t="inlineStr"/>
-      <c r="I53" s="225" t="inlineStr"/>
-      <c r="J53" s="225" t="inlineStr"/>
-      <c r="K53" s="225" t="inlineStr"/>
-      <c r="L53" s="225" t="inlineStr"/>
-    </row>
-    <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="62" t="n">
+      <c r="C66" s="246" t="n"/>
+      <c r="D66" s="246" t="n"/>
+      <c r="E66" s="246" t="n"/>
+      <c r="F66" s="246" t="n"/>
+      <c r="G66" s="246" t="n"/>
+      <c r="H66" s="246" t="n"/>
+      <c r="I66" s="248">
+        <f>SUM(I50:I65)</f>
+        <v/>
+      </c>
+      <c r="J66" s="246" t="n"/>
+      <c r="K66" s="246" t="n"/>
+      <c r="L66" s="246" t="n"/>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="251" t="n"/>
+      <c r="B67" s="251" t="inlineStr">
+        <is>
+          <t>🏛 БЛОК 4: ЮРИДИЧЕСКИЕ РАСХОДЫ, ПОШЛИНЫ, ГАЗ, ЭНЕРГОСБЫТ И IT (8 ПОЗИЦИЙ)</t>
+        </is>
+      </c>
+      <c r="C67" s="251" t="n"/>
+      <c r="D67" s="251" t="n"/>
+      <c r="E67" s="251" t="n"/>
+      <c r="F67" s="251" t="n"/>
+      <c r="G67" s="251" t="n"/>
+      <c r="H67" s="251" t="n"/>
+      <c r="I67" s="251" t="n"/>
+      <c r="J67" s="251" t="n"/>
+      <c r="K67" s="251" t="n"/>
+      <c r="L67" s="251" t="n"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="B54" s="62" t="inlineStr">
+      <c r="B68" s="88" t="inlineStr">
         <is>
           <t>Юр. оформление</t>
         </is>
       </c>
-      <c r="C54" s="62" t="inlineStr">
+      <c r="C68" s="88" t="inlineStr">
         <is>
           <t>Торги</t>
         </is>
       </c>
-      <c r="D54" s="44" t="inlineStr">
+      <c r="D68" s="88" t="inlineStr">
         <is>
           <t>Выпуск квалифицированной ЭЦП (электронная цифровая подпись)</t>
         </is>
       </c>
-      <c r="E54" s="62" t="inlineStr">
+      <c r="E68" s="91" t="inlineStr">
         <is>
           <t>ЭЦП-КОНТУР</t>
         </is>
       </c>
-      <c r="F54" s="62" t="inlineStr">
+      <c r="F68" s="91" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G54" s="216" t="n">
+      <c r="G68" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="173" t="n">
+      <c r="H68" s="89" t="n">
         <v>7000</v>
       </c>
-      <c r="I54" s="217">
-        <f>G54*H54</f>
-        <v/>
-      </c>
-      <c r="J54" s="44" t="inlineStr">
+      <c r="I68" s="90">
+        <f>G68*H68</f>
+        <v/>
+      </c>
+      <c r="J68" s="88" t="inlineStr">
         <is>
           <t>УЦ / Контур</t>
         </is>
       </c>
-      <c r="K54" s="174">
+      <c r="K68" s="244">
         <f>HYPERLINK("https://ca.kontur.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L54" s="44" t="inlineStr">
+      <c r="L68" s="88" t="inlineStr">
         <is>
           <t>ЭЦП для участия в торгах и регистрации права</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="64" t="n">
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="86" t="n">
         <v>2</v>
       </c>
-      <c r="B55" s="64" t="inlineStr">
+      <c r="B69" s="82" t="inlineStr">
         <is>
           <t>Юр. оформление</t>
         </is>
       </c>
-      <c r="C55" s="64" t="inlineStr">
+      <c r="C69" s="82" t="inlineStr">
         <is>
           <t>Росреестр</t>
         </is>
       </c>
-      <c r="D55" s="49" t="inlineStr">
+      <c r="D69" s="82" t="inlineStr">
         <is>
           <t>Государственная пошлина (регистрация перехода права собственности)</t>
         </is>
       </c>
-      <c r="E55" s="64" t="inlineStr">
+      <c r="E69" s="86" t="inlineStr">
         <is>
           <t>ГОСПОШЛИНА-ПРАВО</t>
         </is>
       </c>
-      <c r="F55" s="64" t="inlineStr">
+      <c r="F69" s="86" t="inlineStr">
         <is>
           <t>платеж</t>
         </is>
       </c>
-      <c r="G55" s="218" t="n">
+      <c r="G69" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="172" t="n">
+      <c r="H69" s="83" t="n">
         <v>5000</v>
       </c>
-      <c r="I55" s="219">
-        <f>G55*H55</f>
-        <v/>
-      </c>
-      <c r="J55" s="49" t="inlineStr">
+      <c r="I69" s="84">
+        <f>G69*H69</f>
+        <v/>
+      </c>
+      <c r="J69" s="82" t="inlineStr">
         <is>
           <t>Росреестр</t>
         </is>
       </c>
-      <c r="K55" s="175">
+      <c r="K69" s="244">
         <f>HYPERLINK("https://rosreestr.gov.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L55" s="49" t="inlineStr">
+      <c r="L69" s="82" t="inlineStr">
         <is>
           <t>Официальная пошлина Росреестра</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="19" customHeight="1">
-      <c r="A56" s="62" t="n">
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="91" t="n">
         <v>10</v>
       </c>
-      <c r="B56" s="62" t="inlineStr">
+      <c r="B70" s="88" t="inlineStr">
         <is>
           <t>IT / AI</t>
         </is>
       </c>
-      <c r="C56" s="62" t="inlineStr">
+      <c r="C70" s="88" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="D56" s="44" t="inlineStr">
+      <c r="D70" s="88" t="inlineStr">
         <is>
           <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 1</t>
         </is>
       </c>
-      <c r="E56" s="62" t="inlineStr">
+      <c r="E70" s="91" t="inlineStr">
         <is>
           <t>OPENROUTER-TRANS-1</t>
         </is>
       </c>
-      <c r="F56" s="62" t="inlineStr">
+      <c r="F70" s="91" t="inlineStr">
         <is>
           <t>платёж</t>
         </is>
       </c>
-      <c r="G56" s="216" t="n">
+      <c r="G70" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H56" s="173" t="n">
+      <c r="H70" s="89" t="n">
         <v>3000</v>
       </c>
-      <c r="I56" s="217">
-        <f>G56*H56</f>
-        <v/>
-      </c>
-      <c r="J56" s="44" t="inlineStr">
+      <c r="I70" s="90">
+        <f>G70*H70</f>
+        <v/>
+      </c>
+      <c r="J70" s="88" t="inlineStr">
         <is>
           <t>OpenRouter</t>
         </is>
       </c>
-      <c r="K56" s="174">
+      <c r="K70" s="244">
         <f>HYPERLINK("https://openrouter.ai/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L56" s="44" t="inlineStr">
+      <c r="L70" s="88" t="inlineStr">
         <is>
           <t>Инфраструктура проектов и аналитика</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="A57" s="64" t="n">
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="86" t="n">
         <v>12</v>
       </c>
-      <c r="B57" s="64" t="inlineStr">
+      <c r="B71" s="82" t="inlineStr">
         <is>
           <t>Газ</t>
         </is>
       </c>
-      <c r="C57" s="64" t="inlineStr">
+      <c r="C71" s="82" t="inlineStr">
         <is>
           <t>Безопасность</t>
         </is>
       </c>
-      <c r="D57" s="49" t="inlineStr">
+      <c r="D71" s="82" t="inlineStr">
         <is>
           <t>Акт ВДПО — проверка дымохода и вентканала</t>
         </is>
       </c>
-      <c r="E57" s="64" t="inlineStr">
+      <c r="E71" s="86" t="inlineStr">
         <is>
           <t>ВДПО-АКТ-ВЕНТ</t>
         </is>
       </c>
-      <c r="F57" s="64" t="inlineStr">
+      <c r="F71" s="86" t="inlineStr">
         <is>
           <t>акт</t>
         </is>
       </c>
-      <c r="G57" s="218" t="n">
+      <c r="G71" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H57" s="172" t="n">
+      <c r="H71" s="83" t="n">
         <v>1500</v>
       </c>
-      <c r="I57" s="219">
-        <f>G57*H57</f>
-        <v/>
-      </c>
-      <c r="J57" s="49" t="inlineStr">
+      <c r="I71" s="84">
+        <f>G71*H71</f>
+        <v/>
+      </c>
+      <c r="J71" s="82" t="inlineStr">
         <is>
           <t>ВДПО / Газовая служба</t>
         </is>
       </c>
-      <c r="K57" s="175">
+      <c r="K71" s="244">
         <f>HYPERLINK("https://vdpo71.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L57" s="49" t="inlineStr">
+      <c r="L71" s="82" t="inlineStr">
         <is>
           <t>Обязательная проверка тяги для газовой колонки</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="62" t="n">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="91" t="n">
         <v>13</v>
       </c>
-      <c r="B58" s="62" t="inlineStr">
+      <c r="B72" s="88" t="inlineStr">
         <is>
           <t>Газ</t>
         </is>
       </c>
-      <c r="C58" s="62" t="inlineStr">
+      <c r="C72" s="88" t="inlineStr">
         <is>
           <t>Коммуналка</t>
         </is>
       </c>
-      <c r="D58" s="44" t="inlineStr">
+      <c r="D72" s="88" t="inlineStr">
         <is>
           <t>Оплата квитанций Тулагоргаз (платежки/техобслуживание)</t>
         </is>
       </c>
-      <c r="E58" s="62" t="inlineStr">
+      <c r="E72" s="91" t="inlineStr">
         <is>
           <t>ТУЛАГОРГАЗ-КВИТАНЦИЯ</t>
         </is>
       </c>
-      <c r="F58" s="62" t="inlineStr">
+      <c r="F72" s="91" t="inlineStr">
         <is>
           <t>платеж</t>
         </is>
       </c>
-      <c r="G58" s="216" t="n">
+      <c r="G72" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H58" s="173" t="n">
+      <c r="H72" s="89" t="n">
         <v>800</v>
       </c>
-      <c r="I58" s="217">
-        <f>G58*H58</f>
-        <v/>
-      </c>
-      <c r="J58" s="44" t="inlineStr">
+      <c r="I72" s="90">
+        <f>G72*H72</f>
+        <v/>
+      </c>
+      <c r="J72" s="88" t="inlineStr">
         <is>
           <t>Тулагоргаз</t>
         </is>
       </c>
-      <c r="K58" s="174">
+      <c r="K72" s="244">
         <f>HYPERLINK("https://tulagorgaz.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L58" s="44" t="inlineStr">
+      <c r="L72" s="88" t="inlineStr">
         <is>
           <t>Погашение начислений газовой службы</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="19" customHeight="1">
-      <c r="A59" s="64" t="n">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="86" t="n">
         <v>21</v>
       </c>
-      <c r="B59" s="64" t="inlineStr">
+      <c r="B73" s="82" t="inlineStr">
         <is>
           <t>Энергосбыт</t>
         </is>
       </c>
-      <c r="C59" s="64" t="inlineStr">
+      <c r="C73" s="82" t="inlineStr">
         <is>
           <t>Учёт</t>
         </is>
       </c>
-      <c r="D59" s="49" t="inlineStr">
+      <c r="D73" s="82" t="inlineStr">
         <is>
           <t>Срочный выезд инспектора ТНС энерго Тула (снятие пломбы со старого счётчика)</t>
         </is>
       </c>
-      <c r="E59" s="64" t="inlineStr">
+      <c r="E73" s="86" t="inlineStr">
         <is>
           <t>ТНС-ВЫЕЗД-ПЛОМБА</t>
         </is>
       </c>
-      <c r="F59" s="64" t="inlineStr">
+      <c r="F73" s="86" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G59" s="218" t="n">
+      <c r="G73" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H59" s="172" t="n">
+      <c r="H73" s="83" t="n">
         <v>2500</v>
       </c>
-      <c r="I59" s="219">
-        <f>G59*H59</f>
-        <v/>
-      </c>
-      <c r="J59" s="49" t="inlineStr">
+      <c r="I73" s="84">
+        <f>G73*H73</f>
+        <v/>
+      </c>
+      <c r="J73" s="82" t="inlineStr">
         <is>
           <t>АО "ТНС энерго Тула"</t>
         </is>
       </c>
-      <c r="K59" s="175">
+      <c r="K73" s="244">
         <f>HYPERLINK("https://tns-e.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L59" s="49" t="inlineStr">
+      <c r="L73" s="82" t="inlineStr">
         <is>
           <t>Срочное снятие пломбы за 5 дней</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="19" customHeight="1">
-      <c r="A60" s="62" t="n">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="91" t="n">
         <v>31</v>
       </c>
-      <c r="B60" s="62" t="inlineStr">
+      <c r="B74" s="88" t="inlineStr">
         <is>
           <t>IT / AI</t>
         </is>
       </c>
-      <c r="C60" s="62" t="inlineStr">
+      <c r="C74" s="88" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="D60" s="44" t="inlineStr">
+      <c r="D74" s="88" t="inlineStr">
         <is>
           <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 2</t>
         </is>
       </c>
-      <c r="E60" s="62" t="inlineStr">
+      <c r="E74" s="91" t="inlineStr">
         <is>
           <t>OPENROUTER-TRANS-2</t>
         </is>
       </c>
-      <c r="F60" s="62" t="inlineStr">
+      <c r="F74" s="91" t="inlineStr">
         <is>
           <t>платёж</t>
         </is>
       </c>
-      <c r="G60" s="216" t="n">
+      <c r="G74" s="243" t="n">
         <v>1</v>
       </c>
-      <c r="H60" s="173" t="n">
+      <c r="H74" s="89" t="n">
         <v>2500</v>
       </c>
-      <c r="I60" s="217">
-        <f>G60*H60</f>
-        <v/>
-      </c>
-      <c r="J60" s="44" t="inlineStr">
+      <c r="I74" s="90">
+        <f>G74*H74</f>
+        <v/>
+      </c>
+      <c r="J74" s="88" t="inlineStr">
         <is>
           <t>OpenRouter</t>
         </is>
       </c>
-      <c r="K60" s="174">
+      <c r="K74" s="244">
         <f>HYPERLINK("https://openrouter.ai/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L60" s="44" t="inlineStr">
+      <c r="L74" s="88" t="inlineStr">
         <is>
           <t>Пополнение баланса API для расчётов и смет</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="64" t="n">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="86" t="n">
         <v>33</v>
       </c>
-      <c r="B61" s="64" t="inlineStr">
+      <c r="B75" s="82" t="inlineStr">
         <is>
           <t>Энергосбыт</t>
         </is>
       </c>
-      <c r="C61" s="64" t="inlineStr">
+      <c r="C75" s="82" t="inlineStr">
         <is>
           <t>Учёт</t>
         </is>
       </c>
-      <c r="D61" s="49" t="inlineStr">
+      <c r="D75" s="82" t="inlineStr">
         <is>
           <t>Дистанционная распломбировка старого электросчётчика (согласование)</t>
         </is>
       </c>
-      <c r="E61" s="64" t="inlineStr">
+      <c r="E75" s="86" t="inlineStr">
         <is>
           <t>ТНС-РАСПЛОМБ-ДИСТ</t>
         </is>
       </c>
-      <c r="F61" s="64" t="inlineStr">
+      <c r="F75" s="86" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G61" s="218" t="n">
+      <c r="G75" s="245" t="n">
         <v>1</v>
       </c>
-      <c r="H61" s="172" t="n">
+      <c r="H75" s="83" t="n">
         <v>2200</v>
       </c>
-      <c r="I61" s="219">
-        <f>G61*H61</f>
-        <v/>
-      </c>
-      <c r="J61" s="49" t="inlineStr">
+      <c r="I75" s="84">
+        <f>G75*H75</f>
+        <v/>
+      </c>
+      <c r="J75" s="82" t="inlineStr">
         <is>
           <t>ТНС энерго Тула / Энергосбыт</t>
         </is>
       </c>
-      <c r="K61" s="175">
+      <c r="K75" s="244">
         <f>HYPERLINK("https://tns-e.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L61" s="49" t="inlineStr">
-        <is>
-          <t>Официальное согласование замены электроузла</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="234" t="inlineStr"/>
-      <c r="B62" s="234" t="inlineStr">
+      <c r="L75" s="82" t="inlineStr">
+        <is>
+          <t>Фиксация показаний и снятие пломбы без выезда</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="246" t="n"/>
+      <c r="B76" s="247" t="inlineStr">
         <is>
           <t>ИТОГО ЮР. РАСХОДЫ, СЛУЖБЫ И IT:</t>
         </is>
       </c>
-      <c r="C62" s="234" t="inlineStr"/>
-      <c r="D62" s="234" t="inlineStr"/>
-      <c r="E62" s="234" t="inlineStr"/>
-      <c r="F62" s="234" t="inlineStr"/>
-      <c r="G62" s="234" t="inlineStr"/>
-      <c r="H62" s="234" t="inlineStr"/>
-      <c r="I62" s="235">
-        <f>SUM(I54:I61)</f>
-        <v/>
-      </c>
-      <c r="J62" s="234" t="inlineStr"/>
-      <c r="K62" s="234" t="inlineStr"/>
-      <c r="L62" s="234" t="inlineStr"/>
-    </row>
-    <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="236" t="inlineStr"/>
-      <c r="B63" s="236" t="inlineStr">
+      <c r="C76" s="246" t="n"/>
+      <c r="D76" s="246" t="n"/>
+      <c r="E76" s="246" t="n"/>
+      <c r="F76" s="246" t="n"/>
+      <c r="G76" s="246" t="n"/>
+      <c r="H76" s="246" t="n"/>
+      <c r="I76" s="248">
+        <f>SUM(I68:I75)</f>
+        <v/>
+      </c>
+      <c r="J76" s="246" t="n"/>
+      <c r="K76" s="246" t="n"/>
+      <c r="L76" s="246" t="n"/>
+    </row>
+    <row r="77" ht="25" customHeight="1">
+      <c r="A77" s="238" t="n"/>
+      <c r="B77" s="239" t="inlineStr">
         <is>
           <t>ОБЩИЙ ИТОГО ФАКТ РАСХОДОВ (ДИНАМИЧЕСКИЙ):</t>
         </is>
       </c>
-      <c r="C63" s="236" t="inlineStr"/>
-      <c r="D63" s="236" t="inlineStr"/>
-      <c r="E63" s="236" t="inlineStr"/>
-      <c r="F63" s="236" t="inlineStr"/>
-      <c r="G63" s="236" t="inlineStr"/>
-      <c r="H63" s="236" t="inlineStr"/>
-      <c r="I63" s="237">
-        <f>SUBTOTAL(109, I6:I22, I25:I37, I40:I51, I54:I61)</f>
-        <v/>
-      </c>
-      <c r="J63" s="236" t="inlineStr"/>
-      <c r="K63" s="236" t="inlineStr"/>
-      <c r="L63" s="236" t="inlineStr"/>
+      <c r="C77" s="238" t="n"/>
+      <c r="D77" s="238" t="n"/>
+      <c r="E77" s="238" t="n"/>
+      <c r="F77" s="238" t="n"/>
+      <c r="G77" s="238" t="n"/>
+      <c r="H77" s="238" t="n"/>
+      <c r="I77" s="171">
+        <f>SUM(I30, I48, I66, I76)</f>
+        <v/>
+      </c>
+      <c r="J77" s="238" t="n"/>
+      <c r="K77" s="238" t="n"/>
+      <c r="L77" s="238" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
+++ b/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="167" formatCode="+0.0%"/>
     <numFmt numFmtId="168" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -253,6 +253,37 @@
       <b val="1"/>
       <color rgb="000F172A"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00581C87"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
   <fills count="12">
@@ -658,7 +689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="252">
+  <cellXfs count="286">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1303,6 +1334,106 @@
     <xf numFmtId="0" fontId="33" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="34" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="36" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1737,7 +1868,7 @@
         <v/>
       </c>
       <c r="D5" s="118">
-        <f>'Факт расходов'!F69</f>
+        <f>'Факт расходов'!F74</f>
         <v/>
       </c>
       <c r="E5" s="118" t="n">
@@ -1830,7 +1961,7 @@
         <v>23000</v>
       </c>
       <c r="C11" s="46">
-        <f>SUMIF('Факт расходов'!C5:C68, "*Юр.*", 'Факт расходов'!F5:F68)+SUMIF('Факт расходов'!C5:C68, "*Безопасность*", 'Факт расходов'!F5:F68)+SUMIF('Факт расходов'!C5:C68, "*IT*", 'Факт расходов'!F5:F68)+SUMIF('Факт расходов'!C5:C68, "*Электроэнергия*", 'Факт расходов'!F5:F68)</f>
+        <f>SUMIF('Факт расходов'!C5:C73, "*Юр.*", 'Факт расходов'!F5:F73)+SUMIF('Факт расходов'!C5:C73, "*Безопасность*", 'Факт расходов'!F5:F73)+SUMIF('Факт расходов'!C5:C73, "*IT*", 'Факт расходов'!F5:F73)+SUMIF('Факт расходов'!C5:C73, "*Электроэнергия*", 'Факт расходов'!F5:F73)</f>
         <v/>
       </c>
       <c r="D11" s="124">
@@ -2110,7 +2241,7 @@
         <v/>
       </c>
       <c r="C23" s="46">
-        <f>SUMIF('Факт расходов'!C5:C68, "*Демонтаж*", 'Факт расходов'!F5:F68)</f>
+        <f>SUMIF('Факт расходов'!C5:C73, "*Демонтаж*", 'Факт расходов'!F5:F73)</f>
         <v/>
       </c>
       <c r="D23" s="45">
@@ -2143,7 +2274,7 @@
         <v/>
       </c>
       <c r="C24" s="51">
-        <f>SUMIF('Факт расходов'!C5:C68, "*Двери*", 'Факт расходов'!F5:F68)</f>
+        <f>SUMIF('Факт расходов'!C5:C73, "*Двери*", 'Факт расходов'!F5:F73)</f>
         <v/>
       </c>
       <c r="D24" s="50">
@@ -2176,7 +2307,7 @@
         <v/>
       </c>
       <c r="C25" s="46">
-        <f>SUMIF('Факт расходов'!C5:C68, "*Электрика*", 'Факт расходов'!F5:F68)</f>
+        <f>SUMIF('Факт расходов'!C5:C73, "*Электрика*", 'Факт расходов'!F5:F73)</f>
         <v/>
       </c>
       <c r="D25" s="45">
@@ -2209,7 +2340,7 @@
         <v/>
       </c>
       <c r="C26" s="51">
-        <f>SUMIF('Факт расходов'!C5:C68, "*Сантехника*", 'Факт расходов'!F5:F68)</f>
+        <f>SUMIF('Факт расходов'!C5:C73, "*Сантехника*", 'Факт расходов'!F5:F73)</f>
         <v/>
       </c>
       <c r="D26" s="50">
@@ -2241,7 +2372,7 @@
         <v>5000</v>
       </c>
       <c r="C27" s="46">
-        <f>SUMIF('Факт расходов'!C5:C68, "*Газ*", 'Факт расходов'!F5:F68)</f>
+        <f>SUMIF('Факт расходов'!C5:C73, "*Газ*", 'Факт расходов'!F5:F73)</f>
         <v/>
       </c>
       <c r="D27" s="45">
@@ -2306,7 +2437,7 @@
         <v/>
       </c>
       <c r="C29" s="46">
-        <f>SUMIF('Факт расходов'!C5:C68, "*Черновая*", 'Факт расходов'!F5:F68)</f>
+        <f>SUMIF('Факт расходов'!C5:C73, "*Черновая*", 'Факт расходов'!F5:F73)</f>
         <v/>
       </c>
       <c r="D29" s="45">
@@ -2339,7 +2470,7 @@
         <v/>
       </c>
       <c r="C30" s="51">
-        <f>SUMIF('Факт расходов'!C5:C68, "*Чистовая*", 'Факт расходов'!F5:F68)</f>
+        <f>SUMIF('Факт расходов'!C5:C73, "*Чистовая*", 'Факт расходов'!F5:F73)</f>
         <v/>
       </c>
       <c r="D30" s="50">
@@ -2499,7 +2630,7 @@
         <v>10000</v>
       </c>
       <c r="C35" s="46">
-        <f>SUMIF('Факт расходов'!C5:C68, "*Инструмент*", 'Факт расходов'!F5:F68)+SUMIF('Факт расходов'!C5:C68, "*Расходные*", 'Факт расходов'!F5:F68)+SUMIF('Факт расходов'!C5:C68, "*Логистика*", 'Факт расходов'!F5:F68)</f>
+        <f>SUMIF('Факт расходов'!C5:C73, "*Инструмент*", 'Факт расходов'!F5:F73)+SUMIF('Факт расходов'!C5:C73, "*Расходные*", 'Факт расходов'!F5:F73)+SUMIF('Факт расходов'!C5:C73, "*Логистика*", 'Факт расходов'!F5:F73)</f>
         <v/>
       </c>
       <c r="D35" s="45">
@@ -2531,7 +2662,7 @@
         <v>5000</v>
       </c>
       <c r="C36" s="51">
-        <f>SUMIF('Факт расходов'!C5:C68, "*Оснащение*", 'Факт расходов'!F5:F68)</f>
+        <f>SUMIF('Факт расходов'!C5:C73, "*Оснащение*", 'Факт расходов'!F5:F73)</f>
         <v/>
       </c>
       <c r="D36" s="50">
@@ -2713,11 +2844,11 @@
         </is>
       </c>
       <c r="B45" s="45">
-        <f>'Факт расходов'!E69</f>
+        <f>'Факт расходов'!E74</f>
         <v/>
       </c>
       <c r="C45" s="45">
-        <f>'Факт расходов'!F69</f>
+        <f>'Факт расходов'!F74</f>
         <v/>
       </c>
       <c r="D45" s="124">
@@ -2800,7 +2931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5319,44 +5450,44 @@
       <c r="N54" s="140" t="n"/>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="86" t="n">
+      <c r="A55" s="62" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="86" t="inlineStr">
+      <c r="B55" s="62" t="inlineStr">
         <is>
           <t>23.09.2026</t>
         </is>
       </c>
-      <c r="C55" s="82" t="inlineStr">
+      <c r="C55" s="44" t="inlineStr">
         <is>
           <t>Черновая отделка / Материалы</t>
         </is>
       </c>
-      <c r="D55" s="82" t="inlineStr">
+      <c r="D55" s="44" t="inlineStr">
         <is>
           <t>Штукатурка гипсовая Старатели 30кг 3шт (1515₽), перчатки, мешки 3шт (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E55" s="83" t="n">
+      <c r="E55" s="45" t="n">
         <v>1638</v>
       </c>
-      <c r="F55" s="84" t="n">
+      <c r="F55" s="46" t="n">
         <v>1638</v>
       </c>
-      <c r="G55" s="85">
+      <c r="G55" s="47">
         <f>E55-F55</f>
         <v/>
       </c>
-      <c r="H55" s="115">
+      <c r="H55" s="63">
         <f>IFERROR(G55/E55, 0)</f>
         <v/>
       </c>
-      <c r="I55" s="82" t="inlineStr">
+      <c r="I55" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="J55" s="82" t="inlineStr">
+      <c r="J55" s="44" t="inlineStr">
         <is>
           <t>Чек от 23.09.2026 15:55 (касса 72): штукатурка Старатели 30кг 3шт по 505₽=1515₽, перчатки х/б 13кл 27₽, мешки 3шт по 32₽=96₽</t>
         </is>
@@ -5367,44 +5498,44 @@
       <c r="N55" s="140" t="n"/>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="91" t="n">
+      <c r="A56" s="64" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="91" t="inlineStr">
+      <c r="B56" s="64" t="inlineStr">
         <is>
           <t>23.09.2026</t>
         </is>
       </c>
-      <c r="C56" s="88" t="inlineStr">
+      <c r="C56" s="49" t="inlineStr">
         <is>
           <t>Чистовая отделка / Материалы</t>
         </is>
       </c>
-      <c r="D56" s="88" t="inlineStr">
+      <c r="D56" s="49" t="inlineStr">
         <is>
           <t>Грунт-эмаль Luxens 3в1 белая 2.4кг (1492₽), щетка 5-рядная, кисть Dilwis 70мм (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E56" s="89" t="n">
+      <c r="E56" s="50" t="n">
         <v>1769</v>
       </c>
-      <c r="F56" s="90" t="n">
+      <c r="F56" s="51" t="n">
         <v>1769</v>
       </c>
-      <c r="G56" s="85">
+      <c r="G56" s="47">
         <f>E56-F56</f>
         <v/>
       </c>
-      <c r="H56" s="115">
+      <c r="H56" s="63">
         <f>IFERROR(G56/E56, 0)</f>
         <v/>
       </c>
-      <c r="I56" s="88" t="inlineStr">
+      <c r="I56" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="J56" s="88" t="inlineStr">
+      <c r="J56" s="49" t="inlineStr">
         <is>
           <t>Чек от 23.09.2026 16:10 (касса 75): грунт-эмаль Luxens 3в1 белая 2.4кг (1492₽), кисть Dilwis 70мм (171₽), щетка металл 260мм (106₽)</t>
         </is>
@@ -5415,44 +5546,44 @@
       <c r="N56" s="140" t="n"/>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="86" t="n">
+      <c r="A57" s="62" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="86" t="inlineStr">
+      <c r="B57" s="62" t="inlineStr">
         <is>
           <t>25.09.2026</t>
         </is>
       </c>
-      <c r="C57" s="82" t="inlineStr">
+      <c r="C57" s="44" t="inlineStr">
         <is>
           <t>Черновая отделка / Материалы</t>
         </is>
       </c>
-      <c r="D57" s="82" t="inlineStr">
+      <c r="D57" s="44" t="inlineStr">
         <is>
           <t>Профиль ППН 27х28х3000 3шт, профиль ПП 60х27 1шт, саморезы ПШС и ШСГД/ШСГМ (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E57" s="83" t="n">
+      <c r="E57" s="45" t="n">
         <v>911.7</v>
       </c>
-      <c r="F57" s="84" t="n">
+      <c r="F57" s="46" t="n">
         <v>911.7</v>
       </c>
-      <c r="G57" s="85">
+      <c r="G57" s="47">
         <f>E57-F57</f>
         <v/>
       </c>
-      <c r="H57" s="115">
+      <c r="H57" s="63">
         <f>IFERROR(G57/E57, 0)</f>
         <v/>
       </c>
-      <c r="I57" s="82" t="inlineStr">
+      <c r="I57" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="J57" s="82" t="inlineStr">
+      <c r="J57" s="44" t="inlineStr">
         <is>
           <t>Чек от 25.09.2026 08:18 (касса 78): профиль ППН 3шт (372₽), профиль ПП 1шт (193₽), саморезы оцинкованные и фосфатированные 1.122кг (346.70₽)</t>
         </is>
@@ -5463,44 +5594,44 @@
       <c r="N57" s="140" t="n"/>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="91" t="n">
+      <c r="A58" s="64" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="91" t="inlineStr">
+      <c r="B58" s="64" t="inlineStr">
         <is>
           <t>25.09.2026</t>
         </is>
       </c>
-      <c r="C58" s="88" t="inlineStr">
+      <c r="C58" s="49" t="inlineStr">
         <is>
           <t>Черновая отделка / Материалы</t>
         </is>
       </c>
-      <c r="D58" s="88" t="inlineStr">
+      <c r="D58" s="49" t="inlineStr">
         <is>
           <t>ГСП-Н3 Knauf влагост. 1500х600х12.5 2шт, штукатурка Старатели 30кг, профили 28х27 2шт и 60х27 1шт, перчатки (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E58" s="89" t="n">
+      <c r="E58" s="50" t="n">
         <v>1582</v>
       </c>
-      <c r="F58" s="90" t="n">
+      <c r="F58" s="51" t="n">
         <v>1582</v>
       </c>
-      <c r="G58" s="85">
+      <c r="G58" s="47">
         <f>E58-F58</f>
         <v/>
       </c>
-      <c r="H58" s="115">
+      <c r="H58" s="63">
         <f>IFERROR(G58/E58, 0)</f>
         <v/>
       </c>
-      <c r="I58" s="88" t="inlineStr">
+      <c r="I58" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="J58" s="88" t="inlineStr">
+      <c r="J58" s="49" t="inlineStr">
         <is>
           <t>Чек от 25.09.2026 15:53 (касса 76): ГСП влагост. Knauf 2шт (460₽), штукатурка Старатели 30кг (505₽), профиль ППН 28х27 2шт (282₽), профиль Knauf 60х27 (308₽), перчатки (27₽)</t>
         </is>
@@ -5511,44 +5642,44 @@
       <c r="N58" s="140" t="n"/>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="86" t="n">
+      <c r="A59" s="62" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="86" t="inlineStr">
+      <c r="B59" s="62" t="inlineStr">
         <is>
           <t>26.09.2026</t>
         </is>
       </c>
-      <c r="C59" s="82" t="inlineStr">
+      <c r="C59" s="44" t="inlineStr">
         <is>
           <t>Чистовая отделка / Материалы</t>
         </is>
       </c>
-      <c r="D59" s="82" t="inlineStr">
+      <c r="D59" s="44" t="inlineStr">
         <is>
           <t>Ламинат Kronostep Ultrastep Дуб Ночиолла 33 кл 10мм 24 упак./41.52м², подложка Monlid 3мм 9шт, плинтус белый 8см 20шт</t>
         </is>
       </c>
-      <c r="E59" s="83" t="n">
+      <c r="E59" s="45" t="n">
         <v>45551.52</v>
       </c>
-      <c r="F59" s="84" t="n">
+      <c r="F59" s="46" t="n">
         <v>41914.52</v>
       </c>
-      <c r="G59" s="85">
+      <c r="G59" s="47">
         <f>E59-F59</f>
         <v/>
       </c>
-      <c r="H59" s="115">
+      <c r="H59" s="63">
         <f>IFERROR(G59/E59, 0)</f>
         <v/>
       </c>
-      <c r="I59" s="82" t="inlineStr">
+      <c r="I59" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="J59" s="82" t="inlineStr">
+      <c r="J59" s="44" t="inlineStr">
         <is>
           <t>Чек от 26.09.2026 17:41: ламинат Дуб Ночиолла 24 упак. (32734.52₽ с учетом скидки -3637₽), подложка Monlid 3мм 9шт (4680₽), плинтус белый 80мм 20шт (4500₽). Скидка по промокоду -3 637.00 ₽</t>
         </is>
@@ -5559,44 +5690,44 @@
       <c r="N59" s="140" t="n"/>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="91" t="n">
+      <c r="A60" s="64" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="91" t="inlineStr">
+      <c r="B60" s="64" t="inlineStr">
         <is>
           <t>26.09.2026</t>
         </is>
       </c>
-      <c r="C60" s="88" t="inlineStr">
+      <c r="C60" s="49" t="inlineStr">
         <is>
           <t>Черновая отделка / Материалы</t>
         </is>
       </c>
-      <c r="D60" s="88" t="inlineStr">
+      <c r="D60" s="49" t="inlineStr">
         <is>
           <t>Грунт перекрывающий пятна Axton 1л, клей монтажный Kudo 2шт, валик нат. мех 110мм, макловица-мини (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E60" s="89" t="n">
+      <c r="E60" s="50" t="n">
         <v>1070</v>
       </c>
-      <c r="F60" s="90" t="n">
+      <c r="F60" s="51" t="n">
         <v>1070</v>
       </c>
-      <c r="G60" s="85">
+      <c r="G60" s="47">
         <f>E60-F60</f>
         <v/>
       </c>
-      <c r="H60" s="115">
+      <c r="H60" s="63">
         <f>IFERROR(G60/E60, 0)</f>
         <v/>
       </c>
-      <c r="I60" s="88" t="inlineStr">
+      <c r="I60" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="J60" s="88" t="inlineStr">
+      <c r="J60" s="49" t="inlineStr">
         <is>
           <t>Чек от 26.09.2026 17:40 (касса 76): грунт блокирующий пятна Axton 1л (427₽), клей монтажный Kudo 2шт (410₽), валик 110мм (96₽), макловица-мини (137₽)</t>
         </is>
@@ -5607,44 +5738,44 @@
       <c r="N60" s="140" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="86" t="n">
+      <c r="A61" s="62" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="86" t="inlineStr">
+      <c r="B61" s="62" t="inlineStr">
         <is>
           <t>27.09.2026</t>
         </is>
       </c>
-      <c r="C61" s="82" t="inlineStr">
+      <c r="C61" s="44" t="inlineStr">
         <is>
           <t>Инструмент и расходники</t>
         </is>
       </c>
-      <c r="D61" s="82" t="inlineStr">
+      <c r="D61" s="44" t="inlineStr">
         <is>
           <t>Расходные материалы и инструмент: швабра, тряпки 3шт, краска Olimp 0.9л, лента упак., саморезы, макловица, ножи 2шт, карандаш (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E61" s="83" t="n">
+      <c r="E61" s="45" t="n">
         <v>1707.17</v>
       </c>
-      <c r="F61" s="84" t="n">
+      <c r="F61" s="46" t="n">
         <v>1707.17</v>
       </c>
-      <c r="G61" s="85">
+      <c r="G61" s="47">
         <f>E61-F61</f>
         <v/>
       </c>
-      <c r="H61" s="115">
+      <c r="H61" s="63">
         <f>IFERROR(G61/E61, 0)</f>
         <v/>
       </c>
-      <c r="I61" s="82" t="inlineStr">
+      <c r="I61" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="J61" s="82" t="inlineStr">
+      <c r="J61" s="44" t="inlineStr">
         <is>
           <t>Чек от 27.09.2026 09:53 (касса 72): швабра In Loran (426₽), тряпки 3шт (120₽), краска Olimp акрил 0.9л (294₽), клейкая лента Axton (101₽), саморезы 0.314кг (140.67₽), макловица (137₽), ножи 2шт (160₽), карандаш (50₽) и др.</t>
         </is>
@@ -5655,44 +5786,44 @@
       <c r="N61" s="140" t="n"/>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="91" t="n">
+      <c r="A62" s="64" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="91" t="inlineStr">
+      <c r="B62" s="64" t="inlineStr">
         <is>
           <t>27.09.2026</t>
         </is>
       </c>
-      <c r="C62" s="88" t="inlineStr">
+      <c r="C62" s="49" t="inlineStr">
         <is>
           <t>Электрика / Материалы</t>
         </is>
       </c>
-      <c r="D62" s="88" t="inlineStr">
+      <c r="D62" s="49" t="inlineStr">
         <is>
           <t>Электротовары (расходники/комплектующие электрики, ул. Коминтерна 26)</t>
         </is>
       </c>
-      <c r="E62" s="89" t="n">
+      <c r="E62" s="50" t="n">
         <v>190</v>
       </c>
-      <c r="F62" s="90" t="n">
+      <c r="F62" s="51" t="n">
         <v>190</v>
       </c>
-      <c r="G62" s="85">
+      <c r="G62" s="47">
         <f>E62-F62</f>
         <v/>
       </c>
-      <c r="H62" s="115">
+      <c r="H62" s="63">
         <f>IFERROR(G62/E62, 0)</f>
         <v/>
       </c>
-      <c r="I62" s="88" t="inlineStr">
+      <c r="I62" s="49" t="inlineStr">
         <is>
           <t>Магазин «Электротовары» (Коминтерна 26)</t>
         </is>
       </c>
-      <c r="J62" s="88" t="inlineStr">
+      <c r="J62" s="49" t="inlineStr">
         <is>
           <t>Слип терминала Сбербанк от 27.09.2026 13:08 (карта *6730): покупка электротоваров на ул. Коминтерна 26</t>
         </is>
@@ -5703,44 +5834,44 @@
       <c r="N62" s="140" t="n"/>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="86" t="n">
+      <c r="A63" s="62" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="86" t="inlineStr">
+      <c r="B63" s="62" t="inlineStr">
         <is>
           <t>27.09.2026</t>
         </is>
       </c>
-      <c r="C63" s="82" t="inlineStr">
+      <c r="C63" s="44" t="inlineStr">
         <is>
           <t>Инструмент и расходники</t>
         </is>
       </c>
-      <c r="D63" s="82" t="inlineStr">
+      <c r="D63" s="44" t="inlineStr">
         <is>
           <t>Клинья для плитки СВП 32х8х9мм 50шт (Магазин крепежа, Мосина 29)</t>
         </is>
       </c>
-      <c r="E63" s="83" t="n">
+      <c r="E63" s="45" t="n">
         <v>210</v>
       </c>
-      <c r="F63" s="84" t="n">
+      <c r="F63" s="46" t="n">
         <v>210</v>
       </c>
-      <c r="G63" s="85">
+      <c r="G63" s="47">
         <f>E63-F63</f>
         <v/>
       </c>
-      <c r="H63" s="115">
+      <c r="H63" s="63">
         <f>IFERROR(G63/E63, 0)</f>
         <v/>
       </c>
-      <c r="I63" s="82" t="inlineStr">
+      <c r="I63" s="44" t="inlineStr">
         <is>
           <t>ИП Звягинцева С.Н. (Магазин крепежа)</t>
         </is>
       </c>
-      <c r="J63" s="82" t="inlineStr">
+      <c r="J63" s="44" t="inlineStr">
         <is>
           <t>Чек от 27.09.2026 13:23: клинья для плитки 50шт (210₽)</t>
         </is>
@@ -5751,44 +5882,44 @@
       <c r="N63" s="140" t="n"/>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="91" t="n">
+      <c r="A64" s="64" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="91" t="inlineStr">
+      <c r="B64" s="64" t="inlineStr">
         <is>
           <t>27.09.2026</t>
         </is>
       </c>
-      <c r="C64" s="88" t="inlineStr">
+      <c r="C64" s="49" t="inlineStr">
         <is>
           <t>Логистика и доставка</t>
         </is>
       </c>
-      <c r="D64" s="88" t="inlineStr">
+      <c r="D64" s="49" t="inlineStr">
         <is>
           <t>Такси (оперативная доставка / подвоз материалов на объект)</t>
         </is>
       </c>
-      <c r="E64" s="89" t="n">
+      <c r="E64" s="50" t="n">
         <v>850</v>
       </c>
-      <c r="F64" s="90" t="n">
+      <c r="F64" s="51" t="n">
         <v>850</v>
       </c>
-      <c r="G64" s="85">
+      <c r="G64" s="47">
         <f>E64-F64</f>
         <v/>
       </c>
-      <c r="H64" s="115">
+      <c r="H64" s="63">
         <f>IFERROR(G64/E64, 0)</f>
         <v/>
       </c>
-      <c r="I64" s="88" t="inlineStr">
+      <c r="I64" s="49" t="inlineStr">
         <is>
           <t>Такси (Яндекс Go)</t>
         </is>
       </c>
-      <c r="J64" s="88" t="inlineStr">
+      <c r="J64" s="49" t="inlineStr">
         <is>
           <t>Оперативная доставка материалов на объект ул. Фрунзе 17</t>
         </is>
@@ -5799,44 +5930,44 @@
       <c r="N64" s="140" t="n"/>
     </row>
     <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="86" t="n">
+      <c r="A65" s="62" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="86" t="inlineStr">
+      <c r="B65" s="62" t="inlineStr">
         <is>
           <t>27.09.2026</t>
         </is>
       </c>
-      <c r="C65" s="82" t="inlineStr">
+      <c r="C65" s="44" t="inlineStr">
         <is>
           <t>Чистовая отделка / Работы</t>
         </is>
       </c>
-      <c r="D65" s="82" t="inlineStr">
+      <c r="D65" s="44" t="inlineStr">
         <is>
           <t>Работы плиточника (аванс / подготовка к укладке плитки в санузле)</t>
         </is>
       </c>
-      <c r="E65" s="83" t="n">
+      <c r="E65" s="45" t="n">
         <v>1700</v>
       </c>
-      <c r="F65" s="84" t="n">
+      <c r="F65" s="46" t="n">
         <v>1700</v>
       </c>
-      <c r="G65" s="85">
+      <c r="G65" s="47">
         <f>E65-F65</f>
         <v/>
       </c>
-      <c r="H65" s="115">
+      <c r="H65" s="63">
         <f>IFERROR(G65/E65, 0)</f>
         <v/>
       </c>
-      <c r="I65" s="82" t="inlineStr">
+      <c r="I65" s="44" t="inlineStr">
         <is>
           <t>Плиточник (мастер)</t>
         </is>
       </c>
-      <c r="J65" s="82" t="inlineStr">
+      <c r="J65" s="44" t="inlineStr">
         <is>
           <t>Оплата плиточнику за работы в санузле</t>
         </is>
@@ -5847,44 +5978,44 @@
       <c r="N65" s="140" t="n"/>
     </row>
     <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="91" t="n">
+      <c r="A66" s="64" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="91" t="inlineStr">
+      <c r="B66" s="64" t="inlineStr">
         <is>
           <t>27.09.2026</t>
         </is>
       </c>
-      <c r="C66" s="88" t="inlineStr">
+      <c r="C66" s="49" t="inlineStr">
         <is>
           <t>Черновая отделка / Работы</t>
         </is>
       </c>
-      <c r="D66" s="88" t="inlineStr">
+      <c r="D66" s="49" t="inlineStr">
         <is>
           <t>Работы плиточника: заливка стяжки пола в санузле/туалете</t>
         </is>
       </c>
-      <c r="E66" s="89" t="n">
+      <c r="E66" s="50" t="n">
         <v>3500</v>
       </c>
-      <c r="F66" s="90" t="n">
+      <c r="F66" s="51" t="n">
         <v>3300</v>
       </c>
-      <c r="G66" s="85">
+      <c r="G66" s="47">
         <f>E66-F66</f>
         <v/>
       </c>
-      <c r="H66" s="115">
+      <c r="H66" s="63">
         <f>IFERROR(G66/E66, 0)</f>
         <v/>
       </c>
-      <c r="I66" s="88" t="inlineStr">
+      <c r="I66" s="49" t="inlineStr">
         <is>
           <t>Плиточник (мастер)</t>
         </is>
       </c>
-      <c r="J66" s="88" t="inlineStr">
+      <c r="J66" s="49" t="inlineStr">
         <is>
           <t>Заливка стяжки пола в санузле по маякам (пескобетон М300 + фибра + Cemfix)</t>
         </is>
@@ -5895,44 +6026,44 @@
       <c r="N66" s="140" t="n"/>
     </row>
     <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="86" t="n">
+      <c r="A67" s="62" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="86" t="inlineStr">
+      <c r="B67" s="62" t="inlineStr">
         <is>
           <t>27.09.2026</t>
         </is>
       </c>
-      <c r="C67" s="82" t="inlineStr">
+      <c r="C67" s="44" t="inlineStr">
         <is>
           <t>Черновая отделка / Работы</t>
         </is>
       </c>
-      <c r="D67" s="82" t="inlineStr">
+      <c r="D67" s="44" t="inlineStr">
         <is>
           <t>Оплата за штукатурку туалета (санузла) под 90° под ванну и плитку</t>
         </is>
       </c>
-      <c r="E67" s="83" t="n">
+      <c r="E67" s="45" t="n">
         <v>15000</v>
       </c>
-      <c r="F67" s="84" t="n">
+      <c r="F67" s="46" t="n">
         <v>13400</v>
       </c>
-      <c r="G67" s="85">
+      <c r="G67" s="47">
         <f>E67-F67</f>
         <v/>
       </c>
-      <c r="H67" s="115">
+      <c r="H67" s="63">
         <f>IFERROR(G67/E67, 0)</f>
         <v/>
       </c>
-      <c r="I67" s="82" t="inlineStr">
+      <c r="I67" s="44" t="inlineStr">
         <is>
           <t>Елена (мастер-отделочник)</t>
         </is>
       </c>
-      <c r="J67" s="82" t="inlineStr">
+      <c r="J67" s="44" t="inlineStr">
         <is>
           <t>Штукатурка стен санузла по маякам с выведением геометрии под 90° для монтажа ванны (выгода 1 600 ₽)</t>
         </is>
@@ -5943,44 +6074,44 @@
       <c r="N67" s="140" t="n"/>
     </row>
     <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="91" t="n">
+      <c r="A68" s="64" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="91" t="inlineStr">
+      <c r="B68" s="64" t="inlineStr">
         <is>
           <t>27.09.2026</t>
         </is>
       </c>
-      <c r="C68" s="88" t="inlineStr">
+      <c r="C68" s="49" t="inlineStr">
         <is>
           <t>Сантехника / Материалы</t>
         </is>
       </c>
-      <c r="D68" s="88" t="inlineStr">
+      <c r="D68" s="49" t="inlineStr">
         <is>
           <t>Два крана на радиаторы отопления (запорно-регулировочные краны)</t>
         </is>
       </c>
-      <c r="E68" s="89" t="n">
+      <c r="E68" s="50" t="n">
         <v>1100</v>
       </c>
-      <c r="F68" s="90" t="n">
+      <c r="F68" s="51" t="n">
         <v>1100</v>
       </c>
-      <c r="G68" s="85">
+      <c r="G68" s="47">
         <f>E68-F68</f>
         <v/>
       </c>
-      <c r="H68" s="115">
+      <c r="H68" s="63">
         <f>IFERROR(G68/E68, 0)</f>
         <v/>
       </c>
-      <c r="I68" s="88" t="inlineStr">
+      <c r="I68" s="49" t="inlineStr">
         <is>
           <t>Сантехмаркет / Хозмаг</t>
         </is>
       </c>
-      <c r="J68" s="88" t="inlineStr">
+      <c r="J68" s="49" t="inlineStr">
         <is>
           <t>2 крана для радиаторов отопления (замена / обвязка приборов)</t>
         </is>
@@ -5990,225 +6121,277 @@
       <c r="M68" s="140" t="n"/>
       <c r="N68" s="140" t="n"/>
     </row>
-    <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="238" t="n"/>
-      <c r="B69" s="238" t="n"/>
-      <c r="C69" s="238" t="n"/>
-      <c r="D69" s="239" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДОВ:</t>
-        </is>
-      </c>
-      <c r="E69" s="171">
-        <f>SUM(E5:E68)</f>
-        <v/>
-      </c>
-      <c r="F69" s="171">
-        <f>SUM(F5:F68)</f>
-        <v/>
-      </c>
-      <c r="G69" s="56">
-        <f>SUM(G5:G68)</f>
-        <v/>
-      </c>
-      <c r="H69" s="139">
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="91" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="91" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="C69" s="88" t="inlineStr">
+        <is>
+          <t>Сантехника / Материалы</t>
+        </is>
+      </c>
+      <c r="D69" s="88" t="inlineStr">
+        <is>
+          <t>Материалы сантехники и оснастка: труба ПП арм. D20 2шт, отвод 50х15°, гибкий соединитель D50, биты PH2 (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="E69" s="89" t="n">
+        <v>550</v>
+      </c>
+      <c r="F69" s="90" t="n">
+        <v>550</v>
+      </c>
+      <c r="G69" s="85">
+        <f>E69-F69</f>
+        <v/>
+      </c>
+      <c r="H69" s="105">
         <f>IFERROR(G69/E69, 0)</f>
         <v/>
       </c>
-      <c r="I69" s="238" t="n"/>
-      <c r="J69" s="238" t="n"/>
+      <c r="I69" s="88" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J69" s="88" t="inlineStr">
+        <is>
+          <t>Чек от 29.09.2026 08:15 (касса 74): труба ПП D20 2шт (206₽), отвод 50х15° (50₽), гибкий соединитель D50 (114₽), биты Rage PH2 70мм (180₽)</t>
+        </is>
+      </c>
       <c r="K69" s="140" t="n"/>
       <c r="L69" s="140" t="n"/>
       <c r="M69" s="140" t="n"/>
       <c r="N69" s="140" t="n"/>
     </row>
-    <row r="70">
-      <c r="A70" s="140" t="n"/>
-      <c r="B70" s="140" t="n"/>
-      <c r="C70" s="140" t="n"/>
-      <c r="D70" s="140" t="n"/>
-      <c r="E70" s="140" t="n"/>
-      <c r="F70" s="140" t="n"/>
-      <c r="G70" s="140" t="n"/>
-      <c r="H70" s="140" t="n"/>
-      <c r="I70" s="140" t="n"/>
-      <c r="J70" s="140" t="n"/>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="86" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="86" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="C70" s="82" t="inlineStr">
+        <is>
+          <t>Чистовая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D70" s="82" t="inlineStr">
+        <is>
+          <t>Керамогранит Calacatta superwhite 60х120 (добор 2 упак. / 2.88 м²)</t>
+        </is>
+      </c>
+      <c r="E70" s="83" t="n">
+        <v>5876</v>
+      </c>
+      <c r="F70" s="84" t="n">
+        <v>5876</v>
+      </c>
+      <c r="G70" s="85">
+        <f>E70-F70</f>
+        <v/>
+      </c>
+      <c r="H70" s="105">
+        <f>IFERROR(G70/E70, 0)</f>
+        <v/>
+      </c>
+      <c r="I70" s="82" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J70" s="82" t="inlineStr">
+        <is>
+          <t>Чек от 29.09.2026 08:07 (касса 73, заказ 2161260912448255): керамогранит Calacatta superwhite 60х120 2 упак. по 2938₽ = 5876₽</t>
+        </is>
+      </c>
       <c r="K70" s="140" t="n"/>
       <c r="L70" s="140" t="n"/>
       <c r="M70" s="140" t="n"/>
       <c r="N70" s="140" t="n"/>
     </row>
-    <row r="71">
-      <c r="A71" s="140" t="n"/>
-      <c r="B71" s="140" t="n"/>
-      <c r="C71" s="140" t="n"/>
-      <c r="D71" s="140" t="n"/>
-      <c r="E71" s="140" t="n"/>
-      <c r="F71" s="140" t="n"/>
-      <c r="G71" s="140" t="n"/>
-      <c r="H71" s="140" t="n"/>
-      <c r="I71" s="140" t="n"/>
-      <c r="J71" s="140" t="n"/>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="91" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="91" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="C71" s="88" t="inlineStr">
+        <is>
+          <t>Инструмент и расходники</t>
+        </is>
+      </c>
+      <c r="D71" s="88" t="inlineStr">
+        <is>
+          <t>Уголки для плитки (Михаил)</t>
+        </is>
+      </c>
+      <c r="E71" s="89" t="n">
+        <v>260</v>
+      </c>
+      <c r="F71" s="90" t="n">
+        <v>260</v>
+      </c>
+      <c r="G71" s="85">
+        <f>E71-F71</f>
+        <v/>
+      </c>
+      <c r="H71" s="105">
+        <f>IFERROR(G71/E71, 0)</f>
+        <v/>
+      </c>
+      <c r="I71" s="88" t="inlineStr">
+        <is>
+          <t>Михаил (мастер/плиточник)</t>
+        </is>
+      </c>
+      <c r="J71" s="88" t="inlineStr">
+        <is>
+          <t>Оплата Михаилу за уголки для плитки в санузле (260 ₽)</t>
+        </is>
+      </c>
       <c r="K71" s="140" t="n"/>
       <c r="L71" s="140" t="n"/>
       <c r="M71" s="140" t="n"/>
       <c r="N71" s="140" t="n"/>
     </row>
-    <row r="72">
-      <c r="A72" s="140" t="n"/>
-      <c r="B72" s="140" t="n"/>
-      <c r="C72" s="140" t="n"/>
-      <c r="D72" s="140" t="n"/>
-      <c r="E72" s="140" t="n"/>
-      <c r="F72" s="140" t="n"/>
-      <c r="G72" s="140" t="n"/>
-      <c r="H72" s="140" t="n"/>
-      <c r="I72" s="140" t="n"/>
-      <c r="J72" s="140" t="n"/>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="86" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="86" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="C72" s="82" t="inlineStr">
+        <is>
+          <t>Сантехника / Работы</t>
+        </is>
+      </c>
+      <c r="D72" s="82" t="inlineStr">
+        <is>
+          <t>Работы сантехников (разводка/монтаж узлов водоснабжения и канализации)</t>
+        </is>
+      </c>
+      <c r="E72" s="83" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F72" s="84" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G72" s="85">
+        <f>E72-F72</f>
+        <v/>
+      </c>
+      <c r="H72" s="105">
+        <f>IFERROR(G72/E72, 0)</f>
+        <v/>
+      </c>
+      <c r="I72" s="82" t="inlineStr">
+        <is>
+          <t>Сантехники (мастера)</t>
+        </is>
+      </c>
+      <c r="J72" s="82" t="inlineStr">
+        <is>
+          <t>Оплата работы сантехников за разводку/монтаж в санузле (3 000 ₽)</t>
+        </is>
+      </c>
       <c r="K72" s="140" t="n"/>
       <c r="L72" s="140" t="n"/>
       <c r="M72" s="140" t="n"/>
       <c r="N72" s="140" t="n"/>
     </row>
-    <row r="73">
-      <c r="A73" s="140" t="n"/>
-      <c r="B73" s="140" t="n"/>
-      <c r="C73" s="140" t="n"/>
-      <c r="D73" s="140" t="n"/>
-      <c r="E73" s="140" t="n"/>
-      <c r="F73" s="140" t="n"/>
-      <c r="G73" s="140" t="n"/>
-      <c r="H73" s="140" t="n"/>
-      <c r="I73" s="140" t="n"/>
-      <c r="J73" s="140" t="n"/>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="91" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="91" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="C73" s="88" t="inlineStr">
+        <is>
+          <t>Газ / Работы и материалы</t>
+        </is>
+      </c>
+      <c r="D73" s="88" t="inlineStr">
+        <is>
+          <t>Работы газовщика: перенос / срезка / перемонтаж газовой трубы на кухне</t>
+        </is>
+      </c>
+      <c r="E73" s="89" t="n">
+        <v>7300</v>
+      </c>
+      <c r="F73" s="90" t="n">
+        <v>7300</v>
+      </c>
+      <c r="G73" s="85">
+        <f>E73-F73</f>
+        <v/>
+      </c>
+      <c r="H73" s="105">
+        <f>IFERROR(G73/E73, 0)</f>
+        <v/>
+      </c>
+      <c r="I73" s="88" t="inlineStr">
+        <is>
+          <t>Газовщик (мастер / горгаз)</t>
+        </is>
+      </c>
+      <c r="J73" s="88" t="inlineStr">
+        <is>
+          <t>Оплата газовщику за перенос/срезку и обвязку газовой трубы на кухне (7 300 ₽)</t>
+        </is>
+      </c>
       <c r="K73" s="140" t="n"/>
       <c r="L73" s="140" t="n"/>
       <c r="M73" s="140" t="n"/>
       <c r="N73" s="140" t="n"/>
     </row>
-    <row r="74">
-      <c r="A74" s="140" t="n"/>
-      <c r="B74" s="140" t="n"/>
-      <c r="C74" s="140" t="n"/>
-      <c r="D74" s="140" t="n"/>
-      <c r="E74" s="140" t="n"/>
-      <c r="F74" s="140" t="n"/>
-      <c r="G74" s="140" t="n"/>
-      <c r="H74" s="140" t="n"/>
-      <c r="I74" s="140" t="n"/>
-      <c r="J74" s="140" t="n"/>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="284" t="n"/>
+      <c r="B74" s="284" t="n"/>
+      <c r="C74" s="285" t="n"/>
+      <c r="D74" s="239" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДОВ:</t>
+        </is>
+      </c>
+      <c r="E74" s="171">
+        <f>SUM(E5:E73)</f>
+        <v/>
+      </c>
+      <c r="F74" s="171">
+        <f>SUM(F5:F73)</f>
+        <v/>
+      </c>
+      <c r="G74" s="56">
+        <f>SUM(G5:G73)</f>
+        <v/>
+      </c>
+      <c r="H74" s="66">
+        <f>IFERROR(G74/E74, 0)</f>
+        <v/>
+      </c>
+      <c r="I74" s="285" t="n"/>
+      <c r="J74" s="285" t="n"/>
       <c r="K74" s="140" t="n"/>
       <c r="L74" s="140" t="n"/>
       <c r="M74" s="140" t="n"/>
       <c r="N74" s="140" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="140" t="n"/>
-      <c r="B75" s="140" t="n"/>
-      <c r="C75" s="140" t="n"/>
-      <c r="D75" s="140" t="n"/>
-      <c r="E75" s="140" t="n"/>
-      <c r="F75" s="140" t="n"/>
-      <c r="G75" s="140" t="n"/>
-      <c r="H75" s="140" t="n"/>
-      <c r="I75" s="140" t="n"/>
-      <c r="J75" s="140" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="140" t="n"/>
-      <c r="B76" s="140" t="n"/>
-      <c r="C76" s="140" t="n"/>
-      <c r="D76" s="140" t="n"/>
-      <c r="E76" s="140" t="n"/>
-      <c r="F76" s="140" t="n"/>
-      <c r="G76" s="140" t="n"/>
-      <c r="H76" s="140" t="n"/>
-      <c r="I76" s="140" t="n"/>
-      <c r="J76" s="140" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="140" t="n"/>
-      <c r="B77" s="140" t="n"/>
-      <c r="C77" s="140" t="n"/>
-      <c r="D77" s="140" t="n"/>
-      <c r="E77" s="140" t="n"/>
-      <c r="F77" s="140" t="n"/>
-      <c r="G77" s="140" t="n"/>
-      <c r="H77" s="140" t="n"/>
-      <c r="I77" s="140" t="n"/>
-      <c r="J77" s="140" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="140" t="n"/>
-      <c r="B78" s="140" t="n"/>
-      <c r="C78" s="140" t="n"/>
-      <c r="D78" s="140" t="n"/>
-      <c r="E78" s="140" t="n"/>
-      <c r="F78" s="140" t="n"/>
-      <c r="G78" s="140" t="n"/>
-      <c r="H78" s="140" t="n"/>
-      <c r="I78" s="140" t="n"/>
-      <c r="J78" s="140" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="140" t="n"/>
-      <c r="B79" s="140" t="n"/>
-      <c r="C79" s="140" t="n"/>
-      <c r="D79" s="140" t="n"/>
-      <c r="E79" s="140" t="n"/>
-      <c r="F79" s="140" t="n"/>
-      <c r="G79" s="140" t="n"/>
-      <c r="H79" s="140" t="n"/>
-      <c r="I79" s="140" t="n"/>
-      <c r="J79" s="140" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="140" t="n"/>
-      <c r="B80" s="140" t="n"/>
-      <c r="C80" s="140" t="n"/>
-      <c r="D80" s="140" t="n"/>
-      <c r="E80" s="140" t="n"/>
-      <c r="F80" s="140" t="n"/>
-      <c r="G80" s="140" t="n"/>
-      <c r="H80" s="140" t="n"/>
-      <c r="I80" s="140" t="n"/>
-      <c r="J80" s="140" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="140" t="n"/>
-      <c r="B81" s="140" t="n"/>
-      <c r="C81" s="140" t="n"/>
-      <c r="D81" s="140" t="n"/>
-      <c r="E81" s="140" t="n"/>
-      <c r="F81" s="140" t="n"/>
-      <c r="G81" s="140" t="n"/>
-      <c r="H81" s="140" t="n"/>
-      <c r="I81" s="140" t="n"/>
-      <c r="J81" s="140" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="140" t="n"/>
-      <c r="B82" s="140" t="n"/>
-      <c r="C82" s="140" t="n"/>
-      <c r="D82" s="140" t="n"/>
-      <c r="E82" s="140" t="n"/>
-      <c r="F82" s="140" t="n"/>
-      <c r="G82" s="140" t="n"/>
-      <c r="H82" s="140" t="n"/>
-      <c r="I82" s="140" t="n"/>
-      <c r="J82" s="140" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="140" t="n"/>
-      <c r="B83" s="140" t="n"/>
-      <c r="C83" s="140" t="n"/>
-      <c r="D83" s="140" t="n"/>
-      <c r="E83" s="140" t="n"/>
-      <c r="F83" s="140" t="n"/>
-      <c r="G83" s="140" t="n"/>
-      <c r="H83" s="140" t="n"/>
-      <c r="I83" s="140" t="n"/>
-      <c r="J83" s="140" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6709,7 +6892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6811,9 +6994,9 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="242" t="n"/>
-      <c r="B5" s="242" t="inlineStr">
-        <is>
-          <t>🛁 БЛОК 1: СТРОИТЕЛЬНЫЕ И ЧИСТОВЫЕ МАТЕРИАЛЫ «ЛЕМАНА ПРО» (23 ЧЕКА)</t>
+      <c r="B5" s="252" t="inlineStr">
+        <is>
+          <t>🛁 БЛОК 1: СТРОИТЕЛЬНЫЕ И ЧИСТОВЫЕ МАТЕРИАЛЫ «ЛЕМАНА ПРО» (25 ЧЕКОВ)</t>
         </is>
       </c>
       <c r="C5" s="242" t="n"/>
@@ -6828,50 +7011,50 @@
       <c r="L5" s="242" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="91" t="n">
+      <c r="A6" s="86" t="n">
         <v>8</v>
       </c>
-      <c r="B6" s="88" t="inlineStr">
+      <c r="B6" s="82" t="inlineStr">
         <is>
           <t>Расходники</t>
         </is>
       </c>
-      <c r="C6" s="88" t="inlineStr">
+      <c r="C6" s="82" t="inlineStr">
         <is>
           <t>Пылесос</t>
         </is>
       </c>
-      <c r="D6" s="88" t="inlineStr">
+      <c r="D6" s="82" t="inlineStr">
         <is>
           <t>Мешки для пылесоса синт. 12л (5 шт) — Леруа/Лемана</t>
         </is>
       </c>
-      <c r="E6" s="91" t="inlineStr">
+      <c r="E6" s="86" t="inlineStr">
         <is>
           <t>4607086338088</t>
         </is>
       </c>
-      <c r="F6" s="91" t="inlineStr">
+      <c r="F6" s="86" t="inlineStr">
         <is>
           <t>упак.</t>
         </is>
       </c>
-      <c r="G6" s="243" t="n">
+      <c r="G6" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="89" t="n">
+      <c r="H6" s="83" t="n">
         <v>717</v>
       </c>
-      <c r="I6" s="90">
+      <c r="I6" s="84">
         <f>G6*H6</f>
         <v/>
       </c>
-      <c r="J6" s="88" t="inlineStr">
+      <c r="J6" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K6" s="244">
+      <c r="K6" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=мешки+для+пылесоса+12л", "Открыть ↗")</f>
         <v/>
       </c>
@@ -6882,50 +7065,50 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="86" t="n">
+      <c r="A7" s="91" t="n">
         <v>9</v>
       </c>
-      <c r="B7" s="82" t="inlineStr">
+      <c r="B7" s="88" t="inlineStr">
         <is>
           <t>Инструмент</t>
         </is>
       </c>
-      <c r="C7" s="82" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="D7" s="82" t="inlineStr">
+      <c r="D7" s="88" t="inlineStr">
         <is>
           <t>Лом-гвоздодер, мешки 15шт, лента, перчатки 6п, опрыскиватель</t>
         </is>
       </c>
-      <c r="E7" s="86" t="inlineStr">
+      <c r="E7" s="91" t="inlineStr">
         <is>
           <t>4603333000001</t>
         </is>
       </c>
-      <c r="F7" s="86" t="inlineStr">
+      <c r="F7" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G7" s="245" t="n">
+      <c r="G7" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="83" t="n">
+      <c r="H7" s="89" t="n">
         <v>1830</v>
       </c>
-      <c r="I7" s="84">
+      <c r="I7" s="90">
         <f>G7*H7</f>
         <v/>
       </c>
-      <c r="J7" s="82" t="inlineStr">
+      <c r="J7" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K7" s="244">
+      <c r="K7" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=лом+гвоздодер", "Открыть ↗")</f>
         <v/>
       </c>
@@ -6936,50 +7119,50 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="91" t="n">
+      <c r="A8" s="86" t="n">
         <v>25</v>
       </c>
-      <c r="B8" s="88" t="inlineStr">
+      <c r="B8" s="82" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C8" s="88" t="inlineStr">
+      <c r="C8" s="82" t="inlineStr">
         <is>
           <t>Шпатлевка / Грунт</t>
         </is>
       </c>
-      <c r="D8" s="88" t="inlineStr">
+      <c r="D8" s="82" t="inlineStr">
         <is>
           <t>Материалы для зачистки и грунтования (шпатлевка 20кг, грунт 10л, СТ99, фильтр Rommer)</t>
         </is>
       </c>
-      <c r="E8" s="91" t="inlineStr">
+      <c r="E8" s="86" t="inlineStr">
         <is>
           <t>3276006224277</t>
         </is>
       </c>
-      <c r="F8" s="91" t="inlineStr">
+      <c r="F8" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G8" s="243" t="n">
+      <c r="G8" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="89" t="n">
+      <c r="H8" s="83" t="n">
         <v>4803.6</v>
       </c>
-      <c r="I8" s="90">
+      <c r="I8" s="84">
         <f>G8*H8</f>
         <v/>
       </c>
-      <c r="J8" s="88" t="inlineStr">
+      <c r="J8" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K8" s="244">
+      <c r="K8" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=грунт+axton+10л", "Открыть ↗")</f>
         <v/>
       </c>
@@ -6990,50 +7173,50 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="86" t="n">
+      <c r="A9" s="91" t="n">
         <v>26</v>
       </c>
-      <c r="B9" s="82" t="inlineStr">
+      <c r="B9" s="88" t="inlineStr">
         <is>
           <t>Инструмент</t>
         </is>
       </c>
-      <c r="C9" s="82" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
         <is>
           <t>Ёмкости</t>
         </is>
       </c>
-      <c r="D9" s="82" t="inlineStr">
+      <c r="D9" s="88" t="inlineStr">
         <is>
           <t>Ведро строительное круглое 20 л (2 шт.)</t>
         </is>
       </c>
-      <c r="E9" s="86" t="inlineStr">
+      <c r="E9" s="91" t="inlineStr">
         <is>
           <t>4610008470475</t>
         </is>
       </c>
-      <c r="F9" s="86" t="inlineStr">
+      <c r="F9" s="91" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G9" s="245" t="n">
+      <c r="G9" s="255" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="83" t="n">
+      <c r="H9" s="89" t="n">
         <v>128</v>
       </c>
-      <c r="I9" s="84">
+      <c r="I9" s="90">
         <f>G9*H9</f>
         <v/>
       </c>
-      <c r="J9" s="82" t="inlineStr">
+      <c r="J9" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K9" s="244">
+      <c r="K9" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=ведро+строительное+20л", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7044,50 +7227,50 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="91" t="n">
+      <c r="A10" s="86" t="n">
         <v>28</v>
       </c>
-      <c r="B10" s="88" t="inlineStr">
+      <c r="B10" s="82" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C10" s="88" t="inlineStr">
+      <c r="C10" s="82" t="inlineStr">
         <is>
           <t>Шпатлевка / Шпатели</t>
         </is>
       </c>
-      <c r="D10" s="88" t="inlineStr">
+      <c r="D10" s="82" t="inlineStr">
         <is>
           <t>Материалы для подготовки стен (грунт Axton 10л 4шт, шпатлевка 20кг 2шт, шпатели, мешки)</t>
         </is>
       </c>
-      <c r="E10" s="91" t="inlineStr">
+      <c r="E10" s="86" t="inlineStr">
         <is>
           <t>4601745004252</t>
         </is>
       </c>
-      <c r="F10" s="91" t="inlineStr">
+      <c r="F10" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G10" s="243" t="n">
+      <c r="G10" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="89" t="n">
+      <c r="H10" s="83" t="n">
         <v>3308</v>
       </c>
-      <c r="I10" s="90">
+      <c r="I10" s="84">
         <f>G10*H10</f>
         <v/>
       </c>
-      <c r="J10" s="88" t="inlineStr">
+      <c r="J10" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K10" s="244">
+      <c r="K10" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=шпатлевка+старатели+20кг", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7098,50 +7281,50 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="86" t="n">
+      <c r="A11" s="91" t="n">
         <v>30</v>
       </c>
-      <c r="B11" s="82" t="inlineStr">
+      <c r="B11" s="88" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C11" s="82" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
         <is>
           <t>Штукатурка / Бетонконтакт</t>
         </is>
       </c>
-      <c r="D11" s="82" t="inlineStr">
+      <c r="D11" s="88" t="inlineStr">
         <is>
           <t>Материалы штукатурки и шпаклёвки (Бетонконтакт 12кг 3шт, финиш 5шт, штукатурка 3шт, правило, углы)</t>
         </is>
       </c>
-      <c r="E11" s="86" t="inlineStr">
+      <c r="E11" s="91" t="inlineStr">
         <is>
           <t>4607017518816</t>
         </is>
       </c>
-      <c r="F11" s="86" t="inlineStr">
+      <c r="F11" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G11" s="245" t="n">
+      <c r="G11" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="83" t="n">
+      <c r="H11" s="89" t="n">
         <v>8162</v>
       </c>
-      <c r="I11" s="84">
+      <c r="I11" s="90">
         <f>G11*H11</f>
         <v/>
       </c>
-      <c r="J11" s="82" t="inlineStr">
+      <c r="J11" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K11" s="244">
+      <c r="K11" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=бетонконтакт+axton+12кг", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7152,50 +7335,50 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="91" t="n">
+      <c r="A12" s="86" t="n">
         <v>32</v>
       </c>
-      <c r="B12" s="88" t="inlineStr">
+      <c r="B12" s="82" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C12" s="88" t="inlineStr">
+      <c r="C12" s="82" t="inlineStr">
         <is>
           <t>Шпаклёвка</t>
         </is>
       </c>
-      <c r="D12" s="88" t="inlineStr">
+      <c r="D12" s="82" t="inlineStr">
         <is>
           <t>Материалы штукатурки и шпаклёвки (шпатлевка финиш 20кг, штукатурка 30кг 2шт, перчатки)</t>
         </is>
       </c>
-      <c r="E12" s="91" t="inlineStr">
+      <c r="E12" s="86" t="inlineStr">
         <is>
           <t>4601745002814</t>
         </is>
       </c>
-      <c r="F12" s="91" t="inlineStr">
+      <c r="F12" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G12" s="243" t="n">
+      <c r="G12" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="89" t="n">
+      <c r="H12" s="83" t="n">
         <v>1594</v>
       </c>
-      <c r="I12" s="90">
+      <c r="I12" s="84">
         <f>G12*H12</f>
         <v/>
       </c>
-      <c r="J12" s="88" t="inlineStr">
+      <c r="J12" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K12" s="244">
+      <c r="K12" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=шпатлевка+финишная+старатели", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7206,50 +7389,50 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="86" t="n">
+      <c r="A13" s="91" t="n">
         <v>34</v>
       </c>
-      <c r="B13" s="82" t="inlineStr">
+      <c r="B13" s="88" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C13" s="82" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
         <is>
           <t>Санфаянс / Смесители</t>
         </is>
       </c>
-      <c r="D13" s="82" t="inlineStr">
+      <c r="D13" s="88" t="inlineStr">
         <is>
           <t>Сантехника и санфаянс с/у (ванна Нерея 150, каркас Sensea, унитаз Sanita, раковина 60, смесители 2шт, душ, сифон)</t>
         </is>
       </c>
-      <c r="E13" s="86" t="inlineStr">
+      <c r="E13" s="91" t="inlineStr">
         <is>
           <t>4600779023659</t>
         </is>
       </c>
-      <c r="F13" s="86" t="inlineStr">
+      <c r="F13" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G13" s="245" t="n">
+      <c r="G13" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="83" t="n">
+      <c r="H13" s="89" t="n">
         <v>30021</v>
       </c>
-      <c r="I13" s="84">
+      <c r="I13" s="90">
         <f>G13*H13</f>
         <v/>
       </c>
-      <c r="J13" s="82" t="inlineStr">
+      <c r="J13" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K13" s="244">
+      <c r="K13" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4600779023659", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7260,50 +7443,50 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="91" t="n">
+      <c r="A14" s="86" t="n">
         <v>35</v>
       </c>
-      <c r="B14" s="88" t="inlineStr">
+      <c r="B14" s="82" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C14" s="88" t="inlineStr">
+      <c r="C14" s="82" t="inlineStr">
         <is>
           <t>Керамогранит / Затирка</t>
         </is>
       </c>
-      <c r="D14" s="88" t="inlineStr">
+      <c r="D14" s="82" t="inlineStr">
         <is>
           <t>Керамогранит Calacatta 60х120 (14 упак. / 20.16 м²) + затирка Ceresit CE 40 2кг 2шт</t>
         </is>
       </c>
-      <c r="E14" s="91" t="inlineStr">
+      <c r="E14" s="86" t="inlineStr">
         <is>
           <t>4673766221451</t>
         </is>
       </c>
-      <c r="F14" s="91" t="inlineStr">
+      <c r="F14" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G14" s="243" t="n">
+      <c r="G14" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="89" t="n">
+      <c r="H14" s="83" t="n">
         <v>33457</v>
       </c>
-      <c r="I14" s="90">
+      <c r="I14" s="84">
         <f>G14*H14</f>
         <v/>
       </c>
-      <c r="J14" s="88" t="inlineStr">
+      <c r="J14" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K14" s="244">
+      <c r="K14" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4673766221451", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7314,50 +7497,50 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="86" t="n">
+      <c r="A15" s="91" t="n">
         <v>36</v>
       </c>
-      <c r="B15" s="82" t="inlineStr">
+      <c r="B15" s="88" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C15" s="82" t="inlineStr">
+      <c r="C15" s="88" t="inlineStr">
         <is>
           <t>Плиточный клей</t>
         </is>
       </c>
-      <c r="D15" s="82" t="inlineStr">
+      <c r="D15" s="88" t="inlineStr">
         <is>
           <t>Плиточный клей Unis 2000 C1T 25 кг для формата 60х120 (13 мешков)</t>
         </is>
       </c>
-      <c r="E15" s="86" t="inlineStr">
+      <c r="E15" s="91" t="inlineStr">
         <is>
           <t>4607005180063</t>
         </is>
       </c>
-      <c r="F15" s="86" t="inlineStr">
+      <c r="F15" s="91" t="inlineStr">
         <is>
           <t>мешок</t>
         </is>
       </c>
-      <c r="G15" s="245" t="n">
+      <c r="G15" s="255" t="n">
         <v>13</v>
       </c>
-      <c r="H15" s="83" t="n">
+      <c r="H15" s="89" t="n">
         <v>382.53846</v>
       </c>
-      <c r="I15" s="84">
+      <c r="I15" s="90">
         <f>G15*H15</f>
         <v/>
       </c>
-      <c r="J15" s="82" t="inlineStr">
+      <c r="J15" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K15" s="244">
+      <c r="K15" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4607005180063", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7368,50 +7551,50 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="91" t="n">
+      <c r="A16" s="86" t="n">
         <v>37</v>
       </c>
-      <c r="B16" s="88" t="inlineStr">
+      <c r="B16" s="82" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C16" s="88" t="inlineStr">
+      <c r="C16" s="82" t="inlineStr">
         <is>
           <t>СВП</t>
         </is>
       </c>
-      <c r="D16" s="88" t="inlineStr">
+      <c r="D16" s="82" t="inlineStr">
         <is>
           <t>Система выравнивания плитки СВП DILWIS (зажимы 1 мм 200 шт, клинья 100 шт)</t>
         </is>
       </c>
-      <c r="E16" s="91" t="inlineStr">
+      <c r="E16" s="86" t="inlineStr">
         <is>
           <t>4610085150475</t>
         </is>
       </c>
-      <c r="F16" s="91" t="inlineStr">
+      <c r="F16" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G16" s="243" t="n">
+      <c r="G16" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="89" t="n">
+      <c r="H16" s="83" t="n">
         <v>853</v>
       </c>
-      <c r="I16" s="90">
+      <c r="I16" s="84">
         <f>G16*H16</f>
         <v/>
       </c>
-      <c r="J16" s="88" t="inlineStr">
+      <c r="J16" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K16" s="244">
+      <c r="K16" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4610085150475", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7422,50 +7605,50 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="86" t="n">
+      <c r="A17" s="91" t="n">
         <v>38</v>
       </c>
-      <c r="B17" s="82" t="inlineStr">
+      <c r="B17" s="88" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C17" s="82" t="inlineStr">
+      <c r="C17" s="88" t="inlineStr">
         <is>
           <t>Шпаклёвка</t>
         </is>
       </c>
-      <c r="D17" s="82" t="inlineStr">
+      <c r="D17" s="88" t="inlineStr">
         <is>
           <t>Материалы для штукатурки и шпаклёвки (повторный добор: финиш 20кг, штукатурка 2шт)</t>
         </is>
       </c>
-      <c r="E17" s="86" t="inlineStr">
+      <c r="E17" s="91" t="inlineStr">
         <is>
           <t>4601745000407</t>
         </is>
       </c>
-      <c r="F17" s="86" t="inlineStr">
+      <c r="F17" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G17" s="245" t="n">
+      <c r="G17" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="83" t="n">
+      <c r="H17" s="89" t="n">
         <v>1594</v>
       </c>
-      <c r="I17" s="84">
+      <c r="I17" s="90">
         <f>G17*H17</f>
         <v/>
       </c>
-      <c r="J17" s="82" t="inlineStr">
+      <c r="J17" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K17" s="244">
+      <c r="K17" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=штукатурка+старатели+30кг", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7476,50 +7659,50 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="91" t="n">
+      <c r="A18" s="86" t="n">
         <v>39</v>
       </c>
-      <c r="B18" s="88" t="inlineStr">
+      <c r="B18" s="82" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C18" s="88" t="inlineStr">
+      <c r="C18" s="82" t="inlineStr">
         <is>
           <t>Стяжка / Короба</t>
         </is>
       </c>
-      <c r="D18" s="88" t="inlineStr">
+      <c r="D18" s="82" t="inlineStr">
         <is>
           <t>Материалы для стяжки пола и короба с/у (пескобетон М-300 6шт, Knauf 50х40, ГСП 2шт, фибра, саморезы, стамеска)</t>
         </is>
       </c>
-      <c r="E18" s="91" t="inlineStr">
+      <c r="E18" s="86" t="inlineStr">
         <is>
           <t>4610007550932</t>
         </is>
       </c>
-      <c r="F18" s="91" t="inlineStr">
+      <c r="F18" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G18" s="243" t="n">
+      <c r="G18" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="89" t="n">
+      <c r="H18" s="83" t="n">
         <v>3182.67</v>
       </c>
-      <c r="I18" s="90">
+      <c r="I18" s="84">
         <f>G18*H18</f>
         <v/>
       </c>
-      <c r="J18" s="88" t="inlineStr">
+      <c r="J18" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K18" s="244">
+      <c r="K18" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=пескобетон+м300", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7530,50 +7713,50 @@
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="86" t="n">
+      <c r="A19" s="91" t="n">
         <v>45</v>
       </c>
-      <c r="B19" s="82" t="inlineStr">
+      <c r="B19" s="88" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C19" s="82" t="inlineStr">
+      <c r="C19" s="88" t="inlineStr">
         <is>
           <t>Черновые стены / Гидроизоляция</t>
         </is>
       </c>
-      <c r="D19" s="82" t="inlineStr">
+      <c r="D19" s="88" t="inlineStr">
         <is>
           <t>Штукатурка Старатели 8шт, гидроизоляция Unis 4кг, люк Fonet 200х250, маяки, профиль, фитинги, рулетки</t>
         </is>
       </c>
-      <c r="E19" s="86" t="inlineStr">
+      <c r="E19" s="91" t="inlineStr">
         <is>
           <t>4601745000407</t>
         </is>
       </c>
-      <c r="F19" s="86" t="inlineStr">
+      <c r="F19" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G19" s="245" t="n">
+      <c r="G19" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="83" t="n">
+      <c r="H19" s="89" t="n">
         <v>7827.6</v>
       </c>
-      <c r="I19" s="84">
+      <c r="I19" s="90">
         <f>G19*H19</f>
         <v/>
       </c>
-      <c r="J19" s="82" t="inlineStr">
+      <c r="J19" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K19" s="244">
+      <c r="K19" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4601745000407", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7584,50 +7767,50 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="91" t="n">
+      <c r="A20" s="86" t="n">
         <v>46</v>
       </c>
-      <c r="B20" s="88" t="inlineStr">
+      <c r="B20" s="82" t="inlineStr">
         <is>
           <t>Все зоны</t>
         </is>
       </c>
-      <c r="C20" s="88" t="inlineStr">
+      <c r="C20" s="82" t="inlineStr">
         <is>
           <t>Радиаторы / Трубы</t>
         </is>
       </c>
-      <c r="D20" s="88" t="inlineStr">
+      <c r="D20" s="82" t="inlineStr">
         <is>
           <t>Эмаль аэрозольная Luxens белая сатиновая и матовая 520 мл (2 шт.)</t>
         </is>
       </c>
-      <c r="E20" s="91" t="inlineStr">
+      <c r="E20" s="86" t="inlineStr">
         <is>
           <t>3276007227604</t>
         </is>
       </c>
-      <c r="F20" s="91" t="inlineStr">
+      <c r="F20" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G20" s="243" t="n">
+      <c r="G20" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="89" t="n">
+      <c r="H20" s="83" t="n">
         <v>648</v>
       </c>
-      <c r="I20" s="90">
+      <c r="I20" s="84">
         <f>G20*H20</f>
         <v/>
       </c>
-      <c r="J20" s="88" t="inlineStr">
+      <c r="J20" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K20" s="244">
+      <c r="K20" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=3276007227604", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7638,50 +7821,50 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="86" t="n">
+      <c r="A21" s="91" t="n">
         <v>47</v>
       </c>
-      <c r="B21" s="82" t="inlineStr">
+      <c r="B21" s="88" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C21" s="82" t="inlineStr">
+      <c r="C21" s="88" t="inlineStr">
         <is>
           <t>Стяжка / Добавки</t>
         </is>
       </c>
-      <c r="D21" s="82" t="inlineStr">
+      <c r="D21" s="88" t="inlineStr">
         <is>
           <t>Ускоритель твердения Cemfix для стяжки пола, 1 литр (добавка в пескобетон М300)</t>
         </is>
       </c>
-      <c r="E21" s="86" t="inlineStr">
+      <c r="E21" s="91" t="inlineStr">
         <is>
           <t>4650068600092</t>
         </is>
       </c>
-      <c r="F21" s="86" t="inlineStr">
+      <c r="F21" s="91" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G21" s="245" t="n">
+      <c r="G21" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="83" t="n">
+      <c r="H21" s="89" t="n">
         <v>262</v>
       </c>
-      <c r="I21" s="84">
+      <c r="I21" s="90">
         <f>G21*H21</f>
         <v/>
       </c>
-      <c r="J21" s="82" t="inlineStr">
+      <c r="J21" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K21" s="244">
+      <c r="K21" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4650068600092", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7692,50 +7875,50 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="91" t="n">
+      <c r="A22" s="86" t="n">
         <v>50</v>
       </c>
-      <c r="B22" s="88" t="inlineStr">
+      <c r="B22" s="82" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C22" s="88" t="inlineStr">
+      <c r="C22" s="82" t="inlineStr">
         <is>
           <t>Расходники / Инструмент</t>
         </is>
       </c>
-      <c r="D22" s="88" t="inlineStr">
+      <c r="D22" s="82" t="inlineStr">
         <is>
           <t>Пистолет для герметика скелетный + герметик санитарный силиконовый (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E22" s="91" t="inlineStr">
+      <c r="E22" s="86" t="inlineStr">
         <is>
           <t>82420455</t>
         </is>
       </c>
-      <c r="F22" s="91" t="inlineStr">
+      <c r="F22" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G22" s="243" t="n">
+      <c r="G22" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="89" t="n">
+      <c r="H22" s="83" t="n">
         <v>650</v>
       </c>
-      <c r="I22" s="90">
+      <c r="I22" s="84">
         <f>G22*H22</f>
         <v/>
       </c>
-      <c r="J22" s="88" t="inlineStr">
+      <c r="J22" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K22" s="244">
+      <c r="K22" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=пистолет+для+герметика", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7746,50 +7929,50 @@
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="86" t="n">
+      <c r="A23" s="91" t="n">
         <v>51</v>
       </c>
-      <c r="B23" s="82" t="inlineStr">
+      <c r="B23" s="88" t="inlineStr">
         <is>
           <t>Санузел / Стены</t>
         </is>
       </c>
-      <c r="C23" s="82" t="inlineStr">
+      <c r="C23" s="88" t="inlineStr">
         <is>
           <t>Штукатурка / Мешки</t>
         </is>
       </c>
-      <c r="D23" s="82" t="inlineStr">
+      <c r="D23" s="88" t="inlineStr">
         <is>
           <t>Штукатурка гипсовая Старатели 30кг 3шт, перчатки, мешки 3шт (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E23" s="86" t="inlineStr">
+      <c r="E23" s="91" t="inlineStr">
         <is>
           <t>4601745000407</t>
         </is>
       </c>
-      <c r="F23" s="86" t="inlineStr">
+      <c r="F23" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G23" s="245" t="n">
+      <c r="G23" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="83" t="n">
+      <c r="H23" s="89" t="n">
         <v>1638</v>
       </c>
-      <c r="I23" s="84">
+      <c r="I23" s="90">
         <f>G23*H23</f>
         <v/>
       </c>
-      <c r="J23" s="82" t="inlineStr">
+      <c r="J23" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K23" s="244">
+      <c r="K23" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4601745000407", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7800,50 +7983,50 @@
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="91" t="n">
+      <c r="A24" s="86" t="n">
         <v>52</v>
       </c>
-      <c r="B24" s="88" t="inlineStr">
+      <c r="B24" s="82" t="inlineStr">
         <is>
           <t>Радиаторы / Стены</t>
         </is>
       </c>
-      <c r="C24" s="88" t="inlineStr">
+      <c r="C24" s="82" t="inlineStr">
         <is>
           <t>Краска / Кисти</t>
         </is>
       </c>
-      <c r="D24" s="88" t="inlineStr">
+      <c r="D24" s="82" t="inlineStr">
         <is>
           <t>Грунт-эмаль Luxens 3в1 белая 2.4кг, щетка металл 5-рядная, кисть Dilwis 70мм</t>
         </is>
       </c>
-      <c r="E24" s="91" t="inlineStr">
+      <c r="E24" s="86" t="inlineStr">
         <is>
           <t>4610088004195</t>
         </is>
       </c>
-      <c r="F24" s="91" t="inlineStr">
+      <c r="F24" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G24" s="243" t="n">
+      <c r="G24" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="89" t="n">
+      <c r="H24" s="83" t="n">
         <v>1769</v>
       </c>
-      <c r="I24" s="90">
+      <c r="I24" s="84">
         <f>G24*H24</f>
         <v/>
       </c>
-      <c r="J24" s="88" t="inlineStr">
+      <c r="J24" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K24" s="244">
+      <c r="K24" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4610088004195", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7854,50 +8037,50 @@
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="86" t="n">
+      <c r="A25" s="91" t="n">
         <v>53</v>
       </c>
-      <c r="B25" s="82" t="inlineStr">
+      <c r="B25" s="88" t="inlineStr">
         <is>
           <t>Санузел / Короб</t>
         </is>
       </c>
-      <c r="C25" s="82" t="inlineStr">
+      <c r="C25" s="88" t="inlineStr">
         <is>
           <t>Профиль / Саморезы</t>
         </is>
       </c>
-      <c r="D25" s="82" t="inlineStr">
+      <c r="D25" s="88" t="inlineStr">
         <is>
           <t>Профиль ППН 27х28 3шт, профиль ПП 60х27 1шт, саморезы оцинк./фосфат. (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E25" s="86" t="inlineStr">
+      <c r="E25" s="91" t="inlineStr">
         <is>
           <t>4600776027292</t>
         </is>
       </c>
-      <c r="F25" s="86" t="inlineStr">
+      <c r="F25" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G25" s="245" t="n">
+      <c r="G25" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="83" t="n">
+      <c r="H25" s="89" t="n">
         <v>911.7</v>
       </c>
-      <c r="I25" s="84">
+      <c r="I25" s="90">
         <f>G25*H25</f>
         <v/>
       </c>
-      <c r="J25" s="82" t="inlineStr">
+      <c r="J25" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K25" s="244">
+      <c r="K25" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4600776027292", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7908,50 +8091,50 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="91" t="n">
+      <c r="A26" s="86" t="n">
         <v>54</v>
       </c>
-      <c r="B26" s="88" t="inlineStr">
+      <c r="B26" s="82" t="inlineStr">
         <is>
           <t>Санузел / Короб</t>
         </is>
       </c>
-      <c r="C26" s="88" t="inlineStr">
+      <c r="C26" s="82" t="inlineStr">
         <is>
           <t>ГСП / Профиль / Смеси</t>
         </is>
       </c>
-      <c r="D26" s="88" t="inlineStr">
+      <c r="D26" s="82" t="inlineStr">
         <is>
           <t>ГСП-Н3 Knauf влагост. 1500х600х12.5 2шт, штукатурка Старатели 30кг, профили 28х27 2шт, 60х27 1шт</t>
         </is>
       </c>
-      <c r="E26" s="91" t="inlineStr">
+      <c r="E26" s="86" t="inlineStr">
         <is>
           <t>4607160003634</t>
         </is>
       </c>
-      <c r="F26" s="91" t="inlineStr">
+      <c r="F26" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G26" s="243" t="n">
+      <c r="G26" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="89" t="n">
+      <c r="H26" s="83" t="n">
         <v>1582</v>
       </c>
-      <c r="I26" s="90">
+      <c r="I26" s="84">
         <f>G26*H26</f>
         <v/>
       </c>
-      <c r="J26" s="88" t="inlineStr">
+      <c r="J26" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K26" s="244">
+      <c r="K26" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4607160003634", "Открыть ↗")</f>
         <v/>
       </c>
@@ -7962,50 +8145,50 @@
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="86" t="n">
+      <c r="A27" s="91" t="n">
         <v>55</v>
       </c>
-      <c r="B27" s="82" t="inlineStr">
+      <c r="B27" s="88" t="inlineStr">
         <is>
           <t>Полы / Финиш</t>
         </is>
       </c>
-      <c r="C27" s="82" t="inlineStr">
+      <c r="C27" s="88" t="inlineStr">
         <is>
           <t>Ламинат / Плинтус</t>
         </is>
       </c>
-      <c r="D27" s="82" t="inlineStr">
+      <c r="D27" s="88" t="inlineStr">
         <is>
           <t>Ламинат Kronostep Дуб Ночиолла 33кл 10мм 24 упак./41.52м², подложка Monlid 9шт, плинтус белый 8см 20шт</t>
         </is>
       </c>
-      <c r="E27" s="86" t="inlineStr">
+      <c r="E27" s="91" t="inlineStr">
         <is>
           <t>4607113367721</t>
         </is>
       </c>
-      <c r="F27" s="86" t="inlineStr">
+      <c r="F27" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G27" s="245" t="n">
+      <c r="G27" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="83" t="n">
+      <c r="H27" s="89" t="n">
         <v>41914.52</v>
       </c>
-      <c r="I27" s="84">
+      <c r="I27" s="90">
         <f>G27*H27</f>
         <v/>
       </c>
-      <c r="J27" s="82" t="inlineStr">
+      <c r="J27" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K27" s="244">
+      <c r="K27" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4607113367721", "Открыть ↗")</f>
         <v/>
       </c>
@@ -8016,50 +8199,50 @@
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="91" t="n">
+      <c r="A28" s="86" t="n">
         <v>56</v>
       </c>
-      <c r="B28" s="88" t="inlineStr">
+      <c r="B28" s="82" t="inlineStr">
         <is>
           <t>Стены / Потолок</t>
         </is>
       </c>
-      <c r="C28" s="88" t="inlineStr">
+      <c r="C28" s="82" t="inlineStr">
         <is>
           <t>Грунт / Клей</t>
         </is>
       </c>
-      <c r="D28" s="88" t="inlineStr">
+      <c r="D28" s="82" t="inlineStr">
         <is>
           <t>Грунт перекрывающий пятна Axton 1л, клей монтажный Kudo 2шт, валик нат. мех, макловица-мини</t>
         </is>
       </c>
-      <c r="E28" s="91" t="inlineStr">
+      <c r="E28" s="86" t="inlineStr">
         <is>
           <t>4690364027858</t>
         </is>
       </c>
-      <c r="F28" s="91" t="inlineStr">
+      <c r="F28" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G28" s="243" t="n">
+      <c r="G28" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="89" t="n">
+      <c r="H28" s="83" t="n">
         <v>1070</v>
       </c>
-      <c r="I28" s="90">
+      <c r="I28" s="84">
         <f>G28*H28</f>
         <v/>
       </c>
-      <c r="J28" s="88" t="inlineStr">
+      <c r="J28" s="82" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K28" s="244">
+      <c r="K28" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4690364027858", "Открыть ↗")</f>
         <v/>
       </c>
@@ -8070,50 +8253,50 @@
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="86" t="n">
+      <c r="A29" s="91" t="n">
         <v>57</v>
       </c>
-      <c r="B29" s="82" t="inlineStr">
+      <c r="B29" s="88" t="inlineStr">
         <is>
           <t>Хознужды / Инструмент</t>
         </is>
       </c>
-      <c r="C29" s="82" t="inlineStr">
+      <c r="C29" s="88" t="inlineStr">
         <is>
           <t>Уборка / Краска</t>
         </is>
       </c>
-      <c r="D29" s="82" t="inlineStr">
+      <c r="D29" s="88" t="inlineStr">
         <is>
           <t>Швабра In Loran, тряпки 3шт, краска Olimp 0.9л, упак. лента Axton, саморезы, ножи 2шт, карандаш</t>
         </is>
       </c>
-      <c r="E29" s="86" t="inlineStr">
+      <c r="E29" s="91" t="inlineStr">
         <is>
           <t>4630085515241</t>
         </is>
       </c>
-      <c r="F29" s="86" t="inlineStr">
+      <c r="F29" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G29" s="245" t="n">
+      <c r="G29" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="83" t="n">
+      <c r="H29" s="89" t="n">
         <v>1707.17</v>
       </c>
-      <c r="I29" s="84">
+      <c r="I29" s="90">
         <f>G29*H29</f>
         <v/>
       </c>
-      <c r="J29" s="82" t="inlineStr">
+      <c r="J29" s="88" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K29" s="244">
+      <c r="K29" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=4630085515241", "Открыть ↗")</f>
         <v/>
       </c>
@@ -8123,2324 +8306,2569 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="246" t="n"/>
-      <c r="B30" s="247" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="86" t="n">
+        <v>65</v>
+      </c>
+      <c r="B30" s="82" t="inlineStr">
+        <is>
+          <t>Санузел / Инженерия</t>
+        </is>
+      </c>
+      <c r="C30" s="82" t="inlineStr">
+        <is>
+          <t>Трубы / Фитинги / Биты</t>
+        </is>
+      </c>
+      <c r="D30" s="82" t="inlineStr">
+        <is>
+          <t>Труба ПП D20 2шт, отвод 50х15°, соединитель D50, биты Rage PH2 70мм</t>
+        </is>
+      </c>
+      <c r="E30" s="86" t="inlineStr">
+        <is>
+          <t>4607181620858</t>
+        </is>
+      </c>
+      <c r="F30" s="86" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G30" s="253" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="83" t="n">
+        <v>550</v>
+      </c>
+      <c r="I30" s="84">
+        <f>G30*H30</f>
+        <v/>
+      </c>
+      <c r="J30" s="82" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K30" s="254">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4607181620858", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L30" s="246" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="91" t="n">
+        <v>66</v>
+      </c>
+      <c r="B31" s="88" t="inlineStr">
+        <is>
+          <t>Санузел / Финиш</t>
+        </is>
+      </c>
+      <c r="C31" s="88" t="inlineStr">
+        <is>
+          <t>Керамогранит Calacatta</t>
+        </is>
+      </c>
+      <c r="D31" s="88" t="inlineStr">
+        <is>
+          <t>Керамогранит Calacatta superwhite 60х120 (добор 2 упак. / 2.88 м²)</t>
+        </is>
+      </c>
+      <c r="E31" s="91" t="inlineStr">
+        <is>
+          <t>4673766221451</t>
+        </is>
+      </c>
+      <c r="F31" s="91" t="inlineStr">
+        <is>
+          <t>упак.</t>
+        </is>
+      </c>
+      <c r="G31" s="255" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="89" t="n">
+        <v>2938</v>
+      </c>
+      <c r="I31" s="90">
+        <f>G31*H31</f>
+        <v/>
+      </c>
+      <c r="J31" s="88" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K31" s="256">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=4673766221451", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L31" s="249" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="257" t="n"/>
+      <c r="B32" s="258" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ ЛЕМАНА ПРО (ПО ЧЕКАМ):</t>
         </is>
       </c>
-      <c r="C30" s="246" t="n"/>
-      <c r="D30" s="246" t="n"/>
-      <c r="E30" s="246" t="n"/>
-      <c r="F30" s="246" t="n"/>
-      <c r="G30" s="246" t="n"/>
-      <c r="H30" s="246" t="n"/>
-      <c r="I30" s="248">
-        <f>SUM(I6:I29)</f>
-        <v/>
-      </c>
-      <c r="J30" s="246" t="n"/>
-      <c r="K30" s="246" t="n"/>
-      <c r="L30" s="246" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="249" t="n"/>
-      <c r="B31" s="249" t="inlineStr">
+      <c r="C32" s="259" t="n"/>
+      <c r="D32" s="259" t="n"/>
+      <c r="E32" s="257" t="n"/>
+      <c r="F32" s="257" t="n"/>
+      <c r="G32" s="260" t="n"/>
+      <c r="H32" s="261" t="n"/>
+      <c r="I32" s="261">
+        <f>SUM(I6:I31)</f>
+        <v/>
+      </c>
+      <c r="J32" s="259" t="n"/>
+      <c r="K32" s="257" t="n"/>
+      <c r="L32" s="88" t="inlineStr">
+        <is>
+          <t>Оперативная докупка расходников для демонтажа</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="262" t="n"/>
+      <c r="B33" s="263" t="inlineStr">
         <is>
           <t>⚡ БЛОК 2: ИНЖЕНЕРНЫЕ МАТЕРИАЛЫ, ДВЕРИ И ОСНАЩЕНИЕ (СПЕЦПОСТАВЩИКИ)</t>
         </is>
       </c>
-      <c r="C31" s="249" t="n"/>
-      <c r="D31" s="249" t="n"/>
-      <c r="E31" s="249" t="n"/>
-      <c r="F31" s="249" t="n"/>
-      <c r="G31" s="249" t="n"/>
-      <c r="H31" s="249" t="n"/>
-      <c r="I31" s="249" t="n"/>
-      <c r="J31" s="249" t="n"/>
-      <c r="K31" s="249" t="n"/>
-      <c r="L31" s="249" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="91" t="n">
+      <c r="C33" s="264" t="n"/>
+      <c r="D33" s="264" t="n"/>
+      <c r="E33" s="262" t="n"/>
+      <c r="F33" s="262" t="n"/>
+      <c r="G33" s="265" t="n"/>
+      <c r="H33" s="266" t="n"/>
+      <c r="I33" s="267" t="n"/>
+      <c r="J33" s="264" t="n"/>
+      <c r="K33" s="268" t="n"/>
+      <c r="L33" s="82" t="inlineStr">
+        <is>
+          <t>Замена вводных узлов и прибора учёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="86" t="n">
         <v>6</v>
       </c>
-      <c r="B32" s="88" t="inlineStr">
+      <c r="B34" s="82" t="inlineStr">
         <is>
           <t>Расходники</t>
         </is>
       </c>
-      <c r="C32" s="88" t="inlineStr">
+      <c r="C34" s="82" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="D32" s="88" t="inlineStr">
+      <c r="D34" s="82" t="inlineStr">
         <is>
           <t>Мешки мусорные плотные, перчатки рабочие (хозмаг/рынок)</t>
         </is>
       </c>
-      <c r="E32" s="91" t="inlineStr">
+      <c r="E34" s="86" t="inlineStr">
         <is>
           <t>ХОЗМАГ-МЕШКИ</t>
         </is>
       </c>
-      <c r="F32" s="91" t="inlineStr">
+      <c r="F34" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G32" s="243" t="n">
+      <c r="G34" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="89" t="n">
+      <c r="H34" s="83" t="n">
         <v>300</v>
       </c>
-      <c r="I32" s="90">
-        <f>G32*H32</f>
-        <v/>
-      </c>
-      <c r="J32" s="88" t="inlineStr">
+      <c r="I34" s="84">
+        <f>G34*H34</f>
+        <v/>
+      </c>
+      <c r="J34" s="82" t="inlineStr">
         <is>
           <t>Хозмаг / Рынок</t>
         </is>
       </c>
-      <c r="K32" s="244">
+      <c r="K34" s="254">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=мешки+мусорные+строительные", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L32" s="88" t="inlineStr">
-        <is>
-          <t>Оперативная докупка расходников для демонтажа</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="86" t="n">
+      <c r="L34" s="88" t="inlineStr">
+        <is>
+          <t>Латунные фитинги, муфты, уплотнители</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="91" t="n">
         <v>11</v>
       </c>
-      <c r="B33" s="82" t="inlineStr">
+      <c r="B35" s="88" t="inlineStr">
         <is>
           <t>Сантехника</t>
         </is>
       </c>
-      <c r="C33" s="82" t="inlineStr">
+      <c r="C35" s="88" t="inlineStr">
         <is>
           <t>Учёт воды</t>
         </is>
       </c>
-      <c r="D33" s="82" t="inlineStr">
+      <c r="D35" s="88" t="inlineStr">
         <is>
           <t>Счётчик горячей/холодной воды + кран на ввод (материалы)</t>
         </is>
       </c>
-      <c r="E33" s="86" t="inlineStr">
+      <c r="E35" s="91" t="inlineStr">
         <is>
           <t>СЧЕТЧИК-ВОДЫ</t>
         </is>
       </c>
-      <c r="F33" s="86" t="inlineStr">
+      <c r="F35" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G33" s="245" t="n">
+      <c r="G35" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="83" t="n">
+      <c r="H35" s="89" t="n">
         <v>2100</v>
       </c>
-      <c r="I33" s="84">
-        <f>G33*H33</f>
-        <v/>
-      </c>
-      <c r="J33" s="82" t="inlineStr">
+      <c r="I35" s="90">
+        <f>G35*H35</f>
+        <v/>
+      </c>
+      <c r="J35" s="88" t="inlineStr">
         <is>
           <t>Вадим (сантехник УК)</t>
         </is>
       </c>
-      <c r="K33" s="244">
+      <c r="K35" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=счетчик+воды+универсальный", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L33" s="82" t="inlineStr">
-        <is>
-          <t>Замена вводных узлов и прибора учёта</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="91" t="n">
+      <c r="L35" s="82" t="inlineStr">
+        <is>
+          <t>Металл 1.5 мм, МДФ-панель, надежные замки</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="86" t="n">
         <v>14</v>
       </c>
-      <c r="B34" s="88" t="inlineStr">
+      <c r="B36" s="82" t="inlineStr">
         <is>
           <t>Сантехника</t>
         </is>
       </c>
-      <c r="C34" s="88" t="inlineStr">
+      <c r="C36" s="82" t="inlineStr">
         <is>
           <t>Учёт воды</t>
         </is>
       </c>
-      <c r="D34" s="88" t="inlineStr">
+      <c r="D36" s="82" t="inlineStr">
         <is>
           <t>Покупка и установка счётчика и кранов (доплата за фитинги и муфты)</t>
         </is>
       </c>
-      <c r="E34" s="91" t="inlineStr">
+      <c r="E36" s="86" t="inlineStr">
         <is>
           <t>ФИТИНГИ-САНТЕХ</t>
         </is>
       </c>
-      <c r="F34" s="91" t="inlineStr">
+      <c r="F36" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G34" s="243" t="n">
+      <c r="G36" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="89" t="n">
+      <c r="H36" s="83" t="n">
         <v>2000</v>
       </c>
-      <c r="I34" s="90">
-        <f>G34*H34</f>
-        <v/>
-      </c>
-      <c r="J34" s="88" t="inlineStr">
+      <c r="I36" s="84">
+        <f>G36*H36</f>
+        <v/>
+      </c>
+      <c r="J36" s="82" t="inlineStr">
         <is>
           <t>Вадим (сантехник УК)</t>
         </is>
       </c>
-      <c r="K34" s="244">
+      <c r="K36" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=шаровый+кран+1/2", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L34" s="88" t="inlineStr">
-        <is>
-          <t>Латунные фитинги, муфты, уплотнители</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="86" t="n">
+      <c r="L36" s="88" t="inlineStr">
+        <is>
+          <t>Транспортировка двери на ул. Фрунзе 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="91" t="n">
         <v>15</v>
       </c>
-      <c r="B35" s="82" t="inlineStr">
+      <c r="B37" s="88" t="inlineStr">
         <is>
           <t>Входная группа</t>
         </is>
       </c>
-      <c r="C35" s="82" t="inlineStr">
+      <c r="C37" s="88" t="inlineStr">
         <is>
           <t>Двери</t>
         </is>
       </c>
-      <c r="D35" s="82" t="inlineStr">
+      <c r="D37" s="88" t="inlineStr">
         <is>
           <t>Покупка входной металлической двери с внутренней МДФ-панелью</t>
         </is>
       </c>
-      <c r="E35" s="86" t="inlineStr">
+      <c r="E37" s="91" t="inlineStr">
         <is>
           <t>ДВЕРЬ-ВХОД-МДФ</t>
         </is>
       </c>
-      <c r="F35" s="86" t="inlineStr">
+      <c r="F37" s="91" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G35" s="245" t="n">
+      <c r="G37" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="83" t="n">
+      <c r="H37" s="89" t="n">
         <v>16000</v>
       </c>
-      <c r="I35" s="84">
-        <f>G35*H35</f>
-        <v/>
-      </c>
-      <c r="J35" s="82" t="inlineStr">
+      <c r="I37" s="90">
+        <f>G37*H37</f>
+        <v/>
+      </c>
+      <c r="J37" s="88" t="inlineStr">
         <is>
           <t>Владимир (двери)</t>
         </is>
       </c>
-      <c r="K35" s="244">
+      <c r="K37" s="256">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=входная+металлическая+дверь+мдф", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L35" s="82" t="inlineStr">
-        <is>
-          <t>Металл 1.5 мм, МДФ-панель, надежные замки</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="91" t="n">
+      <c r="L37" s="82" t="inlineStr">
+        <is>
+          <t>Комплектная начинка щита и прибор учёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="86" t="n">
         <v>16</v>
       </c>
-      <c r="B36" s="88" t="inlineStr">
+      <c r="B38" s="82" t="inlineStr">
         <is>
           <t>Входная группа</t>
         </is>
       </c>
-      <c r="C36" s="88" t="inlineStr">
+      <c r="C38" s="82" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="D36" s="88" t="inlineStr">
+      <c r="D38" s="82" t="inlineStr">
         <is>
           <t>Доставка входной металлической двери на объект</t>
         </is>
       </c>
-      <c r="E36" s="91" t="inlineStr">
+      <c r="E38" s="86" t="inlineStr">
         <is>
           <t>ДОСТАВКА-ДВЕРЬ</t>
         </is>
       </c>
-      <c r="F36" s="91" t="inlineStr">
+      <c r="F38" s="86" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G36" s="243" t="n">
+      <c r="G38" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="89" t="n">
+      <c r="H38" s="83" t="n">
         <v>1500</v>
       </c>
-      <c r="I36" s="90">
-        <f>G36*H36</f>
-        <v/>
-      </c>
-      <c r="J36" s="88" t="inlineStr">
+      <c r="I38" s="84">
+        <f>G38*H38</f>
+        <v/>
+      </c>
+      <c r="J38" s="82" t="inlineStr">
         <is>
           <t>Владимир / Доставка</t>
         </is>
       </c>
-      <c r="K36" s="244">
+      <c r="K38" s="254">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=доставка+дверей+грузоперевозки", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L36" s="88" t="inlineStr">
-        <is>
-          <t>Транспортировка двери на ул. Фрунзе 17</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="86" t="n">
+      <c r="L38" s="88" t="inlineStr">
+        <is>
+          <t>Силовой кабель ГОСТ под розетки и свет</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="91" t="n">
         <v>17</v>
       </c>
-      <c r="B37" s="82" t="inlineStr">
+      <c r="B39" s="88" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C37" s="82" t="inlineStr">
+      <c r="C39" s="88" t="inlineStr">
         <is>
           <t>Щит / Автоматика</t>
         </is>
       </c>
-      <c r="D37" s="82" t="inlineStr">
+      <c r="D39" s="88" t="inlineStr">
         <is>
           <t>Черновые материалы электрики (щит 18м, новый электросчётчик, автоматы, УЗО, гофра)</t>
         </is>
       </c>
-      <c r="E37" s="86" t="inlineStr">
+      <c r="E39" s="91" t="inlineStr">
         <is>
           <t>ЩИТ-АВТ-КОМПЛЕКТ</t>
         </is>
       </c>
-      <c r="F37" s="86" t="inlineStr">
+      <c r="F39" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G37" s="245" t="n">
+      <c r="G39" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="83" t="n">
+      <c r="H39" s="89" t="n">
         <v>16500</v>
       </c>
-      <c r="I37" s="84">
-        <f>G37*H37</f>
-        <v/>
-      </c>
-      <c r="J37" s="82" t="inlineStr">
+      <c r="I39" s="90">
+        <f>G39*H39</f>
+        <v/>
+      </c>
+      <c r="J39" s="88" t="inlineStr">
         <is>
           <t>Анатолий / Поставщик</t>
         </is>
       </c>
-      <c r="K37" s="244">
+      <c r="K39" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=щит+встраиваемый+18+модулей", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L37" s="82" t="inlineStr">
-        <is>
-          <t>Комплектная начинка щита и прибор учёта</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="91" t="n">
+      <c r="L39" s="82" t="inlineStr">
+        <is>
+          <t>Дюбель-хомуты и стяжки для трасс</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="86" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="88" t="inlineStr">
+      <c r="B40" s="82" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C38" s="88" t="inlineStr">
+      <c r="C40" s="82" t="inlineStr">
         <is>
           <t>Кабель</t>
         </is>
       </c>
-      <c r="D38" s="88" t="inlineStr">
+      <c r="D40" s="82" t="inlineStr">
         <is>
           <t>Кабель силовой ВВГнг-LS (ГОСТ 3х2.5 и 3х1.5 для всех трасс)</t>
         </is>
       </c>
-      <c r="E38" s="91" t="inlineStr">
+      <c r="E40" s="86" t="inlineStr">
         <is>
           <t>ВВГнг-LS-ГОСТ-1</t>
         </is>
       </c>
-      <c r="F38" s="91" t="inlineStr">
+      <c r="F40" s="86" t="inlineStr">
         <is>
           <t>бухта</t>
         </is>
       </c>
-      <c r="G38" s="243" t="n">
+      <c r="G40" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="89" t="n">
+      <c r="H40" s="83" t="n">
         <v>18000</v>
       </c>
-      <c r="I38" s="90">
-        <f>G38*H38</f>
-        <v/>
-      </c>
-      <c r="J38" s="88" t="inlineStr">
+      <c r="I40" s="84">
+        <f>G40*H40</f>
+        <v/>
+      </c>
+      <c r="J40" s="82" t="inlineStr">
         <is>
           <t>Электромонтаж / Поставщик</t>
         </is>
       </c>
-      <c r="K38" s="244">
+      <c r="K40" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=кабель+ВВГнг-LS+3х2.5", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L38" s="88" t="inlineStr">
-        <is>
-          <t>Силовой кабель ГОСТ под розетки и свет</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="86" t="n">
+      <c r="L40" s="88" t="inlineStr">
+        <is>
+          <t>Дополнительный кабель на трассы кухни и коридора</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="91" t="n">
         <v>20</v>
       </c>
-      <c r="B39" s="82" t="inlineStr">
+      <c r="B41" s="88" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C39" s="82" t="inlineStr">
+      <c r="C41" s="88" t="inlineStr">
         <is>
           <t>Крепёж</t>
         </is>
       </c>
-      <c r="D39" s="82" t="inlineStr">
+      <c r="D41" s="88" t="inlineStr">
         <is>
           <t>Стяжки нейлоновые и крепёж для монтажа кабеля</t>
         </is>
       </c>
-      <c r="E39" s="86" t="inlineStr">
+      <c r="E41" s="91" t="inlineStr">
         <is>
           <t>КРЕПЕЖ-КАБЕЛЬ</t>
         </is>
       </c>
-      <c r="F39" s="86" t="inlineStr">
+      <c r="F41" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G39" s="245" t="n">
+      <c r="G41" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="83" t="n">
+      <c r="H41" s="89" t="n">
         <v>1000</v>
       </c>
-      <c r="I39" s="84">
-        <f>G39*H39</f>
-        <v/>
-      </c>
-      <c r="J39" s="82" t="inlineStr">
+      <c r="I41" s="90">
+        <f>G41*H41</f>
+        <v/>
+      </c>
+      <c r="J41" s="88" t="inlineStr">
         <is>
           <t>Хозмаг / Электромонтаж</t>
         </is>
       </c>
-      <c r="K39" s="244">
+      <c r="K41" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=дюбель+хомут+для+кабеля", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L39" s="82" t="inlineStr">
-        <is>
-          <t>Дюбель-хомуты и стяжки для трасс</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="91" t="n">
+      <c r="L41" s="82" t="inlineStr">
+        <is>
+          <t>Акустическое оснащение объекта для бригад</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="86" t="n">
         <v>23</v>
       </c>
-      <c r="B40" s="88" t="inlineStr">
+      <c r="B42" s="82" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C40" s="88" t="inlineStr">
+      <c r="C42" s="82" t="inlineStr">
         <is>
           <t>Кабель</t>
         </is>
       </c>
-      <c r="D40" s="88" t="inlineStr">
+      <c r="D42" s="82" t="inlineStr">
         <is>
           <t>Докупка силового кабеля ВВГнг-LS (дополнительный метраж трасс)</t>
         </is>
       </c>
-      <c r="E40" s="91" t="inlineStr">
+      <c r="E42" s="86" t="inlineStr">
         <is>
           <t>ВВГнг-LS-ГОСТ-2</t>
         </is>
       </c>
-      <c r="F40" s="91" t="inlineStr">
+      <c r="F42" s="86" t="inlineStr">
         <is>
           <t>бухта</t>
         </is>
       </c>
-      <c r="G40" s="243" t="n">
+      <c r="G42" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="89" t="n">
+      <c r="H42" s="83" t="n">
         <v>13000</v>
       </c>
-      <c r="I40" s="90">
-        <f>G40*H40</f>
-        <v/>
-      </c>
-      <c r="J40" s="88" t="inlineStr">
+      <c r="I42" s="84">
+        <f>G42*H42</f>
+        <v/>
+      </c>
+      <c r="J42" s="82" t="inlineStr">
         <is>
           <t>Электромонтаж / Поставщик</t>
         </is>
       </c>
-      <c r="K40" s="244">
+      <c r="K42" s="254">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=кабель+ВВГнг-LS+3х1.5", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L40" s="88" t="inlineStr">
-        <is>
-          <t>Дополнительный кабель на трассы кухни и коридора</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="86" t="n">
+      <c r="L42" s="88" t="inlineStr">
+        <is>
+          <t>Бытовое снабжение объекта</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="91" t="n">
         <v>27</v>
       </c>
-      <c r="B41" s="82" t="inlineStr">
+      <c r="B43" s="88" t="inlineStr">
         <is>
           <t>Оснащение</t>
         </is>
       </c>
-      <c r="C41" s="82" t="inlineStr">
+      <c r="C43" s="88" t="inlineStr">
         <is>
           <t>Инвентарь</t>
         </is>
       </c>
-      <c r="D41" s="82" t="inlineStr">
+      <c r="D43" s="88" t="inlineStr">
         <is>
           <t>Портативная акустика Xiaomi Bluetooth Speaker Essential Green</t>
         </is>
       </c>
-      <c r="E41" s="86" t="inlineStr">
+      <c r="E43" s="91" t="inlineStr">
         <is>
           <t>XIAOMI-SPK-ESS</t>
         </is>
       </c>
-      <c r="F41" s="86" t="inlineStr">
+      <c r="F43" s="91" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G41" s="245" t="n">
+      <c r="G43" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="83" t="n">
+      <c r="H43" s="89" t="n">
         <v>1250</v>
       </c>
-      <c r="I41" s="84">
-        <f>G41*H41</f>
-        <v/>
-      </c>
-      <c r="J41" s="82" t="inlineStr">
+      <c r="I43" s="90">
+        <f>G43*H43</f>
+        <v/>
+      </c>
+      <c r="J43" s="88" t="inlineStr">
         <is>
           <t>ООО ДНС Ритейл (DNS)</t>
         </is>
       </c>
-      <c r="K41" s="244">
+      <c r="K43" s="256">
         <f>HYPERLINK("https://www.dns-shop.ru/search/?q=Xiaomi+Bluetooth+Speaker", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L41" s="82" t="inlineStr">
-        <is>
-          <t>Акустическое оснащение объекта для бригад</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="91" t="n">
+      <c r="L43" s="82" t="inlineStr">
+        <is>
+          <t>Чек от 15.09.2026: Муфта-восстановитель 110/110, разводка труб под ванну, раковину, унитаз</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="86" t="n">
         <v>29</v>
       </c>
-      <c r="B42" s="88" t="inlineStr">
+      <c r="B44" s="82" t="inlineStr">
         <is>
           <t>Оснащение</t>
         </is>
       </c>
-      <c r="C42" s="88" t="inlineStr">
+      <c r="C44" s="82" t="inlineStr">
         <is>
           <t>Хознужды</t>
         </is>
       </c>
-      <c r="D42" s="88" t="inlineStr">
+      <c r="D44" s="82" t="inlineStr">
         <is>
           <t>Хозрасходы на объект: салфетки влажные и питьевая вода для мастеров</t>
         </is>
       </c>
-      <c r="E42" s="91" t="inlineStr">
+      <c r="E44" s="86" t="inlineStr">
         <is>
           <t>ХОЗ-ВОДА-САЛФЕТКИ</t>
         </is>
       </c>
-      <c r="F42" s="91" t="inlineStr">
+      <c r="F44" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G42" s="243" t="n">
+      <c r="G44" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="89" t="n">
+      <c r="H44" s="83" t="n">
         <v>520</v>
       </c>
-      <c r="I42" s="90">
-        <f>G42*H42</f>
-        <v/>
-      </c>
-      <c r="J42" s="88" t="inlineStr">
+      <c r="I44" s="84">
+        <f>G44*H44</f>
+        <v/>
+      </c>
+      <c r="J44" s="82" t="inlineStr">
         <is>
           <t>Хозмаг / Продукты</t>
         </is>
       </c>
-      <c r="K42" s="244">
+      <c r="K44" s="254">
         <f>HYPERLINK("https://www.avito.ru/tula/produkty_pitaniya?q=питьевая+вода+19л", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L42" s="88" t="inlineStr">
-        <is>
-          <t>Бытовое снабжение объекта</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="86" t="n">
+      <c r="L44" s="88" t="inlineStr">
+        <is>
+          <t>Чек №23 от 19.09.2026: Разводка труб ХВС/ГВС, шаровой кран ввода, планка под смеситель ванны</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="91" t="n">
         <v>43</v>
       </c>
-      <c r="B43" s="82" t="inlineStr">
+      <c r="B45" s="88" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C43" s="82" t="inlineStr">
+      <c r="C45" s="88" t="inlineStr">
         <is>
           <t>Канализация</t>
         </is>
       </c>
-      <c r="D43" s="82" t="inlineStr">
+      <c r="D45" s="88" t="inlineStr">
         <is>
           <t>Канализация с/у (муфта-восстановитель раструба 110/110, трубы ПП 50, тройник 110/50, заглушка, отводы)</t>
         </is>
       </c>
-      <c r="E43" s="86" t="inlineStr">
+      <c r="E45" s="91" t="inlineStr">
         <is>
           <t>КАНАЛ-СУ-110-50</t>
         </is>
       </c>
-      <c r="F43" s="86" t="inlineStr">
+      <c r="F45" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G43" s="245" t="n">
+      <c r="G45" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="83" t="n">
+      <c r="H45" s="89" t="n">
         <v>2988</v>
       </c>
-      <c r="I43" s="84">
-        <f>G43*H43</f>
-        <v/>
-      </c>
-      <c r="J43" s="82" t="inlineStr">
+      <c r="I45" s="90">
+        <f>G45*H45</f>
+        <v/>
+      </c>
+      <c r="J45" s="88" t="inlineStr">
         <is>
           <t>ИП Кучеров М.И. (Полимерстрой)</t>
         </is>
       </c>
-      <c r="K43" s="244">
+      <c r="K45" s="256">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=восстановитель+раструба+110", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L43" s="82" t="inlineStr">
-        <is>
-          <t>Чек от 15.09.2026: Муфта-восстановитель 110/110, разводка труб под ванну, раковину, унитаз</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="91" t="n">
+      <c r="L45" s="82" t="inlineStr">
+        <is>
+          <t>Слип от 27.09.2026 13:08: расходники для электрики</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="86" t="n">
         <v>44</v>
       </c>
-      <c r="B44" s="88" t="inlineStr">
+      <c r="B46" s="82" t="inlineStr">
         <is>
           <t>Санузел / Кухня</t>
         </is>
       </c>
-      <c r="C44" s="88" t="inlineStr">
+      <c r="C46" s="82" t="inlineStr">
         <is>
           <t>Водоснабжение</t>
         </is>
       </c>
-      <c r="D44" s="88" t="inlineStr">
+      <c r="D46" s="82" t="inlineStr">
         <is>
           <t>Трубы армированные Faser 20х2.8 12м, настенная планка смесителя, кран DN15, муфты, клипсы</t>
         </is>
       </c>
-      <c r="E44" s="91" t="inlineStr">
+      <c r="E46" s="86" t="inlineStr">
         <is>
           <t>PPR-FASER-WATSON</t>
         </is>
       </c>
-      <c r="F44" s="91" t="inlineStr">
+      <c r="F46" s="86" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G44" s="243" t="n">
+      <c r="G46" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="89" t="n">
+      <c r="H46" s="83" t="n">
         <v>3139.54</v>
       </c>
-      <c r="I44" s="90">
-        <f>G44*H44</f>
-        <v/>
-      </c>
-      <c r="J44" s="88" t="inlineStr">
+      <c r="I46" s="84">
+        <f>G46*H46</f>
+        <v/>
+      </c>
+      <c r="J46" s="82" t="inlineStr">
         <is>
           <t>ТС «Ваттсон» (Центргазсервис)</t>
         </is>
       </c>
-      <c r="K44" s="244">
+      <c r="K46" s="254">
         <f>HYPERLINK("https://wattson.ru/search/?q=Faser+20", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L44" s="88" t="inlineStr">
-        <is>
-          <t>Чек №23 от 19.09.2026: Разводка труб ХВС/ГВС, шаровой кран ввода, планка под смеситель ванны</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="86" t="n">
+      <c r="L46" s="88" t="inlineStr">
+        <is>
+          <t>Чек от 27.09.2026 13:23: клинья для укладки плитки</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="91" t="n">
         <v>58</v>
       </c>
-      <c r="B45" s="82" t="inlineStr">
+      <c r="B47" s="88" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C45" s="82" t="inlineStr">
+      <c r="C47" s="88" t="inlineStr">
         <is>
           <t>Материалы / Розетки</t>
         </is>
       </c>
-      <c r="D45" s="82" t="inlineStr">
+      <c r="D47" s="88" t="inlineStr">
         <is>
           <t>Электротовары (комплектующие/расходники электрики, ул. Коминтерна 26)</t>
         </is>
       </c>
-      <c r="E45" s="86" t="inlineStr">
+      <c r="E47" s="91" t="inlineStr">
         <is>
           <t>ЭЛЕКТРО-КОМИНТЕРНА</t>
         </is>
       </c>
-      <c r="F45" s="86" t="inlineStr">
+      <c r="F47" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G45" s="245" t="n">
+      <c r="G47" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="83" t="n">
+      <c r="H47" s="89" t="n">
         <v>190</v>
       </c>
-      <c r="I45" s="84">
-        <f>G45*H45</f>
-        <v/>
-      </c>
-      <c r="J45" s="82" t="inlineStr">
+      <c r="I47" s="90">
+        <f>G47*H47</f>
+        <v/>
+      </c>
+      <c r="J47" s="88" t="inlineStr">
         <is>
           <t>Магазин «Электротовары»</t>
         </is>
       </c>
-      <c r="K45" s="244">
+      <c r="K47" s="256">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=электротовары+коминтерна", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L45" s="82" t="inlineStr">
-        <is>
-          <t>Слип от 27.09.2026 13:08: расходники для электрики</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="91" t="n">
+      <c r="L47" s="82" t="inlineStr">
+        <is>
+          <t>Запорно-регулировочные краны на батареи отопления</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="86" t="n">
         <v>59</v>
       </c>
-      <c r="B46" s="88" t="inlineStr">
+      <c r="B48" s="82" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C46" s="88" t="inlineStr">
+      <c r="C48" s="82" t="inlineStr">
         <is>
           <t>СВП / Клинья</t>
         </is>
       </c>
-      <c r="D46" s="88" t="inlineStr">
+      <c r="D48" s="82" t="inlineStr">
         <is>
           <t>Клинья для плитки СВП 32х8х9мм 50шт (Магазин крепежа, ул. Мосина 29)</t>
         </is>
       </c>
-      <c r="E46" s="91" t="inlineStr">
+      <c r="E48" s="86" t="inlineStr">
         <is>
           <t>СВП-КЛИНЬЯ-50</t>
         </is>
       </c>
-      <c r="F46" s="91" t="inlineStr">
+      <c r="F48" s="86" t="inlineStr">
         <is>
           <t>упак.</t>
         </is>
       </c>
-      <c r="G46" s="243" t="n">
+      <c r="G48" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="89" t="n">
+      <c r="H48" s="83" t="n">
         <v>210</v>
       </c>
-      <c r="I46" s="90">
-        <f>G46*H46</f>
-        <v/>
-      </c>
-      <c r="J46" s="88" t="inlineStr">
+      <c r="I48" s="84">
+        <f>G48*H48</f>
+        <v/>
+      </c>
+      <c r="J48" s="82" t="inlineStr">
         <is>
           <t>ИП Звягинцева С.Н. (Крепеж)</t>
         </is>
       </c>
-      <c r="K46" s="244">
+      <c r="K48" s="254">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=клинья+для+плитки+свп", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L46" s="88" t="inlineStr">
-        <is>
-          <t>Чек от 27.09.2026 13:23: клинья для укладки плитки</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="86" t="n">
+      <c r="L48" s="246" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="91" t="n">
         <v>64</v>
       </c>
-      <c r="B47" s="82" t="inlineStr">
+      <c r="B49" s="88" t="inlineStr">
         <is>
           <t>Отопление</t>
         </is>
       </c>
-      <c r="C47" s="82" t="inlineStr">
+      <c r="C49" s="88" t="inlineStr">
         <is>
           <t>Краны радиаторов</t>
         </is>
       </c>
-      <c r="D47" s="82" t="inlineStr">
+      <c r="D49" s="88" t="inlineStr">
         <is>
           <t>Два крана на радиаторы отопления (запорно-регулировочные краны)</t>
         </is>
       </c>
-      <c r="E47" s="86" t="inlineStr">
+      <c r="E49" s="91" t="inlineStr">
         <is>
           <t>КРАНЫ-РАДИАТОР-2</t>
         </is>
       </c>
-      <c r="F47" s="86" t="inlineStr">
+      <c r="F49" s="91" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G47" s="245" t="n">
+      <c r="G49" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="83" t="n">
+      <c r="H49" s="89" t="n">
         <v>1100</v>
       </c>
-      <c r="I47" s="84">
-        <f>G47*H47</f>
-        <v/>
-      </c>
-      <c r="J47" s="82" t="inlineStr">
+      <c r="I49" s="90">
+        <f>G49*H49</f>
+        <v/>
+      </c>
+      <c r="J49" s="88" t="inlineStr">
         <is>
           <t>Сантехмаркет / Хозмаг</t>
         </is>
       </c>
-      <c r="K47" s="244">
+      <c r="K49" s="256">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=кран+для+радиатора+отопления", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L47" s="82" t="inlineStr">
-        <is>
-          <t>Запорно-регулировочные краны на батареи отопления</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="246" t="n"/>
-      <c r="B48" s="247" t="inlineStr">
+      <c r="L49" s="250" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="86" t="n">
+        <v>67</v>
+      </c>
+      <c r="B50" s="82" t="inlineStr">
+        <is>
+          <t>Санузел / Плитка</t>
+        </is>
+      </c>
+      <c r="C50" s="82" t="inlineStr">
+        <is>
+          <t>Уголки для плитки</t>
+        </is>
+      </c>
+      <c r="D50" s="82" t="inlineStr">
+        <is>
+          <t>Уголки для плитки (Михаил)</t>
+        </is>
+      </c>
+      <c r="E50" s="86" t="inlineStr">
+        <is>
+          <t>УГОЛКИ-ПЛИТКА</t>
+        </is>
+      </c>
+      <c r="F50" s="86" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G50" s="253" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="83" t="n">
+        <v>260</v>
+      </c>
+      <c r="I50" s="84">
+        <f>G50*H50</f>
+        <v/>
+      </c>
+      <c r="J50" s="82" t="inlineStr">
+        <is>
+          <t>Михаил (мастер/плиточник)</t>
+        </is>
+      </c>
+      <c r="K50" s="254">
+        <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=уголки+для+плитки", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L50" s="88" t="inlineStr">
+        <is>
+          <t>Аварийное открытие двери после торгов</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="257" t="n"/>
+      <c r="B51" s="258" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ СПЕЦПОСТАВЩИКОВ:</t>
         </is>
       </c>
-      <c r="C48" s="246" t="n"/>
-      <c r="D48" s="246" t="n"/>
-      <c r="E48" s="246" t="n"/>
-      <c r="F48" s="246" t="n"/>
-      <c r="G48" s="246" t="n"/>
-      <c r="H48" s="246" t="n"/>
-      <c r="I48" s="248">
-        <f>SUM(I32:I47)</f>
-        <v/>
-      </c>
-      <c r="J48" s="246" t="n"/>
-      <c r="K48" s="246" t="n"/>
-      <c r="L48" s="246" t="n"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="250" t="n"/>
-      <c r="B49" s="250" t="inlineStr">
-        <is>
-          <t>👷‍♂️ БЛОК 3: РАБОТЫ МАСТЕРОВ, ОТДЕЛКА, ДЕМОНТАЖ И ЛОГИСТИКА (16 ПОЗИЦИЙ)</t>
-        </is>
-      </c>
-      <c r="C49" s="250" t="n"/>
-      <c r="D49" s="250" t="n"/>
-      <c r="E49" s="250" t="n"/>
-      <c r="F49" s="250" t="n"/>
-      <c r="G49" s="250" t="n"/>
-      <c r="H49" s="250" t="n"/>
-      <c r="I49" s="250" t="n"/>
-      <c r="J49" s="250" t="n"/>
-      <c r="K49" s="250" t="n"/>
-      <c r="L49" s="250" t="n"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="91" t="n">
+      <c r="C51" s="259" t="n"/>
+      <c r="D51" s="259" t="n"/>
+      <c r="E51" s="257" t="n"/>
+      <c r="F51" s="257" t="n"/>
+      <c r="G51" s="260" t="n"/>
+      <c r="H51" s="261" t="n"/>
+      <c r="I51" s="261">
+        <f>SUM(I34:I50)</f>
+        <v/>
+      </c>
+      <c r="J51" s="259" t="n"/>
+      <c r="K51" s="257" t="n"/>
+      <c r="L51" s="82" t="inlineStr">
+        <is>
+          <t>Вывоз мебели, санузла, чугуна, досок</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="269" t="n"/>
+      <c r="B52" s="270" t="inlineStr">
+        <is>
+          <t>👷‍♂️ БЛОК 3: РАБОТЫ МАСТЕРОВ, ОТДЕЛКА, ДЕМОНТАЖ И ЛОГИСТИКА (17 ПОЗИЦИЙ)</t>
+        </is>
+      </c>
+      <c r="C52" s="271" t="n"/>
+      <c r="D52" s="271" t="n"/>
+      <c r="E52" s="269" t="n"/>
+      <c r="F52" s="269" t="n"/>
+      <c r="G52" s="272" t="n"/>
+      <c r="H52" s="273" t="n"/>
+      <c r="I52" s="274" t="n"/>
+      <c r="J52" s="271" t="n"/>
+      <c r="K52" s="275" t="n"/>
+      <c r="L52" s="88" t="inlineStr">
+        <is>
+          <t>Перфоратор и монтировки для первичного демонтажа</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="91" t="n">
         <v>3</v>
       </c>
-      <c r="B50" s="88" t="inlineStr">
+      <c r="B53" s="88" t="inlineStr">
         <is>
           <t>Безопасность</t>
         </is>
       </c>
-      <c r="C50" s="88" t="inlineStr">
+      <c r="C53" s="88" t="inlineStr">
         <is>
           <t>Вскрытие</t>
         </is>
       </c>
-      <c r="D50" s="88" t="inlineStr">
+      <c r="D53" s="88" t="inlineStr">
         <is>
           <t>Вскрытие старого замка и обеспечение первого доступа</t>
         </is>
       </c>
-      <c r="E50" s="91" t="inlineStr">
+      <c r="E53" s="91" t="inlineStr">
         <is>
           <t>ВСКРЫТИЕ-ЗАМКА</t>
         </is>
       </c>
-      <c r="F50" s="91" t="inlineStr">
+      <c r="F53" s="91" t="inlineStr">
         <is>
           <t>выезд</t>
         </is>
       </c>
-      <c r="G50" s="243" t="n">
+      <c r="G53" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="89" t="n">
+      <c r="H53" s="89" t="n">
         <v>8000</v>
       </c>
-      <c r="I50" s="90">
-        <f>G50*H50</f>
-        <v/>
-      </c>
-      <c r="J50" s="88" t="inlineStr">
+      <c r="I53" s="90">
+        <f>G53*H53</f>
+        <v/>
+      </c>
+      <c r="J53" s="88" t="inlineStr">
         <is>
           <t>Служба вскрытия</t>
         </is>
       </c>
-      <c r="K50" s="244">
+      <c r="K53" s="256">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=вскрытие+замков", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L50" s="88" t="inlineStr">
-        <is>
-          <t>Аварийное открытие двери после торгов</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="86" t="n">
+      <c r="L53" s="82" t="inlineStr">
+        <is>
+          <t>Тотальная зачистка и вынос мусора без лифта</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="B51" s="82" t="inlineStr">
+      <c r="B54" s="82" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C51" s="82" t="inlineStr">
+      <c r="C54" s="82" t="inlineStr">
         <is>
           <t>Вывоз мусора</t>
         </is>
       </c>
-      <c r="D51" s="82" t="inlineStr">
+      <c r="D54" s="82" t="inlineStr">
         <is>
           <t>Заказ мусорного контейнера 8 м³ (лодочка)</t>
         </is>
       </c>
-      <c r="E51" s="86" t="inlineStr">
+      <c r="E54" s="86" t="inlineStr">
         <is>
           <t>КОНТЕЙНЕР-МУСОР-8М3</t>
         </is>
       </c>
-      <c r="F51" s="86" t="inlineStr">
+      <c r="F54" s="86" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G51" s="245" t="n">
+      <c r="G54" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="83" t="n">
+      <c r="H54" s="83" t="n">
         <v>8500</v>
       </c>
-      <c r="I51" s="84">
-        <f>G51*H51</f>
-        <v/>
-      </c>
-      <c r="J51" s="82" t="inlineStr">
+      <c r="I54" s="84">
+        <f>G54*H54</f>
+        <v/>
+      </c>
+      <c r="J54" s="82" t="inlineStr">
         <is>
           <t>Елена (вывоз мусора)</t>
         </is>
       </c>
-      <c r="K51" s="244">
+      <c r="K54" s="254">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=вывоз+мусора+контейнер+8+м3", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L51" s="82" t="inlineStr">
-        <is>
-          <t>Вывоз мебели, санузла, чугуна, досок</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="91" t="n">
+      <c r="L54" s="88" t="inlineStr">
+        <is>
+          <t>Сняли старые двери, расширили проем, выставили по уровню</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="91" t="n">
         <v>5</v>
       </c>
-      <c r="B52" s="88" t="inlineStr">
+      <c r="B55" s="88" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C52" s="88" t="inlineStr">
+      <c r="C55" s="88" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
-      <c r="D52" s="88" t="inlineStr">
+      <c r="D55" s="88" t="inlineStr">
         <is>
           <t>Аренда инструмента и помощь соседа по дому</t>
         </is>
       </c>
-      <c r="E52" s="91" t="inlineStr">
+      <c r="E55" s="91" t="inlineStr">
         <is>
           <t>АРЕНДА-ИНСТРУМЕНТ</t>
         </is>
       </c>
-      <c r="F52" s="91" t="inlineStr">
+      <c r="F55" s="91" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G52" s="243" t="n">
+      <c r="G55" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="89" t="n">
+      <c r="H55" s="89" t="n">
         <v>1000</v>
       </c>
-      <c r="I52" s="90">
-        <f>G52*H52</f>
-        <v/>
-      </c>
-      <c r="J52" s="88" t="inlineStr">
+      <c r="I55" s="90">
+        <f>G55*H55</f>
+        <v/>
+      </c>
+      <c r="J55" s="88" t="inlineStr">
         <is>
           <t>Сосед по дому</t>
         </is>
       </c>
-      <c r="K52" s="244">
+      <c r="K55" s="256">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=аренда+перфоратора", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L52" s="88" t="inlineStr">
-        <is>
-          <t>Перфоратор и монтировки для первичного демонтажа</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="86" t="n">
+      <c r="L55" s="82" t="inlineStr">
+        <is>
+          <t>Монтаж всей проводки, сборка щита и счётчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="86" t="n">
         <v>7</v>
       </c>
-      <c r="B53" s="82" t="inlineStr">
+      <c r="B56" s="82" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C53" s="82" t="inlineStr">
+      <c r="C56" s="82" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D53" s="82" t="inlineStr">
+      <c r="D56" s="82" t="inlineStr">
         <is>
           <t>Оплата работы бригады разнорабочих (4 чел., 28 чел.-час, спуск с 5 этажа)</t>
         </is>
       </c>
-      <c r="E53" s="86" t="inlineStr">
+      <c r="E56" s="86" t="inlineStr">
         <is>
           <t>ДЕМОНТАЖ-БРИГАДА-1</t>
         </is>
       </c>
-      <c r="F53" s="86" t="inlineStr">
+      <c r="F56" s="86" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="G53" s="245" t="n">
+      <c r="G56" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="83" t="n">
+      <c r="H56" s="83" t="n">
         <v>16000</v>
       </c>
-      <c r="I53" s="84">
-        <f>G53*H53</f>
-        <v/>
-      </c>
-      <c r="J53" s="82" t="inlineStr">
+      <c r="I56" s="84">
+        <f>G56*H56</f>
+        <v/>
+      </c>
+      <c r="J56" s="82" t="inlineStr">
         <is>
           <t>Бригада разнорабочих</t>
         </is>
       </c>
-      <c r="K53" s="244">
+      <c r="K56" s="254">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=демонтаж+квартиры+разнорабочие", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L53" s="82" t="inlineStr">
-        <is>
-          <t>Тотальная зачистка и вынос мусора без лифта</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="91" t="n">
+      <c r="L56" s="88" t="inlineStr">
+        <is>
+          <t>Снятие старых слоев, обеспыливание поверхностей</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="91" t="n">
         <v>18</v>
       </c>
-      <c r="B54" s="88" t="inlineStr">
+      <c r="B57" s="88" t="inlineStr">
         <is>
           <t>Входная группа</t>
         </is>
       </c>
-      <c r="C54" s="88" t="inlineStr">
+      <c r="C57" s="88" t="inlineStr">
         <is>
           <t>Монтаж</t>
         </is>
       </c>
-      <c r="D54" s="88" t="inlineStr">
+      <c r="D57" s="88" t="inlineStr">
         <is>
           <t>Монтаж входной двери (демонтаж 2 старых дверей + монтаж новой)</t>
         </is>
       </c>
-      <c r="E54" s="91" t="inlineStr">
+      <c r="E57" s="91" t="inlineStr">
         <is>
           <t>МОНТАЖ-ДВЕРИ-ВХОД</t>
         </is>
       </c>
-      <c r="F54" s="91" t="inlineStr">
+      <c r="F57" s="91" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G54" s="243" t="n">
+      <c r="G57" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="89" t="n">
+      <c r="H57" s="89" t="n">
         <v>9000</v>
       </c>
-      <c r="I54" s="90">
-        <f>G54*H54</f>
-        <v/>
-      </c>
-      <c r="J54" s="88" t="inlineStr">
+      <c r="I57" s="90">
+        <f>G57*H57</f>
+        <v/>
+      </c>
+      <c r="J57" s="88" t="inlineStr">
         <is>
           <t>Андрей (монтаж дверей)</t>
         </is>
       </c>
-      <c r="K54" s="244">
+      <c r="K57" s="256">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=установка+входных+дверей", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L54" s="88" t="inlineStr">
-        <is>
-          <t>Сняли старые двери, расширили проем, выставили по уровню</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="86" t="n">
+      <c r="L57" s="82" t="inlineStr">
+        <is>
+          <t>Перевозка партии смесей, керамогранита и ванны</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="86" t="n">
         <v>22</v>
       </c>
-      <c r="B55" s="82" t="inlineStr">
+      <c r="B58" s="82" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C55" s="82" t="inlineStr">
+      <c r="C58" s="82" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D55" s="82" t="inlineStr">
+      <c r="D58" s="82" t="inlineStr">
         <is>
           <t>Электромонтажные работы под ключ (разводка 32 точек, штробы, щит, счётчик)</t>
         </is>
       </c>
-      <c r="E55" s="86" t="inlineStr">
+      <c r="E58" s="86" t="inlineStr">
         <is>
           <t>РАБОТА-ЭЛЕКТРИКА-32</t>
         </is>
       </c>
-      <c r="F55" s="86" t="inlineStr">
+      <c r="F58" s="86" t="inlineStr">
         <is>
           <t>договор</t>
         </is>
       </c>
-      <c r="G55" s="245" t="n">
+      <c r="G58" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="83" t="n">
+      <c r="H58" s="83" t="n">
         <v>50000</v>
       </c>
-      <c r="I55" s="84">
-        <f>G55*H55</f>
-        <v/>
-      </c>
-      <c r="J55" s="82" t="inlineStr">
+      <c r="I58" s="84">
+        <f>G58*H58</f>
+        <v/>
+      </c>
+      <c r="J58" s="82" t="inlineStr">
         <is>
           <t>Анатолий Кушнарев (бригада)</t>
         </is>
       </c>
-      <c r="K55" s="244">
+      <c r="K58" s="254">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=электромонтаж+квартиры+под+ключ", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L55" s="82" t="inlineStr">
-        <is>
-          <t>Монтаж всей проводки, сборка щита и счётчика</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="91" t="n">
+      <c r="L58" s="88" t="inlineStr">
+        <is>
+          <t>Разгрузка 1.5 тонн смесей на 5 этаж без лифта</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="91" t="n">
         <v>24</v>
       </c>
-      <c r="B56" s="88" t="inlineStr">
+      <c r="B59" s="88" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C56" s="88" t="inlineStr">
+      <c r="C59" s="88" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D56" s="88" t="inlineStr">
+      <c r="D59" s="88" t="inlineStr">
         <is>
           <t>Зачистка стен/потолка (обои, плитка в зале и спальне), вынос мусора, 1-й слой грунта</t>
         </is>
       </c>
-      <c r="E56" s="91" t="inlineStr">
+      <c r="E59" s="91" t="inlineStr">
         <is>
           <t>ДЕМОНТАЖ-ЗАЧИСТКА-2</t>
         </is>
       </c>
-      <c r="F56" s="91" t="inlineStr">
+      <c r="F59" s="91" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="G56" s="243" t="n">
+      <c r="G59" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H56" s="89" t="n">
+      <c r="H59" s="89" t="n">
         <v>15000</v>
       </c>
-      <c r="I56" s="90">
-        <f>G56*H56</f>
-        <v/>
-      </c>
-      <c r="J56" s="88" t="inlineStr">
+      <c r="I59" s="90">
+        <f>G59*H59</f>
+        <v/>
+      </c>
+      <c r="J59" s="88" t="inlineStr">
         <is>
           <t>Бригада разнорабочих</t>
         </is>
       </c>
-      <c r="K56" s="244">
+      <c r="K59" s="256">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=зачистка+стен+демонтаж+обоев", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L56" s="88" t="inlineStr">
-        <is>
-          <t>Снятие старых слоев, обеспыливание поверхностей</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="86" t="n">
+      <c r="L59" s="82" t="inlineStr">
+        <is>
+          <t>Штукатурка 69 м² + шпаклёвка стен 106 м² по 500₽. White Box под ключ</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="86" t="n">
         <v>40</v>
       </c>
-      <c r="B57" s="82" t="inlineStr">
+      <c r="B60" s="82" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="C57" s="82" t="inlineStr">
+      <c r="C60" s="82" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
-      <c r="D57" s="82" t="inlineStr">
+      <c r="D60" s="82" t="inlineStr">
         <is>
           <t>Грузовое такси / Доставка закупки материалов и сантехники (Лемана — Фрунзе 17)</t>
         </is>
       </c>
-      <c r="E57" s="86" t="inlineStr">
+      <c r="E60" s="86" t="inlineStr">
         <is>
           <t>ГРУЗОТАКСИ-ЛЕРОЙ</t>
         </is>
       </c>
-      <c r="F57" s="86" t="inlineStr">
+      <c r="F60" s="86" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G57" s="245" t="n">
+      <c r="G60" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H57" s="83" t="n">
+      <c r="H60" s="83" t="n">
         <v>2100</v>
       </c>
-      <c r="I57" s="84">
-        <f>G57*H57</f>
-        <v/>
-      </c>
-      <c r="J57" s="82" t="inlineStr">
+      <c r="I60" s="84">
+        <f>G60*H60</f>
+        <v/>
+      </c>
+      <c r="J60" s="82" t="inlineStr">
         <is>
           <t>Грузовое такси / Перевозка</t>
         </is>
       </c>
-      <c r="K57" s="244">
+      <c r="K60" s="254">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=грузоперевозки+грузовое+такси", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L57" s="82" t="inlineStr">
-        <is>
-          <t>Перевозка партии смесей, керамогранита и ванны</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="91" t="n">
+      <c r="L60" s="88" t="inlineStr">
+        <is>
+          <t>Демонтаж старого змеевика, нарезка 2 резьб клуппом под установку запорных кранов</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="91" t="n">
         <v>41</v>
       </c>
-      <c r="B58" s="88" t="inlineStr">
+      <c r="B61" s="88" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C58" s="88" t="inlineStr">
+      <c r="C61" s="88" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D58" s="88" t="inlineStr">
+      <c r="D61" s="88" t="inlineStr">
         <is>
           <t>Погрузка в Лемана ПРО, разгрузка и подъём на 5 этаж + демонтаж плитки пола с/у</t>
         </is>
       </c>
-      <c r="E58" s="91" t="inlineStr">
+      <c r="E61" s="91" t="inlineStr">
         <is>
           <t>ПОДЪЕМ-ДЕМОНТАЖ-СУ</t>
         </is>
       </c>
-      <c r="F58" s="91" t="inlineStr">
+      <c r="F61" s="91" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="G58" s="243" t="n">
+      <c r="G61" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H58" s="89" t="n">
+      <c r="H61" s="89" t="n">
         <v>15000</v>
       </c>
-      <c r="I58" s="90">
-        <f>G58*H58</f>
-        <v/>
-      </c>
-      <c r="J58" s="88" t="inlineStr">
+      <c r="I61" s="90">
+        <f>G61*H61</f>
+        <v/>
+      </c>
+      <c r="J61" s="88" t="inlineStr">
         <is>
           <t>Бригада грузчиков / Разнорабочие</t>
         </is>
       </c>
-      <c r="K58" s="244">
+      <c r="K61" s="256">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=подъем+стройматериалов+на+этаж+грузчики", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L58" s="88" t="inlineStr">
-        <is>
-          <t>Разгрузка 1.5 тонн смесей на 5 этаж без лифта</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="86" t="n">
+      <c r="L61" s="82" t="inlineStr">
+        <is>
+          <t>Оперативный подвоз купленного инструмента и материалов из Лемана ПРО на ул. Фрунзе 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="86" t="n">
         <v>42</v>
       </c>
-      <c r="B59" s="82" t="inlineStr">
+      <c r="B62" s="82" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C59" s="82" t="inlineStr">
+      <c r="C62" s="82" t="inlineStr">
         <is>
           <t>Отделочные работы</t>
         </is>
       </c>
-      <c r="D59" s="82" t="inlineStr">
+      <c r="D62" s="82" t="inlineStr">
         <is>
           <t>Штукатурка (69 м² по 500 ₽) и шпаклёвка стен White Box (106 м² по 500 ₽)</t>
         </is>
       </c>
-      <c r="E59" s="86" t="inlineStr">
+      <c r="E62" s="86" t="inlineStr">
         <is>
           <t>ОТДЕЛКА-СТЕН-ЕЛЕНА</t>
         </is>
       </c>
-      <c r="F59" s="86" t="inlineStr">
+      <c r="F62" s="86" t="inlineStr">
         <is>
           <t>комплекс</t>
         </is>
       </c>
-      <c r="G59" s="245" t="n">
+      <c r="G62" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H59" s="83" t="n">
+      <c r="H62" s="83" t="n">
         <v>87500</v>
       </c>
-      <c r="I59" s="84">
-        <f>G59*H59</f>
-        <v/>
-      </c>
-      <c r="J59" s="82" t="inlineStr">
+      <c r="I62" s="84">
+        <f>G62*H62</f>
+        <v/>
+      </c>
+      <c r="J62" s="82" t="inlineStr">
         <is>
           <t>Елена (мастер-отделочник)</t>
         </is>
       </c>
-      <c r="K59" s="244">
+      <c r="K62" s="254">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=штукатурка+шпаклевка+стен", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L59" s="82" t="inlineStr">
-        <is>
-          <t>Штукатурка 69 м² + шпаклёвка стен 106 м² по 500₽. White Box под ключ</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="91" t="n">
+      <c r="L62" s="88" t="inlineStr">
+        <is>
+          <t>Оперативный подвоз материалов и крепежа</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="91" t="n">
         <v>48</v>
       </c>
-      <c r="B60" s="88" t="inlineStr">
+      <c r="B63" s="88" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C60" s="88" t="inlineStr">
+      <c r="C63" s="88" t="inlineStr">
         <is>
           <t>Сантехника / Работы</t>
         </is>
       </c>
-      <c r="D60" s="88" t="inlineStr">
+      <c r="D63" s="88" t="inlineStr">
         <is>
           <t>Срезка полотенцесушителя и нарезка трубной резьбы на отводах стояка</t>
         </is>
       </c>
-      <c r="E60" s="91" t="inlineStr">
+      <c r="E63" s="91" t="inlineStr">
         <is>
           <t>РАБОТА-САНТЕХ-СУШ</t>
         </is>
       </c>
-      <c r="F60" s="91" t="inlineStr">
+      <c r="F63" s="91" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G60" s="243" t="n">
+      <c r="G63" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H60" s="89" t="n">
+      <c r="H63" s="89" t="n">
         <v>3000</v>
       </c>
-      <c r="I60" s="90">
-        <f>G60*H60</f>
-        <v/>
-      </c>
-      <c r="J60" s="88" t="inlineStr">
+      <c r="I63" s="90">
+        <f>G63*H63</f>
+        <v/>
+      </c>
+      <c r="J63" s="88" t="inlineStr">
         <is>
           <t>Вадим (сантехник УК) / Сантехник</t>
         </is>
       </c>
-      <c r="K60" s="244">
+      <c r="K63" s="256">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=сантехник+срезка+полотенцесушителя", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L60" s="88" t="inlineStr">
-        <is>
-          <t>Демонтаж старого змеевика, нарезка 2 резьб клуппом под установку запорных кранов</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="86" t="n">
+      <c r="L63" s="82" t="inlineStr">
+        <is>
+          <t>Подготовка и аванс плиточнику за работы в с/у</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="86" t="n">
         <v>49</v>
       </c>
-      <c r="B61" s="82" t="inlineStr">
+      <c r="B64" s="82" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="C61" s="82" t="inlineStr">
+      <c r="C64" s="82" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
-      <c r="D61" s="82" t="inlineStr">
+      <c r="D64" s="82" t="inlineStr">
         <is>
           <t>Такси (оперативная доставка материалов и инструмента из Лемана ПРО на объект)</t>
         </is>
       </c>
-      <c r="E61" s="86" t="inlineStr">
+      <c r="E64" s="86" t="inlineStr">
         <is>
           <t>ТАКСИ-ЛЕРОЙ-ОБЪЕКТ</t>
         </is>
       </c>
-      <c r="F61" s="86" t="inlineStr">
+      <c r="F64" s="86" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G61" s="245" t="n">
+      <c r="G64" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H61" s="83" t="n">
+      <c r="H64" s="83" t="n">
         <v>1000</v>
       </c>
-      <c r="I61" s="84">
-        <f>G61*H61</f>
-        <v/>
-      </c>
-      <c r="J61" s="82" t="inlineStr">
+      <c r="I64" s="84">
+        <f>G64*H64</f>
+        <v/>
+      </c>
+      <c r="J64" s="82" t="inlineStr">
         <is>
           <t>Такси (Яндекс Go)</t>
         </is>
       </c>
-      <c r="K61" s="244">
+      <c r="K64" s="254">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=такси+доставка+курьер", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L61" s="82" t="inlineStr">
-        <is>
-          <t>Оперативный подвоз купленного инструмента и материалов из Лемана ПРО на ул. Фрунзе 17</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="91" t="n">
+      <c r="L64" s="88" t="inlineStr">
+        <is>
+          <t>Заливка прочной стяжки пола с/у по маякам с ускорителем Cemfix</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="91" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="88" t="inlineStr">
+      <c r="B65" s="88" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="C62" s="88" t="inlineStr">
+      <c r="C65" s="88" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
-      <c r="D62" s="88" t="inlineStr">
+      <c r="D65" s="88" t="inlineStr">
         <is>
           <t>Такси (оперативная доставка / подвоз материалов на объект)</t>
         </is>
       </c>
-      <c r="E62" s="91" t="inlineStr">
+      <c r="E65" s="91" t="inlineStr">
         <is>
           <t>ТАКСИ-ДОСТАВКА-2</t>
         </is>
       </c>
-      <c r="F62" s="91" t="inlineStr">
+      <c r="F65" s="91" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G62" s="243" t="n">
+      <c r="G65" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H62" s="89" t="n">
+      <c r="H65" s="89" t="n">
         <v>850</v>
       </c>
-      <c r="I62" s="90">
-        <f>G62*H62</f>
-        <v/>
-      </c>
-      <c r="J62" s="88" t="inlineStr">
+      <c r="I65" s="90">
+        <f>G65*H65</f>
+        <v/>
+      </c>
+      <c r="J65" s="88" t="inlineStr">
         <is>
           <t>Такси (Яндекс Go)</t>
         </is>
       </c>
-      <c r="K62" s="244">
+      <c r="K65" s="256">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=такси+доставка+курьер", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L62" s="88" t="inlineStr">
-        <is>
-          <t>Оперативный подвоз материалов и крепежа</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="86" t="n">
+      <c r="L65" s="82" t="inlineStr">
+        <is>
+          <t>Штукатурка стен с/у по маякам с идеальной геометрией 90° под ванну 150см</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="86" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="82" t="inlineStr">
+      <c r="B66" s="82" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C63" s="82" t="inlineStr">
+      <c r="C66" s="82" t="inlineStr">
         <is>
           <t>Плиточные работы</t>
         </is>
       </c>
-      <c r="D63" s="82" t="inlineStr">
+      <c r="D66" s="82" t="inlineStr">
         <is>
           <t>Работы плиточника (аванс / подготовка к укладке плитки в санузле)</t>
         </is>
       </c>
-      <c r="E63" s="86" t="inlineStr">
+      <c r="E66" s="86" t="inlineStr">
         <is>
           <t>РАБОТА-ПЛИТОЧНИК-1</t>
         </is>
       </c>
-      <c r="F63" s="86" t="inlineStr">
+      <c r="F66" s="86" t="inlineStr">
         <is>
           <t>аванс</t>
         </is>
       </c>
-      <c r="G63" s="245" t="n">
+      <c r="G66" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H63" s="83" t="n">
+      <c r="H66" s="83" t="n">
         <v>1700</v>
       </c>
-      <c r="I63" s="84">
-        <f>G63*H63</f>
-        <v/>
-      </c>
-      <c r="J63" s="82" t="inlineStr">
+      <c r="I66" s="84">
+        <f>G66*H66</f>
+        <v/>
+      </c>
+      <c r="J66" s="82" t="inlineStr">
         <is>
           <t>Плиточник (мастер)</t>
         </is>
       </c>
-      <c r="K63" s="244">
+      <c r="K66" s="254">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=плиточник+укладка+плитки", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L63" s="82" t="inlineStr">
-        <is>
-          <t>Подготовка и аванс плиточнику за работы в с/у</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="91" t="n">
+      <c r="L66" s="246" t="n"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="91" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="88" t="inlineStr">
+      <c r="B67" s="88" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C64" s="88" t="inlineStr">
+      <c r="C67" s="88" t="inlineStr">
         <is>
           <t>Стяжка пола</t>
         </is>
       </c>
-      <c r="D64" s="88" t="inlineStr">
+      <c r="D67" s="88" t="inlineStr">
         <is>
           <t>Работы плиточника: заливка стяжки пола в санузле/туалете</t>
         </is>
       </c>
-      <c r="E64" s="91" t="inlineStr">
+      <c r="E67" s="91" t="inlineStr">
         <is>
           <t>СТЯЖКА-ПОЛА-СУ</t>
         </is>
       </c>
-      <c r="F64" s="91" t="inlineStr">
+      <c r="F67" s="91" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G64" s="243" t="n">
+      <c r="G67" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H64" s="89" t="n">
+      <c r="H67" s="89" t="n">
         <v>3300</v>
       </c>
-      <c r="I64" s="90">
-        <f>G64*H64</f>
-        <v/>
-      </c>
-      <c r="J64" s="88" t="inlineStr">
+      <c r="I67" s="90">
+        <f>G67*H67</f>
+        <v/>
+      </c>
+      <c r="J67" s="88" t="inlineStr">
         <is>
           <t>Плиточник (мастер)</t>
         </is>
       </c>
-      <c r="K64" s="244">
+      <c r="K67" s="256">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=стяжка+пола+санузел", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L64" s="88" t="inlineStr">
-        <is>
-          <t>Заливка прочной стяжки пола с/у по маякам с ускорителем Cemfix</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="86" t="n">
+      <c r="L67" s="251" t="n"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="86" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="82" t="inlineStr">
+      <c r="B68" s="82" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C65" s="82" t="inlineStr">
+      <c r="C68" s="82" t="inlineStr">
         <is>
           <t>Штукатурка стен</t>
         </is>
       </c>
-      <c r="D65" s="82" t="inlineStr">
+      <c r="D68" s="82" t="inlineStr">
         <is>
           <t>Оплата за штукатурку туалета (санузла) под 90° под ванну и плитку</t>
         </is>
       </c>
-      <c r="E65" s="86" t="inlineStr">
+      <c r="E68" s="86" t="inlineStr">
         <is>
           <t>ШТУКАТУРКА-СУ-90</t>
         </is>
       </c>
-      <c r="F65" s="86" t="inlineStr">
+      <c r="F68" s="86" t="inlineStr">
         <is>
           <t>комплекс</t>
         </is>
       </c>
-      <c r="G65" s="245" t="n">
+      <c r="G68" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H65" s="83" t="n">
+      <c r="H68" s="83" t="n">
         <v>13400</v>
       </c>
-      <c r="I65" s="84">
-        <f>G65*H65</f>
-        <v/>
-      </c>
-      <c r="J65" s="82" t="inlineStr">
+      <c r="I68" s="84">
+        <f>G68*H68</f>
+        <v/>
+      </c>
+      <c r="J68" s="82" t="inlineStr">
         <is>
           <t>Елена (мастер-отделочник)</t>
         </is>
       </c>
-      <c r="K65" s="244">
+      <c r="K68" s="254">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=штукатурка+санузла+под+90", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L65" s="82" t="inlineStr">
-        <is>
-          <t>Штукатурка стен с/у по маякам с идеальной геометрией 90° под ванну 150см</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="246" t="n"/>
-      <c r="B66" s="247" t="inlineStr">
+      <c r="L68" s="88" t="inlineStr">
+        <is>
+          <t>ЭЦП для участия в торгах и регистрации права</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="91" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="88" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C69" s="88" t="inlineStr">
+        <is>
+          <t>Сантехнические работы</t>
+        </is>
+      </c>
+      <c r="D69" s="88" t="inlineStr">
+        <is>
+          <t>Работы сантехников (разводка/монтаж узлов водоснабжения и канализации)</t>
+        </is>
+      </c>
+      <c r="E69" s="91" t="inlineStr">
+        <is>
+          <t>РАБОТА-САНТЕХ-РАЗВОДКА</t>
+        </is>
+      </c>
+      <c r="F69" s="91" t="inlineStr">
+        <is>
+          <t>комплекс</t>
+        </is>
+      </c>
+      <c r="G69" s="255" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="89" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I69" s="90">
+        <f>G69*H69</f>
+        <v/>
+      </c>
+      <c r="J69" s="88" t="inlineStr">
+        <is>
+          <t>Сантехники (мастера)</t>
+        </is>
+      </c>
+      <c r="K69" s="256">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=разводка+труб+сантехника", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L69" s="82" t="inlineStr">
+        <is>
+          <t>Официальная пошлина Росреестра</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="257" t="n"/>
+      <c r="B70" s="258" t="inlineStr">
         <is>
           <t>ИТОГО РАБОТЫ И ЛОГИСТИКА:</t>
         </is>
       </c>
-      <c r="C66" s="246" t="n"/>
-      <c r="D66" s="246" t="n"/>
-      <c r="E66" s="246" t="n"/>
-      <c r="F66" s="246" t="n"/>
-      <c r="G66" s="246" t="n"/>
-      <c r="H66" s="246" t="n"/>
-      <c r="I66" s="248">
-        <f>SUM(I50:I65)</f>
-        <v/>
-      </c>
-      <c r="J66" s="246" t="n"/>
-      <c r="K66" s="246" t="n"/>
-      <c r="L66" s="246" t="n"/>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="251" t="n"/>
-      <c r="B67" s="251" t="inlineStr">
-        <is>
-          <t>🏛 БЛОК 4: ЮРИДИЧЕСКИЕ РАСХОДЫ, ПОШЛИНЫ, ГАЗ, ЭНЕРГОСБЫТ И IT (8 ПОЗИЦИЙ)</t>
-        </is>
-      </c>
-      <c r="C67" s="251" t="n"/>
-      <c r="D67" s="251" t="n"/>
-      <c r="E67" s="251" t="n"/>
-      <c r="F67" s="251" t="n"/>
-      <c r="G67" s="251" t="n"/>
-      <c r="H67" s="251" t="n"/>
-      <c r="I67" s="251" t="n"/>
-      <c r="J67" s="251" t="n"/>
-      <c r="K67" s="251" t="n"/>
-      <c r="L67" s="251" t="n"/>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="91" t="n">
+      <c r="C70" s="259" t="n"/>
+      <c r="D70" s="259" t="n"/>
+      <c r="E70" s="257" t="n"/>
+      <c r="F70" s="257" t="n"/>
+      <c r="G70" s="260" t="n"/>
+      <c r="H70" s="261" t="n"/>
+      <c r="I70" s="261">
+        <f>SUM(I53:I69)</f>
+        <v/>
+      </c>
+      <c r="J70" s="259" t="n"/>
+      <c r="K70" s="257" t="n"/>
+      <c r="L70" s="88" t="inlineStr">
+        <is>
+          <t>Инфраструктура проектов и аналитика</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="276" t="n"/>
+      <c r="B71" s="277" t="inlineStr">
+        <is>
+          <t>🏛 БЛОК 4: ЮРИДИЧЕСКИЕ РАСХОДЫ, ПОШЛИНЫ, ГАЗ, ЭНЕРГОСБЫТ И IT (9 ПОЗИЦИЙ)</t>
+        </is>
+      </c>
+      <c r="C71" s="278" t="n"/>
+      <c r="D71" s="278" t="n"/>
+      <c r="E71" s="276" t="n"/>
+      <c r="F71" s="276" t="n"/>
+      <c r="G71" s="279" t="n"/>
+      <c r="H71" s="280" t="n"/>
+      <c r="I71" s="281" t="n"/>
+      <c r="J71" s="278" t="n"/>
+      <c r="K71" s="282" t="n"/>
+      <c r="L71" s="82" t="inlineStr">
+        <is>
+          <t>Обязательная проверка тяги для газовой колонки</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="B68" s="88" t="inlineStr">
+      <c r="B72" s="82" t="inlineStr">
         <is>
           <t>Юр. оформление</t>
         </is>
       </c>
-      <c r="C68" s="88" t="inlineStr">
+      <c r="C72" s="82" t="inlineStr">
         <is>
           <t>Торги</t>
         </is>
       </c>
-      <c r="D68" s="88" t="inlineStr">
+      <c r="D72" s="82" t="inlineStr">
         <is>
           <t>Выпуск квалифицированной ЭЦП (электронная цифровая подпись)</t>
         </is>
       </c>
-      <c r="E68" s="91" t="inlineStr">
+      <c r="E72" s="86" t="inlineStr">
         <is>
           <t>ЭЦП-КОНТУР</t>
         </is>
       </c>
-      <c r="F68" s="91" t="inlineStr">
+      <c r="F72" s="86" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G68" s="243" t="n">
+      <c r="G72" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H68" s="89" t="n">
+      <c r="H72" s="83" t="n">
         <v>7000</v>
       </c>
-      <c r="I68" s="90">
-        <f>G68*H68</f>
-        <v/>
-      </c>
-      <c r="J68" s="88" t="inlineStr">
+      <c r="I72" s="84">
+        <f>G72*H72</f>
+        <v/>
+      </c>
+      <c r="J72" s="82" t="inlineStr">
         <is>
           <t>УЦ / Контур</t>
         </is>
       </c>
-      <c r="K68" s="244">
+      <c r="K72" s="254">
         <f>HYPERLINK("https://ca.kontur.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L68" s="88" t="inlineStr">
-        <is>
-          <t>ЭЦП для участия в торгах и регистрации права</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="86" t="n">
+      <c r="L72" s="88" t="inlineStr">
+        <is>
+          <t>Погашение начислений газовой службы</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="91" t="n">
         <v>2</v>
       </c>
-      <c r="B69" s="82" t="inlineStr">
+      <c r="B73" s="88" t="inlineStr">
         <is>
           <t>Юр. оформление</t>
         </is>
       </c>
-      <c r="C69" s="82" t="inlineStr">
+      <c r="C73" s="88" t="inlineStr">
         <is>
           <t>Росреестр</t>
         </is>
       </c>
-      <c r="D69" s="82" t="inlineStr">
+      <c r="D73" s="88" t="inlineStr">
         <is>
           <t>Государственная пошлина (регистрация перехода права собственности)</t>
         </is>
       </c>
-      <c r="E69" s="86" t="inlineStr">
+      <c r="E73" s="91" t="inlineStr">
         <is>
           <t>ГОСПОШЛИНА-ПРАВО</t>
         </is>
       </c>
-      <c r="F69" s="86" t="inlineStr">
+      <c r="F73" s="91" t="inlineStr">
         <is>
           <t>платеж</t>
         </is>
       </c>
-      <c r="G69" s="245" t="n">
+      <c r="G73" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H69" s="83" t="n">
+      <c r="H73" s="89" t="n">
         <v>5000</v>
       </c>
-      <c r="I69" s="84">
-        <f>G69*H69</f>
-        <v/>
-      </c>
-      <c r="J69" s="82" t="inlineStr">
+      <c r="I73" s="90">
+        <f>G73*H73</f>
+        <v/>
+      </c>
+      <c r="J73" s="88" t="inlineStr">
         <is>
           <t>Росреестр</t>
         </is>
       </c>
-      <c r="K69" s="244">
+      <c r="K73" s="256">
         <f>HYPERLINK("https://rosreestr.gov.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L69" s="82" t="inlineStr">
-        <is>
-          <t>Официальная пошлина Росреестра</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="91" t="n">
+      <c r="L73" s="82" t="inlineStr">
+        <is>
+          <t>Срочное снятие пломбы за 5 дней</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="86" t="n">
         <v>10</v>
       </c>
-      <c r="B70" s="88" t="inlineStr">
+      <c r="B74" s="82" t="inlineStr">
         <is>
           <t>IT / AI</t>
         </is>
       </c>
-      <c r="C70" s="88" t="inlineStr">
+      <c r="C74" s="82" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="D70" s="88" t="inlineStr">
+      <c r="D74" s="82" t="inlineStr">
         <is>
           <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 1</t>
         </is>
       </c>
-      <c r="E70" s="91" t="inlineStr">
+      <c r="E74" s="86" t="inlineStr">
         <is>
           <t>OPENROUTER-TRANS-1</t>
         </is>
       </c>
-      <c r="F70" s="91" t="inlineStr">
+      <c r="F74" s="86" t="inlineStr">
         <is>
           <t>платёж</t>
         </is>
       </c>
-      <c r="G70" s="243" t="n">
+      <c r="G74" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H70" s="89" t="n">
+      <c r="H74" s="83" t="n">
         <v>3000</v>
       </c>
-      <c r="I70" s="90">
-        <f>G70*H70</f>
-        <v/>
-      </c>
-      <c r="J70" s="88" t="inlineStr">
+      <c r="I74" s="84">
+        <f>G74*H74</f>
+        <v/>
+      </c>
+      <c r="J74" s="82" t="inlineStr">
         <is>
           <t>OpenRouter</t>
         </is>
       </c>
-      <c r="K70" s="244">
+      <c r="K74" s="254">
         <f>HYPERLINK("https://openrouter.ai/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L70" s="88" t="inlineStr">
-        <is>
-          <t>Инфраструктура проектов и аналитика</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="86" t="n">
+      <c r="L74" s="88" t="inlineStr">
+        <is>
+          <t>Пополнение баланса API для расчётов и смет</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="91" t="n">
         <v>12</v>
       </c>
-      <c r="B71" s="82" t="inlineStr">
+      <c r="B75" s="88" t="inlineStr">
         <is>
           <t>Газ</t>
         </is>
       </c>
-      <c r="C71" s="82" t="inlineStr">
+      <c r="C75" s="88" t="inlineStr">
         <is>
           <t>Безопасность</t>
         </is>
       </c>
-      <c r="D71" s="82" t="inlineStr">
+      <c r="D75" s="88" t="inlineStr">
         <is>
           <t>Акт ВДПО — проверка дымохода и вентканала</t>
         </is>
       </c>
-      <c r="E71" s="86" t="inlineStr">
+      <c r="E75" s="91" t="inlineStr">
         <is>
           <t>ВДПО-АКТ-ВЕНТ</t>
         </is>
       </c>
-      <c r="F71" s="86" t="inlineStr">
+      <c r="F75" s="91" t="inlineStr">
         <is>
           <t>акт</t>
         </is>
       </c>
-      <c r="G71" s="245" t="n">
+      <c r="G75" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H71" s="83" t="n">
+      <c r="H75" s="89" t="n">
         <v>1500</v>
       </c>
-      <c r="I71" s="84">
-        <f>G71*H71</f>
-        <v/>
-      </c>
-      <c r="J71" s="82" t="inlineStr">
+      <c r="I75" s="90">
+        <f>G75*H75</f>
+        <v/>
+      </c>
+      <c r="J75" s="88" t="inlineStr">
         <is>
           <t>ВДПО / Газовая служба</t>
         </is>
       </c>
-      <c r="K71" s="244">
+      <c r="K75" s="256">
         <f>HYPERLINK("https://vdpo71.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L71" s="82" t="inlineStr">
-        <is>
-          <t>Обязательная проверка тяги для газовой колонки</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="91" t="n">
+      <c r="L75" s="82" t="inlineStr">
+        <is>
+          <t>Фиксация показаний и снятие пломбы без выезда</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="86" t="n">
         <v>13</v>
       </c>
-      <c r="B72" s="88" t="inlineStr">
+      <c r="B76" s="82" t="inlineStr">
         <is>
           <t>Газ</t>
         </is>
       </c>
-      <c r="C72" s="88" t="inlineStr">
+      <c r="C76" s="82" t="inlineStr">
         <is>
           <t>Коммуналка</t>
         </is>
       </c>
-      <c r="D72" s="88" t="inlineStr">
+      <c r="D76" s="82" t="inlineStr">
         <is>
           <t>Оплата квитанций Тулагоргаз (платежки/техобслуживание)</t>
         </is>
       </c>
-      <c r="E72" s="91" t="inlineStr">
+      <c r="E76" s="86" t="inlineStr">
         <is>
           <t>ТУЛАГОРГАЗ-КВИТАНЦИЯ</t>
         </is>
       </c>
-      <c r="F72" s="91" t="inlineStr">
+      <c r="F76" s="86" t="inlineStr">
         <is>
           <t>платеж</t>
         </is>
       </c>
-      <c r="G72" s="243" t="n">
+      <c r="G76" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H72" s="89" t="n">
+      <c r="H76" s="83" t="n">
         <v>800</v>
       </c>
-      <c r="I72" s="90">
-        <f>G72*H72</f>
-        <v/>
-      </c>
-      <c r="J72" s="88" t="inlineStr">
+      <c r="I76" s="84">
+        <f>G76*H76</f>
+        <v/>
+      </c>
+      <c r="J76" s="82" t="inlineStr">
         <is>
           <t>Тулагоргаз</t>
         </is>
       </c>
-      <c r="K72" s="244">
+      <c r="K76" s="254">
         <f>HYPERLINK("https://tulagorgaz.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L72" s="88" t="inlineStr">
-        <is>
-          <t>Погашение начислений газовой службы</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="86" t="n">
+      <c r="L76" s="246" t="n"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="91" t="n">
         <v>21</v>
       </c>
-      <c r="B73" s="82" t="inlineStr">
+      <c r="B77" s="88" t="inlineStr">
         <is>
           <t>Энергосбыт</t>
         </is>
       </c>
-      <c r="C73" s="82" t="inlineStr">
+      <c r="C77" s="88" t="inlineStr">
         <is>
           <t>Учёт</t>
         </is>
       </c>
-      <c r="D73" s="82" t="inlineStr">
+      <c r="D77" s="88" t="inlineStr">
         <is>
           <t>Срочный выезд инспектора ТНС энерго Тула (снятие пломбы со старого счётчика)</t>
         </is>
       </c>
-      <c r="E73" s="86" t="inlineStr">
+      <c r="E77" s="91" t="inlineStr">
         <is>
           <t>ТНС-ВЫЕЗД-ПЛОМБА</t>
         </is>
       </c>
-      <c r="F73" s="86" t="inlineStr">
+      <c r="F77" s="91" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G73" s="245" t="n">
+      <c r="G77" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H73" s="83" t="n">
+      <c r="H77" s="89" t="n">
         <v>2500</v>
       </c>
-      <c r="I73" s="84">
-        <f>G73*H73</f>
-        <v/>
-      </c>
-      <c r="J73" s="82" t="inlineStr">
+      <c r="I77" s="90">
+        <f>G77*H77</f>
+        <v/>
+      </c>
+      <c r="J77" s="88" t="inlineStr">
         <is>
           <t>АО "ТНС энерго Тула"</t>
         </is>
       </c>
-      <c r="K73" s="244">
+      <c r="K77" s="256">
         <f>HYPERLINK("https://tns-e.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L73" s="82" t="inlineStr">
-        <is>
-          <t>Срочное снятие пломбы за 5 дней</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="91" t="n">
+      <c r="L77" s="238" t="n"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="86" t="n">
         <v>31</v>
       </c>
-      <c r="B74" s="88" t="inlineStr">
+      <c r="B78" s="82" t="inlineStr">
         <is>
           <t>IT / AI</t>
         </is>
       </c>
-      <c r="C74" s="88" t="inlineStr">
+      <c r="C78" s="82" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="D74" s="88" t="inlineStr">
+      <c r="D78" s="82" t="inlineStr">
         <is>
           <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 2</t>
         </is>
       </c>
-      <c r="E74" s="91" t="inlineStr">
+      <c r="E78" s="86" t="inlineStr">
         <is>
           <t>OPENROUTER-TRANS-2</t>
         </is>
       </c>
-      <c r="F74" s="91" t="inlineStr">
+      <c r="F78" s="86" t="inlineStr">
         <is>
           <t>платёж</t>
         </is>
       </c>
-      <c r="G74" s="243" t="n">
+      <c r="G78" s="253" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="89" t="n">
+      <c r="H78" s="83" t="n">
         <v>2500</v>
       </c>
-      <c r="I74" s="90">
-        <f>G74*H74</f>
-        <v/>
-      </c>
-      <c r="J74" s="88" t="inlineStr">
+      <c r="I78" s="84">
+        <f>G78*H78</f>
+        <v/>
+      </c>
+      <c r="J78" s="82" t="inlineStr">
         <is>
           <t>OpenRouter</t>
         </is>
       </c>
-      <c r="K74" s="244">
+      <c r="K78" s="254">
         <f>HYPERLINK("https://openrouter.ai/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L74" s="88" t="inlineStr">
-        <is>
-          <t>Пополнение баланса API для расчётов и смет</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="86" t="n">
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="91" t="n">
         <v>33</v>
       </c>
-      <c r="B75" s="82" t="inlineStr">
+      <c r="B79" s="88" t="inlineStr">
         <is>
           <t>Энергосбыт</t>
         </is>
       </c>
-      <c r="C75" s="82" t="inlineStr">
+      <c r="C79" s="88" t="inlineStr">
         <is>
           <t>Учёт</t>
         </is>
       </c>
-      <c r="D75" s="82" t="inlineStr">
+      <c r="D79" s="88" t="inlineStr">
         <is>
           <t>Дистанционная распломбировка старого электросчётчика (согласование)</t>
         </is>
       </c>
-      <c r="E75" s="86" t="inlineStr">
+      <c r="E79" s="91" t="inlineStr">
         <is>
           <t>ТНС-РАСПЛОМБ-ДИСТ</t>
         </is>
       </c>
-      <c r="F75" s="86" t="inlineStr">
+      <c r="F79" s="91" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G75" s="245" t="n">
+      <c r="G79" s="255" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="83" t="n">
+      <c r="H79" s="89" t="n">
         <v>2200</v>
       </c>
-      <c r="I75" s="84">
-        <f>G75*H75</f>
-        <v/>
-      </c>
-      <c r="J75" s="82" t="inlineStr">
+      <c r="I79" s="90">
+        <f>G79*H79</f>
+        <v/>
+      </c>
+      <c r="J79" s="88" t="inlineStr">
         <is>
           <t>ТНС энерго Тула / Энергосбыт</t>
         </is>
       </c>
-      <c r="K75" s="244">
+      <c r="K79" s="256">
         <f>HYPERLINK("https://tns-e.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L75" s="82" t="inlineStr">
-        <is>
-          <t>Фиксация показаний и снятие пломбы без выезда</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="246" t="n"/>
-      <c r="B76" s="247" t="inlineStr">
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="86" t="n">
+        <v>69</v>
+      </c>
+      <c r="B80" s="82" t="inlineStr">
+        <is>
+          <t>Газ</t>
+        </is>
+      </c>
+      <c r="C80" s="82" t="inlineStr">
+        <is>
+          <t>Работы и материалы</t>
+        </is>
+      </c>
+      <c r="D80" s="82" t="inlineStr">
+        <is>
+          <t>Работы газовщика: перенос / срезка / перемонтаж газовой трубы на кухне</t>
+        </is>
+      </c>
+      <c r="E80" s="86" t="inlineStr">
+        <is>
+          <t>ГАЗ-ПЕРЕНОС-ТРУБА</t>
+        </is>
+      </c>
+      <c r="F80" s="86" t="inlineStr">
+        <is>
+          <t>комплекс</t>
+        </is>
+      </c>
+      <c r="G80" s="253" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="83" t="n">
+        <v>7300</v>
+      </c>
+      <c r="I80" s="84">
+        <f>G80*H80</f>
+        <v/>
+      </c>
+      <c r="J80" s="82" t="inlineStr">
+        <is>
+          <t>Газовщик (мастер / горгаз)</t>
+        </is>
+      </c>
+      <c r="K80" s="254">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=перенос+газовой+трубы", "Открыть ↗")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="283" t="n"/>
+      <c r="B81" s="258" t="inlineStr">
         <is>
           <t>ИТОГО ЮР. РАСХОДЫ, СЛУЖБЫ И IT:</t>
         </is>
       </c>
-      <c r="C76" s="246" t="n"/>
-      <c r="D76" s="246" t="n"/>
-      <c r="E76" s="246" t="n"/>
-      <c r="F76" s="246" t="n"/>
-      <c r="G76" s="246" t="n"/>
-      <c r="H76" s="246" t="n"/>
-      <c r="I76" s="248">
-        <f>SUM(I68:I75)</f>
-        <v/>
-      </c>
-      <c r="J76" s="246" t="n"/>
-      <c r="K76" s="246" t="n"/>
-      <c r="L76" s="246" t="n"/>
-    </row>
-    <row r="77" ht="25" customHeight="1">
-      <c r="A77" s="238" t="n"/>
-      <c r="B77" s="239" t="inlineStr">
+      <c r="C81" s="283" t="n"/>
+      <c r="D81" s="283" t="n"/>
+      <c r="E81" s="283" t="n"/>
+      <c r="F81" s="283" t="n"/>
+      <c r="G81" s="283" t="n"/>
+      <c r="H81" s="283" t="n"/>
+      <c r="I81" s="261">
+        <f>SUM(I72:I80)</f>
+        <v/>
+      </c>
+      <c r="J81" s="283" t="n"/>
+      <c r="K81" s="283" t="n"/>
+    </row>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="238" t="n"/>
+      <c r="B82" s="239" t="inlineStr">
         <is>
           <t>ОБЩИЙ ИТОГО ФАКТ РАСХОДОВ (ДИНАМИЧЕСКИЙ):</t>
         </is>
       </c>
-      <c r="C77" s="238" t="n"/>
-      <c r="D77" s="238" t="n"/>
-      <c r="E77" s="238" t="n"/>
-      <c r="F77" s="238" t="n"/>
-      <c r="G77" s="238" t="n"/>
-      <c r="H77" s="238" t="n"/>
-      <c r="I77" s="171">
-        <f>SUM(I30, I48, I66, I76)</f>
-        <v/>
-      </c>
-      <c r="J77" s="238" t="n"/>
-      <c r="K77" s="238" t="n"/>
-      <c r="L77" s="238" t="n"/>
+      <c r="C82" s="238" t="n"/>
+      <c r="D82" s="238" t="n"/>
+      <c r="E82" s="238" t="n"/>
+      <c r="F82" s="238" t="n"/>
+      <c r="G82" s="238" t="n"/>
+      <c r="H82" s="238" t="n"/>
+      <c r="I82" s="171">
+        <f>SUM(I32, I51, I70, I81)</f>
+        <v/>
+      </c>
+      <c r="J82" s="238" t="n"/>
+      <c r="K82" s="238" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
+++ b/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
@@ -19,14 +19,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00 &quot;₽&quot;"/>
     <numFmt numFmtId="167" formatCode="+0.0%"/>
     <numFmt numFmtId="168" formatCode="#,##0.##"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="46">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -285,6 +286,22 @@
       <color rgb="00581C87"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000A84FF"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -354,7 +371,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -685,11 +702,39 @@
         <color rgb="000F172A"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001E293B"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="338">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1433,6 +1478,148 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="7" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="7" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="44" fillId="7" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="44" fillId="7" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="44" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="44" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="32" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="10" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="10" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="5" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="5" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="5" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="5" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="11" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="11" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="11" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="11" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="32" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="44" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="44" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="44" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1796,6 +1983,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F172A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1868,7 +2056,7 @@
         <v/>
       </c>
       <c r="D5" s="118">
-        <f>'Факт расходов'!F74</f>
+        <f>'Факт расходов'!F83</f>
         <v/>
       </c>
       <c r="E5" s="118" t="n">
@@ -1961,7 +2149,7 @@
         <v>23000</v>
       </c>
       <c r="C11" s="46">
-        <f>SUMIF('Факт расходов'!C5:C73, "*Юр.*", 'Факт расходов'!F5:F73)+SUMIF('Факт расходов'!C5:C73, "*Безопасность*", 'Факт расходов'!F5:F73)+SUMIF('Факт расходов'!C5:C73, "*IT*", 'Факт расходов'!F5:F73)+SUMIF('Факт расходов'!C5:C73, "*Электроэнергия*", 'Факт расходов'!F5:F73)</f>
+        <f>SUMIF('Факт расходов'!C5:C82, "*Юр.*", 'Факт расходов'!F5:F82)+SUMIF('Факт расходов'!C5:C82, "*Безопасность*", 'Факт расходов'!F5:F82)+SUMIF('Факт расходов'!C5:C82, "*IT*", 'Факт расходов'!F5:F82)+SUMIF('Факт расходов'!C5:C82, "*Электроэнергия*", 'Факт расходов'!F5:F82)</f>
         <v/>
       </c>
       <c r="D11" s="124">
@@ -2241,7 +2429,7 @@
         <v/>
       </c>
       <c r="C23" s="46">
-        <f>SUMIF('Факт расходов'!C5:C73, "*Демонтаж*", 'Факт расходов'!F5:F73)</f>
+        <f>SUMIF('Факт расходов'!C5:C82, "*Демонтаж*", 'Факт расходов'!F5:F82)</f>
         <v/>
       </c>
       <c r="D23" s="45">
@@ -2274,7 +2462,7 @@
         <v/>
       </c>
       <c r="C24" s="51">
-        <f>SUMIF('Факт расходов'!C5:C73, "*Двери*", 'Факт расходов'!F5:F73)</f>
+        <f>SUMIF('Факт расходов'!C5:C82, "*Двери*", 'Факт расходов'!F5:F82)</f>
         <v/>
       </c>
       <c r="D24" s="50">
@@ -2307,7 +2495,7 @@
         <v/>
       </c>
       <c r="C25" s="46">
-        <f>SUMIF('Факт расходов'!C5:C73, "*Электрика*", 'Факт расходов'!F5:F73)</f>
+        <f>SUMIF('Факт расходов'!C5:C82, "*Электрика*", 'Факт расходов'!F5:F82)</f>
         <v/>
       </c>
       <c r="D25" s="45">
@@ -2340,7 +2528,7 @@
         <v/>
       </c>
       <c r="C26" s="51">
-        <f>SUMIF('Факт расходов'!C5:C73, "*Сантехника*", 'Факт расходов'!F5:F73)</f>
+        <f>SUMIF('Факт расходов'!C5:C82, "*Сантехника*", 'Факт расходов'!F5:F82)</f>
         <v/>
       </c>
       <c r="D26" s="50">
@@ -2372,7 +2560,7 @@
         <v>5000</v>
       </c>
       <c r="C27" s="46">
-        <f>SUMIF('Факт расходов'!C5:C73, "*Газ*", 'Факт расходов'!F5:F73)</f>
+        <f>SUMIF('Факт расходов'!C5:C82, "*Газ*", 'Факт расходов'!F5:F82)</f>
         <v/>
       </c>
       <c r="D27" s="45">
@@ -2437,7 +2625,7 @@
         <v/>
       </c>
       <c r="C29" s="46">
-        <f>SUMIF('Факт расходов'!C5:C73, "*Черновая*", 'Факт расходов'!F5:F73)</f>
+        <f>SUMIF('Факт расходов'!C5:C82, "*Черновая*", 'Факт расходов'!F5:F82)</f>
         <v/>
       </c>
       <c r="D29" s="45">
@@ -2470,7 +2658,7 @@
         <v/>
       </c>
       <c r="C30" s="51">
-        <f>SUMIF('Факт расходов'!C5:C73, "*Чистовая*", 'Факт расходов'!F5:F73)</f>
+        <f>SUMIF('Факт расходов'!C5:C82, "*Чистовая*", 'Факт расходов'!F5:F82)</f>
         <v/>
       </c>
       <c r="D30" s="50">
@@ -2630,7 +2818,7 @@
         <v>10000</v>
       </c>
       <c r="C35" s="46">
-        <f>SUMIF('Факт расходов'!C5:C73, "*Инструмент*", 'Факт расходов'!F5:F73)+SUMIF('Факт расходов'!C5:C73, "*Расходные*", 'Факт расходов'!F5:F73)+SUMIF('Факт расходов'!C5:C73, "*Логистика*", 'Факт расходов'!F5:F73)</f>
+        <f>SUMIF('Факт расходов'!C5:C82, "*Инструмент*", 'Факт расходов'!F5:F82)+SUMIF('Факт расходов'!C5:C82, "*Расходные*", 'Факт расходов'!F5:F82)+SUMIF('Факт расходов'!C5:C82, "*Логистика*", 'Факт расходов'!F5:F82)</f>
         <v/>
       </c>
       <c r="D35" s="45">
@@ -2662,7 +2850,7 @@
         <v>5000</v>
       </c>
       <c r="C36" s="51">
-        <f>SUMIF('Факт расходов'!C5:C73, "*Оснащение*", 'Факт расходов'!F5:F73)</f>
+        <f>SUMIF('Факт расходов'!C5:C82, "*Оснащение*", 'Факт расходов'!F5:F82)</f>
         <v/>
       </c>
       <c r="D36" s="50">
@@ -2844,11 +3032,11 @@
         </is>
       </c>
       <c r="B45" s="45">
-        <f>'Факт расходов'!E74</f>
+        <f>'Факт расходов'!E83</f>
         <v/>
       </c>
       <c r="C45" s="45">
-        <f>'Факт расходов'!F74</f>
+        <f>'Факт расходов'!F83</f>
         <v/>
       </c>
       <c r="D45" s="124">
@@ -2928,10 +3116,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F172A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6122,44 +6311,44 @@
       <c r="N68" s="140" t="n"/>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="91" t="n">
+      <c r="A69" s="62" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="91" t="inlineStr">
+      <c r="B69" s="62" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="C69" s="88" t="inlineStr">
+      <c r="C69" s="44" t="inlineStr">
         <is>
           <t>Сантехника / Материалы</t>
         </is>
       </c>
-      <c r="D69" s="88" t="inlineStr">
+      <c r="D69" s="44" t="inlineStr">
         <is>
           <t>Материалы сантехники и оснастка: труба ПП арм. D20 2шт, отвод 50х15°, гибкий соединитель D50, биты PH2 (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E69" s="89" t="n">
+      <c r="E69" s="45" t="n">
         <v>550</v>
       </c>
-      <c r="F69" s="90" t="n">
+      <c r="F69" s="46" t="n">
         <v>550</v>
       </c>
-      <c r="G69" s="85">
+      <c r="G69" s="47">
         <f>E69-F69</f>
         <v/>
       </c>
-      <c r="H69" s="105">
+      <c r="H69" s="63">
         <f>IFERROR(G69/E69, 0)</f>
         <v/>
       </c>
-      <c r="I69" s="88" t="inlineStr">
+      <c r="I69" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="J69" s="88" t="inlineStr">
+      <c r="J69" s="44" t="inlineStr">
         <is>
           <t>Чек от 29.09.2026 08:15 (касса 74): труба ПП D20 2шт (206₽), отвод 50х15° (50₽), гибкий соединитель D50 (114₽), биты Rage PH2 70мм (180₽)</t>
         </is>
@@ -6170,44 +6359,44 @@
       <c r="N69" s="140" t="n"/>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="86" t="n">
+      <c r="A70" s="64" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="86" t="inlineStr">
+      <c r="B70" s="64" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="C70" s="82" t="inlineStr">
+      <c r="C70" s="49" t="inlineStr">
         <is>
           <t>Чистовая отделка / Материалы</t>
         </is>
       </c>
-      <c r="D70" s="82" t="inlineStr">
+      <c r="D70" s="49" t="inlineStr">
         <is>
           <t>Керамогранит Calacatta superwhite 60х120 (добор 2 упак. / 2.88 м²)</t>
         </is>
       </c>
-      <c r="E70" s="83" t="n">
+      <c r="E70" s="50" t="n">
         <v>5876</v>
       </c>
-      <c r="F70" s="84" t="n">
+      <c r="F70" s="51" t="n">
         <v>5876</v>
       </c>
-      <c r="G70" s="85">
+      <c r="G70" s="47">
         <f>E70-F70</f>
         <v/>
       </c>
-      <c r="H70" s="105">
+      <c r="H70" s="63">
         <f>IFERROR(G70/E70, 0)</f>
         <v/>
       </c>
-      <c r="I70" s="82" t="inlineStr">
+      <c r="I70" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="J70" s="82" t="inlineStr">
+      <c r="J70" s="49" t="inlineStr">
         <is>
           <t>Чек от 29.09.2026 08:07 (касса 73, заказ 2161260912448255): керамогранит Calacatta superwhite 60х120 2 упак. по 2938₽ = 5876₽</t>
         </is>
@@ -6218,44 +6407,44 @@
       <c r="N70" s="140" t="n"/>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="91" t="n">
+      <c r="A71" s="62" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="91" t="inlineStr">
+      <c r="B71" s="62" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="C71" s="88" t="inlineStr">
+      <c r="C71" s="44" t="inlineStr">
         <is>
           <t>Инструмент и расходники</t>
         </is>
       </c>
-      <c r="D71" s="88" t="inlineStr">
+      <c r="D71" s="44" t="inlineStr">
         <is>
           <t>Уголки для плитки (Михаил)</t>
         </is>
       </c>
-      <c r="E71" s="89" t="n">
+      <c r="E71" s="45" t="n">
         <v>260</v>
       </c>
-      <c r="F71" s="90" t="n">
+      <c r="F71" s="46" t="n">
         <v>260</v>
       </c>
-      <c r="G71" s="85">
+      <c r="G71" s="47">
         <f>E71-F71</f>
         <v/>
       </c>
-      <c r="H71" s="105">
+      <c r="H71" s="63">
         <f>IFERROR(G71/E71, 0)</f>
         <v/>
       </c>
-      <c r="I71" s="88" t="inlineStr">
+      <c r="I71" s="44" t="inlineStr">
         <is>
           <t>Михаил (мастер/плиточник)</t>
         </is>
       </c>
-      <c r="J71" s="88" t="inlineStr">
+      <c r="J71" s="44" t="inlineStr">
         <is>
           <t>Оплата Михаилу за уголки для плитки в санузле (260 ₽)</t>
         </is>
@@ -6266,44 +6455,44 @@
       <c r="N71" s="140" t="n"/>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="86" t="n">
+      <c r="A72" s="64" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="86" t="inlineStr">
+      <c r="B72" s="64" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="C72" s="82" t="inlineStr">
+      <c r="C72" s="49" t="inlineStr">
         <is>
           <t>Сантехника / Работы</t>
         </is>
       </c>
-      <c r="D72" s="82" t="inlineStr">
+      <c r="D72" s="49" t="inlineStr">
         <is>
           <t>Работы сантехников (разводка/монтаж узлов водоснабжения и канализации)</t>
         </is>
       </c>
-      <c r="E72" s="83" t="n">
+      <c r="E72" s="50" t="n">
         <v>3000</v>
       </c>
-      <c r="F72" s="84" t="n">
+      <c r="F72" s="51" t="n">
         <v>3000</v>
       </c>
-      <c r="G72" s="85">
+      <c r="G72" s="47">
         <f>E72-F72</f>
         <v/>
       </c>
-      <c r="H72" s="105">
+      <c r="H72" s="63">
         <f>IFERROR(G72/E72, 0)</f>
         <v/>
       </c>
-      <c r="I72" s="82" t="inlineStr">
+      <c r="I72" s="49" t="inlineStr">
         <is>
           <t>Сантехники (мастера)</t>
         </is>
       </c>
-      <c r="J72" s="82" t="inlineStr">
+      <c r="J72" s="49" t="inlineStr">
         <is>
           <t>Оплата работы сантехников за разводку/монтаж в санузле (3 000 ₽)</t>
         </is>
@@ -6314,44 +6503,44 @@
       <c r="N72" s="140" t="n"/>
     </row>
     <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="91" t="n">
+      <c r="A73" s="62" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="91" t="inlineStr">
+      <c r="B73" s="62" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="C73" s="88" t="inlineStr">
+      <c r="C73" s="44" t="inlineStr">
         <is>
           <t>Газ / Работы и материалы</t>
         </is>
       </c>
-      <c r="D73" s="88" t="inlineStr">
+      <c r="D73" s="44" t="inlineStr">
         <is>
           <t>Работы газовщика: перенос / срезка / перемонтаж газовой трубы на кухне</t>
         </is>
       </c>
-      <c r="E73" s="89" t="n">
+      <c r="E73" s="45" t="n">
         <v>7300</v>
       </c>
-      <c r="F73" s="90" t="n">
+      <c r="F73" s="46" t="n">
         <v>7300</v>
       </c>
-      <c r="G73" s="85">
+      <c r="G73" s="47">
         <f>E73-F73</f>
         <v/>
       </c>
-      <c r="H73" s="105">
+      <c r="H73" s="63">
         <f>IFERROR(G73/E73, 0)</f>
         <v/>
       </c>
-      <c r="I73" s="88" t="inlineStr">
+      <c r="I73" s="44" t="inlineStr">
         <is>
           <t>Газовщик (мастер / горгаз)</t>
         </is>
       </c>
-      <c r="J73" s="88" t="inlineStr">
+      <c r="J73" s="44" t="inlineStr">
         <is>
           <t>Оплата газовщику за перенос/срезку и обвязку газовой трубы на кухне (7 300 ₽)</t>
         </is>
@@ -6361,37 +6550,829 @@
       <c r="M73" s="140" t="n"/>
       <c r="N73" s="140" t="n"/>
     </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="284" t="n"/>
-      <c r="B74" s="284" t="n"/>
-      <c r="C74" s="285" t="n"/>
-      <c r="D74" s="239" t="inlineStr">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="64" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="64" t="inlineStr">
+        <is>
+          <t>07.10.2026</t>
+        </is>
+      </c>
+      <c r="C74" s="49" t="inlineStr">
+        <is>
+          <t>Чистовая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D74" s="49" t="inlineStr">
+        <is>
+          <t>Материалы для поклейки обоев (обои Twid 12 рул., клей Kleo 4 шт., грунтовка Knauf 10 кг, шпатели, валики, салфетки)</t>
+        </is>
+      </c>
+      <c r="E74" s="50" t="n">
+        <v>27045</v>
+      </c>
+      <c r="F74" s="51" t="n">
+        <v>24893</v>
+      </c>
+      <c r="G74" s="47">
+        <f>E74-F74</f>
+        <v/>
+      </c>
+      <c r="H74" s="63">
+        <f>IF(E74&gt;0;G74/E74;0)</f>
+        <v/>
+      </c>
+      <c r="I74" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J74" s="49" t="inlineStr">
+        <is>
+          <t>Чек от 07.10.2026 18:25 (касса 4): обои Twid 1.06х10 12 рул. (19 376 ₽ с учетом скидки), грунтовка Knauf 10кг (1 421 ₽), клей Kleo 4 шт. (3 328 ₽), шпатели, салфетки, валик и бюгель. Скидка по промокоду -2 152 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="62" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="62" t="inlineStr">
+        <is>
+          <t>07.10.2026</t>
+        </is>
+      </c>
+      <c r="C75" s="44" t="inlineStr">
+        <is>
+          <t>Логистика и доставка</t>
+        </is>
+      </c>
+      <c r="D75" s="44" t="inlineStr">
+        <is>
+          <t>Такси (доставка / подвоз материалов на объект ул. Фрунзе 17)</t>
+        </is>
+      </c>
+      <c r="E75" s="45" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F75" s="46" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G75" s="47">
+        <f>E75-F75</f>
+        <v/>
+      </c>
+      <c r="H75" s="63">
+        <f>IF(E75&gt;0;G75/E75;0)</f>
+        <v/>
+      </c>
+      <c r="I75" s="44" t="inlineStr">
+        <is>
+          <t>Такси</t>
+        </is>
+      </c>
+      <c r="J75" s="44" t="inlineStr">
+        <is>
+          <t>Оперативная доставка материалов и оснащения на объект ул. Фрунзе 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="64" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="64" t="inlineStr">
+        <is>
+          <t>07.10.2026</t>
+        </is>
+      </c>
+      <c r="C76" s="49" t="inlineStr">
+        <is>
+          <t>Безопасность / Доступ</t>
+        </is>
+      </c>
+      <c r="D76" s="49" t="inlineStr">
+        <is>
+          <t>Ключи от домофона (дубликаты для мастеров и объекта)</t>
+        </is>
+      </c>
+      <c r="E76" s="50" t="n">
+        <v>500</v>
+      </c>
+      <c r="F76" s="51" t="n">
+        <v>500</v>
+      </c>
+      <c r="G76" s="47">
+        <f>E76-F76</f>
+        <v/>
+      </c>
+      <c r="H76" s="63">
+        <f>IF(E76&gt;0;G76/E76;0)</f>
+        <v/>
+      </c>
+      <c r="I76" s="49" t="inlineStr">
+        <is>
+          <t>Изготовление ключей</t>
+        </is>
+      </c>
+      <c r="J76" s="49" t="inlineStr">
+        <is>
+          <t>Изготовление комплекта домофонных ключей для доступа рабочих</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="62" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="62" t="inlineStr">
+        <is>
+          <t>07.10.2026</t>
+        </is>
+      </c>
+      <c r="C77" s="44" t="inlineStr">
+        <is>
+          <t>Хоз. инвентарь / Оснащение</t>
+        </is>
+      </c>
+      <c r="D77" s="44" t="inlineStr">
+        <is>
+          <t>Зарядка для колонки Xiaomi (оснащение объекта)</t>
+        </is>
+      </c>
+      <c r="E77" s="45" t="n">
+        <v>550</v>
+      </c>
+      <c r="F77" s="46" t="n">
+        <v>550</v>
+      </c>
+      <c r="G77" s="47">
+        <f>E77-F77</f>
+        <v/>
+      </c>
+      <c r="H77" s="63">
+        <f>IF(E77&gt;0;G77/E77;0)</f>
+        <v/>
+      </c>
+      <c r="I77" s="44" t="inlineStr">
+        <is>
+          <t>Магазин электроники</t>
+        </is>
+      </c>
+      <c r="J77" s="44" t="inlineStr">
+        <is>
+          <t>Кабель/ЗУ для строительной портативной колонки мастеров</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="64" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="64" t="inlineStr">
+        <is>
+          <t>08.10.2026</t>
+        </is>
+      </c>
+      <c r="C78" s="49" t="inlineStr">
+        <is>
+          <t>Чистовая отделка / Работы</t>
+        </is>
+      </c>
+      <c r="D78" s="49" t="inlineStr">
+        <is>
+          <t>Работы плиточника: укладка плитки в санузле, фартук на кухне, фартук ванной из плитки, лючки на магнитах, отверстия под розетки</t>
+        </is>
+      </c>
+      <c r="E78" s="50" t="n">
+        <v>86000</v>
+      </c>
+      <c r="F78" s="51" t="n">
+        <v>86000</v>
+      </c>
+      <c r="G78" s="47">
+        <f>E78-F78</f>
+        <v/>
+      </c>
+      <c r="H78" s="63">
+        <f>IFERROR(G78/E78, 0)</f>
+        <v/>
+      </c>
+      <c r="I78" s="49" t="inlineStr">
+        <is>
+          <t>Плиточник (мастер)</t>
+        </is>
+      </c>
+      <c r="J78" s="49" t="inlineStr">
+        <is>
+          <t>Работы плиточника: санузел + фартук на кухне + фартук ванной из плитки + лючки на магнитах + отверстия под розетки. Согласованная оплата 86 000 ₽</t>
+        </is>
+      </c>
+      <c r="K78" s="140" t="n"/>
+      <c r="L78" s="140" t="n"/>
+      <c r="M78" s="140" t="n"/>
+      <c r="N78" s="140" t="n"/>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="62" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="62" t="inlineStr">
+        <is>
+          <t>08.10.2026</t>
+        </is>
+      </c>
+      <c r="C79" s="44" t="inlineStr">
+        <is>
+          <t>Сантехника / Материалы</t>
+        </is>
+      </c>
+      <c r="D79" s="44" t="inlineStr">
+        <is>
+          <t>Фиттинги для труб «Американка» на трубы ПП на полотенцесушитель</t>
+        </is>
+      </c>
+      <c r="E79" s="45" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F79" s="46" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G79" s="47">
+        <f>E79-F79</f>
+        <v/>
+      </c>
+      <c r="H79" s="63">
+        <f>IFERROR(G79/E79, 0)</f>
+        <v/>
+      </c>
+      <c r="I79" s="44" t="inlineStr">
+        <is>
+          <t>Сантехмаркет / Хозмаг</t>
+        </is>
+      </c>
+      <c r="J79" s="44" t="inlineStr">
+        <is>
+          <t>Фиттинги («американки») для подключения полотенцесушителя на ПП-трубы</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="64" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="64" t="inlineStr">
+        <is>
+          <t>08.10.2026</t>
+        </is>
+      </c>
+      <c r="C80" s="49" t="inlineStr">
+        <is>
+          <t>Сантехника / Материалы</t>
+        </is>
+      </c>
+      <c r="D80" s="49" t="inlineStr">
+        <is>
+          <t>Зажим для стекла (оснащение санузла)</t>
+        </is>
+      </c>
+      <c r="E80" s="50" t="n">
+        <v>800</v>
+      </c>
+      <c r="F80" s="51" t="n">
+        <v>800</v>
+      </c>
+      <c r="G80" s="47">
+        <f>E80-F80</f>
+        <v/>
+      </c>
+      <c r="H80" s="63">
+        <f>IFERROR(G80/E80, 0)</f>
+        <v/>
+      </c>
+      <c r="I80" s="49" t="inlineStr">
+        <is>
+          <t>Хозмаг / Сантехмаркет</t>
+        </is>
+      </c>
+      <c r="J80" s="49" t="inlineStr">
+        <is>
+          <t>Зажим для стекла (крепёж стеклянного экрана/полки в санузле)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="62" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="62" t="inlineStr">
+        <is>
+          <t>04.10.2026</t>
+        </is>
+      </c>
+      <c r="C81" s="44" t="inlineStr">
+        <is>
+          <t>Хоз. инвентарь / Оснащение</t>
+        </is>
+      </c>
+      <c r="D81" s="44" t="inlineStr">
+        <is>
+          <t>Вертикальный пылесос Timberk T-VCH-52 ДР (для финального клининга/стейджинга)</t>
+        </is>
+      </c>
+      <c r="E81" s="45" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F81" s="46" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G81" s="47">
+        <f>E81-F81</f>
+        <v/>
+      </c>
+      <c r="H81" s="63">
+        <f>IFERROR(G81/E81, 0)</f>
+        <v/>
+      </c>
+      <c r="I81" s="44" t="inlineStr">
+        <is>
+          <t>Техника Даром (ИП Панин И.П., Тула)</t>
+        </is>
+      </c>
+      <c r="J81" s="44" t="inlineStr">
+        <is>
+          <t>Кассовый чек от 04.10.2026, сохранён в Смета_и_чеки (Чек_ТехникаДаром_Пылесос_Timberk_08.10.2026.jpg). Верхний пылесос для финальной уборки объекта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="64" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="64" t="inlineStr">
+        <is>
+          <t>08.10.2026</t>
+        </is>
+      </c>
+      <c r="C82" s="49" t="inlineStr">
+        <is>
+          <t>Логистика и доставка</t>
+        </is>
+      </c>
+      <c r="D82" s="49" t="inlineStr">
+        <is>
+          <t>Такси (оперативная поездка по объекту)</t>
+        </is>
+      </c>
+      <c r="E82" s="50" t="n">
+        <v>700</v>
+      </c>
+      <c r="F82" s="51" t="n">
+        <v>700</v>
+      </c>
+      <c r="G82" s="47">
+        <f>E82-F82</f>
+        <v/>
+      </c>
+      <c r="H82" s="63">
+        <f>IFERROR(G82/E82, 0)</f>
+        <v/>
+      </c>
+      <c r="I82" s="49" t="inlineStr">
+        <is>
+          <t>Такси</t>
+        </is>
+      </c>
+      <c r="J82" s="49" t="inlineStr">
+        <is>
+          <t>Такси (оперативная поездка по объекту), чек не сохранён.</t>
+        </is>
+      </c>
+      <c r="K82" s="140" t="n"/>
+      <c r="L82" s="140" t="n"/>
+      <c r="M82" s="140" t="n"/>
+      <c r="N82" s="140" t="n"/>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="94" t="n"/>
+      <c r="B83" s="94" t="n"/>
+      <c r="C83" s="54" t="n"/>
+      <c r="D83" s="65" t="inlineStr">
         <is>
           <t>ИТОГО РАСХОДОВ:</t>
         </is>
       </c>
-      <c r="E74" s="171">
-        <f>SUM(E5:E73)</f>
-        <v/>
-      </c>
-      <c r="F74" s="171">
-        <f>SUM(F5:F73)</f>
-        <v/>
-      </c>
-      <c r="G74" s="56">
-        <f>SUM(G5:G73)</f>
-        <v/>
-      </c>
-      <c r="H74" s="66">
-        <f>IFERROR(G74/E74, 0)</f>
-        <v/>
-      </c>
-      <c r="I74" s="285" t="n"/>
-      <c r="J74" s="285" t="n"/>
-      <c r="K74" s="140" t="n"/>
-      <c r="L74" s="140" t="n"/>
-      <c r="M74" s="140" t="n"/>
-      <c r="N74" s="140" t="n"/>
+      <c r="E83" s="55">
+        <f>SUM(E5:E82)</f>
+        <v/>
+      </c>
+      <c r="F83" s="55">
+        <f>SUM(F5:F82)</f>
+        <v/>
+      </c>
+      <c r="G83" s="55">
+        <f>SUM(G5:G82)</f>
+        <v/>
+      </c>
+      <c r="H83" s="104">
+        <f>IFERROR(G83/E83, 0)</f>
+        <v/>
+      </c>
+      <c r="I83" s="54" t="n"/>
+      <c r="J83" s="54" t="n"/>
+      <c r="K83" s="140" t="n"/>
+      <c r="L83" s="140" t="n"/>
+      <c r="M83" s="140" t="n"/>
+      <c r="N83" s="140" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="140" t="n"/>
+      <c r="B84" s="140" t="n"/>
+      <c r="C84" s="140" t="n"/>
+      <c r="D84" s="140" t="n"/>
+      <c r="E84" s="140" t="n"/>
+      <c r="F84" s="140" t="n"/>
+      <c r="G84" s="140" t="n"/>
+      <c r="H84" s="140" t="n"/>
+      <c r="I84" s="140" t="n"/>
+      <c r="J84" s="140" t="n"/>
+      <c r="K84" s="140" t="n"/>
+      <c r="L84" s="140" t="n"/>
+      <c r="M84" s="140" t="n"/>
+      <c r="N84" s="140" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="140" t="n"/>
+      <c r="B85" s="140" t="n"/>
+      <c r="C85" s="140" t="n"/>
+      <c r="D85" s="140" t="n"/>
+      <c r="E85" s="140" t="n"/>
+      <c r="F85" s="140" t="n"/>
+      <c r="G85" s="140" t="n"/>
+      <c r="H85" s="140" t="n"/>
+      <c r="I85" s="140" t="n"/>
+      <c r="J85" s="140" t="n"/>
+      <c r="K85" s="140" t="n"/>
+      <c r="L85" s="140" t="n"/>
+      <c r="M85" s="140" t="n"/>
+      <c r="N85" s="140" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="140" t="n"/>
+      <c r="B86" s="140" t="n"/>
+      <c r="C86" s="140" t="n"/>
+      <c r="D86" s="140" t="n"/>
+      <c r="E86" s="140" t="n"/>
+      <c r="F86" s="140" t="n"/>
+      <c r="G86" s="140" t="n"/>
+      <c r="H86" s="140" t="n"/>
+      <c r="I86" s="140" t="n"/>
+      <c r="J86" s="140" t="n"/>
+      <c r="K86" s="140" t="n"/>
+      <c r="L86" s="140" t="n"/>
+      <c r="M86" s="140" t="n"/>
+      <c r="N86" s="140" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="140" t="n"/>
+      <c r="B87" s="140" t="n"/>
+      <c r="C87" s="140" t="n"/>
+      <c r="D87" s="140" t="n"/>
+      <c r="E87" s="140" t="n"/>
+      <c r="F87" s="140" t="n"/>
+      <c r="G87" s="140" t="n"/>
+      <c r="H87" s="140" t="n"/>
+      <c r="I87" s="140" t="n"/>
+      <c r="J87" s="140" t="n"/>
+      <c r="K87" s="140" t="n"/>
+      <c r="L87" s="140" t="n"/>
+      <c r="M87" s="140" t="n"/>
+      <c r="N87" s="140" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="140" t="n"/>
+      <c r="B88" s="140" t="n"/>
+      <c r="C88" s="140" t="n"/>
+      <c r="D88" s="140" t="n"/>
+      <c r="E88" s="140" t="n"/>
+      <c r="F88" s="140" t="n"/>
+      <c r="G88" s="140" t="n"/>
+      <c r="H88" s="140" t="n"/>
+      <c r="I88" s="140" t="n"/>
+      <c r="J88" s="140" t="n"/>
+      <c r="K88" s="140" t="n"/>
+      <c r="L88" s="140" t="n"/>
+      <c r="M88" s="140" t="n"/>
+      <c r="N88" s="140" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="140" t="n"/>
+      <c r="B89" s="140" t="n"/>
+      <c r="C89" s="140" t="n"/>
+      <c r="D89" s="140" t="n"/>
+      <c r="E89" s="140" t="n"/>
+      <c r="F89" s="140" t="n"/>
+      <c r="G89" s="140" t="n"/>
+      <c r="H89" s="140" t="n"/>
+      <c r="I89" s="140" t="n"/>
+      <c r="J89" s="140" t="n"/>
+      <c r="K89" s="140" t="n"/>
+      <c r="L89" s="140" t="n"/>
+      <c r="M89" s="140" t="n"/>
+      <c r="N89" s="140" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="140" t="n"/>
+      <c r="B90" s="140" t="n"/>
+      <c r="C90" s="140" t="n"/>
+      <c r="D90" s="140" t="n"/>
+      <c r="E90" s="140" t="n"/>
+      <c r="F90" s="140" t="n"/>
+      <c r="G90" s="140" t="n"/>
+      <c r="H90" s="140" t="n"/>
+      <c r="I90" s="140" t="n"/>
+      <c r="J90" s="140" t="n"/>
+      <c r="K90" s="140" t="n"/>
+      <c r="L90" s="140" t="n"/>
+      <c r="M90" s="140" t="n"/>
+      <c r="N90" s="140" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="140" t="n"/>
+      <c r="B91" s="140" t="n"/>
+      <c r="C91" s="140" t="n"/>
+      <c r="D91" s="140" t="n"/>
+      <c r="E91" s="140" t="n"/>
+      <c r="F91" s="140" t="n"/>
+      <c r="G91" s="140" t="n"/>
+      <c r="H91" s="140" t="n"/>
+      <c r="I91" s="140" t="n"/>
+      <c r="J91" s="140" t="n"/>
+      <c r="K91" s="140" t="n"/>
+      <c r="L91" s="140" t="n"/>
+      <c r="M91" s="140" t="n"/>
+      <c r="N91" s="140" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="140" t="n"/>
+      <c r="B92" s="140" t="n"/>
+      <c r="C92" s="140" t="n"/>
+      <c r="D92" s="140" t="n"/>
+      <c r="E92" s="140" t="n"/>
+      <c r="F92" s="140" t="n"/>
+      <c r="G92" s="140" t="n"/>
+      <c r="H92" s="140" t="n"/>
+      <c r="I92" s="140" t="n"/>
+      <c r="J92" s="140" t="n"/>
+      <c r="K92" s="140" t="n"/>
+      <c r="L92" s="140" t="n"/>
+      <c r="M92" s="140" t="n"/>
+      <c r="N92" s="140" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="140" t="n"/>
+      <c r="B93" s="140" t="n"/>
+      <c r="C93" s="140" t="n"/>
+      <c r="D93" s="140" t="n"/>
+      <c r="E93" s="140" t="n"/>
+      <c r="F93" s="140" t="n"/>
+      <c r="G93" s="140" t="n"/>
+      <c r="H93" s="140" t="n"/>
+      <c r="I93" s="140" t="n"/>
+      <c r="J93" s="140" t="n"/>
+      <c r="K93" s="140" t="n"/>
+      <c r="L93" s="140" t="n"/>
+      <c r="M93" s="140" t="n"/>
+      <c r="N93" s="140" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="140" t="n"/>
+      <c r="B94" s="140" t="n"/>
+      <c r="C94" s="140" t="n"/>
+      <c r="D94" s="140" t="n"/>
+      <c r="E94" s="140" t="n"/>
+      <c r="F94" s="140" t="n"/>
+      <c r="G94" s="140" t="n"/>
+      <c r="H94" s="140" t="n"/>
+      <c r="I94" s="140" t="n"/>
+      <c r="J94" s="140" t="n"/>
+      <c r="K94" s="140" t="n"/>
+      <c r="L94" s="140" t="n"/>
+      <c r="M94" s="140" t="n"/>
+      <c r="N94" s="140" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="140" t="n"/>
+      <c r="B95" s="140" t="n"/>
+      <c r="C95" s="140" t="n"/>
+      <c r="D95" s="140" t="n"/>
+      <c r="E95" s="140" t="n"/>
+      <c r="F95" s="140" t="n"/>
+      <c r="G95" s="140" t="n"/>
+      <c r="H95" s="140" t="n"/>
+      <c r="I95" s="140" t="n"/>
+      <c r="J95" s="140" t="n"/>
+      <c r="K95" s="140" t="n"/>
+      <c r="L95" s="140" t="n"/>
+      <c r="M95" s="140" t="n"/>
+      <c r="N95" s="140" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="140" t="n"/>
+      <c r="B96" s="140" t="n"/>
+      <c r="C96" s="140" t="n"/>
+      <c r="D96" s="140" t="n"/>
+      <c r="E96" s="140" t="n"/>
+      <c r="F96" s="140" t="n"/>
+      <c r="G96" s="140" t="n"/>
+      <c r="H96" s="140" t="n"/>
+      <c r="I96" s="140" t="n"/>
+      <c r="J96" s="140" t="n"/>
+      <c r="K96" s="140" t="n"/>
+      <c r="L96" s="140" t="n"/>
+      <c r="M96" s="140" t="n"/>
+      <c r="N96" s="140" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="140" t="n"/>
+      <c r="B97" s="140" t="n"/>
+      <c r="C97" s="140" t="n"/>
+      <c r="D97" s="140" t="n"/>
+      <c r="E97" s="140" t="n"/>
+      <c r="F97" s="140" t="n"/>
+      <c r="G97" s="140" t="n"/>
+      <c r="H97" s="140" t="n"/>
+      <c r="I97" s="140" t="n"/>
+      <c r="J97" s="140" t="n"/>
+      <c r="K97" s="140" t="n"/>
+      <c r="L97" s="140" t="n"/>
+      <c r="M97" s="140" t="n"/>
+      <c r="N97" s="140" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="140" t="n"/>
+      <c r="B98" s="140" t="n"/>
+      <c r="C98" s="140" t="n"/>
+      <c r="D98" s="140" t="n"/>
+      <c r="E98" s="140" t="n"/>
+      <c r="F98" s="140" t="n"/>
+      <c r="G98" s="140" t="n"/>
+      <c r="H98" s="140" t="n"/>
+      <c r="I98" s="140" t="n"/>
+      <c r="J98" s="140" t="n"/>
+      <c r="K98" s="140" t="n"/>
+      <c r="L98" s="140" t="n"/>
+      <c r="M98" s="140" t="n"/>
+      <c r="N98" s="140" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="140" t="n"/>
+      <c r="B99" s="140" t="n"/>
+      <c r="C99" s="140" t="n"/>
+      <c r="D99" s="140" t="n"/>
+      <c r="E99" s="140" t="n"/>
+      <c r="F99" s="140" t="n"/>
+      <c r="G99" s="140" t="n"/>
+      <c r="H99" s="140" t="n"/>
+      <c r="I99" s="140" t="n"/>
+      <c r="J99" s="140" t="n"/>
+      <c r="K99" s="140" t="n"/>
+      <c r="L99" s="140" t="n"/>
+      <c r="M99" s="140" t="n"/>
+      <c r="N99" s="140" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="140" t="n"/>
+      <c r="B100" s="140" t="n"/>
+      <c r="C100" s="140" t="n"/>
+      <c r="D100" s="140" t="n"/>
+      <c r="E100" s="140" t="n"/>
+      <c r="F100" s="140" t="n"/>
+      <c r="G100" s="140" t="n"/>
+      <c r="H100" s="140" t="n"/>
+      <c r="I100" s="140" t="n"/>
+      <c r="J100" s="140" t="n"/>
+      <c r="K100" s="140" t="n"/>
+      <c r="L100" s="140" t="n"/>
+      <c r="M100" s="140" t="n"/>
+      <c r="N100" s="140" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="140" t="n"/>
+      <c r="B101" s="140" t="n"/>
+      <c r="C101" s="140" t="n"/>
+      <c r="D101" s="140" t="n"/>
+      <c r="E101" s="140" t="n"/>
+      <c r="F101" s="140" t="n"/>
+      <c r="G101" s="140" t="n"/>
+      <c r="H101" s="140" t="n"/>
+      <c r="I101" s="140" t="n"/>
+      <c r="J101" s="140" t="n"/>
+      <c r="K101" s="140" t="n"/>
+      <c r="L101" s="140" t="n"/>
+      <c r="M101" s="140" t="n"/>
+      <c r="N101" s="140" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="140" t="n"/>
+      <c r="B102" s="140" t="n"/>
+      <c r="C102" s="140" t="n"/>
+      <c r="D102" s="140" t="n"/>
+      <c r="E102" s="140" t="n"/>
+      <c r="F102" s="140" t="n"/>
+      <c r="G102" s="140" t="n"/>
+      <c r="H102" s="140" t="n"/>
+      <c r="I102" s="140" t="n"/>
+      <c r="J102" s="140" t="n"/>
+      <c r="K102" s="140" t="n"/>
+      <c r="L102" s="140" t="n"/>
+      <c r="M102" s="140" t="n"/>
+      <c r="N102" s="140" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="140" t="n"/>
+      <c r="B103" s="140" t="n"/>
+      <c r="C103" s="140" t="n"/>
+      <c r="D103" s="140" t="n"/>
+      <c r="E103" s="140" t="n"/>
+      <c r="F103" s="140" t="n"/>
+      <c r="G103" s="140" t="n"/>
+      <c r="H103" s="140" t="n"/>
+      <c r="I103" s="140" t="n"/>
+      <c r="J103" s="140" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="140" t="n"/>
+      <c r="B104" s="140" t="n"/>
+      <c r="C104" s="140" t="n"/>
+      <c r="D104" s="140" t="n"/>
+      <c r="E104" s="140" t="n"/>
+      <c r="F104" s="140" t="n"/>
+      <c r="G104" s="140" t="n"/>
+      <c r="H104" s="140" t="n"/>
+      <c r="I104" s="140" t="n"/>
+      <c r="J104" s="140" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="140" t="n"/>
+      <c r="B105" s="140" t="n"/>
+      <c r="C105" s="140" t="n"/>
+      <c r="D105" s="140" t="n"/>
+      <c r="E105" s="140" t="n"/>
+      <c r="F105" s="140" t="n"/>
+      <c r="G105" s="140" t="n"/>
+      <c r="H105" s="140" t="n"/>
+      <c r="I105" s="140" t="n"/>
+      <c r="J105" s="140" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="140" t="n"/>
+      <c r="B106" s="140" t="n"/>
+      <c r="C106" s="140" t="n"/>
+      <c r="D106" s="140" t="n"/>
+      <c r="E106" s="140" t="n"/>
+      <c r="F106" s="140" t="n"/>
+      <c r="G106" s="140" t="n"/>
+      <c r="H106" s="140" t="n"/>
+      <c r="I106" s="140" t="n"/>
+      <c r="J106" s="140" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="140" t="n"/>
+      <c r="B107" s="140" t="n"/>
+      <c r="C107" s="140" t="n"/>
+      <c r="D107" s="140" t="n"/>
+      <c r="E107" s="140" t="n"/>
+      <c r="F107" s="140" t="n"/>
+      <c r="G107" s="140" t="n"/>
+      <c r="H107" s="140" t="n"/>
+      <c r="I107" s="140" t="n"/>
+      <c r="J107" s="140" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="140" t="n"/>
+      <c r="B108" s="140" t="n"/>
+      <c r="C108" s="140" t="n"/>
+      <c r="D108" s="140" t="n"/>
+      <c r="E108" s="140" t="n"/>
+      <c r="F108" s="140" t="n"/>
+      <c r="G108" s="140" t="n"/>
+      <c r="H108" s="140" t="n"/>
+      <c r="I108" s="140" t="n"/>
+      <c r="J108" s="140" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="140" t="n"/>
+      <c r="B109" s="140" t="n"/>
+      <c r="C109" s="140" t="n"/>
+      <c r="D109" s="140" t="n"/>
+      <c r="E109" s="140" t="n"/>
+      <c r="F109" s="140" t="n"/>
+      <c r="G109" s="140" t="n"/>
+      <c r="H109" s="140" t="n"/>
+      <c r="I109" s="140" t="n"/>
+      <c r="J109" s="140" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6401,6 +7382,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F172A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -6889,3986 +7871,4145 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F172A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="240" t="inlineStr">
-        <is>
-          <t>ГЕНЕРАЛЬНАЯ МАТРИЦА БЮДЖЕТА И КОМПЛЕКТАЦИИ (ФРУНЗЕ 17)</t>
-        </is>
-      </c>
+      <c r="A1" s="321" t="inlineStr">
+        <is>
+          <t>ГЕНЕРАЛЬНАЯ МАТРИЦА БЮДЖЕТА И КОМПЛЕКТАЦИИ (630 657,80 ₽)</t>
+        </is>
+      </c>
+      <c r="B1" s="322" t="n"/>
+      <c r="C1" s="322" t="n"/>
+      <c r="D1" s="322" t="n"/>
+      <c r="E1" s="322" t="n"/>
+      <c r="F1" s="322" t="n"/>
+      <c r="G1" s="322" t="n"/>
+      <c r="H1" s="322" t="n"/>
+      <c r="I1" s="322" t="n"/>
+      <c r="J1" s="322" t="n"/>
+      <c r="K1" s="322" t="n"/>
+      <c r="L1" s="322" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Полная структура расходов Фрунзе 17 | Точная сверка с листом «Факт расходов» (1-в-1 до копейки, все 64 позиции)</t>
-        </is>
-      </c>
+      <c r="A2" s="323" t="inlineStr">
+        <is>
+          <t>Полная структура расходов Фрунзе 17 | Точная сверка с листом «Факт расходов» (1-в-1 до копейки, все 78 позиций)</t>
+        </is>
+      </c>
+      <c r="B2" s="322" t="n"/>
+      <c r="C2" s="322" t="n"/>
+      <c r="D2" s="322" t="n"/>
+      <c r="E2" s="322" t="n"/>
+      <c r="F2" s="322" t="n"/>
+      <c r="G2" s="322" t="n"/>
+      <c r="H2" s="322" t="n"/>
+      <c r="I2" s="322" t="n"/>
+      <c r="J2" s="322" t="n"/>
+      <c r="K2" s="322" t="n"/>
+      <c r="L2" s="322" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="241" t="inlineStr">
+      <c r="A3" s="323" t="inlineStr">
         <is>
           <t>💡 Используй значки [-] и [+] для сворачивания блоков (Материалы, Спецпоставщики, Работы, Юр. расходы)</t>
         </is>
       </c>
+      <c r="B3" s="322" t="n"/>
+      <c r="C3" s="322" t="n"/>
+      <c r="D3" s="322" t="n"/>
+      <c r="E3" s="322" t="n"/>
+      <c r="F3" s="322" t="n"/>
+      <c r="G3" s="322" t="n"/>
+      <c r="H3" s="322" t="n"/>
+      <c r="I3" s="322" t="n"/>
+      <c r="J3" s="322" t="n"/>
+      <c r="K3" s="322" t="n"/>
+      <c r="L3" s="322" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="81" t="inlineStr">
+      <c r="A4" s="324" t="inlineStr">
         <is>
           <t>№ в Факте</t>
         </is>
       </c>
-      <c r="B4" s="81" t="inlineStr">
+      <c r="B4" s="324" t="inlineStr">
         <is>
           <t>Зона / Помещение</t>
         </is>
       </c>
-      <c r="C4" s="81" t="inlineStr">
+      <c r="C4" s="324" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="D4" s="81" t="inlineStr">
+      <c r="D4" s="324" t="inlineStr">
         <is>
           <t>Наименование расхода</t>
         </is>
       </c>
-      <c r="E4" s="81" t="inlineStr">
+      <c r="E4" s="324" t="inlineStr">
         <is>
           <t>Артикул / Код</t>
         </is>
       </c>
-      <c r="F4" s="81" t="inlineStr">
+      <c r="F4" s="324" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="G4" s="81" t="inlineStr">
+      <c r="G4" s="324" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="H4" s="81" t="inlineStr">
+      <c r="H4" s="324" t="inlineStr">
         <is>
           <t>Цена / ед. (₽)</t>
         </is>
       </c>
-      <c r="I4" s="81" t="inlineStr">
+      <c r="I4" s="324" t="inlineStr">
         <is>
           <t>Сумма (₽)</t>
         </is>
       </c>
-      <c r="J4" s="81" t="inlineStr">
+      <c r="J4" s="324" t="inlineStr">
         <is>
           <t>Поставщик / Подрядчик</t>
         </is>
       </c>
-      <c r="K4" s="81" t="inlineStr">
+      <c r="K4" s="324" t="inlineStr">
         <is>
           <t>Ссылка / Документ</t>
         </is>
       </c>
-      <c r="L4" s="81" t="inlineStr">
+      <c r="L4" s="324" t="inlineStr">
         <is>
           <t>Примечание / Назначение</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="242" t="n"/>
-      <c r="B5" s="252" t="inlineStr">
-        <is>
-          <t>🛁 БЛОК 1: СТРОИТЕЛЬНЫЕ И ЧИСТОВЫЕ МАТЕРИАЛЫ «ЛЕМАНА ПРО» (25 ЧЕКОВ)</t>
-        </is>
-      </c>
-      <c r="C5" s="242" t="n"/>
-      <c r="D5" s="242" t="n"/>
-      <c r="E5" s="242" t="n"/>
-      <c r="F5" s="242" t="n"/>
-      <c r="G5" s="242" t="n"/>
-      <c r="H5" s="242" t="n"/>
-      <c r="I5" s="242" t="n"/>
-      <c r="J5" s="242" t="n"/>
-      <c r="K5" s="242" t="n"/>
-      <c r="L5" s="242" t="n"/>
+      <c r="A5" s="322" t="n"/>
+      <c r="B5" s="325" t="inlineStr">
+        <is>
+          <t>🛁 БЛОК 1: СТРОИТЕЛЬНЫЕ И ЧИСТОВЫЕ МАТЕРИАЛЫ «ЛЕМАНА ПРО» (27 ЧЕКОВ)</t>
+        </is>
+      </c>
+      <c r="C5" s="322" t="n"/>
+      <c r="D5" s="322" t="n"/>
+      <c r="E5" s="322" t="n"/>
+      <c r="F5" s="322" t="n"/>
+      <c r="G5" s="322" t="n"/>
+      <c r="H5" s="322" t="n"/>
+      <c r="I5" s="322" t="n"/>
+      <c r="J5" s="322" t="n"/>
+      <c r="K5" s="322" t="n"/>
+      <c r="L5" s="322" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="86" t="n">
+      <c r="A6" s="64" t="n">
         <v>8</v>
       </c>
-      <c r="B6" s="82" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>Расходники</t>
         </is>
       </c>
-      <c r="C6" s="82" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>Пылесос</t>
         </is>
       </c>
-      <c r="D6" s="82" t="inlineStr">
+      <c r="D6" s="49" t="inlineStr">
         <is>
           <t>Мешки для пылесоса синт. 12л (5 шт) — Леруа/Лемана</t>
         </is>
       </c>
-      <c r="E6" s="86" t="inlineStr">
-        <is>
-          <t>4607086338088</t>
-        </is>
-      </c>
-      <c r="F6" s="86" t="inlineStr">
+      <c r="E6" s="49" t="n">
+        <v>4607086338088</v>
+      </c>
+      <c r="F6" s="64" t="inlineStr">
         <is>
           <t>упак.</t>
         </is>
       </c>
-      <c r="G6" s="253" t="n">
+      <c r="G6" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="83" t="n">
+      <c r="H6" s="172" t="n">
         <v>717</v>
       </c>
-      <c r="I6" s="84">
+      <c r="I6" s="172">
         <f>G6*H6</f>
         <v/>
       </c>
-      <c r="J6" s="82" t="inlineStr">
+      <c r="J6" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K6" s="254">
+      <c r="K6" s="175">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=мешки+для+пылесоса+12л", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L6" s="88" t="inlineStr">
-        <is>
-          <t>Чек 3831 от 23.08.2026: Сбор пыли штробления</t>
-        </is>
-      </c>
+      <c r="L6" s="49" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="91" t="n">
+      <c r="A7" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="B7" s="88" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>Инструмент</t>
         </is>
       </c>
-      <c r="C7" s="88" t="inlineStr">
+      <c r="C7" s="44" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="D7" s="88" t="inlineStr">
+      <c r="D7" s="44" t="inlineStr">
         <is>
           <t>Лом-гвоздодер, мешки 15шт, лента, перчатки 6п, опрыскиватель</t>
         </is>
       </c>
-      <c r="E7" s="91" t="inlineStr">
-        <is>
-          <t>4603333000001</t>
-        </is>
-      </c>
-      <c r="F7" s="91" t="inlineStr">
+      <c r="E7" s="44" t="n">
+        <v>4603333000001</v>
+      </c>
+      <c r="F7" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G7" s="255" t="n">
+      <c r="G7" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="89" t="n">
+      <c r="H7" s="173" t="n">
         <v>1830</v>
       </c>
-      <c r="I7" s="90">
+      <c r="I7" s="173">
         <f>G7*H7</f>
         <v/>
       </c>
-      <c r="J7" s="88" t="inlineStr">
+      <c r="J7" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K7" s="256">
+      <c r="K7" s="174">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=лом+гвоздодер", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L7" s="82" t="inlineStr">
-        <is>
-          <t>Чек 3832 от 23.08.2026: Инструмент демонтажа</t>
-        </is>
-      </c>
+      <c r="L7" s="44" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="86" t="n">
+      <c r="A8" s="64" t="n">
         <v>25</v>
       </c>
-      <c r="B8" s="82" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C8" s="82" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>Шпатлевка / Грунт</t>
         </is>
       </c>
-      <c r="D8" s="82" t="inlineStr">
+      <c r="D8" s="49" t="inlineStr">
         <is>
           <t>Материалы для зачистки и грунтования (шпатлевка 20кг, грунт 10л, СТ99, фильтр Rommer)</t>
         </is>
       </c>
-      <c r="E8" s="86" t="inlineStr">
-        <is>
-          <t>3276006224277</t>
-        </is>
-      </c>
-      <c r="F8" s="86" t="inlineStr">
+      <c r="E8" s="49" t="n">
+        <v>3276006224277</v>
+      </c>
+      <c r="F8" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G8" s="253" t="n">
+      <c r="G8" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="83" t="n">
+      <c r="H8" s="172" t="n">
         <v>4803.6</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="172">
         <f>G8*H8</f>
         <v/>
       </c>
-      <c r="J8" s="82" t="inlineStr">
+      <c r="J8" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K8" s="254">
+      <c r="K8" s="175">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=грунт+axton+10л", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L8" s="88" t="inlineStr">
-        <is>
-          <t>Чек от 30.08.2026: Подготовка стен зала и с/у</t>
-        </is>
-      </c>
+      <c r="L8" s="49" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="91" t="n">
+      <c r="A9" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="B9" s="88" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>Инструмент</t>
         </is>
       </c>
-      <c r="C9" s="88" t="inlineStr">
+      <c r="C9" s="44" t="inlineStr">
         <is>
           <t>Ёмкости</t>
         </is>
       </c>
-      <c r="D9" s="88" t="inlineStr">
+      <c r="D9" s="44" t="inlineStr">
         <is>
           <t>Ведро строительное круглое 20 л (2 шт.)</t>
         </is>
       </c>
-      <c r="E9" s="91" t="inlineStr">
-        <is>
-          <t>4610008470475</t>
-        </is>
-      </c>
-      <c r="F9" s="91" t="inlineStr">
+      <c r="E9" s="44" t="n">
+        <v>4610008470475</v>
+      </c>
+      <c r="F9" s="62" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G9" s="255" t="n">
+      <c r="G9" s="327" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="89" t="n">
+      <c r="H9" s="173" t="n">
         <v>128</v>
       </c>
-      <c r="I9" s="90">
+      <c r="I9" s="173">
         <f>G9*H9</f>
         <v/>
       </c>
-      <c r="J9" s="88" t="inlineStr">
+      <c r="J9" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K9" s="256">
+      <c r="K9" s="174">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=ведро+строительное+20л", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L9" s="82" t="inlineStr">
-        <is>
-          <t>Чек от 30.08.2026: Ёмкости для замеса растворов</t>
-        </is>
-      </c>
+      <c r="L9" s="44" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="86" t="n">
+      <c r="A10" s="64" t="n">
         <v>28</v>
       </c>
-      <c r="B10" s="82" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C10" s="82" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>Шпатлевка / Шпатели</t>
         </is>
       </c>
-      <c r="D10" s="82" t="inlineStr">
+      <c r="D10" s="49" t="inlineStr">
         <is>
           <t>Материалы для подготовки стен (грунт Axton 10л 4шт, шпатлевка 20кг 2шт, шпатели, мешки)</t>
         </is>
       </c>
-      <c r="E10" s="86" t="inlineStr">
-        <is>
-          <t>4601745004252</t>
-        </is>
-      </c>
-      <c r="F10" s="86" t="inlineStr">
+      <c r="E10" s="49" t="n">
+        <v>4601745004252</v>
+      </c>
+      <c r="F10" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G10" s="253" t="n">
+      <c r="G10" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="83" t="n">
+      <c r="H10" s="172" t="n">
         <v>3308</v>
       </c>
-      <c r="I10" s="84">
+      <c r="I10" s="172">
         <f>G10*H10</f>
         <v/>
       </c>
-      <c r="J10" s="82" t="inlineStr">
+      <c r="J10" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K10" s="254">
+      <c r="K10" s="175">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=шпатлевка+старатели+20кг", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L10" s="88" t="inlineStr">
-        <is>
-          <t>Чек от 05.09.2026: Подготовка спальни</t>
-        </is>
-      </c>
+      <c r="L10" s="49" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="91" t="n">
+      <c r="A11" s="62" t="n">
         <v>30</v>
       </c>
-      <c r="B11" s="88" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C11" s="88" t="inlineStr">
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>Штукатурка / Бетонконтакт</t>
         </is>
       </c>
-      <c r="D11" s="88" t="inlineStr">
+      <c r="D11" s="44" t="inlineStr">
         <is>
           <t>Материалы штукатурки и шпаклёвки (Бетонконтакт 12кг 3шт, финиш 5шт, штукатурка 3шт, правило, углы)</t>
         </is>
       </c>
-      <c r="E11" s="91" t="inlineStr">
-        <is>
-          <t>4607017518816</t>
-        </is>
-      </c>
-      <c r="F11" s="91" t="inlineStr">
+      <c r="E11" s="44" t="n">
+        <v>4607017518816</v>
+      </c>
+      <c r="F11" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G11" s="255" t="n">
+      <c r="G11" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="89" t="n">
+      <c r="H11" s="173" t="n">
         <v>8162</v>
       </c>
-      <c r="I11" s="90">
+      <c r="I11" s="173">
         <f>G11*H11</f>
         <v/>
       </c>
-      <c r="J11" s="88" t="inlineStr">
+      <c r="J11" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K11" s="256">
+      <c r="K11" s="174">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=бетонконтакт+axton+12кг", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L11" s="82" t="inlineStr">
-        <is>
-          <t>Чек от 06.09.2026: Основное выравнивание стен</t>
-        </is>
-      </c>
+      <c r="L11" s="44" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="86" t="n">
+      <c r="A12" s="64" t="n">
         <v>32</v>
       </c>
-      <c r="B12" s="82" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C12" s="82" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>Шпаклёвка</t>
         </is>
       </c>
-      <c r="D12" s="82" t="inlineStr">
+      <c r="D12" s="49" t="inlineStr">
         <is>
           <t>Материалы штукатурки и шпаклёвки (шпатлевка финиш 20кг, штукатурка 30кг 2шт, перчатки)</t>
         </is>
       </c>
-      <c r="E12" s="86" t="inlineStr">
-        <is>
-          <t>4601745002814</t>
-        </is>
-      </c>
-      <c r="F12" s="86" t="inlineStr">
+      <c r="E12" s="49" t="n">
+        <v>4601745002814</v>
+      </c>
+      <c r="F12" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G12" s="253" t="n">
+      <c r="G12" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="83" t="n">
+      <c r="H12" s="172" t="n">
         <v>1594</v>
       </c>
-      <c r="I12" s="84">
+      <c r="I12" s="172">
         <f>G12*H12</f>
         <v/>
       </c>
-      <c r="J12" s="82" t="inlineStr">
+      <c r="J12" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K12" s="254">
+      <c r="K12" s="175">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=шпатлевка+финишная+старатели", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L12" s="88" t="inlineStr">
-        <is>
-          <t>Чек от 08.09.2026: Добор смесей на спальню</t>
-        </is>
-      </c>
+      <c r="L12" s="49" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="91" t="n">
+      <c r="A13" s="62" t="n">
         <v>34</v>
       </c>
-      <c r="B13" s="88" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C13" s="88" t="inlineStr">
+      <c r="C13" s="44" t="inlineStr">
         <is>
           <t>Санфаянс / Смесители</t>
         </is>
       </c>
-      <c r="D13" s="88" t="inlineStr">
+      <c r="D13" s="44" t="inlineStr">
         <is>
           <t>Сантехника и санфаянс с/у (ванна Нерея 150, каркас Sensea, унитаз Sanita, раковина 60, смесители 2шт, душ, сифон)</t>
         </is>
       </c>
-      <c r="E13" s="91" t="inlineStr">
-        <is>
-          <t>4600779023659</t>
-        </is>
-      </c>
-      <c r="F13" s="91" t="inlineStr">
+      <c r="E13" s="44" t="n">
+        <v>4600779023659</v>
+      </c>
+      <c r="F13" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G13" s="255" t="n">
+      <c r="G13" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="89" t="n">
+      <c r="H13" s="173" t="n">
         <v>30021</v>
       </c>
-      <c r="I13" s="90">
+      <c r="I13" s="173">
         <f>G13*H13</f>
         <v/>
       </c>
-      <c r="J13" s="88" t="inlineStr">
+      <c r="J13" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K13" s="256">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4600779023659", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L13" s="82" t="inlineStr">
-        <is>
-          <t>Чек от 13.09.2026 (заказ 774): Полный комплект с/у</t>
-        </is>
-      </c>
+      <c r="K13" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%92%D0%B0%D0%BD%D0%BD%D0%B0+%D0%9D%D0%B5%D1%80%D0%B5%D1%8F+150%D1%8570+%D0%B0%D0%BA%D1%80%D0%B8%D0%BB%D0%BE%D0%B2%D0%B0%D1%8F", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L13" s="44" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="86" t="n">
+      <c r="A14" s="64" t="n">
         <v>35</v>
       </c>
-      <c r="B14" s="82" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C14" s="82" t="inlineStr">
+      <c r="C14" s="49" t="inlineStr">
         <is>
           <t>Керамогранит / Затирка</t>
         </is>
       </c>
-      <c r="D14" s="82" t="inlineStr">
+      <c r="D14" s="49" t="inlineStr">
         <is>
           <t>Керамогранит Calacatta 60х120 (14 упак. / 20.16 м²) + затирка Ceresit CE 40 2кг 2шт</t>
         </is>
       </c>
-      <c r="E14" s="86" t="inlineStr">
-        <is>
-          <t>4673766221451</t>
-        </is>
-      </c>
-      <c r="F14" s="86" t="inlineStr">
+      <c r="E14" s="49" t="n">
+        <v>4673766221451</v>
+      </c>
+      <c r="F14" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G14" s="253" t="n">
+      <c r="G14" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="83" t="n">
+      <c r="H14" s="172" t="n">
         <v>33457</v>
       </c>
-      <c r="I14" s="84">
+      <c r="I14" s="172">
         <f>G14*H14</f>
         <v/>
       </c>
-      <c r="J14" s="82" t="inlineStr">
+      <c r="J14" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K14" s="254">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4673766221451", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L14" s="88" t="inlineStr">
-        <is>
-          <t>Чек от 13.09.2026 (заказ 774): Плитка на все стены с/у</t>
-        </is>
-      </c>
+      <c r="K14" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%9A%D0%B5%D1%80%D0%B0%D0%BC%D0%BE%D0%B3%D1%80%D0%B0%D0%BD%D0%B8%D1%82+Calacatta+60%D1%85120", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L14" s="49" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="91" t="n">
+      <c r="A15" s="62" t="n">
         <v>36</v>
       </c>
-      <c r="B15" s="88" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C15" s="88" t="inlineStr">
+      <c r="C15" s="44" t="inlineStr">
         <is>
           <t>Плиточный клей</t>
         </is>
       </c>
-      <c r="D15" s="88" t="inlineStr">
+      <c r="D15" s="44" t="inlineStr">
         <is>
           <t>Плиточный клей Unis 2000 C1T 25 кг для формата 60х120 (13 мешков)</t>
         </is>
       </c>
-      <c r="E15" s="91" t="inlineStr">
-        <is>
-          <t>4607005180063</t>
-        </is>
-      </c>
-      <c r="F15" s="91" t="inlineStr">
+      <c r="E15" s="44" t="n">
+        <v>4607005180063</v>
+      </c>
+      <c r="F15" s="62" t="inlineStr">
         <is>
           <t>мешок</t>
         </is>
       </c>
-      <c r="G15" s="255" t="n">
+      <c r="G15" s="327" t="n">
         <v>13</v>
       </c>
-      <c r="H15" s="89" t="n">
+      <c r="H15" s="173" t="n">
         <v>382.53846</v>
       </c>
-      <c r="I15" s="90">
+      <c r="I15" s="173">
         <f>G15*H15</f>
         <v/>
       </c>
-      <c r="J15" s="88" t="inlineStr">
+      <c r="J15" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K15" s="256">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4607005180063", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L15" s="82" t="inlineStr">
-        <is>
-          <t>Чек от 13.09.2026 (заказ 774): Клей под керамогранит</t>
-        </is>
-      </c>
+      <c r="K15" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%9F%D0%BB%D0%B8%D1%82%D0%BE%D1%87%D0%BD%D1%8B%D0%B9+%D0%BA%D0%BB%D0%B5%D0%B9+Unis+2000+C1T", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L15" s="44" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="86" t="n">
+      <c r="A16" s="64" t="n">
         <v>37</v>
       </c>
-      <c r="B16" s="82" t="inlineStr">
+      <c r="B16" s="49" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C16" s="82" t="inlineStr">
+      <c r="C16" s="49" t="inlineStr">
         <is>
           <t>СВП</t>
         </is>
       </c>
-      <c r="D16" s="82" t="inlineStr">
+      <c r="D16" s="49" t="inlineStr">
         <is>
           <t>Система выравнивания плитки СВП DILWIS (зажимы 1 мм 200 шт, клинья 100 шт)</t>
         </is>
       </c>
-      <c r="E16" s="86" t="inlineStr">
-        <is>
-          <t>4610085150475</t>
-        </is>
-      </c>
-      <c r="F16" s="86" t="inlineStr">
+      <c r="E16" s="49" t="n">
+        <v>4610085150475</v>
+      </c>
+      <c r="F16" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G16" s="253" t="n">
+      <c r="G16" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="83" t="n">
+      <c r="H16" s="172" t="n">
         <v>853</v>
       </c>
-      <c r="I16" s="84">
+      <c r="I16" s="172">
         <f>G16*H16</f>
         <v/>
       </c>
-      <c r="J16" s="82" t="inlineStr">
+      <c r="J16" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K16" s="254">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4610085150475", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L16" s="88" t="inlineStr">
-        <is>
-          <t>Чек от 13.09.2026 (заказ 774): Идеальный шов 1 мм</t>
-        </is>
-      </c>
+      <c r="K16" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%A1%D0%92%D0%9F+DILWIS+%D0%B7%D0%B0%D0%B6%D0%B8%D0%BC%D1%8B+%D0%B4%D0%BB%D1%8F+%D0%BF%D0%BB%D0%B8%D1%82%D0%BA%D0%B8", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L16" s="49" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="91" t="n">
+      <c r="A17" s="62" t="n">
         <v>38</v>
       </c>
-      <c r="B17" s="88" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C17" s="88" t="inlineStr">
+      <c r="C17" s="44" t="inlineStr">
         <is>
           <t>Шпаклёвка</t>
         </is>
       </c>
-      <c r="D17" s="88" t="inlineStr">
+      <c r="D17" s="44" t="inlineStr">
         <is>
           <t>Материалы для штукатурки и шпаклёвки (повторный добор: финиш 20кг, штукатурка 2шт)</t>
         </is>
       </c>
-      <c r="E17" s="91" t="inlineStr">
-        <is>
-          <t>4601745000407</t>
-        </is>
-      </c>
-      <c r="F17" s="91" t="inlineStr">
+      <c r="E17" s="44" t="n">
+        <v>4601745000407</v>
+      </c>
+      <c r="F17" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G17" s="255" t="n">
+      <c r="G17" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="89" t="n">
+      <c r="H17" s="173" t="n">
         <v>1594</v>
       </c>
-      <c r="I17" s="90">
+      <c r="I17" s="173">
         <f>G17*H17</f>
         <v/>
       </c>
-      <c r="J17" s="88" t="inlineStr">
+      <c r="J17" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K17" s="256">
+      <c r="K17" s="174">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=штукатурка+старатели+30кг", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L17" s="82" t="inlineStr">
-        <is>
-          <t>Чек от 13.09.2026: Добор смесей на гардероб</t>
-        </is>
-      </c>
+      <c r="L17" s="44" t="inlineStr"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="86" t="n">
+      <c r="A18" s="64" t="n">
         <v>39</v>
       </c>
-      <c r="B18" s="82" t="inlineStr">
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C18" s="82" t="inlineStr">
+      <c r="C18" s="49" t="inlineStr">
         <is>
           <t>Стяжка / Короба</t>
         </is>
       </c>
-      <c r="D18" s="82" t="inlineStr">
+      <c r="D18" s="49" t="inlineStr">
         <is>
           <t>Материалы для стяжки пола и короба с/у (пескобетон М-300 6шт, Knauf 50х40, ГСП 2шт, фибра, саморезы, стамеска)</t>
         </is>
       </c>
-      <c r="E18" s="86" t="inlineStr">
-        <is>
-          <t>4610007550932</t>
-        </is>
-      </c>
-      <c r="F18" s="86" t="inlineStr">
+      <c r="E18" s="49" t="n">
+        <v>4610007550932</v>
+      </c>
+      <c r="F18" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G18" s="253" t="n">
+      <c r="G18" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="83" t="n">
+      <c r="H18" s="172" t="n">
         <v>3182.67</v>
       </c>
-      <c r="I18" s="84">
+      <c r="I18" s="172">
         <f>G18*H18</f>
         <v/>
       </c>
-      <c r="J18" s="82" t="inlineStr">
+      <c r="J18" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K18" s="254">
+      <c r="K18" s="175">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=пескобетон+м300", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L18" s="88" t="inlineStr">
-        <is>
-          <t>Чек №201 от 13.09.2026: Стяжка пола и стояк с/у</t>
-        </is>
-      </c>
+      <c r="L18" s="49" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="91" t="n">
+      <c r="A19" s="62" t="n">
         <v>45</v>
       </c>
-      <c r="B19" s="88" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C19" s="88" t="inlineStr">
+      <c r="C19" s="44" t="inlineStr">
         <is>
           <t>Черновые стены / Гидроизоляция</t>
         </is>
       </c>
-      <c r="D19" s="88" t="inlineStr">
+      <c r="D19" s="44" t="inlineStr">
         <is>
           <t>Штукатурка Старатели 8шт, гидроизоляция Unis 4кг, люк Fonet 200х250, маяки, профиль, фитинги, рулетки</t>
         </is>
       </c>
-      <c r="E19" s="91" t="inlineStr">
-        <is>
-          <t>4601745000407</t>
-        </is>
-      </c>
-      <c r="F19" s="91" t="inlineStr">
+      <c r="E19" s="44" t="n">
+        <v>4601745000407</v>
+      </c>
+      <c r="F19" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G19" s="255" t="n">
+      <c r="G19" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="89" t="n">
+      <c r="H19" s="173" t="n">
         <v>7827.6</v>
       </c>
-      <c r="I19" s="90">
+      <c r="I19" s="173">
         <f>G19*H19</f>
         <v/>
       </c>
-      <c r="J19" s="88" t="inlineStr">
+      <c r="J19" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K19" s="256">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4601745000407", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L19" s="82" t="inlineStr">
-        <is>
-          <t>Чек от 20.09.2026 12:03: Выравнивание ванны под 90°, гидроизоляция, люк стояка</t>
-        </is>
-      </c>
+      <c r="K19" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%A8%D1%82%D1%83%D0%BA%D0%B0%D1%82%D1%83%D1%80%D0%BA%D0%B0+%D0%B3%D0%B8%D0%BF%D1%81%D0%BE%D0%B2%D0%B0%D1%8F+%D0%A1%D1%82%D0%B0%D1%80%D0%B0%D1%82%D0%B5%D0%BB%D0%B8+30%D0%BA%D0%B3", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L19" s="44" t="inlineStr"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="86" t="n">
+      <c r="A20" s="64" t="n">
         <v>46</v>
       </c>
-      <c r="B20" s="82" t="inlineStr">
+      <c r="B20" s="49" t="inlineStr">
         <is>
           <t>Все зоны</t>
         </is>
       </c>
-      <c r="C20" s="82" t="inlineStr">
+      <c r="C20" s="49" t="inlineStr">
         <is>
           <t>Радиаторы / Трубы</t>
         </is>
       </c>
-      <c r="D20" s="82" t="inlineStr">
+      <c r="D20" s="49" t="inlineStr">
         <is>
           <t>Эмаль аэрозольная Luxens белая сатиновая и матовая 520 мл (2 шт.)</t>
         </is>
       </c>
-      <c r="E20" s="86" t="inlineStr">
-        <is>
-          <t>3276007227604</t>
-        </is>
-      </c>
-      <c r="F20" s="86" t="inlineStr">
+      <c r="E20" s="49" t="n">
+        <v>3276007227604</v>
+      </c>
+      <c r="F20" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G20" s="253" t="n">
+      <c r="G20" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="83" t="n">
+      <c r="H20" s="172" t="n">
         <v>648</v>
       </c>
-      <c r="I20" s="84">
+      <c r="I20" s="172">
         <f>G20*H20</f>
         <v/>
       </c>
-      <c r="J20" s="82" t="inlineStr">
+      <c r="J20" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K20" s="254">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=3276007227604", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L20" s="88" t="inlineStr">
-        <is>
-          <t>Чек №123 от 20.09.2026 12:39: Покраска чугунных радиаторов отопления и труб</t>
-        </is>
-      </c>
+      <c r="K20" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%AD%D0%BC%D0%B0%D0%BB%D1%8C+%D0%B0%D1%8D%D1%80%D0%BE%D0%B7%D0%BE%D0%BB%D1%8C%D0%BD%D0%B0%D1%8F+Luxens+%D0%B1%D0%B5%D0%BB%D0%B0%D1%8F+%D1%81%D0%B0%D1%82%D0%B8%D0%BD%D0%BE%D0%B2%D0%B0%D1%8F", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L20" s="49" t="inlineStr"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="91" t="n">
+      <c r="A21" s="62" t="n">
         <v>47</v>
       </c>
-      <c r="B21" s="88" t="inlineStr">
+      <c r="B21" s="44" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C21" s="88" t="inlineStr">
+      <c r="C21" s="44" t="inlineStr">
         <is>
           <t>Стяжка / Добавки</t>
         </is>
       </c>
-      <c r="D21" s="88" t="inlineStr">
+      <c r="D21" s="44" t="inlineStr">
         <is>
           <t>Ускоритель твердения Cemfix для стяжки пола, 1 литр (добавка в пескобетон М300)</t>
         </is>
       </c>
-      <c r="E21" s="91" t="inlineStr">
-        <is>
-          <t>4650068600092</t>
-        </is>
-      </c>
-      <c r="F21" s="91" t="inlineStr">
+      <c r="E21" s="44" t="n">
+        <v>4650068600092</v>
+      </c>
+      <c r="F21" s="62" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G21" s="255" t="n">
+      <c r="G21" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="89" t="n">
+      <c r="H21" s="173" t="n">
         <v>262</v>
       </c>
-      <c r="I21" s="90">
+      <c r="I21" s="173">
         <f>G21*H21</f>
         <v/>
       </c>
-      <c r="J21" s="88" t="inlineStr">
+      <c r="J21" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K21" s="256">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4650068600092", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L21" s="82" t="inlineStr">
-        <is>
-          <t>Чек №138 от 20.09.2026 13:02: Ускорение набора прочности стяжки пола с/у</t>
-        </is>
-      </c>
+      <c r="K21" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%A3%D1%81%D0%BA%D0%BE%D1%80%D0%B8%D1%82%D0%B5%D0%BB%D1%8C+%D1%82%D0%B2%D0%B5%D1%80%D0%B4%D0%B5%D0%BD%D0%B8%D1%8F+Cemfix", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L21" s="44" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="86" t="n">
+      <c r="A22" s="64" t="n">
         <v>50</v>
       </c>
-      <c r="B22" s="82" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C22" s="82" t="inlineStr">
+      <c r="C22" s="49" t="inlineStr">
         <is>
           <t>Расходники / Инструмент</t>
         </is>
       </c>
-      <c r="D22" s="82" t="inlineStr">
+      <c r="D22" s="49" t="inlineStr">
         <is>
           <t>Пистолет для герметика скелетный + герметик санитарный силиконовый (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E22" s="86" t="inlineStr">
-        <is>
-          <t>82420455</t>
-        </is>
-      </c>
-      <c r="F22" s="86" t="inlineStr">
+      <c r="E22" s="49" t="n">
+        <v>82420455</v>
+      </c>
+      <c r="F22" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G22" s="253" t="n">
+      <c r="G22" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="83" t="n">
+      <c r="H22" s="172" t="n">
         <v>650</v>
       </c>
-      <c r="I22" s="84">
+      <c r="I22" s="172">
         <f>G22*H22</f>
         <v/>
       </c>
-      <c r="J22" s="82" t="inlineStr">
+      <c r="J22" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K22" s="254">
+      <c r="K22" s="175">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=пистолет+для+герметика", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L22" s="88" t="inlineStr">
-        <is>
-          <t>Покупка от 21.09.2026: Пистолет и санитарный герметик для ванны и швов</t>
-        </is>
-      </c>
+      <c r="L22" s="49" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="91" t="n">
+      <c r="A23" s="62" t="n">
         <v>51</v>
       </c>
-      <c r="B23" s="88" t="inlineStr">
+      <c r="B23" s="44" t="inlineStr">
         <is>
           <t>Санузел / Стены</t>
         </is>
       </c>
-      <c r="C23" s="88" t="inlineStr">
+      <c r="C23" s="44" t="inlineStr">
         <is>
           <t>Штукатурка / Мешки</t>
         </is>
       </c>
-      <c r="D23" s="88" t="inlineStr">
+      <c r="D23" s="44" t="inlineStr">
         <is>
           <t>Штукатурка гипсовая Старатели 30кг 3шт, перчатки, мешки 3шт (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E23" s="91" t="inlineStr">
-        <is>
-          <t>4601745000407</t>
-        </is>
-      </c>
-      <c r="F23" s="91" t="inlineStr">
+      <c r="E23" s="44" t="n">
+        <v>4601745000407</v>
+      </c>
+      <c r="F23" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G23" s="255" t="n">
+      <c r="G23" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="89" t="n">
+      <c r="H23" s="173" t="n">
         <v>1638</v>
       </c>
-      <c r="I23" s="90">
+      <c r="I23" s="173">
         <f>G23*H23</f>
         <v/>
       </c>
-      <c r="J23" s="88" t="inlineStr">
+      <c r="J23" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K23" s="256">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4601745000407", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L23" s="82" t="inlineStr">
-        <is>
-          <t>Чек от 23.09.2026 15:55: Штукатурка Старатели 3шт (1515₽), перчатки, мешки</t>
-        </is>
-      </c>
+      <c r="K23" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%A8%D1%82%D1%83%D0%BA%D0%B0%D1%82%D1%83%D1%80%D0%BA%D0%B0+%D0%B3%D0%B8%D0%BF%D1%81%D0%BE%D0%B2%D0%B0%D1%8F+%D0%A1%D1%82%D0%B0%D1%80%D0%B0%D1%82%D0%B5%D0%BB%D0%B8+30%D0%BA%D0%B3", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L23" s="44" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="86" t="n">
+      <c r="A24" s="64" t="n">
         <v>52</v>
       </c>
-      <c r="B24" s="82" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>Радиаторы / Стены</t>
         </is>
       </c>
-      <c r="C24" s="82" t="inlineStr">
+      <c r="C24" s="49" t="inlineStr">
         <is>
           <t>Краска / Кисти</t>
         </is>
       </c>
-      <c r="D24" s="82" t="inlineStr">
+      <c r="D24" s="49" t="inlineStr">
         <is>
           <t>Грунт-эмаль Luxens 3в1 белая 2.4кг, щетка металл 5-рядная, кисть Dilwis 70мм</t>
         </is>
       </c>
-      <c r="E24" s="86" t="inlineStr">
-        <is>
-          <t>4610088004195</t>
-        </is>
-      </c>
-      <c r="F24" s="86" t="inlineStr">
+      <c r="E24" s="49" t="n">
+        <v>4610088004195</v>
+      </c>
+      <c r="F24" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G24" s="253" t="n">
+      <c r="G24" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="83" t="n">
+      <c r="H24" s="172" t="n">
         <v>1769</v>
       </c>
-      <c r="I24" s="84">
+      <c r="I24" s="172">
         <f>G24*H24</f>
         <v/>
       </c>
-      <c r="J24" s="82" t="inlineStr">
+      <c r="J24" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K24" s="254">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4610088004195", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L24" s="88" t="inlineStr">
-        <is>
-          <t>Чек от 23.09.2026 16:10: Грунт-эмаль Luxens 3в1 2.4кг (1492₽), кисть, щетка</t>
-        </is>
-      </c>
+      <c r="K24" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%93%D1%80%D1%83%D0%BD%D1%82+%D1%8D%D0%BC%D0%B0%D0%BB%D1%8C+Luxens+3%D0%B21+%D0%B1%D0%B5%D0%BB%D0%B0%D1%8F", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L24" s="49" t="inlineStr"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="91" t="n">
+      <c r="A25" s="62" t="n">
         <v>53</v>
       </c>
-      <c r="B25" s="88" t="inlineStr">
+      <c r="B25" s="44" t="inlineStr">
         <is>
           <t>Санузел / Короб</t>
         </is>
       </c>
-      <c r="C25" s="88" t="inlineStr">
+      <c r="C25" s="44" t="inlineStr">
         <is>
           <t>Профиль / Саморезы</t>
         </is>
       </c>
-      <c r="D25" s="88" t="inlineStr">
+      <c r="D25" s="44" t="inlineStr">
         <is>
           <t>Профиль ППН 27х28 3шт, профиль ПП 60х27 1шт, саморезы оцинк./фосфат. (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="E25" s="91" t="inlineStr">
-        <is>
-          <t>4600776027292</t>
-        </is>
-      </c>
-      <c r="F25" s="91" t="inlineStr">
+      <c r="E25" s="44" t="n">
+        <v>4600776027292</v>
+      </c>
+      <c r="F25" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G25" s="255" t="n">
+      <c r="G25" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="89" t="n">
+      <c r="H25" s="173" t="n">
         <v>911.7</v>
       </c>
-      <c r="I25" s="90">
+      <c r="I25" s="173">
         <f>G25*H25</f>
         <v/>
       </c>
-      <c r="J25" s="88" t="inlineStr">
+      <c r="J25" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K25" s="256">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4600776027292", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L25" s="82" t="inlineStr">
-        <is>
-          <t>Чек от 25.09.2026 08:18: Профили каркаса короба с/у и крепеж</t>
-        </is>
-      </c>
+      <c r="K25" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%9F%D1%80%D0%BE%D1%84%D0%B8%D0%BB%D1%8C+%D0%9F%D0%9F+60%D1%8527+Knauf", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L25" s="44" t="inlineStr"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="86" t="n">
+      <c r="A26" s="64" t="n">
         <v>54</v>
       </c>
-      <c r="B26" s="82" t="inlineStr">
+      <c r="B26" s="49" t="inlineStr">
         <is>
           <t>Санузел / Короб</t>
         </is>
       </c>
-      <c r="C26" s="82" t="inlineStr">
+      <c r="C26" s="49" t="inlineStr">
         <is>
           <t>ГСП / Профиль / Смеси</t>
         </is>
       </c>
-      <c r="D26" s="82" t="inlineStr">
+      <c r="D26" s="49" t="inlineStr">
         <is>
           <t>ГСП-Н3 Knauf влагост. 1500х600х12.5 2шт, штукатурка Старатели 30кг, профили 28х27 2шт, 60х27 1шт</t>
         </is>
       </c>
-      <c r="E26" s="86" t="inlineStr">
-        <is>
-          <t>4607160003634</t>
-        </is>
-      </c>
-      <c r="F26" s="86" t="inlineStr">
+      <c r="E26" s="49" t="n">
+        <v>4607160003634</v>
+      </c>
+      <c r="F26" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G26" s="253" t="n">
+      <c r="G26" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="83" t="n">
+      <c r="H26" s="172" t="n">
         <v>1582</v>
       </c>
-      <c r="I26" s="84">
+      <c r="I26" s="172">
         <f>G26*H26</f>
         <v/>
       </c>
-      <c r="J26" s="82" t="inlineStr">
+      <c r="J26" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K26" s="254">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4607160003634", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L26" s="88" t="inlineStr">
-        <is>
-          <t>Чек от 25.09.2026 15:53: Влагостойкие плиты Knauf для короба с/у, штукатурка</t>
-        </is>
-      </c>
+      <c r="K26" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%93%D0%A1%D0%9F+%D0%9D3+Knauf+%D0%B2%D0%BB%D0%B0%D0%B3%D0%BE%D1%81%D1%82%D0%BE%D0%B9%D0%BA%D0%B8%D0%B9", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L26" s="49" t="inlineStr"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="91" t="n">
+      <c r="A27" s="62" t="n">
         <v>55</v>
       </c>
-      <c r="B27" s="88" t="inlineStr">
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>Полы / Финиш</t>
         </is>
       </c>
-      <c r="C27" s="88" t="inlineStr">
+      <c r="C27" s="44" t="inlineStr">
         <is>
           <t>Ламинат / Плинтус</t>
         </is>
       </c>
-      <c r="D27" s="88" t="inlineStr">
+      <c r="D27" s="44" t="inlineStr">
         <is>
           <t>Ламинат Kronostep Дуб Ночиолла 33кл 10мм 24 упак./41.52м², подложка Monlid 9шт, плинтус белый 8см 20шт</t>
         </is>
       </c>
-      <c r="E27" s="91" t="inlineStr">
-        <is>
-          <t>4607113367721</t>
-        </is>
-      </c>
-      <c r="F27" s="91" t="inlineStr">
+      <c r="E27" s="44" t="n">
+        <v>4607113367721</v>
+      </c>
+      <c r="F27" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G27" s="255" t="n">
+      <c r="G27" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="89" t="n">
+      <c r="H27" s="173" t="n">
         <v>41914.52</v>
       </c>
-      <c r="I27" s="90">
+      <c r="I27" s="173">
         <f>G27*H27</f>
         <v/>
       </c>
-      <c r="J27" s="88" t="inlineStr">
+      <c r="J27" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K27" s="256">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4607113367721", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L27" s="82" t="inlineStr">
-        <is>
-          <t>Чек от 26.09.2026 17:41: Ламинат 10мм единым контуром, подложка 3мм, плинтус 80мм. Скидка -3637₽</t>
-        </is>
-      </c>
+      <c r="K27" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%9B%D0%B0%D0%BC%D0%B8%D0%BD%D0%B0%D1%82+Kronostep+%D0%94%D1%83%D0%B1+%D0%9D%D0%BE%D1%87%D0%B8%D0%BE%D0%BB%D0%BB%D0%B0+33+%D0%BA%D0%BB%D0%B0%D1%81%D1%81+10%D0%BC%D0%BC", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L27" s="44" t="inlineStr"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="86" t="n">
+      <c r="A28" s="64" t="n">
         <v>56</v>
       </c>
-      <c r="B28" s="82" t="inlineStr">
+      <c r="B28" s="49" t="inlineStr">
         <is>
           <t>Стены / Потолок</t>
         </is>
       </c>
-      <c r="C28" s="82" t="inlineStr">
+      <c r="C28" s="49" t="inlineStr">
         <is>
           <t>Грунт / Клей</t>
         </is>
       </c>
-      <c r="D28" s="82" t="inlineStr">
+      <c r="D28" s="49" t="inlineStr">
         <is>
           <t>Грунт перекрывающий пятна Axton 1л, клей монтажный Kudo 2шт, валик нат. мех, макловица-мини</t>
         </is>
       </c>
-      <c r="E28" s="86" t="inlineStr">
-        <is>
-          <t>4690364027858</t>
-        </is>
-      </c>
-      <c r="F28" s="86" t="inlineStr">
+      <c r="E28" s="49" t="n">
+        <v>4690364027858</v>
+      </c>
+      <c r="F28" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G28" s="253" t="n">
+      <c r="G28" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="83" t="n">
+      <c r="H28" s="172" t="n">
         <v>1070</v>
       </c>
-      <c r="I28" s="84">
+      <c r="I28" s="172">
         <f>G28*H28</f>
         <v/>
       </c>
-      <c r="J28" s="82" t="inlineStr">
+      <c r="J28" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K28" s="254">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4690364027858", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L28" s="88" t="inlineStr">
-        <is>
-          <t>Чек от 26.09.2026 17:40: Блокирующий грунт Axton от старых пятен, клей Kudo</t>
-        </is>
-      </c>
+      <c r="K28" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%93%D1%80%D1%83%D0%BD%D1%82+%D0%BF%D0%B5%D1%80%D0%B5%D0%BA%D1%80%D1%8B%D0%B2%D0%B0%D1%8E%D1%89%D0%B8%D0%B9+%D0%BF%D1%8F%D1%82%D0%BD%D0%B0+Axton", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L28" s="49" t="inlineStr"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="91" t="n">
+      <c r="A29" s="62" t="n">
         <v>57</v>
       </c>
-      <c r="B29" s="88" t="inlineStr">
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>Хознужды / Инструмент</t>
         </is>
       </c>
-      <c r="C29" s="88" t="inlineStr">
+      <c r="C29" s="44" t="inlineStr">
         <is>
           <t>Уборка / Краска</t>
         </is>
       </c>
-      <c r="D29" s="88" t="inlineStr">
+      <c r="D29" s="44" t="inlineStr">
         <is>
           <t>Швабра In Loran, тряпки 3шт, краска Olimp 0.9л, упак. лента Axton, саморезы, ножи 2шт, карандаш</t>
         </is>
       </c>
-      <c r="E29" s="91" t="inlineStr">
-        <is>
-          <t>4630085515241</t>
-        </is>
-      </c>
-      <c r="F29" s="91" t="inlineStr">
+      <c r="E29" s="44" t="n">
+        <v>4630085515241</v>
+      </c>
+      <c r="F29" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G29" s="255" t="n">
+      <c r="G29" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="89" t="n">
+      <c r="H29" s="173" t="n">
         <v>1707.17</v>
       </c>
-      <c r="I29" s="90">
+      <c r="I29" s="173">
         <f>G29*H29</f>
         <v/>
       </c>
-      <c r="J29" s="88" t="inlineStr">
+      <c r="J29" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K29" s="256">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4630085515241", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L29" s="82" t="inlineStr">
-        <is>
-          <t>Чек от 27.09.2026 09:53: Инструмент для уборки, расходники, краска Olimp</t>
-        </is>
-      </c>
+      <c r="K29" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%9A%D1%80%D0%B0%D1%81%D0%BA%D0%B0+%D0%9E%D0%BB%D0%B8%D0%BC%D0%BF+%D1%84%D0%B0%D1%81%D0%B0%D0%B4%D0%BD%D0%B0%D1%8F+%D0%B1%D0%B5%D0%BB%D0%B0%D1%8F", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L29" s="44" t="inlineStr"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="86" t="n">
+      <c r="A30" s="64" t="n">
         <v>65</v>
       </c>
-      <c r="B30" s="82" t="inlineStr">
+      <c r="B30" s="49" t="inlineStr">
         <is>
           <t>Санузел / Инженерия</t>
         </is>
       </c>
-      <c r="C30" s="82" t="inlineStr">
+      <c r="C30" s="49" t="inlineStr">
         <is>
           <t>Трубы / Фитинги / Биты</t>
         </is>
       </c>
-      <c r="D30" s="82" t="inlineStr">
+      <c r="D30" s="49" t="inlineStr">
         <is>
           <t>Труба ПП D20 2шт, отвод 50х15°, соединитель D50, биты Rage PH2 70мм</t>
         </is>
       </c>
-      <c r="E30" s="86" t="inlineStr">
-        <is>
-          <t>4607181620858</t>
-        </is>
-      </c>
-      <c r="F30" s="86" t="inlineStr">
+      <c r="E30" s="49" t="n">
+        <v>4607181620858</v>
+      </c>
+      <c r="F30" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G30" s="253" t="n">
+      <c r="G30" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="83" t="n">
+      <c r="H30" s="172" t="n">
         <v>550</v>
       </c>
-      <c r="I30" s="84">
+      <c r="I30" s="172">
         <f>G30*H30</f>
         <v/>
       </c>
-      <c r="J30" s="82" t="inlineStr">
+      <c r="J30" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K30" s="254">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4607181620858", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L30" s="246" t="n"/>
+      <c r="K30" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%A2%D1%80%D1%83%D0%B1%D0%B0+%D0%BF%D0%BE%D0%BB%D0%B8%D0%BF%D1%80%D0%BE%D0%BF%D0%B8%D0%BB%D0%B5%D0%BD%D0%BE%D0%B2%D0%B0%D1%8F+20+%D0%BC%D0%BC+Valtec", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L30" s="49" t="inlineStr"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="91" t="n">
+      <c r="A31" s="62" t="n">
         <v>66</v>
       </c>
-      <c r="B31" s="88" t="inlineStr">
+      <c r="B31" s="44" t="inlineStr">
         <is>
           <t>Санузел / Финиш</t>
         </is>
       </c>
-      <c r="C31" s="88" t="inlineStr">
+      <c r="C31" s="44" t="inlineStr">
         <is>
           <t>Керамогранит Calacatta</t>
         </is>
       </c>
-      <c r="D31" s="88" t="inlineStr">
+      <c r="D31" s="44" t="inlineStr">
         <is>
           <t>Керамогранит Calacatta superwhite 60х120 (добор 2 упак. / 2.88 м²)</t>
         </is>
       </c>
-      <c r="E31" s="91" t="inlineStr">
-        <is>
-          <t>4673766221451</t>
-        </is>
-      </c>
-      <c r="F31" s="91" t="inlineStr">
+      <c r="E31" s="44" t="n">
+        <v>4673766221451</v>
+      </c>
+      <c r="F31" s="62" t="inlineStr">
         <is>
           <t>упак.</t>
         </is>
       </c>
-      <c r="G31" s="255" t="n">
+      <c r="G31" s="327" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="89" t="n">
+      <c r="H31" s="173" t="n">
         <v>2938</v>
       </c>
-      <c r="I31" s="90">
+      <c r="I31" s="173">
         <f>G31*H31</f>
         <v/>
       </c>
-      <c r="J31" s="88" t="inlineStr">
+      <c r="J31" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="K31" s="256">
-        <f>HYPERLINK("https://lemanapro.ru/search/?q=4673766221451", "Открыть ↗")</f>
-        <v/>
-      </c>
-      <c r="L31" s="249" t="n"/>
+      <c r="K31" s="174">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%9A%D0%B5%D1%80%D0%B0%D0%BC%D0%BE%D0%B3%D1%80%D0%B0%D0%BD%D0%B8%D1%82+Calacatta+60%D1%85120", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L31" s="44" t="inlineStr"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="257" t="n"/>
-      <c r="B32" s="258" t="inlineStr">
+      <c r="A32" s="64" t="n">
+        <v>70</v>
+      </c>
+      <c r="B32" s="49" t="inlineStr">
+        <is>
+          <t>Все зоны / Стены</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="inlineStr">
+        <is>
+          <t>Обои / Чистовая отделка</t>
+        </is>
+      </c>
+      <c r="D32" s="49" t="inlineStr">
+        <is>
+          <t>Материалы для поклейки обоев (обои Twid 12 рул., клей Kleo 4 шт., грунтовка Knauf 10 кг, шпатели, валики, салфетки)</t>
+        </is>
+      </c>
+      <c r="E32" s="49" t="n">
+        <v>4607160007070</v>
+      </c>
+      <c r="F32" s="64" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G32" s="326" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="172" t="n">
+        <v>24893</v>
+      </c>
+      <c r="I32" s="172">
+        <f>G32*H32</f>
+        <v/>
+      </c>
+      <c r="J32" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="K32" s="175">
+        <f>HYPERLINK("https://lemanapro.ru/search/?q=%D0%9E%D0%B1%D0%BE%D0%B8+%D0%B2%D0%B8%D0%BD%D0%B8%D0%BB%D0%BE%D0%B2%D1%8B%D0%B5+%D0%BD%D0%B0+%D1%84%D0%BB%D0%B8%D0%B7%D0%B5%D0%BB%D0%B8%D0%BD%D0%B5+1.06+Twid", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L32" s="49" t="inlineStr"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="322" t="n"/>
+      <c r="B33" s="328" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ ЛЕМАНА ПРО (ПО ЧЕКАМ):</t>
         </is>
       </c>
-      <c r="C32" s="259" t="n"/>
-      <c r="D32" s="259" t="n"/>
-      <c r="E32" s="257" t="n"/>
-      <c r="F32" s="257" t="n"/>
-      <c r="G32" s="260" t="n"/>
-      <c r="H32" s="261" t="n"/>
-      <c r="I32" s="261">
-        <f>SUM(I6:I31)</f>
-        <v/>
-      </c>
-      <c r="J32" s="259" t="n"/>
-      <c r="K32" s="257" t="n"/>
-      <c r="L32" s="88" t="inlineStr">
-        <is>
-          <t>Оперативная докупка расходников для демонтажа</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="262" t="n"/>
-      <c r="B33" s="263" t="inlineStr">
-        <is>
-          <t>⚡ БЛОК 2: ИНЖЕНЕРНЫЕ МАТЕРИАЛЫ, ДВЕРИ И ОСНАЩЕНИЕ (СПЕЦПОСТАВЩИКИ)</t>
-        </is>
-      </c>
-      <c r="C33" s="264" t="n"/>
-      <c r="D33" s="264" t="n"/>
-      <c r="E33" s="262" t="n"/>
-      <c r="F33" s="262" t="n"/>
-      <c r="G33" s="265" t="n"/>
-      <c r="H33" s="266" t="n"/>
-      <c r="I33" s="267" t="n"/>
-      <c r="J33" s="264" t="n"/>
-      <c r="K33" s="268" t="n"/>
-      <c r="L33" s="82" t="inlineStr">
-        <is>
-          <t>Замена вводных узлов и прибора учёта</t>
-        </is>
-      </c>
+      <c r="C33" s="322" t="n"/>
+      <c r="D33" s="322" t="n"/>
+      <c r="E33" s="322" t="n"/>
+      <c r="F33" s="322" t="n"/>
+      <c r="G33" s="329" t="n"/>
+      <c r="H33" s="330" t="n"/>
+      <c r="I33" s="331">
+        <f>SUM(I6:I32)</f>
+        <v/>
+      </c>
+      <c r="J33" s="322" t="n"/>
+      <c r="K33" s="322" t="n"/>
+      <c r="L33" s="322" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="86" t="n">
+      <c r="A34" s="322" t="n"/>
+      <c r="B34" s="332" t="inlineStr">
+        <is>
+          <t>⚡ БЛОК 2: ИНЖЕНЕРНЫЕ МАТЕРИАЛЫ, ДВЕРИ И ОСНАЩЕНИЕ (СПЕЦПОСТАВЩИКИ) (21 ПОЗИЦИЙ)</t>
+        </is>
+      </c>
+      <c r="C34" s="322" t="n"/>
+      <c r="D34" s="322" t="n"/>
+      <c r="E34" s="322" t="n"/>
+      <c r="F34" s="322" t="n"/>
+      <c r="G34" s="329" t="n"/>
+      <c r="H34" s="330" t="n"/>
+      <c r="I34" s="330" t="n"/>
+      <c r="J34" s="322" t="n"/>
+      <c r="K34" s="322" t="n"/>
+      <c r="L34" s="322" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="B34" s="82" t="inlineStr">
+      <c r="B35" s="44" t="inlineStr">
         <is>
           <t>Расходники</t>
         </is>
       </c>
-      <c r="C34" s="82" t="inlineStr">
+      <c r="C35" s="44" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="D34" s="82" t="inlineStr">
+      <c r="D35" s="44" t="inlineStr">
         <is>
           <t>Мешки мусорные плотные, перчатки рабочие (хозмаг/рынок)</t>
         </is>
       </c>
-      <c r="E34" s="86" t="inlineStr">
+      <c r="E35" s="44" t="inlineStr">
         <is>
           <t>ХОЗМАГ-МЕШКИ</t>
         </is>
       </c>
-      <c r="F34" s="86" t="inlineStr">
+      <c r="F35" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G34" s="253" t="n">
+      <c r="G35" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="83" t="n">
+      <c r="H35" s="173" t="n">
         <v>300</v>
       </c>
-      <c r="I34" s="84">
-        <f>G34*H34</f>
-        <v/>
-      </c>
-      <c r="J34" s="82" t="inlineStr">
+      <c r="I35" s="173">
+        <f>G35*H35</f>
+        <v/>
+      </c>
+      <c r="J35" s="44" t="inlineStr">
         <is>
           <t>Хозмаг / Рынок</t>
         </is>
       </c>
-      <c r="K34" s="254">
+      <c r="K35" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=мешки+мусорные+строительные", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L34" s="88" t="inlineStr">
-        <is>
-          <t>Латунные фитинги, муфты, уплотнители</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="91" t="n">
+      <c r="L35" s="44" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="64" t="n">
         <v>11</v>
       </c>
-      <c r="B35" s="88" t="inlineStr">
+      <c r="B36" s="49" t="inlineStr">
         <is>
           <t>Сантехника</t>
         </is>
       </c>
-      <c r="C35" s="88" t="inlineStr">
+      <c r="C36" s="49" t="inlineStr">
         <is>
           <t>Учёт воды</t>
         </is>
       </c>
-      <c r="D35" s="88" t="inlineStr">
+      <c r="D36" s="49" t="inlineStr">
         <is>
           <t>Счётчик горячей/холодной воды + кран на ввод (материалы)</t>
         </is>
       </c>
-      <c r="E35" s="91" t="inlineStr">
+      <c r="E36" s="49" t="inlineStr">
         <is>
           <t>СЧЕТЧИК-ВОДЫ</t>
         </is>
       </c>
-      <c r="F35" s="91" t="inlineStr">
+      <c r="F36" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G35" s="255" t="n">
+      <c r="G36" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="89" t="n">
+      <c r="H36" s="172" t="n">
         <v>2100</v>
       </c>
-      <c r="I35" s="90">
-        <f>G35*H35</f>
-        <v/>
-      </c>
-      <c r="J35" s="88" t="inlineStr">
+      <c r="I36" s="172">
+        <f>G36*H36</f>
+        <v/>
+      </c>
+      <c r="J36" s="49" t="inlineStr">
         <is>
           <t>Вадим (сантехник УК)</t>
         </is>
       </c>
-      <c r="K35" s="256">
+      <c r="K36" s="175">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=счетчик+воды+универсальный", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L35" s="82" t="inlineStr">
-        <is>
-          <t>Металл 1.5 мм, МДФ-панель, надежные замки</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="86" t="n">
+      <c r="L36" s="49" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="B36" s="82" t="inlineStr">
+      <c r="B37" s="44" t="inlineStr">
         <is>
           <t>Сантехника</t>
         </is>
       </c>
-      <c r="C36" s="82" t="inlineStr">
+      <c r="C37" s="44" t="inlineStr">
         <is>
           <t>Учёт воды</t>
         </is>
       </c>
-      <c r="D36" s="82" t="inlineStr">
+      <c r="D37" s="44" t="inlineStr">
         <is>
           <t>Покупка и установка счётчика и кранов (доплата за фитинги и муфты)</t>
         </is>
       </c>
-      <c r="E36" s="86" t="inlineStr">
+      <c r="E37" s="44" t="inlineStr">
         <is>
           <t>ФИТИНГИ-САНТЕХ</t>
         </is>
       </c>
-      <c r="F36" s="86" t="inlineStr">
+      <c r="F37" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G36" s="253" t="n">
+      <c r="G37" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="83" t="n">
+      <c r="H37" s="173" t="n">
         <v>2000</v>
       </c>
-      <c r="I36" s="84">
-        <f>G36*H36</f>
-        <v/>
-      </c>
-      <c r="J36" s="82" t="inlineStr">
+      <c r="I37" s="173">
+        <f>G37*H37</f>
+        <v/>
+      </c>
+      <c r="J37" s="44" t="inlineStr">
         <is>
           <t>Вадим (сантехник УК)</t>
         </is>
       </c>
-      <c r="K36" s="254">
+      <c r="K37" s="174">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=шаровый+кран+1/2", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L36" s="88" t="inlineStr">
-        <is>
-          <t>Транспортировка двери на ул. Фрунзе 17</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="91" t="n">
+      <c r="L37" s="44" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="64" t="n">
         <v>15</v>
       </c>
-      <c r="B37" s="88" t="inlineStr">
+      <c r="B38" s="49" t="inlineStr">
         <is>
           <t>Входная группа</t>
         </is>
       </c>
-      <c r="C37" s="88" t="inlineStr">
+      <c r="C38" s="49" t="inlineStr">
         <is>
           <t>Двери</t>
         </is>
       </c>
-      <c r="D37" s="88" t="inlineStr">
+      <c r="D38" s="49" t="inlineStr">
         <is>
           <t>Покупка входной металлической двери с внутренней МДФ-панелью</t>
         </is>
       </c>
-      <c r="E37" s="91" t="inlineStr">
+      <c r="E38" s="49" t="inlineStr">
         <is>
           <t>ДВЕРЬ-ВХОД-МДФ</t>
         </is>
       </c>
-      <c r="F37" s="91" t="inlineStr">
+      <c r="F38" s="64" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G37" s="255" t="n">
+      <c r="G38" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="89" t="n">
+      <c r="H38" s="172" t="n">
         <v>16000</v>
       </c>
-      <c r="I37" s="90">
-        <f>G37*H37</f>
-        <v/>
-      </c>
-      <c r="J37" s="88" t="inlineStr">
+      <c r="I38" s="172">
+        <f>G38*H38</f>
+        <v/>
+      </c>
+      <c r="J38" s="49" t="inlineStr">
         <is>
           <t>Владимир (двери)</t>
         </is>
       </c>
-      <c r="K37" s="256">
+      <c r="K38" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=входная+металлическая+дверь+мдф", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L37" s="82" t="inlineStr">
-        <is>
-          <t>Комплектная начинка щита и прибор учёта</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="86" t="n">
+      <c r="L38" s="49" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="B38" s="82" t="inlineStr">
+      <c r="B39" s="44" t="inlineStr">
         <is>
           <t>Входная группа</t>
         </is>
       </c>
-      <c r="C38" s="82" t="inlineStr">
+      <c r="C39" s="44" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="D38" s="82" t="inlineStr">
+      <c r="D39" s="44" t="inlineStr">
         <is>
           <t>Доставка входной металлической двери на объект</t>
         </is>
       </c>
-      <c r="E38" s="86" t="inlineStr">
+      <c r="E39" s="44" t="inlineStr">
         <is>
           <t>ДОСТАВКА-ДВЕРЬ</t>
         </is>
       </c>
-      <c r="F38" s="86" t="inlineStr">
+      <c r="F39" s="62" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G38" s="253" t="n">
+      <c r="G39" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="83" t="n">
+      <c r="H39" s="173" t="n">
         <v>1500</v>
       </c>
-      <c r="I38" s="84">
-        <f>G38*H38</f>
-        <v/>
-      </c>
-      <c r="J38" s="82" t="inlineStr">
+      <c r="I39" s="173">
+        <f>G39*H39</f>
+        <v/>
+      </c>
+      <c r="J39" s="44" t="inlineStr">
         <is>
           <t>Владимир / Доставка</t>
         </is>
       </c>
-      <c r="K38" s="254">
+      <c r="K39" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=доставка+дверей+грузоперевозки", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L38" s="88" t="inlineStr">
-        <is>
-          <t>Силовой кабель ГОСТ под розетки и свет</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="91" t="n">
+      <c r="L39" s="44" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="64" t="n">
         <v>17</v>
       </c>
-      <c r="B39" s="88" t="inlineStr">
+      <c r="B40" s="49" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C39" s="88" t="inlineStr">
+      <c r="C40" s="49" t="inlineStr">
         <is>
           <t>Щит / Автоматика</t>
         </is>
       </c>
-      <c r="D39" s="88" t="inlineStr">
+      <c r="D40" s="49" t="inlineStr">
         <is>
           <t>Черновые материалы электрики (щит 18м, новый электросчётчик, автоматы, УЗО, гофра)</t>
         </is>
       </c>
-      <c r="E39" s="91" t="inlineStr">
+      <c r="E40" s="49" t="inlineStr">
         <is>
           <t>ЩИТ-АВТ-КОМПЛЕКТ</t>
         </is>
       </c>
-      <c r="F39" s="91" t="inlineStr">
+      <c r="F40" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G39" s="255" t="n">
+      <c r="G40" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="89" t="n">
+      <c r="H40" s="172" t="n">
         <v>16500</v>
       </c>
-      <c r="I39" s="90">
-        <f>G39*H39</f>
-        <v/>
-      </c>
-      <c r="J39" s="88" t="inlineStr">
+      <c r="I40" s="172">
+        <f>G40*H40</f>
+        <v/>
+      </c>
+      <c r="J40" s="49" t="inlineStr">
         <is>
           <t>Анатолий / Поставщик</t>
         </is>
       </c>
-      <c r="K39" s="256">
+      <c r="K40" s="175">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=щит+встраиваемый+18+модулей", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L39" s="82" t="inlineStr">
-        <is>
-          <t>Дюбель-хомуты и стяжки для трасс</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="86" t="n">
+      <c r="L40" s="49" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="B40" s="82" t="inlineStr">
+      <c r="B41" s="44" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C40" s="82" t="inlineStr">
+      <c r="C41" s="44" t="inlineStr">
         <is>
           <t>Кабель</t>
         </is>
       </c>
-      <c r="D40" s="82" t="inlineStr">
+      <c r="D41" s="44" t="inlineStr">
         <is>
           <t>Кабель силовой ВВГнг-LS (ГОСТ 3х2.5 и 3х1.5 для всех трасс)</t>
         </is>
       </c>
-      <c r="E40" s="86" t="inlineStr">
+      <c r="E41" s="44" t="inlineStr">
         <is>
           <t>ВВГнг-LS-ГОСТ-1</t>
         </is>
       </c>
-      <c r="F40" s="86" t="inlineStr">
+      <c r="F41" s="62" t="inlineStr">
         <is>
           <t>бухта</t>
         </is>
       </c>
-      <c r="G40" s="253" t="n">
+      <c r="G41" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="83" t="n">
+      <c r="H41" s="173" t="n">
         <v>18000</v>
       </c>
-      <c r="I40" s="84">
-        <f>G40*H40</f>
-        <v/>
-      </c>
-      <c r="J40" s="82" t="inlineStr">
+      <c r="I41" s="173">
+        <f>G41*H41</f>
+        <v/>
+      </c>
+      <c r="J41" s="44" t="inlineStr">
         <is>
           <t>Электромонтаж / Поставщик</t>
         </is>
       </c>
-      <c r="K40" s="254">
+      <c r="K41" s="174">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=кабель+ВВГнг-LS+3х2.5", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L40" s="88" t="inlineStr">
-        <is>
-          <t>Дополнительный кабель на трассы кухни и коридора</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="91" t="n">
+      <c r="L41" s="44" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="64" t="n">
         <v>20</v>
       </c>
-      <c r="B41" s="88" t="inlineStr">
+      <c r="B42" s="49" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C41" s="88" t="inlineStr">
+      <c r="C42" s="49" t="inlineStr">
         <is>
           <t>Крепёж</t>
         </is>
       </c>
-      <c r="D41" s="88" t="inlineStr">
+      <c r="D42" s="49" t="inlineStr">
         <is>
           <t>Стяжки нейлоновые и крепёж для монтажа кабеля</t>
         </is>
       </c>
-      <c r="E41" s="91" t="inlineStr">
+      <c r="E42" s="49" t="inlineStr">
         <is>
           <t>КРЕПЕЖ-КАБЕЛЬ</t>
         </is>
       </c>
-      <c r="F41" s="91" t="inlineStr">
+      <c r="F42" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G41" s="255" t="n">
+      <c r="G42" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="89" t="n">
+      <c r="H42" s="172" t="n">
         <v>1000</v>
       </c>
-      <c r="I41" s="90">
-        <f>G41*H41</f>
-        <v/>
-      </c>
-      <c r="J41" s="88" t="inlineStr">
+      <c r="I42" s="172">
+        <f>G42*H42</f>
+        <v/>
+      </c>
+      <c r="J42" s="49" t="inlineStr">
         <is>
           <t>Хозмаг / Электромонтаж</t>
         </is>
       </c>
-      <c r="K41" s="256">
+      <c r="K42" s="175">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=дюбель+хомут+для+кабеля", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L41" s="82" t="inlineStr">
-        <is>
-          <t>Акустическое оснащение объекта для бригад</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="86" t="n">
+      <c r="L42" s="49" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="62" t="n">
         <v>23</v>
       </c>
-      <c r="B42" s="82" t="inlineStr">
+      <c r="B43" s="44" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C42" s="82" t="inlineStr">
+      <c r="C43" s="44" t="inlineStr">
         <is>
           <t>Кабель</t>
         </is>
       </c>
-      <c r="D42" s="82" t="inlineStr">
+      <c r="D43" s="44" t="inlineStr">
         <is>
           <t>Докупка силового кабеля ВВГнг-LS (дополнительный метраж трасс)</t>
         </is>
       </c>
-      <c r="E42" s="86" t="inlineStr">
+      <c r="E43" s="44" t="inlineStr">
         <is>
           <t>ВВГнг-LS-ГОСТ-2</t>
         </is>
       </c>
-      <c r="F42" s="86" t="inlineStr">
+      <c r="F43" s="62" t="inlineStr">
         <is>
           <t>бухта</t>
         </is>
       </c>
-      <c r="G42" s="253" t="n">
+      <c r="G43" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="83" t="n">
+      <c r="H43" s="173" t="n">
         <v>13000</v>
       </c>
-      <c r="I42" s="84">
-        <f>G42*H42</f>
-        <v/>
-      </c>
-      <c r="J42" s="82" t="inlineStr">
+      <c r="I43" s="173">
+        <f>G43*H43</f>
+        <v/>
+      </c>
+      <c r="J43" s="44" t="inlineStr">
         <is>
           <t>Электромонтаж / Поставщик</t>
         </is>
       </c>
-      <c r="K42" s="254">
+      <c r="K43" s="174">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=кабель+ВВГнг-LS+3х1.5", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L42" s="88" t="inlineStr">
-        <is>
-          <t>Бытовое снабжение объекта</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="91" t="n">
+      <c r="L43" s="44" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="64" t="n">
         <v>27</v>
       </c>
-      <c r="B43" s="88" t="inlineStr">
+      <c r="B44" s="49" t="inlineStr">
         <is>
           <t>Оснащение</t>
         </is>
       </c>
-      <c r="C43" s="88" t="inlineStr">
+      <c r="C44" s="49" t="inlineStr">
         <is>
           <t>Инвентарь</t>
         </is>
       </c>
-      <c r="D43" s="88" t="inlineStr">
+      <c r="D44" s="49" t="inlineStr">
         <is>
           <t>Портативная акустика Xiaomi Bluetooth Speaker Essential Green</t>
         </is>
       </c>
-      <c r="E43" s="91" t="inlineStr">
+      <c r="E44" s="49" t="inlineStr">
         <is>
           <t>XIAOMI-SPK-ESS</t>
         </is>
       </c>
-      <c r="F43" s="91" t="inlineStr">
+      <c r="F44" s="64" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G43" s="255" t="n">
+      <c r="G44" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="89" t="n">
+      <c r="H44" s="172" t="n">
         <v>1250</v>
       </c>
-      <c r="I43" s="90">
-        <f>G43*H43</f>
-        <v/>
-      </c>
-      <c r="J43" s="88" t="inlineStr">
+      <c r="I44" s="172">
+        <f>G44*H44</f>
+        <v/>
+      </c>
+      <c r="J44" s="49" t="inlineStr">
         <is>
           <t>ООО ДНС Ритейл (DNS)</t>
         </is>
       </c>
-      <c r="K43" s="256">
+      <c r="K44" s="175">
         <f>HYPERLINK("https://www.dns-shop.ru/search/?q=Xiaomi+Bluetooth+Speaker", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L43" s="82" t="inlineStr">
-        <is>
-          <t>Чек от 15.09.2026: Муфта-восстановитель 110/110, разводка труб под ванну, раковину, унитаз</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="86" t="n">
+      <c r="L44" s="49" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="62" t="n">
         <v>29</v>
       </c>
-      <c r="B44" s="82" t="inlineStr">
+      <c r="B45" s="44" t="inlineStr">
         <is>
           <t>Оснащение</t>
         </is>
       </c>
-      <c r="C44" s="82" t="inlineStr">
+      <c r="C45" s="44" t="inlineStr">
         <is>
           <t>Хознужды</t>
         </is>
       </c>
-      <c r="D44" s="82" t="inlineStr">
+      <c r="D45" s="44" t="inlineStr">
         <is>
           <t>Хозрасходы на объект: салфетки влажные и питьевая вода для мастеров</t>
         </is>
       </c>
-      <c r="E44" s="86" t="inlineStr">
+      <c r="E45" s="44" t="inlineStr">
         <is>
           <t>ХОЗ-ВОДА-САЛФЕТКИ</t>
         </is>
       </c>
-      <c r="F44" s="86" t="inlineStr">
+      <c r="F45" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G44" s="253" t="n">
+      <c r="G45" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="83" t="n">
+      <c r="H45" s="173" t="n">
         <v>520</v>
       </c>
-      <c r="I44" s="84">
-        <f>G44*H44</f>
-        <v/>
-      </c>
-      <c r="J44" s="82" t="inlineStr">
+      <c r="I45" s="173">
+        <f>G45*H45</f>
+        <v/>
+      </c>
+      <c r="J45" s="44" t="inlineStr">
         <is>
           <t>Хозмаг / Продукты</t>
         </is>
       </c>
-      <c r="K44" s="254">
+      <c r="K45" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/produkty_pitaniya?q=питьевая+вода+19л", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L44" s="88" t="inlineStr">
-        <is>
-          <t>Чек №23 от 19.09.2026: Разводка труб ХВС/ГВС, шаровой кран ввода, планка под смеситель ванны</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="91" t="n">
+      <c r="L45" s="44" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="64" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="88" t="inlineStr">
+      <c r="B46" s="49" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C45" s="88" t="inlineStr">
+      <c r="C46" s="49" t="inlineStr">
         <is>
           <t>Канализация</t>
         </is>
       </c>
-      <c r="D45" s="88" t="inlineStr">
+      <c r="D46" s="49" t="inlineStr">
         <is>
           <t>Канализация с/у (муфта-восстановитель раструба 110/110, трубы ПП 50, тройник 110/50, заглушка, отводы)</t>
         </is>
       </c>
-      <c r="E45" s="91" t="inlineStr">
+      <c r="E46" s="49" t="inlineStr">
         <is>
           <t>КАНАЛ-СУ-110-50</t>
         </is>
       </c>
-      <c r="F45" s="91" t="inlineStr">
+      <c r="F46" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G45" s="255" t="n">
+      <c r="G46" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="89" t="n">
+      <c r="H46" s="172" t="n">
         <v>2988</v>
       </c>
-      <c r="I45" s="90">
-        <f>G45*H45</f>
-        <v/>
-      </c>
-      <c r="J45" s="88" t="inlineStr">
+      <c r="I46" s="172">
+        <f>G46*H46</f>
+        <v/>
+      </c>
+      <c r="J46" s="49" t="inlineStr">
         <is>
           <t>ИП Кучеров М.И. (Полимерстрой)</t>
         </is>
       </c>
-      <c r="K45" s="256">
+      <c r="K46" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=восстановитель+раструба+110", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L45" s="82" t="inlineStr">
-        <is>
-          <t>Слип от 27.09.2026 13:08: расходники для электрики</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="86" t="n">
+      <c r="L46" s="49" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="62" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="82" t="inlineStr">
+      <c r="B47" s="44" t="inlineStr">
         <is>
           <t>Санузел / Кухня</t>
         </is>
       </c>
-      <c r="C46" s="82" t="inlineStr">
+      <c r="C47" s="44" t="inlineStr">
         <is>
           <t>Водоснабжение</t>
         </is>
       </c>
-      <c r="D46" s="82" t="inlineStr">
+      <c r="D47" s="44" t="inlineStr">
         <is>
           <t>Трубы армированные Faser 20х2.8 12м, настенная планка смесителя, кран DN15, муфты, клипсы</t>
         </is>
       </c>
-      <c r="E46" s="86" t="inlineStr">
+      <c r="E47" s="44" t="inlineStr">
         <is>
           <t>PPR-FASER-WATSON</t>
         </is>
       </c>
-      <c r="F46" s="86" t="inlineStr">
+      <c r="F47" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G46" s="253" t="n">
+      <c r="G47" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="83" t="n">
+      <c r="H47" s="173" t="n">
         <v>3139.54</v>
       </c>
-      <c r="I46" s="84">
-        <f>G46*H46</f>
-        <v/>
-      </c>
-      <c r="J46" s="82" t="inlineStr">
+      <c r="I47" s="173">
+        <f>G47*H47</f>
+        <v/>
+      </c>
+      <c r="J47" s="44" t="inlineStr">
         <is>
           <t>ТС «Ваттсон» (Центргазсервис)</t>
         </is>
       </c>
-      <c r="K46" s="254">
+      <c r="K47" s="174">
         <f>HYPERLINK("https://wattson.ru/search/?q=Faser+20", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L46" s="88" t="inlineStr">
-        <is>
-          <t>Чек от 27.09.2026 13:23: клинья для укладки плитки</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="91" t="n">
+      <c r="L47" s="44" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="64" t="n">
         <v>58</v>
       </c>
-      <c r="B47" s="88" t="inlineStr">
+      <c r="B48" s="49" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C47" s="88" t="inlineStr">
+      <c r="C48" s="49" t="inlineStr">
         <is>
           <t>Материалы / Розетки</t>
         </is>
       </c>
-      <c r="D47" s="88" t="inlineStr">
+      <c r="D48" s="49" t="inlineStr">
         <is>
           <t>Электротовары (комплектующие/расходники электрики, ул. Коминтерна 26)</t>
         </is>
       </c>
-      <c r="E47" s="91" t="inlineStr">
+      <c r="E48" s="49" t="inlineStr">
         <is>
           <t>ЭЛЕКТРО-КОМИНТЕРНА</t>
         </is>
       </c>
-      <c r="F47" s="91" t="inlineStr">
+      <c r="F48" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G47" s="255" t="n">
+      <c r="G48" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="89" t="n">
+      <c r="H48" s="172" t="n">
         <v>190</v>
       </c>
-      <c r="I47" s="90">
-        <f>G47*H47</f>
-        <v/>
-      </c>
-      <c r="J47" s="88" t="inlineStr">
+      <c r="I48" s="172">
+        <f>G48*H48</f>
+        <v/>
+      </c>
+      <c r="J48" s="49" t="inlineStr">
         <is>
           <t>Магазин «Электротовары»</t>
         </is>
       </c>
-      <c r="K47" s="256">
+      <c r="K48" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=электротовары+коминтерна", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L47" s="82" t="inlineStr">
-        <is>
-          <t>Запорно-регулировочные краны на батареи отопления</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="86" t="n">
+      <c r="L48" s="49" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="62" t="n">
         <v>59</v>
       </c>
-      <c r="B48" s="82" t="inlineStr">
+      <c r="B49" s="44" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C48" s="82" t="inlineStr">
+      <c r="C49" s="44" t="inlineStr">
         <is>
           <t>СВП / Клинья</t>
         </is>
       </c>
-      <c r="D48" s="82" t="inlineStr">
+      <c r="D49" s="44" t="inlineStr">
         <is>
           <t>Клинья для плитки СВП 32х8х9мм 50шт (Магазин крепежа, ул. Мосина 29)</t>
         </is>
       </c>
-      <c r="E48" s="86" t="inlineStr">
+      <c r="E49" s="44" t="inlineStr">
         <is>
           <t>СВП-КЛИНЬЯ-50</t>
         </is>
       </c>
-      <c r="F48" s="86" t="inlineStr">
+      <c r="F49" s="62" t="inlineStr">
         <is>
           <t>упак.</t>
         </is>
       </c>
-      <c r="G48" s="253" t="n">
+      <c r="G49" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="83" t="n">
+      <c r="H49" s="173" t="n">
         <v>210</v>
       </c>
-      <c r="I48" s="84">
-        <f>G48*H48</f>
-        <v/>
-      </c>
-      <c r="J48" s="82" t="inlineStr">
+      <c r="I49" s="173">
+        <f>G49*H49</f>
+        <v/>
+      </c>
+      <c r="J49" s="44" t="inlineStr">
         <is>
           <t>ИП Звягинцева С.Н. (Крепеж)</t>
         </is>
       </c>
-      <c r="K48" s="254">
+      <c r="K49" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=клинья+для+плитки+свп", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L48" s="246" t="n"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="91" t="n">
+      <c r="L49" s="44" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="64" t="n">
         <v>64</v>
       </c>
-      <c r="B49" s="88" t="inlineStr">
+      <c r="B50" s="49" t="inlineStr">
         <is>
           <t>Отопление</t>
         </is>
       </c>
-      <c r="C49" s="88" t="inlineStr">
+      <c r="C50" s="49" t="inlineStr">
         <is>
           <t>Краны радиаторов</t>
         </is>
       </c>
-      <c r="D49" s="88" t="inlineStr">
+      <c r="D50" s="49" t="inlineStr">
         <is>
           <t>Два крана на радиаторы отопления (запорно-регулировочные краны)</t>
         </is>
       </c>
-      <c r="E49" s="91" t="inlineStr">
+      <c r="E50" s="49" t="inlineStr">
         <is>
           <t>КРАНЫ-РАДИАТОР-2</t>
         </is>
       </c>
-      <c r="F49" s="91" t="inlineStr">
+      <c r="F50" s="64" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G49" s="255" t="n">
+      <c r="G50" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="89" t="n">
+      <c r="H50" s="172" t="n">
         <v>1100</v>
       </c>
-      <c r="I49" s="90">
-        <f>G49*H49</f>
-        <v/>
-      </c>
-      <c r="J49" s="88" t="inlineStr">
+      <c r="I50" s="172">
+        <f>G50*H50</f>
+        <v/>
+      </c>
+      <c r="J50" s="49" t="inlineStr">
         <is>
           <t>Сантехмаркет / Хозмаг</t>
         </is>
       </c>
-      <c r="K49" s="256">
+      <c r="K50" s="175">
         <f>HYPERLINK("https://lemanapro.ru/search/?q=кран+для+радиатора+отопления", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L49" s="250" t="n"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="86" t="n">
+      <c r="L50" s="49" t="inlineStr"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="62" t="n">
         <v>67</v>
       </c>
-      <c r="B50" s="82" t="inlineStr">
+      <c r="B51" s="44" t="inlineStr">
         <is>
           <t>Санузел / Плитка</t>
         </is>
       </c>
-      <c r="C50" s="82" t="inlineStr">
+      <c r="C51" s="44" t="inlineStr">
         <is>
           <t>Уголки для плитки</t>
         </is>
       </c>
-      <c r="D50" s="82" t="inlineStr">
+      <c r="D51" s="44" t="inlineStr">
         <is>
           <t>Уголки для плитки (Михаил)</t>
         </is>
       </c>
-      <c r="E50" s="86" t="inlineStr">
+      <c r="E51" s="44" t="inlineStr">
         <is>
           <t>УГОЛКИ-ПЛИТКА</t>
         </is>
       </c>
-      <c r="F50" s="86" t="inlineStr">
+      <c r="F51" s="62" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="G50" s="253" t="n">
+      <c r="G51" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="83" t="n">
+      <c r="H51" s="173" t="n">
         <v>260</v>
       </c>
-      <c r="I50" s="84">
-        <f>G50*H50</f>
-        <v/>
-      </c>
-      <c r="J50" s="82" t="inlineStr">
+      <c r="I51" s="173">
+        <f>G51*H51</f>
+        <v/>
+      </c>
+      <c r="J51" s="44" t="inlineStr">
         <is>
           <t>Михаил (мастер/плиточник)</t>
         </is>
       </c>
-      <c r="K50" s="254">
+      <c r="K51" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/remont_i_stroitelstvo?q=уголки+для+плитки", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L50" s="88" t="inlineStr">
-        <is>
-          <t>Аварийное открытие двери после торгов</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="257" t="n"/>
-      <c r="B51" s="258" t="inlineStr">
+      <c r="L51" s="44" t="inlineStr"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="64" t="n">
+        <v>73</v>
+      </c>
+      <c r="B52" s="49" t="inlineStr">
+        <is>
+          <t>Оснащение</t>
+        </is>
+      </c>
+      <c r="C52" s="49" t="inlineStr">
+        <is>
+          <t>Инвентарь</t>
+        </is>
+      </c>
+      <c r="D52" s="49" t="inlineStr">
+        <is>
+          <t>Зарядка для колонки Xiaomi (оснащение объекта)</t>
+        </is>
+      </c>
+      <c r="E52" s="49" t="inlineStr">
+        <is>
+          <t>ЗУ-XIAOMI-TYPEC</t>
+        </is>
+      </c>
+      <c r="F52" s="64" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G52" s="326" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="172" t="n">
+        <v>550</v>
+      </c>
+      <c r="I52" s="172">
+        <f>G52*H52</f>
+        <v/>
+      </c>
+      <c r="J52" s="49" t="inlineStr">
+        <is>
+          <t>Магазин электроники</t>
+        </is>
+      </c>
+      <c r="K52" s="175">
+        <f>HYPERLINK("https://www.dns-shop.ru/search/?q=%D0%B7%D0%B0%D1%80%D1%8F%D0%B4%D0%BD%D0%BE%D0%B5+%D1%83%D1%81%D1%82%D1%80%D0%BE%D0%B9%D1%81%D1%82%D0%B2%D0%BE+Type+C+20W", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L52" s="49" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="62" t="n">
+        <v>75</v>
+      </c>
+      <c r="B53" s="44" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C53" s="44" t="inlineStr">
+        <is>
+          <t>Сантехника / Материалы</t>
+        </is>
+      </c>
+      <c r="D53" s="44" t="inlineStr">
+        <is>
+          <t>Фиттинги для труб «Американка» на трубы ПП на полотенцесушитель</t>
+        </is>
+      </c>
+      <c r="E53" s="44" t="inlineStr">
+        <is>
+          <t>ФИТТИНГИ-АМЕРИКАНКА</t>
+        </is>
+      </c>
+      <c r="F53" s="62" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G53" s="327" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="173" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I53" s="173">
+        <f>G53*H53</f>
+        <v/>
+      </c>
+      <c r="J53" s="44" t="inlineStr">
+        <is>
+          <t>Сантехмаркет / Хозмаг</t>
+        </is>
+      </c>
+      <c r="K53" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=фитинги+американка+для+труб", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L53" s="44" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="64" t="n">
+        <v>76</v>
+      </c>
+      <c r="B54" s="49" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C54" s="49" t="inlineStr">
+        <is>
+          <t>Сантехника / Материалы</t>
+        </is>
+      </c>
+      <c r="D54" s="49" t="inlineStr">
+        <is>
+          <t>Зажим для стекла (оснащение санузла)</t>
+        </is>
+      </c>
+      <c r="E54" s="49" t="inlineStr">
+        <is>
+          <t>ЗАЖИМ-СТЕКЛО-СУ</t>
+        </is>
+      </c>
+      <c r="F54" s="64" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G54" s="326" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="172" t="n">
+        <v>800</v>
+      </c>
+      <c r="I54" s="172">
+        <f>G54*H54</f>
+        <v/>
+      </c>
+      <c r="J54" s="49" t="inlineStr">
+        <is>
+          <t>Хозмаг / Сантехмаркет</t>
+        </is>
+      </c>
+      <c r="K54" s="175">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=зажим+для+стекла+санузел", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L54" s="49" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="62" t="n">
+        <v>77</v>
+      </c>
+      <c r="B55" s="44" t="inlineStr">
+        <is>
+          <t>Оснащение</t>
+        </is>
+      </c>
+      <c r="C55" s="44" t="inlineStr">
+        <is>
+          <t>Инвентарь</t>
+        </is>
+      </c>
+      <c r="D55" s="44" t="inlineStr">
+        <is>
+          <t>Вертикальный пылесос Timberk T-VCH-52 ДР (для финального клининга/стейджинга)</t>
+        </is>
+      </c>
+      <c r="E55" s="44" t="inlineStr">
+        <is>
+          <t>TIMBERK-TVCH52</t>
+        </is>
+      </c>
+      <c r="F55" s="62" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G55" s="327" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="173" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I55" s="173">
+        <f>G55*H55</f>
+        <v/>
+      </c>
+      <c r="J55" s="44" t="inlineStr">
+        <is>
+          <t>Техника Даром (ИП Панин И.П., Тула)</t>
+        </is>
+      </c>
+      <c r="K55" s="174">
+        <f>HYPERLINK("https://www.dns-shop.ru/search/?q=Timberk+T-VCH-52", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L55" s="44" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="322" t="n"/>
+      <c r="B56" s="328" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ СПЕЦПОСТАВЩИКОВ:</t>
         </is>
       </c>
-      <c r="C51" s="259" t="n"/>
-      <c r="D51" s="259" t="n"/>
-      <c r="E51" s="257" t="n"/>
-      <c r="F51" s="257" t="n"/>
-      <c r="G51" s="260" t="n"/>
-      <c r="H51" s="261" t="n"/>
-      <c r="I51" s="261">
-        <f>SUM(I34:I50)</f>
-        <v/>
-      </c>
-      <c r="J51" s="259" t="n"/>
-      <c r="K51" s="257" t="n"/>
-      <c r="L51" s="82" t="inlineStr">
-        <is>
-          <t>Вывоз мебели, санузла, чугуна, досок</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="269" t="n"/>
-      <c r="B52" s="270" t="inlineStr">
-        <is>
-          <t>👷‍♂️ БЛОК 3: РАБОТЫ МАСТЕРОВ, ОТДЕЛКА, ДЕМОНТАЖ И ЛОГИСТИКА (17 ПОЗИЦИЙ)</t>
-        </is>
-      </c>
-      <c r="C52" s="271" t="n"/>
-      <c r="D52" s="271" t="n"/>
-      <c r="E52" s="269" t="n"/>
-      <c r="F52" s="269" t="n"/>
-      <c r="G52" s="272" t="n"/>
-      <c r="H52" s="273" t="n"/>
-      <c r="I52" s="274" t="n"/>
-      <c r="J52" s="271" t="n"/>
-      <c r="K52" s="275" t="n"/>
-      <c r="L52" s="88" t="inlineStr">
-        <is>
-          <t>Перфоратор и монтировки для первичного демонтажа</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="91" t="n">
+      <c r="C56" s="322" t="n"/>
+      <c r="D56" s="322" t="n"/>
+      <c r="E56" s="322" t="n"/>
+      <c r="F56" s="322" t="n"/>
+      <c r="G56" s="333" t="n"/>
+      <c r="H56" s="334" t="n"/>
+      <c r="I56" s="331">
+        <f>SUM(I35:I55)</f>
+        <v/>
+      </c>
+      <c r="J56" s="322" t="n"/>
+      <c r="K56" s="322" t="n"/>
+      <c r="L56" s="322" t="n"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="322" t="n"/>
+      <c r="B57" s="335" t="inlineStr">
+        <is>
+          <t>👷‍♂️ БЛОК 3: РАБОТЫ МАСТЕРОВ, ОТДЕЛКА, ДЕМОНТАЖ И ЛОГИСТИКА (20 ПОЗИЦИЙ)</t>
+        </is>
+      </c>
+      <c r="C57" s="322" t="n"/>
+      <c r="D57" s="322" t="n"/>
+      <c r="E57" s="322" t="n"/>
+      <c r="F57" s="322" t="n"/>
+      <c r="G57" s="333" t="n"/>
+      <c r="H57" s="334" t="n"/>
+      <c r="I57" s="334" t="n"/>
+      <c r="J57" s="322" t="n"/>
+      <c r="K57" s="322" t="n"/>
+      <c r="L57" s="322" t="n"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="B53" s="88" t="inlineStr">
+      <c r="B58" s="49" t="inlineStr">
         <is>
           <t>Безопасность</t>
         </is>
       </c>
-      <c r="C53" s="88" t="inlineStr">
+      <c r="C58" s="49" t="inlineStr">
         <is>
           <t>Вскрытие</t>
         </is>
       </c>
-      <c r="D53" s="88" t="inlineStr">
+      <c r="D58" s="49" t="inlineStr">
         <is>
           <t>Вскрытие старого замка и обеспечение первого доступа</t>
         </is>
       </c>
-      <c r="E53" s="91" t="inlineStr">
+      <c r="E58" s="49" t="inlineStr">
         <is>
           <t>ВСКРЫТИЕ-ЗАМКА</t>
         </is>
       </c>
-      <c r="F53" s="91" t="inlineStr">
+      <c r="F58" s="64" t="inlineStr">
         <is>
           <t>выезд</t>
         </is>
       </c>
-      <c r="G53" s="255" t="n">
+      <c r="G58" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="89" t="n">
+      <c r="H58" s="172" t="n">
         <v>8000</v>
       </c>
-      <c r="I53" s="90">
-        <f>G53*H53</f>
-        <v/>
-      </c>
-      <c r="J53" s="88" t="inlineStr">
+      <c r="I58" s="172">
+        <f>G58*H58</f>
+        <v/>
+      </c>
+      <c r="J58" s="49" t="inlineStr">
         <is>
           <t>Служба вскрытия</t>
         </is>
       </c>
-      <c r="K53" s="256">
+      <c r="K58" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=вскрытие+замков", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L53" s="82" t="inlineStr">
-        <is>
-          <t>Тотальная зачистка и вынос мусора без лифта</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="86" t="n">
+      <c r="L58" s="49" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="B54" s="82" t="inlineStr">
+      <c r="B59" s="44" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C54" s="82" t="inlineStr">
+      <c r="C59" s="44" t="inlineStr">
         <is>
           <t>Вывоз мусора</t>
         </is>
       </c>
-      <c r="D54" s="82" t="inlineStr">
+      <c r="D59" s="44" t="inlineStr">
         <is>
           <t>Заказ мусорного контейнера 8 м³ (лодочка)</t>
         </is>
       </c>
-      <c r="E54" s="86" t="inlineStr">
+      <c r="E59" s="44" t="inlineStr">
         <is>
           <t>КОНТЕЙНЕР-МУСОР-8М3</t>
         </is>
       </c>
-      <c r="F54" s="86" t="inlineStr">
+      <c r="F59" s="62" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G54" s="253" t="n">
+      <c r="G59" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="83" t="n">
+      <c r="H59" s="173" t="n">
         <v>8500</v>
       </c>
-      <c r="I54" s="84">
-        <f>G54*H54</f>
-        <v/>
-      </c>
-      <c r="J54" s="82" t="inlineStr">
+      <c r="I59" s="173">
+        <f>G59*H59</f>
+        <v/>
+      </c>
+      <c r="J59" s="44" t="inlineStr">
         <is>
           <t>Елена (вывоз мусора)</t>
         </is>
       </c>
-      <c r="K54" s="254">
+      <c r="K59" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=вывоз+мусора+контейнер+8+м3", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L54" s="88" t="inlineStr">
-        <is>
-          <t>Сняли старые двери, расширили проем, выставили по уровню</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="91" t="n">
+      <c r="L59" s="44" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="64" t="n">
         <v>5</v>
       </c>
-      <c r="B55" s="88" t="inlineStr">
+      <c r="B60" s="49" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C55" s="88" t="inlineStr">
+      <c r="C60" s="49" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
-      <c r="D55" s="88" t="inlineStr">
+      <c r="D60" s="49" t="inlineStr">
         <is>
           <t>Аренда инструмента и помощь соседа по дому</t>
         </is>
       </c>
-      <c r="E55" s="91" t="inlineStr">
+      <c r="E60" s="49" t="inlineStr">
         <is>
           <t>АРЕНДА-ИНСТРУМЕНТ</t>
         </is>
       </c>
-      <c r="F55" s="91" t="inlineStr">
+      <c r="F60" s="64" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G55" s="255" t="n">
+      <c r="G60" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="89" t="n">
+      <c r="H60" s="172" t="n">
         <v>1000</v>
       </c>
-      <c r="I55" s="90">
-        <f>G55*H55</f>
-        <v/>
-      </c>
-      <c r="J55" s="88" t="inlineStr">
+      <c r="I60" s="172">
+        <f>G60*H60</f>
+        <v/>
+      </c>
+      <c r="J60" s="49" t="inlineStr">
         <is>
           <t>Сосед по дому</t>
         </is>
       </c>
-      <c r="K55" s="256">
+      <c r="K60" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=аренда+перфоратора", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L55" s="82" t="inlineStr">
-        <is>
-          <t>Монтаж всей проводки, сборка щита и счётчика</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="86" t="n">
+      <c r="L60" s="49" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="B56" s="82" t="inlineStr">
+      <c r="B61" s="44" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C56" s="82" t="inlineStr">
+      <c r="C61" s="44" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D56" s="82" t="inlineStr">
+      <c r="D61" s="44" t="inlineStr">
         <is>
           <t>Оплата работы бригады разнорабочих (4 чел., 28 чел.-час, спуск с 5 этажа)</t>
         </is>
       </c>
-      <c r="E56" s="86" t="inlineStr">
+      <c r="E61" s="44" t="inlineStr">
         <is>
           <t>ДЕМОНТАЖ-БРИГАДА-1</t>
         </is>
       </c>
-      <c r="F56" s="86" t="inlineStr">
+      <c r="F61" s="62" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="G56" s="253" t="n">
+      <c r="G61" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H56" s="83" t="n">
+      <c r="H61" s="173" t="n">
         <v>16000</v>
       </c>
-      <c r="I56" s="84">
-        <f>G56*H56</f>
-        <v/>
-      </c>
-      <c r="J56" s="82" t="inlineStr">
+      <c r="I61" s="173">
+        <f>G61*H61</f>
+        <v/>
+      </c>
+      <c r="J61" s="44" t="inlineStr">
         <is>
           <t>Бригада разнорабочих</t>
         </is>
       </c>
-      <c r="K56" s="254">
+      <c r="K61" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=демонтаж+квартиры+разнорабочие", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L56" s="88" t="inlineStr">
-        <is>
-          <t>Снятие старых слоев, обеспыливание поверхностей</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="91" t="n">
+      <c r="L61" s="44" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="64" t="n">
         <v>18</v>
       </c>
-      <c r="B57" s="88" t="inlineStr">
+      <c r="B62" s="49" t="inlineStr">
         <is>
           <t>Входная группа</t>
         </is>
       </c>
-      <c r="C57" s="88" t="inlineStr">
+      <c r="C62" s="49" t="inlineStr">
         <is>
           <t>Монтаж</t>
         </is>
       </c>
-      <c r="D57" s="88" t="inlineStr">
+      <c r="D62" s="49" t="inlineStr">
         <is>
           <t>Монтаж входной двери (демонтаж 2 старых дверей + монтаж новой)</t>
         </is>
       </c>
-      <c r="E57" s="91" t="inlineStr">
+      <c r="E62" s="49" t="inlineStr">
         <is>
           <t>МОНТАЖ-ДВЕРИ-ВХОД</t>
         </is>
       </c>
-      <c r="F57" s="91" t="inlineStr">
+      <c r="F62" s="64" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G57" s="255" t="n">
+      <c r="G62" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H57" s="89" t="n">
+      <c r="H62" s="172" t="n">
         <v>9000</v>
       </c>
-      <c r="I57" s="90">
-        <f>G57*H57</f>
-        <v/>
-      </c>
-      <c r="J57" s="88" t="inlineStr">
+      <c r="I62" s="172">
+        <f>G62*H62</f>
+        <v/>
+      </c>
+      <c r="J62" s="49" t="inlineStr">
         <is>
           <t>Андрей (монтаж дверей)</t>
         </is>
       </c>
-      <c r="K57" s="256">
+      <c r="K62" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=установка+входных+дверей", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L57" s="82" t="inlineStr">
-        <is>
-          <t>Перевозка партии смесей, керамогранита и ванны</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="86" t="n">
+      <c r="L62" s="49" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="B58" s="82" t="inlineStr">
+      <c r="B63" s="44" t="inlineStr">
         <is>
           <t>Электрика</t>
         </is>
       </c>
-      <c r="C58" s="82" t="inlineStr">
+      <c r="C63" s="44" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D58" s="82" t="inlineStr">
+      <c r="D63" s="44" t="inlineStr">
         <is>
           <t>Электромонтажные работы под ключ (разводка 32 точек, штробы, щит, счётчик)</t>
         </is>
       </c>
-      <c r="E58" s="86" t="inlineStr">
+      <c r="E63" s="44" t="inlineStr">
         <is>
           <t>РАБОТА-ЭЛЕКТРИКА-32</t>
         </is>
       </c>
-      <c r="F58" s="86" t="inlineStr">
+      <c r="F63" s="62" t="inlineStr">
         <is>
           <t>договор</t>
         </is>
       </c>
-      <c r="G58" s="253" t="n">
+      <c r="G63" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H58" s="83" t="n">
+      <c r="H63" s="173" t="n">
         <v>50000</v>
       </c>
-      <c r="I58" s="84">
-        <f>G58*H58</f>
-        <v/>
-      </c>
-      <c r="J58" s="82" t="inlineStr">
+      <c r="I63" s="173">
+        <f>G63*H63</f>
+        <v/>
+      </c>
+      <c r="J63" s="44" t="inlineStr">
         <is>
           <t>Анатолий Кушнарев (бригада)</t>
         </is>
       </c>
-      <c r="K58" s="254">
+      <c r="K63" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=электромонтаж+квартиры+под+ключ", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L58" s="88" t="inlineStr">
-        <is>
-          <t>Разгрузка 1.5 тонн смесей на 5 этаж без лифта</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="91" t="n">
+      <c r="L63" s="44" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="64" t="n">
         <v>24</v>
       </c>
-      <c r="B59" s="88" t="inlineStr">
+      <c r="B64" s="49" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C59" s="88" t="inlineStr">
+      <c r="C64" s="49" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D59" s="88" t="inlineStr">
+      <c r="D64" s="49" t="inlineStr">
         <is>
           <t>Зачистка стен/потолка (обои, плитка в зале и спальне), вынос мусора, 1-й слой грунта</t>
         </is>
       </c>
-      <c r="E59" s="91" t="inlineStr">
+      <c r="E64" s="49" t="inlineStr">
         <is>
           <t>ДЕМОНТАЖ-ЗАЧИСТКА-2</t>
         </is>
       </c>
-      <c r="F59" s="91" t="inlineStr">
+      <c r="F64" s="64" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="G59" s="255" t="n">
+      <c r="G64" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H59" s="89" t="n">
+      <c r="H64" s="172" t="n">
         <v>15000</v>
       </c>
-      <c r="I59" s="90">
-        <f>G59*H59</f>
-        <v/>
-      </c>
-      <c r="J59" s="88" t="inlineStr">
+      <c r="I64" s="172">
+        <f>G64*H64</f>
+        <v/>
+      </c>
+      <c r="J64" s="49" t="inlineStr">
         <is>
           <t>Бригада разнорабочих</t>
         </is>
       </c>
-      <c r="K59" s="256">
+      <c r="K64" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=зачистка+стен+демонтаж+обоев", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L59" s="82" t="inlineStr">
-        <is>
-          <t>Штукатурка 69 м² + шпаклёвка стен 106 м² по 500₽. White Box под ключ</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="86" t="n">
+      <c r="L64" s="49" t="inlineStr"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="62" t="n">
         <v>40</v>
       </c>
-      <c r="B60" s="82" t="inlineStr">
+      <c r="B65" s="44" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="C60" s="82" t="inlineStr">
+      <c r="C65" s="44" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
-      <c r="D60" s="82" t="inlineStr">
+      <c r="D65" s="44" t="inlineStr">
         <is>
           <t>Грузовое такси / Доставка закупки материалов и сантехники (Лемана — Фрунзе 17)</t>
         </is>
       </c>
-      <c r="E60" s="86" t="inlineStr">
+      <c r="E65" s="44" t="inlineStr">
         <is>
           <t>ГРУЗОТАКСИ-ЛЕРОЙ</t>
         </is>
       </c>
-      <c r="F60" s="86" t="inlineStr">
+      <c r="F65" s="62" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G60" s="253" t="n">
+      <c r="G65" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H60" s="83" t="n">
+      <c r="H65" s="173" t="n">
         <v>2100</v>
       </c>
-      <c r="I60" s="84">
-        <f>G60*H60</f>
-        <v/>
-      </c>
-      <c r="J60" s="82" t="inlineStr">
+      <c r="I65" s="173">
+        <f>G65*H65</f>
+        <v/>
+      </c>
+      <c r="J65" s="44" t="inlineStr">
         <is>
           <t>Грузовое такси / Перевозка</t>
         </is>
       </c>
-      <c r="K60" s="254">
+      <c r="K65" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=грузоперевозки+грузовое+такси", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L60" s="88" t="inlineStr">
-        <is>
-          <t>Демонтаж старого змеевика, нарезка 2 резьб клуппом под установку запорных кранов</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="91" t="n">
+      <c r="L65" s="44" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="64" t="n">
         <v>41</v>
       </c>
-      <c r="B61" s="88" t="inlineStr">
+      <c r="B66" s="49" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="C61" s="88" t="inlineStr">
+      <c r="C66" s="49" t="inlineStr">
         <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="D61" s="88" t="inlineStr">
+      <c r="D66" s="49" t="inlineStr">
         <is>
           <t>Погрузка в Лемана ПРО, разгрузка и подъём на 5 этаж + демонтаж плитки пола с/у</t>
         </is>
       </c>
-      <c r="E61" s="91" t="inlineStr">
+      <c r="E66" s="49" t="inlineStr">
         <is>
           <t>ПОДЪЕМ-ДЕМОНТАЖ-СУ</t>
         </is>
       </c>
-      <c r="F61" s="91" t="inlineStr">
+      <c r="F66" s="64" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="G61" s="255" t="n">
+      <c r="G66" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H61" s="89" t="n">
+      <c r="H66" s="172" t="n">
         <v>15000</v>
       </c>
-      <c r="I61" s="90">
-        <f>G61*H61</f>
-        <v/>
-      </c>
-      <c r="J61" s="88" t="inlineStr">
+      <c r="I66" s="172">
+        <f>G66*H66</f>
+        <v/>
+      </c>
+      <c r="J66" s="49" t="inlineStr">
         <is>
           <t>Бригада грузчиков / Разнорабочие</t>
         </is>
       </c>
-      <c r="K61" s="256">
+      <c r="K66" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=подъем+стройматериалов+на+этаж+грузчики", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L61" s="82" t="inlineStr">
-        <is>
-          <t>Оперативный подвоз купленного инструмента и материалов из Лемана ПРО на ул. Фрунзе 17</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="86" t="n">
+      <c r="L66" s="49" t="inlineStr"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="62" t="n">
         <v>42</v>
       </c>
-      <c r="B62" s="82" t="inlineStr">
+      <c r="B67" s="44" t="inlineStr">
         <is>
           <t>Черновые стены</t>
         </is>
       </c>
-      <c r="C62" s="82" t="inlineStr">
+      <c r="C67" s="44" t="inlineStr">
         <is>
           <t>Отделочные работы</t>
         </is>
       </c>
-      <c r="D62" s="82" t="inlineStr">
+      <c r="D67" s="44" t="inlineStr">
         <is>
           <t>Штукатурка (69 м² по 500 ₽) и шпаклёвка стен White Box (106 м² по 500 ₽)</t>
         </is>
       </c>
-      <c r="E62" s="86" t="inlineStr">
+      <c r="E67" s="44" t="inlineStr">
         <is>
           <t>ОТДЕЛКА-СТЕН-ЕЛЕНА</t>
         </is>
       </c>
-      <c r="F62" s="86" t="inlineStr">
+      <c r="F67" s="62" t="inlineStr">
         <is>
           <t>комплекс</t>
         </is>
       </c>
-      <c r="G62" s="253" t="n">
+      <c r="G67" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H62" s="83" t="n">
+      <c r="H67" s="173" t="n">
         <v>87500</v>
       </c>
-      <c r="I62" s="84">
-        <f>G62*H62</f>
-        <v/>
-      </c>
-      <c r="J62" s="82" t="inlineStr">
+      <c r="I67" s="173">
+        <f>G67*H67</f>
+        <v/>
+      </c>
+      <c r="J67" s="44" t="inlineStr">
         <is>
           <t>Елена (мастер-отделочник)</t>
         </is>
       </c>
-      <c r="K62" s="254">
+      <c r="K67" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=штукатурка+шпаклевка+стен", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L62" s="88" t="inlineStr">
-        <is>
-          <t>Оперативный подвоз материалов и крепежа</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="91" t="n">
+      <c r="L67" s="44" t="inlineStr"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="64" t="n">
         <v>48</v>
       </c>
-      <c r="B63" s="88" t="inlineStr">
+      <c r="B68" s="49" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C63" s="88" t="inlineStr">
+      <c r="C68" s="49" t="inlineStr">
         <is>
           <t>Сантехника / Работы</t>
         </is>
       </c>
-      <c r="D63" s="88" t="inlineStr">
+      <c r="D68" s="49" t="inlineStr">
         <is>
           <t>Срезка полотенцесушителя и нарезка трубной резьбы на отводах стояка</t>
         </is>
       </c>
-      <c r="E63" s="91" t="inlineStr">
+      <c r="E68" s="49" t="inlineStr">
         <is>
           <t>РАБОТА-САНТЕХ-СУШ</t>
         </is>
       </c>
-      <c r="F63" s="91" t="inlineStr">
+      <c r="F68" s="64" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G63" s="255" t="n">
+      <c r="G68" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H63" s="89" t="n">
+      <c r="H68" s="172" t="n">
         <v>3000</v>
       </c>
-      <c r="I63" s="90">
-        <f>G63*H63</f>
-        <v/>
-      </c>
-      <c r="J63" s="88" t="inlineStr">
+      <c r="I68" s="172">
+        <f>G68*H68</f>
+        <v/>
+      </c>
+      <c r="J68" s="49" t="inlineStr">
         <is>
           <t>Вадим (сантехник УК) / Сантехник</t>
         </is>
       </c>
-      <c r="K63" s="256">
+      <c r="K68" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=сантехник+срезка+полотенцесушителя", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L63" s="82" t="inlineStr">
-        <is>
-          <t>Подготовка и аванс плиточнику за работы в с/у</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="86" t="n">
+      <c r="L68" s="49" t="inlineStr"/>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="62" t="n">
         <v>49</v>
       </c>
-      <c r="B64" s="82" t="inlineStr">
+      <c r="B69" s="44" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="C64" s="82" t="inlineStr">
+      <c r="C69" s="44" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
-      <c r="D64" s="82" t="inlineStr">
+      <c r="D69" s="44" t="inlineStr">
         <is>
           <t>Такси (оперативная доставка материалов и инструмента из Лемана ПРО на объект)</t>
         </is>
       </c>
-      <c r="E64" s="86" t="inlineStr">
+      <c r="E69" s="44" t="inlineStr">
         <is>
           <t>ТАКСИ-ЛЕРОЙ-ОБЪЕКТ</t>
         </is>
       </c>
-      <c r="F64" s="86" t="inlineStr">
+      <c r="F69" s="62" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G64" s="253" t="n">
+      <c r="G69" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H64" s="83" t="n">
+      <c r="H69" s="173" t="n">
         <v>1000</v>
       </c>
-      <c r="I64" s="84">
-        <f>G64*H64</f>
-        <v/>
-      </c>
-      <c r="J64" s="82" t="inlineStr">
+      <c r="I69" s="173">
+        <f>G69*H69</f>
+        <v/>
+      </c>
+      <c r="J69" s="44" t="inlineStr">
         <is>
           <t>Такси (Яндекс Go)</t>
         </is>
       </c>
-      <c r="K64" s="254">
+      <c r="K69" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=такси+доставка+курьер", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L64" s="88" t="inlineStr">
-        <is>
-          <t>Заливка прочной стяжки пола с/у по маякам с ускорителем Cemfix</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="91" t="n">
+      <c r="L69" s="44" t="inlineStr"/>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="64" t="n">
         <v>60</v>
       </c>
-      <c r="B65" s="88" t="inlineStr">
+      <c r="B70" s="49" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="C65" s="88" t="inlineStr">
+      <c r="C70" s="49" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
-      <c r="D65" s="88" t="inlineStr">
+      <c r="D70" s="49" t="inlineStr">
         <is>
           <t>Такси (оперативная доставка / подвоз материалов на объект)</t>
         </is>
       </c>
-      <c r="E65" s="91" t="inlineStr">
+      <c r="E70" s="49" t="inlineStr">
         <is>
           <t>ТАКСИ-ДОСТАВКА-2</t>
         </is>
       </c>
-      <c r="F65" s="91" t="inlineStr">
+      <c r="F70" s="64" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="G65" s="255" t="n">
+      <c r="G70" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H65" s="89" t="n">
+      <c r="H70" s="172" t="n">
         <v>850</v>
       </c>
-      <c r="I65" s="90">
-        <f>G65*H65</f>
-        <v/>
-      </c>
-      <c r="J65" s="88" t="inlineStr">
+      <c r="I70" s="172">
+        <f>G70*H70</f>
+        <v/>
+      </c>
+      <c r="J70" s="49" t="inlineStr">
         <is>
           <t>Такси (Яндекс Go)</t>
         </is>
       </c>
-      <c r="K65" s="256">
+      <c r="K70" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=такси+доставка+курьер", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L65" s="82" t="inlineStr">
-        <is>
-          <t>Штукатурка стен с/у по маякам с идеальной геометрией 90° под ванну 150см</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="86" t="n">
+      <c r="L70" s="49" t="inlineStr"/>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="62" t="n">
         <v>61</v>
       </c>
-      <c r="B66" s="82" t="inlineStr">
+      <c r="B71" s="44" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C66" s="82" t="inlineStr">
+      <c r="C71" s="44" t="inlineStr">
         <is>
           <t>Плиточные работы</t>
         </is>
       </c>
-      <c r="D66" s="82" t="inlineStr">
+      <c r="D71" s="44" t="inlineStr">
         <is>
           <t>Работы плиточника (аванс / подготовка к укладке плитки в санузле)</t>
         </is>
       </c>
-      <c r="E66" s="86" t="inlineStr">
+      <c r="E71" s="44" t="inlineStr">
         <is>
           <t>РАБОТА-ПЛИТОЧНИК-1</t>
         </is>
       </c>
-      <c r="F66" s="86" t="inlineStr">
+      <c r="F71" s="62" t="inlineStr">
         <is>
           <t>аванс</t>
         </is>
       </c>
-      <c r="G66" s="253" t="n">
+      <c r="G71" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H66" s="83" t="n">
+      <c r="H71" s="173" t="n">
         <v>1700</v>
       </c>
-      <c r="I66" s="84">
-        <f>G66*H66</f>
-        <v/>
-      </c>
-      <c r="J66" s="82" t="inlineStr">
+      <c r="I71" s="173">
+        <f>G71*H71</f>
+        <v/>
+      </c>
+      <c r="J71" s="44" t="inlineStr">
         <is>
           <t>Плиточник (мастер)</t>
         </is>
       </c>
-      <c r="K66" s="254">
+      <c r="K71" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=плиточник+укладка+плитки", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L66" s="246" t="n"/>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="91" t="n">
+      <c r="L71" s="44" t="inlineStr"/>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="64" t="n">
         <v>62</v>
       </c>
-      <c r="B67" s="88" t="inlineStr">
+      <c r="B72" s="49" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C67" s="88" t="inlineStr">
+      <c r="C72" s="49" t="inlineStr">
         <is>
           <t>Стяжка пола</t>
         </is>
       </c>
-      <c r="D67" s="88" t="inlineStr">
+      <c r="D72" s="49" t="inlineStr">
         <is>
           <t>Работы плиточника: заливка стяжки пола в санузле/туалете</t>
         </is>
       </c>
-      <c r="E67" s="91" t="inlineStr">
+      <c r="E72" s="49" t="inlineStr">
         <is>
           <t>СТЯЖКА-ПОЛА-СУ</t>
         </is>
       </c>
-      <c r="F67" s="91" t="inlineStr">
+      <c r="F72" s="64" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G67" s="255" t="n">
+      <c r="G72" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H67" s="89" t="n">
+      <c r="H72" s="172" t="n">
         <v>3300</v>
       </c>
-      <c r="I67" s="90">
-        <f>G67*H67</f>
-        <v/>
-      </c>
-      <c r="J67" s="88" t="inlineStr">
+      <c r="I72" s="172">
+        <f>G72*H72</f>
+        <v/>
+      </c>
+      <c r="J72" s="49" t="inlineStr">
         <is>
           <t>Плиточник (мастер)</t>
         </is>
       </c>
-      <c r="K67" s="256">
+      <c r="K72" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=стяжка+пола+санузел", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L67" s="251" t="n"/>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="86" t="n">
+      <c r="L72" s="49" t="inlineStr"/>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="62" t="n">
         <v>63</v>
       </c>
-      <c r="B68" s="82" t="inlineStr">
+      <c r="B73" s="44" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C68" s="82" t="inlineStr">
+      <c r="C73" s="44" t="inlineStr">
         <is>
           <t>Штукатурка стен</t>
         </is>
       </c>
-      <c r="D68" s="82" t="inlineStr">
+      <c r="D73" s="44" t="inlineStr">
         <is>
           <t>Оплата за штукатурку туалета (санузла) под 90° под ванну и плитку</t>
         </is>
       </c>
-      <c r="E68" s="86" t="inlineStr">
+      <c r="E73" s="44" t="inlineStr">
         <is>
           <t>ШТУКАТУРКА-СУ-90</t>
         </is>
       </c>
-      <c r="F68" s="86" t="inlineStr">
+      <c r="F73" s="62" t="inlineStr">
         <is>
           <t>комплекс</t>
         </is>
       </c>
-      <c r="G68" s="253" t="n">
+      <c r="G73" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H68" s="83" t="n">
+      <c r="H73" s="173" t="n">
         <v>13400</v>
       </c>
-      <c r="I68" s="84">
-        <f>G68*H68</f>
-        <v/>
-      </c>
-      <c r="J68" s="82" t="inlineStr">
+      <c r="I73" s="173">
+        <f>G73*H73</f>
+        <v/>
+      </c>
+      <c r="J73" s="44" t="inlineStr">
         <is>
           <t>Елена (мастер-отделочник)</t>
         </is>
       </c>
-      <c r="K68" s="254">
+      <c r="K73" s="174">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=штукатурка+санузла+под+90", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L68" s="88" t="inlineStr">
-        <is>
-          <t>ЭЦП для участия в торгах и регистрации права</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="91" t="n">
+      <c r="L73" s="44" t="inlineStr"/>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="64" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="88" t="inlineStr">
+      <c r="B74" s="49" t="inlineStr">
         <is>
           <t>Санузел</t>
         </is>
       </c>
-      <c r="C69" s="88" t="inlineStr">
+      <c r="C74" s="49" t="inlineStr">
         <is>
           <t>Сантехнические работы</t>
         </is>
       </c>
-      <c r="D69" s="88" t="inlineStr">
+      <c r="D74" s="49" t="inlineStr">
         <is>
           <t>Работы сантехников (разводка/монтаж узлов водоснабжения и канализации)</t>
         </is>
       </c>
-      <c r="E69" s="91" t="inlineStr">
+      <c r="E74" s="49" t="inlineStr">
         <is>
           <t>РАБОТА-САНТЕХ-РАЗВОДКА</t>
         </is>
       </c>
-      <c r="F69" s="91" t="inlineStr">
+      <c r="F74" s="64" t="inlineStr">
         <is>
           <t>комплекс</t>
         </is>
       </c>
-      <c r="G69" s="255" t="n">
+      <c r="G74" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H69" s="89" t="n">
+      <c r="H74" s="172" t="n">
         <v>3000</v>
       </c>
-      <c r="I69" s="90">
-        <f>G69*H69</f>
-        <v/>
-      </c>
-      <c r="J69" s="88" t="inlineStr">
+      <c r="I74" s="172">
+        <f>G74*H74</f>
+        <v/>
+      </c>
+      <c r="J74" s="49" t="inlineStr">
         <is>
           <t>Сантехники (мастера)</t>
         </is>
       </c>
-      <c r="K69" s="256">
+      <c r="K74" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=разводка+труб+сантехника", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L69" s="82" t="inlineStr">
-        <is>
-          <t>Официальная пошлина Росреестра</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="257" t="n"/>
-      <c r="B70" s="258" t="inlineStr">
+      <c r="L74" s="49" t="inlineStr"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="62" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="44" t="inlineStr">
+        <is>
+          <t>Логистика</t>
+        </is>
+      </c>
+      <c r="C75" s="44" t="inlineStr">
+        <is>
+          <t>Доставка</t>
+        </is>
+      </c>
+      <c r="D75" s="44" t="inlineStr">
+        <is>
+          <t>Такси (оперативная доставка / подвоз материалов на объект ул. Фрунзе 17)</t>
+        </is>
+      </c>
+      <c r="E75" s="44" t="inlineStr">
+        <is>
+          <t>ТАКСИ-ОБЪЕКТ-3</t>
+        </is>
+      </c>
+      <c r="F75" s="62" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="G75" s="327" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="173" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I75" s="173">
+        <f>G75*H75</f>
+        <v/>
+      </c>
+      <c r="J75" s="44" t="inlineStr">
+        <is>
+          <t>Такси</t>
+        </is>
+      </c>
+      <c r="K75" s="174">
+        <f>HYPERLINK("https://taxi.yandex.ru/", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L75" s="44" t="inlineStr"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="64" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="49" t="inlineStr">
+        <is>
+          <t>Санузел / Кухня</t>
+        </is>
+      </c>
+      <c r="C76" s="49" t="inlineStr">
+        <is>
+          <t>Плиточные работы</t>
+        </is>
+      </c>
+      <c r="D76" s="49" t="inlineStr">
+        <is>
+          <t>Работы плиточника: укладка плитки в санузле, фартук на кухне, фартук ванной из плитки, лючки на магнитах, отверстия под розетки</t>
+        </is>
+      </c>
+      <c r="E76" s="49" t="inlineStr">
+        <is>
+          <t>РАБОТА-ПЛИТОЧНИК-ФИНАЛ</t>
+        </is>
+      </c>
+      <c r="F76" s="64" t="inlineStr">
+        <is>
+          <t>комплекс</t>
+        </is>
+      </c>
+      <c r="G76" s="326" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="172" t="n">
+        <v>86000</v>
+      </c>
+      <c r="I76" s="172">
+        <f>G76*H76</f>
+        <v/>
+      </c>
+      <c r="J76" s="49" t="inlineStr">
+        <is>
+          <t>Плиточник (мастер)</t>
+        </is>
+      </c>
+      <c r="K76" s="175">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=укладка+плитки+санузел", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L76" s="49" t="inlineStr"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="62" t="n">
+        <v>78</v>
+      </c>
+      <c r="B77" s="44" t="inlineStr">
+        <is>
+          <t>Логистика</t>
+        </is>
+      </c>
+      <c r="C77" s="44" t="inlineStr">
+        <is>
+          <t>Доставка</t>
+        </is>
+      </c>
+      <c r="D77" s="44" t="inlineStr">
+        <is>
+          <t>Такси (оперативная поездка по объекту)</t>
+        </is>
+      </c>
+      <c r="E77" s="44" t="inlineStr">
+        <is>
+          <t>ТАКСИ-ОБЪЕКТ-4</t>
+        </is>
+      </c>
+      <c r="F77" s="62" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="G77" s="327" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="173" t="n">
+        <v>700</v>
+      </c>
+      <c r="I77" s="173">
+        <f>G77*H77</f>
+        <v/>
+      </c>
+      <c r="J77" s="44" t="inlineStr">
+        <is>
+          <t>Такси</t>
+        </is>
+      </c>
+      <c r="K77" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=такси", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L77" s="44" t="inlineStr"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="322" t="n"/>
+      <c r="B78" s="328" t="inlineStr">
         <is>
           <t>ИТОГО РАБОТЫ И ЛОГИСТИКА:</t>
         </is>
       </c>
-      <c r="C70" s="259" t="n"/>
-      <c r="D70" s="259" t="n"/>
-      <c r="E70" s="257" t="n"/>
-      <c r="F70" s="257" t="n"/>
-      <c r="G70" s="260" t="n"/>
-      <c r="H70" s="261" t="n"/>
-      <c r="I70" s="261">
-        <f>SUM(I53:I69)</f>
-        <v/>
-      </c>
-      <c r="J70" s="259" t="n"/>
-      <c r="K70" s="257" t="n"/>
-      <c r="L70" s="88" t="inlineStr">
-        <is>
-          <t>Инфраструктура проектов и аналитика</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="276" t="n"/>
-      <c r="B71" s="277" t="inlineStr">
-        <is>
-          <t>🏛 БЛОК 4: ЮРИДИЧЕСКИЕ РАСХОДЫ, ПОШЛИНЫ, ГАЗ, ЭНЕРГОСБЫТ И IT (9 ПОЗИЦИЙ)</t>
-        </is>
-      </c>
-      <c r="C71" s="278" t="n"/>
-      <c r="D71" s="278" t="n"/>
-      <c r="E71" s="276" t="n"/>
-      <c r="F71" s="276" t="n"/>
-      <c r="G71" s="279" t="n"/>
-      <c r="H71" s="280" t="n"/>
-      <c r="I71" s="281" t="n"/>
-      <c r="J71" s="278" t="n"/>
-      <c r="K71" s="282" t="n"/>
-      <c r="L71" s="82" t="inlineStr">
-        <is>
-          <t>Обязательная проверка тяги для газовой колонки</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="86" t="n">
+      <c r="C78" s="322" t="n"/>
+      <c r="D78" s="322" t="n"/>
+      <c r="E78" s="322" t="n"/>
+      <c r="F78" s="322" t="n"/>
+      <c r="G78" s="333" t="n"/>
+      <c r="H78" s="334" t="n"/>
+      <c r="I78" s="331">
+        <f>SUM(I58:I77)</f>
+        <v/>
+      </c>
+      <c r="J78" s="322" t="n"/>
+      <c r="K78" s="322" t="n"/>
+      <c r="L78" s="322" t="n"/>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="322" t="n"/>
+      <c r="B79" s="336" t="inlineStr">
+        <is>
+          <t>🏛 БЛОК 4: ЮРИДИЧЕСКИЕ РАСХОДЫ, ПОШЛИНЫ, ГАЗ, ЭНЕРГОСБЫТ И IT (10 ПОЗИЦИЙ)</t>
+        </is>
+      </c>
+      <c r="C79" s="322" t="n"/>
+      <c r="D79" s="322" t="n"/>
+      <c r="E79" s="322" t="n"/>
+      <c r="F79" s="322" t="n"/>
+      <c r="G79" s="333" t="n"/>
+      <c r="H79" s="334" t="n"/>
+      <c r="I79" s="334" t="n"/>
+      <c r="J79" s="322" t="n"/>
+      <c r="K79" s="322" t="n"/>
+      <c r="L79" s="322" t="n"/>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="B72" s="82" t="inlineStr">
+      <c r="B80" s="49" t="inlineStr">
         <is>
           <t>Юр. оформление</t>
         </is>
       </c>
-      <c r="C72" s="82" t="inlineStr">
+      <c r="C80" s="49" t="inlineStr">
         <is>
           <t>Торги</t>
         </is>
       </c>
-      <c r="D72" s="82" t="inlineStr">
+      <c r="D80" s="49" t="inlineStr">
         <is>
           <t>Выпуск квалифицированной ЭЦП (электронная цифровая подпись)</t>
         </is>
       </c>
-      <c r="E72" s="86" t="inlineStr">
+      <c r="E80" s="49" t="inlineStr">
         <is>
           <t>ЭЦП-КОНТУР</t>
         </is>
       </c>
-      <c r="F72" s="86" t="inlineStr">
+      <c r="F80" s="64" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="G72" s="253" t="n">
+      <c r="G80" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H72" s="83" t="n">
+      <c r="H80" s="172" t="n">
         <v>7000</v>
       </c>
-      <c r="I72" s="84">
-        <f>G72*H72</f>
-        <v/>
-      </c>
-      <c r="J72" s="82" t="inlineStr">
+      <c r="I80" s="172">
+        <f>G80*H80</f>
+        <v/>
+      </c>
+      <c r="J80" s="49" t="inlineStr">
         <is>
           <t>УЦ / Контур</t>
         </is>
       </c>
-      <c r="K72" s="254">
+      <c r="K80" s="175">
         <f>HYPERLINK("https://ca.kontur.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L72" s="88" t="inlineStr">
-        <is>
-          <t>Погашение начислений газовой службы</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="91" t="n">
+      <c r="L80" s="49" t="inlineStr"/>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="B73" s="88" t="inlineStr">
+      <c r="B81" s="44" t="inlineStr">
         <is>
           <t>Юр. оформление</t>
         </is>
       </c>
-      <c r="C73" s="88" t="inlineStr">
+      <c r="C81" s="44" t="inlineStr">
         <is>
           <t>Росреестр</t>
         </is>
       </c>
-      <c r="D73" s="88" t="inlineStr">
+      <c r="D81" s="44" t="inlineStr">
         <is>
           <t>Государственная пошлина (регистрация перехода права собственности)</t>
         </is>
       </c>
-      <c r="E73" s="91" t="inlineStr">
+      <c r="E81" s="44" t="inlineStr">
         <is>
           <t>ГОСПОШЛИНА-ПРАВО</t>
         </is>
       </c>
-      <c r="F73" s="91" t="inlineStr">
+      <c r="F81" s="62" t="inlineStr">
         <is>
           <t>платеж</t>
         </is>
       </c>
-      <c r="G73" s="255" t="n">
+      <c r="G81" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H73" s="89" t="n">
+      <c r="H81" s="173" t="n">
         <v>5000</v>
       </c>
-      <c r="I73" s="90">
-        <f>G73*H73</f>
-        <v/>
-      </c>
-      <c r="J73" s="88" t="inlineStr">
+      <c r="I81" s="173">
+        <f>G81*H81</f>
+        <v/>
+      </c>
+      <c r="J81" s="44" t="inlineStr">
         <is>
           <t>Росреестр</t>
         </is>
       </c>
-      <c r="K73" s="256">
+      <c r="K81" s="174">
         <f>HYPERLINK("https://rosreestr.gov.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L73" s="82" t="inlineStr">
-        <is>
-          <t>Срочное снятие пломбы за 5 дней</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="86" t="n">
+      <c r="L81" s="44" t="inlineStr"/>
+    </row>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="64" t="n">
         <v>10</v>
       </c>
-      <c r="B74" s="82" t="inlineStr">
+      <c r="B82" s="49" t="inlineStr">
         <is>
           <t>IT / AI</t>
         </is>
       </c>
-      <c r="C74" s="82" t="inlineStr">
+      <c r="C82" s="49" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="D74" s="82" t="inlineStr">
+      <c r="D82" s="49" t="inlineStr">
         <is>
           <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 1</t>
         </is>
       </c>
-      <c r="E74" s="86" t="inlineStr">
+      <c r="E82" s="49" t="inlineStr">
         <is>
           <t>OPENROUTER-TRANS-1</t>
         </is>
       </c>
-      <c r="F74" s="86" t="inlineStr">
+      <c r="F82" s="64" t="inlineStr">
         <is>
           <t>платёж</t>
         </is>
       </c>
-      <c r="G74" s="253" t="n">
+      <c r="G82" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="83" t="n">
+      <c r="H82" s="172" t="n">
         <v>3000</v>
       </c>
-      <c r="I74" s="84">
-        <f>G74*H74</f>
-        <v/>
-      </c>
-      <c r="J74" s="82" t="inlineStr">
+      <c r="I82" s="172">
+        <f>G82*H82</f>
+        <v/>
+      </c>
+      <c r="J82" s="49" t="inlineStr">
         <is>
           <t>OpenRouter</t>
         </is>
       </c>
-      <c r="K74" s="254">
+      <c r="K82" s="175">
         <f>HYPERLINK("https://openrouter.ai/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L74" s="88" t="inlineStr">
-        <is>
-          <t>Пополнение баланса API для расчётов и смет</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="91" t="n">
+      <c r="L82" s="49" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="B75" s="88" t="inlineStr">
+      <c r="B83" s="44" t="inlineStr">
         <is>
           <t>Газ</t>
         </is>
       </c>
-      <c r="C75" s="88" t="inlineStr">
+      <c r="C83" s="44" t="inlineStr">
         <is>
           <t>Безопасность</t>
         </is>
       </c>
-      <c r="D75" s="88" t="inlineStr">
+      <c r="D83" s="44" t="inlineStr">
         <is>
           <t>Акт ВДПО — проверка дымохода и вентканала</t>
         </is>
       </c>
-      <c r="E75" s="91" t="inlineStr">
+      <c r="E83" s="44" t="inlineStr">
         <is>
           <t>ВДПО-АКТ-ВЕНТ</t>
         </is>
       </c>
-      <c r="F75" s="91" t="inlineStr">
+      <c r="F83" s="62" t="inlineStr">
         <is>
           <t>акт</t>
         </is>
       </c>
-      <c r="G75" s="255" t="n">
+      <c r="G83" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="89" t="n">
+      <c r="H83" s="173" t="n">
         <v>1500</v>
       </c>
-      <c r="I75" s="90">
-        <f>G75*H75</f>
-        <v/>
-      </c>
-      <c r="J75" s="88" t="inlineStr">
+      <c r="I83" s="173">
+        <f>G83*H83</f>
+        <v/>
+      </c>
+      <c r="J83" s="44" t="inlineStr">
         <is>
           <t>ВДПО / Газовая служба</t>
         </is>
       </c>
-      <c r="K75" s="256">
+      <c r="K83" s="174">
         <f>HYPERLINK("https://vdpo71.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L75" s="82" t="inlineStr">
-        <is>
-          <t>Фиксация показаний и снятие пломбы без выезда</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="86" t="n">
+      <c r="L83" s="44" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="64" t="n">
         <v>13</v>
       </c>
-      <c r="B76" s="82" t="inlineStr">
+      <c r="B84" s="49" t="inlineStr">
         <is>
           <t>Газ</t>
         </is>
       </c>
-      <c r="C76" s="82" t="inlineStr">
+      <c r="C84" s="49" t="inlineStr">
         <is>
           <t>Коммуналка</t>
         </is>
       </c>
-      <c r="D76" s="82" t="inlineStr">
+      <c r="D84" s="49" t="inlineStr">
         <is>
           <t>Оплата квитанций Тулагоргаз (платежки/техобслуживание)</t>
         </is>
       </c>
-      <c r="E76" s="86" t="inlineStr">
+      <c r="E84" s="49" t="inlineStr">
         <is>
           <t>ТУЛАГОРГАЗ-КВИТАНЦИЯ</t>
         </is>
       </c>
-      <c r="F76" s="86" t="inlineStr">
+      <c r="F84" s="64" t="inlineStr">
         <is>
           <t>платеж</t>
         </is>
       </c>
-      <c r="G76" s="253" t="n">
+      <c r="G84" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H76" s="83" t="n">
+      <c r="H84" s="172" t="n">
         <v>800</v>
       </c>
-      <c r="I76" s="84">
-        <f>G76*H76</f>
-        <v/>
-      </c>
-      <c r="J76" s="82" t="inlineStr">
+      <c r="I84" s="172">
+        <f>G84*H84</f>
+        <v/>
+      </c>
+      <c r="J84" s="49" t="inlineStr">
         <is>
           <t>Тулагоргаз</t>
         </is>
       </c>
-      <c r="K76" s="254">
+      <c r="K84" s="175">
         <f>HYPERLINK("https://tulagorgaz.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L76" s="246" t="n"/>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="91" t="n">
+      <c r="L84" s="49" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="62" t="n">
         <v>21</v>
       </c>
-      <c r="B77" s="88" t="inlineStr">
+      <c r="B85" s="44" t="inlineStr">
         <is>
           <t>Энергосбыт</t>
         </is>
       </c>
-      <c r="C77" s="88" t="inlineStr">
+      <c r="C85" s="44" t="inlineStr">
         <is>
           <t>Учёт</t>
         </is>
       </c>
-      <c r="D77" s="88" t="inlineStr">
+      <c r="D85" s="44" t="inlineStr">
         <is>
           <t>Срочный выезд инспектора ТНС энерго Тула (снятие пломбы со старого счётчика)</t>
         </is>
       </c>
-      <c r="E77" s="91" t="inlineStr">
+      <c r="E85" s="44" t="inlineStr">
         <is>
           <t>ТНС-ВЫЕЗД-ПЛОМБА</t>
         </is>
       </c>
-      <c r="F77" s="91" t="inlineStr">
+      <c r="F85" s="62" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G77" s="255" t="n">
+      <c r="G85" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H77" s="89" t="n">
+      <c r="H85" s="173" t="n">
         <v>2500</v>
       </c>
-      <c r="I77" s="90">
-        <f>G77*H77</f>
-        <v/>
-      </c>
-      <c r="J77" s="88" t="inlineStr">
+      <c r="I85" s="173">
+        <f>G85*H85</f>
+        <v/>
+      </c>
+      <c r="J85" s="44" t="inlineStr">
         <is>
           <t>АО "ТНС энерго Тула"</t>
         </is>
       </c>
-      <c r="K77" s="256">
+      <c r="K85" s="174">
         <f>HYPERLINK("https://tns-e.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-      <c r="L77" s="238" t="n"/>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="86" t="n">
+      <c r="L85" s="44" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="64" t="n">
         <v>31</v>
       </c>
-      <c r="B78" s="82" t="inlineStr">
+      <c r="B86" s="49" t="inlineStr">
         <is>
           <t>IT / AI</t>
         </is>
       </c>
-      <c r="C78" s="82" t="inlineStr">
+      <c r="C86" s="49" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="D78" s="82" t="inlineStr">
+      <c r="D86" s="49" t="inlineStr">
         <is>
           <t>Пополнение баланса OpenRouter (AI-ассистент Hermes) — транш 2</t>
         </is>
       </c>
-      <c r="E78" s="86" t="inlineStr">
+      <c r="E86" s="49" t="inlineStr">
         <is>
           <t>OPENROUTER-TRANS-2</t>
         </is>
       </c>
-      <c r="F78" s="86" t="inlineStr">
+      <c r="F86" s="64" t="inlineStr">
         <is>
           <t>платёж</t>
         </is>
       </c>
-      <c r="G78" s="253" t="n">
+      <c r="G86" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H78" s="83" t="n">
+      <c r="H86" s="172" t="n">
         <v>2500</v>
       </c>
-      <c r="I78" s="84">
-        <f>G78*H78</f>
-        <v/>
-      </c>
-      <c r="J78" s="82" t="inlineStr">
+      <c r="I86" s="172">
+        <f>G86*H86</f>
+        <v/>
+      </c>
+      <c r="J86" s="49" t="inlineStr">
         <is>
           <t>OpenRouter</t>
         </is>
       </c>
-      <c r="K78" s="254">
+      <c r="K86" s="175">
         <f>HYPERLINK("https://openrouter.ai/", "Открыть ↗")</f>
         <v/>
       </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="91" t="n">
+      <c r="L86" s="49" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="62" t="n">
         <v>33</v>
       </c>
-      <c r="B79" s="88" t="inlineStr">
+      <c r="B87" s="44" t="inlineStr">
         <is>
           <t>Энергосбыт</t>
         </is>
       </c>
-      <c r="C79" s="88" t="inlineStr">
+      <c r="C87" s="44" t="inlineStr">
         <is>
           <t>Учёт</t>
         </is>
       </c>
-      <c r="D79" s="88" t="inlineStr">
+      <c r="D87" s="44" t="inlineStr">
         <is>
           <t>Дистанционная распломбировка старого электросчётчика (согласование)</t>
         </is>
       </c>
-      <c r="E79" s="91" t="inlineStr">
+      <c r="E87" s="44" t="inlineStr">
         <is>
           <t>ТНС-РАСПЛОМБ-ДИСТ</t>
         </is>
       </c>
-      <c r="F79" s="91" t="inlineStr">
+      <c r="F87" s="62" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="G79" s="255" t="n">
+      <c r="G87" s="327" t="n">
         <v>1</v>
       </c>
-      <c r="H79" s="89" t="n">
+      <c r="H87" s="173" t="n">
         <v>2200</v>
       </c>
-      <c r="I79" s="90">
-        <f>G79*H79</f>
-        <v/>
-      </c>
-      <c r="J79" s="88" t="inlineStr">
+      <c r="I87" s="173">
+        <f>G87*H87</f>
+        <v/>
+      </c>
+      <c r="J87" s="44" t="inlineStr">
         <is>
           <t>ТНС энерго Тула / Энергосбыт</t>
         </is>
       </c>
-      <c r="K79" s="256">
+      <c r="K87" s="174">
         <f>HYPERLINK("https://tns-e.ru/", "Открыть ↗")</f>
         <v/>
       </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="86" t="n">
+      <c r="L87" s="44" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="64" t="n">
         <v>69</v>
       </c>
-      <c r="B80" s="82" t="inlineStr">
+      <c r="B88" s="49" t="inlineStr">
         <is>
           <t>Газ</t>
         </is>
       </c>
-      <c r="C80" s="82" t="inlineStr">
+      <c r="C88" s="49" t="inlineStr">
         <is>
           <t>Работы и материалы</t>
         </is>
       </c>
-      <c r="D80" s="82" t="inlineStr">
+      <c r="D88" s="49" t="inlineStr">
         <is>
           <t>Работы газовщика: перенос / срезка / перемонтаж газовой трубы на кухне</t>
         </is>
       </c>
-      <c r="E80" s="86" t="inlineStr">
+      <c r="E88" s="49" t="inlineStr">
         <is>
           <t>ГАЗ-ПЕРЕНОС-ТРУБА</t>
         </is>
       </c>
-      <c r="F80" s="86" t="inlineStr">
+      <c r="F88" s="64" t="inlineStr">
         <is>
           <t>комплекс</t>
         </is>
       </c>
-      <c r="G80" s="253" t="n">
+      <c r="G88" s="326" t="n">
         <v>1</v>
       </c>
-      <c r="H80" s="83" t="n">
+      <c r="H88" s="172" t="n">
         <v>7300</v>
       </c>
-      <c r="I80" s="84">
-        <f>G80*H80</f>
-        <v/>
-      </c>
-      <c r="J80" s="82" t="inlineStr">
+      <c r="I88" s="172">
+        <f>G88*H88</f>
+        <v/>
+      </c>
+      <c r="J88" s="49" t="inlineStr">
         <is>
           <t>Газовщик (мастер / горгаз)</t>
         </is>
       </c>
-      <c r="K80" s="254">
+      <c r="K88" s="175">
         <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=перенос+газовой+трубы", "Открыть ↗")</f>
         <v/>
       </c>
-    </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="283" t="n"/>
-      <c r="B81" s="258" t="inlineStr">
+      <c r="L88" s="49" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="62" t="n">
+        <v>72</v>
+      </c>
+      <c r="B89" s="44" t="inlineStr">
+        <is>
+          <t>Безопасность</t>
+        </is>
+      </c>
+      <c r="C89" s="44" t="inlineStr">
+        <is>
+          <t>Доступ</t>
+        </is>
+      </c>
+      <c r="D89" s="44" t="inlineStr">
+        <is>
+          <t>Ключи от домофона (дубликаты для мастеров и объекта)</t>
+        </is>
+      </c>
+      <c r="E89" s="44" t="inlineStr">
+        <is>
+          <t>КЛЮЧИ-ДОМОФОН-3</t>
+        </is>
+      </c>
+      <c r="F89" s="62" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G89" s="327" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="173" t="n">
+        <v>500</v>
+      </c>
+      <c r="I89" s="173">
+        <f>G89*H89</f>
+        <v/>
+      </c>
+      <c r="J89" s="44" t="inlineStr">
+        <is>
+          <t>Изготовление ключей</t>
+        </is>
+      </c>
+      <c r="K89" s="174">
+        <f>HYPERLINK("https://www.avito.ru/tula/predlozheniya_uslug?q=%D0%B8%D0%B7%D0%B3%D0%BE%D1%82%D0%BE%D0%B2%D0%BB%D0%B5%D0%BD%D0%B8%D0%B5+%D0%BA%D0%BB%D1%8E%D1%87%D0%B5%D0%B9+%D0%B4%D0%BE%D0%BC%D0%BE%D1%84%D0%BE%D0%BD", "Открыть ↗")</f>
+        <v/>
+      </c>
+      <c r="L89" s="44" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="328" t="inlineStr">
         <is>
           <t>ИТОГО ЮР. РАСХОДЫ, СЛУЖБЫ И IT:</t>
         </is>
       </c>
-      <c r="C81" s="283" t="n"/>
-      <c r="D81" s="283" t="n"/>
-      <c r="E81" s="283" t="n"/>
-      <c r="F81" s="283" t="n"/>
-      <c r="G81" s="283" t="n"/>
-      <c r="H81" s="283" t="n"/>
-      <c r="I81" s="261">
-        <f>SUM(I72:I80)</f>
-        <v/>
-      </c>
-      <c r="J81" s="283" t="n"/>
-      <c r="K81" s="283" t="n"/>
-    </row>
-    <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="238" t="n"/>
-      <c r="B82" s="239" t="inlineStr">
+      <c r="I90" s="331">
+        <f>SUM(I80:I89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="170" t="inlineStr">
         <is>
           <t>ОБЩИЙ ИТОГО ФАКТ РАСХОДОВ (ДИНАМИЧЕСКИЙ):</t>
         </is>
       </c>
-      <c r="C82" s="238" t="n"/>
-      <c r="D82" s="238" t="n"/>
-      <c r="E82" s="238" t="n"/>
-      <c r="F82" s="238" t="n"/>
-      <c r="G82" s="238" t="n"/>
-      <c r="H82" s="238" t="n"/>
-      <c r="I82" s="171">
-        <f>SUM(I32, I51, I70, I81)</f>
-        <v/>
-      </c>
-      <c r="J82" s="238" t="n"/>
-      <c r="K82" s="238" t="n"/>
+      <c r="I91" s="337">
+        <f>SUM(I33, I56, I78, I90)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
